--- a/Resultats_modeles_coleo_2024.xlsx
+++ b/Resultats_modeles_coleo_2024.xlsx
@@ -24,32 +24,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="68">
   <si>
     <t>ab.colsx</t>
   </si>
   <si>
-    <t>***</t>
-  </si>
-  <si>
-    <t>AC_UC</t>
-  </si>
-  <si>
-    <t>AC_LC</t>
-  </si>
-  <si>
-    <t>AC_BC</t>
-  </si>
-  <si>
-    <t>UC_LC</t>
-  </si>
-  <si>
-    <t>UC_BC</t>
-  </si>
-  <si>
-    <t>BC_LC</t>
-  </si>
-  <si>
     <t>toutes métriques fonistiques + toutes métriques d'habitats</t>
   </si>
   <si>
@@ -65,13 +44,376 @@
     <t>Y</t>
   </si>
   <si>
-    <t>P-value retenue</t>
-  </si>
-  <si>
-    <t>Résultat du modèle</t>
-  </si>
-  <si>
     <t>Ligne du code</t>
+  </si>
+  <si>
+    <t>1er modèle description</t>
+  </si>
+  <si>
+    <t>1er modèle P-value</t>
+  </si>
+  <si>
+    <t>2ème modèle description</t>
+  </si>
+  <si>
+    <t>2ème modèle P-value</t>
+  </si>
+  <si>
+    <t>ab.colsx ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>ab.colsx ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>infra : 2.22e-16 ***</t>
+  </si>
+  <si>
+    <t>infra inf : 0.03114087 *</t>
+  </si>
+  <si>
+    <t>infra supp : 1.9902e-08 ***</t>
+  </si>
+  <si>
+    <t>supra : 0.00074195 ***</t>
+  </si>
+  <si>
+    <t>AICc 1er modèle</t>
+  </si>
+  <si>
+    <t>AICc 2ème modèle</t>
+  </si>
+  <si>
+    <t>2.22e-16 ***</t>
+  </si>
+  <si>
+    <t>3.7801e-06 ***</t>
+  </si>
+  <si>
+    <t>Dharma</t>
+  </si>
+  <si>
+    <t>Pas de soucis avec les présupposés du modèle</t>
+  </si>
+  <si>
+    <t>AC_UC (0,05 / 6 = 0,008)</t>
+  </si>
+  <si>
+    <t>&lt; 0.001 ***</t>
+  </si>
+  <si>
+    <t>0.0040433 **</t>
+  </si>
+  <si>
+    <t>0.0031270 **</t>
+  </si>
+  <si>
+    <t>N.S</t>
+  </si>
+  <si>
+    <t>Conclusion</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On retrouve un effet de stratification verticale pour l'abondance cumulée totale des coléoptères saproxyliques, avec une différence d'abondance entre la strate </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supra &amp; infra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, ainsi qu'entre</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> infra.supp &amp; infra.inf, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">et </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>infra.supp &amp; infra</t>
+    </r>
+  </si>
+  <si>
+    <t>sr.colsx</t>
+  </si>
+  <si>
+    <t>Gaussian</t>
+  </si>
+  <si>
+    <t>sr.colsx ~ strate + (1 | LOCA / placette) + exp(pos+0|ID) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>infra inf : 0.41284</t>
+  </si>
+  <si>
+    <t>infra supp : 3.4678e-05 ***</t>
+  </si>
+  <si>
+    <t>supra :0.17427</t>
+  </si>
+  <si>
+    <t>sr.colsx ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>Modèle 1</t>
+  </si>
+  <si>
+    <t>Choix modèle mieux ajusté (delta &gt; 2)</t>
+  </si>
+  <si>
+    <t>0.0049384 **</t>
+  </si>
+  <si>
+    <t>0.0048236 **</t>
+  </si>
+  <si>
+    <t>N.S (0.0277350)</t>
+  </si>
+  <si>
+    <t>AC_LC (0,05 / 6 = 0,008)</t>
+  </si>
+  <si>
+    <t>AC_BC (0,05 / 6 = 0,008)</t>
+  </si>
+  <si>
+    <t>UC_LC (0,05 / 6 = 0,008)</t>
+  </si>
+  <si>
+    <t>UC_BC (0,05 / 6 = 0,008)</t>
+  </si>
+  <si>
+    <t>BC_LC (0,05 / 6 = 0,008)</t>
+  </si>
+  <si>
+    <t>ab.colsxrar</t>
+  </si>
+  <si>
+    <t>ab.colsxrar ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>infra : 0.00083824 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra inf : 0.00123878 ** </t>
+  </si>
+  <si>
+    <t>infra supp : &lt; 2.22e-16 ***</t>
+  </si>
+  <si>
+    <t>supra : 0.00041702 ***</t>
+  </si>
+  <si>
+    <t>620.6581</t>
+  </si>
+  <si>
+    <t>620.6582</t>
+  </si>
+  <si>
+    <t>620.6583</t>
+  </si>
+  <si>
+    <t>620.6584</t>
+  </si>
+  <si>
+    <t>660.7834</t>
+  </si>
+  <si>
+    <t>660.7835</t>
+  </si>
+  <si>
+    <t>660.7836</t>
+  </si>
+  <si>
+    <t>660.7837</t>
+  </si>
+  <si>
+    <t>ab.colsxrar ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>&lt; 2.22e-16 ***</t>
+  </si>
+  <si>
+    <t>3.2334e-10 ***</t>
+  </si>
+  <si>
+    <t>0.0068681 **</t>
+  </si>
+  <si>
+    <t>0.0023164 **</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On retrouve un effet de stratification verticale pour La richesse spécifique cumulée totale des coléoptères saproxyliques, avec une différence de diversité spécifique entre la strate </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>infra.supp &amp; infra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, et </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>infra.supp &amp; infra.inf</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On retrouve un effet de stratification verticale pour l'abondance cumulée totale des coléoptères saproxyliques, avec une différence d'abondance entre la strate </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>infra &amp; infra.inf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>infra.supp &amp; infra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>infra.supp &amp; infra.inf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, la strate </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">supra &amp; infra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">ainsi que </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supra et infra.supp</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -121,7 +463,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -130,6 +472,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -410,70 +767,773 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="72.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.33203125" customWidth="1"/>
+    <col min="7" max="7" width="57.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="20.33203125" customWidth="1"/>
+    <col min="10" max="10" width="33.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="33.5546875" customWidth="1"/>
+    <col min="12" max="12" width="38.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="24.109375" style="7" customWidth="1"/>
+    <col min="20" max="20" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" t="s">
-        <v>8</v>
+        <v>21</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="T1" s="1"/>
+      <c r="U1" t="s">
+        <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
+      <c r="B2" s="3">
+        <v>321</v>
+      </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>1</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2">
+        <v>955.84</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2">
+        <v>976.73</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="R2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3">
+        <v>321</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3">
+        <v>955.84</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3">
+        <v>976.73</v>
+      </c>
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" t="s">
+        <v>25</v>
+      </c>
+      <c r="P3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R3" t="s">
+        <v>27</v>
+      </c>
+      <c r="S3" s="8"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="3">
+        <v>321</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4">
+        <v>955.84</v>
+      </c>
+      <c r="G4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="I4">
+        <v>976.73</v>
+      </c>
+      <c r="J4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4" t="s">
+        <v>25</v>
+      </c>
+      <c r="P4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>24</v>
+      </c>
+      <c r="R4" t="s">
+        <v>27</v>
+      </c>
+      <c r="S4" s="8"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="3">
+        <v>321</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5">
+        <v>955.84</v>
+      </c>
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5">
+        <v>976.73</v>
+      </c>
+      <c r="J5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>24</v>
+      </c>
+      <c r="R5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S5" s="8"/>
+    </row>
+    <row r="6" spans="1:21" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="3">
+        <v>393</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6">
+        <v>641.5</v>
+      </c>
+      <c r="G6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6">
+        <v>646.24</v>
+      </c>
+      <c r="J6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" t="s">
+        <v>41</v>
+      </c>
+      <c r="P6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>24</v>
+      </c>
+      <c r="R6" t="s">
+        <v>27</v>
+      </c>
+      <c r="S6" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="3">
+        <v>393</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7">
+        <v>641.5</v>
+      </c>
+      <c r="G7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7">
+        <v>646.24</v>
+      </c>
+      <c r="J7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7" t="s">
+        <v>22</v>
+      </c>
+      <c r="M7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P7" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R7" t="s">
+        <v>27</v>
+      </c>
+      <c r="S7" s="8"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="3">
+        <v>393</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8">
+        <v>641.5</v>
+      </c>
+      <c r="G8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="I8">
+        <v>646.24</v>
+      </c>
+      <c r="J8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" t="s">
+        <v>37</v>
+      </c>
+      <c r="L8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" t="s">
+        <v>27</v>
+      </c>
+      <c r="N8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O8" t="s">
+        <v>41</v>
+      </c>
+      <c r="P8" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>24</v>
+      </c>
+      <c r="R8" t="s">
+        <v>27</v>
+      </c>
+      <c r="S8" s="8"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="3">
+        <v>393</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9">
+        <v>641.5</v>
+      </c>
+      <c r="G9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="5"/>
+      <c r="I9">
+        <v>646.24</v>
+      </c>
+      <c r="J9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L9" t="s">
+        <v>22</v>
+      </c>
+      <c r="M9" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" t="s">
+        <v>41</v>
+      </c>
+      <c r="P9" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>24</v>
+      </c>
+      <c r="R9" t="s">
+        <v>27</v>
+      </c>
+      <c r="S9" s="8"/>
+    </row>
+    <row r="10" spans="1:21" ht="120" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="3">
+        <v>455</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I10" t="s">
+        <v>57</v>
+      </c>
+      <c r="J10" t="s">
+        <v>63</v>
+      </c>
+      <c r="K10" t="s">
+        <v>37</v>
+      </c>
+      <c r="L10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M10" t="s">
+        <v>24</v>
+      </c>
+      <c r="N10" t="s">
+        <v>27</v>
+      </c>
+      <c r="O10" t="s">
+        <v>65</v>
+      </c>
+      <c r="P10" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>24</v>
+      </c>
+      <c r="R10" t="s">
+        <v>64</v>
+      </c>
+      <c r="S10" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="3">
+        <v>455</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" s="5"/>
+      <c r="I11" t="s">
+        <v>58</v>
+      </c>
+      <c r="J11" t="s">
+        <v>63</v>
+      </c>
+      <c r="K11" t="s">
+        <v>37</v>
+      </c>
+      <c r="L11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N11" t="s">
+        <v>27</v>
+      </c>
+      <c r="O11" t="s">
+        <v>65</v>
+      </c>
+      <c r="P11" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>24</v>
+      </c>
+      <c r="R11" t="s">
+        <v>64</v>
+      </c>
+      <c r="S11" s="8"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="3">
+        <v>455</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12" s="5"/>
+      <c r="I12" t="s">
+        <v>59</v>
+      </c>
+      <c r="J12" t="s">
+        <v>63</v>
+      </c>
+      <c r="K12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L12" t="s">
+        <v>22</v>
+      </c>
+      <c r="M12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N12" t="s">
+        <v>27</v>
+      </c>
+      <c r="O12" t="s">
+        <v>65</v>
+      </c>
+      <c r="P12" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>24</v>
+      </c>
+      <c r="R12" t="s">
+        <v>64</v>
+      </c>
+      <c r="S12" s="8"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="3">
+        <v>455</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" t="s">
+        <v>61</v>
+      </c>
+      <c r="H13" s="5"/>
+      <c r="I13" t="s">
+        <v>60</v>
+      </c>
+      <c r="J13" t="s">
+        <v>63</v>
+      </c>
+      <c r="K13" t="s">
+        <v>37</v>
+      </c>
+      <c r="L13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" t="s">
+        <v>24</v>
+      </c>
+      <c r="N13" t="s">
+        <v>27</v>
+      </c>
+      <c r="O13" t="s">
+        <v>65</v>
+      </c>
+      <c r="P13" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>24</v>
+      </c>
+      <c r="R13" t="s">
+        <v>64</v>
+      </c>
+      <c r="S13" s="8"/>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="H2:H5"/>
+    <mergeCell ref="S2:S5"/>
+    <mergeCell ref="H6:H9"/>
+    <mergeCell ref="S6:S9"/>
+    <mergeCell ref="H10:H13"/>
+    <mergeCell ref="S10:S13"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Resultats_modeles_coleo_2024.xlsx
+++ b/Resultats_modeles_coleo_2024.xlsx
@@ -12,7 +12,8 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Enssillage_resultats" sheetId="1" r:id="rId1"/>
+    <sheet name="Bugs_&amp;_errors" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913" refMode="R1C1"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="313">
   <si>
     <t>ab.colsx</t>
   </si>
@@ -113,6 +114,168 @@
     <t>Conclusion</t>
   </si>
   <si>
+    <t>sr.colsx</t>
+  </si>
+  <si>
+    <t>Gaussian</t>
+  </si>
+  <si>
+    <t>sr.colsx ~ strate + (1 | LOCA / placette) + exp(pos+0|ID) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>infra inf : 0.41284</t>
+  </si>
+  <si>
+    <t>infra supp : 3.4678e-05 ***</t>
+  </si>
+  <si>
+    <t>supra :0.17427</t>
+  </si>
+  <si>
+    <t>sr.colsx ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>Modèle 1</t>
+  </si>
+  <si>
+    <t>Choix modèle mieux ajusté (delta &gt; 2)</t>
+  </si>
+  <si>
+    <t>0.0049384 **</t>
+  </si>
+  <si>
+    <t>0.0048236 **</t>
+  </si>
+  <si>
+    <t>N.S (0.0277350)</t>
+  </si>
+  <si>
+    <t>AC_LC (0,05 / 6 = 0,008)</t>
+  </si>
+  <si>
+    <t>AC_BC (0,05 / 6 = 0,008)</t>
+  </si>
+  <si>
+    <t>UC_LC (0,05 / 6 = 0,008)</t>
+  </si>
+  <si>
+    <t>UC_BC (0,05 / 6 = 0,008)</t>
+  </si>
+  <si>
+    <t>BC_LC (0,05 / 6 = 0,008)</t>
+  </si>
+  <si>
+    <t>ab.colsxrar</t>
+  </si>
+  <si>
+    <t>ab.colsxrar ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>infra : 0.00083824 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra inf : 0.00123878 ** </t>
+  </si>
+  <si>
+    <t>infra supp : &lt; 2.22e-16 ***</t>
+  </si>
+  <si>
+    <t>supra : 0.00041702 ***</t>
+  </si>
+  <si>
+    <t>620.6581</t>
+  </si>
+  <si>
+    <t>660.7834</t>
+  </si>
+  <si>
+    <t>ab.colsxrar ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>&lt; 2.22e-16 ***</t>
+  </si>
+  <si>
+    <t>3.2334e-10 ***</t>
+  </si>
+  <si>
+    <t>0.0068681 **</t>
+  </si>
+  <si>
+    <t>0.0023164 **</t>
+  </si>
+  <si>
+    <t>Problème de convergence du modèle avec exp(pos+0|ID)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loi </t>
+  </si>
+  <si>
+    <t>gaussian</t>
+  </si>
+  <si>
+    <t>log-normal</t>
+  </si>
+  <si>
+    <t>Modèles</t>
+  </si>
+  <si>
+    <t>nbinom</t>
+  </si>
+  <si>
+    <t>non</t>
+  </si>
+  <si>
+    <t>oui</t>
+  </si>
+  <si>
+    <t>sr.colsxrar</t>
+  </si>
+  <si>
+    <t>genpoiss</t>
+  </si>
+  <si>
+    <t>sr.colsxrar ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>sr.colsxrar ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>330.9763</t>
+  </si>
+  <si>
+    <t>infra :&lt; 2e-16 ***</t>
+  </si>
+  <si>
+    <t>infra inf : 1.87e-06 ***</t>
+  </si>
+  <si>
+    <t>infra supp : 1.34e-15 ***</t>
+  </si>
+  <si>
+    <t>supra : 0.000378 ***</t>
+  </si>
+  <si>
+    <t>374.6217</t>
+  </si>
+  <si>
+    <t>&lt;2e-16 ***</t>
+  </si>
+  <si>
+    <t>5.759e-11 ***</t>
+  </si>
+  <si>
+    <t>Modèle 2</t>
+  </si>
+  <si>
+    <t>Soucis de surdispersion en nbinom (1 &amp; 2), passage en poisson (genpoiss) qui fit également avec fitdistplus, plus de soucis avec les présupposés du modèle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00207 ** </t>
+  </si>
+  <si>
+    <t>0.00511 **</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">On retrouve un effet de stratification verticale pour l'abondance cumulée totale des coléoptères saproxyliques, avec une différence d'abondance entre la strate </t>
     </r>
@@ -146,7 +309,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> infra.supp &amp; infra.inf, </t>
+      <t xml:space="preserve"> intra.supp &amp; intra.inf, </t>
     </r>
     <r>
       <rPr>
@@ -167,116 +330,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>infra.supp &amp; infra</t>
-    </r>
-  </si>
-  <si>
-    <t>sr.colsx</t>
-  </si>
-  <si>
-    <t>Gaussian</t>
-  </si>
-  <si>
-    <t>sr.colsx ~ strate + (1 | LOCA / placette) + exp(pos+0|ID) + offset(log(prop.trap.season))</t>
-  </si>
-  <si>
-    <t>infra inf : 0.41284</t>
-  </si>
-  <si>
-    <t>infra supp : 3.4678e-05 ***</t>
-  </si>
-  <si>
-    <t>supra :0.17427</t>
-  </si>
-  <si>
-    <t>sr.colsx ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
-  </si>
-  <si>
-    <t>Modèle 1</t>
-  </si>
-  <si>
-    <t>Choix modèle mieux ajusté (delta &gt; 2)</t>
-  </si>
-  <si>
-    <t>0.0049384 **</t>
-  </si>
-  <si>
-    <t>0.0048236 **</t>
-  </si>
-  <si>
-    <t>N.S (0.0277350)</t>
-  </si>
-  <si>
-    <t>AC_LC (0,05 / 6 = 0,008)</t>
-  </si>
-  <si>
-    <t>AC_BC (0,05 / 6 = 0,008)</t>
-  </si>
-  <si>
-    <t>UC_LC (0,05 / 6 = 0,008)</t>
-  </si>
-  <si>
-    <t>UC_BC (0,05 / 6 = 0,008)</t>
-  </si>
-  <si>
-    <t>BC_LC (0,05 / 6 = 0,008)</t>
-  </si>
-  <si>
-    <t>ab.colsxrar</t>
-  </si>
-  <si>
-    <t>ab.colsxrar ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
-  </si>
-  <si>
-    <t>infra : 0.00083824 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">infra inf : 0.00123878 ** </t>
-  </si>
-  <si>
-    <t>infra supp : &lt; 2.22e-16 ***</t>
-  </si>
-  <si>
-    <t>supra : 0.00041702 ***</t>
-  </si>
-  <si>
-    <t>620.6581</t>
-  </si>
-  <si>
-    <t>620.6582</t>
-  </si>
-  <si>
-    <t>620.6583</t>
-  </si>
-  <si>
-    <t>620.6584</t>
-  </si>
-  <si>
-    <t>660.7834</t>
-  </si>
-  <si>
-    <t>660.7835</t>
-  </si>
-  <si>
-    <t>660.7836</t>
-  </si>
-  <si>
-    <t>660.7837</t>
-  </si>
-  <si>
-    <t>ab.colsxrar ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
-  </si>
-  <si>
-    <t>&lt; 2.22e-16 ***</t>
-  </si>
-  <si>
-    <t>3.2334e-10 ***</t>
-  </si>
-  <si>
-    <t>0.0068681 **</t>
-  </si>
-  <si>
-    <t>0.0023164 **</t>
+      <t>intra.supp &amp; infra</t>
+    </r>
   </si>
   <si>
     <r>
@@ -291,7 +346,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>infra.supp &amp; infra</t>
+      <t>intra.supp &amp; infra</t>
     </r>
     <r>
       <rPr>
@@ -312,12 +367,12 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>infra.supp &amp; infra.inf</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">On retrouve un effet de stratification verticale pour l'abondance cumulée totale des coléoptères saproxyliques, avec une différence d'abondance entre la strate </t>
+      <t>intra.supp &amp; intra.inf</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On retrouve un effet de stratification verticale pour l'abondance cumulée totale des coléoptères saproxyliques rares, avec une différence d'abondance entre la strate </t>
     </r>
     <r>
       <rPr>
@@ -328,7 +383,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>infra &amp; infra.inf</t>
+      <t>infra &amp; intra.inf</t>
     </r>
     <r>
       <rPr>
@@ -349,7 +404,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>infra.supp &amp; infra</t>
+      <t>intra.supp &amp; infra</t>
     </r>
     <r>
       <rPr>
@@ -370,7 +425,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>infra.supp &amp; infra.inf</t>
+      <t>intra.supp &amp; intra.inf</t>
     </r>
     <r>
       <rPr>
@@ -412,7 +467,1323 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>supra et infra.supp</t>
+      <t>supra et intra.supp</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On retrouve un effet de stratification verticale pour La richesse spécifique cumulée totale des coléoptères saproxyliques rares, avec une différence de diversité entre les strates </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>infra &amp; intra.inf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; infra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; intra.inf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, la strate </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supra &amp; infra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ainsi que </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supra &amp; intra.supp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>ab.colsxcom</t>
+  </si>
+  <si>
+    <t>ab.colsxcom ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>ab.colsxcom ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>infra inf : 0.324155</t>
+  </si>
+  <si>
+    <t>infra supp : 3.38e-06 ***</t>
+  </si>
+  <si>
+    <t>supra : 0.000112 ***</t>
+  </si>
+  <si>
+    <t>930.4896</t>
+  </si>
+  <si>
+    <t>949.2164</t>
+  </si>
+  <si>
+    <t>1.076e-05 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00221 ** </t>
+  </si>
+  <si>
+    <t>N.S (0.01575 *)</t>
+  </si>
+  <si>
+    <t>sr.colsxcom</t>
+  </si>
+  <si>
+    <t>sr.colsxcom ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>sr.colsxcom ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>infra inf : 0.77042</t>
+  </si>
+  <si>
+    <t>infra supp : 0.00143 **</t>
+  </si>
+  <si>
+    <t>supra : 0.41473</t>
+  </si>
+  <si>
+    <t>614.1401</t>
+  </si>
+  <si>
+    <t>618.5605</t>
+  </si>
+  <si>
+    <t>0.009558 **</t>
+  </si>
+  <si>
+    <t>0.0079 **</t>
+  </si>
+  <si>
+    <t>N.S (0.0198 *)</t>
+  </si>
+  <si>
+    <r>
+      <t>En ce qui concerne l'abondance cumulée totale des coléoptères saproxyliques communs, elle différe entre les strates</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> supra &amp; infra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; intra.inf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> et </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; infra</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">En ce qui concerne la richesse spécifique cumulée totale des coléoptères saproxyliques communs, elle différe seulement entre les strates </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; infra</t>
+    </r>
+  </si>
+  <si>
+    <t>ab.cav</t>
+  </si>
+  <si>
+    <t>ab.cav ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>ab.cav ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>infra inf : 0.01367 *</t>
+  </si>
+  <si>
+    <t>infra supp : 5.67e-07 ***</t>
+  </si>
+  <si>
+    <t>supra : 0.00589 **</t>
+  </si>
+  <si>
+    <t>685.2339</t>
+  </si>
+  <si>
+    <t>702.1384</t>
+  </si>
+  <si>
+    <t>2.588e-05 ***</t>
+  </si>
+  <si>
+    <t>N.S (0.0296 *)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N.S </t>
+  </si>
+  <si>
+    <r>
+      <t>En ce qui concerne l'abondance cumulée totale des coléoptères saproxyliques cavicoles, elle différe seulement entre les strates</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> intra.supp &amp; infra</t>
+    </r>
+  </si>
+  <si>
+    <t>sr.cav</t>
+  </si>
+  <si>
+    <t>sr.cav ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>sr.cav ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>453.7887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra inf : 0.02961 * </t>
+  </si>
+  <si>
+    <t>infra supp : 0.00903 **</t>
+  </si>
+  <si>
+    <t>supra : 0.06915 .</t>
+  </si>
+  <si>
+    <t>467.9944</t>
+  </si>
+  <si>
+    <t>9.44e-05 ***</t>
+  </si>
+  <si>
+    <t>N.S (0.0302 *)</t>
+  </si>
+  <si>
+    <t>N.S (0.0553 .)</t>
+  </si>
+  <si>
+    <t>N.S (0.0648 .)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pour la richesse spécifique cumulée totale des coléoptères saproxyliques cavicoles, elle diffère uniquement entre les strates </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; infra</t>
+    </r>
+  </si>
+  <si>
+    <t>ab.fon</t>
+  </si>
+  <si>
+    <t>ab.fon ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>ab.fon ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>861.6836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra inf : 0.01796 * </t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra supp : 0.00394 ** </t>
+  </si>
+  <si>
+    <t xml:space="preserve">supra : 0.08737 . </t>
+  </si>
+  <si>
+    <t>863.6748</t>
+  </si>
+  <si>
+    <t>0.02911 *</t>
+  </si>
+  <si>
+    <t>N.S (0.0201 *)</t>
+  </si>
+  <si>
+    <t>N.S (0.0826 .)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N.S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : aucunes différences entre les strates comparées 2 à 2 pour l'abondance cumulée totale des coléoptères saproxyliques fongicoles</t>
+    </r>
+  </si>
+  <si>
+    <t>470.2642</t>
+  </si>
+  <si>
+    <t>478.399</t>
+  </si>
+  <si>
+    <t>0.001687 **</t>
+  </si>
+  <si>
+    <t>sr.fon</t>
+  </si>
+  <si>
+    <t>sr.fon ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>sr.fon ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra inf : 0.0440 * </t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra supp : 0.4673  </t>
+  </si>
+  <si>
+    <t>supra : 0.0342 *</t>
+  </si>
+  <si>
+    <t>N.S (0.0247 * )</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pour la richesse spécifique cumulée totale des coléoptères saproxyliques fongicoles, elle diffère uniquement entre les strates </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">supra &amp; intra.inf </t>
+    </r>
+  </si>
+  <si>
+    <t>ab.fonspe</t>
+  </si>
+  <si>
+    <t>nbinom1</t>
+  </si>
+  <si>
+    <t>ab.fonspe ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>ab.fonspe ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>484.316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra inf : 0.515549  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra supp : 0.007862 **   </t>
+  </si>
+  <si>
+    <t>supra : 0.000385 ***</t>
+  </si>
+  <si>
+    <t>495.8483</t>
+  </si>
+  <si>
+    <t>0.000338 ***</t>
+  </si>
+  <si>
+    <t>0.00227 **</t>
+  </si>
+  <si>
+    <t>N.S (0.03897 *)</t>
+  </si>
+  <si>
+    <t>N.S (0.02251 *)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pour l'abondance cumulée totale des coléoptères saproxyliques fongicoles spécialistes, elle diffère seulement entre </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supra &amp; infra</t>
+    </r>
+  </si>
+  <si>
+    <t>sr.fonspe</t>
+  </si>
+  <si>
+    <t>genpois</t>
+  </si>
+  <si>
+    <t>sr.fonspe ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>315.5848</t>
+  </si>
+  <si>
+    <t>sr.fonspe ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>319.8235</t>
+  </si>
+  <si>
+    <t>0.0104 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra inf : 0.2605 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra supp : 0.9030 </t>
+  </si>
+  <si>
+    <t>supra : 0.0144 *</t>
+  </si>
+  <si>
+    <t>0.00293 **</t>
+  </si>
+  <si>
+    <t>N.S (0.06779 .)</t>
+  </si>
+  <si>
+    <t>N.S (0.05244 .)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pour la richesse spécifique cumulée totale des coléoptères saproxyliques fongicoles spécialistes, elle diffère uniquement pour les strates </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supra &amp; intra.inf</t>
+    </r>
+  </si>
+  <si>
+    <t>ab.suc</t>
+  </si>
+  <si>
+    <t>ab.suc ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>ab.suc ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>371.9953</t>
+  </si>
+  <si>
+    <t>382.6358</t>
+  </si>
+  <si>
+    <t>0.0005162 ***</t>
+  </si>
+  <si>
+    <t>infra : 0.00152 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra inf : 0.00444 ** </t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra supp : 0.14261  </t>
+  </si>
+  <si>
+    <t>supra : 0.09619 .</t>
+  </si>
+  <si>
+    <t>5.98e-06 ***</t>
+  </si>
+  <si>
+    <t>N.S (0.0228 *)</t>
+  </si>
+  <si>
+    <t>&lt;0.001 ***</t>
+  </si>
+  <si>
+    <t>N.S (0.0143 *)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pour l'abondance cumulée totale des coléoptères saproxyliques succicoles, elle diffère seulement entre les strates </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supra &amp; intra.inf</t>
+    </r>
+  </si>
+  <si>
+    <t>sr.suc</t>
+  </si>
+  <si>
+    <t>sr.suc ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>sr.suc ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>infra : 0.00684 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra inf : 0.10598 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra supp : 0.81094  </t>
+  </si>
+  <si>
+    <t>supra : 0.20243</t>
+  </si>
+  <si>
+    <t>266.49</t>
+  </si>
+  <si>
+    <t>267.4356</t>
+  </si>
+  <si>
+    <t>0.0014 **</t>
+  </si>
+  <si>
+    <t>0.04668 *</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">N.S </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: aucunes différences entre les strates comparées 2 à 2 pour la richesse spécifique cumulée totale des coléoptères saproxyliques succicoles</t>
+    </r>
+  </si>
+  <si>
+    <t>ab.lig</t>
+  </si>
+  <si>
+    <t>N.S (0.024 *)</t>
+  </si>
+  <si>
+    <t>ab.lig ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>ab.lig ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>infra : &lt; 2e-16 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra inf : 0.03669 * </t>
+  </si>
+  <si>
+    <t>infra supp : 3.16e-08 ***</t>
+  </si>
+  <si>
+    <t>supra : 0.00101 **</t>
+  </si>
+  <si>
+    <t>949.4589</t>
+  </si>
+  <si>
+    <t>969.5341</t>
+  </si>
+  <si>
+    <t>5.617e-06 ***</t>
+  </si>
+  <si>
+    <t>0.00556 **</t>
+  </si>
+  <si>
+    <t>0.00322 **</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pour l'abondance cumulée totale des coléoptères saproxyliques lignicoles, elle diffère sur plusieurs des strates comparées 2 à 2, qui sont </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supra &amp; infra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> intra.supp &amp; intra.inf,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">et </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; infra</t>
+    </r>
+  </si>
+  <si>
+    <t>sr.lig</t>
+  </si>
+  <si>
+    <t>sr.lig ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>sr.lig ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra inf : 0.5510 </t>
+  </si>
+  <si>
+    <t>infra supp : 5.58e-06 ***</t>
+  </si>
+  <si>
+    <t>supra : 0.0529 .</t>
+  </si>
+  <si>
+    <t>620.5829</t>
+  </si>
+  <si>
+    <t>634.0627</t>
+  </si>
+  <si>
+    <t>0.0001336 ***</t>
+  </si>
+  <si>
+    <t>N.S (0.0452 *)</t>
+  </si>
+  <si>
+    <r>
+      <t>Pour la richesse spécifique cumulée totale des coléoptères saproxyliques lignicoles, elle diffère uniquement sur la comparaison 2 à 2 des strates</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> intra.supp &amp; intra.inf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, et </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; infra</t>
+    </r>
+  </si>
+  <si>
+    <t>ab.flo</t>
+  </si>
+  <si>
+    <t>ab.flo ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>ab.flo ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra inf : 0.00242 ** </t>
+  </si>
+  <si>
+    <t>infra supp : 2.99e-09 ***</t>
+  </si>
+  <si>
+    <t>supra : 2.75e-11 ***</t>
+  </si>
+  <si>
+    <t>745.4168</t>
+  </si>
+  <si>
+    <t>790.4968</t>
+  </si>
+  <si>
+    <t>2.849e-11 ***</t>
+  </si>
+  <si>
+    <t>N.S (0.01275 *)</t>
+  </si>
+  <si>
+    <t>0.00547 **</t>
+  </si>
+  <si>
+    <t>0.00146 **</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pour l'abondance cumulée totale des coléoptères saproxyliques floricoles, elle diffère sur plusieurs des strates comparées 2 à 2, qui sont </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supra &amp; infra.inf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supra &amp; infra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; intra.inf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, et </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; infra</t>
+    </r>
+  </si>
+  <si>
+    <t>sr.flo</t>
+  </si>
+  <si>
+    <t>sr.flo ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>sr.flo ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>infra inf : 0.000134 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra supp : 1.09e-12 *** </t>
+  </si>
+  <si>
+    <t>supra : 1.34e-05 ***</t>
+  </si>
+  <si>
+    <t>466.81</t>
+  </si>
+  <si>
+    <t>500.5577</t>
+  </si>
+  <si>
+    <t>7.317e-09 ***</t>
+  </si>
+  <si>
+    <t>0.00519 **</t>
+  </si>
+  <si>
+    <t>N.S (0.01931 *)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pour la richesse spécifique cumulée totale des coléoptères saproxyliques floricoles, elle diffère sur la comparaison 2 à 2 de plusieurs strates qui sont : </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supra &amp; infra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; intra.inf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; infra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, et </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.inf et infra</t>
+    </r>
+  </si>
+  <si>
+    <t>ab.pho</t>
+  </si>
+  <si>
+    <t>ab.pho ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>ab.pho ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>infra inf : 0.000144 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra supp : 0.001362 **  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">supra : 0.078224 . </t>
+  </si>
+  <si>
+    <t>450.869</t>
+  </si>
+  <si>
+    <t>459.3375</t>
+  </si>
+  <si>
+    <t>0.001442 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00712 ** </t>
+  </si>
+  <si>
+    <t>sr.pho</t>
+  </si>
+  <si>
+    <t>sr.pho ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>sr.pho ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>infra : 5.38e-08 ***</t>
+  </si>
+  <si>
+    <t>infra inf : 5.07e-05 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">supra : 0.5505  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra supp : 0.0316 *   </t>
+  </si>
+  <si>
+    <t>1.98e-11 ***</t>
+  </si>
+  <si>
+    <t>262.2215</t>
+  </si>
+  <si>
+    <t>272.1756</t>
+  </si>
+  <si>
+    <t>0.0007147 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt; 0.001 *** </t>
+  </si>
+  <si>
+    <t>0.00347 **</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">En ce qui concerne l'abondance cumulée totale des coléoptères saproxyliques pholeophiles, elle diffère sur plusieurs des strates comparées 2 à 2, qui sont </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; infra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, et </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.inf &amp; infra</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">En ce qui concerne la richesse spécifique cumulée totale des coléoptères saproxyliques pholeophiles, elle diffère sur plusieurs des strates comparées 2 à 2, qui sont </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supra &amp; intra.inf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, et </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.inf &amp; infra</t>
+    </r>
+  </si>
+  <si>
+    <t>ab.myc</t>
+  </si>
+  <si>
+    <t>ab.myc ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>ab.myc ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>infra inf : 0.075864 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra supp : 0.004308 **    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">supra : 0.000249 ***  </t>
+  </si>
+  <si>
+    <t>753.5138</t>
+  </si>
+  <si>
+    <t>&lt; 2e-16 ***</t>
+  </si>
+  <si>
+    <t>761.3229</t>
+  </si>
+  <si>
+    <t>0.001967 **</t>
+  </si>
+  <si>
+    <t>N.S (0.0223 *)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pour l'abondance cumulée totale des coléoptères saproxyliques mycétophages, seul une différence est observée pour la comparaison 2 à 2 des strates </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supra &amp; infra</t>
+    </r>
+  </si>
+  <si>
+    <t>sr.myc</t>
+  </si>
+  <si>
+    <t>sr.myc ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>sr.myc ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>infra inf : 0.6821</t>
+  </si>
+  <si>
+    <t>supra : 0.0129 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra supp : 0.2125     </t>
+  </si>
+  <si>
+    <t>399.8433</t>
+  </si>
+  <si>
+    <t>401.8182</t>
+  </si>
+  <si>
+    <t>0.02933 *</t>
+  </si>
+  <si>
+    <t>N.S (0.0233 *)</t>
+  </si>
+  <si>
+    <t>N.S (0.0622 .)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N.S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : aucunes différences entre les strates comparées 2 à 2 pour la richesse spécifique cumulée totale des coléoptères saproxyliques mycétophages</t>
     </r>
   </si>
 </sst>
@@ -463,7 +1834,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -475,17 +1846,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -767,7 +2141,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:U89"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.6640625" style="3" bestFit="1" customWidth="1"/>
@@ -786,7 +2160,7 @@
     <col min="16" max="16" width="21.21875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="20.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="24.109375" style="7" customWidth="1"/>
+    <col min="19" max="19" width="24.109375" style="9" customWidth="1"/>
     <col min="20" max="20" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -822,7 +2196,7 @@
         <v>4</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>21</v>
@@ -831,21 +2205,21 @@
         <v>23</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="6" t="s">
+      <c r="S1" s="5" t="s">
         <v>28</v>
       </c>
       <c r="T1" s="1"/>
@@ -875,7 +2249,7 @@
       <c r="G2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="6" t="s">
         <v>19</v>
       </c>
       <c r="I2">
@@ -885,7 +2259,7 @@
         <v>20</v>
       </c>
       <c r="K2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -909,7 +2283,7 @@
         <v>27</v>
       </c>
       <c r="S2" s="8" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
@@ -934,7 +2308,7 @@
       <c r="G3" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="5"/>
+      <c r="H3" s="6"/>
       <c r="I3">
         <v>976.73</v>
       </c>
@@ -942,7 +2316,7 @@
         <v>20</v>
       </c>
       <c r="K3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
@@ -989,7 +2363,7 @@
       <c r="G4" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="5"/>
+      <c r="H4" s="6"/>
       <c r="I4">
         <v>976.73</v>
       </c>
@@ -997,7 +2371,7 @@
         <v>20</v>
       </c>
       <c r="K4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
@@ -1044,7 +2418,7 @@
       <c r="G5" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="5"/>
+      <c r="H5" s="6"/>
       <c r="I5">
         <v>976.73</v>
       </c>
@@ -1052,7 +2426,7 @@
         <v>20</v>
       </c>
       <c r="K5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L5" t="s">
         <v>22</v>
@@ -1079,16 +2453,16 @@
     </row>
     <row r="6" spans="1:21" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="3">
         <v>393</v>
       </c>
       <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
         <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
       </c>
       <c r="E6" t="s">
         <v>13</v>
@@ -1097,34 +2471,34 @@
         <v>641.5</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>19</v>
       </c>
       <c r="I6">
         <v>646.24</v>
       </c>
       <c r="J6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" t="s">
+        <v>40</v>
+      </c>
+      <c r="P6" t="s">
         <v>39</v>
-      </c>
-      <c r="K6" t="s">
-        <v>37</v>
-      </c>
-      <c r="L6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M6" t="s">
-        <v>27</v>
-      </c>
-      <c r="N6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O6" t="s">
-        <v>41</v>
-      </c>
-      <c r="P6" t="s">
-        <v>40</v>
       </c>
       <c r="Q6" t="s">
         <v>24</v>
@@ -1133,55 +2507,55 @@
         <v>27</v>
       </c>
       <c r="S6" s="8" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" s="3">
         <v>393</v>
       </c>
       <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
         <v>31</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>32</v>
-      </c>
-      <c r="E7" t="s">
-        <v>33</v>
       </c>
       <c r="F7">
         <v>641.5</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="5"/>
+        <v>35</v>
+      </c>
+      <c r="H7" s="6"/>
       <c r="I7">
         <v>646.24</v>
       </c>
       <c r="J7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" t="s">
+        <v>22</v>
+      </c>
+      <c r="M7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P7" t="s">
         <v>39</v>
-      </c>
-      <c r="K7" t="s">
-        <v>37</v>
-      </c>
-      <c r="L7" t="s">
-        <v>22</v>
-      </c>
-      <c r="M7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N7" t="s">
-        <v>27</v>
-      </c>
-      <c r="O7" t="s">
-        <v>41</v>
-      </c>
-      <c r="P7" t="s">
-        <v>40</v>
       </c>
       <c r="Q7" t="s">
         <v>24</v>
@@ -1193,50 +2567,50 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" s="3">
         <v>393</v>
       </c>
       <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
         <v>31</v>
       </c>
-      <c r="D8" t="s">
-        <v>32</v>
-      </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F8">
         <v>641.5</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
-      </c>
-      <c r="H8" s="5"/>
+        <v>35</v>
+      </c>
+      <c r="H8" s="6"/>
       <c r="I8">
         <v>646.24</v>
       </c>
       <c r="J8" t="s">
+        <v>38</v>
+      </c>
+      <c r="K8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" t="s">
+        <v>27</v>
+      </c>
+      <c r="N8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O8" t="s">
+        <v>40</v>
+      </c>
+      <c r="P8" t="s">
         <v>39</v>
-      </c>
-      <c r="K8" t="s">
-        <v>37</v>
-      </c>
-      <c r="L8" t="s">
-        <v>22</v>
-      </c>
-      <c r="M8" t="s">
-        <v>27</v>
-      </c>
-      <c r="N8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O8" t="s">
-        <v>41</v>
-      </c>
-      <c r="P8" t="s">
-        <v>40</v>
       </c>
       <c r="Q8" t="s">
         <v>24</v>
@@ -1248,50 +2622,50 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" s="3">
         <v>393</v>
       </c>
       <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
         <v>31</v>
       </c>
-      <c r="D9" t="s">
-        <v>32</v>
-      </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F9">
         <v>641.5</v>
       </c>
       <c r="G9" t="s">
-        <v>36</v>
-      </c>
-      <c r="H9" s="5"/>
+        <v>35</v>
+      </c>
+      <c r="H9" s="6"/>
       <c r="I9">
         <v>646.24</v>
       </c>
       <c r="J9" t="s">
+        <v>38</v>
+      </c>
+      <c r="K9" t="s">
+        <v>36</v>
+      </c>
+      <c r="L9" t="s">
+        <v>22</v>
+      </c>
+      <c r="M9" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" t="s">
+        <v>40</v>
+      </c>
+      <c r="P9" t="s">
         <v>39</v>
-      </c>
-      <c r="K9" t="s">
-        <v>37</v>
-      </c>
-      <c r="L9" t="s">
-        <v>22</v>
-      </c>
-      <c r="M9" t="s">
-        <v>27</v>
-      </c>
-      <c r="N9" t="s">
-        <v>27</v>
-      </c>
-      <c r="O9" t="s">
-        <v>41</v>
-      </c>
-      <c r="P9" t="s">
-        <v>40</v>
       </c>
       <c r="Q9" t="s">
         <v>24</v>
@@ -1303,37 +2677,37 @@
     </row>
     <row r="10" spans="1:21" ht="120" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10" s="3">
         <v>455</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" t="s">
         <v>48</v>
       </c>
-      <c r="E10" t="s">
-        <v>49</v>
-      </c>
       <c r="F10" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" t="s">
         <v>53</v>
       </c>
-      <c r="G10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="I10" t="s">
-        <v>57</v>
-      </c>
       <c r="J10" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="K10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L10" t="s">
         <v>22</v>
@@ -1345,7 +2719,7 @@
         <v>27</v>
       </c>
       <c r="O10" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="P10" t="s">
         <v>24</v>
@@ -1354,43 +2728,43 @@
         <v>24</v>
       </c>
       <c r="R10" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="S10" s="8" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B11" s="3">
         <v>455</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F11" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" t="s">
         <v>54</v>
       </c>
-      <c r="G11" t="s">
-        <v>61</v>
-      </c>
-      <c r="H11" s="5"/>
+      <c r="H11" s="6"/>
       <c r="I11" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="J11" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="K11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L11" t="s">
         <v>22</v>
@@ -1402,7 +2776,7 @@
         <v>27</v>
       </c>
       <c r="O11" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="P11" t="s">
         <v>24</v>
@@ -1411,41 +2785,41 @@
         <v>24</v>
       </c>
       <c r="R11" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="S11" s="8"/>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B12" s="3">
         <v>455</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G12" t="s">
-        <v>61</v>
-      </c>
-      <c r="H12" s="5"/>
+        <v>54</v>
+      </c>
+      <c r="H12" s="6"/>
       <c r="I12" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="J12" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="K12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L12" t="s">
         <v>22</v>
@@ -1457,7 +2831,7 @@
         <v>27</v>
       </c>
       <c r="O12" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="P12" t="s">
         <v>24</v>
@@ -1466,41 +2840,41 @@
         <v>24</v>
       </c>
       <c r="R12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="S12" s="8"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13" s="3">
         <v>455</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E13" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" t="s">
         <v>52</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
+        <v>54</v>
+      </c>
+      <c r="H13" s="6"/>
+      <c r="I13" t="s">
+        <v>53</v>
+      </c>
+      <c r="J13" t="s">
         <v>56</v>
       </c>
-      <c r="G13" t="s">
-        <v>61</v>
-      </c>
-      <c r="H13" s="5"/>
-      <c r="I13" t="s">
-        <v>60</v>
-      </c>
-      <c r="J13" t="s">
-        <v>63</v>
-      </c>
       <c r="K13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L13" t="s">
         <v>22</v>
@@ -1512,7 +2886,7 @@
         <v>27</v>
       </c>
       <c r="O13" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="P13" t="s">
         <v>24</v>
@@ -1521,12 +2895,4301 @@
         <v>24</v>
       </c>
       <c r="R13" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="S13" s="8"/>
     </row>
+    <row r="14" spans="1:21" ht="131.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" s="3">
+        <v>523</v>
+      </c>
+      <c r="C14" t="s">
+        <v>174</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I14" t="s">
+        <v>76</v>
+      </c>
+      <c r="J14" t="s">
+        <v>78</v>
+      </c>
+      <c r="K14" t="s">
+        <v>36</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="M14" t="s">
+        <v>24</v>
+      </c>
+      <c r="N14" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" t="s">
+        <v>81</v>
+      </c>
+      <c r="P14" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>24</v>
+      </c>
+      <c r="R14" t="s">
+        <v>24</v>
+      </c>
+      <c r="S14" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="3">
+        <v>523</v>
+      </c>
+      <c r="C15" t="s">
+        <v>174</v>
+      </c>
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" t="s">
+        <v>71</v>
+      </c>
+      <c r="G15" t="s">
+        <v>70</v>
+      </c>
+      <c r="H15" s="6"/>
+      <c r="I15" t="s">
+        <v>76</v>
+      </c>
+      <c r="J15" t="s">
+        <v>78</v>
+      </c>
+      <c r="K15" t="s">
+        <v>36</v>
+      </c>
+      <c r="L15" s="7"/>
+      <c r="M15" t="s">
+        <v>24</v>
+      </c>
+      <c r="N15" t="s">
+        <v>27</v>
+      </c>
+      <c r="O15" t="s">
+        <v>81</v>
+      </c>
+      <c r="P15" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>24</v>
+      </c>
+      <c r="R15" t="s">
+        <v>24</v>
+      </c>
+      <c r="S15" s="8"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="3">
+        <v>523</v>
+      </c>
+      <c r="C16" t="s">
+        <v>174</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" t="s">
+        <v>70</v>
+      </c>
+      <c r="H16" s="6"/>
+      <c r="I16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J16" t="s">
+        <v>78</v>
+      </c>
+      <c r="K16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L16" s="7"/>
+      <c r="M16" t="s">
+        <v>24</v>
+      </c>
+      <c r="N16" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" t="s">
+        <v>81</v>
+      </c>
+      <c r="P16" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>24</v>
+      </c>
+      <c r="R16" t="s">
+        <v>24</v>
+      </c>
+      <c r="S16" s="8"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="3">
+        <v>523</v>
+      </c>
+      <c r="C17" t="s">
+        <v>174</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" t="s">
+        <v>70</v>
+      </c>
+      <c r="H17" s="6"/>
+      <c r="I17" t="s">
+        <v>76</v>
+      </c>
+      <c r="J17" t="s">
+        <v>78</v>
+      </c>
+      <c r="K17" t="s">
+        <v>36</v>
+      </c>
+      <c r="L17" s="7"/>
+      <c r="M17" t="s">
+        <v>24</v>
+      </c>
+      <c r="N17" t="s">
+        <v>27</v>
+      </c>
+      <c r="O17" t="s">
+        <v>81</v>
+      </c>
+      <c r="P17" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>24</v>
+      </c>
+      <c r="R17" t="s">
+        <v>24</v>
+      </c>
+      <c r="S17" s="8"/>
+    </row>
+    <row r="18" spans="1:19" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" s="3">
+        <v>582</v>
+      </c>
+      <c r="C18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" t="s">
+        <v>88</v>
+      </c>
+      <c r="E18" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" t="s">
+        <v>93</v>
+      </c>
+      <c r="G18" t="s">
+        <v>89</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I18" t="s">
+        <v>94</v>
+      </c>
+      <c r="J18" t="s">
+        <v>95</v>
+      </c>
+      <c r="K18" t="s">
+        <v>36</v>
+      </c>
+      <c r="L18" t="s">
+        <v>22</v>
+      </c>
+      <c r="M18" t="s">
+        <v>27</v>
+      </c>
+      <c r="N18" t="s">
+        <v>97</v>
+      </c>
+      <c r="O18" t="s">
+        <v>24</v>
+      </c>
+      <c r="P18" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>24</v>
+      </c>
+      <c r="R18" t="s">
+        <v>27</v>
+      </c>
+      <c r="S18" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" s="3">
+        <v>582</v>
+      </c>
+      <c r="C19" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" t="s">
+        <v>88</v>
+      </c>
+      <c r="E19" t="s">
+        <v>90</v>
+      </c>
+      <c r="F19" t="s">
+        <v>93</v>
+      </c>
+      <c r="G19" t="s">
+        <v>89</v>
+      </c>
+      <c r="H19" s="6"/>
+      <c r="I19" t="s">
+        <v>94</v>
+      </c>
+      <c r="J19" t="s">
+        <v>95</v>
+      </c>
+      <c r="K19" t="s">
+        <v>36</v>
+      </c>
+      <c r="L19" t="s">
+        <v>22</v>
+      </c>
+      <c r="M19" t="s">
+        <v>27</v>
+      </c>
+      <c r="N19" t="s">
+        <v>97</v>
+      </c>
+      <c r="O19" t="s">
+        <v>24</v>
+      </c>
+      <c r="P19" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>24</v>
+      </c>
+      <c r="R19" t="s">
+        <v>27</v>
+      </c>
+      <c r="S19" s="8"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="3">
+        <v>582</v>
+      </c>
+      <c r="C20" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" t="s">
+        <v>88</v>
+      </c>
+      <c r="E20" t="s">
+        <v>91</v>
+      </c>
+      <c r="F20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G20" t="s">
+        <v>89</v>
+      </c>
+      <c r="H20" s="6"/>
+      <c r="I20" t="s">
+        <v>94</v>
+      </c>
+      <c r="J20" t="s">
+        <v>95</v>
+      </c>
+      <c r="K20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L20" t="s">
+        <v>22</v>
+      </c>
+      <c r="M20" t="s">
+        <v>27</v>
+      </c>
+      <c r="N20" t="s">
+        <v>97</v>
+      </c>
+      <c r="O20" t="s">
+        <v>24</v>
+      </c>
+      <c r="P20" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>24</v>
+      </c>
+      <c r="R20" t="s">
+        <v>27</v>
+      </c>
+      <c r="S20" s="8"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" s="3">
+        <v>582</v>
+      </c>
+      <c r="C21" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" t="s">
+        <v>92</v>
+      </c>
+      <c r="F21" t="s">
+        <v>93</v>
+      </c>
+      <c r="G21" t="s">
+        <v>89</v>
+      </c>
+      <c r="H21" s="6"/>
+      <c r="I21" t="s">
+        <v>94</v>
+      </c>
+      <c r="J21" t="s">
+        <v>95</v>
+      </c>
+      <c r="K21" t="s">
+        <v>36</v>
+      </c>
+      <c r="L21" t="s">
+        <v>22</v>
+      </c>
+      <c r="M21" t="s">
+        <v>27</v>
+      </c>
+      <c r="N21" t="s">
+        <v>97</v>
+      </c>
+      <c r="O21" t="s">
+        <v>24</v>
+      </c>
+      <c r="P21" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>24</v>
+      </c>
+      <c r="R21" t="s">
+        <v>27</v>
+      </c>
+      <c r="S21" s="8"/>
+    </row>
+    <row r="22" spans="1:19" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" s="3">
+        <v>639</v>
+      </c>
+      <c r="C22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" t="s">
+        <v>99</v>
+      </c>
+      <c r="E22" t="s">
+        <v>72</v>
+      </c>
+      <c r="F22" t="s">
+        <v>104</v>
+      </c>
+      <c r="G22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I22" t="s">
+        <v>105</v>
+      </c>
+      <c r="J22" t="s">
+        <v>106</v>
+      </c>
+      <c r="K22" t="s">
+        <v>36</v>
+      </c>
+      <c r="L22" t="s">
+        <v>22</v>
+      </c>
+      <c r="M22" t="s">
+        <v>27</v>
+      </c>
+      <c r="N22" t="s">
+        <v>27</v>
+      </c>
+      <c r="O22" t="s">
+        <v>27</v>
+      </c>
+      <c r="P22" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>107</v>
+      </c>
+      <c r="R22" t="s">
+        <v>27</v>
+      </c>
+      <c r="S22" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>98</v>
+      </c>
+      <c r="B23" s="3">
+        <v>639</v>
+      </c>
+      <c r="C23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" t="s">
+        <v>99</v>
+      </c>
+      <c r="E23" t="s">
+        <v>101</v>
+      </c>
+      <c r="F23" t="s">
+        <v>104</v>
+      </c>
+      <c r="G23" t="s">
+        <v>100</v>
+      </c>
+      <c r="H23" s="6"/>
+      <c r="I23" t="s">
+        <v>105</v>
+      </c>
+      <c r="J23" t="s">
+        <v>106</v>
+      </c>
+      <c r="K23" t="s">
+        <v>36</v>
+      </c>
+      <c r="L23" t="s">
+        <v>22</v>
+      </c>
+      <c r="M23" t="s">
+        <v>27</v>
+      </c>
+      <c r="N23" t="s">
+        <v>27</v>
+      </c>
+      <c r="O23" t="s">
+        <v>27</v>
+      </c>
+      <c r="P23" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>107</v>
+      </c>
+      <c r="R23" t="s">
+        <v>27</v>
+      </c>
+      <c r="S23" s="8"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" s="3">
+        <v>639</v>
+      </c>
+      <c r="C24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" t="s">
+        <v>102</v>
+      </c>
+      <c r="F24" t="s">
+        <v>104</v>
+      </c>
+      <c r="G24" t="s">
+        <v>100</v>
+      </c>
+      <c r="H24" s="6"/>
+      <c r="I24" t="s">
+        <v>105</v>
+      </c>
+      <c r="J24" t="s">
+        <v>106</v>
+      </c>
+      <c r="K24" t="s">
+        <v>36</v>
+      </c>
+      <c r="L24" t="s">
+        <v>22</v>
+      </c>
+      <c r="M24" t="s">
+        <v>27</v>
+      </c>
+      <c r="N24" t="s">
+        <v>27</v>
+      </c>
+      <c r="O24" t="s">
+        <v>27</v>
+      </c>
+      <c r="P24" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>107</v>
+      </c>
+      <c r="R24" t="s">
+        <v>27</v>
+      </c>
+      <c r="S24" s="8"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" s="3">
+        <v>639</v>
+      </c>
+      <c r="C25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" t="s">
+        <v>99</v>
+      </c>
+      <c r="E25" t="s">
+        <v>103</v>
+      </c>
+      <c r="F25" t="s">
+        <v>104</v>
+      </c>
+      <c r="G25" t="s">
+        <v>100</v>
+      </c>
+      <c r="H25" s="6"/>
+      <c r="I25" t="s">
+        <v>105</v>
+      </c>
+      <c r="J25" t="s">
+        <v>106</v>
+      </c>
+      <c r="K25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L25" t="s">
+        <v>22</v>
+      </c>
+      <c r="M25" t="s">
+        <v>27</v>
+      </c>
+      <c r="N25" t="s">
+        <v>27</v>
+      </c>
+      <c r="O25" t="s">
+        <v>27</v>
+      </c>
+      <c r="P25" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>107</v>
+      </c>
+      <c r="R25" t="s">
+        <v>27</v>
+      </c>
+      <c r="S25" s="8"/>
+    </row>
+    <row r="26" spans="1:19" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="3">
+        <v>697</v>
+      </c>
+      <c r="C26" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" t="s">
+        <v>112</v>
+      </c>
+      <c r="E26" t="s">
+        <v>72</v>
+      </c>
+      <c r="F26" t="s">
+        <v>117</v>
+      </c>
+      <c r="G26" t="s">
+        <v>113</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I26" t="s">
+        <v>118</v>
+      </c>
+      <c r="J26" t="s">
+        <v>119</v>
+      </c>
+      <c r="K26" t="s">
+        <v>36</v>
+      </c>
+      <c r="L26" t="s">
+        <v>22</v>
+      </c>
+      <c r="M26" t="s">
+        <v>27</v>
+      </c>
+      <c r="N26" t="s">
+        <v>27</v>
+      </c>
+      <c r="O26" t="s">
+        <v>120</v>
+      </c>
+      <c r="P26" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>24</v>
+      </c>
+      <c r="R26" t="s">
+        <v>27</v>
+      </c>
+      <c r="S26" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>111</v>
+      </c>
+      <c r="B27" s="3">
+        <v>697</v>
+      </c>
+      <c r="C27" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" t="s">
+        <v>112</v>
+      </c>
+      <c r="E27" t="s">
+        <v>114</v>
+      </c>
+      <c r="F27" t="s">
+        <v>117</v>
+      </c>
+      <c r="G27" t="s">
+        <v>113</v>
+      </c>
+      <c r="H27" s="6"/>
+      <c r="I27" t="s">
+        <v>118</v>
+      </c>
+      <c r="J27" t="s">
+        <v>119</v>
+      </c>
+      <c r="K27" t="s">
+        <v>36</v>
+      </c>
+      <c r="L27" t="s">
+        <v>22</v>
+      </c>
+      <c r="M27" t="s">
+        <v>27</v>
+      </c>
+      <c r="N27" t="s">
+        <v>27</v>
+      </c>
+      <c r="O27" t="s">
+        <v>120</v>
+      </c>
+      <c r="P27" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>24</v>
+      </c>
+      <c r="R27" t="s">
+        <v>27</v>
+      </c>
+      <c r="S27" s="8"/>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>111</v>
+      </c>
+      <c r="B28" s="3">
+        <v>697</v>
+      </c>
+      <c r="C28" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" t="s">
+        <v>112</v>
+      </c>
+      <c r="E28" t="s">
+        <v>115</v>
+      </c>
+      <c r="F28" t="s">
+        <v>117</v>
+      </c>
+      <c r="G28" t="s">
+        <v>113</v>
+      </c>
+      <c r="H28" s="6"/>
+      <c r="I28" t="s">
+        <v>118</v>
+      </c>
+      <c r="J28" t="s">
+        <v>119</v>
+      </c>
+      <c r="K28" t="s">
+        <v>36</v>
+      </c>
+      <c r="L28" t="s">
+        <v>22</v>
+      </c>
+      <c r="M28" t="s">
+        <v>27</v>
+      </c>
+      <c r="N28" t="s">
+        <v>27</v>
+      </c>
+      <c r="O28" t="s">
+        <v>120</v>
+      </c>
+      <c r="P28" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>24</v>
+      </c>
+      <c r="R28" t="s">
+        <v>27</v>
+      </c>
+      <c r="S28" s="8"/>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" s="3">
+        <v>697</v>
+      </c>
+      <c r="C29" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" t="s">
+        <v>112</v>
+      </c>
+      <c r="E29" t="s">
+        <v>116</v>
+      </c>
+      <c r="F29" t="s">
+        <v>117</v>
+      </c>
+      <c r="G29" t="s">
+        <v>113</v>
+      </c>
+      <c r="H29" s="6"/>
+      <c r="I29" t="s">
+        <v>118</v>
+      </c>
+      <c r="J29" t="s">
+        <v>119</v>
+      </c>
+      <c r="K29" t="s">
+        <v>36</v>
+      </c>
+      <c r="L29" t="s">
+        <v>22</v>
+      </c>
+      <c r="M29" t="s">
+        <v>27</v>
+      </c>
+      <c r="N29" t="s">
+        <v>27</v>
+      </c>
+      <c r="O29" t="s">
+        <v>120</v>
+      </c>
+      <c r="P29" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>24</v>
+      </c>
+      <c r="R29" t="s">
+        <v>27</v>
+      </c>
+      <c r="S29" s="8"/>
+    </row>
+    <row r="30" spans="1:19" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>123</v>
+      </c>
+      <c r="B30" s="3">
+        <v>755</v>
+      </c>
+      <c r="C30" t="s">
+        <v>174</v>
+      </c>
+      <c r="D30" t="s">
+        <v>124</v>
+      </c>
+      <c r="E30" t="s">
+        <v>72</v>
+      </c>
+      <c r="F30" t="s">
+        <v>126</v>
+      </c>
+      <c r="G30" t="s">
+        <v>125</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I30" t="s">
+        <v>130</v>
+      </c>
+      <c r="J30" t="s">
+        <v>131</v>
+      </c>
+      <c r="K30" t="s">
+        <v>36</v>
+      </c>
+      <c r="L30" t="s">
+        <v>22</v>
+      </c>
+      <c r="M30" t="s">
+        <v>27</v>
+      </c>
+      <c r="N30" t="s">
+        <v>27</v>
+      </c>
+      <c r="O30" t="s">
+        <v>132</v>
+      </c>
+      <c r="P30" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>24</v>
+      </c>
+      <c r="R30" t="s">
+        <v>134</v>
+      </c>
+      <c r="S30" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>123</v>
+      </c>
+      <c r="B31" s="3">
+        <v>755</v>
+      </c>
+      <c r="C31" t="s">
+        <v>174</v>
+      </c>
+      <c r="D31" t="s">
+        <v>124</v>
+      </c>
+      <c r="E31" t="s">
+        <v>127</v>
+      </c>
+      <c r="F31" t="s">
+        <v>126</v>
+      </c>
+      <c r="G31" t="s">
+        <v>125</v>
+      </c>
+      <c r="H31" s="6"/>
+      <c r="I31" t="s">
+        <v>130</v>
+      </c>
+      <c r="J31" t="s">
+        <v>131</v>
+      </c>
+      <c r="K31" t="s">
+        <v>36</v>
+      </c>
+      <c r="L31" t="s">
+        <v>22</v>
+      </c>
+      <c r="M31" t="s">
+        <v>27</v>
+      </c>
+      <c r="N31" t="s">
+        <v>27</v>
+      </c>
+      <c r="O31" t="s">
+        <v>132</v>
+      </c>
+      <c r="P31" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>24</v>
+      </c>
+      <c r="R31" t="s">
+        <v>134</v>
+      </c>
+      <c r="S31" s="8"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>123</v>
+      </c>
+      <c r="B32" s="3">
+        <v>755</v>
+      </c>
+      <c r="C32" t="s">
+        <v>174</v>
+      </c>
+      <c r="D32" t="s">
+        <v>124</v>
+      </c>
+      <c r="E32" t="s">
+        <v>128</v>
+      </c>
+      <c r="F32" t="s">
+        <v>126</v>
+      </c>
+      <c r="G32" t="s">
+        <v>125</v>
+      </c>
+      <c r="H32" s="6"/>
+      <c r="I32" t="s">
+        <v>130</v>
+      </c>
+      <c r="J32" t="s">
+        <v>131</v>
+      </c>
+      <c r="K32" t="s">
+        <v>36</v>
+      </c>
+      <c r="L32" t="s">
+        <v>22</v>
+      </c>
+      <c r="M32" t="s">
+        <v>27</v>
+      </c>
+      <c r="N32" t="s">
+        <v>27</v>
+      </c>
+      <c r="O32" t="s">
+        <v>132</v>
+      </c>
+      <c r="P32" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>24</v>
+      </c>
+      <c r="R32" t="s">
+        <v>134</v>
+      </c>
+      <c r="S32" s="8"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>123</v>
+      </c>
+      <c r="B33" s="3">
+        <v>755</v>
+      </c>
+      <c r="C33" t="s">
+        <v>174</v>
+      </c>
+      <c r="D33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E33" t="s">
+        <v>129</v>
+      </c>
+      <c r="F33" t="s">
+        <v>126</v>
+      </c>
+      <c r="G33" t="s">
+        <v>125</v>
+      </c>
+      <c r="H33" s="6"/>
+      <c r="I33" t="s">
+        <v>130</v>
+      </c>
+      <c r="J33" t="s">
+        <v>131</v>
+      </c>
+      <c r="K33" t="s">
+        <v>36</v>
+      </c>
+      <c r="L33" t="s">
+        <v>22</v>
+      </c>
+      <c r="M33" t="s">
+        <v>27</v>
+      </c>
+      <c r="N33" t="s">
+        <v>27</v>
+      </c>
+      <c r="O33" t="s">
+        <v>132</v>
+      </c>
+      <c r="P33" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>24</v>
+      </c>
+      <c r="R33" t="s">
+        <v>134</v>
+      </c>
+      <c r="S33" s="8"/>
+    </row>
+    <row r="34" spans="1:19" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>136</v>
+      </c>
+      <c r="B34" s="3">
+        <v>813</v>
+      </c>
+      <c r="C34" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" t="s">
+        <v>137</v>
+      </c>
+      <c r="E34" t="s">
+        <v>72</v>
+      </c>
+      <c r="F34" t="s">
+        <v>139</v>
+      </c>
+      <c r="G34" t="s">
+        <v>138</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I34" t="s">
+        <v>143</v>
+      </c>
+      <c r="J34" t="s">
+        <v>144</v>
+      </c>
+      <c r="K34" t="s">
+        <v>36</v>
+      </c>
+      <c r="L34" t="s">
+        <v>22</v>
+      </c>
+      <c r="M34" t="s">
+        <v>27</v>
+      </c>
+      <c r="N34" t="s">
+        <v>27</v>
+      </c>
+      <c r="O34" t="s">
+        <v>27</v>
+      </c>
+      <c r="P34" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>145</v>
+      </c>
+      <c r="R34" t="s">
+        <v>146</v>
+      </c>
+      <c r="S34" s="8" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>136</v>
+      </c>
+      <c r="B35" s="3">
+        <v>813</v>
+      </c>
+      <c r="C35" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" t="s">
+        <v>137</v>
+      </c>
+      <c r="E35" t="s">
+        <v>140</v>
+      </c>
+      <c r="F35" t="s">
+        <v>139</v>
+      </c>
+      <c r="G35" t="s">
+        <v>138</v>
+      </c>
+      <c r="H35" s="6"/>
+      <c r="I35" t="s">
+        <v>143</v>
+      </c>
+      <c r="J35" t="s">
+        <v>144</v>
+      </c>
+      <c r="K35" t="s">
+        <v>36</v>
+      </c>
+      <c r="L35" t="s">
+        <v>22</v>
+      </c>
+      <c r="M35" t="s">
+        <v>27</v>
+      </c>
+      <c r="N35" t="s">
+        <v>27</v>
+      </c>
+      <c r="O35" t="s">
+        <v>27</v>
+      </c>
+      <c r="P35" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>145</v>
+      </c>
+      <c r="R35" t="s">
+        <v>146</v>
+      </c>
+      <c r="S35" s="8"/>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>136</v>
+      </c>
+      <c r="B36" s="3">
+        <v>813</v>
+      </c>
+      <c r="C36" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" t="s">
+        <v>137</v>
+      </c>
+      <c r="E36" t="s">
+        <v>141</v>
+      </c>
+      <c r="F36" t="s">
+        <v>139</v>
+      </c>
+      <c r="G36" t="s">
+        <v>138</v>
+      </c>
+      <c r="H36" s="6"/>
+      <c r="I36" t="s">
+        <v>143</v>
+      </c>
+      <c r="J36" t="s">
+        <v>144</v>
+      </c>
+      <c r="K36" t="s">
+        <v>36</v>
+      </c>
+      <c r="L36" t="s">
+        <v>22</v>
+      </c>
+      <c r="M36" t="s">
+        <v>27</v>
+      </c>
+      <c r="N36" t="s">
+        <v>27</v>
+      </c>
+      <c r="O36" t="s">
+        <v>27</v>
+      </c>
+      <c r="P36" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>145</v>
+      </c>
+      <c r="R36" t="s">
+        <v>146</v>
+      </c>
+      <c r="S36" s="8"/>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>136</v>
+      </c>
+      <c r="B37" s="3">
+        <v>813</v>
+      </c>
+      <c r="C37" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" t="s">
+        <v>137</v>
+      </c>
+      <c r="E37" t="s">
+        <v>142</v>
+      </c>
+      <c r="F37" t="s">
+        <v>139</v>
+      </c>
+      <c r="G37" t="s">
+        <v>138</v>
+      </c>
+      <c r="H37" s="6"/>
+      <c r="I37" t="s">
+        <v>143</v>
+      </c>
+      <c r="J37" t="s">
+        <v>144</v>
+      </c>
+      <c r="K37" t="s">
+        <v>36</v>
+      </c>
+      <c r="L37" t="s">
+        <v>22</v>
+      </c>
+      <c r="M37" t="s">
+        <v>27</v>
+      </c>
+      <c r="N37" t="s">
+        <v>27</v>
+      </c>
+      <c r="O37" t="s">
+        <v>27</v>
+      </c>
+      <c r="P37" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>145</v>
+      </c>
+      <c r="R37" t="s">
+        <v>146</v>
+      </c>
+      <c r="S37" s="8"/>
+    </row>
+    <row r="38" spans="1:19" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>151</v>
+      </c>
+      <c r="B38" s="3">
+        <v>871</v>
+      </c>
+      <c r="C38" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" t="s">
+        <v>152</v>
+      </c>
+      <c r="E38" t="s">
+        <v>72</v>
+      </c>
+      <c r="F38" t="s">
+        <v>148</v>
+      </c>
+      <c r="G38" t="s">
+        <v>153</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I38" t="s">
+        <v>149</v>
+      </c>
+      <c r="J38" t="s">
+        <v>150</v>
+      </c>
+      <c r="K38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L38" t="s">
+        <v>22</v>
+      </c>
+      <c r="M38" t="s">
+        <v>157</v>
+      </c>
+      <c r="N38" t="s">
+        <v>24</v>
+      </c>
+      <c r="O38" t="s">
+        <v>27</v>
+      </c>
+      <c r="P38" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>27</v>
+      </c>
+      <c r="R38" t="s">
+        <v>27</v>
+      </c>
+      <c r="S38" s="8" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>151</v>
+      </c>
+      <c r="B39" s="3">
+        <v>871</v>
+      </c>
+      <c r="C39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" t="s">
+        <v>152</v>
+      </c>
+      <c r="E39" t="s">
+        <v>154</v>
+      </c>
+      <c r="F39" t="s">
+        <v>148</v>
+      </c>
+      <c r="G39" t="s">
+        <v>153</v>
+      </c>
+      <c r="H39" s="6"/>
+      <c r="I39" t="s">
+        <v>149</v>
+      </c>
+      <c r="J39" t="s">
+        <v>150</v>
+      </c>
+      <c r="K39" t="s">
+        <v>36</v>
+      </c>
+      <c r="L39" t="s">
+        <v>22</v>
+      </c>
+      <c r="M39" t="s">
+        <v>157</v>
+      </c>
+      <c r="N39" t="s">
+        <v>24</v>
+      </c>
+      <c r="O39" t="s">
+        <v>27</v>
+      </c>
+      <c r="P39" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>27</v>
+      </c>
+      <c r="R39" t="s">
+        <v>27</v>
+      </c>
+      <c r="S39" s="8"/>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>151</v>
+      </c>
+      <c r="B40" s="3">
+        <v>871</v>
+      </c>
+      <c r="C40" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" t="s">
+        <v>152</v>
+      </c>
+      <c r="E40" t="s">
+        <v>155</v>
+      </c>
+      <c r="F40" t="s">
+        <v>148</v>
+      </c>
+      <c r="G40" t="s">
+        <v>153</v>
+      </c>
+      <c r="H40" s="6"/>
+      <c r="I40" t="s">
+        <v>149</v>
+      </c>
+      <c r="J40" t="s">
+        <v>150</v>
+      </c>
+      <c r="K40" t="s">
+        <v>36</v>
+      </c>
+      <c r="L40" t="s">
+        <v>22</v>
+      </c>
+      <c r="M40" t="s">
+        <v>157</v>
+      </c>
+      <c r="N40" t="s">
+        <v>24</v>
+      </c>
+      <c r="O40" t="s">
+        <v>27</v>
+      </c>
+      <c r="P40" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>27</v>
+      </c>
+      <c r="R40" t="s">
+        <v>27</v>
+      </c>
+      <c r="S40" s="8"/>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>151</v>
+      </c>
+      <c r="B41" s="3">
+        <v>871</v>
+      </c>
+      <c r="C41" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" t="s">
+        <v>152</v>
+      </c>
+      <c r="E41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F41" t="s">
+        <v>148</v>
+      </c>
+      <c r="G41" t="s">
+        <v>153</v>
+      </c>
+      <c r="H41" s="6"/>
+      <c r="I41" t="s">
+        <v>149</v>
+      </c>
+      <c r="J41" t="s">
+        <v>150</v>
+      </c>
+      <c r="K41" t="s">
+        <v>36</v>
+      </c>
+      <c r="L41" t="s">
+        <v>22</v>
+      </c>
+      <c r="M41" t="s">
+        <v>157</v>
+      </c>
+      <c r="N41" t="s">
+        <v>24</v>
+      </c>
+      <c r="O41" t="s">
+        <v>27</v>
+      </c>
+      <c r="P41" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>27</v>
+      </c>
+      <c r="R41" t="s">
+        <v>27</v>
+      </c>
+      <c r="S41" s="8"/>
+    </row>
+    <row r="42" spans="1:19" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>159</v>
+      </c>
+      <c r="B42" s="3">
+        <v>929</v>
+      </c>
+      <c r="C42" t="s">
+        <v>160</v>
+      </c>
+      <c r="D42" t="s">
+        <v>161</v>
+      </c>
+      <c r="E42" t="s">
+        <v>72</v>
+      </c>
+      <c r="F42" t="s">
+        <v>163</v>
+      </c>
+      <c r="G42" t="s">
+        <v>162</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I42" t="s">
+        <v>167</v>
+      </c>
+      <c r="J42" t="s">
+        <v>168</v>
+      </c>
+      <c r="K42" t="s">
+        <v>36</v>
+      </c>
+      <c r="L42" t="s">
+        <v>22</v>
+      </c>
+      <c r="M42" t="s">
+        <v>27</v>
+      </c>
+      <c r="N42" t="s">
+        <v>171</v>
+      </c>
+      <c r="O42" t="s">
+        <v>169</v>
+      </c>
+      <c r="P42" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>170</v>
+      </c>
+      <c r="R42" t="s">
+        <v>27</v>
+      </c>
+      <c r="S42" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>159</v>
+      </c>
+      <c r="B43" s="3">
+        <v>929</v>
+      </c>
+      <c r="C43" t="s">
+        <v>160</v>
+      </c>
+      <c r="D43" t="s">
+        <v>161</v>
+      </c>
+      <c r="E43" t="s">
+        <v>164</v>
+      </c>
+      <c r="F43" t="s">
+        <v>163</v>
+      </c>
+      <c r="G43" t="s">
+        <v>162</v>
+      </c>
+      <c r="H43" s="6"/>
+      <c r="I43" t="s">
+        <v>167</v>
+      </c>
+      <c r="J43" t="s">
+        <v>168</v>
+      </c>
+      <c r="K43" t="s">
+        <v>36</v>
+      </c>
+      <c r="L43" t="s">
+        <v>22</v>
+      </c>
+      <c r="M43" t="s">
+        <v>27</v>
+      </c>
+      <c r="N43" t="s">
+        <v>171</v>
+      </c>
+      <c r="O43" t="s">
+        <v>169</v>
+      </c>
+      <c r="P43" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>170</v>
+      </c>
+      <c r="R43" t="s">
+        <v>27</v>
+      </c>
+      <c r="S43" s="8"/>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>159</v>
+      </c>
+      <c r="B44" s="3">
+        <v>929</v>
+      </c>
+      <c r="C44" t="s">
+        <v>160</v>
+      </c>
+      <c r="D44" t="s">
+        <v>161</v>
+      </c>
+      <c r="E44" t="s">
+        <v>165</v>
+      </c>
+      <c r="F44" t="s">
+        <v>163</v>
+      </c>
+      <c r="G44" t="s">
+        <v>162</v>
+      </c>
+      <c r="H44" s="6"/>
+      <c r="I44" t="s">
+        <v>167</v>
+      </c>
+      <c r="J44" t="s">
+        <v>168</v>
+      </c>
+      <c r="K44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L44" t="s">
+        <v>22</v>
+      </c>
+      <c r="M44" t="s">
+        <v>27</v>
+      </c>
+      <c r="N44" t="s">
+        <v>171</v>
+      </c>
+      <c r="O44" t="s">
+        <v>169</v>
+      </c>
+      <c r="P44" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>170</v>
+      </c>
+      <c r="R44" t="s">
+        <v>27</v>
+      </c>
+      <c r="S44" s="8"/>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>159</v>
+      </c>
+      <c r="B45" s="3">
+        <v>929</v>
+      </c>
+      <c r="C45" t="s">
+        <v>160</v>
+      </c>
+      <c r="D45" t="s">
+        <v>161</v>
+      </c>
+      <c r="E45" t="s">
+        <v>166</v>
+      </c>
+      <c r="F45" t="s">
+        <v>163</v>
+      </c>
+      <c r="G45" t="s">
+        <v>162</v>
+      </c>
+      <c r="H45" s="6"/>
+      <c r="I45" t="s">
+        <v>167</v>
+      </c>
+      <c r="J45" t="s">
+        <v>168</v>
+      </c>
+      <c r="K45" t="s">
+        <v>36</v>
+      </c>
+      <c r="L45" t="s">
+        <v>22</v>
+      </c>
+      <c r="M45" t="s">
+        <v>27</v>
+      </c>
+      <c r="N45" t="s">
+        <v>171</v>
+      </c>
+      <c r="O45" t="s">
+        <v>169</v>
+      </c>
+      <c r="P45" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>170</v>
+      </c>
+      <c r="R45" t="s">
+        <v>27</v>
+      </c>
+      <c r="S45" s="8"/>
+    </row>
+    <row r="46" spans="1:19" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>173</v>
+      </c>
+      <c r="B46" s="3">
+        <v>987</v>
+      </c>
+      <c r="C46" t="s">
+        <v>174</v>
+      </c>
+      <c r="D46" t="s">
+        <v>175</v>
+      </c>
+      <c r="E46" t="s">
+        <v>72</v>
+      </c>
+      <c r="F46" t="s">
+        <v>176</v>
+      </c>
+      <c r="G46" t="s">
+        <v>177</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I46" t="s">
+        <v>178</v>
+      </c>
+      <c r="J46" t="s">
+        <v>179</v>
+      </c>
+      <c r="K46" t="s">
+        <v>36</v>
+      </c>
+      <c r="L46" t="s">
+        <v>22</v>
+      </c>
+      <c r="M46" t="s">
+        <v>185</v>
+      </c>
+      <c r="N46" t="s">
+        <v>183</v>
+      </c>
+      <c r="O46" t="s">
+        <v>184</v>
+      </c>
+      <c r="P46" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>27</v>
+      </c>
+      <c r="R46" t="s">
+        <v>27</v>
+      </c>
+      <c r="S46" s="8" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>173</v>
+      </c>
+      <c r="B47" s="3">
+        <v>987</v>
+      </c>
+      <c r="C47" t="s">
+        <v>174</v>
+      </c>
+      <c r="D47" t="s">
+        <v>175</v>
+      </c>
+      <c r="E47" t="s">
+        <v>180</v>
+      </c>
+      <c r="F47" t="s">
+        <v>176</v>
+      </c>
+      <c r="G47" t="s">
+        <v>177</v>
+      </c>
+      <c r="H47" s="6"/>
+      <c r="I47" t="s">
+        <v>178</v>
+      </c>
+      <c r="J47" t="s">
+        <v>179</v>
+      </c>
+      <c r="K47" t="s">
+        <v>36</v>
+      </c>
+      <c r="L47" t="s">
+        <v>22</v>
+      </c>
+      <c r="M47" t="s">
+        <v>185</v>
+      </c>
+      <c r="N47" t="s">
+        <v>183</v>
+      </c>
+      <c r="O47" t="s">
+        <v>184</v>
+      </c>
+      <c r="P47" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>27</v>
+      </c>
+      <c r="R47" t="s">
+        <v>27</v>
+      </c>
+      <c r="S47" s="8"/>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>173</v>
+      </c>
+      <c r="B48" s="3">
+        <v>987</v>
+      </c>
+      <c r="C48" t="s">
+        <v>174</v>
+      </c>
+      <c r="D48" t="s">
+        <v>175</v>
+      </c>
+      <c r="E48" t="s">
+        <v>181</v>
+      </c>
+      <c r="F48" t="s">
+        <v>176</v>
+      </c>
+      <c r="G48" t="s">
+        <v>177</v>
+      </c>
+      <c r="H48" s="6"/>
+      <c r="I48" t="s">
+        <v>178</v>
+      </c>
+      <c r="J48" t="s">
+        <v>179</v>
+      </c>
+      <c r="K48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M48" t="s">
+        <v>185</v>
+      </c>
+      <c r="N48" t="s">
+        <v>183</v>
+      </c>
+      <c r="O48" t="s">
+        <v>184</v>
+      </c>
+      <c r="P48" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>27</v>
+      </c>
+      <c r="R48" t="s">
+        <v>27</v>
+      </c>
+      <c r="S48" s="8"/>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>173</v>
+      </c>
+      <c r="B49" s="3">
+        <v>987</v>
+      </c>
+      <c r="C49" t="s">
+        <v>174</v>
+      </c>
+      <c r="D49" t="s">
+        <v>175</v>
+      </c>
+      <c r="E49" t="s">
+        <v>182</v>
+      </c>
+      <c r="F49" t="s">
+        <v>176</v>
+      </c>
+      <c r="G49" t="s">
+        <v>177</v>
+      </c>
+      <c r="H49" s="6"/>
+      <c r="I49" t="s">
+        <v>178</v>
+      </c>
+      <c r="J49" t="s">
+        <v>179</v>
+      </c>
+      <c r="K49" t="s">
+        <v>36</v>
+      </c>
+      <c r="L49" t="s">
+        <v>22</v>
+      </c>
+      <c r="M49" t="s">
+        <v>185</v>
+      </c>
+      <c r="N49" t="s">
+        <v>183</v>
+      </c>
+      <c r="O49" t="s">
+        <v>184</v>
+      </c>
+      <c r="P49" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>27</v>
+      </c>
+      <c r="R49" t="s">
+        <v>27</v>
+      </c>
+      <c r="S49" s="8"/>
+    </row>
+    <row r="50" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>187</v>
+      </c>
+      <c r="B50" s="3">
+        <v>1045</v>
+      </c>
+      <c r="C50" t="s">
+        <v>160</v>
+      </c>
+      <c r="D50" t="s">
+        <v>188</v>
+      </c>
+      <c r="E50" t="s">
+        <v>193</v>
+      </c>
+      <c r="F50" t="s">
+        <v>190</v>
+      </c>
+      <c r="G50" t="s">
+        <v>189</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I50" t="s">
+        <v>191</v>
+      </c>
+      <c r="J50" t="s">
+        <v>192</v>
+      </c>
+      <c r="K50" t="s">
+        <v>36</v>
+      </c>
+      <c r="L50" t="s">
+        <v>22</v>
+      </c>
+      <c r="M50" t="s">
+        <v>200</v>
+      </c>
+      <c r="N50" t="s">
+        <v>199</v>
+      </c>
+      <c r="O50" t="s">
+        <v>27</v>
+      </c>
+      <c r="P50" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>27</v>
+      </c>
+      <c r="R50" t="s">
+        <v>198</v>
+      </c>
+      <c r="S50" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>187</v>
+      </c>
+      <c r="B51" s="3">
+        <v>1045</v>
+      </c>
+      <c r="C51" t="s">
+        <v>160</v>
+      </c>
+      <c r="D51" t="s">
+        <v>188</v>
+      </c>
+      <c r="E51" t="s">
+        <v>194</v>
+      </c>
+      <c r="F51" t="s">
+        <v>190</v>
+      </c>
+      <c r="G51" t="s">
+        <v>189</v>
+      </c>
+      <c r="H51" s="6"/>
+      <c r="I51" t="s">
+        <v>191</v>
+      </c>
+      <c r="J51" t="s">
+        <v>192</v>
+      </c>
+      <c r="K51" t="s">
+        <v>36</v>
+      </c>
+      <c r="L51" t="s">
+        <v>22</v>
+      </c>
+      <c r="M51" t="s">
+        <v>200</v>
+      </c>
+      <c r="N51" t="s">
+        <v>199</v>
+      </c>
+      <c r="O51" t="s">
+        <v>27</v>
+      </c>
+      <c r="P51" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>27</v>
+      </c>
+      <c r="R51" t="s">
+        <v>198</v>
+      </c>
+      <c r="S51" s="8"/>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>187</v>
+      </c>
+      <c r="B52" s="3">
+        <v>1045</v>
+      </c>
+      <c r="C52" t="s">
+        <v>160</v>
+      </c>
+      <c r="D52" t="s">
+        <v>188</v>
+      </c>
+      <c r="E52" t="s">
+        <v>195</v>
+      </c>
+      <c r="F52" t="s">
+        <v>190</v>
+      </c>
+      <c r="G52" t="s">
+        <v>189</v>
+      </c>
+      <c r="H52" s="6"/>
+      <c r="I52" t="s">
+        <v>191</v>
+      </c>
+      <c r="J52" t="s">
+        <v>192</v>
+      </c>
+      <c r="K52" t="s">
+        <v>36</v>
+      </c>
+      <c r="L52" t="s">
+        <v>22</v>
+      </c>
+      <c r="M52" t="s">
+        <v>200</v>
+      </c>
+      <c r="N52" t="s">
+        <v>199</v>
+      </c>
+      <c r="O52" t="s">
+        <v>27</v>
+      </c>
+      <c r="P52" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>27</v>
+      </c>
+      <c r="R52" t="s">
+        <v>198</v>
+      </c>
+      <c r="S52" s="8"/>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>187</v>
+      </c>
+      <c r="B53" s="3">
+        <v>1045</v>
+      </c>
+      <c r="C53" t="s">
+        <v>160</v>
+      </c>
+      <c r="D53" t="s">
+        <v>188</v>
+      </c>
+      <c r="E53" t="s">
+        <v>196</v>
+      </c>
+      <c r="F53" t="s">
+        <v>190</v>
+      </c>
+      <c r="G53" t="s">
+        <v>189</v>
+      </c>
+      <c r="H53" s="6"/>
+      <c r="I53" t="s">
+        <v>191</v>
+      </c>
+      <c r="J53" t="s">
+        <v>192</v>
+      </c>
+      <c r="K53" t="s">
+        <v>36</v>
+      </c>
+      <c r="L53" t="s">
+        <v>22</v>
+      </c>
+      <c r="M53" t="s">
+        <v>200</v>
+      </c>
+      <c r="N53" t="s">
+        <v>199</v>
+      </c>
+      <c r="O53" t="s">
+        <v>27</v>
+      </c>
+      <c r="P53" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>27</v>
+      </c>
+      <c r="R53" t="s">
+        <v>198</v>
+      </c>
+      <c r="S53" s="8"/>
+    </row>
+    <row r="54" spans="1:19" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>202</v>
+      </c>
+      <c r="B54" s="3">
+        <v>1103</v>
+      </c>
+      <c r="C54" t="s">
+        <v>174</v>
+      </c>
+      <c r="D54" t="s">
+        <v>203</v>
+      </c>
+      <c r="E54" t="s">
+        <v>205</v>
+      </c>
+      <c r="F54" t="s">
+        <v>209</v>
+      </c>
+      <c r="G54" t="s">
+        <v>204</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="I54" t="s">
+        <v>210</v>
+      </c>
+      <c r="J54" t="s">
+        <v>212</v>
+      </c>
+      <c r="K54" t="s">
+        <v>79</v>
+      </c>
+      <c r="L54" t="s">
+        <v>22</v>
+      </c>
+      <c r="M54" t="s">
+        <v>27</v>
+      </c>
+      <c r="N54" t="s">
+        <v>215</v>
+      </c>
+      <c r="O54" t="s">
+        <v>27</v>
+      </c>
+      <c r="P54" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>27</v>
+      </c>
+      <c r="R54" t="s">
+        <v>27</v>
+      </c>
+      <c r="S54" s="8" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>202</v>
+      </c>
+      <c r="B55" s="3">
+        <v>1103</v>
+      </c>
+      <c r="C55" t="s">
+        <v>174</v>
+      </c>
+      <c r="D55" t="s">
+        <v>203</v>
+      </c>
+      <c r="E55" t="s">
+        <v>206</v>
+      </c>
+      <c r="F55" t="s">
+        <v>209</v>
+      </c>
+      <c r="G55" t="s">
+        <v>204</v>
+      </c>
+      <c r="H55" s="6"/>
+      <c r="I55" t="s">
+        <v>210</v>
+      </c>
+      <c r="J55" t="s">
+        <v>212</v>
+      </c>
+      <c r="K55" t="s">
+        <v>79</v>
+      </c>
+      <c r="L55" t="s">
+        <v>22</v>
+      </c>
+      <c r="M55" t="s">
+        <v>27</v>
+      </c>
+      <c r="N55" t="s">
+        <v>215</v>
+      </c>
+      <c r="O55" t="s">
+        <v>27</v>
+      </c>
+      <c r="P55" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>27</v>
+      </c>
+      <c r="R55" t="s">
+        <v>27</v>
+      </c>
+      <c r="S55" s="8"/>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>202</v>
+      </c>
+      <c r="B56" s="3">
+        <v>1103</v>
+      </c>
+      <c r="C56" t="s">
+        <v>174</v>
+      </c>
+      <c r="D56" t="s">
+        <v>203</v>
+      </c>
+      <c r="E56" t="s">
+        <v>207</v>
+      </c>
+      <c r="F56" t="s">
+        <v>209</v>
+      </c>
+      <c r="G56" t="s">
+        <v>204</v>
+      </c>
+      <c r="H56" s="6"/>
+      <c r="I56" t="s">
+        <v>210</v>
+      </c>
+      <c r="J56" t="s">
+        <v>212</v>
+      </c>
+      <c r="K56" t="s">
+        <v>79</v>
+      </c>
+      <c r="L56" t="s">
+        <v>22</v>
+      </c>
+      <c r="M56" t="s">
+        <v>27</v>
+      </c>
+      <c r="N56" t="s">
+        <v>215</v>
+      </c>
+      <c r="O56" t="s">
+        <v>27</v>
+      </c>
+      <c r="P56" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>27</v>
+      </c>
+      <c r="R56" t="s">
+        <v>27</v>
+      </c>
+      <c r="S56" s="8"/>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>202</v>
+      </c>
+      <c r="B57" s="3">
+        <v>1103</v>
+      </c>
+      <c r="C57" t="s">
+        <v>174</v>
+      </c>
+      <c r="D57" t="s">
+        <v>203</v>
+      </c>
+      <c r="E57" t="s">
+        <v>208</v>
+      </c>
+      <c r="F57" t="s">
+        <v>209</v>
+      </c>
+      <c r="G57" t="s">
+        <v>204</v>
+      </c>
+      <c r="H57" s="6"/>
+      <c r="I57" t="s">
+        <v>210</v>
+      </c>
+      <c r="J57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K57" t="s">
+        <v>79</v>
+      </c>
+      <c r="L57" t="s">
+        <v>22</v>
+      </c>
+      <c r="M57" t="s">
+        <v>27</v>
+      </c>
+      <c r="N57" t="s">
+        <v>215</v>
+      </c>
+      <c r="O57" t="s">
+        <v>27</v>
+      </c>
+      <c r="P57" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>27</v>
+      </c>
+      <c r="R57" t="s">
+        <v>27</v>
+      </c>
+      <c r="S57" s="8"/>
+    </row>
+    <row r="58" spans="1:19" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>214</v>
+      </c>
+      <c r="B58" s="3">
+        <v>1161</v>
+      </c>
+      <c r="C58" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" t="s">
+        <v>216</v>
+      </c>
+      <c r="E58" t="s">
+        <v>218</v>
+      </c>
+      <c r="F58" t="s">
+        <v>222</v>
+      </c>
+      <c r="G58" t="s">
+        <v>217</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I58" t="s">
+        <v>223</v>
+      </c>
+      <c r="J58" t="s">
+        <v>224</v>
+      </c>
+      <c r="K58" t="s">
+        <v>36</v>
+      </c>
+      <c r="L58" t="s">
+        <v>22</v>
+      </c>
+      <c r="M58" t="s">
+        <v>27</v>
+      </c>
+      <c r="N58" t="s">
+        <v>27</v>
+      </c>
+      <c r="O58" t="s">
+        <v>225</v>
+      </c>
+      <c r="P58" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>199</v>
+      </c>
+      <c r="R58" t="s">
+        <v>27</v>
+      </c>
+      <c r="S58" s="8" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>214</v>
+      </c>
+      <c r="B59" s="3">
+        <v>1161</v>
+      </c>
+      <c r="C59" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" t="s">
+        <v>216</v>
+      </c>
+      <c r="E59" t="s">
+        <v>219</v>
+      </c>
+      <c r="F59" t="s">
+        <v>222</v>
+      </c>
+      <c r="G59" t="s">
+        <v>217</v>
+      </c>
+      <c r="H59" s="6"/>
+      <c r="I59" t="s">
+        <v>223</v>
+      </c>
+      <c r="J59" t="s">
+        <v>224</v>
+      </c>
+      <c r="K59" t="s">
+        <v>36</v>
+      </c>
+      <c r="L59" t="s">
+        <v>22</v>
+      </c>
+      <c r="M59" t="s">
+        <v>27</v>
+      </c>
+      <c r="N59" t="s">
+        <v>27</v>
+      </c>
+      <c r="O59" t="s">
+        <v>225</v>
+      </c>
+      <c r="P59" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>199</v>
+      </c>
+      <c r="R59" t="s">
+        <v>27</v>
+      </c>
+      <c r="S59" s="8"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>214</v>
+      </c>
+      <c r="B60" s="3">
+        <v>1161</v>
+      </c>
+      <c r="C60" t="s">
+        <v>3</v>
+      </c>
+      <c r="D60" t="s">
+        <v>216</v>
+      </c>
+      <c r="E60" t="s">
+        <v>220</v>
+      </c>
+      <c r="F60" t="s">
+        <v>222</v>
+      </c>
+      <c r="G60" t="s">
+        <v>217</v>
+      </c>
+      <c r="H60" s="6"/>
+      <c r="I60" t="s">
+        <v>223</v>
+      </c>
+      <c r="J60" t="s">
+        <v>224</v>
+      </c>
+      <c r="K60" t="s">
+        <v>36</v>
+      </c>
+      <c r="L60" t="s">
+        <v>22</v>
+      </c>
+      <c r="M60" t="s">
+        <v>27</v>
+      </c>
+      <c r="N60" t="s">
+        <v>27</v>
+      </c>
+      <c r="O60" t="s">
+        <v>225</v>
+      </c>
+      <c r="P60" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>199</v>
+      </c>
+      <c r="R60" t="s">
+        <v>27</v>
+      </c>
+      <c r="S60" s="8"/>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>214</v>
+      </c>
+      <c r="B61" s="3">
+        <v>1161</v>
+      </c>
+      <c r="C61" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" t="s">
+        <v>216</v>
+      </c>
+      <c r="E61" t="s">
+        <v>221</v>
+      </c>
+      <c r="F61" t="s">
+        <v>222</v>
+      </c>
+      <c r="G61" t="s">
+        <v>217</v>
+      </c>
+      <c r="H61" s="6"/>
+      <c r="I61" t="s">
+        <v>223</v>
+      </c>
+      <c r="J61" t="s">
+        <v>224</v>
+      </c>
+      <c r="K61" t="s">
+        <v>36</v>
+      </c>
+      <c r="L61" t="s">
+        <v>22</v>
+      </c>
+      <c r="M61" t="s">
+        <v>27</v>
+      </c>
+      <c r="N61" t="s">
+        <v>27</v>
+      </c>
+      <c r="O61" t="s">
+        <v>225</v>
+      </c>
+      <c r="P61" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>199</v>
+      </c>
+      <c r="R61" t="s">
+        <v>27</v>
+      </c>
+      <c r="S61" s="8"/>
+    </row>
+    <row r="62" spans="1:19" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>228</v>
+      </c>
+      <c r="B62" s="3">
+        <v>1219</v>
+      </c>
+      <c r="C62" t="s">
+        <v>30</v>
+      </c>
+      <c r="D62" t="s">
+        <v>229</v>
+      </c>
+      <c r="E62" t="s">
+        <v>218</v>
+      </c>
+      <c r="F62" t="s">
+        <v>234</v>
+      </c>
+      <c r="G62" t="s">
+        <v>230</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I62" t="s">
+        <v>235</v>
+      </c>
+      <c r="J62" t="s">
+        <v>236</v>
+      </c>
+      <c r="K62" t="s">
+        <v>36</v>
+      </c>
+      <c r="L62" t="s">
+        <v>22</v>
+      </c>
+      <c r="M62" t="s">
+        <v>237</v>
+      </c>
+      <c r="N62" t="s">
+        <v>27</v>
+      </c>
+      <c r="O62" t="s">
+        <v>27</v>
+      </c>
+      <c r="P62" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>199</v>
+      </c>
+      <c r="R62" t="s">
+        <v>27</v>
+      </c>
+      <c r="S62" s="8" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>228</v>
+      </c>
+      <c r="B63" s="3">
+        <v>1219</v>
+      </c>
+      <c r="C63" t="s">
+        <v>30</v>
+      </c>
+      <c r="D63" t="s">
+        <v>229</v>
+      </c>
+      <c r="E63" t="s">
+        <v>231</v>
+      </c>
+      <c r="F63" t="s">
+        <v>234</v>
+      </c>
+      <c r="G63" t="s">
+        <v>230</v>
+      </c>
+      <c r="H63" s="6"/>
+      <c r="I63" t="s">
+        <v>235</v>
+      </c>
+      <c r="J63" t="s">
+        <v>236</v>
+      </c>
+      <c r="K63" t="s">
+        <v>36</v>
+      </c>
+      <c r="L63" t="s">
+        <v>22</v>
+      </c>
+      <c r="M63" t="s">
+        <v>237</v>
+      </c>
+      <c r="N63" t="s">
+        <v>27</v>
+      </c>
+      <c r="O63" t="s">
+        <v>27</v>
+      </c>
+      <c r="P63" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>199</v>
+      </c>
+      <c r="R63" t="s">
+        <v>27</v>
+      </c>
+      <c r="S63" s="8"/>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>228</v>
+      </c>
+      <c r="B64" s="3">
+        <v>1219</v>
+      </c>
+      <c r="C64" t="s">
+        <v>30</v>
+      </c>
+      <c r="D64" t="s">
+        <v>229</v>
+      </c>
+      <c r="E64" t="s">
+        <v>232</v>
+      </c>
+      <c r="F64" t="s">
+        <v>234</v>
+      </c>
+      <c r="G64" t="s">
+        <v>230</v>
+      </c>
+      <c r="H64" s="6"/>
+      <c r="I64" t="s">
+        <v>235</v>
+      </c>
+      <c r="J64" t="s">
+        <v>236</v>
+      </c>
+      <c r="K64" t="s">
+        <v>36</v>
+      </c>
+      <c r="L64" t="s">
+        <v>22</v>
+      </c>
+      <c r="M64" t="s">
+        <v>237</v>
+      </c>
+      <c r="N64" t="s">
+        <v>27</v>
+      </c>
+      <c r="O64" t="s">
+        <v>27</v>
+      </c>
+      <c r="P64" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>199</v>
+      </c>
+      <c r="R64" t="s">
+        <v>27</v>
+      </c>
+      <c r="S64" s="8"/>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>228</v>
+      </c>
+      <c r="B65" s="3">
+        <v>1219</v>
+      </c>
+      <c r="C65" t="s">
+        <v>30</v>
+      </c>
+      <c r="D65" t="s">
+        <v>229</v>
+      </c>
+      <c r="E65" t="s">
+        <v>233</v>
+      </c>
+      <c r="F65" t="s">
+        <v>234</v>
+      </c>
+      <c r="G65" t="s">
+        <v>230</v>
+      </c>
+      <c r="H65" s="6"/>
+      <c r="I65" t="s">
+        <v>235</v>
+      </c>
+      <c r="J65" t="s">
+        <v>236</v>
+      </c>
+      <c r="K65" t="s">
+        <v>36</v>
+      </c>
+      <c r="L65" t="s">
+        <v>22</v>
+      </c>
+      <c r="M65" t="s">
+        <v>237</v>
+      </c>
+      <c r="N65" t="s">
+        <v>27</v>
+      </c>
+      <c r="O65" t="s">
+        <v>27</v>
+      </c>
+      <c r="P65" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>199</v>
+      </c>
+      <c r="R65" t="s">
+        <v>27</v>
+      </c>
+      <c r="S65" s="8"/>
+    </row>
+    <row r="66" spans="1:19" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>239</v>
+      </c>
+      <c r="B66" s="3">
+        <v>1277</v>
+      </c>
+      <c r="C66" t="s">
+        <v>3</v>
+      </c>
+      <c r="D66" t="s">
+        <v>240</v>
+      </c>
+      <c r="E66" t="s">
+        <v>218</v>
+      </c>
+      <c r="F66" t="s">
+        <v>245</v>
+      </c>
+      <c r="G66" t="s">
+        <v>241</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I66" t="s">
+        <v>246</v>
+      </c>
+      <c r="J66" t="s">
+        <v>247</v>
+      </c>
+      <c r="K66" t="s">
+        <v>36</v>
+      </c>
+      <c r="L66" t="s">
+        <v>22</v>
+      </c>
+      <c r="M66" t="s">
+        <v>27</v>
+      </c>
+      <c r="N66" t="s">
+        <v>250</v>
+      </c>
+      <c r="O66" t="s">
+        <v>199</v>
+      </c>
+      <c r="P66" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>199</v>
+      </c>
+      <c r="R66" t="s">
+        <v>248</v>
+      </c>
+      <c r="S66" s="8" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>239</v>
+      </c>
+      <c r="B67" s="3">
+        <v>1277</v>
+      </c>
+      <c r="C67" t="s">
+        <v>3</v>
+      </c>
+      <c r="D67" t="s">
+        <v>240</v>
+      </c>
+      <c r="E67" t="s">
+        <v>242</v>
+      </c>
+      <c r="F67" t="s">
+        <v>245</v>
+      </c>
+      <c r="G67" t="s">
+        <v>241</v>
+      </c>
+      <c r="H67" s="6"/>
+      <c r="I67" t="s">
+        <v>246</v>
+      </c>
+      <c r="J67" t="s">
+        <v>247</v>
+      </c>
+      <c r="K67" t="s">
+        <v>36</v>
+      </c>
+      <c r="L67" t="s">
+        <v>22</v>
+      </c>
+      <c r="M67" t="s">
+        <v>27</v>
+      </c>
+      <c r="N67" t="s">
+        <v>250</v>
+      </c>
+      <c r="O67" t="s">
+        <v>199</v>
+      </c>
+      <c r="P67" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>199</v>
+      </c>
+      <c r="R67" t="s">
+        <v>248</v>
+      </c>
+      <c r="S67" s="8"/>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>239</v>
+      </c>
+      <c r="B68" s="3">
+        <v>1277</v>
+      </c>
+      <c r="C68" t="s">
+        <v>3</v>
+      </c>
+      <c r="D68" t="s">
+        <v>240</v>
+      </c>
+      <c r="E68" t="s">
+        <v>243</v>
+      </c>
+      <c r="F68" t="s">
+        <v>245</v>
+      </c>
+      <c r="G68" t="s">
+        <v>241</v>
+      </c>
+      <c r="H68" s="6"/>
+      <c r="I68" t="s">
+        <v>246</v>
+      </c>
+      <c r="J68" t="s">
+        <v>247</v>
+      </c>
+      <c r="K68" t="s">
+        <v>36</v>
+      </c>
+      <c r="L68" t="s">
+        <v>22</v>
+      </c>
+      <c r="M68" t="s">
+        <v>27</v>
+      </c>
+      <c r="N68" t="s">
+        <v>250</v>
+      </c>
+      <c r="O68" t="s">
+        <v>199</v>
+      </c>
+      <c r="P68" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>199</v>
+      </c>
+      <c r="R68" t="s">
+        <v>248</v>
+      </c>
+      <c r="S68" s="8"/>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>239</v>
+      </c>
+      <c r="B69" s="3">
+        <v>1277</v>
+      </c>
+      <c r="C69" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" t="s">
+        <v>240</v>
+      </c>
+      <c r="E69" t="s">
+        <v>244</v>
+      </c>
+      <c r="F69" t="s">
+        <v>245</v>
+      </c>
+      <c r="G69" t="s">
+        <v>241</v>
+      </c>
+      <c r="H69" s="6"/>
+      <c r="I69" t="s">
+        <v>246</v>
+      </c>
+      <c r="J69" t="s">
+        <v>247</v>
+      </c>
+      <c r="K69" t="s">
+        <v>36</v>
+      </c>
+      <c r="L69" t="s">
+        <v>22</v>
+      </c>
+      <c r="M69" t="s">
+        <v>27</v>
+      </c>
+      <c r="N69" t="s">
+        <v>250</v>
+      </c>
+      <c r="O69" t="s">
+        <v>199</v>
+      </c>
+      <c r="P69" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>199</v>
+      </c>
+      <c r="R69" t="s">
+        <v>248</v>
+      </c>
+      <c r="S69" s="8"/>
+    </row>
+    <row r="70" spans="1:19" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>252</v>
+      </c>
+      <c r="B70" s="3">
+        <v>1335</v>
+      </c>
+      <c r="C70" t="s">
+        <v>174</v>
+      </c>
+      <c r="D70" t="s">
+        <v>253</v>
+      </c>
+      <c r="E70" t="s">
+        <v>218</v>
+      </c>
+      <c r="F70" t="s">
+        <v>258</v>
+      </c>
+      <c r="G70" t="s">
+        <v>254</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I70" t="s">
+        <v>259</v>
+      </c>
+      <c r="J70" t="s">
+        <v>260</v>
+      </c>
+      <c r="K70" t="s">
+        <v>36</v>
+      </c>
+      <c r="L70" t="s">
+        <v>22</v>
+      </c>
+      <c r="M70" t="s">
+        <v>262</v>
+      </c>
+      <c r="N70" t="s">
+        <v>27</v>
+      </c>
+      <c r="O70" t="s">
+        <v>24</v>
+      </c>
+      <c r="P70" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>24</v>
+      </c>
+      <c r="R70" t="s">
+        <v>24</v>
+      </c>
+      <c r="S70" s="8" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>252</v>
+      </c>
+      <c r="B71" s="3">
+        <v>1335</v>
+      </c>
+      <c r="C71" t="s">
+        <v>174</v>
+      </c>
+      <c r="D71" t="s">
+        <v>253</v>
+      </c>
+      <c r="E71" t="s">
+        <v>255</v>
+      </c>
+      <c r="F71" t="s">
+        <v>258</v>
+      </c>
+      <c r="G71" t="s">
+        <v>254</v>
+      </c>
+      <c r="H71" s="6"/>
+      <c r="I71" t="s">
+        <v>259</v>
+      </c>
+      <c r="J71" t="s">
+        <v>260</v>
+      </c>
+      <c r="K71" t="s">
+        <v>36</v>
+      </c>
+      <c r="L71" t="s">
+        <v>22</v>
+      </c>
+      <c r="M71" t="s">
+        <v>262</v>
+      </c>
+      <c r="N71" t="s">
+        <v>27</v>
+      </c>
+      <c r="O71" t="s">
+        <v>24</v>
+      </c>
+      <c r="P71" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>24</v>
+      </c>
+      <c r="R71" t="s">
+        <v>24</v>
+      </c>
+      <c r="S71" s="8"/>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>252</v>
+      </c>
+      <c r="B72" s="3">
+        <v>1335</v>
+      </c>
+      <c r="C72" t="s">
+        <v>174</v>
+      </c>
+      <c r="D72" t="s">
+        <v>253</v>
+      </c>
+      <c r="E72" t="s">
+        <v>256</v>
+      </c>
+      <c r="F72" t="s">
+        <v>258</v>
+      </c>
+      <c r="G72" t="s">
+        <v>254</v>
+      </c>
+      <c r="H72" s="6"/>
+      <c r="I72" t="s">
+        <v>259</v>
+      </c>
+      <c r="J72" t="s">
+        <v>260</v>
+      </c>
+      <c r="K72" t="s">
+        <v>36</v>
+      </c>
+      <c r="L72" t="s">
+        <v>22</v>
+      </c>
+      <c r="M72" t="s">
+        <v>262</v>
+      </c>
+      <c r="N72" t="s">
+        <v>27</v>
+      </c>
+      <c r="O72" t="s">
+        <v>24</v>
+      </c>
+      <c r="P72" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>24</v>
+      </c>
+      <c r="R72" t="s">
+        <v>24</v>
+      </c>
+      <c r="S72" s="8"/>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>252</v>
+      </c>
+      <c r="B73" s="3">
+        <v>1335</v>
+      </c>
+      <c r="C73" t="s">
+        <v>174</v>
+      </c>
+      <c r="D73" t="s">
+        <v>253</v>
+      </c>
+      <c r="E73" t="s">
+        <v>257</v>
+      </c>
+      <c r="F73" t="s">
+        <v>258</v>
+      </c>
+      <c r="G73" t="s">
+        <v>254</v>
+      </c>
+      <c r="H73" s="6"/>
+      <c r="I73" t="s">
+        <v>259</v>
+      </c>
+      <c r="J73" t="s">
+        <v>260</v>
+      </c>
+      <c r="K73" t="s">
+        <v>36</v>
+      </c>
+      <c r="L73" t="s">
+        <v>22</v>
+      </c>
+      <c r="M73" t="s">
+        <v>262</v>
+      </c>
+      <c r="N73" t="s">
+        <v>27</v>
+      </c>
+      <c r="O73" t="s">
+        <v>24</v>
+      </c>
+      <c r="P73" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>24</v>
+      </c>
+      <c r="R73" t="s">
+        <v>24</v>
+      </c>
+      <c r="S73" s="8"/>
+    </row>
+    <row r="74" spans="1:19" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>264</v>
+      </c>
+      <c r="B74" s="3">
+        <v>1393</v>
+      </c>
+      <c r="C74" t="s">
+        <v>160</v>
+      </c>
+      <c r="D74" t="s">
+        <v>265</v>
+      </c>
+      <c r="E74" t="s">
+        <v>218</v>
+      </c>
+      <c r="F74" t="s">
+        <v>270</v>
+      </c>
+      <c r="G74" t="s">
+        <v>266</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I74" t="s">
+        <v>271</v>
+      </c>
+      <c r="J74" t="s">
+        <v>272</v>
+      </c>
+      <c r="K74" t="s">
+        <v>36</v>
+      </c>
+      <c r="L74" t="s">
+        <v>22</v>
+      </c>
+      <c r="M74" t="s">
+        <v>27</v>
+      </c>
+      <c r="N74" t="s">
+        <v>27</v>
+      </c>
+      <c r="O74" t="s">
+        <v>27</v>
+      </c>
+      <c r="P74" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>273</v>
+      </c>
+      <c r="R74" t="s">
+        <v>24</v>
+      </c>
+      <c r="S74" s="8" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>264</v>
+      </c>
+      <c r="B75" s="3">
+        <v>1393</v>
+      </c>
+      <c r="C75" t="s">
+        <v>160</v>
+      </c>
+      <c r="D75" t="s">
+        <v>265</v>
+      </c>
+      <c r="E75" t="s">
+        <v>267</v>
+      </c>
+      <c r="F75" t="s">
+        <v>270</v>
+      </c>
+      <c r="G75" t="s">
+        <v>266</v>
+      </c>
+      <c r="H75" s="6"/>
+      <c r="I75" t="s">
+        <v>271</v>
+      </c>
+      <c r="J75" t="s">
+        <v>272</v>
+      </c>
+      <c r="K75" t="s">
+        <v>36</v>
+      </c>
+      <c r="L75" t="s">
+        <v>22</v>
+      </c>
+      <c r="M75" t="s">
+        <v>27</v>
+      </c>
+      <c r="N75" t="s">
+        <v>27</v>
+      </c>
+      <c r="O75" t="s">
+        <v>27</v>
+      </c>
+      <c r="P75" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>273</v>
+      </c>
+      <c r="R75" t="s">
+        <v>24</v>
+      </c>
+      <c r="S75" s="8"/>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>264</v>
+      </c>
+      <c r="B76" s="3">
+        <v>1393</v>
+      </c>
+      <c r="C76" t="s">
+        <v>160</v>
+      </c>
+      <c r="D76" t="s">
+        <v>265</v>
+      </c>
+      <c r="E76" t="s">
+        <v>268</v>
+      </c>
+      <c r="F76" t="s">
+        <v>270</v>
+      </c>
+      <c r="G76" t="s">
+        <v>266</v>
+      </c>
+      <c r="H76" s="6"/>
+      <c r="I76" t="s">
+        <v>271</v>
+      </c>
+      <c r="J76" t="s">
+        <v>272</v>
+      </c>
+      <c r="K76" t="s">
+        <v>36</v>
+      </c>
+      <c r="L76" t="s">
+        <v>22</v>
+      </c>
+      <c r="M76" t="s">
+        <v>27</v>
+      </c>
+      <c r="N76" t="s">
+        <v>27</v>
+      </c>
+      <c r="O76" t="s">
+        <v>27</v>
+      </c>
+      <c r="P76" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>273</v>
+      </c>
+      <c r="R76" t="s">
+        <v>24</v>
+      </c>
+      <c r="S76" s="8"/>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>264</v>
+      </c>
+      <c r="B77" s="3">
+        <v>1393</v>
+      </c>
+      <c r="C77" t="s">
+        <v>160</v>
+      </c>
+      <c r="D77" t="s">
+        <v>265</v>
+      </c>
+      <c r="E77" t="s">
+        <v>269</v>
+      </c>
+      <c r="F77" t="s">
+        <v>270</v>
+      </c>
+      <c r="G77" t="s">
+        <v>266</v>
+      </c>
+      <c r="H77" s="6"/>
+      <c r="I77" t="s">
+        <v>271</v>
+      </c>
+      <c r="J77" t="s">
+        <v>272</v>
+      </c>
+      <c r="K77" t="s">
+        <v>36</v>
+      </c>
+      <c r="L77" t="s">
+        <v>22</v>
+      </c>
+      <c r="M77" t="s">
+        <v>27</v>
+      </c>
+      <c r="N77" t="s">
+        <v>27</v>
+      </c>
+      <c r="O77" t="s">
+        <v>27</v>
+      </c>
+      <c r="P77" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>273</v>
+      </c>
+      <c r="R77" t="s">
+        <v>24</v>
+      </c>
+      <c r="S77" s="8"/>
+    </row>
+    <row r="78" spans="1:19" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>274</v>
+      </c>
+      <c r="B78" s="3">
+        <v>1451</v>
+      </c>
+      <c r="C78" t="s">
+        <v>174</v>
+      </c>
+      <c r="D78" t="s">
+        <v>275</v>
+      </c>
+      <c r="E78" t="s">
+        <v>277</v>
+      </c>
+      <c r="F78" t="s">
+        <v>282</v>
+      </c>
+      <c r="G78" t="s">
+        <v>276</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="I78" t="s">
+        <v>283</v>
+      </c>
+      <c r="J78" t="s">
+        <v>284</v>
+      </c>
+      <c r="K78" t="s">
+        <v>36</v>
+      </c>
+      <c r="L78" t="s">
+        <v>22</v>
+      </c>
+      <c r="M78" t="s">
+        <v>27</v>
+      </c>
+      <c r="N78" t="s">
+        <v>286</v>
+      </c>
+      <c r="O78" t="s">
+        <v>27</v>
+      </c>
+      <c r="P78" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>27</v>
+      </c>
+      <c r="R78" t="s">
+        <v>285</v>
+      </c>
+      <c r="S78" s="8" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>274</v>
+      </c>
+      <c r="B79" s="3">
+        <v>1451</v>
+      </c>
+      <c r="C79" t="s">
+        <v>174</v>
+      </c>
+      <c r="D79" t="s">
+        <v>275</v>
+      </c>
+      <c r="E79" t="s">
+        <v>278</v>
+      </c>
+      <c r="F79" t="s">
+        <v>282</v>
+      </c>
+      <c r="G79" t="s">
+        <v>276</v>
+      </c>
+      <c r="H79" s="6"/>
+      <c r="I79" t="s">
+        <v>283</v>
+      </c>
+      <c r="J79" t="s">
+        <v>284</v>
+      </c>
+      <c r="K79" t="s">
+        <v>36</v>
+      </c>
+      <c r="L79" t="s">
+        <v>22</v>
+      </c>
+      <c r="M79" t="s">
+        <v>27</v>
+      </c>
+      <c r="N79" t="s">
+        <v>286</v>
+      </c>
+      <c r="O79" t="s">
+        <v>27</v>
+      </c>
+      <c r="P79" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>27</v>
+      </c>
+      <c r="R79" t="s">
+        <v>285</v>
+      </c>
+      <c r="S79" s="8"/>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>274</v>
+      </c>
+      <c r="B80" s="3">
+        <v>1451</v>
+      </c>
+      <c r="C80" t="s">
+        <v>174</v>
+      </c>
+      <c r="D80" t="s">
+        <v>275</v>
+      </c>
+      <c r="E80" t="s">
+        <v>280</v>
+      </c>
+      <c r="F80" t="s">
+        <v>282</v>
+      </c>
+      <c r="G80" t="s">
+        <v>276</v>
+      </c>
+      <c r="H80" s="6"/>
+      <c r="I80" t="s">
+        <v>283</v>
+      </c>
+      <c r="J80" t="s">
+        <v>284</v>
+      </c>
+      <c r="K80" t="s">
+        <v>36</v>
+      </c>
+      <c r="L80" t="s">
+        <v>22</v>
+      </c>
+      <c r="M80" t="s">
+        <v>27</v>
+      </c>
+      <c r="N80" t="s">
+        <v>286</v>
+      </c>
+      <c r="O80" t="s">
+        <v>27</v>
+      </c>
+      <c r="P80" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>27</v>
+      </c>
+      <c r="R80" t="s">
+        <v>285</v>
+      </c>
+      <c r="S80" s="8"/>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>274</v>
+      </c>
+      <c r="B81" s="3">
+        <v>1451</v>
+      </c>
+      <c r="C81" t="s">
+        <v>174</v>
+      </c>
+      <c r="D81" t="s">
+        <v>275</v>
+      </c>
+      <c r="E81" t="s">
+        <v>279</v>
+      </c>
+      <c r="F81" t="s">
+        <v>282</v>
+      </c>
+      <c r="G81" t="s">
+        <v>276</v>
+      </c>
+      <c r="H81" s="6"/>
+      <c r="I81" t="s">
+        <v>283</v>
+      </c>
+      <c r="J81" t="s">
+        <v>284</v>
+      </c>
+      <c r="K81" t="s">
+        <v>36</v>
+      </c>
+      <c r="L81" t="s">
+        <v>22</v>
+      </c>
+      <c r="M81" t="s">
+        <v>27</v>
+      </c>
+      <c r="N81" t="s">
+        <v>286</v>
+      </c>
+      <c r="O81" t="s">
+        <v>27</v>
+      </c>
+      <c r="P81" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>27</v>
+      </c>
+      <c r="R81" t="s">
+        <v>285</v>
+      </c>
+      <c r="S81" s="8"/>
+    </row>
+    <row r="82" spans="1:19" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>289</v>
+      </c>
+      <c r="B82" s="3">
+        <v>1509</v>
+      </c>
+      <c r="C82" t="s">
+        <v>30</v>
+      </c>
+      <c r="D82" t="s">
+        <v>290</v>
+      </c>
+      <c r="E82" t="s">
+        <v>218</v>
+      </c>
+      <c r="F82" t="s">
+        <v>295</v>
+      </c>
+      <c r="G82" t="s">
+        <v>291</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="I82" t="s">
+        <v>297</v>
+      </c>
+      <c r="J82" t="s">
+        <v>298</v>
+      </c>
+      <c r="K82" t="s">
+        <v>36</v>
+      </c>
+      <c r="L82" t="s">
+        <v>22</v>
+      </c>
+      <c r="M82" t="s">
+        <v>27</v>
+      </c>
+      <c r="N82" t="s">
+        <v>27</v>
+      </c>
+      <c r="O82" t="s">
+        <v>211</v>
+      </c>
+      <c r="P82" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>299</v>
+      </c>
+      <c r="R82" t="s">
+        <v>27</v>
+      </c>
+      <c r="S82" s="8" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>289</v>
+      </c>
+      <c r="B83" s="3">
+        <v>1509</v>
+      </c>
+      <c r="C83" t="s">
+        <v>30</v>
+      </c>
+      <c r="D83" t="s">
+        <v>290</v>
+      </c>
+      <c r="E83" t="s">
+        <v>292</v>
+      </c>
+      <c r="F83" t="s">
+        <v>295</v>
+      </c>
+      <c r="G83" t="s">
+        <v>291</v>
+      </c>
+      <c r="H83" s="6"/>
+      <c r="I83" t="s">
+        <v>297</v>
+      </c>
+      <c r="J83" t="s">
+        <v>298</v>
+      </c>
+      <c r="K83" t="s">
+        <v>36</v>
+      </c>
+      <c r="L83" t="s">
+        <v>22</v>
+      </c>
+      <c r="M83" t="s">
+        <v>27</v>
+      </c>
+      <c r="N83" t="s">
+        <v>27</v>
+      </c>
+      <c r="O83" t="s">
+        <v>211</v>
+      </c>
+      <c r="P83" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>299</v>
+      </c>
+      <c r="R83" t="s">
+        <v>27</v>
+      </c>
+      <c r="S83" s="8"/>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>289</v>
+      </c>
+      <c r="B84" s="3">
+        <v>1509</v>
+      </c>
+      <c r="C84" t="s">
+        <v>30</v>
+      </c>
+      <c r="D84" t="s">
+        <v>290</v>
+      </c>
+      <c r="E84" t="s">
+        <v>293</v>
+      </c>
+      <c r="F84" t="s">
+        <v>295</v>
+      </c>
+      <c r="G84" t="s">
+        <v>291</v>
+      </c>
+      <c r="H84" s="6"/>
+      <c r="I84" t="s">
+        <v>297</v>
+      </c>
+      <c r="J84" t="s">
+        <v>298</v>
+      </c>
+      <c r="K84" t="s">
+        <v>36</v>
+      </c>
+      <c r="L84" t="s">
+        <v>22</v>
+      </c>
+      <c r="M84" t="s">
+        <v>27</v>
+      </c>
+      <c r="N84" t="s">
+        <v>27</v>
+      </c>
+      <c r="O84" t="s">
+        <v>211</v>
+      </c>
+      <c r="P84" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>299</v>
+      </c>
+      <c r="R84" t="s">
+        <v>27</v>
+      </c>
+      <c r="S84" s="8"/>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>289</v>
+      </c>
+      <c r="B85" s="3">
+        <v>1509</v>
+      </c>
+      <c r="C85" t="s">
+        <v>30</v>
+      </c>
+      <c r="D85" t="s">
+        <v>290</v>
+      </c>
+      <c r="E85" t="s">
+        <v>294</v>
+      </c>
+      <c r="F85" t="s">
+        <v>295</v>
+      </c>
+      <c r="G85" t="s">
+        <v>291</v>
+      </c>
+      <c r="H85" s="6"/>
+      <c r="I85" t="s">
+        <v>297</v>
+      </c>
+      <c r="J85" t="s">
+        <v>298</v>
+      </c>
+      <c r="K85" t="s">
+        <v>36</v>
+      </c>
+      <c r="L85" t="s">
+        <v>22</v>
+      </c>
+      <c r="M85" t="s">
+        <v>27</v>
+      </c>
+      <c r="N85" t="s">
+        <v>27</v>
+      </c>
+      <c r="O85" t="s">
+        <v>211</v>
+      </c>
+      <c r="P85" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>299</v>
+      </c>
+      <c r="R85" t="s">
+        <v>27</v>
+      </c>
+      <c r="S85" s="8"/>
+    </row>
+    <row r="86" spans="1:19" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>301</v>
+      </c>
+      <c r="B86" s="3">
+        <v>1567</v>
+      </c>
+      <c r="C86" t="s">
+        <v>174</v>
+      </c>
+      <c r="D86" t="s">
+        <v>302</v>
+      </c>
+      <c r="E86" t="s">
+        <v>218</v>
+      </c>
+      <c r="F86" t="s">
+        <v>307</v>
+      </c>
+      <c r="G86" t="s">
+        <v>303</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="I86" t="s">
+        <v>308</v>
+      </c>
+      <c r="J86" t="s">
+        <v>309</v>
+      </c>
+      <c r="K86" t="s">
+        <v>36</v>
+      </c>
+      <c r="L86" t="s">
+        <v>22</v>
+      </c>
+      <c r="M86" t="s">
+        <v>27</v>
+      </c>
+      <c r="N86" t="s">
+        <v>310</v>
+      </c>
+      <c r="O86" t="s">
+        <v>311</v>
+      </c>
+      <c r="P86" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>27</v>
+      </c>
+      <c r="R86" t="s">
+        <v>27</v>
+      </c>
+      <c r="S86" s="8" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>301</v>
+      </c>
+      <c r="B87" s="3">
+        <v>1567</v>
+      </c>
+      <c r="C87" t="s">
+        <v>174</v>
+      </c>
+      <c r="D87" t="s">
+        <v>302</v>
+      </c>
+      <c r="E87" t="s">
+        <v>304</v>
+      </c>
+      <c r="F87" t="s">
+        <v>307</v>
+      </c>
+      <c r="G87" t="s">
+        <v>303</v>
+      </c>
+      <c r="H87" s="6"/>
+      <c r="I87" t="s">
+        <v>308</v>
+      </c>
+      <c r="J87" t="s">
+        <v>309</v>
+      </c>
+      <c r="K87" t="s">
+        <v>36</v>
+      </c>
+      <c r="L87" t="s">
+        <v>22</v>
+      </c>
+      <c r="M87" t="s">
+        <v>27</v>
+      </c>
+      <c r="N87" t="s">
+        <v>310</v>
+      </c>
+      <c r="O87" t="s">
+        <v>311</v>
+      </c>
+      <c r="P87" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>27</v>
+      </c>
+      <c r="R87" t="s">
+        <v>27</v>
+      </c>
+      <c r="S87" s="8"/>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>301</v>
+      </c>
+      <c r="B88" s="3">
+        <v>1567</v>
+      </c>
+      <c r="C88" t="s">
+        <v>174</v>
+      </c>
+      <c r="D88" t="s">
+        <v>302</v>
+      </c>
+      <c r="E88" t="s">
+        <v>306</v>
+      </c>
+      <c r="F88" t="s">
+        <v>307</v>
+      </c>
+      <c r="G88" t="s">
+        <v>303</v>
+      </c>
+      <c r="H88" s="6"/>
+      <c r="I88" t="s">
+        <v>308</v>
+      </c>
+      <c r="J88" t="s">
+        <v>309</v>
+      </c>
+      <c r="K88" t="s">
+        <v>36</v>
+      </c>
+      <c r="L88" t="s">
+        <v>22</v>
+      </c>
+      <c r="M88" t="s">
+        <v>27</v>
+      </c>
+      <c r="N88" t="s">
+        <v>310</v>
+      </c>
+      <c r="O88" t="s">
+        <v>311</v>
+      </c>
+      <c r="P88" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>27</v>
+      </c>
+      <c r="R88" t="s">
+        <v>27</v>
+      </c>
+      <c r="S88" s="8"/>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>301</v>
+      </c>
+      <c r="B89" s="3">
+        <v>1567</v>
+      </c>
+      <c r="C89" t="s">
+        <v>174</v>
+      </c>
+      <c r="D89" t="s">
+        <v>302</v>
+      </c>
+      <c r="E89" t="s">
+        <v>305</v>
+      </c>
+      <c r="F89" t="s">
+        <v>307</v>
+      </c>
+      <c r="G89" t="s">
+        <v>303</v>
+      </c>
+      <c r="H89" s="6"/>
+      <c r="I89" t="s">
+        <v>308</v>
+      </c>
+      <c r="J89" t="s">
+        <v>309</v>
+      </c>
+      <c r="K89" t="s">
+        <v>36</v>
+      </c>
+      <c r="L89" t="s">
+        <v>22</v>
+      </c>
+      <c r="M89" t="s">
+        <v>27</v>
+      </c>
+      <c r="N89" t="s">
+        <v>310</v>
+      </c>
+      <c r="O89" t="s">
+        <v>311</v>
+      </c>
+      <c r="P89" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>27</v>
+      </c>
+      <c r="R89" t="s">
+        <v>27</v>
+      </c>
+      <c r="S89" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="45">
+    <mergeCell ref="H82:H85"/>
+    <mergeCell ref="S82:S85"/>
+    <mergeCell ref="H86:H89"/>
+    <mergeCell ref="S86:S89"/>
+    <mergeCell ref="H70:H73"/>
+    <mergeCell ref="S70:S73"/>
+    <mergeCell ref="H74:H77"/>
+    <mergeCell ref="S74:S77"/>
+    <mergeCell ref="H78:H81"/>
+    <mergeCell ref="S78:S81"/>
+    <mergeCell ref="H58:H61"/>
+    <mergeCell ref="S58:S61"/>
+    <mergeCell ref="H62:H65"/>
+    <mergeCell ref="S62:S65"/>
+    <mergeCell ref="H66:H69"/>
+    <mergeCell ref="S66:S69"/>
+    <mergeCell ref="H46:H49"/>
+    <mergeCell ref="S46:S49"/>
+    <mergeCell ref="H50:H53"/>
+    <mergeCell ref="S50:S53"/>
+    <mergeCell ref="H54:H57"/>
+    <mergeCell ref="S54:S57"/>
+    <mergeCell ref="H34:H37"/>
+    <mergeCell ref="S34:S37"/>
+    <mergeCell ref="H38:H41"/>
+    <mergeCell ref="S38:S41"/>
+    <mergeCell ref="H42:H45"/>
+    <mergeCell ref="S42:S45"/>
+    <mergeCell ref="H22:H25"/>
+    <mergeCell ref="S22:S25"/>
+    <mergeCell ref="H26:H29"/>
+    <mergeCell ref="S26:S29"/>
+    <mergeCell ref="H30:H33"/>
+    <mergeCell ref="S30:S33"/>
+    <mergeCell ref="H14:H17"/>
+    <mergeCell ref="L14:L17"/>
+    <mergeCell ref="S14:S17"/>
+    <mergeCell ref="H18:H21"/>
+    <mergeCell ref="S18:S21"/>
     <mergeCell ref="H2:H5"/>
     <mergeCell ref="S2:S5"/>
     <mergeCell ref="H6:H9"/>
@@ -1537,4 +7200,93 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Resultats_modeles_coleo_2024.xlsx
+++ b/Resultats_modeles_coleo_2024.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2464" uniqueCount="501">
   <si>
     <t>ab.colsx</t>
   </si>
@@ -1784,6 +1784,1160 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> : aucunes différences entre les strates comparées 2 à 2 pour la richesse spécifique cumulée totale des coléoptères saproxyliques mycétophages</t>
+    </r>
+  </si>
+  <si>
+    <t>ab.xyl</t>
+  </si>
+  <si>
+    <t>sr.xyl</t>
+  </si>
+  <si>
+    <t>truncated_genpois</t>
+  </si>
+  <si>
+    <t>sr.xyl ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>sr.xyl ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>infra inf : 0.167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra supp : 2.04e-09 ***     </t>
+  </si>
+  <si>
+    <t>supra : 2.28e-12 ***</t>
+  </si>
+  <si>
+    <t>422.2892</t>
+  </si>
+  <si>
+    <t>466.4268</t>
+  </si>
+  <si>
+    <t>4.523e-11 ***</t>
+  </si>
+  <si>
+    <t>&lt; 1e-04 ***</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">En ce qui concerne la richesse spécifique cumulée totale des coléoptères saproxyliques larvaires xylophages, elle diffère sur plusieurs des strates comparées 2 à 2, qui sont </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supra &amp; intra.inf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supra &amp; infra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; intra.inf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, et </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; infra</t>
+    </r>
+  </si>
+  <si>
+    <t>ab.sxy</t>
+  </si>
+  <si>
+    <t>lognormal(link = "identity")</t>
+  </si>
+  <si>
+    <t>ab.sxy ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>ab.sxy ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>725.9916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra inf : 0.3483 </t>
+  </si>
+  <si>
+    <t>infra supp : 4.58e-05 ***</t>
+  </si>
+  <si>
+    <t>supra : 0.0256 *</t>
+  </si>
+  <si>
+    <t>736.1654</t>
+  </si>
+  <si>
+    <t>0.0006441 ***</t>
+  </si>
+  <si>
+    <t>0.00659 **</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pour l'abondance cumulée totale des coléoptères saproxylique larvaires saproxylophages, elle différe sur 2 comparaison de strates 2 à 2 qui sont </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; intra.inf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, et </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; infra</t>
+    </r>
+  </si>
+  <si>
+    <t>sr.sxy</t>
+  </si>
+  <si>
+    <t>sr.sxy ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>sr.sxy ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>467.2723</t>
+  </si>
+  <si>
+    <t>infra inf : 0.027772 *</t>
+  </si>
+  <si>
+    <t>infra supp : 0.000163 ***</t>
+  </si>
+  <si>
+    <t>supra : 0.057069 .</t>
+  </si>
+  <si>
+    <t>491.2692</t>
+  </si>
+  <si>
+    <t>8.422e-07 ***</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">En ce qui concerne la richesse spécifique cumulée totale des coléoptères saproxyliques larvaires saproxylophages, elle diffère sur plusieurs des strates comparées 2 à 2, qui sont </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supra &amp; intra.supp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supra &amp; intra.inf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, et </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; infra</t>
+    </r>
+  </si>
+  <si>
+    <t>ab.zoo</t>
+  </si>
+  <si>
+    <t>gaussian(link = "log")</t>
+  </si>
+  <si>
+    <t>ab.zoo ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>ab.zoo ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>infra inf : 0.025869 *</t>
+  </si>
+  <si>
+    <t>infra supp : 4.95e-09 ***</t>
+  </si>
+  <si>
+    <t>supra : 0.000955 ***</t>
+  </si>
+  <si>
+    <t>725.9477</t>
+  </si>
+  <si>
+    <t>763.8545</t>
+  </si>
+  <si>
+    <t>9.58e-10 ***</t>
+  </si>
+  <si>
+    <t>0.00482 **</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pour l'abondance cumulée totale des coléoptères saproxyliques larvaires zoophages, elle diffère sur plusieurs des strates comparées 2 à 2, qui sont </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supra &amp; intra.supp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supra &amp; infra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; intra.inf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, et </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; infra</t>
+    </r>
+  </si>
+  <si>
+    <t>sr.zoo</t>
+  </si>
+  <si>
+    <t>sr.zoo ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>sr.zoo ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>431.6754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra inf : 0.0693 . </t>
+  </si>
+  <si>
+    <t>infra supp : 7.23e-07 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">supra : 0.1667 </t>
+  </si>
+  <si>
+    <t>451.1683</t>
+  </si>
+  <si>
+    <t>7.44e-06 ***</t>
+  </si>
+  <si>
+    <t>N.S (0.01130 *)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00184 ** </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">En ce qui concerne la richesse spécifique cumulée totale des coléoptères saproxyliques larvaires zoophages, elle diffère sur plusieurs des strates comparées 2 à 2, qui sont </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supra &amp; intra.supp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, et </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; infra</t>
+    </r>
+  </si>
+  <si>
+    <t>ab.cavspe</t>
+  </si>
+  <si>
+    <t>ab.cavspe ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>ab.cavspe ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra : 0.157187 </t>
+  </si>
+  <si>
+    <t>infra inf : 0.000993 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra supp : 0.375627  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">supra : 0.716945 </t>
+  </si>
+  <si>
+    <t>308.9908</t>
+  </si>
+  <si>
+    <t>0.0135 *</t>
+  </si>
+  <si>
+    <t>316.8113</t>
+  </si>
+  <si>
+    <t>0.001956 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00546 ** </t>
+  </si>
+  <si>
+    <t>0.00165 **</t>
+  </si>
+  <si>
+    <t>N.S (0.06506 .)</t>
+  </si>
+  <si>
+    <t>sr.cavspe</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pour l'abondance cumulée totale des coléoptères saproxyliques larvaires cavicoles spécialistes, elle diffère sur plusieurs des strates comparées 2 à 2, qui sont </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supra &amp; intra.inf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, et </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.inf &amp; infra</t>
+    </r>
+  </si>
+  <si>
+    <t>sr.cavspe ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season</t>
+  </si>
+  <si>
+    <t>sr.cavspe ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season</t>
+  </si>
+  <si>
+    <t>245.6462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra : 0.25402 </t>
+  </si>
+  <si>
+    <t>infra inf : 0.00754 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra supp : 0.20404  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">supra : 0.65584  </t>
+  </si>
+  <si>
+    <t>0.0267 *</t>
+  </si>
+  <si>
+    <t>249.4546</t>
+  </si>
+  <si>
+    <t>0.01268 *</t>
+  </si>
+  <si>
+    <t>N.S (0.0373 *)</t>
+  </si>
+  <si>
+    <t>N.S (0.0125 *)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N.S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : aucunes différences entre les strates comparées 2 à 2 pour la richesse spécifique cumulée totale des coléoptères saproxyliques larvaires cavicoles spécialistes</t>
+    </r>
+  </si>
+  <si>
+    <t>Remarque</t>
+  </si>
+  <si>
+    <t>Choix de la distribution via fitdistrplus : geom. Famille correspondante dans glmmTMB : nbinom2()</t>
+  </si>
+  <si>
+    <t>nbinom2</t>
+  </si>
+  <si>
+    <t>infra inf : 0.90394</t>
+  </si>
+  <si>
+    <t>infra supp : 1e-05 ***</t>
+  </si>
+  <si>
+    <t>supra : 0.00133 **</t>
+  </si>
+  <si>
+    <t>797.8552</t>
+  </si>
+  <si>
+    <t>ab.xyl ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>ab.xyl ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>814.7558</t>
+  </si>
+  <si>
+    <t>2.592e-05 ***</t>
+  </si>
+  <si>
+    <t>dispersion et loi de distribution mal ajustés pour log-normal, 2ème choix sur geom et donc nbinom2 après avoir tenté de régler la surdispersion avec dispformula = ~ strate qui n'a pas fonctioné</t>
+  </si>
+  <si>
+    <t>N.S (0.01107 *)</t>
+  </si>
+  <si>
+    <t>0.00771 **</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pour l'abondance cumulée totale des coléoptères saproxyliques larvaires xylophages, elle diffère sur plusieurs strates qui sont </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; intra.inf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, et </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; infra</t>
+    </r>
+  </si>
+  <si>
+    <t>CWM_diam</t>
+  </si>
+  <si>
+    <t>lognormal</t>
+  </si>
+  <si>
+    <t>CWM_diam ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>CWM_diam ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>54.16182</t>
+  </si>
+  <si>
+    <t>infra inf : 0.0496 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra supp : 0.8867  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">supra : 0.7838  </t>
+  </si>
+  <si>
+    <t>52.11842</t>
+  </si>
+  <si>
+    <t>0.1734</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N.S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : aucunes différences entre les strates comparées 2 à 2 pour le Trait moyen de préférence de classe de diamètre du substrat saproxylique, pas d'effet strate.</t>
+    </r>
+  </si>
+  <si>
+    <t>CWM_canop</t>
+  </si>
+  <si>
+    <t>CWM_decay</t>
+  </si>
+  <si>
+    <t>N.S (0.07539 .)</t>
+  </si>
+  <si>
+    <t>0.00415 **</t>
+  </si>
+  <si>
+    <t>CWM_decay ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>CWM_decay ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>infra inf : 0.000762 ***</t>
+  </si>
+  <si>
+    <t>infra supp : 0.082906 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">supra : 0.338093 </t>
+  </si>
+  <si>
+    <t>13.54536</t>
+  </si>
+  <si>
+    <t>17.59597</t>
+  </si>
+  <si>
+    <t>0.01134 *</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Seul la comparaison entre </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.inf &amp; infra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> est significative pour le Trait moyen de préférence de stade de saproxylation du substrat saproxylique</t>
+    </r>
+  </si>
+  <si>
+    <t>CWM_size</t>
+  </si>
+  <si>
+    <t>CWM_size ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>CWM_size ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>infra inf : 0.03865 *</t>
+  </si>
+  <si>
+    <t>infra supp : 2.08e-13 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">supra : 0.00166 ** </t>
+  </si>
+  <si>
+    <t>252.6993</t>
+  </si>
+  <si>
+    <t>284.6468</t>
+  </si>
+  <si>
+    <t>1.761e-08 ***</t>
+  </si>
+  <si>
+    <t>N.S (0.00884 **)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pour la comparaison des strates 2 à 2 concernant la Taille moyenne de l’assemblage d’espèces, l'assemblage des espèces par rapport à leur taille moyenne diffère entre les strates </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supra &amp; intra.supp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; intra.inf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, et </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; infra</t>
+    </r>
+  </si>
+  <si>
+    <t>FD_diam</t>
+  </si>
+  <si>
+    <t>FD_diam ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>FD_diam ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>-30.42083</t>
+  </si>
+  <si>
+    <t>infra inf : 0.00759 **</t>
+  </si>
+  <si>
+    <t>infra supp : 0.09162 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">supra : 0.61722     </t>
+  </si>
+  <si>
+    <t>-25.66816</t>
+  </si>
+  <si>
+    <t>0.008195 **</t>
+  </si>
+  <si>
+    <t>N.S (0.00825 **)</t>
+  </si>
+  <si>
+    <t>N.S (0.03787 *)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N.S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : aucunes différences entre les strates comparées 2 à 2 pour la Variance de trait de préférence de classe de diamètre du substrat saproxylique</t>
+    </r>
+  </si>
+  <si>
+    <t>FD_canop</t>
+  </si>
+  <si>
+    <t>beta_family</t>
+  </si>
+  <si>
+    <t>FD_canop ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>FD_canop ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>-22.90872</t>
+  </si>
+  <si>
+    <t>infra : 8.52e-07 ***</t>
+  </si>
+  <si>
+    <t>infra inf : 0.76093</t>
+  </si>
+  <si>
+    <t>infra supp : 0.00541 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">supra : 0.00631 ** </t>
+  </si>
+  <si>
+    <t>-18.33089</t>
+  </si>
+  <si>
+    <t>8.67e-07 ***</t>
+  </si>
+  <si>
+    <t>N.S (0.0277 *)</t>
+  </si>
+  <si>
+    <t>N.S (0.0320 *)</t>
+  </si>
+  <si>
+    <t>N.S (0.0108 *)</t>
+  </si>
+  <si>
+    <t>N.S (0.0129 *)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N.S :</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> aucunes différences entre les strates comparées 2 à 2 pour la Variance de trait de préférence de canopée (= héliophilie moyenne) de l’assemblage</t>
+    </r>
+  </si>
+  <si>
+    <t>FD_decay</t>
+  </si>
+  <si>
+    <t>FD_decay ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>FD_decay ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>infra : 7.2e-15 ***</t>
+  </si>
+  <si>
+    <t>infra inf : 0.042398 *</t>
+  </si>
+  <si>
+    <t>infra supp : 0.000113 ***</t>
+  </si>
+  <si>
+    <t>supra : 0.000147 ***</t>
+  </si>
+  <si>
+    <t>-142.3195</t>
+  </si>
+  <si>
+    <t>-132.0498</t>
+  </si>
+  <si>
+    <t>0.0006155 ***</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pour la comparaison des strates 2 à 2 concernant la Variance de trait de préférence de stade de saproxylation du substrat, cette variance diffère entre les strates </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supra &amp; infra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, et</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> intra.supp &amp; infra</t>
+    </r>
+  </si>
+  <si>
+    <t>FD_size</t>
+  </si>
+  <si>
+    <t>FD_size ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>FD_size ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>-74.84554</t>
+  </si>
+  <si>
+    <t>infra inf : 0.03178 *</t>
+  </si>
+  <si>
+    <t>infra supp : 9.18e-13 ***</t>
+  </si>
+  <si>
+    <t>supra : 0.00401 **</t>
+  </si>
+  <si>
+    <t>-41.68336</t>
+  </si>
+  <si>
+    <t>9.738e-09 ***</t>
+  </si>
+  <si>
+    <t>N.S (0.0205 *)</t>
+  </si>
+  <si>
+    <r>
+      <t>Pour la comparaison des strates 2 à 2 concernant la Variance de trait de préférence de stade de saproxylation du substrat, cette variance diffère entre les strates</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> supra &amp; intra.supp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; intra.in</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">f, et </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; infra</t>
     </r>
   </si>
 </sst>
@@ -1834,7 +2988,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1849,17 +3003,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2141,11 +3298,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U89"/>
+  <dimension ref="A1:U153"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="72.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.33203125" customWidth="1"/>
@@ -2153,14 +3310,14 @@
     <col min="8" max="9" width="20.33203125" customWidth="1"/>
     <col min="10" max="10" width="33.5546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="33.5546875" customWidth="1"/>
-    <col min="12" max="12" width="38.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="63.88671875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="21.5546875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="21" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="21.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="21.21875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="20.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="24.109375" style="9" customWidth="1"/>
+    <col min="19" max="19" width="24.109375" style="6" customWidth="1"/>
     <col min="20" max="20" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2222,7 +3379,9 @@
       <c r="S1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="T1" s="1"/>
+      <c r="T1" s="1" t="s">
+        <v>401</v>
+      </c>
       <c r="U1" t="s">
         <v>1</v>
       </c>
@@ -2249,7 +3408,7 @@
       <c r="G2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I2">
@@ -2308,7 +3467,7 @@
       <c r="G3" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="6"/>
+      <c r="H3" s="7"/>
       <c r="I3">
         <v>976.73</v>
       </c>
@@ -2363,7 +3522,7 @@
       <c r="G4" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="6"/>
+      <c r="H4" s="7"/>
       <c r="I4">
         <v>976.73</v>
       </c>
@@ -2418,7 +3577,7 @@
       <c r="G5" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="6"/>
+      <c r="H5" s="7"/>
       <c r="I5">
         <v>976.73</v>
       </c>
@@ -2473,7 +3632,7 @@
       <c r="G6" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I6">
@@ -2532,7 +3691,7 @@
       <c r="G7" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="6"/>
+      <c r="H7" s="7"/>
       <c r="I7">
         <v>646.24</v>
       </c>
@@ -2587,7 +3746,7 @@
       <c r="G8" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="6"/>
+      <c r="H8" s="7"/>
       <c r="I8">
         <v>646.24</v>
       </c>
@@ -2642,7 +3801,7 @@
       <c r="G9" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="6"/>
+      <c r="H9" s="7"/>
       <c r="I9">
         <v>646.24</v>
       </c>
@@ -2697,7 +3856,7 @@
       <c r="G10" t="s">
         <v>54</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="7" t="s">
         <v>55</v>
       </c>
       <c r="I10" t="s">
@@ -2756,7 +3915,7 @@
       <c r="G11" t="s">
         <v>54</v>
       </c>
-      <c r="H11" s="6"/>
+      <c r="H11" s="7"/>
       <c r="I11" t="s">
         <v>53</v>
       </c>
@@ -2811,7 +3970,7 @@
       <c r="G12" t="s">
         <v>54</v>
       </c>
-      <c r="H12" s="6"/>
+      <c r="H12" s="7"/>
       <c r="I12" t="s">
         <v>53</v>
       </c>
@@ -2866,7 +4025,7 @@
       <c r="G13" t="s">
         <v>54</v>
       </c>
-      <c r="H13" s="6"/>
+      <c r="H13" s="7"/>
       <c r="I13" t="s">
         <v>53</v>
       </c>
@@ -2921,7 +4080,7 @@
       <c r="G14" t="s">
         <v>70</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="7" t="s">
         <v>77</v>
       </c>
       <c r="I14" t="s">
@@ -2933,7 +4092,7 @@
       <c r="K14" t="s">
         <v>36</v>
       </c>
-      <c r="L14" s="7" t="s">
+      <c r="L14" s="9" t="s">
         <v>80</v>
       </c>
       <c r="M14" t="s">
@@ -2980,7 +4139,7 @@
       <c r="G15" t="s">
         <v>70</v>
       </c>
-      <c r="H15" s="6"/>
+      <c r="H15" s="7"/>
       <c r="I15" t="s">
         <v>76</v>
       </c>
@@ -2990,7 +4149,7 @@
       <c r="K15" t="s">
         <v>36</v>
       </c>
-      <c r="L15" s="7"/>
+      <c r="L15" s="9"/>
       <c r="M15" t="s">
         <v>24</v>
       </c>
@@ -3033,7 +4192,7 @@
       <c r="G16" t="s">
         <v>70</v>
       </c>
-      <c r="H16" s="6"/>
+      <c r="H16" s="7"/>
       <c r="I16" t="s">
         <v>76</v>
       </c>
@@ -3043,7 +4202,7 @@
       <c r="K16" t="s">
         <v>36</v>
       </c>
-      <c r="L16" s="7"/>
+      <c r="L16" s="9"/>
       <c r="M16" t="s">
         <v>24</v>
       </c>
@@ -3086,7 +4245,7 @@
       <c r="G17" t="s">
         <v>70</v>
       </c>
-      <c r="H17" s="6"/>
+      <c r="H17" s="7"/>
       <c r="I17" t="s">
         <v>76</v>
       </c>
@@ -3096,7 +4255,7 @@
       <c r="K17" t="s">
         <v>36</v>
       </c>
-      <c r="L17" s="7"/>
+      <c r="L17" s="9"/>
       <c r="M17" t="s">
         <v>24</v>
       </c>
@@ -3139,7 +4298,7 @@
       <c r="G18" t="s">
         <v>89</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="H18" s="7" t="s">
         <v>77</v>
       </c>
       <c r="I18" t="s">
@@ -3198,7 +4357,7 @@
       <c r="G19" t="s">
         <v>89</v>
       </c>
-      <c r="H19" s="6"/>
+      <c r="H19" s="7"/>
       <c r="I19" t="s">
         <v>94</v>
       </c>
@@ -3253,7 +4412,7 @@
       <c r="G20" t="s">
         <v>89</v>
       </c>
-      <c r="H20" s="6"/>
+      <c r="H20" s="7"/>
       <c r="I20" t="s">
         <v>94</v>
       </c>
@@ -3308,7 +4467,7 @@
       <c r="G21" t="s">
         <v>89</v>
       </c>
-      <c r="H21" s="6"/>
+      <c r="H21" s="7"/>
       <c r="I21" t="s">
         <v>94</v>
       </c>
@@ -3363,7 +4522,7 @@
       <c r="G22" t="s">
         <v>100</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="H22" s="7" t="s">
         <v>77</v>
       </c>
       <c r="I22" t="s">
@@ -3422,7 +4581,7 @@
       <c r="G23" t="s">
         <v>100</v>
       </c>
-      <c r="H23" s="6"/>
+      <c r="H23" s="7"/>
       <c r="I23" t="s">
         <v>105</v>
       </c>
@@ -3477,7 +4636,7 @@
       <c r="G24" t="s">
         <v>100</v>
       </c>
-      <c r="H24" s="6"/>
+      <c r="H24" s="7"/>
       <c r="I24" t="s">
         <v>105</v>
       </c>
@@ -3532,7 +4691,7 @@
       <c r="G25" t="s">
         <v>100</v>
       </c>
-      <c r="H25" s="6"/>
+      <c r="H25" s="7"/>
       <c r="I25" t="s">
         <v>105</v>
       </c>
@@ -3587,7 +4746,7 @@
       <c r="G26" t="s">
         <v>113</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="H26" s="7" t="s">
         <v>77</v>
       </c>
       <c r="I26" t="s">
@@ -3646,7 +4805,7 @@
       <c r="G27" t="s">
         <v>113</v>
       </c>
-      <c r="H27" s="6"/>
+      <c r="H27" s="7"/>
       <c r="I27" t="s">
         <v>118</v>
       </c>
@@ -3701,7 +4860,7 @@
       <c r="G28" t="s">
         <v>113</v>
       </c>
-      <c r="H28" s="6"/>
+      <c r="H28" s="7"/>
       <c r="I28" t="s">
         <v>118</v>
       </c>
@@ -3756,7 +4915,7 @@
       <c r="G29" t="s">
         <v>113</v>
       </c>
-      <c r="H29" s="6"/>
+      <c r="H29" s="7"/>
       <c r="I29" t="s">
         <v>118</v>
       </c>
@@ -3811,7 +4970,7 @@
       <c r="G30" t="s">
         <v>125</v>
       </c>
-      <c r="H30" s="6" t="s">
+      <c r="H30" s="7" t="s">
         <v>77</v>
       </c>
       <c r="I30" t="s">
@@ -3870,7 +5029,7 @@
       <c r="G31" t="s">
         <v>125</v>
       </c>
-      <c r="H31" s="6"/>
+      <c r="H31" s="7"/>
       <c r="I31" t="s">
         <v>130</v>
       </c>
@@ -3925,7 +5084,7 @@
       <c r="G32" t="s">
         <v>125</v>
       </c>
-      <c r="H32" s="6"/>
+      <c r="H32" s="7"/>
       <c r="I32" t="s">
         <v>130</v>
       </c>
@@ -3980,7 +5139,7 @@
       <c r="G33" t="s">
         <v>125</v>
       </c>
-      <c r="H33" s="6"/>
+      <c r="H33" s="7"/>
       <c r="I33" t="s">
         <v>130</v>
       </c>
@@ -4035,7 +5194,7 @@
       <c r="G34" t="s">
         <v>138</v>
       </c>
-      <c r="H34" s="6" t="s">
+      <c r="H34" s="7" t="s">
         <v>77</v>
       </c>
       <c r="I34" t="s">
@@ -4094,7 +5253,7 @@
       <c r="G35" t="s">
         <v>138</v>
       </c>
-      <c r="H35" s="6"/>
+      <c r="H35" s="7"/>
       <c r="I35" t="s">
         <v>143</v>
       </c>
@@ -4149,7 +5308,7 @@
       <c r="G36" t="s">
         <v>138</v>
       </c>
-      <c r="H36" s="6"/>
+      <c r="H36" s="7"/>
       <c r="I36" t="s">
         <v>143</v>
       </c>
@@ -4204,7 +5363,7 @@
       <c r="G37" t="s">
         <v>138</v>
       </c>
-      <c r="H37" s="6"/>
+      <c r="H37" s="7"/>
       <c r="I37" t="s">
         <v>143</v>
       </c>
@@ -4259,7 +5418,7 @@
       <c r="G38" t="s">
         <v>153</v>
       </c>
-      <c r="H38" s="6" t="s">
+      <c r="H38" s="7" t="s">
         <v>77</v>
       </c>
       <c r="I38" t="s">
@@ -4318,7 +5477,7 @@
       <c r="G39" t="s">
         <v>153</v>
       </c>
-      <c r="H39" s="6"/>
+      <c r="H39" s="7"/>
       <c r="I39" t="s">
         <v>149</v>
       </c>
@@ -4373,7 +5532,7 @@
       <c r="G40" t="s">
         <v>153</v>
       </c>
-      <c r="H40" s="6"/>
+      <c r="H40" s="7"/>
       <c r="I40" t="s">
         <v>149</v>
       </c>
@@ -4428,7 +5587,7 @@
       <c r="G41" t="s">
         <v>153</v>
       </c>
-      <c r="H41" s="6"/>
+      <c r="H41" s="7"/>
       <c r="I41" t="s">
         <v>149</v>
       </c>
@@ -4483,7 +5642,7 @@
       <c r="G42" t="s">
         <v>162</v>
       </c>
-      <c r="H42" s="6" t="s">
+      <c r="H42" s="7" t="s">
         <v>77</v>
       </c>
       <c r="I42" t="s">
@@ -4542,7 +5701,7 @@
       <c r="G43" t="s">
         <v>162</v>
       </c>
-      <c r="H43" s="6"/>
+      <c r="H43" s="7"/>
       <c r="I43" t="s">
         <v>167</v>
       </c>
@@ -4597,7 +5756,7 @@
       <c r="G44" t="s">
         <v>162</v>
       </c>
-      <c r="H44" s="6"/>
+      <c r="H44" s="7"/>
       <c r="I44" t="s">
         <v>167</v>
       </c>
@@ -4652,7 +5811,7 @@
       <c r="G45" t="s">
         <v>162</v>
       </c>
-      <c r="H45" s="6"/>
+      <c r="H45" s="7"/>
       <c r="I45" t="s">
         <v>167</v>
       </c>
@@ -4707,7 +5866,7 @@
       <c r="G46" t="s">
         <v>177</v>
       </c>
-      <c r="H46" s="6" t="s">
+      <c r="H46" s="7" t="s">
         <v>77</v>
       </c>
       <c r="I46" t="s">
@@ -4766,7 +5925,7 @@
       <c r="G47" t="s">
         <v>177</v>
       </c>
-      <c r="H47" s="6"/>
+      <c r="H47" s="7"/>
       <c r="I47" t="s">
         <v>178</v>
       </c>
@@ -4821,7 +5980,7 @@
       <c r="G48" t="s">
         <v>177</v>
       </c>
-      <c r="H48" s="6"/>
+      <c r="H48" s="7"/>
       <c r="I48" t="s">
         <v>178</v>
       </c>
@@ -4876,7 +6035,7 @@
       <c r="G49" t="s">
         <v>177</v>
       </c>
-      <c r="H49" s="6"/>
+      <c r="H49" s="7"/>
       <c r="I49" t="s">
         <v>178</v>
       </c>
@@ -4931,7 +6090,7 @@
       <c r="G50" t="s">
         <v>189</v>
       </c>
-      <c r="H50" s="6" t="s">
+      <c r="H50" s="7" t="s">
         <v>197</v>
       </c>
       <c r="I50" t="s">
@@ -4990,7 +6149,7 @@
       <c r="G51" t="s">
         <v>189</v>
       </c>
-      <c r="H51" s="6"/>
+      <c r="H51" s="7"/>
       <c r="I51" t="s">
         <v>191</v>
       </c>
@@ -5045,7 +6204,7 @@
       <c r="G52" t="s">
         <v>189</v>
       </c>
-      <c r="H52" s="6"/>
+      <c r="H52" s="7"/>
       <c r="I52" t="s">
         <v>191</v>
       </c>
@@ -5100,7 +6259,7 @@
       <c r="G53" t="s">
         <v>189</v>
       </c>
-      <c r="H53" s="6"/>
+      <c r="H53" s="7"/>
       <c r="I53" t="s">
         <v>191</v>
       </c>
@@ -5155,7 +6314,7 @@
       <c r="G54" t="s">
         <v>204</v>
       </c>
-      <c r="H54" s="6" t="s">
+      <c r="H54" s="7" t="s">
         <v>211</v>
       </c>
       <c r="I54" t="s">
@@ -5214,7 +6373,7 @@
       <c r="G55" t="s">
         <v>204</v>
       </c>
-      <c r="H55" s="6"/>
+      <c r="H55" s="7"/>
       <c r="I55" t="s">
         <v>210</v>
       </c>
@@ -5269,7 +6428,7 @@
       <c r="G56" t="s">
         <v>204</v>
       </c>
-      <c r="H56" s="6"/>
+      <c r="H56" s="7"/>
       <c r="I56" t="s">
         <v>210</v>
       </c>
@@ -5324,7 +6483,7 @@
       <c r="G57" t="s">
         <v>204</v>
       </c>
-      <c r="H57" s="6"/>
+      <c r="H57" s="7"/>
       <c r="I57" t="s">
         <v>210</v>
       </c>
@@ -5379,7 +6538,7 @@
       <c r="G58" t="s">
         <v>217</v>
       </c>
-      <c r="H58" s="6" t="s">
+      <c r="H58" s="7" t="s">
         <v>77</v>
       </c>
       <c r="I58" t="s">
@@ -5438,7 +6597,7 @@
       <c r="G59" t="s">
         <v>217</v>
       </c>
-      <c r="H59" s="6"/>
+      <c r="H59" s="7"/>
       <c r="I59" t="s">
         <v>223</v>
       </c>
@@ -5493,7 +6652,7 @@
       <c r="G60" t="s">
         <v>217</v>
       </c>
-      <c r="H60" s="6"/>
+      <c r="H60" s="7"/>
       <c r="I60" t="s">
         <v>223</v>
       </c>
@@ -5548,7 +6707,7 @@
       <c r="G61" t="s">
         <v>217</v>
       </c>
-      <c r="H61" s="6"/>
+      <c r="H61" s="7"/>
       <c r="I61" t="s">
         <v>223</v>
       </c>
@@ -5603,7 +6762,7 @@
       <c r="G62" t="s">
         <v>230</v>
       </c>
-      <c r="H62" s="6" t="s">
+      <c r="H62" s="7" t="s">
         <v>77</v>
       </c>
       <c r="I62" t="s">
@@ -5662,7 +6821,7 @@
       <c r="G63" t="s">
         <v>230</v>
       </c>
-      <c r="H63" s="6"/>
+      <c r="H63" s="7"/>
       <c r="I63" t="s">
         <v>235</v>
       </c>
@@ -5717,7 +6876,7 @@
       <c r="G64" t="s">
         <v>230</v>
       </c>
-      <c r="H64" s="6"/>
+      <c r="H64" s="7"/>
       <c r="I64" t="s">
         <v>235</v>
       </c>
@@ -5772,7 +6931,7 @@
       <c r="G65" t="s">
         <v>230</v>
       </c>
-      <c r="H65" s="6"/>
+      <c r="H65" s="7"/>
       <c r="I65" t="s">
         <v>235</v>
       </c>
@@ -5827,7 +6986,7 @@
       <c r="G66" t="s">
         <v>241</v>
       </c>
-      <c r="H66" s="6" t="s">
+      <c r="H66" s="7" t="s">
         <v>77</v>
       </c>
       <c r="I66" t="s">
@@ -5886,7 +7045,7 @@
       <c r="G67" t="s">
         <v>241</v>
       </c>
-      <c r="H67" s="6"/>
+      <c r="H67" s="7"/>
       <c r="I67" t="s">
         <v>246</v>
       </c>
@@ -5941,7 +7100,7 @@
       <c r="G68" t="s">
         <v>241</v>
       </c>
-      <c r="H68" s="6"/>
+      <c r="H68" s="7"/>
       <c r="I68" t="s">
         <v>246</v>
       </c>
@@ -5996,7 +7155,7 @@
       <c r="G69" t="s">
         <v>241</v>
       </c>
-      <c r="H69" s="6"/>
+      <c r="H69" s="7"/>
       <c r="I69" t="s">
         <v>246</v>
       </c>
@@ -6051,7 +7210,7 @@
       <c r="G70" t="s">
         <v>254</v>
       </c>
-      <c r="H70" s="6" t="s">
+      <c r="H70" s="7" t="s">
         <v>77</v>
       </c>
       <c r="I70" t="s">
@@ -6110,7 +7269,7 @@
       <c r="G71" t="s">
         <v>254</v>
       </c>
-      <c r="H71" s="6"/>
+      <c r="H71" s="7"/>
       <c r="I71" t="s">
         <v>259</v>
       </c>
@@ -6165,7 +7324,7 @@
       <c r="G72" t="s">
         <v>254</v>
       </c>
-      <c r="H72" s="6"/>
+      <c r="H72" s="7"/>
       <c r="I72" t="s">
         <v>259</v>
       </c>
@@ -6220,7 +7379,7 @@
       <c r="G73" t="s">
         <v>254</v>
       </c>
-      <c r="H73" s="6"/>
+      <c r="H73" s="7"/>
       <c r="I73" t="s">
         <v>259</v>
       </c>
@@ -6275,7 +7434,7 @@
       <c r="G74" t="s">
         <v>266</v>
       </c>
-      <c r="H74" s="6" t="s">
+      <c r="H74" s="7" t="s">
         <v>77</v>
       </c>
       <c r="I74" t="s">
@@ -6334,7 +7493,7 @@
       <c r="G75" t="s">
         <v>266</v>
       </c>
-      <c r="H75" s="6"/>
+      <c r="H75" s="7"/>
       <c r="I75" t="s">
         <v>271</v>
       </c>
@@ -6389,7 +7548,7 @@
       <c r="G76" t="s">
         <v>266</v>
       </c>
-      <c r="H76" s="6"/>
+      <c r="H76" s="7"/>
       <c r="I76" t="s">
         <v>271</v>
       </c>
@@ -6444,7 +7603,7 @@
       <c r="G77" t="s">
         <v>266</v>
       </c>
-      <c r="H77" s="6"/>
+      <c r="H77" s="7"/>
       <c r="I77" t="s">
         <v>271</v>
       </c>
@@ -6499,7 +7658,7 @@
       <c r="G78" t="s">
         <v>276</v>
       </c>
-      <c r="H78" s="6" t="s">
+      <c r="H78" s="7" t="s">
         <v>281</v>
       </c>
       <c r="I78" t="s">
@@ -6558,7 +7717,7 @@
       <c r="G79" t="s">
         <v>276</v>
       </c>
-      <c r="H79" s="6"/>
+      <c r="H79" s="7"/>
       <c r="I79" t="s">
         <v>283</v>
       </c>
@@ -6613,7 +7772,7 @@
       <c r="G80" t="s">
         <v>276</v>
       </c>
-      <c r="H80" s="6"/>
+      <c r="H80" s="7"/>
       <c r="I80" t="s">
         <v>283</v>
       </c>
@@ -6646,7 +7805,7 @@
       </c>
       <c r="S80" s="8"/>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>274</v>
       </c>
@@ -6668,7 +7827,7 @@
       <c r="G81" t="s">
         <v>276</v>
       </c>
-      <c r="H81" s="6"/>
+      <c r="H81" s="7"/>
       <c r="I81" t="s">
         <v>283</v>
       </c>
@@ -6701,7 +7860,7 @@
       </c>
       <c r="S81" s="8"/>
     </row>
-    <row r="82" spans="1:19" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:20" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>289</v>
       </c>
@@ -6723,7 +7882,7 @@
       <c r="G82" t="s">
         <v>291</v>
       </c>
-      <c r="H82" s="6" t="s">
+      <c r="H82" s="7" t="s">
         <v>296</v>
       </c>
       <c r="I82" t="s">
@@ -6760,7 +7919,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>289</v>
       </c>
@@ -6782,7 +7941,7 @@
       <c r="G83" t="s">
         <v>291</v>
       </c>
-      <c r="H83" s="6"/>
+      <c r="H83" s="7"/>
       <c r="I83" t="s">
         <v>297</v>
       </c>
@@ -6815,7 +7974,7 @@
       </c>
       <c r="S83" s="8"/>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>289</v>
       </c>
@@ -6837,7 +7996,7 @@
       <c r="G84" t="s">
         <v>291</v>
       </c>
-      <c r="H84" s="6"/>
+      <c r="H84" s="7"/>
       <c r="I84" t="s">
         <v>297</v>
       </c>
@@ -6870,7 +8029,7 @@
       </c>
       <c r="S84" s="8"/>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>289</v>
       </c>
@@ -6892,7 +8051,7 @@
       <c r="G85" t="s">
         <v>291</v>
       </c>
-      <c r="H85" s="6"/>
+      <c r="H85" s="7"/>
       <c r="I85" t="s">
         <v>297</v>
       </c>
@@ -6925,7 +8084,7 @@
       </c>
       <c r="S85" s="8"/>
     </row>
-    <row r="86" spans="1:19" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:20" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>301</v>
       </c>
@@ -6947,7 +8106,7 @@
       <c r="G86" t="s">
         <v>303</v>
       </c>
-      <c r="H86" s="6" t="s">
+      <c r="H86" s="7" t="s">
         <v>296</v>
       </c>
       <c r="I86" t="s">
@@ -6984,7 +8143,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>301</v>
       </c>
@@ -7006,7 +8165,7 @@
       <c r="G87" t="s">
         <v>303</v>
       </c>
-      <c r="H87" s="6"/>
+      <c r="H87" s="7"/>
       <c r="I87" t="s">
         <v>308</v>
       </c>
@@ -7039,7 +8198,7 @@
       </c>
       <c r="S87" s="8"/>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>301</v>
       </c>
@@ -7061,7 +8220,7 @@
       <c r="G88" t="s">
         <v>303</v>
       </c>
-      <c r="H88" s="6"/>
+      <c r="H88" s="7"/>
       <c r="I88" t="s">
         <v>308</v>
       </c>
@@ -7094,7 +8253,7 @@
       </c>
       <c r="S88" s="8"/>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>301</v>
       </c>
@@ -7116,7 +8275,7 @@
       <c r="G89" t="s">
         <v>303</v>
       </c>
-      <c r="H89" s="6"/>
+      <c r="H89" s="7"/>
       <c r="I89" t="s">
         <v>308</v>
       </c>
@@ -7149,8 +8308,3456 @@
       </c>
       <c r="S89" s="8"/>
     </row>
+    <row r="90" spans="1:20" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>313</v>
+      </c>
+      <c r="B90" s="3">
+        <v>1625</v>
+      </c>
+      <c r="C90" t="s">
+        <v>403</v>
+      </c>
+      <c r="D90" t="s">
+        <v>408</v>
+      </c>
+      <c r="E90" t="s">
+        <v>218</v>
+      </c>
+      <c r="F90" t="s">
+        <v>407</v>
+      </c>
+      <c r="G90" t="s">
+        <v>409</v>
+      </c>
+      <c r="H90" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="I90" t="s">
+        <v>410</v>
+      </c>
+      <c r="J90" t="s">
+        <v>411</v>
+      </c>
+      <c r="K90" t="s">
+        <v>36</v>
+      </c>
+      <c r="L90" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="M90" t="s">
+        <v>27</v>
+      </c>
+      <c r="N90" t="s">
+        <v>413</v>
+      </c>
+      <c r="O90" t="s">
+        <v>414</v>
+      </c>
+      <c r="P90" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>24</v>
+      </c>
+      <c r="R90" t="s">
+        <v>27</v>
+      </c>
+      <c r="S90" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="T90" s="10" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>313</v>
+      </c>
+      <c r="B91" s="3">
+        <v>1625</v>
+      </c>
+      <c r="C91" t="s">
+        <v>403</v>
+      </c>
+      <c r="D91" t="s">
+        <v>408</v>
+      </c>
+      <c r="E91" t="s">
+        <v>404</v>
+      </c>
+      <c r="F91" t="s">
+        <v>407</v>
+      </c>
+      <c r="G91" t="s">
+        <v>409</v>
+      </c>
+      <c r="H91" s="7"/>
+      <c r="I91" t="s">
+        <v>410</v>
+      </c>
+      <c r="J91" t="s">
+        <v>411</v>
+      </c>
+      <c r="K91" t="s">
+        <v>36</v>
+      </c>
+      <c r="L91" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="M91" t="s">
+        <v>27</v>
+      </c>
+      <c r="N91" t="s">
+        <v>413</v>
+      </c>
+      <c r="O91" t="s">
+        <v>414</v>
+      </c>
+      <c r="P91" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>24</v>
+      </c>
+      <c r="R91" t="s">
+        <v>27</v>
+      </c>
+      <c r="S91" s="8"/>
+    </row>
+    <row r="92" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>313</v>
+      </c>
+      <c r="B92" s="3">
+        <v>1625</v>
+      </c>
+      <c r="C92" t="s">
+        <v>403</v>
+      </c>
+      <c r="D92" t="s">
+        <v>408</v>
+      </c>
+      <c r="E92" t="s">
+        <v>405</v>
+      </c>
+      <c r="F92" t="s">
+        <v>407</v>
+      </c>
+      <c r="G92" t="s">
+        <v>409</v>
+      </c>
+      <c r="H92" s="7"/>
+      <c r="I92" t="s">
+        <v>410</v>
+      </c>
+      <c r="J92" t="s">
+        <v>411</v>
+      </c>
+      <c r="K92" t="s">
+        <v>36</v>
+      </c>
+      <c r="L92" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="M92" t="s">
+        <v>27</v>
+      </c>
+      <c r="N92" t="s">
+        <v>413</v>
+      </c>
+      <c r="O92" t="s">
+        <v>414</v>
+      </c>
+      <c r="P92" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>24</v>
+      </c>
+      <c r="R92" t="s">
+        <v>27</v>
+      </c>
+      <c r="S92" s="8"/>
+    </row>
+    <row r="93" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>313</v>
+      </c>
+      <c r="B93" s="3">
+        <v>1625</v>
+      </c>
+      <c r="C93" t="s">
+        <v>403</v>
+      </c>
+      <c r="D93" t="s">
+        <v>408</v>
+      </c>
+      <c r="E93" t="s">
+        <v>406</v>
+      </c>
+      <c r="F93" t="s">
+        <v>407</v>
+      </c>
+      <c r="G93" t="s">
+        <v>409</v>
+      </c>
+      <c r="H93" s="7"/>
+      <c r="I93" t="s">
+        <v>410</v>
+      </c>
+      <c r="J93" t="s">
+        <v>411</v>
+      </c>
+      <c r="K93" t="s">
+        <v>36</v>
+      </c>
+      <c r="L93" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="M93" t="s">
+        <v>27</v>
+      </c>
+      <c r="N93" t="s">
+        <v>413</v>
+      </c>
+      <c r="O93" t="s">
+        <v>414</v>
+      </c>
+      <c r="P93" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>24</v>
+      </c>
+      <c r="R93" t="s">
+        <v>27</v>
+      </c>
+      <c r="S93" s="8"/>
+    </row>
+    <row r="94" spans="1:20" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>314</v>
+      </c>
+      <c r="B94" s="3">
+        <v>1686</v>
+      </c>
+      <c r="C94" t="s">
+        <v>315</v>
+      </c>
+      <c r="D94" t="s">
+        <v>316</v>
+      </c>
+      <c r="E94" t="s">
+        <v>218</v>
+      </c>
+      <c r="F94" t="s">
+        <v>321</v>
+      </c>
+      <c r="G94" t="s">
+        <v>317</v>
+      </c>
+      <c r="H94" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="I94" t="s">
+        <v>322</v>
+      </c>
+      <c r="J94" t="s">
+        <v>323</v>
+      </c>
+      <c r="K94" t="s">
+        <v>36</v>
+      </c>
+      <c r="L94" t="s">
+        <v>22</v>
+      </c>
+      <c r="M94" t="s">
+        <v>27</v>
+      </c>
+      <c r="N94" t="s">
+        <v>324</v>
+      </c>
+      <c r="O94" t="s">
+        <v>324</v>
+      </c>
+      <c r="P94" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>324</v>
+      </c>
+      <c r="R94" t="s">
+        <v>27</v>
+      </c>
+      <c r="S94" s="8" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>314</v>
+      </c>
+      <c r="B95" s="3">
+        <v>1686</v>
+      </c>
+      <c r="C95" t="s">
+        <v>315</v>
+      </c>
+      <c r="D95" t="s">
+        <v>316</v>
+      </c>
+      <c r="E95" t="s">
+        <v>318</v>
+      </c>
+      <c r="F95" t="s">
+        <v>321</v>
+      </c>
+      <c r="G95" t="s">
+        <v>317</v>
+      </c>
+      <c r="H95" s="7"/>
+      <c r="I95" t="s">
+        <v>322</v>
+      </c>
+      <c r="J95" t="s">
+        <v>323</v>
+      </c>
+      <c r="K95" t="s">
+        <v>36</v>
+      </c>
+      <c r="L95" t="s">
+        <v>22</v>
+      </c>
+      <c r="M95" t="s">
+        <v>27</v>
+      </c>
+      <c r="N95" t="s">
+        <v>324</v>
+      </c>
+      <c r="O95" t="s">
+        <v>324</v>
+      </c>
+      <c r="P95" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>324</v>
+      </c>
+      <c r="R95" t="s">
+        <v>27</v>
+      </c>
+      <c r="S95" s="8"/>
+    </row>
+    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>314</v>
+      </c>
+      <c r="B96" s="3">
+        <v>1686</v>
+      </c>
+      <c r="C96" t="s">
+        <v>315</v>
+      </c>
+      <c r="D96" t="s">
+        <v>316</v>
+      </c>
+      <c r="E96" t="s">
+        <v>319</v>
+      </c>
+      <c r="F96" t="s">
+        <v>321</v>
+      </c>
+      <c r="G96" t="s">
+        <v>317</v>
+      </c>
+      <c r="H96" s="7"/>
+      <c r="I96" t="s">
+        <v>322</v>
+      </c>
+      <c r="J96" t="s">
+        <v>323</v>
+      </c>
+      <c r="K96" t="s">
+        <v>36</v>
+      </c>
+      <c r="L96" t="s">
+        <v>22</v>
+      </c>
+      <c r="M96" t="s">
+        <v>27</v>
+      </c>
+      <c r="N96" t="s">
+        <v>324</v>
+      </c>
+      <c r="O96" t="s">
+        <v>324</v>
+      </c>
+      <c r="P96" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>324</v>
+      </c>
+      <c r="R96" t="s">
+        <v>27</v>
+      </c>
+      <c r="S96" s="8"/>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>314</v>
+      </c>
+      <c r="B97" s="3">
+        <v>1686</v>
+      </c>
+      <c r="C97" t="s">
+        <v>315</v>
+      </c>
+      <c r="D97" t="s">
+        <v>316</v>
+      </c>
+      <c r="E97" t="s">
+        <v>320</v>
+      </c>
+      <c r="F97" t="s">
+        <v>321</v>
+      </c>
+      <c r="G97" t="s">
+        <v>317</v>
+      </c>
+      <c r="H97" s="7"/>
+      <c r="I97" t="s">
+        <v>322</v>
+      </c>
+      <c r="J97" t="s">
+        <v>323</v>
+      </c>
+      <c r="K97" t="s">
+        <v>36</v>
+      </c>
+      <c r="L97" t="s">
+        <v>22</v>
+      </c>
+      <c r="M97" t="s">
+        <v>27</v>
+      </c>
+      <c r="N97" t="s">
+        <v>324</v>
+      </c>
+      <c r="O97" t="s">
+        <v>324</v>
+      </c>
+      <c r="P97" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>324</v>
+      </c>
+      <c r="R97" t="s">
+        <v>27</v>
+      </c>
+      <c r="S97" s="8"/>
+    </row>
+    <row r="98" spans="1:19" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>326</v>
+      </c>
+      <c r="B98" s="3">
+        <v>1744</v>
+      </c>
+      <c r="C98" t="s">
+        <v>327</v>
+      </c>
+      <c r="D98" t="s">
+        <v>328</v>
+      </c>
+      <c r="E98" t="s">
+        <v>218</v>
+      </c>
+      <c r="F98" t="s">
+        <v>330</v>
+      </c>
+      <c r="G98" t="s">
+        <v>329</v>
+      </c>
+      <c r="H98" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="I98" t="s">
+        <v>334</v>
+      </c>
+      <c r="J98" t="s">
+        <v>335</v>
+      </c>
+      <c r="K98" t="s">
+        <v>36</v>
+      </c>
+      <c r="L98" t="s">
+        <v>22</v>
+      </c>
+      <c r="M98" t="s">
+        <v>27</v>
+      </c>
+      <c r="N98" t="s">
+        <v>27</v>
+      </c>
+      <c r="O98" t="s">
+        <v>27</v>
+      </c>
+      <c r="P98" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>24</v>
+      </c>
+      <c r="R98" t="s">
+        <v>27</v>
+      </c>
+      <c r="S98" s="8" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>326</v>
+      </c>
+      <c r="B99" s="3">
+        <v>1744</v>
+      </c>
+      <c r="C99" t="s">
+        <v>327</v>
+      </c>
+      <c r="D99" t="s">
+        <v>328</v>
+      </c>
+      <c r="E99" t="s">
+        <v>331</v>
+      </c>
+      <c r="F99" t="s">
+        <v>330</v>
+      </c>
+      <c r="G99" t="s">
+        <v>329</v>
+      </c>
+      <c r="H99" s="7"/>
+      <c r="I99" t="s">
+        <v>334</v>
+      </c>
+      <c r="J99" t="s">
+        <v>335</v>
+      </c>
+      <c r="K99" t="s">
+        <v>36</v>
+      </c>
+      <c r="L99" t="s">
+        <v>22</v>
+      </c>
+      <c r="M99" t="s">
+        <v>27</v>
+      </c>
+      <c r="N99" t="s">
+        <v>27</v>
+      </c>
+      <c r="O99" t="s">
+        <v>27</v>
+      </c>
+      <c r="P99" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>24</v>
+      </c>
+      <c r="R99" t="s">
+        <v>27</v>
+      </c>
+      <c r="S99" s="8"/>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>326</v>
+      </c>
+      <c r="B100" s="3">
+        <v>1744</v>
+      </c>
+      <c r="C100" t="s">
+        <v>327</v>
+      </c>
+      <c r="D100" t="s">
+        <v>328</v>
+      </c>
+      <c r="E100" t="s">
+        <v>332</v>
+      </c>
+      <c r="F100" t="s">
+        <v>330</v>
+      </c>
+      <c r="G100" t="s">
+        <v>329</v>
+      </c>
+      <c r="H100" s="7"/>
+      <c r="I100" t="s">
+        <v>334</v>
+      </c>
+      <c r="J100" t="s">
+        <v>335</v>
+      </c>
+      <c r="K100" t="s">
+        <v>36</v>
+      </c>
+      <c r="L100" t="s">
+        <v>22</v>
+      </c>
+      <c r="M100" t="s">
+        <v>27</v>
+      </c>
+      <c r="N100" t="s">
+        <v>27</v>
+      </c>
+      <c r="O100" t="s">
+        <v>27</v>
+      </c>
+      <c r="P100" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>24</v>
+      </c>
+      <c r="R100" t="s">
+        <v>27</v>
+      </c>
+      <c r="S100" s="8"/>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>326</v>
+      </c>
+      <c r="B101" s="3">
+        <v>1744</v>
+      </c>
+      <c r="C101" t="s">
+        <v>327</v>
+      </c>
+      <c r="D101" t="s">
+        <v>328</v>
+      </c>
+      <c r="E101" t="s">
+        <v>333</v>
+      </c>
+      <c r="F101" t="s">
+        <v>330</v>
+      </c>
+      <c r="G101" t="s">
+        <v>329</v>
+      </c>
+      <c r="H101" s="7"/>
+      <c r="I101" t="s">
+        <v>334</v>
+      </c>
+      <c r="J101" t="s">
+        <v>335</v>
+      </c>
+      <c r="K101" t="s">
+        <v>36</v>
+      </c>
+      <c r="L101" t="s">
+        <v>22</v>
+      </c>
+      <c r="M101" t="s">
+        <v>27</v>
+      </c>
+      <c r="N101" t="s">
+        <v>27</v>
+      </c>
+      <c r="O101" t="s">
+        <v>27</v>
+      </c>
+      <c r="P101" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>24</v>
+      </c>
+      <c r="R101" t="s">
+        <v>27</v>
+      </c>
+      <c r="S101" s="8"/>
+    </row>
+    <row r="102" spans="1:19" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>338</v>
+      </c>
+      <c r="B102" s="3">
+        <v>1802</v>
+      </c>
+      <c r="C102" t="s">
+        <v>160</v>
+      </c>
+      <c r="D102" t="s">
+        <v>339</v>
+      </c>
+      <c r="E102" t="s">
+        <v>218</v>
+      </c>
+      <c r="F102" t="s">
+        <v>341</v>
+      </c>
+      <c r="G102" t="s">
+        <v>340</v>
+      </c>
+      <c r="H102" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="I102" t="s">
+        <v>345</v>
+      </c>
+      <c r="J102" t="s">
+        <v>346</v>
+      </c>
+      <c r="K102" t="s">
+        <v>36</v>
+      </c>
+      <c r="L102" t="s">
+        <v>22</v>
+      </c>
+      <c r="M102" t="s">
+        <v>24</v>
+      </c>
+      <c r="N102" t="s">
+        <v>24</v>
+      </c>
+      <c r="O102" t="s">
+        <v>27</v>
+      </c>
+      <c r="P102" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>24</v>
+      </c>
+      <c r="R102" t="s">
+        <v>27</v>
+      </c>
+      <c r="S102" s="8" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>338</v>
+      </c>
+      <c r="B103" s="3">
+        <v>1802</v>
+      </c>
+      <c r="C103" t="s">
+        <v>160</v>
+      </c>
+      <c r="D103" t="s">
+        <v>339</v>
+      </c>
+      <c r="E103" t="s">
+        <v>342</v>
+      </c>
+      <c r="F103" t="s">
+        <v>341</v>
+      </c>
+      <c r="G103" t="s">
+        <v>340</v>
+      </c>
+      <c r="H103" s="7"/>
+      <c r="I103" t="s">
+        <v>345</v>
+      </c>
+      <c r="J103" t="s">
+        <v>346</v>
+      </c>
+      <c r="K103" t="s">
+        <v>36</v>
+      </c>
+      <c r="L103" t="s">
+        <v>22</v>
+      </c>
+      <c r="M103" t="s">
+        <v>24</v>
+      </c>
+      <c r="N103" t="s">
+        <v>24</v>
+      </c>
+      <c r="O103" t="s">
+        <v>27</v>
+      </c>
+      <c r="P103" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>24</v>
+      </c>
+      <c r="R103" t="s">
+        <v>27</v>
+      </c>
+      <c r="S103" s="8"/>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>338</v>
+      </c>
+      <c r="B104" s="3">
+        <v>1802</v>
+      </c>
+      <c r="C104" t="s">
+        <v>160</v>
+      </c>
+      <c r="D104" t="s">
+        <v>339</v>
+      </c>
+      <c r="E104" t="s">
+        <v>343</v>
+      </c>
+      <c r="F104" t="s">
+        <v>341</v>
+      </c>
+      <c r="G104" t="s">
+        <v>340</v>
+      </c>
+      <c r="H104" s="7"/>
+      <c r="I104" t="s">
+        <v>345</v>
+      </c>
+      <c r="J104" t="s">
+        <v>346</v>
+      </c>
+      <c r="K104" t="s">
+        <v>36</v>
+      </c>
+      <c r="L104" t="s">
+        <v>22</v>
+      </c>
+      <c r="M104" t="s">
+        <v>24</v>
+      </c>
+      <c r="N104" t="s">
+        <v>24</v>
+      </c>
+      <c r="O104" t="s">
+        <v>27</v>
+      </c>
+      <c r="P104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>24</v>
+      </c>
+      <c r="R104" t="s">
+        <v>27</v>
+      </c>
+      <c r="S104" s="8"/>
+    </row>
+    <row r="105" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>338</v>
+      </c>
+      <c r="B105" s="3">
+        <v>1802</v>
+      </c>
+      <c r="C105" t="s">
+        <v>160</v>
+      </c>
+      <c r="D105" t="s">
+        <v>339</v>
+      </c>
+      <c r="E105" t="s">
+        <v>344</v>
+      </c>
+      <c r="F105" t="s">
+        <v>341</v>
+      </c>
+      <c r="G105" t="s">
+        <v>340</v>
+      </c>
+      <c r="H105" s="7"/>
+      <c r="I105" t="s">
+        <v>345</v>
+      </c>
+      <c r="J105" t="s">
+        <v>346</v>
+      </c>
+      <c r="K105" t="s">
+        <v>36</v>
+      </c>
+      <c r="L105" t="s">
+        <v>22</v>
+      </c>
+      <c r="M105" t="s">
+        <v>24</v>
+      </c>
+      <c r="N105" t="s">
+        <v>24</v>
+      </c>
+      <c r="O105" t="s">
+        <v>27</v>
+      </c>
+      <c r="P105" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>24</v>
+      </c>
+      <c r="R105" t="s">
+        <v>27</v>
+      </c>
+      <c r="S105" s="8"/>
+    </row>
+    <row r="106" spans="1:19" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>348</v>
+      </c>
+      <c r="B106" s="3">
+        <v>1860</v>
+      </c>
+      <c r="C106" t="s">
+        <v>349</v>
+      </c>
+      <c r="D106" t="s">
+        <v>350</v>
+      </c>
+      <c r="E106" t="s">
+        <v>218</v>
+      </c>
+      <c r="F106" t="s">
+        <v>355</v>
+      </c>
+      <c r="G106" t="s">
+        <v>351</v>
+      </c>
+      <c r="H106" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="I106" t="s">
+        <v>356</v>
+      </c>
+      <c r="J106" t="s">
+        <v>357</v>
+      </c>
+      <c r="K106" t="s">
+        <v>36</v>
+      </c>
+      <c r="L106" t="s">
+        <v>22</v>
+      </c>
+      <c r="M106" t="s">
+        <v>24</v>
+      </c>
+      <c r="N106" t="s">
+        <v>27</v>
+      </c>
+      <c r="O106" t="s">
+        <v>358</v>
+      </c>
+      <c r="P106" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>24</v>
+      </c>
+      <c r="R106" t="s">
+        <v>27</v>
+      </c>
+      <c r="S106" s="8" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>348</v>
+      </c>
+      <c r="B107" s="3">
+        <v>1860</v>
+      </c>
+      <c r="C107" t="s">
+        <v>349</v>
+      </c>
+      <c r="D107" t="s">
+        <v>350</v>
+      </c>
+      <c r="E107" t="s">
+        <v>352</v>
+      </c>
+      <c r="F107" t="s">
+        <v>355</v>
+      </c>
+      <c r="G107" t="s">
+        <v>351</v>
+      </c>
+      <c r="H107" s="7"/>
+      <c r="I107" t="s">
+        <v>356</v>
+      </c>
+      <c r="J107" t="s">
+        <v>357</v>
+      </c>
+      <c r="K107" t="s">
+        <v>36</v>
+      </c>
+      <c r="L107" t="s">
+        <v>22</v>
+      </c>
+      <c r="M107" t="s">
+        <v>24</v>
+      </c>
+      <c r="N107" t="s">
+        <v>27</v>
+      </c>
+      <c r="O107" t="s">
+        <v>358</v>
+      </c>
+      <c r="P107" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>24</v>
+      </c>
+      <c r="R107" t="s">
+        <v>27</v>
+      </c>
+      <c r="S107" s="8"/>
+    </row>
+    <row r="108" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>348</v>
+      </c>
+      <c r="B108" s="3">
+        <v>1860</v>
+      </c>
+      <c r="C108" t="s">
+        <v>349</v>
+      </c>
+      <c r="D108" t="s">
+        <v>350</v>
+      </c>
+      <c r="E108" t="s">
+        <v>353</v>
+      </c>
+      <c r="F108" t="s">
+        <v>355</v>
+      </c>
+      <c r="G108" t="s">
+        <v>351</v>
+      </c>
+      <c r="H108" s="7"/>
+      <c r="I108" t="s">
+        <v>356</v>
+      </c>
+      <c r="J108" t="s">
+        <v>357</v>
+      </c>
+      <c r="K108" t="s">
+        <v>36</v>
+      </c>
+      <c r="L108" t="s">
+        <v>22</v>
+      </c>
+      <c r="M108" t="s">
+        <v>24</v>
+      </c>
+      <c r="N108" t="s">
+        <v>27</v>
+      </c>
+      <c r="O108" t="s">
+        <v>358</v>
+      </c>
+      <c r="P108" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>24</v>
+      </c>
+      <c r="R108" t="s">
+        <v>27</v>
+      </c>
+      <c r="S108" s="8"/>
+    </row>
+    <row r="109" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>348</v>
+      </c>
+      <c r="B109" s="3">
+        <v>1860</v>
+      </c>
+      <c r="C109" t="s">
+        <v>349</v>
+      </c>
+      <c r="D109" t="s">
+        <v>350</v>
+      </c>
+      <c r="E109" t="s">
+        <v>354</v>
+      </c>
+      <c r="F109" t="s">
+        <v>355</v>
+      </c>
+      <c r="G109" t="s">
+        <v>351</v>
+      </c>
+      <c r="H109" s="7"/>
+      <c r="I109" t="s">
+        <v>356</v>
+      </c>
+      <c r="J109" t="s">
+        <v>357</v>
+      </c>
+      <c r="K109" t="s">
+        <v>36</v>
+      </c>
+      <c r="L109" t="s">
+        <v>22</v>
+      </c>
+      <c r="M109" t="s">
+        <v>24</v>
+      </c>
+      <c r="N109" t="s">
+        <v>27</v>
+      </c>
+      <c r="O109" t="s">
+        <v>358</v>
+      </c>
+      <c r="P109" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>24</v>
+      </c>
+      <c r="R109" t="s">
+        <v>27</v>
+      </c>
+      <c r="S109" s="8"/>
+    </row>
+    <row r="110" spans="1:19" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>360</v>
+      </c>
+      <c r="B110" s="3">
+        <v>1918</v>
+      </c>
+      <c r="C110" t="s">
+        <v>160</v>
+      </c>
+      <c r="D110" t="s">
+        <v>361</v>
+      </c>
+      <c r="E110" t="s">
+        <v>218</v>
+      </c>
+      <c r="F110" t="s">
+        <v>363</v>
+      </c>
+      <c r="G110" t="s">
+        <v>362</v>
+      </c>
+      <c r="H110" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="I110" t="s">
+        <v>367</v>
+      </c>
+      <c r="J110" t="s">
+        <v>368</v>
+      </c>
+      <c r="K110" t="s">
+        <v>36</v>
+      </c>
+      <c r="L110" t="s">
+        <v>22</v>
+      </c>
+      <c r="M110" t="s">
+        <v>370</v>
+      </c>
+      <c r="N110" t="s">
+        <v>27</v>
+      </c>
+      <c r="O110" t="s">
+        <v>27</v>
+      </c>
+      <c r="P110" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>24</v>
+      </c>
+      <c r="R110" t="s">
+        <v>27</v>
+      </c>
+      <c r="S110" s="8" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>360</v>
+      </c>
+      <c r="B111" s="3">
+        <v>1918</v>
+      </c>
+      <c r="C111" t="s">
+        <v>160</v>
+      </c>
+      <c r="D111" t="s">
+        <v>361</v>
+      </c>
+      <c r="E111" t="s">
+        <v>364</v>
+      </c>
+      <c r="F111" t="s">
+        <v>363</v>
+      </c>
+      <c r="G111" t="s">
+        <v>362</v>
+      </c>
+      <c r="H111" s="7"/>
+      <c r="I111" t="s">
+        <v>367</v>
+      </c>
+      <c r="J111" t="s">
+        <v>368</v>
+      </c>
+      <c r="K111" t="s">
+        <v>36</v>
+      </c>
+      <c r="L111" t="s">
+        <v>22</v>
+      </c>
+      <c r="M111" t="s">
+        <v>370</v>
+      </c>
+      <c r="N111" t="s">
+        <v>27</v>
+      </c>
+      <c r="O111" t="s">
+        <v>27</v>
+      </c>
+      <c r="P111" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>24</v>
+      </c>
+      <c r="R111" t="s">
+        <v>27</v>
+      </c>
+      <c r="S111" s="8"/>
+    </row>
+    <row r="112" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>360</v>
+      </c>
+      <c r="B112" s="3">
+        <v>1918</v>
+      </c>
+      <c r="C112" t="s">
+        <v>160</v>
+      </c>
+      <c r="D112" t="s">
+        <v>361</v>
+      </c>
+      <c r="E112" t="s">
+        <v>365</v>
+      </c>
+      <c r="F112" t="s">
+        <v>363</v>
+      </c>
+      <c r="G112" t="s">
+        <v>362</v>
+      </c>
+      <c r="H112" s="7"/>
+      <c r="I112" t="s">
+        <v>367</v>
+      </c>
+      <c r="J112" t="s">
+        <v>368</v>
+      </c>
+      <c r="K112" t="s">
+        <v>36</v>
+      </c>
+      <c r="L112" t="s">
+        <v>22</v>
+      </c>
+      <c r="M112" t="s">
+        <v>370</v>
+      </c>
+      <c r="N112" t="s">
+        <v>27</v>
+      </c>
+      <c r="O112" t="s">
+        <v>27</v>
+      </c>
+      <c r="P112" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>24</v>
+      </c>
+      <c r="R112" t="s">
+        <v>27</v>
+      </c>
+      <c r="S112" s="8"/>
+    </row>
+    <row r="113" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>360</v>
+      </c>
+      <c r="B113" s="3">
+        <v>1918</v>
+      </c>
+      <c r="C113" t="s">
+        <v>160</v>
+      </c>
+      <c r="D113" t="s">
+        <v>361</v>
+      </c>
+      <c r="E113" t="s">
+        <v>366</v>
+      </c>
+      <c r="F113" t="s">
+        <v>363</v>
+      </c>
+      <c r="G113" t="s">
+        <v>362</v>
+      </c>
+      <c r="H113" s="7"/>
+      <c r="I113" t="s">
+        <v>367</v>
+      </c>
+      <c r="J113" t="s">
+        <v>368</v>
+      </c>
+      <c r="K113" t="s">
+        <v>36</v>
+      </c>
+      <c r="L113" t="s">
+        <v>22</v>
+      </c>
+      <c r="M113" t="s">
+        <v>370</v>
+      </c>
+      <c r="N113" t="s">
+        <v>27</v>
+      </c>
+      <c r="O113" t="s">
+        <v>27</v>
+      </c>
+      <c r="P113" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>24</v>
+      </c>
+      <c r="R113" t="s">
+        <v>27</v>
+      </c>
+      <c r="S113" s="8"/>
+    </row>
+    <row r="114" spans="1:19" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>372</v>
+      </c>
+      <c r="B114" s="3">
+        <v>1976</v>
+      </c>
+      <c r="C114" t="s">
+        <v>160</v>
+      </c>
+      <c r="D114" t="s">
+        <v>373</v>
+      </c>
+      <c r="E114" t="s">
+        <v>375</v>
+      </c>
+      <c r="F114" t="s">
+        <v>379</v>
+      </c>
+      <c r="G114" t="s">
+        <v>374</v>
+      </c>
+      <c r="H114" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="I114" t="s">
+        <v>381</v>
+      </c>
+      <c r="J114" t="s">
+        <v>382</v>
+      </c>
+      <c r="K114" t="s">
+        <v>36</v>
+      </c>
+      <c r="L114" t="s">
+        <v>22</v>
+      </c>
+      <c r="M114" t="s">
+        <v>27</v>
+      </c>
+      <c r="N114" t="s">
+        <v>384</v>
+      </c>
+      <c r="O114" t="s">
+        <v>27</v>
+      </c>
+      <c r="P114" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>27</v>
+      </c>
+      <c r="R114" t="s">
+        <v>383</v>
+      </c>
+      <c r="S114" s="8" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>372</v>
+      </c>
+      <c r="B115" s="3">
+        <v>1976</v>
+      </c>
+      <c r="C115" t="s">
+        <v>160</v>
+      </c>
+      <c r="D115" t="s">
+        <v>373</v>
+      </c>
+      <c r="E115" t="s">
+        <v>376</v>
+      </c>
+      <c r="F115" t="s">
+        <v>379</v>
+      </c>
+      <c r="G115" t="s">
+        <v>374</v>
+      </c>
+      <c r="H115" s="7"/>
+      <c r="I115" t="s">
+        <v>381</v>
+      </c>
+      <c r="J115" t="s">
+        <v>382</v>
+      </c>
+      <c r="K115" t="s">
+        <v>36</v>
+      </c>
+      <c r="L115" t="s">
+        <v>22</v>
+      </c>
+      <c r="M115" t="s">
+        <v>27</v>
+      </c>
+      <c r="N115" t="s">
+        <v>384</v>
+      </c>
+      <c r="O115" t="s">
+        <v>27</v>
+      </c>
+      <c r="P115" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>27</v>
+      </c>
+      <c r="R115" t="s">
+        <v>383</v>
+      </c>
+      <c r="S115" s="8"/>
+    </row>
+    <row r="116" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>372</v>
+      </c>
+      <c r="B116" s="3">
+        <v>1976</v>
+      </c>
+      <c r="C116" t="s">
+        <v>160</v>
+      </c>
+      <c r="D116" t="s">
+        <v>373</v>
+      </c>
+      <c r="E116" t="s">
+        <v>377</v>
+      </c>
+      <c r="F116" t="s">
+        <v>379</v>
+      </c>
+      <c r="G116" t="s">
+        <v>374</v>
+      </c>
+      <c r="H116" s="7"/>
+      <c r="I116" t="s">
+        <v>381</v>
+      </c>
+      <c r="J116" t="s">
+        <v>382</v>
+      </c>
+      <c r="K116" t="s">
+        <v>36</v>
+      </c>
+      <c r="L116" t="s">
+        <v>22</v>
+      </c>
+      <c r="M116" t="s">
+        <v>27</v>
+      </c>
+      <c r="N116" t="s">
+        <v>384</v>
+      </c>
+      <c r="O116" t="s">
+        <v>27</v>
+      </c>
+      <c r="P116" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>27</v>
+      </c>
+      <c r="R116" t="s">
+        <v>383</v>
+      </c>
+      <c r="S116" s="8"/>
+    </row>
+    <row r="117" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>372</v>
+      </c>
+      <c r="B117" s="3">
+        <v>1976</v>
+      </c>
+      <c r="C117" t="s">
+        <v>160</v>
+      </c>
+      <c r="D117" t="s">
+        <v>373</v>
+      </c>
+      <c r="E117" t="s">
+        <v>378</v>
+      </c>
+      <c r="F117" t="s">
+        <v>379</v>
+      </c>
+      <c r="G117" t="s">
+        <v>374</v>
+      </c>
+      <c r="H117" s="7"/>
+      <c r="I117" t="s">
+        <v>381</v>
+      </c>
+      <c r="J117" t="s">
+        <v>382</v>
+      </c>
+      <c r="K117" t="s">
+        <v>36</v>
+      </c>
+      <c r="L117" t="s">
+        <v>22</v>
+      </c>
+      <c r="M117" t="s">
+        <v>27</v>
+      </c>
+      <c r="N117" t="s">
+        <v>384</v>
+      </c>
+      <c r="O117" t="s">
+        <v>27</v>
+      </c>
+      <c r="P117" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>27</v>
+      </c>
+      <c r="R117" t="s">
+        <v>383</v>
+      </c>
+      <c r="S117" s="8"/>
+    </row>
+    <row r="118" spans="1:19" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>386</v>
+      </c>
+      <c r="B118" s="3">
+        <v>2034</v>
+      </c>
+      <c r="C118" t="s">
+        <v>174</v>
+      </c>
+      <c r="D118" t="s">
+        <v>388</v>
+      </c>
+      <c r="E118" t="s">
+        <v>391</v>
+      </c>
+      <c r="F118" t="s">
+        <v>390</v>
+      </c>
+      <c r="G118" t="s">
+        <v>389</v>
+      </c>
+      <c r="H118" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="I118" t="s">
+        <v>396</v>
+      </c>
+      <c r="J118" t="s">
+        <v>397</v>
+      </c>
+      <c r="K118" t="s">
+        <v>36</v>
+      </c>
+      <c r="L118" t="s">
+        <v>22</v>
+      </c>
+      <c r="M118" t="s">
+        <v>27</v>
+      </c>
+      <c r="N118" t="s">
+        <v>27</v>
+      </c>
+      <c r="O118" t="s">
+        <v>399</v>
+      </c>
+      <c r="P118" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>27</v>
+      </c>
+      <c r="R118" t="s">
+        <v>398</v>
+      </c>
+      <c r="S118" s="8" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>386</v>
+      </c>
+      <c r="B119" s="3">
+        <v>2034</v>
+      </c>
+      <c r="C119" t="s">
+        <v>174</v>
+      </c>
+      <c r="D119" t="s">
+        <v>388</v>
+      </c>
+      <c r="E119" t="s">
+        <v>392</v>
+      </c>
+      <c r="F119" t="s">
+        <v>390</v>
+      </c>
+      <c r="G119" t="s">
+        <v>389</v>
+      </c>
+      <c r="H119" s="7"/>
+      <c r="I119" t="s">
+        <v>396</v>
+      </c>
+      <c r="J119" t="s">
+        <v>397</v>
+      </c>
+      <c r="K119" t="s">
+        <v>36</v>
+      </c>
+      <c r="L119" t="s">
+        <v>22</v>
+      </c>
+      <c r="M119" t="s">
+        <v>27</v>
+      </c>
+      <c r="N119" t="s">
+        <v>27</v>
+      </c>
+      <c r="O119" t="s">
+        <v>399</v>
+      </c>
+      <c r="P119" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>27</v>
+      </c>
+      <c r="R119" t="s">
+        <v>398</v>
+      </c>
+      <c r="S119" s="8"/>
+    </row>
+    <row r="120" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>386</v>
+      </c>
+      <c r="B120" s="3">
+        <v>2034</v>
+      </c>
+      <c r="C120" t="s">
+        <v>174</v>
+      </c>
+      <c r="D120" t="s">
+        <v>388</v>
+      </c>
+      <c r="E120" t="s">
+        <v>393</v>
+      </c>
+      <c r="F120" t="s">
+        <v>390</v>
+      </c>
+      <c r="G120" t="s">
+        <v>389</v>
+      </c>
+      <c r="H120" s="7"/>
+      <c r="I120" t="s">
+        <v>396</v>
+      </c>
+      <c r="J120" t="s">
+        <v>397</v>
+      </c>
+      <c r="K120" t="s">
+        <v>36</v>
+      </c>
+      <c r="L120" t="s">
+        <v>22</v>
+      </c>
+      <c r="M120" t="s">
+        <v>27</v>
+      </c>
+      <c r="N120" t="s">
+        <v>27</v>
+      </c>
+      <c r="O120" t="s">
+        <v>399</v>
+      </c>
+      <c r="P120" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>27</v>
+      </c>
+      <c r="R120" t="s">
+        <v>398</v>
+      </c>
+      <c r="S120" s="8"/>
+    </row>
+    <row r="121" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>386</v>
+      </c>
+      <c r="B121" s="3">
+        <v>2034</v>
+      </c>
+      <c r="C121" t="s">
+        <v>174</v>
+      </c>
+      <c r="D121" t="s">
+        <v>388</v>
+      </c>
+      <c r="E121" t="s">
+        <v>394</v>
+      </c>
+      <c r="F121" t="s">
+        <v>390</v>
+      </c>
+      <c r="G121" t="s">
+        <v>389</v>
+      </c>
+      <c r="H121" s="7"/>
+      <c r="I121" t="s">
+        <v>396</v>
+      </c>
+      <c r="J121" t="s">
+        <v>397</v>
+      </c>
+      <c r="K121" t="s">
+        <v>36</v>
+      </c>
+      <c r="L121" t="s">
+        <v>22</v>
+      </c>
+      <c r="M121" t="s">
+        <v>27</v>
+      </c>
+      <c r="N121" t="s">
+        <v>27</v>
+      </c>
+      <c r="O121" t="s">
+        <v>399</v>
+      </c>
+      <c r="P121" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>27</v>
+      </c>
+      <c r="R121" t="s">
+        <v>398</v>
+      </c>
+      <c r="S121" s="8"/>
+    </row>
+    <row r="122" spans="1:19" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>416</v>
+      </c>
+      <c r="B122" s="3">
+        <v>2090</v>
+      </c>
+      <c r="C122" t="s">
+        <v>417</v>
+      </c>
+      <c r="D122" t="s">
+        <v>418</v>
+      </c>
+      <c r="E122" t="s">
+        <v>391</v>
+      </c>
+      <c r="F122" t="s">
+        <v>420</v>
+      </c>
+      <c r="G122" t="s">
+        <v>419</v>
+      </c>
+      <c r="H122" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="I122" t="s">
+        <v>424</v>
+      </c>
+      <c r="J122" t="s">
+        <v>425</v>
+      </c>
+      <c r="K122" t="s">
+        <v>36</v>
+      </c>
+      <c r="L122" t="s">
+        <v>22</v>
+      </c>
+      <c r="M122" t="s">
+        <v>27</v>
+      </c>
+      <c r="N122" t="s">
+        <v>27</v>
+      </c>
+      <c r="O122" t="s">
+        <v>27</v>
+      </c>
+      <c r="P122" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>27</v>
+      </c>
+      <c r="R122" t="s">
+        <v>27</v>
+      </c>
+      <c r="S122" s="8" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>416</v>
+      </c>
+      <c r="B123" s="3">
+        <v>2090</v>
+      </c>
+      <c r="C123" t="s">
+        <v>417</v>
+      </c>
+      <c r="D123" t="s">
+        <v>418</v>
+      </c>
+      <c r="E123" t="s">
+        <v>421</v>
+      </c>
+      <c r="F123" t="s">
+        <v>420</v>
+      </c>
+      <c r="G123" t="s">
+        <v>419</v>
+      </c>
+      <c r="H123" s="7"/>
+      <c r="I123" t="s">
+        <v>424</v>
+      </c>
+      <c r="J123" t="s">
+        <v>425</v>
+      </c>
+      <c r="K123" t="s">
+        <v>36</v>
+      </c>
+      <c r="L123" t="s">
+        <v>22</v>
+      </c>
+      <c r="M123" t="s">
+        <v>27</v>
+      </c>
+      <c r="N123" t="s">
+        <v>27</v>
+      </c>
+      <c r="O123" t="s">
+        <v>27</v>
+      </c>
+      <c r="P123" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>27</v>
+      </c>
+      <c r="R123" t="s">
+        <v>27</v>
+      </c>
+      <c r="S123" s="8"/>
+    </row>
+    <row r="124" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>416</v>
+      </c>
+      <c r="B124" s="3">
+        <v>2090</v>
+      </c>
+      <c r="C124" t="s">
+        <v>417</v>
+      </c>
+      <c r="D124" t="s">
+        <v>418</v>
+      </c>
+      <c r="E124" t="s">
+        <v>422</v>
+      </c>
+      <c r="F124" t="s">
+        <v>420</v>
+      </c>
+      <c r="G124" t="s">
+        <v>419</v>
+      </c>
+      <c r="H124" s="7"/>
+      <c r="I124" t="s">
+        <v>424</v>
+      </c>
+      <c r="J124" t="s">
+        <v>425</v>
+      </c>
+      <c r="K124" t="s">
+        <v>36</v>
+      </c>
+      <c r="L124" t="s">
+        <v>22</v>
+      </c>
+      <c r="M124" t="s">
+        <v>27</v>
+      </c>
+      <c r="N124" t="s">
+        <v>27</v>
+      </c>
+      <c r="O124" t="s">
+        <v>27</v>
+      </c>
+      <c r="P124" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>27</v>
+      </c>
+      <c r="R124" t="s">
+        <v>27</v>
+      </c>
+      <c r="S124" s="8"/>
+    </row>
+    <row r="125" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>416</v>
+      </c>
+      <c r="B125" s="3">
+        <v>2090</v>
+      </c>
+      <c r="C125" t="s">
+        <v>417</v>
+      </c>
+      <c r="D125" t="s">
+        <v>418</v>
+      </c>
+      <c r="E125" t="s">
+        <v>423</v>
+      </c>
+      <c r="F125" t="s">
+        <v>420</v>
+      </c>
+      <c r="G125" t="s">
+        <v>419</v>
+      </c>
+      <c r="H125" s="7"/>
+      <c r="I125" t="s">
+        <v>424</v>
+      </c>
+      <c r="J125" t="s">
+        <v>425</v>
+      </c>
+      <c r="K125" t="s">
+        <v>36</v>
+      </c>
+      <c r="L125" t="s">
+        <v>22</v>
+      </c>
+      <c r="M125" t="s">
+        <v>27</v>
+      </c>
+      <c r="N125" t="s">
+        <v>27</v>
+      </c>
+      <c r="O125" t="s">
+        <v>27</v>
+      </c>
+      <c r="P125" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>27</v>
+      </c>
+      <c r="R125" t="s">
+        <v>27</v>
+      </c>
+      <c r="S125" s="8"/>
+    </row>
+    <row r="126" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="127" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="128" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="129" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="130" spans="1:19" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>428</v>
+      </c>
+      <c r="B130" s="3">
+        <v>2214</v>
+      </c>
+      <c r="C130" t="s">
+        <v>61</v>
+      </c>
+      <c r="D130" t="s">
+        <v>431</v>
+      </c>
+      <c r="E130" t="s">
+        <v>218</v>
+      </c>
+      <c r="F130" t="s">
+        <v>436</v>
+      </c>
+      <c r="G130" t="s">
+        <v>432</v>
+      </c>
+      <c r="H130" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="I130" t="s">
+        <v>437</v>
+      </c>
+      <c r="J130" t="s">
+        <v>438</v>
+      </c>
+      <c r="K130" t="s">
+        <v>36</v>
+      </c>
+      <c r="L130" t="s">
+        <v>22</v>
+      </c>
+      <c r="M130" t="s">
+        <v>27</v>
+      </c>
+      <c r="N130" t="s">
+        <v>429</v>
+      </c>
+      <c r="O130" t="s">
+        <v>27</v>
+      </c>
+      <c r="P130" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>27</v>
+      </c>
+      <c r="R130" t="s">
+        <v>430</v>
+      </c>
+      <c r="S130" s="8" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="131" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>428</v>
+      </c>
+      <c r="B131" s="3">
+        <v>2214</v>
+      </c>
+      <c r="C131" t="s">
+        <v>61</v>
+      </c>
+      <c r="D131" t="s">
+        <v>431</v>
+      </c>
+      <c r="E131" t="s">
+        <v>433</v>
+      </c>
+      <c r="F131" t="s">
+        <v>436</v>
+      </c>
+      <c r="G131" t="s">
+        <v>432</v>
+      </c>
+      <c r="H131" s="7"/>
+      <c r="I131" t="s">
+        <v>437</v>
+      </c>
+      <c r="J131" t="s">
+        <v>438</v>
+      </c>
+      <c r="K131" t="s">
+        <v>36</v>
+      </c>
+      <c r="L131" t="s">
+        <v>22</v>
+      </c>
+      <c r="M131" t="s">
+        <v>27</v>
+      </c>
+      <c r="N131" t="s">
+        <v>429</v>
+      </c>
+      <c r="O131" t="s">
+        <v>27</v>
+      </c>
+      <c r="P131" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>27</v>
+      </c>
+      <c r="R131" t="s">
+        <v>430</v>
+      </c>
+      <c r="S131" s="8"/>
+    </row>
+    <row r="132" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>428</v>
+      </c>
+      <c r="B132" s="3">
+        <v>2214</v>
+      </c>
+      <c r="C132" t="s">
+        <v>61</v>
+      </c>
+      <c r="D132" t="s">
+        <v>431</v>
+      </c>
+      <c r="E132" t="s">
+        <v>434</v>
+      </c>
+      <c r="F132" t="s">
+        <v>436</v>
+      </c>
+      <c r="G132" t="s">
+        <v>432</v>
+      </c>
+      <c r="H132" s="7"/>
+      <c r="I132" t="s">
+        <v>437</v>
+      </c>
+      <c r="J132" t="s">
+        <v>438</v>
+      </c>
+      <c r="K132" t="s">
+        <v>36</v>
+      </c>
+      <c r="L132" t="s">
+        <v>22</v>
+      </c>
+      <c r="M132" t="s">
+        <v>27</v>
+      </c>
+      <c r="N132" t="s">
+        <v>429</v>
+      </c>
+      <c r="O132" t="s">
+        <v>27</v>
+      </c>
+      <c r="P132" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>27</v>
+      </c>
+      <c r="R132" t="s">
+        <v>430</v>
+      </c>
+      <c r="S132" s="8"/>
+    </row>
+    <row r="133" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>428</v>
+      </c>
+      <c r="B133" s="3">
+        <v>2214</v>
+      </c>
+      <c r="C133" t="s">
+        <v>61</v>
+      </c>
+      <c r="D133" t="s">
+        <v>431</v>
+      </c>
+      <c r="E133" t="s">
+        <v>435</v>
+      </c>
+      <c r="F133" t="s">
+        <v>436</v>
+      </c>
+      <c r="G133" t="s">
+        <v>432</v>
+      </c>
+      <c r="H133" s="7"/>
+      <c r="I133" t="s">
+        <v>437</v>
+      </c>
+      <c r="J133" t="s">
+        <v>438</v>
+      </c>
+      <c r="K133" t="s">
+        <v>36</v>
+      </c>
+      <c r="L133" t="s">
+        <v>22</v>
+      </c>
+      <c r="M133" t="s">
+        <v>27</v>
+      </c>
+      <c r="N133" t="s">
+        <v>429</v>
+      </c>
+      <c r="O133" t="s">
+        <v>27</v>
+      </c>
+      <c r="P133" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>27</v>
+      </c>
+      <c r="R133" t="s">
+        <v>430</v>
+      </c>
+      <c r="S133" s="8"/>
+    </row>
+    <row r="134" spans="1:19" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>440</v>
+      </c>
+      <c r="B134" s="3">
+        <v>2272</v>
+      </c>
+      <c r="C134" t="s">
+        <v>417</v>
+      </c>
+      <c r="D134" t="s">
+        <v>441</v>
+      </c>
+      <c r="E134" t="s">
+        <v>218</v>
+      </c>
+      <c r="F134" t="s">
+        <v>446</v>
+      </c>
+      <c r="G134" t="s">
+        <v>442</v>
+      </c>
+      <c r="H134" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="I134" t="s">
+        <v>447</v>
+      </c>
+      <c r="J134" t="s">
+        <v>448</v>
+      </c>
+      <c r="K134" t="s">
+        <v>36</v>
+      </c>
+      <c r="L134" t="s">
+        <v>22</v>
+      </c>
+      <c r="M134" t="s">
+        <v>24</v>
+      </c>
+      <c r="N134" t="s">
+        <v>27</v>
+      </c>
+      <c r="O134" t="s">
+        <v>449</v>
+      </c>
+      <c r="P134" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>24</v>
+      </c>
+      <c r="R134" t="s">
+        <v>27</v>
+      </c>
+      <c r="S134" s="8" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="135" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>440</v>
+      </c>
+      <c r="B135" s="3">
+        <v>2272</v>
+      </c>
+      <c r="C135" t="s">
+        <v>417</v>
+      </c>
+      <c r="D135" t="s">
+        <v>441</v>
+      </c>
+      <c r="E135" t="s">
+        <v>443</v>
+      </c>
+      <c r="F135" t="s">
+        <v>446</v>
+      </c>
+      <c r="G135" t="s">
+        <v>442</v>
+      </c>
+      <c r="H135" s="7"/>
+      <c r="I135" t="s">
+        <v>447</v>
+      </c>
+      <c r="J135" t="s">
+        <v>448</v>
+      </c>
+      <c r="K135" t="s">
+        <v>36</v>
+      </c>
+      <c r="L135" t="s">
+        <v>22</v>
+      </c>
+      <c r="M135" t="s">
+        <v>24</v>
+      </c>
+      <c r="N135" t="s">
+        <v>27</v>
+      </c>
+      <c r="O135" t="s">
+        <v>449</v>
+      </c>
+      <c r="P135" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>24</v>
+      </c>
+      <c r="R135" t="s">
+        <v>27</v>
+      </c>
+      <c r="S135" s="8"/>
+    </row>
+    <row r="136" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>440</v>
+      </c>
+      <c r="B136" s="3">
+        <v>2272</v>
+      </c>
+      <c r="C136" t="s">
+        <v>417</v>
+      </c>
+      <c r="D136" t="s">
+        <v>441</v>
+      </c>
+      <c r="E136" t="s">
+        <v>444</v>
+      </c>
+      <c r="F136" t="s">
+        <v>446</v>
+      </c>
+      <c r="G136" t="s">
+        <v>442</v>
+      </c>
+      <c r="H136" s="7"/>
+      <c r="I136" t="s">
+        <v>447</v>
+      </c>
+      <c r="J136" t="s">
+        <v>448</v>
+      </c>
+      <c r="K136" t="s">
+        <v>36</v>
+      </c>
+      <c r="L136" t="s">
+        <v>22</v>
+      </c>
+      <c r="M136" t="s">
+        <v>24</v>
+      </c>
+      <c r="N136" t="s">
+        <v>27</v>
+      </c>
+      <c r="O136" t="s">
+        <v>449</v>
+      </c>
+      <c r="P136" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>24</v>
+      </c>
+      <c r="R136" t="s">
+        <v>27</v>
+      </c>
+      <c r="S136" s="8"/>
+    </row>
+    <row r="137" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>440</v>
+      </c>
+      <c r="B137" s="3">
+        <v>2272</v>
+      </c>
+      <c r="C137" t="s">
+        <v>417</v>
+      </c>
+      <c r="D137" t="s">
+        <v>441</v>
+      </c>
+      <c r="E137" t="s">
+        <v>445</v>
+      </c>
+      <c r="F137" t="s">
+        <v>446</v>
+      </c>
+      <c r="G137" t="s">
+        <v>442</v>
+      </c>
+      <c r="H137" s="7"/>
+      <c r="I137" t="s">
+        <v>447</v>
+      </c>
+      <c r="J137" t="s">
+        <v>448</v>
+      </c>
+      <c r="K137" t="s">
+        <v>36</v>
+      </c>
+      <c r="L137" t="s">
+        <v>22</v>
+      </c>
+      <c r="M137" t="s">
+        <v>24</v>
+      </c>
+      <c r="N137" t="s">
+        <v>27</v>
+      </c>
+      <c r="O137" t="s">
+        <v>449</v>
+      </c>
+      <c r="P137" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>24</v>
+      </c>
+      <c r="R137" t="s">
+        <v>27</v>
+      </c>
+      <c r="S137" s="8"/>
+    </row>
+    <row r="138" spans="1:19" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>451</v>
+      </c>
+      <c r="B138" s="3">
+        <v>2330</v>
+      </c>
+      <c r="C138" t="s">
+        <v>61</v>
+      </c>
+      <c r="D138" t="s">
+        <v>452</v>
+      </c>
+      <c r="E138" t="s">
+        <v>218</v>
+      </c>
+      <c r="F138" t="s">
+        <v>454</v>
+      </c>
+      <c r="G138" t="s">
+        <v>453</v>
+      </c>
+      <c r="H138" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="I138" t="s">
+        <v>458</v>
+      </c>
+      <c r="J138" t="s">
+        <v>459</v>
+      </c>
+      <c r="K138" t="s">
+        <v>36</v>
+      </c>
+      <c r="L138" t="s">
+        <v>22</v>
+      </c>
+      <c r="M138" t="s">
+        <v>27</v>
+      </c>
+      <c r="N138" t="s">
+        <v>460</v>
+      </c>
+      <c r="O138" t="s">
+        <v>27</v>
+      </c>
+      <c r="P138" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>27</v>
+      </c>
+      <c r="R138" t="s">
+        <v>461</v>
+      </c>
+      <c r="S138" s="8" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="139" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>451</v>
+      </c>
+      <c r="B139" s="3">
+        <v>2330</v>
+      </c>
+      <c r="C139" t="s">
+        <v>61</v>
+      </c>
+      <c r="D139" t="s">
+        <v>452</v>
+      </c>
+      <c r="E139" t="s">
+        <v>455</v>
+      </c>
+      <c r="F139" t="s">
+        <v>454</v>
+      </c>
+      <c r="G139" t="s">
+        <v>453</v>
+      </c>
+      <c r="H139" s="7"/>
+      <c r="I139" t="s">
+        <v>458</v>
+      </c>
+      <c r="J139" t="s">
+        <v>459</v>
+      </c>
+      <c r="K139" t="s">
+        <v>36</v>
+      </c>
+      <c r="L139" t="s">
+        <v>22</v>
+      </c>
+      <c r="M139" t="s">
+        <v>27</v>
+      </c>
+      <c r="N139" t="s">
+        <v>460</v>
+      </c>
+      <c r="O139" t="s">
+        <v>27</v>
+      </c>
+      <c r="P139" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>27</v>
+      </c>
+      <c r="R139" t="s">
+        <v>461</v>
+      </c>
+      <c r="S139" s="8"/>
+    </row>
+    <row r="140" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>451</v>
+      </c>
+      <c r="B140" s="3">
+        <v>2330</v>
+      </c>
+      <c r="C140" t="s">
+        <v>61</v>
+      </c>
+      <c r="D140" t="s">
+        <v>452</v>
+      </c>
+      <c r="E140" t="s">
+        <v>456</v>
+      </c>
+      <c r="F140" t="s">
+        <v>454</v>
+      </c>
+      <c r="G140" t="s">
+        <v>453</v>
+      </c>
+      <c r="H140" s="7"/>
+      <c r="I140" t="s">
+        <v>458</v>
+      </c>
+      <c r="J140" t="s">
+        <v>459</v>
+      </c>
+      <c r="K140" t="s">
+        <v>36</v>
+      </c>
+      <c r="L140" t="s">
+        <v>22</v>
+      </c>
+      <c r="M140" t="s">
+        <v>27</v>
+      </c>
+      <c r="N140" t="s">
+        <v>460</v>
+      </c>
+      <c r="O140" t="s">
+        <v>27</v>
+      </c>
+      <c r="P140" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>27</v>
+      </c>
+      <c r="R140" t="s">
+        <v>461</v>
+      </c>
+      <c r="S140" s="8"/>
+    </row>
+    <row r="141" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>451</v>
+      </c>
+      <c r="B141" s="3">
+        <v>2330</v>
+      </c>
+      <c r="C141" t="s">
+        <v>61</v>
+      </c>
+      <c r="D141" t="s">
+        <v>452</v>
+      </c>
+      <c r="E141" t="s">
+        <v>457</v>
+      </c>
+      <c r="F141" t="s">
+        <v>454</v>
+      </c>
+      <c r="G141" t="s">
+        <v>453</v>
+      </c>
+      <c r="H141" s="7"/>
+      <c r="I141" t="s">
+        <v>458</v>
+      </c>
+      <c r="J141" t="s">
+        <v>459</v>
+      </c>
+      <c r="K141" t="s">
+        <v>36</v>
+      </c>
+      <c r="L141" t="s">
+        <v>22</v>
+      </c>
+      <c r="M141" t="s">
+        <v>27</v>
+      </c>
+      <c r="N141" t="s">
+        <v>460</v>
+      </c>
+      <c r="O141" t="s">
+        <v>27</v>
+      </c>
+      <c r="P141" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>27</v>
+      </c>
+      <c r="R141" t="s">
+        <v>461</v>
+      </c>
+      <c r="S141" s="8"/>
+    </row>
+    <row r="142" spans="1:19" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>463</v>
+      </c>
+      <c r="B142" s="3">
+        <v>2388</v>
+      </c>
+      <c r="C142" t="s">
+        <v>464</v>
+      </c>
+      <c r="D142" t="s">
+        <v>465</v>
+      </c>
+      <c r="E142" t="s">
+        <v>468</v>
+      </c>
+      <c r="F142" t="s">
+        <v>467</v>
+      </c>
+      <c r="G142" t="s">
+        <v>466</v>
+      </c>
+      <c r="H142" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="I142" t="s">
+        <v>472</v>
+      </c>
+      <c r="J142" t="s">
+        <v>459</v>
+      </c>
+      <c r="K142" t="s">
+        <v>36</v>
+      </c>
+      <c r="L142" t="s">
+        <v>22</v>
+      </c>
+      <c r="M142" t="s">
+        <v>27</v>
+      </c>
+      <c r="N142" t="s">
+        <v>477</v>
+      </c>
+      <c r="O142" t="s">
+        <v>475</v>
+      </c>
+      <c r="P142" t="s">
+        <v>476</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>474</v>
+      </c>
+      <c r="R142" t="s">
+        <v>27</v>
+      </c>
+      <c r="S142" s="8" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="143" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>463</v>
+      </c>
+      <c r="B143" s="3">
+        <v>2388</v>
+      </c>
+      <c r="C143" t="s">
+        <v>464</v>
+      </c>
+      <c r="D143" t="s">
+        <v>465</v>
+      </c>
+      <c r="E143" t="s">
+        <v>469</v>
+      </c>
+      <c r="F143" t="s">
+        <v>467</v>
+      </c>
+      <c r="G143" t="s">
+        <v>466</v>
+      </c>
+      <c r="H143" s="7"/>
+      <c r="I143" t="s">
+        <v>472</v>
+      </c>
+      <c r="J143" t="s">
+        <v>459</v>
+      </c>
+      <c r="K143" t="s">
+        <v>36</v>
+      </c>
+      <c r="L143" t="s">
+        <v>22</v>
+      </c>
+      <c r="M143" t="s">
+        <v>27</v>
+      </c>
+      <c r="N143" t="s">
+        <v>477</v>
+      </c>
+      <c r="O143" t="s">
+        <v>475</v>
+      </c>
+      <c r="P143" t="s">
+        <v>476</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>474</v>
+      </c>
+      <c r="R143" t="s">
+        <v>27</v>
+      </c>
+      <c r="S143" s="8"/>
+    </row>
+    <row r="144" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>463</v>
+      </c>
+      <c r="B144" s="3">
+        <v>2388</v>
+      </c>
+      <c r="C144" t="s">
+        <v>464</v>
+      </c>
+      <c r="D144" t="s">
+        <v>465</v>
+      </c>
+      <c r="E144" t="s">
+        <v>470</v>
+      </c>
+      <c r="F144" t="s">
+        <v>467</v>
+      </c>
+      <c r="G144" t="s">
+        <v>466</v>
+      </c>
+      <c r="H144" s="7"/>
+      <c r="I144" t="s">
+        <v>472</v>
+      </c>
+      <c r="J144" t="s">
+        <v>459</v>
+      </c>
+      <c r="K144" t="s">
+        <v>36</v>
+      </c>
+      <c r="L144" t="s">
+        <v>22</v>
+      </c>
+      <c r="M144" t="s">
+        <v>27</v>
+      </c>
+      <c r="N144" t="s">
+        <v>477</v>
+      </c>
+      <c r="O144" t="s">
+        <v>475</v>
+      </c>
+      <c r="P144" t="s">
+        <v>476</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>474</v>
+      </c>
+      <c r="R144" t="s">
+        <v>27</v>
+      </c>
+      <c r="S144" s="8"/>
+    </row>
+    <row r="145" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>463</v>
+      </c>
+      <c r="B145" s="3">
+        <v>2388</v>
+      </c>
+      <c r="C145" t="s">
+        <v>464</v>
+      </c>
+      <c r="D145" t="s">
+        <v>465</v>
+      </c>
+      <c r="E145" t="s">
+        <v>471</v>
+      </c>
+      <c r="F145" t="s">
+        <v>467</v>
+      </c>
+      <c r="G145" t="s">
+        <v>466</v>
+      </c>
+      <c r="H145" s="7"/>
+      <c r="I145" t="s">
+        <v>472</v>
+      </c>
+      <c r="J145" t="s">
+        <v>459</v>
+      </c>
+      <c r="K145" t="s">
+        <v>36</v>
+      </c>
+      <c r="L145" t="s">
+        <v>22</v>
+      </c>
+      <c r="M145" t="s">
+        <v>27</v>
+      </c>
+      <c r="N145" t="s">
+        <v>477</v>
+      </c>
+      <c r="O145" t="s">
+        <v>475</v>
+      </c>
+      <c r="P145" t="s">
+        <v>476</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>474</v>
+      </c>
+      <c r="R145" t="s">
+        <v>27</v>
+      </c>
+      <c r="S145" s="8"/>
+    </row>
+    <row r="146" spans="1:19" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>479</v>
+      </c>
+      <c r="B146" s="3">
+        <v>2446</v>
+      </c>
+      <c r="C146" t="s">
+        <v>464</v>
+      </c>
+      <c r="D146" t="s">
+        <v>480</v>
+      </c>
+      <c r="E146" t="s">
+        <v>482</v>
+      </c>
+      <c r="F146" t="s">
+        <v>486</v>
+      </c>
+      <c r="G146" t="s">
+        <v>481</v>
+      </c>
+      <c r="H146" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="I146" t="s">
+        <v>487</v>
+      </c>
+      <c r="J146" t="s">
+        <v>488</v>
+      </c>
+      <c r="K146" t="s">
+        <v>36</v>
+      </c>
+      <c r="L146" t="s">
+        <v>22</v>
+      </c>
+      <c r="M146" t="s">
+        <v>27</v>
+      </c>
+      <c r="N146" t="s">
+        <v>27</v>
+      </c>
+      <c r="O146" t="s">
+        <v>24</v>
+      </c>
+      <c r="P146" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>24</v>
+      </c>
+      <c r="R146" t="s">
+        <v>27</v>
+      </c>
+      <c r="S146" s="8" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="147" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>479</v>
+      </c>
+      <c r="B147" s="3">
+        <v>2446</v>
+      </c>
+      <c r="C147" t="s">
+        <v>464</v>
+      </c>
+      <c r="D147" t="s">
+        <v>480</v>
+      </c>
+      <c r="E147" t="s">
+        <v>483</v>
+      </c>
+      <c r="F147" t="s">
+        <v>486</v>
+      </c>
+      <c r="G147" t="s">
+        <v>481</v>
+      </c>
+      <c r="H147" s="7"/>
+      <c r="I147" t="s">
+        <v>487</v>
+      </c>
+      <c r="J147" t="s">
+        <v>488</v>
+      </c>
+      <c r="K147" t="s">
+        <v>36</v>
+      </c>
+      <c r="L147" t="s">
+        <v>22</v>
+      </c>
+      <c r="M147" t="s">
+        <v>27</v>
+      </c>
+      <c r="N147" t="s">
+        <v>27</v>
+      </c>
+      <c r="O147" t="s">
+        <v>24</v>
+      </c>
+      <c r="P147" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>24</v>
+      </c>
+      <c r="R147" t="s">
+        <v>27</v>
+      </c>
+      <c r="S147" s="8"/>
+    </row>
+    <row r="148" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>479</v>
+      </c>
+      <c r="B148" s="3">
+        <v>2446</v>
+      </c>
+      <c r="C148" t="s">
+        <v>464</v>
+      </c>
+      <c r="D148" t="s">
+        <v>480</v>
+      </c>
+      <c r="E148" t="s">
+        <v>484</v>
+      </c>
+      <c r="F148" t="s">
+        <v>486</v>
+      </c>
+      <c r="G148" t="s">
+        <v>481</v>
+      </c>
+      <c r="H148" s="7"/>
+      <c r="I148" t="s">
+        <v>487</v>
+      </c>
+      <c r="J148" t="s">
+        <v>488</v>
+      </c>
+      <c r="K148" t="s">
+        <v>36</v>
+      </c>
+      <c r="L148" t="s">
+        <v>22</v>
+      </c>
+      <c r="M148" t="s">
+        <v>27</v>
+      </c>
+      <c r="N148" t="s">
+        <v>27</v>
+      </c>
+      <c r="O148" t="s">
+        <v>24</v>
+      </c>
+      <c r="P148" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>24</v>
+      </c>
+      <c r="R148" t="s">
+        <v>27</v>
+      </c>
+      <c r="S148" s="8"/>
+    </row>
+    <row r="149" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>479</v>
+      </c>
+      <c r="B149" s="3">
+        <v>2446</v>
+      </c>
+      <c r="C149" t="s">
+        <v>464</v>
+      </c>
+      <c r="D149" t="s">
+        <v>480</v>
+      </c>
+      <c r="E149" t="s">
+        <v>485</v>
+      </c>
+      <c r="F149" t="s">
+        <v>486</v>
+      </c>
+      <c r="G149" t="s">
+        <v>481</v>
+      </c>
+      <c r="H149" s="7"/>
+      <c r="I149" t="s">
+        <v>487</v>
+      </c>
+      <c r="J149" t="s">
+        <v>488</v>
+      </c>
+      <c r="K149" t="s">
+        <v>36</v>
+      </c>
+      <c r="L149" t="s">
+        <v>22</v>
+      </c>
+      <c r="M149" t="s">
+        <v>27</v>
+      </c>
+      <c r="N149" t="s">
+        <v>27</v>
+      </c>
+      <c r="O149" t="s">
+        <v>24</v>
+      </c>
+      <c r="P149" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>24</v>
+      </c>
+      <c r="R149" t="s">
+        <v>27</v>
+      </c>
+      <c r="S149" s="8"/>
+    </row>
+    <row r="150" spans="1:19" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>490</v>
+      </c>
+      <c r="B150" s="3">
+        <v>2504</v>
+      </c>
+      <c r="C150" t="s">
+        <v>417</v>
+      </c>
+      <c r="D150" t="s">
+        <v>491</v>
+      </c>
+      <c r="E150" t="s">
+        <v>218</v>
+      </c>
+      <c r="F150" t="s">
+        <v>493</v>
+      </c>
+      <c r="G150" t="s">
+        <v>492</v>
+      </c>
+      <c r="H150" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="I150" t="s">
+        <v>497</v>
+      </c>
+      <c r="J150" t="s">
+        <v>498</v>
+      </c>
+      <c r="K150" t="s">
+        <v>36</v>
+      </c>
+      <c r="L150" t="s">
+        <v>22</v>
+      </c>
+      <c r="M150" t="s">
+        <v>24</v>
+      </c>
+      <c r="N150" t="s">
+        <v>27</v>
+      </c>
+      <c r="O150" t="s">
+        <v>499</v>
+      </c>
+      <c r="P150" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q150" t="s">
+        <v>24</v>
+      </c>
+      <c r="R150" t="s">
+        <v>27</v>
+      </c>
+      <c r="S150" s="8" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="151" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>490</v>
+      </c>
+      <c r="B151" s="3">
+        <v>2504</v>
+      </c>
+      <c r="C151" t="s">
+        <v>417</v>
+      </c>
+      <c r="D151" t="s">
+        <v>491</v>
+      </c>
+      <c r="E151" t="s">
+        <v>494</v>
+      </c>
+      <c r="F151" t="s">
+        <v>493</v>
+      </c>
+      <c r="G151" t="s">
+        <v>492</v>
+      </c>
+      <c r="H151" s="7"/>
+      <c r="I151" t="s">
+        <v>497</v>
+      </c>
+      <c r="J151" t="s">
+        <v>498</v>
+      </c>
+      <c r="K151" t="s">
+        <v>36</v>
+      </c>
+      <c r="L151" t="s">
+        <v>22</v>
+      </c>
+      <c r="M151" t="s">
+        <v>24</v>
+      </c>
+      <c r="N151" t="s">
+        <v>27</v>
+      </c>
+      <c r="O151" t="s">
+        <v>499</v>
+      </c>
+      <c r="P151" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q151" t="s">
+        <v>24</v>
+      </c>
+      <c r="R151" t="s">
+        <v>27</v>
+      </c>
+      <c r="S151" s="8"/>
+    </row>
+    <row r="152" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>490</v>
+      </c>
+      <c r="B152" s="3">
+        <v>2504</v>
+      </c>
+      <c r="C152" t="s">
+        <v>417</v>
+      </c>
+      <c r="D152" t="s">
+        <v>491</v>
+      </c>
+      <c r="E152" t="s">
+        <v>495</v>
+      </c>
+      <c r="F152" t="s">
+        <v>493</v>
+      </c>
+      <c r="G152" t="s">
+        <v>492</v>
+      </c>
+      <c r="H152" s="7"/>
+      <c r="I152" t="s">
+        <v>497</v>
+      </c>
+      <c r="J152" t="s">
+        <v>498</v>
+      </c>
+      <c r="K152" t="s">
+        <v>36</v>
+      </c>
+      <c r="L152" t="s">
+        <v>22</v>
+      </c>
+      <c r="M152" t="s">
+        <v>24</v>
+      </c>
+      <c r="N152" t="s">
+        <v>27</v>
+      </c>
+      <c r="O152" t="s">
+        <v>499</v>
+      </c>
+      <c r="P152" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q152" t="s">
+        <v>24</v>
+      </c>
+      <c r="R152" t="s">
+        <v>27</v>
+      </c>
+      <c r="S152" s="8"/>
+    </row>
+    <row r="153" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>490</v>
+      </c>
+      <c r="B153" s="3">
+        <v>2504</v>
+      </c>
+      <c r="C153" t="s">
+        <v>417</v>
+      </c>
+      <c r="D153" t="s">
+        <v>491</v>
+      </c>
+      <c r="E153" t="s">
+        <v>496</v>
+      </c>
+      <c r="F153" t="s">
+        <v>493</v>
+      </c>
+      <c r="G153" t="s">
+        <v>492</v>
+      </c>
+      <c r="H153" s="7"/>
+      <c r="I153" t="s">
+        <v>497</v>
+      </c>
+      <c r="J153" t="s">
+        <v>498</v>
+      </c>
+      <c r="K153" t="s">
+        <v>36</v>
+      </c>
+      <c r="L153" t="s">
+        <v>22</v>
+      </c>
+      <c r="M153" t="s">
+        <v>24</v>
+      </c>
+      <c r="N153" t="s">
+        <v>27</v>
+      </c>
+      <c r="O153" t="s">
+        <v>499</v>
+      </c>
+      <c r="P153" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>24</v>
+      </c>
+      <c r="R153" t="s">
+        <v>27</v>
+      </c>
+      <c r="S153" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="75">
+    <mergeCell ref="H142:H145"/>
+    <mergeCell ref="S142:S145"/>
+    <mergeCell ref="H146:H149"/>
+    <mergeCell ref="S146:S149"/>
+    <mergeCell ref="H150:H153"/>
+    <mergeCell ref="S150:S153"/>
+    <mergeCell ref="H130:H133"/>
+    <mergeCell ref="S130:S133"/>
+    <mergeCell ref="H134:H137"/>
+    <mergeCell ref="S134:S137"/>
+    <mergeCell ref="H138:H141"/>
+    <mergeCell ref="S138:S141"/>
+    <mergeCell ref="H118:H121"/>
+    <mergeCell ref="S118:S121"/>
+    <mergeCell ref="H90:H93"/>
+    <mergeCell ref="S90:S93"/>
+    <mergeCell ref="H122:H125"/>
+    <mergeCell ref="S122:S125"/>
+    <mergeCell ref="H106:H109"/>
+    <mergeCell ref="S106:S109"/>
+    <mergeCell ref="H110:H113"/>
+    <mergeCell ref="S110:S113"/>
+    <mergeCell ref="H114:H117"/>
+    <mergeCell ref="S114:S117"/>
+    <mergeCell ref="H94:H97"/>
+    <mergeCell ref="S94:S97"/>
+    <mergeCell ref="H98:H101"/>
+    <mergeCell ref="S98:S101"/>
+    <mergeCell ref="H102:H105"/>
+    <mergeCell ref="S102:S105"/>
+    <mergeCell ref="H2:H5"/>
+    <mergeCell ref="S2:S5"/>
+    <mergeCell ref="H6:H9"/>
+    <mergeCell ref="S6:S9"/>
+    <mergeCell ref="H10:H13"/>
+    <mergeCell ref="S10:S13"/>
+    <mergeCell ref="H14:H17"/>
+    <mergeCell ref="L14:L17"/>
+    <mergeCell ref="S14:S17"/>
+    <mergeCell ref="H18:H21"/>
+    <mergeCell ref="S18:S21"/>
+    <mergeCell ref="H22:H25"/>
+    <mergeCell ref="S22:S25"/>
+    <mergeCell ref="H26:H29"/>
+    <mergeCell ref="S26:S29"/>
+    <mergeCell ref="H30:H33"/>
+    <mergeCell ref="S30:S33"/>
+    <mergeCell ref="H34:H37"/>
+    <mergeCell ref="S34:S37"/>
+    <mergeCell ref="H38:H41"/>
+    <mergeCell ref="S38:S41"/>
+    <mergeCell ref="H42:H45"/>
+    <mergeCell ref="S42:S45"/>
+    <mergeCell ref="H46:H49"/>
+    <mergeCell ref="S46:S49"/>
+    <mergeCell ref="H50:H53"/>
+    <mergeCell ref="S50:S53"/>
+    <mergeCell ref="H54:H57"/>
+    <mergeCell ref="S54:S57"/>
+    <mergeCell ref="H58:H61"/>
+    <mergeCell ref="S58:S61"/>
+    <mergeCell ref="H62:H65"/>
+    <mergeCell ref="S62:S65"/>
+    <mergeCell ref="H66:H69"/>
+    <mergeCell ref="S66:S69"/>
     <mergeCell ref="H82:H85"/>
     <mergeCell ref="S82:S85"/>
     <mergeCell ref="H86:H89"/>
@@ -7161,41 +11768,6 @@
     <mergeCell ref="S74:S77"/>
     <mergeCell ref="H78:H81"/>
     <mergeCell ref="S78:S81"/>
-    <mergeCell ref="H58:H61"/>
-    <mergeCell ref="S58:S61"/>
-    <mergeCell ref="H62:H65"/>
-    <mergeCell ref="S62:S65"/>
-    <mergeCell ref="H66:H69"/>
-    <mergeCell ref="S66:S69"/>
-    <mergeCell ref="H46:H49"/>
-    <mergeCell ref="S46:S49"/>
-    <mergeCell ref="H50:H53"/>
-    <mergeCell ref="S50:S53"/>
-    <mergeCell ref="H54:H57"/>
-    <mergeCell ref="S54:S57"/>
-    <mergeCell ref="H34:H37"/>
-    <mergeCell ref="S34:S37"/>
-    <mergeCell ref="H38:H41"/>
-    <mergeCell ref="S38:S41"/>
-    <mergeCell ref="H42:H45"/>
-    <mergeCell ref="S42:S45"/>
-    <mergeCell ref="H22:H25"/>
-    <mergeCell ref="S22:S25"/>
-    <mergeCell ref="H26:H29"/>
-    <mergeCell ref="S26:S29"/>
-    <mergeCell ref="H30:H33"/>
-    <mergeCell ref="S30:S33"/>
-    <mergeCell ref="H14:H17"/>
-    <mergeCell ref="L14:L17"/>
-    <mergeCell ref="S14:S17"/>
-    <mergeCell ref="H18:H21"/>
-    <mergeCell ref="S18:S21"/>
-    <mergeCell ref="H2:H5"/>
-    <mergeCell ref="S2:S5"/>
-    <mergeCell ref="H6:H9"/>
-    <mergeCell ref="S6:S9"/>
-    <mergeCell ref="H10:H13"/>
-    <mergeCell ref="S10:S13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Resultats_modeles_coleo_2024.xlsx
+++ b/Resultats_modeles_coleo_2024.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2464" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2527" uniqueCount="514">
   <si>
     <t>ab.colsx</t>
   </si>
@@ -2939,6 +2939,121 @@
       </rPr>
       <t>intra.supp &amp; infra</t>
     </r>
+  </si>
+  <si>
+    <t>t_family (Student)</t>
+  </si>
+  <si>
+    <t>CWM_canop ~ strate + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t>CWM_canop ~ 1 + (1 | LOCA / placette) + offset(log(prop.trap.season))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infra : &lt; 2e-16 *** </t>
+  </si>
+  <si>
+    <t>infra inf : 0.535</t>
+  </si>
+  <si>
+    <t>infra supp : 4.40e-06 ***</t>
+  </si>
+  <si>
+    <t>supra : 3.09e-06 ***</t>
+  </si>
+  <si>
+    <t>-57.22125</t>
+  </si>
+  <si>
+    <t>-32.60404</t>
+  </si>
+  <si>
+    <t>5.671e-07 ***</t>
+  </si>
+  <si>
+    <t>Pas de soucis avec les présupposés du modèle, difficulté à trouver la bonne loi</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pour la comparaison des strates 2 à 2 en ce qui concerne le Trait moyen de préférence de canopée (= héliophilie moyenne) de l’assemblage d’espèces, des différences sont observées entre </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supra &amp; intra.inf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supra &amp; infra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra.supp &amp; intra.inf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, et</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> intra.supp &amp; infra</t>
+    </r>
+  </si>
+  <si>
+    <t>Test de plusieurs packages pour pallier au manque de distributions dans glmmTMB qui ne fit pas avec Dharma : lme4 (glmer, glmer.nb), gamlss. Finalement les autres packages ne fonctionnent pas, distribution qui fit trouvée dans glmmTMB : t_family</t>
   </si>
 </sst>
 </file>
@@ -3006,6 +3121,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3014,9 +3132,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3408,7 +3523,7 @@
       <c r="G2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="8" t="s">
         <v>19</v>
       </c>
       <c r="I2">
@@ -3441,7 +3556,7 @@
       <c r="R2" t="s">
         <v>27</v>
       </c>
-      <c r="S2" s="8" t="s">
+      <c r="S2" s="9" t="s">
         <v>83</v>
       </c>
     </row>
@@ -3467,7 +3582,7 @@
       <c r="G3" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="7"/>
+      <c r="H3" s="8"/>
       <c r="I3">
         <v>976.73</v>
       </c>
@@ -3498,7 +3613,7 @@
       <c r="R3" t="s">
         <v>27</v>
       </c>
-      <c r="S3" s="8"/>
+      <c r="S3" s="9"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -3522,7 +3637,7 @@
       <c r="G4" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="7"/>
+      <c r="H4" s="8"/>
       <c r="I4">
         <v>976.73</v>
       </c>
@@ -3553,7 +3668,7 @@
       <c r="R4" t="s">
         <v>27</v>
       </c>
-      <c r="S4" s="8"/>
+      <c r="S4" s="9"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -3577,7 +3692,7 @@
       <c r="G5" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="7"/>
+      <c r="H5" s="8"/>
       <c r="I5">
         <v>976.73</v>
       </c>
@@ -3608,7 +3723,7 @@
       <c r="R5" t="s">
         <v>27</v>
       </c>
-      <c r="S5" s="8"/>
+      <c r="S5" s="9"/>
     </row>
     <row r="6" spans="1:21" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -3632,7 +3747,7 @@
       <c r="G6" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="8" t="s">
         <v>19</v>
       </c>
       <c r="I6">
@@ -3665,7 +3780,7 @@
       <c r="R6" t="s">
         <v>27</v>
       </c>
-      <c r="S6" s="8" t="s">
+      <c r="S6" s="9" t="s">
         <v>84</v>
       </c>
     </row>
@@ -3691,7 +3806,7 @@
       <c r="G7" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="7"/>
+      <c r="H7" s="8"/>
       <c r="I7">
         <v>646.24</v>
       </c>
@@ -3722,7 +3837,7 @@
       <c r="R7" t="s">
         <v>27</v>
       </c>
-      <c r="S7" s="8"/>
+      <c r="S7" s="9"/>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -3746,7 +3861,7 @@
       <c r="G8" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="7"/>
+      <c r="H8" s="8"/>
       <c r="I8">
         <v>646.24</v>
       </c>
@@ -3777,7 +3892,7 @@
       <c r="R8" t="s">
         <v>27</v>
       </c>
-      <c r="S8" s="8"/>
+      <c r="S8" s="9"/>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -3801,7 +3916,7 @@
       <c r="G9" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="7"/>
+      <c r="H9" s="8"/>
       <c r="I9">
         <v>646.24</v>
       </c>
@@ -3832,7 +3947,7 @@
       <c r="R9" t="s">
         <v>27</v>
       </c>
-      <c r="S9" s="8"/>
+      <c r="S9" s="9"/>
     </row>
     <row r="10" spans="1:21" ht="120" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -3856,7 +3971,7 @@
       <c r="G10" t="s">
         <v>54</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="8" t="s">
         <v>55</v>
       </c>
       <c r="I10" t="s">
@@ -3889,7 +4004,7 @@
       <c r="R10" t="s">
         <v>57</v>
       </c>
-      <c r="S10" s="8" t="s">
+      <c r="S10" s="9" t="s">
         <v>85</v>
       </c>
     </row>
@@ -3915,7 +4030,7 @@
       <c r="G11" t="s">
         <v>54</v>
       </c>
-      <c r="H11" s="7"/>
+      <c r="H11" s="8"/>
       <c r="I11" t="s">
         <v>53</v>
       </c>
@@ -3946,7 +4061,7 @@
       <c r="R11" t="s">
         <v>57</v>
       </c>
-      <c r="S11" s="8"/>
+      <c r="S11" s="9"/>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -3970,7 +4085,7 @@
       <c r="G12" t="s">
         <v>54</v>
       </c>
-      <c r="H12" s="7"/>
+      <c r="H12" s="8"/>
       <c r="I12" t="s">
         <v>53</v>
       </c>
@@ -4001,7 +4116,7 @@
       <c r="R12" t="s">
         <v>57</v>
       </c>
-      <c r="S12" s="8"/>
+      <c r="S12" s="9"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -4025,7 +4140,7 @@
       <c r="G13" t="s">
         <v>54</v>
       </c>
-      <c r="H13" s="7"/>
+      <c r="H13" s="8"/>
       <c r="I13" t="s">
         <v>53</v>
       </c>
@@ -4056,7 +4171,7 @@
       <c r="R13" t="s">
         <v>57</v>
       </c>
-      <c r="S13" s="8"/>
+      <c r="S13" s="9"/>
     </row>
     <row r="14" spans="1:21" ht="131.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -4080,7 +4195,7 @@
       <c r="G14" t="s">
         <v>70</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="8" t="s">
         <v>77</v>
       </c>
       <c r="I14" t="s">
@@ -4092,7 +4207,7 @@
       <c r="K14" t="s">
         <v>36</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="L14" s="10" t="s">
         <v>80</v>
       </c>
       <c r="M14" t="s">
@@ -4113,7 +4228,7 @@
       <c r="R14" t="s">
         <v>24</v>
       </c>
-      <c r="S14" s="8" t="s">
+      <c r="S14" s="9" t="s">
         <v>86</v>
       </c>
     </row>
@@ -4139,7 +4254,7 @@
       <c r="G15" t="s">
         <v>70</v>
       </c>
-      <c r="H15" s="7"/>
+      <c r="H15" s="8"/>
       <c r="I15" t="s">
         <v>76</v>
       </c>
@@ -4149,7 +4264,7 @@
       <c r="K15" t="s">
         <v>36</v>
       </c>
-      <c r="L15" s="9"/>
+      <c r="L15" s="10"/>
       <c r="M15" t="s">
         <v>24</v>
       </c>
@@ -4168,7 +4283,7 @@
       <c r="R15" t="s">
         <v>24</v>
       </c>
-      <c r="S15" s="8"/>
+      <c r="S15" s="9"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -4192,7 +4307,7 @@
       <c r="G16" t="s">
         <v>70</v>
       </c>
-      <c r="H16" s="7"/>
+      <c r="H16" s="8"/>
       <c r="I16" t="s">
         <v>76</v>
       </c>
@@ -4202,7 +4317,7 @@
       <c r="K16" t="s">
         <v>36</v>
       </c>
-      <c r="L16" s="9"/>
+      <c r="L16" s="10"/>
       <c r="M16" t="s">
         <v>24</v>
       </c>
@@ -4221,7 +4336,7 @@
       <c r="R16" t="s">
         <v>24</v>
       </c>
-      <c r="S16" s="8"/>
+      <c r="S16" s="9"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
@@ -4245,7 +4360,7 @@
       <c r="G17" t="s">
         <v>70</v>
       </c>
-      <c r="H17" s="7"/>
+      <c r="H17" s="8"/>
       <c r="I17" t="s">
         <v>76</v>
       </c>
@@ -4255,7 +4370,7 @@
       <c r="K17" t="s">
         <v>36</v>
       </c>
-      <c r="L17" s="9"/>
+      <c r="L17" s="10"/>
       <c r="M17" t="s">
         <v>24</v>
       </c>
@@ -4274,7 +4389,7 @@
       <c r="R17" t="s">
         <v>24</v>
       </c>
-      <c r="S17" s="8"/>
+      <c r="S17" s="9"/>
     </row>
     <row r="18" spans="1:19" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -4298,7 +4413,7 @@
       <c r="G18" t="s">
         <v>89</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H18" s="8" t="s">
         <v>77</v>
       </c>
       <c r="I18" t="s">
@@ -4331,7 +4446,7 @@
       <c r="R18" t="s">
         <v>27</v>
       </c>
-      <c r="S18" s="8" t="s">
+      <c r="S18" s="9" t="s">
         <v>109</v>
       </c>
     </row>
@@ -4357,7 +4472,7 @@
       <c r="G19" t="s">
         <v>89</v>
       </c>
-      <c r="H19" s="7"/>
+      <c r="H19" s="8"/>
       <c r="I19" t="s">
         <v>94</v>
       </c>
@@ -4388,7 +4503,7 @@
       <c r="R19" t="s">
         <v>27</v>
       </c>
-      <c r="S19" s="8"/>
+      <c r="S19" s="9"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
@@ -4412,7 +4527,7 @@
       <c r="G20" t="s">
         <v>89</v>
       </c>
-      <c r="H20" s="7"/>
+      <c r="H20" s="8"/>
       <c r="I20" t="s">
         <v>94</v>
       </c>
@@ -4443,7 +4558,7 @@
       <c r="R20" t="s">
         <v>27</v>
       </c>
-      <c r="S20" s="8"/>
+      <c r="S20" s="9"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
@@ -4467,7 +4582,7 @@
       <c r="G21" t="s">
         <v>89</v>
       </c>
-      <c r="H21" s="7"/>
+      <c r="H21" s="8"/>
       <c r="I21" t="s">
         <v>94</v>
       </c>
@@ -4498,7 +4613,7 @@
       <c r="R21" t="s">
         <v>27</v>
       </c>
-      <c r="S21" s="8"/>
+      <c r="S21" s="9"/>
     </row>
     <row r="22" spans="1:19" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
@@ -4522,7 +4637,7 @@
       <c r="G22" t="s">
         <v>100</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="H22" s="8" t="s">
         <v>77</v>
       </c>
       <c r="I22" t="s">
@@ -4555,7 +4670,7 @@
       <c r="R22" t="s">
         <v>27</v>
       </c>
-      <c r="S22" s="8" t="s">
+      <c r="S22" s="9" t="s">
         <v>110</v>
       </c>
     </row>
@@ -4581,7 +4696,7 @@
       <c r="G23" t="s">
         <v>100</v>
       </c>
-      <c r="H23" s="7"/>
+      <c r="H23" s="8"/>
       <c r="I23" t="s">
         <v>105</v>
       </c>
@@ -4612,7 +4727,7 @@
       <c r="R23" t="s">
         <v>27</v>
       </c>
-      <c r="S23" s="8"/>
+      <c r="S23" s="9"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
@@ -4636,7 +4751,7 @@
       <c r="G24" t="s">
         <v>100</v>
       </c>
-      <c r="H24" s="7"/>
+      <c r="H24" s="8"/>
       <c r="I24" t="s">
         <v>105</v>
       </c>
@@ -4667,7 +4782,7 @@
       <c r="R24" t="s">
         <v>27</v>
       </c>
-      <c r="S24" s="8"/>
+      <c r="S24" s="9"/>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
@@ -4691,7 +4806,7 @@
       <c r="G25" t="s">
         <v>100</v>
       </c>
-      <c r="H25" s="7"/>
+      <c r="H25" s="8"/>
       <c r="I25" t="s">
         <v>105</v>
       </c>
@@ -4722,7 +4837,7 @@
       <c r="R25" t="s">
         <v>27</v>
       </c>
-      <c r="S25" s="8"/>
+      <c r="S25" s="9"/>
     </row>
     <row r="26" spans="1:19" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
@@ -4746,7 +4861,7 @@
       <c r="G26" t="s">
         <v>113</v>
       </c>
-      <c r="H26" s="7" t="s">
+      <c r="H26" s="8" t="s">
         <v>77</v>
       </c>
       <c r="I26" t="s">
@@ -4779,7 +4894,7 @@
       <c r="R26" t="s">
         <v>27</v>
       </c>
-      <c r="S26" s="8" t="s">
+      <c r="S26" s="9" t="s">
         <v>122</v>
       </c>
     </row>
@@ -4805,7 +4920,7 @@
       <c r="G27" t="s">
         <v>113</v>
       </c>
-      <c r="H27" s="7"/>
+      <c r="H27" s="8"/>
       <c r="I27" t="s">
         <v>118</v>
       </c>
@@ -4836,7 +4951,7 @@
       <c r="R27" t="s">
         <v>27</v>
       </c>
-      <c r="S27" s="8"/>
+      <c r="S27" s="9"/>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -4860,7 +4975,7 @@
       <c r="G28" t="s">
         <v>113</v>
       </c>
-      <c r="H28" s="7"/>
+      <c r="H28" s="8"/>
       <c r="I28" t="s">
         <v>118</v>
       </c>
@@ -4891,7 +5006,7 @@
       <c r="R28" t="s">
         <v>27</v>
       </c>
-      <c r="S28" s="8"/>
+      <c r="S28" s="9"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -4915,7 +5030,7 @@
       <c r="G29" t="s">
         <v>113</v>
       </c>
-      <c r="H29" s="7"/>
+      <c r="H29" s="8"/>
       <c r="I29" t="s">
         <v>118</v>
       </c>
@@ -4946,7 +5061,7 @@
       <c r="R29" t="s">
         <v>27</v>
       </c>
-      <c r="S29" s="8"/>
+      <c r="S29" s="9"/>
     </row>
     <row r="30" spans="1:19" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
@@ -4970,7 +5085,7 @@
       <c r="G30" t="s">
         <v>125</v>
       </c>
-      <c r="H30" s="7" t="s">
+      <c r="H30" s="8" t="s">
         <v>77</v>
       </c>
       <c r="I30" t="s">
@@ -5003,7 +5118,7 @@
       <c r="R30" t="s">
         <v>134</v>
       </c>
-      <c r="S30" s="8" t="s">
+      <c r="S30" s="9" t="s">
         <v>135</v>
       </c>
     </row>
@@ -5029,7 +5144,7 @@
       <c r="G31" t="s">
         <v>125</v>
       </c>
-      <c r="H31" s="7"/>
+      <c r="H31" s="8"/>
       <c r="I31" t="s">
         <v>130</v>
       </c>
@@ -5060,7 +5175,7 @@
       <c r="R31" t="s">
         <v>134</v>
       </c>
-      <c r="S31" s="8"/>
+      <c r="S31" s="9"/>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
@@ -5084,7 +5199,7 @@
       <c r="G32" t="s">
         <v>125</v>
       </c>
-      <c r="H32" s="7"/>
+      <c r="H32" s="8"/>
       <c r="I32" t="s">
         <v>130</v>
       </c>
@@ -5115,7 +5230,7 @@
       <c r="R32" t="s">
         <v>134</v>
       </c>
-      <c r="S32" s="8"/>
+      <c r="S32" s="9"/>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
@@ -5139,7 +5254,7 @@
       <c r="G33" t="s">
         <v>125</v>
       </c>
-      <c r="H33" s="7"/>
+      <c r="H33" s="8"/>
       <c r="I33" t="s">
         <v>130</v>
       </c>
@@ -5170,7 +5285,7 @@
       <c r="R33" t="s">
         <v>134</v>
       </c>
-      <c r="S33" s="8"/>
+      <c r="S33" s="9"/>
     </row>
     <row r="34" spans="1:19" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
@@ -5194,7 +5309,7 @@
       <c r="G34" t="s">
         <v>138</v>
       </c>
-      <c r="H34" s="7" t="s">
+      <c r="H34" s="8" t="s">
         <v>77</v>
       </c>
       <c r="I34" t="s">
@@ -5227,7 +5342,7 @@
       <c r="R34" t="s">
         <v>146</v>
       </c>
-      <c r="S34" s="8" t="s">
+      <c r="S34" s="9" t="s">
         <v>147</v>
       </c>
     </row>
@@ -5253,7 +5368,7 @@
       <c r="G35" t="s">
         <v>138</v>
       </c>
-      <c r="H35" s="7"/>
+      <c r="H35" s="8"/>
       <c r="I35" t="s">
         <v>143</v>
       </c>
@@ -5284,7 +5399,7 @@
       <c r="R35" t="s">
         <v>146</v>
       </c>
-      <c r="S35" s="8"/>
+      <c r="S35" s="9"/>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
@@ -5308,7 +5423,7 @@
       <c r="G36" t="s">
         <v>138</v>
       </c>
-      <c r="H36" s="7"/>
+      <c r="H36" s="8"/>
       <c r="I36" t="s">
         <v>143</v>
       </c>
@@ -5339,7 +5454,7 @@
       <c r="R36" t="s">
         <v>146</v>
       </c>
-      <c r="S36" s="8"/>
+      <c r="S36" s="9"/>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
@@ -5363,7 +5478,7 @@
       <c r="G37" t="s">
         <v>138</v>
       </c>
-      <c r="H37" s="7"/>
+      <c r="H37" s="8"/>
       <c r="I37" t="s">
         <v>143</v>
       </c>
@@ -5394,7 +5509,7 @@
       <c r="R37" t="s">
         <v>146</v>
       </c>
-      <c r="S37" s="8"/>
+      <c r="S37" s="9"/>
     </row>
     <row r="38" spans="1:19" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
@@ -5418,7 +5533,7 @@
       <c r="G38" t="s">
         <v>153</v>
       </c>
-      <c r="H38" s="7" t="s">
+      <c r="H38" s="8" t="s">
         <v>77</v>
       </c>
       <c r="I38" t="s">
@@ -5451,7 +5566,7 @@
       <c r="R38" t="s">
         <v>27</v>
       </c>
-      <c r="S38" s="8" t="s">
+      <c r="S38" s="9" t="s">
         <v>158</v>
       </c>
     </row>
@@ -5477,7 +5592,7 @@
       <c r="G39" t="s">
         <v>153</v>
       </c>
-      <c r="H39" s="7"/>
+      <c r="H39" s="8"/>
       <c r="I39" t="s">
         <v>149</v>
       </c>
@@ -5508,7 +5623,7 @@
       <c r="R39" t="s">
         <v>27</v>
       </c>
-      <c r="S39" s="8"/>
+      <c r="S39" s="9"/>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
@@ -5532,7 +5647,7 @@
       <c r="G40" t="s">
         <v>153</v>
       </c>
-      <c r="H40" s="7"/>
+      <c r="H40" s="8"/>
       <c r="I40" t="s">
         <v>149</v>
       </c>
@@ -5563,7 +5678,7 @@
       <c r="R40" t="s">
         <v>27</v>
       </c>
-      <c r="S40" s="8"/>
+      <c r="S40" s="9"/>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
@@ -5587,7 +5702,7 @@
       <c r="G41" t="s">
         <v>153</v>
       </c>
-      <c r="H41" s="7"/>
+      <c r="H41" s="8"/>
       <c r="I41" t="s">
         <v>149</v>
       </c>
@@ -5618,7 +5733,7 @@
       <c r="R41" t="s">
         <v>27</v>
       </c>
-      <c r="S41" s="8"/>
+      <c r="S41" s="9"/>
     </row>
     <row r="42" spans="1:19" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
@@ -5642,7 +5757,7 @@
       <c r="G42" t="s">
         <v>162</v>
       </c>
-      <c r="H42" s="7" t="s">
+      <c r="H42" s="8" t="s">
         <v>77</v>
       </c>
       <c r="I42" t="s">
@@ -5675,7 +5790,7 @@
       <c r="R42" t="s">
         <v>27</v>
       </c>
-      <c r="S42" s="8" t="s">
+      <c r="S42" s="9" t="s">
         <v>172</v>
       </c>
     </row>
@@ -5701,7 +5816,7 @@
       <c r="G43" t="s">
         <v>162</v>
       </c>
-      <c r="H43" s="7"/>
+      <c r="H43" s="8"/>
       <c r="I43" t="s">
         <v>167</v>
       </c>
@@ -5732,7 +5847,7 @@
       <c r="R43" t="s">
         <v>27</v>
       </c>
-      <c r="S43" s="8"/>
+      <c r="S43" s="9"/>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
@@ -5756,7 +5871,7 @@
       <c r="G44" t="s">
         <v>162</v>
       </c>
-      <c r="H44" s="7"/>
+      <c r="H44" s="8"/>
       <c r="I44" t="s">
         <v>167</v>
       </c>
@@ -5787,7 +5902,7 @@
       <c r="R44" t="s">
         <v>27</v>
       </c>
-      <c r="S44" s="8"/>
+      <c r="S44" s="9"/>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
@@ -5811,7 +5926,7 @@
       <c r="G45" t="s">
         <v>162</v>
       </c>
-      <c r="H45" s="7"/>
+      <c r="H45" s="8"/>
       <c r="I45" t="s">
         <v>167</v>
       </c>
@@ -5842,7 +5957,7 @@
       <c r="R45" t="s">
         <v>27</v>
       </c>
-      <c r="S45" s="8"/>
+      <c r="S45" s="9"/>
     </row>
     <row r="46" spans="1:19" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
@@ -5866,7 +5981,7 @@
       <c r="G46" t="s">
         <v>177</v>
       </c>
-      <c r="H46" s="7" t="s">
+      <c r="H46" s="8" t="s">
         <v>77</v>
       </c>
       <c r="I46" t="s">
@@ -5899,7 +6014,7 @@
       <c r="R46" t="s">
         <v>27</v>
       </c>
-      <c r="S46" s="8" t="s">
+      <c r="S46" s="9" t="s">
         <v>186</v>
       </c>
     </row>
@@ -5925,7 +6040,7 @@
       <c r="G47" t="s">
         <v>177</v>
       </c>
-      <c r="H47" s="7"/>
+      <c r="H47" s="8"/>
       <c r="I47" t="s">
         <v>178</v>
       </c>
@@ -5956,7 +6071,7 @@
       <c r="R47" t="s">
         <v>27</v>
       </c>
-      <c r="S47" s="8"/>
+      <c r="S47" s="9"/>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
@@ -5980,7 +6095,7 @@
       <c r="G48" t="s">
         <v>177</v>
       </c>
-      <c r="H48" s="7"/>
+      <c r="H48" s="8"/>
       <c r="I48" t="s">
         <v>178</v>
       </c>
@@ -6011,7 +6126,7 @@
       <c r="R48" t="s">
         <v>27</v>
       </c>
-      <c r="S48" s="8"/>
+      <c r="S48" s="9"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
@@ -6035,7 +6150,7 @@
       <c r="G49" t="s">
         <v>177</v>
       </c>
-      <c r="H49" s="7"/>
+      <c r="H49" s="8"/>
       <c r="I49" t="s">
         <v>178</v>
       </c>
@@ -6066,7 +6181,7 @@
       <c r="R49" t="s">
         <v>27</v>
       </c>
-      <c r="S49" s="8"/>
+      <c r="S49" s="9"/>
     </row>
     <row r="50" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
@@ -6090,7 +6205,7 @@
       <c r="G50" t="s">
         <v>189</v>
       </c>
-      <c r="H50" s="7" t="s">
+      <c r="H50" s="8" t="s">
         <v>197</v>
       </c>
       <c r="I50" t="s">
@@ -6123,7 +6238,7 @@
       <c r="R50" t="s">
         <v>198</v>
       </c>
-      <c r="S50" s="8" t="s">
+      <c r="S50" s="9" t="s">
         <v>201</v>
       </c>
     </row>
@@ -6149,7 +6264,7 @@
       <c r="G51" t="s">
         <v>189</v>
       </c>
-      <c r="H51" s="7"/>
+      <c r="H51" s="8"/>
       <c r="I51" t="s">
         <v>191</v>
       </c>
@@ -6180,7 +6295,7 @@
       <c r="R51" t="s">
         <v>198</v>
       </c>
-      <c r="S51" s="8"/>
+      <c r="S51" s="9"/>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
@@ -6204,7 +6319,7 @@
       <c r="G52" t="s">
         <v>189</v>
       </c>
-      <c r="H52" s="7"/>
+      <c r="H52" s="8"/>
       <c r="I52" t="s">
         <v>191</v>
       </c>
@@ -6235,7 +6350,7 @@
       <c r="R52" t="s">
         <v>198</v>
       </c>
-      <c r="S52" s="8"/>
+      <c r="S52" s="9"/>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
@@ -6259,7 +6374,7 @@
       <c r="G53" t="s">
         <v>189</v>
       </c>
-      <c r="H53" s="7"/>
+      <c r="H53" s="8"/>
       <c r="I53" t="s">
         <v>191</v>
       </c>
@@ -6290,7 +6405,7 @@
       <c r="R53" t="s">
         <v>198</v>
       </c>
-      <c r="S53" s="8"/>
+      <c r="S53" s="9"/>
     </row>
     <row r="54" spans="1:19" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
@@ -6314,7 +6429,7 @@
       <c r="G54" t="s">
         <v>204</v>
       </c>
-      <c r="H54" s="7" t="s">
+      <c r="H54" s="8" t="s">
         <v>211</v>
       </c>
       <c r="I54" t="s">
@@ -6347,7 +6462,7 @@
       <c r="R54" t="s">
         <v>27</v>
       </c>
-      <c r="S54" s="8" t="s">
+      <c r="S54" s="9" t="s">
         <v>213</v>
       </c>
     </row>
@@ -6373,7 +6488,7 @@
       <c r="G55" t="s">
         <v>204</v>
       </c>
-      <c r="H55" s="7"/>
+      <c r="H55" s="8"/>
       <c r="I55" t="s">
         <v>210</v>
       </c>
@@ -6404,7 +6519,7 @@
       <c r="R55" t="s">
         <v>27</v>
       </c>
-      <c r="S55" s="8"/>
+      <c r="S55" s="9"/>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
@@ -6428,7 +6543,7 @@
       <c r="G56" t="s">
         <v>204</v>
       </c>
-      <c r="H56" s="7"/>
+      <c r="H56" s="8"/>
       <c r="I56" t="s">
         <v>210</v>
       </c>
@@ -6459,7 +6574,7 @@
       <c r="R56" t="s">
         <v>27</v>
       </c>
-      <c r="S56" s="8"/>
+      <c r="S56" s="9"/>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
@@ -6483,7 +6598,7 @@
       <c r="G57" t="s">
         <v>204</v>
       </c>
-      <c r="H57" s="7"/>
+      <c r="H57" s="8"/>
       <c r="I57" t="s">
         <v>210</v>
       </c>
@@ -6514,7 +6629,7 @@
       <c r="R57" t="s">
         <v>27</v>
       </c>
-      <c r="S57" s="8"/>
+      <c r="S57" s="9"/>
     </row>
     <row r="58" spans="1:19" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
@@ -6538,7 +6653,7 @@
       <c r="G58" t="s">
         <v>217</v>
       </c>
-      <c r="H58" s="7" t="s">
+      <c r="H58" s="8" t="s">
         <v>77</v>
       </c>
       <c r="I58" t="s">
@@ -6571,7 +6686,7 @@
       <c r="R58" t="s">
         <v>27</v>
       </c>
-      <c r="S58" s="8" t="s">
+      <c r="S58" s="9" t="s">
         <v>227</v>
       </c>
     </row>
@@ -6597,7 +6712,7 @@
       <c r="G59" t="s">
         <v>217</v>
       </c>
-      <c r="H59" s="7"/>
+      <c r="H59" s="8"/>
       <c r="I59" t="s">
         <v>223</v>
       </c>
@@ -6628,7 +6743,7 @@
       <c r="R59" t="s">
         <v>27</v>
       </c>
-      <c r="S59" s="8"/>
+      <c r="S59" s="9"/>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
@@ -6652,7 +6767,7 @@
       <c r="G60" t="s">
         <v>217</v>
       </c>
-      <c r="H60" s="7"/>
+      <c r="H60" s="8"/>
       <c r="I60" t="s">
         <v>223</v>
       </c>
@@ -6683,7 +6798,7 @@
       <c r="R60" t="s">
         <v>27</v>
       </c>
-      <c r="S60" s="8"/>
+      <c r="S60" s="9"/>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
@@ -6707,7 +6822,7 @@
       <c r="G61" t="s">
         <v>217</v>
       </c>
-      <c r="H61" s="7"/>
+      <c r="H61" s="8"/>
       <c r="I61" t="s">
         <v>223</v>
       </c>
@@ -6738,7 +6853,7 @@
       <c r="R61" t="s">
         <v>27</v>
       </c>
-      <c r="S61" s="8"/>
+      <c r="S61" s="9"/>
     </row>
     <row r="62" spans="1:19" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
@@ -6762,7 +6877,7 @@
       <c r="G62" t="s">
         <v>230</v>
       </c>
-      <c r="H62" s="7" t="s">
+      <c r="H62" s="8" t="s">
         <v>77</v>
       </c>
       <c r="I62" t="s">
@@ -6795,7 +6910,7 @@
       <c r="R62" t="s">
         <v>27</v>
       </c>
-      <c r="S62" s="8" t="s">
+      <c r="S62" s="9" t="s">
         <v>238</v>
       </c>
     </row>
@@ -6821,7 +6936,7 @@
       <c r="G63" t="s">
         <v>230</v>
       </c>
-      <c r="H63" s="7"/>
+      <c r="H63" s="8"/>
       <c r="I63" t="s">
         <v>235</v>
       </c>
@@ -6852,7 +6967,7 @@
       <c r="R63" t="s">
         <v>27</v>
       </c>
-      <c r="S63" s="8"/>
+      <c r="S63" s="9"/>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
@@ -6876,7 +6991,7 @@
       <c r="G64" t="s">
         <v>230</v>
       </c>
-      <c r="H64" s="7"/>
+      <c r="H64" s="8"/>
       <c r="I64" t="s">
         <v>235</v>
       </c>
@@ -6907,7 +7022,7 @@
       <c r="R64" t="s">
         <v>27</v>
       </c>
-      <c r="S64" s="8"/>
+      <c r="S64" s="9"/>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
@@ -6931,7 +7046,7 @@
       <c r="G65" t="s">
         <v>230</v>
       </c>
-      <c r="H65" s="7"/>
+      <c r="H65" s="8"/>
       <c r="I65" t="s">
         <v>235</v>
       </c>
@@ -6962,7 +7077,7 @@
       <c r="R65" t="s">
         <v>27</v>
       </c>
-      <c r="S65" s="8"/>
+      <c r="S65" s="9"/>
     </row>
     <row r="66" spans="1:19" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
@@ -6986,7 +7101,7 @@
       <c r="G66" t="s">
         <v>241</v>
       </c>
-      <c r="H66" s="7" t="s">
+      <c r="H66" s="8" t="s">
         <v>77</v>
       </c>
       <c r="I66" t="s">
@@ -7019,7 +7134,7 @@
       <c r="R66" t="s">
         <v>248</v>
       </c>
-      <c r="S66" s="8" t="s">
+      <c r="S66" s="9" t="s">
         <v>251</v>
       </c>
     </row>
@@ -7045,7 +7160,7 @@
       <c r="G67" t="s">
         <v>241</v>
       </c>
-      <c r="H67" s="7"/>
+      <c r="H67" s="8"/>
       <c r="I67" t="s">
         <v>246</v>
       </c>
@@ -7076,7 +7191,7 @@
       <c r="R67" t="s">
         <v>248</v>
       </c>
-      <c r="S67" s="8"/>
+      <c r="S67" s="9"/>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
@@ -7100,7 +7215,7 @@
       <c r="G68" t="s">
         <v>241</v>
       </c>
-      <c r="H68" s="7"/>
+      <c r="H68" s="8"/>
       <c r="I68" t="s">
         <v>246</v>
       </c>
@@ -7131,7 +7246,7 @@
       <c r="R68" t="s">
         <v>248</v>
       </c>
-      <c r="S68" s="8"/>
+      <c r="S68" s="9"/>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
@@ -7155,7 +7270,7 @@
       <c r="G69" t="s">
         <v>241</v>
       </c>
-      <c r="H69" s="7"/>
+      <c r="H69" s="8"/>
       <c r="I69" t="s">
         <v>246</v>
       </c>
@@ -7186,7 +7301,7 @@
       <c r="R69" t="s">
         <v>248</v>
       </c>
-      <c r="S69" s="8"/>
+      <c r="S69" s="9"/>
     </row>
     <row r="70" spans="1:19" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
@@ -7210,7 +7325,7 @@
       <c r="G70" t="s">
         <v>254</v>
       </c>
-      <c r="H70" s="7" t="s">
+      <c r="H70" s="8" t="s">
         <v>77</v>
       </c>
       <c r="I70" t="s">
@@ -7243,7 +7358,7 @@
       <c r="R70" t="s">
         <v>24</v>
       </c>
-      <c r="S70" s="8" t="s">
+      <c r="S70" s="9" t="s">
         <v>263</v>
       </c>
     </row>
@@ -7269,7 +7384,7 @@
       <c r="G71" t="s">
         <v>254</v>
       </c>
-      <c r="H71" s="7"/>
+      <c r="H71" s="8"/>
       <c r="I71" t="s">
         <v>259</v>
       </c>
@@ -7300,7 +7415,7 @@
       <c r="R71" t="s">
         <v>24</v>
       </c>
-      <c r="S71" s="8"/>
+      <c r="S71" s="9"/>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
@@ -7324,7 +7439,7 @@
       <c r="G72" t="s">
         <v>254</v>
       </c>
-      <c r="H72" s="7"/>
+      <c r="H72" s="8"/>
       <c r="I72" t="s">
         <v>259</v>
       </c>
@@ -7355,7 +7470,7 @@
       <c r="R72" t="s">
         <v>24</v>
       </c>
-      <c r="S72" s="8"/>
+      <c r="S72" s="9"/>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
@@ -7379,7 +7494,7 @@
       <c r="G73" t="s">
         <v>254</v>
       </c>
-      <c r="H73" s="7"/>
+      <c r="H73" s="8"/>
       <c r="I73" t="s">
         <v>259</v>
       </c>
@@ -7410,7 +7525,7 @@
       <c r="R73" t="s">
         <v>24</v>
       </c>
-      <c r="S73" s="8"/>
+      <c r="S73" s="9"/>
     </row>
     <row r="74" spans="1:19" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
@@ -7434,7 +7549,7 @@
       <c r="G74" t="s">
         <v>266</v>
       </c>
-      <c r="H74" s="7" t="s">
+      <c r="H74" s="8" t="s">
         <v>77</v>
       </c>
       <c r="I74" t="s">
@@ -7467,7 +7582,7 @@
       <c r="R74" t="s">
         <v>24</v>
       </c>
-      <c r="S74" s="8" t="s">
+      <c r="S74" s="9" t="s">
         <v>287</v>
       </c>
     </row>
@@ -7493,7 +7608,7 @@
       <c r="G75" t="s">
         <v>266</v>
       </c>
-      <c r="H75" s="7"/>
+      <c r="H75" s="8"/>
       <c r="I75" t="s">
         <v>271</v>
       </c>
@@ -7524,7 +7639,7 @@
       <c r="R75" t="s">
         <v>24</v>
       </c>
-      <c r="S75" s="8"/>
+      <c r="S75" s="9"/>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
@@ -7548,7 +7663,7 @@
       <c r="G76" t="s">
         <v>266</v>
       </c>
-      <c r="H76" s="7"/>
+      <c r="H76" s="8"/>
       <c r="I76" t="s">
         <v>271</v>
       </c>
@@ -7579,7 +7694,7 @@
       <c r="R76" t="s">
         <v>24</v>
       </c>
-      <c r="S76" s="8"/>
+      <c r="S76" s="9"/>
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
@@ -7603,7 +7718,7 @@
       <c r="G77" t="s">
         <v>266</v>
       </c>
-      <c r="H77" s="7"/>
+      <c r="H77" s="8"/>
       <c r="I77" t="s">
         <v>271</v>
       </c>
@@ -7634,7 +7749,7 @@
       <c r="R77" t="s">
         <v>24</v>
       </c>
-      <c r="S77" s="8"/>
+      <c r="S77" s="9"/>
     </row>
     <row r="78" spans="1:19" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
@@ -7658,7 +7773,7 @@
       <c r="G78" t="s">
         <v>276</v>
       </c>
-      <c r="H78" s="7" t="s">
+      <c r="H78" s="8" t="s">
         <v>281</v>
       </c>
       <c r="I78" t="s">
@@ -7691,7 +7806,7 @@
       <c r="R78" t="s">
         <v>285</v>
       </c>
-      <c r="S78" s="8" t="s">
+      <c r="S78" s="9" t="s">
         <v>288</v>
       </c>
     </row>
@@ -7717,7 +7832,7 @@
       <c r="G79" t="s">
         <v>276</v>
       </c>
-      <c r="H79" s="7"/>
+      <c r="H79" s="8"/>
       <c r="I79" t="s">
         <v>283</v>
       </c>
@@ -7748,7 +7863,7 @@
       <c r="R79" t="s">
         <v>285</v>
       </c>
-      <c r="S79" s="8"/>
+      <c r="S79" s="9"/>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
@@ -7772,7 +7887,7 @@
       <c r="G80" t="s">
         <v>276</v>
       </c>
-      <c r="H80" s="7"/>
+      <c r="H80" s="8"/>
       <c r="I80" t="s">
         <v>283</v>
       </c>
@@ -7803,7 +7918,7 @@
       <c r="R80" t="s">
         <v>285</v>
       </c>
-      <c r="S80" s="8"/>
+      <c r="S80" s="9"/>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
@@ -7827,7 +7942,7 @@
       <c r="G81" t="s">
         <v>276</v>
       </c>
-      <c r="H81" s="7"/>
+      <c r="H81" s="8"/>
       <c r="I81" t="s">
         <v>283</v>
       </c>
@@ -7858,7 +7973,7 @@
       <c r="R81" t="s">
         <v>285</v>
       </c>
-      <c r="S81" s="8"/>
+      <c r="S81" s="9"/>
     </row>
     <row r="82" spans="1:20" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
@@ -7882,7 +7997,7 @@
       <c r="G82" t="s">
         <v>291</v>
       </c>
-      <c r="H82" s="7" t="s">
+      <c r="H82" s="8" t="s">
         <v>296</v>
       </c>
       <c r="I82" t="s">
@@ -7915,7 +8030,7 @@
       <c r="R82" t="s">
         <v>27</v>
       </c>
-      <c r="S82" s="8" t="s">
+      <c r="S82" s="9" t="s">
         <v>300</v>
       </c>
     </row>
@@ -7941,7 +8056,7 @@
       <c r="G83" t="s">
         <v>291</v>
       </c>
-      <c r="H83" s="7"/>
+      <c r="H83" s="8"/>
       <c r="I83" t="s">
         <v>297</v>
       </c>
@@ -7972,7 +8087,7 @@
       <c r="R83" t="s">
         <v>27</v>
       </c>
-      <c r="S83" s="8"/>
+      <c r="S83" s="9"/>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
@@ -7996,7 +8111,7 @@
       <c r="G84" t="s">
         <v>291</v>
       </c>
-      <c r="H84" s="7"/>
+      <c r="H84" s="8"/>
       <c r="I84" t="s">
         <v>297</v>
       </c>
@@ -8027,7 +8142,7 @@
       <c r="R84" t="s">
         <v>27</v>
       </c>
-      <c r="S84" s="8"/>
+      <c r="S84" s="9"/>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
@@ -8051,7 +8166,7 @@
       <c r="G85" t="s">
         <v>291</v>
       </c>
-      <c r="H85" s="7"/>
+      <c r="H85" s="8"/>
       <c r="I85" t="s">
         <v>297</v>
       </c>
@@ -8082,7 +8197,7 @@
       <c r="R85" t="s">
         <v>27</v>
       </c>
-      <c r="S85" s="8"/>
+      <c r="S85" s="9"/>
     </row>
     <row r="86" spans="1:20" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
@@ -8106,7 +8221,7 @@
       <c r="G86" t="s">
         <v>303</v>
       </c>
-      <c r="H86" s="7" t="s">
+      <c r="H86" s="8" t="s">
         <v>296</v>
       </c>
       <c r="I86" t="s">
@@ -8139,7 +8254,7 @@
       <c r="R86" t="s">
         <v>27</v>
       </c>
-      <c r="S86" s="8" t="s">
+      <c r="S86" s="9" t="s">
         <v>312</v>
       </c>
     </row>
@@ -8165,7 +8280,7 @@
       <c r="G87" t="s">
         <v>303</v>
       </c>
-      <c r="H87" s="7"/>
+      <c r="H87" s="8"/>
       <c r="I87" t="s">
         <v>308</v>
       </c>
@@ -8196,7 +8311,7 @@
       <c r="R87" t="s">
         <v>27</v>
       </c>
-      <c r="S87" s="8"/>
+      <c r="S87" s="9"/>
     </row>
     <row r="88" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
@@ -8220,7 +8335,7 @@
       <c r="G88" t="s">
         <v>303</v>
       </c>
-      <c r="H88" s="7"/>
+      <c r="H88" s="8"/>
       <c r="I88" t="s">
         <v>308</v>
       </c>
@@ -8251,7 +8366,7 @@
       <c r="R88" t="s">
         <v>27</v>
       </c>
-      <c r="S88" s="8"/>
+      <c r="S88" s="9"/>
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
@@ -8275,7 +8390,7 @@
       <c r="G89" t="s">
         <v>303</v>
       </c>
-      <c r="H89" s="7"/>
+      <c r="H89" s="8"/>
       <c r="I89" t="s">
         <v>308</v>
       </c>
@@ -8306,7 +8421,7 @@
       <c r="R89" t="s">
         <v>27</v>
       </c>
-      <c r="S89" s="8"/>
+      <c r="S89" s="9"/>
     </row>
     <row r="90" spans="1:20" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
@@ -8330,7 +8445,7 @@
       <c r="G90" t="s">
         <v>409</v>
       </c>
-      <c r="H90" s="7" t="s">
+      <c r="H90" s="8" t="s">
         <v>296</v>
       </c>
       <c r="I90" t="s">
@@ -8342,7 +8457,7 @@
       <c r="K90" t="s">
         <v>36</v>
       </c>
-      <c r="L90" s="10" t="s">
+      <c r="L90" s="7" t="s">
         <v>412</v>
       </c>
       <c r="M90" t="s">
@@ -8363,10 +8478,10 @@
       <c r="R90" t="s">
         <v>27</v>
       </c>
-      <c r="S90" s="8" t="s">
+      <c r="S90" s="9" t="s">
         <v>415</v>
       </c>
-      <c r="T90" s="10" t="s">
+      <c r="T90" s="7" t="s">
         <v>402</v>
       </c>
     </row>
@@ -8392,7 +8507,7 @@
       <c r="G91" t="s">
         <v>409</v>
       </c>
-      <c r="H91" s="7"/>
+      <c r="H91" s="8"/>
       <c r="I91" t="s">
         <v>410</v>
       </c>
@@ -8402,7 +8517,7 @@
       <c r="K91" t="s">
         <v>36</v>
       </c>
-      <c r="L91" s="10" t="s">
+      <c r="L91" s="7" t="s">
         <v>412</v>
       </c>
       <c r="M91" t="s">
@@ -8423,7 +8538,7 @@
       <c r="R91" t="s">
         <v>27</v>
       </c>
-      <c r="S91" s="8"/>
+      <c r="S91" s="9"/>
     </row>
     <row r="92" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
@@ -8447,7 +8562,7 @@
       <c r="G92" t="s">
         <v>409</v>
       </c>
-      <c r="H92" s="7"/>
+      <c r="H92" s="8"/>
       <c r="I92" t="s">
         <v>410</v>
       </c>
@@ -8457,7 +8572,7 @@
       <c r="K92" t="s">
         <v>36</v>
       </c>
-      <c r="L92" s="10" t="s">
+      <c r="L92" s="7" t="s">
         <v>412</v>
       </c>
       <c r="M92" t="s">
@@ -8478,7 +8593,7 @@
       <c r="R92" t="s">
         <v>27</v>
       </c>
-      <c r="S92" s="8"/>
+      <c r="S92" s="9"/>
     </row>
     <row r="93" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
@@ -8502,7 +8617,7 @@
       <c r="G93" t="s">
         <v>409</v>
       </c>
-      <c r="H93" s="7"/>
+      <c r="H93" s="8"/>
       <c r="I93" t="s">
         <v>410</v>
       </c>
@@ -8512,7 +8627,7 @@
       <c r="K93" t="s">
         <v>36</v>
       </c>
-      <c r="L93" s="10" t="s">
+      <c r="L93" s="7" t="s">
         <v>412</v>
       </c>
       <c r="M93" t="s">
@@ -8533,7 +8648,7 @@
       <c r="R93" t="s">
         <v>27</v>
       </c>
-      <c r="S93" s="8"/>
+      <c r="S93" s="9"/>
     </row>
     <row r="94" spans="1:20" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
@@ -8557,7 +8672,7 @@
       <c r="G94" t="s">
         <v>317</v>
       </c>
-      <c r="H94" s="7" t="s">
+      <c r="H94" s="8" t="s">
         <v>296</v>
       </c>
       <c r="I94" t="s">
@@ -8590,7 +8705,7 @@
       <c r="R94" t="s">
         <v>27</v>
       </c>
-      <c r="S94" s="8" t="s">
+      <c r="S94" s="9" t="s">
         <v>325</v>
       </c>
     </row>
@@ -8616,7 +8731,7 @@
       <c r="G95" t="s">
         <v>317</v>
       </c>
-      <c r="H95" s="7"/>
+      <c r="H95" s="8"/>
       <c r="I95" t="s">
         <v>322</v>
       </c>
@@ -8647,7 +8762,7 @@
       <c r="R95" t="s">
         <v>27</v>
       </c>
-      <c r="S95" s="8"/>
+      <c r="S95" s="9"/>
     </row>
     <row r="96" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
@@ -8671,7 +8786,7 @@
       <c r="G96" t="s">
         <v>317</v>
       </c>
-      <c r="H96" s="7"/>
+      <c r="H96" s="8"/>
       <c r="I96" t="s">
         <v>322</v>
       </c>
@@ -8702,7 +8817,7 @@
       <c r="R96" t="s">
         <v>27</v>
       </c>
-      <c r="S96" s="8"/>
+      <c r="S96" s="9"/>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
@@ -8726,7 +8841,7 @@
       <c r="G97" t="s">
         <v>317</v>
       </c>
-      <c r="H97" s="7"/>
+      <c r="H97" s="8"/>
       <c r="I97" t="s">
         <v>322</v>
       </c>
@@ -8757,7 +8872,7 @@
       <c r="R97" t="s">
         <v>27</v>
       </c>
-      <c r="S97" s="8"/>
+      <c r="S97" s="9"/>
     </row>
     <row r="98" spans="1:19" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
@@ -8781,7 +8896,7 @@
       <c r="G98" t="s">
         <v>329</v>
       </c>
-      <c r="H98" s="7" t="s">
+      <c r="H98" s="8" t="s">
         <v>296</v>
       </c>
       <c r="I98" t="s">
@@ -8814,7 +8929,7 @@
       <c r="R98" t="s">
         <v>27</v>
       </c>
-      <c r="S98" s="8" t="s">
+      <c r="S98" s="9" t="s">
         <v>337</v>
       </c>
     </row>
@@ -8840,7 +8955,7 @@
       <c r="G99" t="s">
         <v>329</v>
       </c>
-      <c r="H99" s="7"/>
+      <c r="H99" s="8"/>
       <c r="I99" t="s">
         <v>334</v>
       </c>
@@ -8871,7 +8986,7 @@
       <c r="R99" t="s">
         <v>27</v>
       </c>
-      <c r="S99" s="8"/>
+      <c r="S99" s="9"/>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
@@ -8895,7 +9010,7 @@
       <c r="G100" t="s">
         <v>329</v>
       </c>
-      <c r="H100" s="7"/>
+      <c r="H100" s="8"/>
       <c r="I100" t="s">
         <v>334</v>
       </c>
@@ -8926,7 +9041,7 @@
       <c r="R100" t="s">
         <v>27</v>
       </c>
-      <c r="S100" s="8"/>
+      <c r="S100" s="9"/>
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
@@ -8950,7 +9065,7 @@
       <c r="G101" t="s">
         <v>329</v>
       </c>
-      <c r="H101" s="7"/>
+      <c r="H101" s="8"/>
       <c r="I101" t="s">
         <v>334</v>
       </c>
@@ -8981,7 +9096,7 @@
       <c r="R101" t="s">
         <v>27</v>
       </c>
-      <c r="S101" s="8"/>
+      <c r="S101" s="9"/>
     </row>
     <row r="102" spans="1:19" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
@@ -9005,7 +9120,7 @@
       <c r="G102" t="s">
         <v>340</v>
       </c>
-      <c r="H102" s="7" t="s">
+      <c r="H102" s="8" t="s">
         <v>296</v>
       </c>
       <c r="I102" t="s">
@@ -9038,7 +9153,7 @@
       <c r="R102" t="s">
         <v>27</v>
       </c>
-      <c r="S102" s="8" t="s">
+      <c r="S102" s="9" t="s">
         <v>347</v>
       </c>
     </row>
@@ -9064,7 +9179,7 @@
       <c r="G103" t="s">
         <v>340</v>
       </c>
-      <c r="H103" s="7"/>
+      <c r="H103" s="8"/>
       <c r="I103" t="s">
         <v>345</v>
       </c>
@@ -9095,7 +9210,7 @@
       <c r="R103" t="s">
         <v>27</v>
       </c>
-      <c r="S103" s="8"/>
+      <c r="S103" s="9"/>
     </row>
     <row r="104" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
@@ -9119,7 +9234,7 @@
       <c r="G104" t="s">
         <v>340</v>
       </c>
-      <c r="H104" s="7"/>
+      <c r="H104" s="8"/>
       <c r="I104" t="s">
         <v>345</v>
       </c>
@@ -9150,7 +9265,7 @@
       <c r="R104" t="s">
         <v>27</v>
       </c>
-      <c r="S104" s="8"/>
+      <c r="S104" s="9"/>
     </row>
     <row r="105" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
@@ -9174,7 +9289,7 @@
       <c r="G105" t="s">
         <v>340</v>
       </c>
-      <c r="H105" s="7"/>
+      <c r="H105" s="8"/>
       <c r="I105" t="s">
         <v>345</v>
       </c>
@@ -9205,7 +9320,7 @@
       <c r="R105" t="s">
         <v>27</v>
       </c>
-      <c r="S105" s="8"/>
+      <c r="S105" s="9"/>
     </row>
     <row r="106" spans="1:19" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
@@ -9229,7 +9344,7 @@
       <c r="G106" t="s">
         <v>351</v>
       </c>
-      <c r="H106" s="7" t="s">
+      <c r="H106" s="8" t="s">
         <v>296</v>
       </c>
       <c r="I106" t="s">
@@ -9262,7 +9377,7 @@
       <c r="R106" t="s">
         <v>27</v>
       </c>
-      <c r="S106" s="8" t="s">
+      <c r="S106" s="9" t="s">
         <v>359</v>
       </c>
     </row>
@@ -9288,7 +9403,7 @@
       <c r="G107" t="s">
         <v>351</v>
       </c>
-      <c r="H107" s="7"/>
+      <c r="H107" s="8"/>
       <c r="I107" t="s">
         <v>356</v>
       </c>
@@ -9319,7 +9434,7 @@
       <c r="R107" t="s">
         <v>27</v>
       </c>
-      <c r="S107" s="8"/>
+      <c r="S107" s="9"/>
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
@@ -9343,7 +9458,7 @@
       <c r="G108" t="s">
         <v>351</v>
       </c>
-      <c r="H108" s="7"/>
+      <c r="H108" s="8"/>
       <c r="I108" t="s">
         <v>356</v>
       </c>
@@ -9374,7 +9489,7 @@
       <c r="R108" t="s">
         <v>27</v>
       </c>
-      <c r="S108" s="8"/>
+      <c r="S108" s="9"/>
     </row>
     <row r="109" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
@@ -9398,7 +9513,7 @@
       <c r="G109" t="s">
         <v>351</v>
       </c>
-      <c r="H109" s="7"/>
+      <c r="H109" s="8"/>
       <c r="I109" t="s">
         <v>356</v>
       </c>
@@ -9429,7 +9544,7 @@
       <c r="R109" t="s">
         <v>27</v>
       </c>
-      <c r="S109" s="8"/>
+      <c r="S109" s="9"/>
     </row>
     <row r="110" spans="1:19" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
@@ -9453,7 +9568,7 @@
       <c r="G110" t="s">
         <v>362</v>
       </c>
-      <c r="H110" s="7" t="s">
+      <c r="H110" s="8" t="s">
         <v>296</v>
       </c>
       <c r="I110" t="s">
@@ -9486,7 +9601,7 @@
       <c r="R110" t="s">
         <v>27</v>
       </c>
-      <c r="S110" s="8" t="s">
+      <c r="S110" s="9" t="s">
         <v>371</v>
       </c>
     </row>
@@ -9512,7 +9627,7 @@
       <c r="G111" t="s">
         <v>362</v>
       </c>
-      <c r="H111" s="7"/>
+      <c r="H111" s="8"/>
       <c r="I111" t="s">
         <v>367</v>
       </c>
@@ -9543,7 +9658,7 @@
       <c r="R111" t="s">
         <v>27</v>
       </c>
-      <c r="S111" s="8"/>
+      <c r="S111" s="9"/>
     </row>
     <row r="112" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
@@ -9567,7 +9682,7 @@
       <c r="G112" t="s">
         <v>362</v>
       </c>
-      <c r="H112" s="7"/>
+      <c r="H112" s="8"/>
       <c r="I112" t="s">
         <v>367</v>
       </c>
@@ -9598,9 +9713,9 @@
       <c r="R112" t="s">
         <v>27</v>
       </c>
-      <c r="S112" s="8"/>
-    </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="S112" s="9"/>
+    </row>
+    <row r="113" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>360</v>
       </c>
@@ -9622,7 +9737,7 @@
       <c r="G113" t="s">
         <v>362</v>
       </c>
-      <c r="H113" s="7"/>
+      <c r="H113" s="8"/>
       <c r="I113" t="s">
         <v>367</v>
       </c>
@@ -9653,9 +9768,9 @@
       <c r="R113" t="s">
         <v>27</v>
       </c>
-      <c r="S113" s="8"/>
-    </row>
-    <row r="114" spans="1:19" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S113" s="9"/>
+    </row>
+    <row r="114" spans="1:20" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>372</v>
       </c>
@@ -9677,7 +9792,7 @@
       <c r="G114" t="s">
         <v>374</v>
       </c>
-      <c r="H114" s="7" t="s">
+      <c r="H114" s="8" t="s">
         <v>380</v>
       </c>
       <c r="I114" t="s">
@@ -9710,11 +9825,11 @@
       <c r="R114" t="s">
         <v>383</v>
       </c>
-      <c r="S114" s="8" t="s">
+      <c r="S114" s="9" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>372</v>
       </c>
@@ -9736,7 +9851,7 @@
       <c r="G115" t="s">
         <v>374</v>
       </c>
-      <c r="H115" s="7"/>
+      <c r="H115" s="8"/>
       <c r="I115" t="s">
         <v>381</v>
       </c>
@@ -9767,9 +9882,9 @@
       <c r="R115" t="s">
         <v>383</v>
       </c>
-      <c r="S115" s="8"/>
-    </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="S115" s="9"/>
+    </row>
+    <row r="116" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>372</v>
       </c>
@@ -9791,7 +9906,7 @@
       <c r="G116" t="s">
         <v>374</v>
       </c>
-      <c r="H116" s="7"/>
+      <c r="H116" s="8"/>
       <c r="I116" t="s">
         <v>381</v>
       </c>
@@ -9822,9 +9937,9 @@
       <c r="R116" t="s">
         <v>383</v>
       </c>
-      <c r="S116" s="8"/>
-    </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="S116" s="9"/>
+    </row>
+    <row r="117" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>372</v>
       </c>
@@ -9846,7 +9961,7 @@
       <c r="G117" t="s">
         <v>374</v>
       </c>
-      <c r="H117" s="7"/>
+      <c r="H117" s="8"/>
       <c r="I117" t="s">
         <v>381</v>
       </c>
@@ -9877,9 +9992,9 @@
       <c r="R117" t="s">
         <v>383</v>
       </c>
-      <c r="S117" s="8"/>
-    </row>
-    <row r="118" spans="1:19" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S117" s="9"/>
+    </row>
+    <row r="118" spans="1:20" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>386</v>
       </c>
@@ -9901,7 +10016,7 @@
       <c r="G118" t="s">
         <v>389</v>
       </c>
-      <c r="H118" s="7" t="s">
+      <c r="H118" s="8" t="s">
         <v>395</v>
       </c>
       <c r="I118" t="s">
@@ -9934,11 +10049,11 @@
       <c r="R118" t="s">
         <v>398</v>
       </c>
-      <c r="S118" s="8" t="s">
+      <c r="S118" s="9" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>386</v>
       </c>
@@ -9960,7 +10075,7 @@
       <c r="G119" t="s">
         <v>389</v>
       </c>
-      <c r="H119" s="7"/>
+      <c r="H119" s="8"/>
       <c r="I119" t="s">
         <v>396</v>
       </c>
@@ -9991,9 +10106,9 @@
       <c r="R119" t="s">
         <v>398</v>
       </c>
-      <c r="S119" s="8"/>
-    </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="S119" s="9"/>
+    </row>
+    <row r="120" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>386</v>
       </c>
@@ -10015,7 +10130,7 @@
       <c r="G120" t="s">
         <v>389</v>
       </c>
-      <c r="H120" s="7"/>
+      <c r="H120" s="8"/>
       <c r="I120" t="s">
         <v>396</v>
       </c>
@@ -10046,9 +10161,9 @@
       <c r="R120" t="s">
         <v>398</v>
       </c>
-      <c r="S120" s="8"/>
-    </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="S120" s="9"/>
+    </row>
+    <row r="121" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>386</v>
       </c>
@@ -10070,7 +10185,7 @@
       <c r="G121" t="s">
         <v>389</v>
       </c>
-      <c r="H121" s="7"/>
+      <c r="H121" s="8"/>
       <c r="I121" t="s">
         <v>396</v>
       </c>
@@ -10101,9 +10216,9 @@
       <c r="R121" t="s">
         <v>398</v>
       </c>
-      <c r="S121" s="8"/>
-    </row>
-    <row r="122" spans="1:19" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S121" s="9"/>
+    </row>
+    <row r="122" spans="1:20" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>416</v>
       </c>
@@ -10125,7 +10240,7 @@
       <c r="G122" t="s">
         <v>419</v>
       </c>
-      <c r="H122" s="7" t="s">
+      <c r="H122" s="8" t="s">
         <v>296</v>
       </c>
       <c r="I122" t="s">
@@ -10158,11 +10273,11 @@
       <c r="R122" t="s">
         <v>27</v>
       </c>
-      <c r="S122" s="8" t="s">
+      <c r="S122" s="9" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>416</v>
       </c>
@@ -10184,7 +10299,7 @@
       <c r="G123" t="s">
         <v>419</v>
       </c>
-      <c r="H123" s="7"/>
+      <c r="H123" s="8"/>
       <c r="I123" t="s">
         <v>424</v>
       </c>
@@ -10215,9 +10330,9 @@
       <c r="R123" t="s">
         <v>27</v>
       </c>
-      <c r="S123" s="8"/>
-    </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="S123" s="9"/>
+    </row>
+    <row r="124" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>416</v>
       </c>
@@ -10239,7 +10354,7 @@
       <c r="G124" t="s">
         <v>419</v>
       </c>
-      <c r="H124" s="7"/>
+      <c r="H124" s="8"/>
       <c r="I124" t="s">
         <v>424</v>
       </c>
@@ -10270,9 +10385,9 @@
       <c r="R124" t="s">
         <v>27</v>
       </c>
-      <c r="S124" s="8"/>
-    </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="S124" s="9"/>
+    </row>
+    <row r="125" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>416</v>
       </c>
@@ -10294,7 +10409,7 @@
       <c r="G125" t="s">
         <v>419</v>
       </c>
-      <c r="H125" s="7"/>
+      <c r="H125" s="8"/>
       <c r="I125" t="s">
         <v>424</v>
       </c>
@@ -10325,29 +10440,239 @@
       <c r="R125" t="s">
         <v>27</v>
       </c>
-      <c r="S125" s="8"/>
-    </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="S125" s="9"/>
+    </row>
+    <row r="126" spans="1:20" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B126" s="3">
+        <v>2151</v>
+      </c>
+      <c r="C126" t="s">
+        <v>501</v>
+      </c>
+      <c r="D126" t="s">
+        <v>502</v>
+      </c>
+      <c r="E126" t="s">
+        <v>504</v>
+      </c>
+      <c r="F126" t="s">
+        <v>508</v>
+      </c>
+      <c r="G126" t="s">
+        <v>503</v>
+      </c>
+      <c r="H126" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="I126" t="s">
+        <v>509</v>
+      </c>
+      <c r="J126" t="s">
+        <v>510</v>
+      </c>
+      <c r="K126" t="s">
+        <v>36</v>
+      </c>
+      <c r="L126" t="s">
+        <v>511</v>
+      </c>
+      <c r="M126" t="s">
+        <v>27</v>
+      </c>
+      <c r="N126" t="s">
+        <v>324</v>
+      </c>
+      <c r="O126" t="s">
+        <v>324</v>
+      </c>
+      <c r="P126" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>324</v>
+      </c>
+      <c r="R126" t="s">
+        <v>27</v>
+      </c>
+      <c r="S126" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="T126" s="10" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="127" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B127" s="3">
+        <v>2151</v>
+      </c>
+      <c r="C127" t="s">
+        <v>501</v>
+      </c>
+      <c r="D127" t="s">
+        <v>502</v>
+      </c>
+      <c r="E127" t="s">
+        <v>505</v>
+      </c>
+      <c r="F127" t="s">
+        <v>508</v>
+      </c>
+      <c r="G127" t="s">
+        <v>503</v>
+      </c>
+      <c r="H127" s="8"/>
+      <c r="I127" t="s">
+        <v>509</v>
+      </c>
+      <c r="J127" t="s">
+        <v>510</v>
+      </c>
+      <c r="K127" t="s">
+        <v>36</v>
+      </c>
+      <c r="L127" t="s">
+        <v>511</v>
+      </c>
+      <c r="M127" t="s">
+        <v>27</v>
+      </c>
+      <c r="N127" t="s">
+        <v>324</v>
+      </c>
+      <c r="O127" t="s">
+        <v>324</v>
+      </c>
+      <c r="P127" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>324</v>
+      </c>
+      <c r="R127" t="s">
+        <v>27</v>
+      </c>
+      <c r="S127" s="9"/>
+      <c r="T127" s="10"/>
+    </row>
+    <row r="128" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B128" s="3">
+        <v>2151</v>
+      </c>
+      <c r="C128" t="s">
+        <v>501</v>
+      </c>
+      <c r="D128" t="s">
+        <v>502</v>
+      </c>
+      <c r="E128" t="s">
+        <v>506</v>
+      </c>
+      <c r="F128" t="s">
+        <v>508</v>
+      </c>
+      <c r="G128" t="s">
+        <v>503</v>
+      </c>
+      <c r="H128" s="8"/>
+      <c r="I128" t="s">
+        <v>509</v>
+      </c>
+      <c r="J128" t="s">
+        <v>510</v>
+      </c>
+      <c r="K128" t="s">
+        <v>36</v>
+      </c>
+      <c r="L128" t="s">
+        <v>511</v>
+      </c>
+      <c r="M128" t="s">
+        <v>27</v>
+      </c>
+      <c r="N128" t="s">
+        <v>324</v>
+      </c>
+      <c r="O128" t="s">
+        <v>324</v>
+      </c>
+      <c r="P128" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>324</v>
+      </c>
+      <c r="R128" t="s">
+        <v>27</v>
+      </c>
+      <c r="S128" s="9"/>
+      <c r="T128" s="10"/>
+    </row>
+    <row r="129" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="130" spans="1:19" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B129" s="3">
+        <v>2151</v>
+      </c>
+      <c r="C129" t="s">
+        <v>501</v>
+      </c>
+      <c r="D129" t="s">
+        <v>502</v>
+      </c>
+      <c r="E129" t="s">
+        <v>507</v>
+      </c>
+      <c r="F129" t="s">
+        <v>508</v>
+      </c>
+      <c r="G129" t="s">
+        <v>503</v>
+      </c>
+      <c r="H129" s="8"/>
+      <c r="I129" t="s">
+        <v>509</v>
+      </c>
+      <c r="J129" t="s">
+        <v>510</v>
+      </c>
+      <c r="K129" t="s">
+        <v>36</v>
+      </c>
+      <c r="L129" t="s">
+        <v>511</v>
+      </c>
+      <c r="M129" t="s">
+        <v>27</v>
+      </c>
+      <c r="N129" t="s">
+        <v>324</v>
+      </c>
+      <c r="O129" t="s">
+        <v>324</v>
+      </c>
+      <c r="P129" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>324</v>
+      </c>
+      <c r="R129" t="s">
+        <v>27</v>
+      </c>
+      <c r="S129" s="9"/>
+      <c r="T129" s="10"/>
+    </row>
+    <row r="130" spans="1:20" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>428</v>
       </c>
@@ -10369,7 +10694,7 @@
       <c r="G130" t="s">
         <v>432</v>
       </c>
-      <c r="H130" s="7" t="s">
+      <c r="H130" s="8" t="s">
         <v>296</v>
       </c>
       <c r="I130" t="s">
@@ -10402,11 +10727,11 @@
       <c r="R130" t="s">
         <v>430</v>
       </c>
-      <c r="S130" s="8" t="s">
+      <c r="S130" s="9" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>428</v>
       </c>
@@ -10428,7 +10753,7 @@
       <c r="G131" t="s">
         <v>432</v>
       </c>
-      <c r="H131" s="7"/>
+      <c r="H131" s="8"/>
       <c r="I131" t="s">
         <v>437</v>
       </c>
@@ -10459,9 +10784,9 @@
       <c r="R131" t="s">
         <v>430</v>
       </c>
-      <c r="S131" s="8"/>
-    </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="S131" s="9"/>
+    </row>
+    <row r="132" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>428</v>
       </c>
@@ -10483,7 +10808,7 @@
       <c r="G132" t="s">
         <v>432</v>
       </c>
-      <c r="H132" s="7"/>
+      <c r="H132" s="8"/>
       <c r="I132" t="s">
         <v>437</v>
       </c>
@@ -10514,9 +10839,9 @@
       <c r="R132" t="s">
         <v>430</v>
       </c>
-      <c r="S132" s="8"/>
-    </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="S132" s="9"/>
+    </row>
+    <row r="133" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>428</v>
       </c>
@@ -10538,7 +10863,7 @@
       <c r="G133" t="s">
         <v>432</v>
       </c>
-      <c r="H133" s="7"/>
+      <c r="H133" s="8"/>
       <c r="I133" t="s">
         <v>437</v>
       </c>
@@ -10569,9 +10894,9 @@
       <c r="R133" t="s">
         <v>430</v>
       </c>
-      <c r="S133" s="8"/>
-    </row>
-    <row r="134" spans="1:19" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S133" s="9"/>
+    </row>
+    <row r="134" spans="1:20" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>440</v>
       </c>
@@ -10593,7 +10918,7 @@
       <c r="G134" t="s">
         <v>442</v>
       </c>
-      <c r="H134" s="7" t="s">
+      <c r="H134" s="8" t="s">
         <v>296</v>
       </c>
       <c r="I134" t="s">
@@ -10626,11 +10951,11 @@
       <c r="R134" t="s">
         <v>27</v>
       </c>
-      <c r="S134" s="8" t="s">
+      <c r="S134" s="9" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>440</v>
       </c>
@@ -10652,7 +10977,7 @@
       <c r="G135" t="s">
         <v>442</v>
       </c>
-      <c r="H135" s="7"/>
+      <c r="H135" s="8"/>
       <c r="I135" t="s">
         <v>447</v>
       </c>
@@ -10683,9 +11008,9 @@
       <c r="R135" t="s">
         <v>27</v>
       </c>
-      <c r="S135" s="8"/>
-    </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="S135" s="9"/>
+    </row>
+    <row r="136" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>440</v>
       </c>
@@ -10707,7 +11032,7 @@
       <c r="G136" t="s">
         <v>442</v>
       </c>
-      <c r="H136" s="7"/>
+      <c r="H136" s="8"/>
       <c r="I136" t="s">
         <v>447</v>
       </c>
@@ -10738,9 +11063,9 @@
       <c r="R136" t="s">
         <v>27</v>
       </c>
-      <c r="S136" s="8"/>
-    </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="S136" s="9"/>
+    </row>
+    <row r="137" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>440</v>
       </c>
@@ -10762,7 +11087,7 @@
       <c r="G137" t="s">
         <v>442</v>
       </c>
-      <c r="H137" s="7"/>
+      <c r="H137" s="8"/>
       <c r="I137" t="s">
         <v>447</v>
       </c>
@@ -10793,9 +11118,9 @@
       <c r="R137" t="s">
         <v>27</v>
       </c>
-      <c r="S137" s="8"/>
-    </row>
-    <row r="138" spans="1:19" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S137" s="9"/>
+    </row>
+    <row r="138" spans="1:20" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>451</v>
       </c>
@@ -10817,7 +11142,7 @@
       <c r="G138" t="s">
         <v>453</v>
       </c>
-      <c r="H138" s="7" t="s">
+      <c r="H138" s="8" t="s">
         <v>296</v>
       </c>
       <c r="I138" t="s">
@@ -10850,11 +11175,11 @@
       <c r="R138" t="s">
         <v>461</v>
       </c>
-      <c r="S138" s="8" t="s">
+      <c r="S138" s="9" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>451</v>
       </c>
@@ -10876,7 +11201,7 @@
       <c r="G139" t="s">
         <v>453</v>
       </c>
-      <c r="H139" s="7"/>
+      <c r="H139" s="8"/>
       <c r="I139" t="s">
         <v>458</v>
       </c>
@@ -10907,9 +11232,9 @@
       <c r="R139" t="s">
         <v>461</v>
       </c>
-      <c r="S139" s="8"/>
-    </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="S139" s="9"/>
+    </row>
+    <row r="140" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>451</v>
       </c>
@@ -10931,7 +11256,7 @@
       <c r="G140" t="s">
         <v>453</v>
       </c>
-      <c r="H140" s="7"/>
+      <c r="H140" s="8"/>
       <c r="I140" t="s">
         <v>458</v>
       </c>
@@ -10962,9 +11287,9 @@
       <c r="R140" t="s">
         <v>461</v>
       </c>
-      <c r="S140" s="8"/>
-    </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="S140" s="9"/>
+    </row>
+    <row r="141" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>451</v>
       </c>
@@ -10986,7 +11311,7 @@
       <c r="G141" t="s">
         <v>453</v>
       </c>
-      <c r="H141" s="7"/>
+      <c r="H141" s="8"/>
       <c r="I141" t="s">
         <v>458</v>
       </c>
@@ -11017,9 +11342,9 @@
       <c r="R141" t="s">
         <v>461</v>
       </c>
-      <c r="S141" s="8"/>
-    </row>
-    <row r="142" spans="1:19" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S141" s="9"/>
+    </row>
+    <row r="142" spans="1:20" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>463</v>
       </c>
@@ -11041,7 +11366,7 @@
       <c r="G142" t="s">
         <v>466</v>
       </c>
-      <c r="H142" s="7" t="s">
+      <c r="H142" s="8" t="s">
         <v>473</v>
       </c>
       <c r="I142" t="s">
@@ -11074,11 +11399,11 @@
       <c r="R142" t="s">
         <v>27</v>
       </c>
-      <c r="S142" s="8" t="s">
+      <c r="S142" s="9" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>463</v>
       </c>
@@ -11100,7 +11425,7 @@
       <c r="G143" t="s">
         <v>466</v>
       </c>
-      <c r="H143" s="7"/>
+      <c r="H143" s="8"/>
       <c r="I143" t="s">
         <v>472</v>
       </c>
@@ -11131,9 +11456,9 @@
       <c r="R143" t="s">
         <v>27</v>
       </c>
-      <c r="S143" s="8"/>
-    </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="S143" s="9"/>
+    </row>
+    <row r="144" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>463</v>
       </c>
@@ -11155,7 +11480,7 @@
       <c r="G144" t="s">
         <v>466</v>
       </c>
-      <c r="H144" s="7"/>
+      <c r="H144" s="8"/>
       <c r="I144" t="s">
         <v>472</v>
       </c>
@@ -11186,7 +11511,7 @@
       <c r="R144" t="s">
         <v>27</v>
       </c>
-      <c r="S144" s="8"/>
+      <c r="S144" s="9"/>
     </row>
     <row r="145" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
@@ -11210,7 +11535,7 @@
       <c r="G145" t="s">
         <v>466</v>
       </c>
-      <c r="H145" s="7"/>
+      <c r="H145" s="8"/>
       <c r="I145" t="s">
         <v>472</v>
       </c>
@@ -11241,7 +11566,7 @@
       <c r="R145" t="s">
         <v>27</v>
       </c>
-      <c r="S145" s="8"/>
+      <c r="S145" s="9"/>
     </row>
     <row r="146" spans="1:19" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
@@ -11265,7 +11590,7 @@
       <c r="G146" t="s">
         <v>481</v>
       </c>
-      <c r="H146" s="7" t="s">
+      <c r="H146" s="8" t="s">
         <v>296</v>
       </c>
       <c r="I146" t="s">
@@ -11298,7 +11623,7 @@
       <c r="R146" t="s">
         <v>27</v>
       </c>
-      <c r="S146" s="8" t="s">
+      <c r="S146" s="9" t="s">
         <v>489</v>
       </c>
     </row>
@@ -11324,7 +11649,7 @@
       <c r="G147" t="s">
         <v>481</v>
       </c>
-      <c r="H147" s="7"/>
+      <c r="H147" s="8"/>
       <c r="I147" t="s">
         <v>487</v>
       </c>
@@ -11355,7 +11680,7 @@
       <c r="R147" t="s">
         <v>27</v>
       </c>
-      <c r="S147" s="8"/>
+      <c r="S147" s="9"/>
     </row>
     <row r="148" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
@@ -11379,7 +11704,7 @@
       <c r="G148" t="s">
         <v>481</v>
       </c>
-      <c r="H148" s="7"/>
+      <c r="H148" s="8"/>
       <c r="I148" t="s">
         <v>487</v>
       </c>
@@ -11410,7 +11735,7 @@
       <c r="R148" t="s">
         <v>27</v>
       </c>
-      <c r="S148" s="8"/>
+      <c r="S148" s="9"/>
     </row>
     <row r="149" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
@@ -11434,7 +11759,7 @@
       <c r="G149" t="s">
         <v>481</v>
       </c>
-      <c r="H149" s="7"/>
+      <c r="H149" s="8"/>
       <c r="I149" t="s">
         <v>487</v>
       </c>
@@ -11465,7 +11790,7 @@
       <c r="R149" t="s">
         <v>27</v>
       </c>
-      <c r="S149" s="8"/>
+      <c r="S149" s="9"/>
     </row>
     <row r="150" spans="1:19" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
@@ -11489,7 +11814,7 @@
       <c r="G150" t="s">
         <v>492</v>
       </c>
-      <c r="H150" s="7" t="s">
+      <c r="H150" s="8" t="s">
         <v>296</v>
       </c>
       <c r="I150" t="s">
@@ -11522,7 +11847,7 @@
       <c r="R150" t="s">
         <v>27</v>
       </c>
-      <c r="S150" s="8" t="s">
+      <c r="S150" s="9" t="s">
         <v>500</v>
       </c>
     </row>
@@ -11548,7 +11873,7 @@
       <c r="G151" t="s">
         <v>492</v>
       </c>
-      <c r="H151" s="7"/>
+      <c r="H151" s="8"/>
       <c r="I151" t="s">
         <v>497</v>
       </c>
@@ -11579,7 +11904,7 @@
       <c r="R151" t="s">
         <v>27</v>
       </c>
-      <c r="S151" s="8"/>
+      <c r="S151" s="9"/>
     </row>
     <row r="152" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
@@ -11603,7 +11928,7 @@
       <c r="G152" t="s">
         <v>492</v>
       </c>
-      <c r="H152" s="7"/>
+      <c r="H152" s="8"/>
       <c r="I152" t="s">
         <v>497</v>
       </c>
@@ -11634,7 +11959,7 @@
       <c r="R152" t="s">
         <v>27</v>
       </c>
-      <c r="S152" s="8"/>
+      <c r="S152" s="9"/>
     </row>
     <row r="153" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
@@ -11658,7 +11983,7 @@
       <c r="G153" t="s">
         <v>492</v>
       </c>
-      <c r="H153" s="7"/>
+      <c r="H153" s="8"/>
       <c r="I153" t="s">
         <v>497</v>
       </c>
@@ -11689,22 +12014,60 @@
       <c r="R153" t="s">
         <v>27</v>
       </c>
-      <c r="S153" s="8"/>
+      <c r="S153" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="75">
-    <mergeCell ref="H142:H145"/>
-    <mergeCell ref="S142:S145"/>
-    <mergeCell ref="H146:H149"/>
-    <mergeCell ref="S146:S149"/>
-    <mergeCell ref="H150:H153"/>
-    <mergeCell ref="S150:S153"/>
-    <mergeCell ref="H130:H133"/>
-    <mergeCell ref="S130:S133"/>
-    <mergeCell ref="H134:H137"/>
-    <mergeCell ref="S134:S137"/>
-    <mergeCell ref="H138:H141"/>
-    <mergeCell ref="S138:S141"/>
+  <mergeCells count="78">
+    <mergeCell ref="H126:H129"/>
+    <mergeCell ref="S126:S129"/>
+    <mergeCell ref="T126:T129"/>
+    <mergeCell ref="H86:H89"/>
+    <mergeCell ref="S86:S89"/>
+    <mergeCell ref="H70:H73"/>
+    <mergeCell ref="S70:S73"/>
+    <mergeCell ref="H74:H77"/>
+    <mergeCell ref="S74:S77"/>
+    <mergeCell ref="H78:H81"/>
+    <mergeCell ref="S78:S81"/>
+    <mergeCell ref="H62:H65"/>
+    <mergeCell ref="S62:S65"/>
+    <mergeCell ref="H66:H69"/>
+    <mergeCell ref="S66:S69"/>
+    <mergeCell ref="H82:H85"/>
+    <mergeCell ref="S82:S85"/>
+    <mergeCell ref="H50:H53"/>
+    <mergeCell ref="S50:S53"/>
+    <mergeCell ref="H54:H57"/>
+    <mergeCell ref="S54:S57"/>
+    <mergeCell ref="H58:H61"/>
+    <mergeCell ref="S58:S61"/>
+    <mergeCell ref="H38:H41"/>
+    <mergeCell ref="S38:S41"/>
+    <mergeCell ref="H42:H45"/>
+    <mergeCell ref="S42:S45"/>
+    <mergeCell ref="H46:H49"/>
+    <mergeCell ref="S46:S49"/>
+    <mergeCell ref="S26:S29"/>
+    <mergeCell ref="H30:H33"/>
+    <mergeCell ref="S30:S33"/>
+    <mergeCell ref="H34:H37"/>
+    <mergeCell ref="S34:S37"/>
+    <mergeCell ref="H102:H105"/>
+    <mergeCell ref="S102:S105"/>
+    <mergeCell ref="H2:H5"/>
+    <mergeCell ref="S2:S5"/>
+    <mergeCell ref="H6:H9"/>
+    <mergeCell ref="S6:S9"/>
+    <mergeCell ref="H10:H13"/>
+    <mergeCell ref="S10:S13"/>
+    <mergeCell ref="H14:H17"/>
+    <mergeCell ref="L14:L17"/>
+    <mergeCell ref="S14:S17"/>
+    <mergeCell ref="H18:H21"/>
+    <mergeCell ref="S18:S21"/>
+    <mergeCell ref="H22:H25"/>
+    <mergeCell ref="S22:S25"/>
+    <mergeCell ref="H26:H29"/>
     <mergeCell ref="H118:H121"/>
     <mergeCell ref="S118:S121"/>
     <mergeCell ref="H90:H93"/>
@@ -11721,53 +12084,18 @@
     <mergeCell ref="S94:S97"/>
     <mergeCell ref="H98:H101"/>
     <mergeCell ref="S98:S101"/>
-    <mergeCell ref="H102:H105"/>
-    <mergeCell ref="S102:S105"/>
-    <mergeCell ref="H2:H5"/>
-    <mergeCell ref="S2:S5"/>
-    <mergeCell ref="H6:H9"/>
-    <mergeCell ref="S6:S9"/>
-    <mergeCell ref="H10:H13"/>
-    <mergeCell ref="S10:S13"/>
-    <mergeCell ref="H14:H17"/>
-    <mergeCell ref="L14:L17"/>
-    <mergeCell ref="S14:S17"/>
-    <mergeCell ref="H18:H21"/>
-    <mergeCell ref="S18:S21"/>
-    <mergeCell ref="H22:H25"/>
-    <mergeCell ref="S22:S25"/>
-    <mergeCell ref="H26:H29"/>
-    <mergeCell ref="S26:S29"/>
-    <mergeCell ref="H30:H33"/>
-    <mergeCell ref="S30:S33"/>
-    <mergeCell ref="H34:H37"/>
-    <mergeCell ref="S34:S37"/>
-    <mergeCell ref="H38:H41"/>
-    <mergeCell ref="S38:S41"/>
-    <mergeCell ref="H42:H45"/>
-    <mergeCell ref="S42:S45"/>
-    <mergeCell ref="H46:H49"/>
-    <mergeCell ref="S46:S49"/>
-    <mergeCell ref="H50:H53"/>
-    <mergeCell ref="S50:S53"/>
-    <mergeCell ref="H54:H57"/>
-    <mergeCell ref="S54:S57"/>
-    <mergeCell ref="H58:H61"/>
-    <mergeCell ref="S58:S61"/>
-    <mergeCell ref="H62:H65"/>
-    <mergeCell ref="S62:S65"/>
-    <mergeCell ref="H66:H69"/>
-    <mergeCell ref="S66:S69"/>
-    <mergeCell ref="H82:H85"/>
-    <mergeCell ref="S82:S85"/>
-    <mergeCell ref="H86:H89"/>
-    <mergeCell ref="S86:S89"/>
-    <mergeCell ref="H70:H73"/>
-    <mergeCell ref="S70:S73"/>
-    <mergeCell ref="H74:H77"/>
-    <mergeCell ref="S74:S77"/>
-    <mergeCell ref="H78:H81"/>
-    <mergeCell ref="S78:S81"/>
+    <mergeCell ref="H130:H133"/>
+    <mergeCell ref="S130:S133"/>
+    <mergeCell ref="H134:H137"/>
+    <mergeCell ref="S134:S137"/>
+    <mergeCell ref="H138:H141"/>
+    <mergeCell ref="S138:S141"/>
+    <mergeCell ref="H142:H145"/>
+    <mergeCell ref="S142:S145"/>
+    <mergeCell ref="H146:H149"/>
+    <mergeCell ref="S146:S149"/>
+    <mergeCell ref="H150:H153"/>
+    <mergeCell ref="S150:S153"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Resultats_modeles_coleo_2024.xlsx
+++ b/Resultats_modeles_coleo_2024.xlsx
@@ -12018,53 +12018,18 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="H126:H129"/>
-    <mergeCell ref="S126:S129"/>
-    <mergeCell ref="T126:T129"/>
-    <mergeCell ref="H86:H89"/>
-    <mergeCell ref="S86:S89"/>
-    <mergeCell ref="H70:H73"/>
-    <mergeCell ref="S70:S73"/>
-    <mergeCell ref="H74:H77"/>
-    <mergeCell ref="S74:S77"/>
-    <mergeCell ref="H78:H81"/>
-    <mergeCell ref="S78:S81"/>
-    <mergeCell ref="H62:H65"/>
-    <mergeCell ref="S62:S65"/>
-    <mergeCell ref="H66:H69"/>
-    <mergeCell ref="S66:S69"/>
-    <mergeCell ref="H82:H85"/>
-    <mergeCell ref="S82:S85"/>
-    <mergeCell ref="H50:H53"/>
-    <mergeCell ref="S50:S53"/>
-    <mergeCell ref="H54:H57"/>
-    <mergeCell ref="S54:S57"/>
-    <mergeCell ref="H58:H61"/>
-    <mergeCell ref="S58:S61"/>
-    <mergeCell ref="H38:H41"/>
-    <mergeCell ref="S38:S41"/>
-    <mergeCell ref="H42:H45"/>
-    <mergeCell ref="S42:S45"/>
-    <mergeCell ref="H46:H49"/>
-    <mergeCell ref="S46:S49"/>
-    <mergeCell ref="S26:S29"/>
-    <mergeCell ref="H30:H33"/>
-    <mergeCell ref="S30:S33"/>
-    <mergeCell ref="H34:H37"/>
-    <mergeCell ref="S34:S37"/>
-    <mergeCell ref="H102:H105"/>
-    <mergeCell ref="S102:S105"/>
-    <mergeCell ref="H2:H5"/>
-    <mergeCell ref="S2:S5"/>
-    <mergeCell ref="H6:H9"/>
-    <mergeCell ref="S6:S9"/>
-    <mergeCell ref="H10:H13"/>
-    <mergeCell ref="S10:S13"/>
-    <mergeCell ref="H14:H17"/>
-    <mergeCell ref="L14:L17"/>
-    <mergeCell ref="S14:S17"/>
-    <mergeCell ref="H18:H21"/>
-    <mergeCell ref="S18:S21"/>
+    <mergeCell ref="H142:H145"/>
+    <mergeCell ref="S142:S145"/>
+    <mergeCell ref="H146:H149"/>
+    <mergeCell ref="S146:S149"/>
+    <mergeCell ref="H150:H153"/>
+    <mergeCell ref="S150:S153"/>
+    <mergeCell ref="H130:H133"/>
+    <mergeCell ref="S130:S133"/>
+    <mergeCell ref="H134:H137"/>
+    <mergeCell ref="S134:S137"/>
+    <mergeCell ref="H138:H141"/>
+    <mergeCell ref="S138:S141"/>
     <mergeCell ref="H22:H25"/>
     <mergeCell ref="S22:S25"/>
     <mergeCell ref="H26:H29"/>
@@ -12072,8 +12037,6 @@
     <mergeCell ref="S118:S121"/>
     <mergeCell ref="H90:H93"/>
     <mergeCell ref="S90:S93"/>
-    <mergeCell ref="H122:H125"/>
-    <mergeCell ref="S122:S125"/>
     <mergeCell ref="H106:H109"/>
     <mergeCell ref="S106:S109"/>
     <mergeCell ref="H110:H113"/>
@@ -12083,19 +12046,56 @@
     <mergeCell ref="H94:H97"/>
     <mergeCell ref="S94:S97"/>
     <mergeCell ref="H98:H101"/>
+    <mergeCell ref="H14:H17"/>
+    <mergeCell ref="L14:L17"/>
+    <mergeCell ref="S14:S17"/>
+    <mergeCell ref="H18:H21"/>
+    <mergeCell ref="S18:S21"/>
+    <mergeCell ref="H2:H5"/>
+    <mergeCell ref="S2:S5"/>
+    <mergeCell ref="H6:H9"/>
+    <mergeCell ref="S6:S9"/>
+    <mergeCell ref="H10:H13"/>
+    <mergeCell ref="S10:S13"/>
+    <mergeCell ref="S26:S29"/>
+    <mergeCell ref="H30:H33"/>
+    <mergeCell ref="S30:S33"/>
+    <mergeCell ref="H34:H37"/>
+    <mergeCell ref="S34:S37"/>
+    <mergeCell ref="H38:H41"/>
+    <mergeCell ref="S38:S41"/>
+    <mergeCell ref="H42:H45"/>
+    <mergeCell ref="S42:S45"/>
+    <mergeCell ref="H46:H49"/>
+    <mergeCell ref="S46:S49"/>
+    <mergeCell ref="H50:H53"/>
+    <mergeCell ref="S50:S53"/>
+    <mergeCell ref="H54:H57"/>
+    <mergeCell ref="S54:S57"/>
+    <mergeCell ref="H58:H61"/>
+    <mergeCell ref="S58:S61"/>
+    <mergeCell ref="H62:H65"/>
+    <mergeCell ref="S62:S65"/>
+    <mergeCell ref="H66:H69"/>
+    <mergeCell ref="S66:S69"/>
+    <mergeCell ref="H82:H85"/>
+    <mergeCell ref="S82:S85"/>
+    <mergeCell ref="H70:H73"/>
+    <mergeCell ref="S70:S73"/>
+    <mergeCell ref="H74:H77"/>
+    <mergeCell ref="S74:S77"/>
+    <mergeCell ref="H78:H81"/>
+    <mergeCell ref="S78:S81"/>
+    <mergeCell ref="H126:H129"/>
+    <mergeCell ref="S126:S129"/>
+    <mergeCell ref="T126:T129"/>
+    <mergeCell ref="H86:H89"/>
+    <mergeCell ref="S86:S89"/>
+    <mergeCell ref="H102:H105"/>
+    <mergeCell ref="S102:S105"/>
+    <mergeCell ref="H122:H125"/>
+    <mergeCell ref="S122:S125"/>
     <mergeCell ref="S98:S101"/>
-    <mergeCell ref="H130:H133"/>
-    <mergeCell ref="S130:S133"/>
-    <mergeCell ref="H134:H137"/>
-    <mergeCell ref="S134:S137"/>
-    <mergeCell ref="H138:H141"/>
-    <mergeCell ref="S138:S141"/>
-    <mergeCell ref="H142:H145"/>
-    <mergeCell ref="S142:S145"/>
-    <mergeCell ref="H146:H149"/>
-    <mergeCell ref="S146:S149"/>
-    <mergeCell ref="H150:H153"/>
-    <mergeCell ref="S150:S153"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Resultats_modeles_coleo_2024.xlsx
+++ b/Resultats_modeles_coleo_2024.xlsx
@@ -4208,6 +4208,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4216,9 +4219,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4640,7 +4640,7 @@
       <c r="G2" t="s">
         <v>154</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I2" t="s">
@@ -4697,7 +4697,7 @@
       <c r="Z2" t="s">
         <v>173</v>
       </c>
-      <c r="AA2" s="10" t="s">
+      <c r="AA2" s="11" t="s">
         <v>45</v>
       </c>
     </row>
@@ -4723,7 +4723,7 @@
       <c r="G3" t="s">
         <v>154</v>
       </c>
-      <c r="H3" s="11"/>
+      <c r="H3" s="12"/>
       <c r="I3" t="s">
         <v>150</v>
       </c>
@@ -4778,7 +4778,7 @@
       <c r="Z3" t="s">
         <v>173</v>
       </c>
-      <c r="AA3" s="10"/>
+      <c r="AA3" s="11"/>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -4802,7 +4802,7 @@
       <c r="G4" t="s">
         <v>154</v>
       </c>
-      <c r="H4" s="11"/>
+      <c r="H4" s="12"/>
       <c r="I4" t="s">
         <v>150</v>
       </c>
@@ -4857,7 +4857,7 @@
       <c r="Z4" t="s">
         <v>173</v>
       </c>
-      <c r="AA4" s="10"/>
+      <c r="AA4" s="11"/>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -4881,7 +4881,7 @@
       <c r="G5" t="s">
         <v>154</v>
       </c>
-      <c r="H5" s="11"/>
+      <c r="H5" s="12"/>
       <c r="I5" t="s">
         <v>150</v>
       </c>
@@ -4936,7 +4936,7 @@
       <c r="Z5" t="s">
         <v>173</v>
       </c>
-      <c r="AA5" s="10"/>
+      <c r="AA5" s="11"/>
     </row>
     <row r="6" spans="1:29" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -4960,7 +4960,7 @@
       <c r="G6" t="s">
         <v>184</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I6" t="s">
@@ -5017,10 +5017,10 @@
       <c r="Z6" t="s">
         <v>182</v>
       </c>
-      <c r="AA6" s="10" t="s">
+      <c r="AA6" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="AB6" s="10" t="s">
+      <c r="AB6" s="11" t="s">
         <v>174</v>
       </c>
     </row>
@@ -5046,7 +5046,7 @@
       <c r="G7" t="s">
         <v>184</v>
       </c>
-      <c r="H7" s="11"/>
+      <c r="H7" s="12"/>
       <c r="I7" t="s">
         <v>189</v>
       </c>
@@ -5101,8 +5101,8 @@
       <c r="Z7" t="s">
         <v>182</v>
       </c>
-      <c r="AA7" s="10"/>
-      <c r="AB7" s="10"/>
+      <c r="AA7" s="11"/>
+      <c r="AB7" s="11"/>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -5126,7 +5126,7 @@
       <c r="G8" t="s">
         <v>184</v>
       </c>
-      <c r="H8" s="11"/>
+      <c r="H8" s="12"/>
       <c r="I8" t="s">
         <v>189</v>
       </c>
@@ -5181,8 +5181,8 @@
       <c r="Z8" t="s">
         <v>182</v>
       </c>
-      <c r="AA8" s="10"/>
-      <c r="AB8" s="10"/>
+      <c r="AA8" s="11"/>
+      <c r="AB8" s="11"/>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -5206,7 +5206,7 @@
       <c r="G9" t="s">
         <v>184</v>
       </c>
-      <c r="H9" s="11"/>
+      <c r="H9" s="12"/>
       <c r="I9" t="s">
         <v>189</v>
       </c>
@@ -5261,8 +5261,8 @@
       <c r="Z9" t="s">
         <v>182</v>
       </c>
-      <c r="AA9" s="10"/>
-      <c r="AB9" s="10"/>
+      <c r="AA9" s="11"/>
+      <c r="AB9" s="11"/>
     </row>
     <row r="10" spans="1:29" ht="120" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -5286,7 +5286,7 @@
       <c r="G10" t="s">
         <v>194</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I10" t="s">
@@ -5343,10 +5343,10 @@
       <c r="Z10" t="s">
         <v>208</v>
       </c>
-      <c r="AA10" s="10" t="s">
+      <c r="AA10" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="AB10" s="10" t="s">
+      <c r="AB10" s="11" t="s">
         <v>209</v>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       <c r="G11" t="s">
         <v>194</v>
       </c>
-      <c r="H11" s="11"/>
+      <c r="H11" s="12"/>
       <c r="I11" t="s">
         <v>199</v>
       </c>
@@ -5427,8 +5427,8 @@
       <c r="Z11" t="s">
         <v>208</v>
       </c>
-      <c r="AA11" s="10"/>
-      <c r="AB11" s="10"/>
+      <c r="AA11" s="11"/>
+      <c r="AB11" s="11"/>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -5452,7 +5452,7 @@
       <c r="G12" t="s">
         <v>194</v>
       </c>
-      <c r="H12" s="11"/>
+      <c r="H12" s="12"/>
       <c r="I12" t="s">
         <v>199</v>
       </c>
@@ -5507,8 +5507,8 @@
       <c r="Z12" t="s">
         <v>208</v>
       </c>
-      <c r="AA12" s="10"/>
-      <c r="AB12" s="10"/>
+      <c r="AA12" s="11"/>
+      <c r="AB12" s="11"/>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -5532,7 +5532,7 @@
       <c r="G13" t="s">
         <v>194</v>
       </c>
-      <c r="H13" s="11"/>
+      <c r="H13" s="12"/>
       <c r="I13" t="s">
         <v>199</v>
       </c>
@@ -5587,8 +5587,8 @@
       <c r="Z13" t="s">
         <v>208</v>
       </c>
-      <c r="AA13" s="10"/>
-      <c r="AB13" s="10"/>
+      <c r="AA13" s="11"/>
+      <c r="AB13" s="11"/>
     </row>
     <row r="14" spans="1:29" ht="131.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -5612,7 +5612,7 @@
       <c r="G14" t="s">
         <v>211</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I14" t="s">
@@ -5624,7 +5624,7 @@
       <c r="K14" t="s">
         <v>20</v>
       </c>
-      <c r="L14" s="10" t="s">
+      <c r="L14" s="11" t="s">
         <v>44</v>
       </c>
       <c r="M14" t="s">
@@ -5669,7 +5669,7 @@
       <c r="Z14" t="s">
         <v>223</v>
       </c>
-      <c r="AA14" s="10" t="s">
+      <c r="AA14" s="11" t="s">
         <v>48</v>
       </c>
     </row>
@@ -5695,7 +5695,7 @@
       <c r="G15" t="s">
         <v>211</v>
       </c>
-      <c r="H15" s="11"/>
+      <c r="H15" s="12"/>
       <c r="I15" t="s">
         <v>213</v>
       </c>
@@ -5705,7 +5705,7 @@
       <c r="K15" t="s">
         <v>20</v>
       </c>
-      <c r="L15" s="10"/>
+      <c r="L15" s="11"/>
       <c r="M15" t="s">
         <v>15</v>
       </c>
@@ -5748,7 +5748,7 @@
       <c r="Z15" t="s">
         <v>223</v>
       </c>
-      <c r="AA15" s="10"/>
+      <c r="AA15" s="11"/>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -5772,7 +5772,7 @@
       <c r="G16" t="s">
         <v>211</v>
       </c>
-      <c r="H16" s="11"/>
+      <c r="H16" s="12"/>
       <c r="I16" t="s">
         <v>213</v>
       </c>
@@ -5782,7 +5782,7 @@
       <c r="K16" t="s">
         <v>20</v>
       </c>
-      <c r="L16" s="10"/>
+      <c r="L16" s="11"/>
       <c r="M16" t="s">
         <v>15</v>
       </c>
@@ -5825,7 +5825,7 @@
       <c r="Z16" t="s">
         <v>223</v>
       </c>
-      <c r="AA16" s="10"/>
+      <c r="AA16" s="11"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
@@ -5849,7 +5849,7 @@
       <c r="G17" t="s">
         <v>211</v>
       </c>
-      <c r="H17" s="11"/>
+      <c r="H17" s="12"/>
       <c r="I17" t="s">
         <v>213</v>
       </c>
@@ -5859,7 +5859,7 @@
       <c r="K17" t="s">
         <v>20</v>
       </c>
-      <c r="L17" s="10"/>
+      <c r="L17" s="11"/>
       <c r="M17" t="s">
         <v>15</v>
       </c>
@@ -5902,7 +5902,7 @@
       <c r="Z17" t="s">
         <v>223</v>
       </c>
-      <c r="AA17" s="10"/>
+      <c r="AA17" s="11"/>
     </row>
     <row r="18" spans="1:28" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -5926,7 +5926,7 @@
       <c r="G18" t="s">
         <v>225</v>
       </c>
-      <c r="H18" s="11" t="s">
+      <c r="H18" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I18" t="s">
@@ -5983,10 +5983,10 @@
       <c r="Z18" t="s">
         <v>240</v>
       </c>
-      <c r="AA18" s="10" t="s">
+      <c r="AA18" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="AB18" s="10" t="s">
+      <c r="AB18" s="11" t="s">
         <v>241</v>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       <c r="G19" t="s">
         <v>225</v>
       </c>
-      <c r="H19" s="11"/>
+      <c r="H19" s="12"/>
       <c r="I19" t="s">
         <v>230</v>
       </c>
@@ -6067,8 +6067,8 @@
       <c r="Z19" t="s">
         <v>240</v>
       </c>
-      <c r="AA19" s="10"/>
-      <c r="AB19" s="10"/>
+      <c r="AA19" s="11"/>
+      <c r="AB19" s="11"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
@@ -6092,7 +6092,7 @@
       <c r="G20" t="s">
         <v>225</v>
       </c>
-      <c r="H20" s="11"/>
+      <c r="H20" s="12"/>
       <c r="I20" t="s">
         <v>230</v>
       </c>
@@ -6147,8 +6147,8 @@
       <c r="Z20" t="s">
         <v>240</v>
       </c>
-      <c r="AA20" s="10"/>
-      <c r="AB20" s="10"/>
+      <c r="AA20" s="11"/>
+      <c r="AB20" s="11"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
@@ -6172,7 +6172,7 @@
       <c r="G21" t="s">
         <v>225</v>
       </c>
-      <c r="H21" s="11"/>
+      <c r="H21" s="12"/>
       <c r="I21" t="s">
         <v>230</v>
       </c>
@@ -6227,8 +6227,8 @@
       <c r="Z21" t="s">
         <v>240</v>
       </c>
-      <c r="AA21" s="10"/>
-      <c r="AB21" s="10"/>
+      <c r="AA21" s="11"/>
+      <c r="AB21" s="11"/>
     </row>
     <row r="22" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
@@ -6252,7 +6252,7 @@
       <c r="G22" t="s">
         <v>243</v>
       </c>
-      <c r="H22" s="11" t="s">
+      <c r="H22" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I22" t="s">
@@ -6297,7 +6297,7 @@
       <c r="Z22" t="s">
         <v>258</v>
       </c>
-      <c r="AA22" s="10" t="s">
+      <c r="AA22" s="11" t="s">
         <v>52</v>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       <c r="G23" t="s">
         <v>243</v>
       </c>
-      <c r="H23" s="11"/>
+      <c r="H23" s="12"/>
       <c r="I23" t="s">
         <v>249</v>
       </c>
@@ -6366,7 +6366,7 @@
       <c r="Z23" t="s">
         <v>258</v>
       </c>
-      <c r="AA23" s="10"/>
+      <c r="AA23" s="11"/>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
@@ -6390,7 +6390,7 @@
       <c r="G24" t="s">
         <v>243</v>
       </c>
-      <c r="H24" s="11"/>
+      <c r="H24" s="12"/>
       <c r="I24" t="s">
         <v>249</v>
       </c>
@@ -6433,7 +6433,7 @@
       <c r="Z24" t="s">
         <v>258</v>
       </c>
-      <c r="AA24" s="10"/>
+      <c r="AA24" s="11"/>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
@@ -6457,7 +6457,7 @@
       <c r="G25" t="s">
         <v>243</v>
       </c>
-      <c r="H25" s="11"/>
+      <c r="H25" s="12"/>
       <c r="I25" t="s">
         <v>249</v>
       </c>
@@ -6500,7 +6500,7 @@
       <c r="Z25" t="s">
         <v>258</v>
       </c>
-      <c r="AA25" s="10"/>
+      <c r="AA25" s="11"/>
     </row>
     <row r="26" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
@@ -6524,7 +6524,7 @@
       <c r="G26" t="s">
         <v>261</v>
       </c>
-      <c r="H26" s="11" t="s">
+      <c r="H26" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I26" t="s">
@@ -6581,10 +6581,10 @@
       <c r="Z26" t="s">
         <v>278</v>
       </c>
-      <c r="AA26" s="10" t="s">
+      <c r="AA26" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="AB26" s="10" t="s">
+      <c r="AB26" s="11" t="s">
         <v>279</v>
       </c>
     </row>
@@ -6610,7 +6610,7 @@
       <c r="G27" t="s">
         <v>261</v>
       </c>
-      <c r="H27" s="11"/>
+      <c r="H27" s="12"/>
       <c r="I27" t="s">
         <v>266</v>
       </c>
@@ -6665,8 +6665,8 @@
       <c r="Z27" t="s">
         <v>278</v>
       </c>
-      <c r="AA27" s="10"/>
-      <c r="AB27" s="10"/>
+      <c r="AA27" s="11"/>
+      <c r="AB27" s="11"/>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -6690,7 +6690,7 @@
       <c r="G28" t="s">
         <v>261</v>
       </c>
-      <c r="H28" s="11"/>
+      <c r="H28" s="12"/>
       <c r="I28" t="s">
         <v>266</v>
       </c>
@@ -6745,8 +6745,8 @@
       <c r="Z28" t="s">
         <v>278</v>
       </c>
-      <c r="AA28" s="10"/>
-      <c r="AB28" s="10"/>
+      <c r="AA28" s="11"/>
+      <c r="AB28" s="11"/>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -6770,7 +6770,7 @@
       <c r="G29" t="s">
         <v>261</v>
       </c>
-      <c r="H29" s="11"/>
+      <c r="H29" s="12"/>
       <c r="I29" t="s">
         <v>266</v>
       </c>
@@ -6825,8 +6825,8 @@
       <c r="Z29" t="s">
         <v>278</v>
       </c>
-      <c r="AA29" s="10"/>
-      <c r="AB29" s="10"/>
+      <c r="AA29" s="11"/>
+      <c r="AB29" s="11"/>
     </row>
     <row r="30" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
@@ -6850,7 +6850,7 @@
       <c r="G30" t="s">
         <v>282</v>
       </c>
-      <c r="H30" s="11" t="s">
+      <c r="H30" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I30" t="s">
@@ -6907,10 +6907,10 @@
       <c r="Z30" t="s">
         <v>298</v>
       </c>
-      <c r="AA30" s="10" t="s">
+      <c r="AA30" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="AB30" s="10" t="s">
+      <c r="AB30" s="11" t="s">
         <v>299</v>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       <c r="G31" t="s">
         <v>282</v>
       </c>
-      <c r="H31" s="11"/>
+      <c r="H31" s="12"/>
       <c r="I31" t="s">
         <v>287</v>
       </c>
@@ -6991,8 +6991,8 @@
       <c r="Z31" t="s">
         <v>298</v>
       </c>
-      <c r="AA31" s="10"/>
-      <c r="AB31" s="10"/>
+      <c r="AA31" s="11"/>
+      <c r="AB31" s="11"/>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
@@ -7016,7 +7016,7 @@
       <c r="G32" t="s">
         <v>282</v>
       </c>
-      <c r="H32" s="11"/>
+      <c r="H32" s="12"/>
       <c r="I32" t="s">
         <v>287</v>
       </c>
@@ -7071,8 +7071,8 @@
       <c r="Z32" t="s">
         <v>298</v>
       </c>
-      <c r="AA32" s="10"/>
-      <c r="AB32" s="10"/>
+      <c r="AA32" s="11"/>
+      <c r="AB32" s="11"/>
     </row>
     <row r="33" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
@@ -7096,7 +7096,7 @@
       <c r="G33" t="s">
         <v>282</v>
       </c>
-      <c r="H33" s="11"/>
+      <c r="H33" s="12"/>
       <c r="I33" t="s">
         <v>287</v>
       </c>
@@ -7151,8 +7151,8 @@
       <c r="Z33" t="s">
         <v>298</v>
       </c>
-      <c r="AA33" s="10"/>
-      <c r="AB33" s="10"/>
+      <c r="AA33" s="11"/>
+      <c r="AB33" s="11"/>
     </row>
     <row r="34" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
@@ -7176,7 +7176,7 @@
       <c r="G34" t="s">
         <v>302</v>
       </c>
-      <c r="H34" s="11" t="s">
+      <c r="H34" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I34" t="s">
@@ -7221,7 +7221,7 @@
       <c r="Z34" t="s">
         <v>316</v>
       </c>
-      <c r="AA34" s="10" t="s">
+      <c r="AA34" s="11" t="s">
         <v>308</v>
       </c>
     </row>
@@ -7247,7 +7247,7 @@
       <c r="G35" t="s">
         <v>302</v>
       </c>
-      <c r="H35" s="11"/>
+      <c r="H35" s="12"/>
       <c r="I35" t="s">
         <v>306</v>
       </c>
@@ -7290,7 +7290,7 @@
       <c r="Z35" t="s">
         <v>316</v>
       </c>
-      <c r="AA35" s="10"/>
+      <c r="AA35" s="11"/>
     </row>
     <row r="36" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
@@ -7314,7 +7314,7 @@
       <c r="G36" t="s">
         <v>302</v>
       </c>
-      <c r="H36" s="11"/>
+      <c r="H36" s="12"/>
       <c r="I36" t="s">
         <v>306</v>
       </c>
@@ -7357,7 +7357,7 @@
       <c r="Z36" t="s">
         <v>316</v>
       </c>
-      <c r="AA36" s="10"/>
+      <c r="AA36" s="11"/>
     </row>
     <row r="37" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
@@ -7381,7 +7381,7 @@
       <c r="G37" t="s">
         <v>302</v>
       </c>
-      <c r="H37" s="11"/>
+      <c r="H37" s="12"/>
       <c r="I37" t="s">
         <v>306</v>
       </c>
@@ -7424,7 +7424,7 @@
       <c r="Z37" t="s">
         <v>316</v>
       </c>
-      <c r="AA37" s="10"/>
+      <c r="AA37" s="11"/>
     </row>
     <row r="38" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
@@ -7448,7 +7448,7 @@
       <c r="G38" t="s">
         <v>320</v>
       </c>
-      <c r="H38" s="11" t="s">
+      <c r="H38" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I38" t="s">
@@ -7493,7 +7493,7 @@
       <c r="Z38" t="s">
         <v>332</v>
       </c>
-      <c r="AA38" s="10" t="s">
+      <c r="AA38" s="11" t="s">
         <v>317</v>
       </c>
     </row>
@@ -7519,7 +7519,7 @@
       <c r="G39" t="s">
         <v>320</v>
       </c>
-      <c r="H39" s="11"/>
+      <c r="H39" s="12"/>
       <c r="I39" t="s">
         <v>324</v>
       </c>
@@ -7562,7 +7562,7 @@
       <c r="Z39" t="s">
         <v>332</v>
       </c>
-      <c r="AA39" s="10"/>
+      <c r="AA39" s="11"/>
     </row>
     <row r="40" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
@@ -7586,7 +7586,7 @@
       <c r="G40" t="s">
         <v>320</v>
       </c>
-      <c r="H40" s="11"/>
+      <c r="H40" s="12"/>
       <c r="I40" t="s">
         <v>324</v>
       </c>
@@ -7629,7 +7629,7 @@
       <c r="Z40" t="s">
         <v>332</v>
       </c>
-      <c r="AA40" s="10"/>
+      <c r="AA40" s="11"/>
     </row>
     <row r="41" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
@@ -7653,7 +7653,7 @@
       <c r="G41" t="s">
         <v>320</v>
       </c>
-      <c r="H41" s="11"/>
+      <c r="H41" s="12"/>
       <c r="I41" t="s">
         <v>324</v>
       </c>
@@ -7696,7 +7696,7 @@
       <c r="Z41" t="s">
         <v>332</v>
       </c>
-      <c r="AA41" s="10"/>
+      <c r="AA41" s="11"/>
     </row>
     <row r="42" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
@@ -7720,7 +7720,7 @@
       <c r="G42" t="s">
         <v>334</v>
       </c>
-      <c r="H42" s="11" t="s">
+      <c r="H42" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I42" t="s">
@@ -7765,7 +7765,7 @@
       <c r="Z42" t="s">
         <v>348</v>
       </c>
-      <c r="AA42" s="10" t="s">
+      <c r="AA42" s="11" t="s">
         <v>340</v>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       <c r="G43" t="s">
         <v>334</v>
       </c>
-      <c r="H43" s="11"/>
+      <c r="H43" s="12"/>
       <c r="I43" t="s">
         <v>338</v>
       </c>
@@ -7834,7 +7834,7 @@
       <c r="Z43" t="s">
         <v>348</v>
       </c>
-      <c r="AA43" s="10"/>
+      <c r="AA43" s="11"/>
     </row>
     <row r="44" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
@@ -7858,7 +7858,7 @@
       <c r="G44" t="s">
         <v>334</v>
       </c>
-      <c r="H44" s="11"/>
+      <c r="H44" s="12"/>
       <c r="I44" t="s">
         <v>338</v>
       </c>
@@ -7901,7 +7901,7 @@
       <c r="Z44" t="s">
         <v>348</v>
       </c>
-      <c r="AA44" s="10"/>
+      <c r="AA44" s="11"/>
     </row>
     <row r="45" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
@@ -7925,7 +7925,7 @@
       <c r="G45" t="s">
         <v>334</v>
       </c>
-      <c r="H45" s="11"/>
+      <c r="H45" s="12"/>
       <c r="I45" t="s">
         <v>338</v>
       </c>
@@ -7968,7 +7968,7 @@
       <c r="Z45" t="s">
         <v>348</v>
       </c>
-      <c r="AA45" s="10"/>
+      <c r="AA45" s="11"/>
     </row>
     <row r="46" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
@@ -7992,7 +7992,7 @@
       <c r="G46" t="s">
         <v>350</v>
       </c>
-      <c r="H46" s="11" t="s">
+      <c r="H46" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I46" t="s">
@@ -8037,7 +8037,7 @@
       <c r="Z46" t="s">
         <v>364</v>
       </c>
-      <c r="AA46" s="10" t="s">
+      <c r="AA46" s="11" t="s">
         <v>357</v>
       </c>
     </row>
@@ -8063,7 +8063,7 @@
       <c r="G47" t="s">
         <v>350</v>
       </c>
-      <c r="H47" s="11"/>
+      <c r="H47" s="12"/>
       <c r="I47" t="s">
         <v>355</v>
       </c>
@@ -8106,7 +8106,7 @@
       <c r="Z47" t="s">
         <v>364</v>
       </c>
-      <c r="AA47" s="10"/>
+      <c r="AA47" s="11"/>
     </row>
     <row r="48" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
@@ -8130,7 +8130,7 @@
       <c r="G48" t="s">
         <v>350</v>
       </c>
-      <c r="H48" s="11"/>
+      <c r="H48" s="12"/>
       <c r="I48" t="s">
         <v>355</v>
       </c>
@@ -8173,7 +8173,7 @@
       <c r="Z48" t="s">
         <v>364</v>
       </c>
-      <c r="AA48" s="10"/>
+      <c r="AA48" s="11"/>
     </row>
     <row r="49" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
@@ -8197,7 +8197,7 @@
       <c r="G49" t="s">
         <v>350</v>
       </c>
-      <c r="H49" s="11"/>
+      <c r="H49" s="12"/>
       <c r="I49" t="s">
         <v>355</v>
       </c>
@@ -8240,7 +8240,7 @@
       <c r="Z49" t="s">
         <v>364</v>
       </c>
-      <c r="AA49" s="10"/>
+      <c r="AA49" s="11"/>
     </row>
     <row r="50" spans="1:28" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
@@ -8264,7 +8264,7 @@
       <c r="G50" t="s">
         <v>366</v>
       </c>
-      <c r="H50" s="11" t="s">
+      <c r="H50" s="12" t="s">
         <v>371</v>
       </c>
       <c r="I50" t="s">
@@ -8321,7 +8321,7 @@
       <c r="Z50" t="s">
         <v>384</v>
       </c>
-      <c r="AA50" s="10" t="s">
+      <c r="AA50" s="11" t="s">
         <v>377</v>
       </c>
     </row>
@@ -8347,7 +8347,7 @@
       <c r="G51" t="s">
         <v>366</v>
       </c>
-      <c r="H51" s="11"/>
+      <c r="H51" s="12"/>
       <c r="I51" t="s">
         <v>373</v>
       </c>
@@ -8402,7 +8402,7 @@
       <c r="Z51" t="s">
         <v>384</v>
       </c>
-      <c r="AA51" s="10"/>
+      <c r="AA51" s="11"/>
     </row>
     <row r="52" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
@@ -8426,7 +8426,7 @@
       <c r="G52" t="s">
         <v>366</v>
       </c>
-      <c r="H52" s="11"/>
+      <c r="H52" s="12"/>
       <c r="I52" t="s">
         <v>373</v>
       </c>
@@ -8481,7 +8481,7 @@
       <c r="Z52" t="s">
         <v>384</v>
       </c>
-      <c r="AA52" s="10"/>
+      <c r="AA52" s="11"/>
     </row>
     <row r="53" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
@@ -8505,7 +8505,7 @@
       <c r="G53" t="s">
         <v>366</v>
       </c>
-      <c r="H53" s="11"/>
+      <c r="H53" s="12"/>
       <c r="I53" t="s">
         <v>373</v>
       </c>
@@ -8560,7 +8560,7 @@
       <c r="Z53" t="s">
         <v>384</v>
       </c>
-      <c r="AA53" s="10"/>
+      <c r="AA53" s="11"/>
     </row>
     <row r="54" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
@@ -8584,7 +8584,7 @@
       <c r="G54" t="s">
         <v>387</v>
       </c>
-      <c r="H54" s="11" t="s">
+      <c r="H54" s="12" t="s">
         <v>68</v>
       </c>
       <c r="I54" t="s">
@@ -8629,10 +8629,10 @@
       <c r="Z54" t="s">
         <v>400</v>
       </c>
-      <c r="AA54" s="10" t="s">
+      <c r="AA54" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="AB54" s="10" t="s">
+      <c r="AB54" s="11" t="s">
         <v>401</v>
       </c>
     </row>
@@ -8658,7 +8658,7 @@
       <c r="G55" t="s">
         <v>387</v>
       </c>
-      <c r="H55" s="11"/>
+      <c r="H55" s="12"/>
       <c r="I55" t="s">
         <v>394</v>
       </c>
@@ -8701,8 +8701,8 @@
       <c r="Z55" t="s">
         <v>400</v>
       </c>
-      <c r="AA55" s="10"/>
-      <c r="AB55" s="10"/>
+      <c r="AA55" s="11"/>
+      <c r="AB55" s="11"/>
     </row>
     <row r="56" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
@@ -8726,7 +8726,7 @@
       <c r="G56" t="s">
         <v>387</v>
       </c>
-      <c r="H56" s="11"/>
+      <c r="H56" s="12"/>
       <c r="I56" t="s">
         <v>394</v>
       </c>
@@ -8769,8 +8769,8 @@
       <c r="Z56" t="s">
         <v>400</v>
       </c>
-      <c r="AA56" s="10"/>
-      <c r="AB56" s="10"/>
+      <c r="AA56" s="11"/>
+      <c r="AB56" s="11"/>
     </row>
     <row r="57" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
@@ -8794,7 +8794,7 @@
       <c r="G57" t="s">
         <v>387</v>
       </c>
-      <c r="H57" s="11"/>
+      <c r="H57" s="12"/>
       <c r="I57" t="s">
         <v>394</v>
       </c>
@@ -8837,8 +8837,8 @@
       <c r="Z57" t="s">
         <v>400</v>
       </c>
-      <c r="AA57" s="10"/>
-      <c r="AB57" s="10"/>
+      <c r="AA57" s="11"/>
+      <c r="AB57" s="11"/>
     </row>
     <row r="58" spans="1:28" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
@@ -8862,7 +8862,7 @@
       <c r="G58" t="s">
         <v>404</v>
       </c>
-      <c r="H58" s="11" t="s">
+      <c r="H58" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I58" t="s">
@@ -8919,7 +8919,7 @@
       <c r="Z58" t="s">
         <v>419</v>
       </c>
-      <c r="AA58" s="10" t="s">
+      <c r="AA58" s="11" t="s">
         <v>72</v>
       </c>
     </row>
@@ -8945,7 +8945,7 @@
       <c r="G59" t="s">
         <v>404</v>
       </c>
-      <c r="H59" s="11"/>
+      <c r="H59" s="12"/>
       <c r="I59" t="s">
         <v>409</v>
       </c>
@@ -9000,7 +9000,7 @@
       <c r="Z59" t="s">
         <v>419</v>
       </c>
-      <c r="AA59" s="10"/>
+      <c r="AA59" s="11"/>
     </row>
     <row r="60" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
@@ -9024,7 +9024,7 @@
       <c r="G60" t="s">
         <v>404</v>
       </c>
-      <c r="H60" s="11"/>
+      <c r="H60" s="12"/>
       <c r="I60" t="s">
         <v>409</v>
       </c>
@@ -9079,7 +9079,7 @@
       <c r="Z60" t="s">
         <v>419</v>
       </c>
-      <c r="AA60" s="10"/>
+      <c r="AA60" s="11"/>
     </row>
     <row r="61" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
@@ -9103,7 +9103,7 @@
       <c r="G61" t="s">
         <v>404</v>
       </c>
-      <c r="H61" s="11"/>
+      <c r="H61" s="12"/>
       <c r="I61" t="s">
         <v>409</v>
       </c>
@@ -9158,7 +9158,7 @@
       <c r="Z61" t="s">
         <v>419</v>
       </c>
-      <c r="AA61" s="10"/>
+      <c r="AA61" s="11"/>
     </row>
     <row r="62" spans="1:28" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
@@ -9182,7 +9182,7 @@
       <c r="G62" t="s">
         <v>75</v>
       </c>
-      <c r="H62" s="11" t="s">
+      <c r="H62" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I62" t="s">
@@ -9239,10 +9239,10 @@
       <c r="Z62" t="s">
         <v>428</v>
       </c>
-      <c r="AA62" s="10" t="s">
+      <c r="AA62" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="AB62" s="10" t="s">
+      <c r="AB62" s="11" t="s">
         <v>420</v>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       <c r="G63" t="s">
         <v>75</v>
       </c>
-      <c r="H63" s="11"/>
+      <c r="H63" s="12"/>
       <c r="I63" t="s">
         <v>80</v>
       </c>
@@ -9323,8 +9323,8 @@
       <c r="Z63" t="s">
         <v>428</v>
       </c>
-      <c r="AA63" s="10"/>
-      <c r="AB63" s="10"/>
+      <c r="AA63" s="11"/>
+      <c r="AB63" s="11"/>
     </row>
     <row r="64" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
@@ -9348,7 +9348,7 @@
       <c r="G64" t="s">
         <v>75</v>
       </c>
-      <c r="H64" s="11"/>
+      <c r="H64" s="12"/>
       <c r="I64" t="s">
         <v>80</v>
       </c>
@@ -9403,8 +9403,8 @@
       <c r="Z64" t="s">
         <v>428</v>
       </c>
-      <c r="AA64" s="10"/>
-      <c r="AB64" s="10"/>
+      <c r="AA64" s="11"/>
+      <c r="AB64" s="11"/>
     </row>
     <row r="65" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
@@ -9428,7 +9428,7 @@
       <c r="G65" t="s">
         <v>75</v>
       </c>
-      <c r="H65" s="11"/>
+      <c r="H65" s="12"/>
       <c r="I65" t="s">
         <v>80</v>
       </c>
@@ -9483,8 +9483,8 @@
       <c r="Z65" t="s">
         <v>428</v>
       </c>
-      <c r="AA65" s="10"/>
-      <c r="AB65" s="10"/>
+      <c r="AA65" s="11"/>
+      <c r="AB65" s="11"/>
     </row>
     <row r="66" spans="1:28" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
@@ -9508,7 +9508,7 @@
       <c r="G66" t="s">
         <v>430</v>
       </c>
-      <c r="H66" s="11" t="s">
+      <c r="H66" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I66" t="s">
@@ -9565,7 +9565,7 @@
       <c r="Z66" t="s">
         <v>444</v>
       </c>
-      <c r="AA66" s="10" t="s">
+      <c r="AA66" s="11" t="s">
         <v>436</v>
       </c>
     </row>
@@ -9591,7 +9591,7 @@
       <c r="G67" t="s">
         <v>430</v>
       </c>
-      <c r="H67" s="11"/>
+      <c r="H67" s="12"/>
       <c r="I67" t="s">
         <v>434</v>
       </c>
@@ -9646,7 +9646,7 @@
       <c r="Z67" t="s">
         <v>444</v>
       </c>
-      <c r="AA67" s="10"/>
+      <c r="AA67" s="11"/>
     </row>
     <row r="68" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
@@ -9670,7 +9670,7 @@
       <c r="G68" t="s">
         <v>430</v>
       </c>
-      <c r="H68" s="11"/>
+      <c r="H68" s="12"/>
       <c r="I68" t="s">
         <v>434</v>
       </c>
@@ -9725,7 +9725,7 @@
       <c r="Z68" t="s">
         <v>444</v>
       </c>
-      <c r="AA68" s="10"/>
+      <c r="AA68" s="11"/>
     </row>
     <row r="69" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
@@ -9749,7 +9749,7 @@
       <c r="G69" t="s">
         <v>430</v>
       </c>
-      <c r="H69" s="11"/>
+      <c r="H69" s="12"/>
       <c r="I69" t="s">
         <v>434</v>
       </c>
@@ -9804,7 +9804,7 @@
       <c r="Z69" t="s">
         <v>444</v>
       </c>
-      <c r="AA69" s="10"/>
+      <c r="AA69" s="11"/>
     </row>
     <row r="70" spans="1:28" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
@@ -9828,7 +9828,7 @@
       <c r="G70" t="s">
         <v>447</v>
       </c>
-      <c r="H70" s="11" t="s">
+      <c r="H70" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I70" t="s">
@@ -9885,7 +9885,7 @@
       <c r="Z70" t="s">
         <v>463</v>
       </c>
-      <c r="AA70" s="10" t="s">
+      <c r="AA70" s="11" t="s">
         <v>456</v>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       <c r="G71" t="s">
         <v>447</v>
       </c>
-      <c r="H71" s="11"/>
+      <c r="H71" s="12"/>
       <c r="I71" t="s">
         <v>452</v>
       </c>
@@ -9966,7 +9966,7 @@
       <c r="Z71" t="s">
         <v>463</v>
       </c>
-      <c r="AA71" s="10"/>
+      <c r="AA71" s="11"/>
     </row>
     <row r="72" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
@@ -9990,7 +9990,7 @@
       <c r="G72" t="s">
         <v>447</v>
       </c>
-      <c r="H72" s="11"/>
+      <c r="H72" s="12"/>
       <c r="I72" t="s">
         <v>452</v>
       </c>
@@ -10045,7 +10045,7 @@
       <c r="Z72" t="s">
         <v>463</v>
       </c>
-      <c r="AA72" s="10"/>
+      <c r="AA72" s="11"/>
     </row>
     <row r="73" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
@@ -10069,7 +10069,7 @@
       <c r="G73" t="s">
         <v>447</v>
       </c>
-      <c r="H73" s="11"/>
+      <c r="H73" s="12"/>
       <c r="I73" t="s">
         <v>452</v>
       </c>
@@ -10124,7 +10124,7 @@
       <c r="Z73" t="s">
         <v>463</v>
       </c>
-      <c r="AA73" s="10"/>
+      <c r="AA73" s="11"/>
     </row>
     <row r="74" spans="1:28" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
@@ -10148,7 +10148,7 @@
       <c r="G74" t="s">
         <v>465</v>
       </c>
-      <c r="H74" s="11" t="s">
+      <c r="H74" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I74" t="s">
@@ -10193,7 +10193,7 @@
       <c r="Z74" t="s">
         <v>479</v>
       </c>
-      <c r="AA74" s="10" t="s">
+      <c r="AA74" s="11" t="s">
         <v>472</v>
       </c>
     </row>
@@ -10219,7 +10219,7 @@
       <c r="G75" t="s">
         <v>465</v>
       </c>
-      <c r="H75" s="11"/>
+      <c r="H75" s="12"/>
       <c r="I75" t="s">
         <v>470</v>
       </c>
@@ -10262,7 +10262,7 @@
       <c r="Z75" t="s">
         <v>479</v>
       </c>
-      <c r="AA75" s="10"/>
+      <c r="AA75" s="11"/>
     </row>
     <row r="76" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
@@ -10286,7 +10286,7 @@
       <c r="G76" t="s">
         <v>465</v>
       </c>
-      <c r="H76" s="11"/>
+      <c r="H76" s="12"/>
       <c r="I76" t="s">
         <v>470</v>
       </c>
@@ -10329,7 +10329,7 @@
       <c r="Z76" t="s">
         <v>479</v>
       </c>
-      <c r="AA76" s="10"/>
+      <c r="AA76" s="11"/>
     </row>
     <row r="77" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
@@ -10353,7 +10353,7 @@
       <c r="G77" t="s">
         <v>465</v>
       </c>
-      <c r="H77" s="11"/>
+      <c r="H77" s="12"/>
       <c r="I77" t="s">
         <v>470</v>
       </c>
@@ -10396,7 +10396,7 @@
       <c r="Z77" t="s">
         <v>479</v>
       </c>
-      <c r="AA77" s="10"/>
+      <c r="AA77" s="11"/>
     </row>
     <row r="78" spans="1:28" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
@@ -10420,7 +10420,7 @@
       <c r="G78" t="s">
         <v>482</v>
       </c>
-      <c r="H78" s="11" t="s">
+      <c r="H78" s="12" t="s">
         <v>488</v>
       </c>
       <c r="I78" t="s">
@@ -10465,7 +10465,7 @@
       <c r="Z78" t="s">
         <v>498</v>
       </c>
-      <c r="AA78" s="10" t="s">
+      <c r="AA78" s="11" t="s">
         <v>480</v>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
       <c r="G79" t="s">
         <v>482</v>
       </c>
-      <c r="H79" s="11"/>
+      <c r="H79" s="12"/>
       <c r="I79" t="s">
         <v>489</v>
       </c>
@@ -10534,7 +10534,7 @@
       <c r="Z79" t="s">
         <v>498</v>
       </c>
-      <c r="AA79" s="10"/>
+      <c r="AA79" s="11"/>
     </row>
     <row r="80" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
@@ -10558,7 +10558,7 @@
       <c r="G80" t="s">
         <v>482</v>
       </c>
-      <c r="H80" s="11"/>
+      <c r="H80" s="12"/>
       <c r="I80" t="s">
         <v>489</v>
       </c>
@@ -10601,7 +10601,7 @@
       <c r="Z80" t="s">
         <v>498</v>
       </c>
-      <c r="AA80" s="10"/>
+      <c r="AA80" s="11"/>
     </row>
     <row r="81" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
@@ -10625,7 +10625,7 @@
       <c r="G81" t="s">
         <v>482</v>
       </c>
-      <c r="H81" s="11"/>
+      <c r="H81" s="12"/>
       <c r="I81" t="s">
         <v>489</v>
       </c>
@@ -10668,7 +10668,7 @@
       <c r="Z81" t="s">
         <v>498</v>
       </c>
-      <c r="AA81" s="10"/>
+      <c r="AA81" s="11"/>
     </row>
     <row r="82" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
@@ -10692,7 +10692,7 @@
       <c r="G82" t="s">
         <v>500</v>
       </c>
-      <c r="H82" s="11" t="s">
+      <c r="H82" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I82" t="s">
@@ -10737,7 +10737,7 @@
       <c r="Z82" t="s">
         <v>513</v>
       </c>
-      <c r="AA82" s="10" t="s">
+      <c r="AA82" s="11" t="s">
         <v>90</v>
       </c>
     </row>
@@ -10763,7 +10763,7 @@
       <c r="G83" t="s">
         <v>500</v>
       </c>
-      <c r="H83" s="11"/>
+      <c r="H83" s="12"/>
       <c r="I83" t="s">
         <v>505</v>
       </c>
@@ -10806,7 +10806,7 @@
       <c r="Z83" t="s">
         <v>513</v>
       </c>
-      <c r="AA83" s="10"/>
+      <c r="AA83" s="11"/>
     </row>
     <row r="84" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
@@ -10830,7 +10830,7 @@
       <c r="G84" t="s">
         <v>500</v>
       </c>
-      <c r="H84" s="11"/>
+      <c r="H84" s="12"/>
       <c r="I84" t="s">
         <v>505</v>
       </c>
@@ -10873,7 +10873,7 @@
       <c r="Z84" t="s">
         <v>513</v>
       </c>
-      <c r="AA84" s="10"/>
+      <c r="AA84" s="11"/>
     </row>
     <row r="85" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
@@ -10897,7 +10897,7 @@
       <c r="G85" t="s">
         <v>500</v>
       </c>
-      <c r="H85" s="11"/>
+      <c r="H85" s="12"/>
       <c r="I85" t="s">
         <v>505</v>
       </c>
@@ -10940,7 +10940,7 @@
       <c r="Z85" t="s">
         <v>513</v>
       </c>
-      <c r="AA85" s="10"/>
+      <c r="AA85" s="11"/>
     </row>
     <row r="86" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
@@ -10964,7 +10964,7 @@
       <c r="G86" t="s">
         <v>516</v>
       </c>
-      <c r="H86" s="11" t="s">
+      <c r="H86" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I86" t="s">
@@ -11009,7 +11009,7 @@
       <c r="Z86" t="s">
         <v>528</v>
       </c>
-      <c r="AA86" s="10" t="s">
+      <c r="AA86" s="11" t="s">
         <v>92</v>
       </c>
     </row>
@@ -11035,7 +11035,7 @@
       <c r="G87" t="s">
         <v>516</v>
       </c>
-      <c r="H87" s="11"/>
+      <c r="H87" s="12"/>
       <c r="I87" t="s">
         <v>520</v>
       </c>
@@ -11078,7 +11078,7 @@
       <c r="Z87" t="s">
         <v>528</v>
       </c>
-      <c r="AA87" s="10"/>
+      <c r="AA87" s="11"/>
     </row>
     <row r="88" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
@@ -11102,7 +11102,7 @@
       <c r="G88" t="s">
         <v>516</v>
       </c>
-      <c r="H88" s="11"/>
+      <c r="H88" s="12"/>
       <c r="I88" t="s">
         <v>520</v>
       </c>
@@ -11145,7 +11145,7 @@
       <c r="Z88" t="s">
         <v>528</v>
       </c>
-      <c r="AA88" s="10"/>
+      <c r="AA88" s="11"/>
     </row>
     <row r="89" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
@@ -11169,7 +11169,7 @@
       <c r="G89" t="s">
         <v>516</v>
       </c>
-      <c r="H89" s="11"/>
+      <c r="H89" s="12"/>
       <c r="I89" t="s">
         <v>520</v>
       </c>
@@ -11212,7 +11212,7 @@
       <c r="Z89" t="s">
         <v>528</v>
       </c>
-      <c r="AA89" s="10"/>
+      <c r="AA89" s="11"/>
     </row>
     <row r="90" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
@@ -11236,7 +11236,7 @@
       <c r="G90" t="s">
         <v>532</v>
       </c>
-      <c r="H90" s="11" t="s">
+      <c r="H90" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I90" t="s">
@@ -11248,7 +11248,7 @@
       <c r="K90" t="s">
         <v>20</v>
       </c>
-      <c r="L90" s="10" t="s">
+      <c r="L90" s="11" t="s">
         <v>538</v>
       </c>
       <c r="M90" t="s">
@@ -11293,7 +11293,7 @@
       <c r="Z90" t="s">
         <v>548</v>
       </c>
-      <c r="AA90" s="10" t="s">
+      <c r="AA90" s="11" t="s">
         <v>114</v>
       </c>
       <c r="AB90" s="5"/>
@@ -11320,7 +11320,7 @@
       <c r="G91" t="s">
         <v>532</v>
       </c>
-      <c r="H91" s="11"/>
+      <c r="H91" s="12"/>
       <c r="I91" t="s">
         <v>536</v>
       </c>
@@ -11330,7 +11330,7 @@
       <c r="K91" t="s">
         <v>20</v>
       </c>
-      <c r="L91" s="10"/>
+      <c r="L91" s="11"/>
       <c r="M91" t="s">
         <v>16</v>
       </c>
@@ -11373,7 +11373,7 @@
       <c r="Z91" t="s">
         <v>548</v>
       </c>
-      <c r="AA91" s="10"/>
+      <c r="AA91" s="11"/>
       <c r="AB91" s="5"/>
     </row>
     <row r="92" spans="1:28" x14ac:dyDescent="0.3">
@@ -11398,7 +11398,7 @@
       <c r="G92" t="s">
         <v>532</v>
       </c>
-      <c r="H92" s="11"/>
+      <c r="H92" s="12"/>
       <c r="I92" t="s">
         <v>536</v>
       </c>
@@ -11408,7 +11408,7 @@
       <c r="K92" t="s">
         <v>20</v>
       </c>
-      <c r="L92" s="10"/>
+      <c r="L92" s="11"/>
       <c r="M92" t="s">
         <v>16</v>
       </c>
@@ -11451,7 +11451,7 @@
       <c r="Z92" t="s">
         <v>548</v>
       </c>
-      <c r="AA92" s="10"/>
+      <c r="AA92" s="11"/>
       <c r="AB92" s="5"/>
     </row>
     <row r="93" spans="1:28" x14ac:dyDescent="0.3">
@@ -11476,7 +11476,7 @@
       <c r="G93" t="s">
         <v>532</v>
       </c>
-      <c r="H93" s="11"/>
+      <c r="H93" s="12"/>
       <c r="I93" t="s">
         <v>536</v>
       </c>
@@ -11486,7 +11486,7 @@
       <c r="K93" t="s">
         <v>20</v>
       </c>
-      <c r="L93" s="10"/>
+      <c r="L93" s="11"/>
       <c r="M93" t="s">
         <v>16</v>
       </c>
@@ -11529,7 +11529,7 @@
       <c r="Z93" t="s">
         <v>548</v>
       </c>
-      <c r="AA93" s="10"/>
+      <c r="AA93" s="11"/>
       <c r="AB93" s="5"/>
     </row>
     <row r="94" spans="1:28" ht="144" customHeight="1" x14ac:dyDescent="0.3">
@@ -11554,7 +11554,7 @@
       <c r="G94" t="s">
         <v>554</v>
       </c>
-      <c r="H94" s="11" t="s">
+      <c r="H94" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I94" t="s">
@@ -11611,7 +11611,7 @@
       <c r="Z94" t="s">
         <v>563</v>
       </c>
-      <c r="AA94" s="10" t="s">
+      <c r="AA94" s="11" t="s">
         <v>96</v>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       <c r="G95" t="s">
         <v>554</v>
       </c>
-      <c r="H95" s="11"/>
+      <c r="H95" s="12"/>
       <c r="I95" t="s">
         <v>555</v>
       </c>
@@ -11692,7 +11692,7 @@
       <c r="Z95" t="s">
         <v>563</v>
       </c>
-      <c r="AA95" s="10"/>
+      <c r="AA95" s="11"/>
     </row>
     <row r="96" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
@@ -11716,7 +11716,7 @@
       <c r="G96" t="s">
         <v>554</v>
       </c>
-      <c r="H96" s="11"/>
+      <c r="H96" s="12"/>
       <c r="I96" t="s">
         <v>555</v>
       </c>
@@ -11771,7 +11771,7 @@
       <c r="Z96" t="s">
         <v>563</v>
       </c>
-      <c r="AA96" s="10"/>
+      <c r="AA96" s="11"/>
     </row>
     <row r="97" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
@@ -11795,7 +11795,7 @@
       <c r="G97" t="s">
         <v>554</v>
       </c>
-      <c r="H97" s="11"/>
+      <c r="H97" s="12"/>
       <c r="I97" t="s">
         <v>555</v>
       </c>
@@ -11850,7 +11850,7 @@
       <c r="Z97" t="s">
         <v>563</v>
       </c>
-      <c r="AA97" s="10"/>
+      <c r="AA97" s="11"/>
     </row>
     <row r="98" spans="1:27" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
@@ -11874,7 +11874,7 @@
       <c r="G98" t="s">
         <v>570</v>
       </c>
-      <c r="H98" s="11" t="s">
+      <c r="H98" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I98" t="s">
@@ -11931,7 +11931,7 @@
       <c r="Z98" t="s">
         <v>582</v>
       </c>
-      <c r="AA98" s="10" t="s">
+      <c r="AA98" s="11" t="s">
         <v>574</v>
       </c>
     </row>
@@ -11957,7 +11957,7 @@
       <c r="G99" t="s">
         <v>570</v>
       </c>
-      <c r="H99" s="11"/>
+      <c r="H99" s="12"/>
       <c r="I99" t="s">
         <v>571</v>
       </c>
@@ -12012,7 +12012,7 @@
       <c r="Z99" t="s">
         <v>582</v>
       </c>
-      <c r="AA99" s="10"/>
+      <c r="AA99" s="11"/>
     </row>
     <row r="100" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
@@ -12036,7 +12036,7 @@
       <c r="G100" t="s">
         <v>570</v>
       </c>
-      <c r="H100" s="11"/>
+      <c r="H100" s="12"/>
       <c r="I100" t="s">
         <v>571</v>
       </c>
@@ -12091,7 +12091,7 @@
       <c r="Z100" t="s">
         <v>582</v>
       </c>
-      <c r="AA100" s="10"/>
+      <c r="AA100" s="11"/>
     </row>
     <row r="101" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
@@ -12115,7 +12115,7 @@
       <c r="G101" t="s">
         <v>570</v>
       </c>
-      <c r="H101" s="11"/>
+      <c r="H101" s="12"/>
       <c r="I101" t="s">
         <v>571</v>
       </c>
@@ -12170,7 +12170,7 @@
       <c r="Z101" t="s">
         <v>582</v>
       </c>
-      <c r="AA101" s="10"/>
+      <c r="AA101" s="11"/>
     </row>
     <row r="102" spans="1:27" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
@@ -12194,7 +12194,7 @@
       <c r="G102" t="s">
         <v>589</v>
       </c>
-      <c r="H102" s="11" t="s">
+      <c r="H102" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I102" t="s">
@@ -12251,7 +12251,7 @@
       <c r="Z102" t="s">
         <v>598</v>
       </c>
-      <c r="AA102" s="10" t="s">
+      <c r="AA102" s="11" t="s">
         <v>100</v>
       </c>
     </row>
@@ -12277,7 +12277,7 @@
       <c r="G103" t="s">
         <v>589</v>
       </c>
-      <c r="H103" s="11"/>
+      <c r="H103" s="12"/>
       <c r="I103" t="s">
         <v>585</v>
       </c>
@@ -12332,7 +12332,7 @@
       <c r="Z103" t="s">
         <v>598</v>
       </c>
-      <c r="AA103" s="10"/>
+      <c r="AA103" s="11"/>
     </row>
     <row r="104" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
@@ -12356,7 +12356,7 @@
       <c r="G104" t="s">
         <v>589</v>
       </c>
-      <c r="H104" s="11"/>
+      <c r="H104" s="12"/>
       <c r="I104" t="s">
         <v>585</v>
       </c>
@@ -12411,7 +12411,7 @@
       <c r="Z104" t="s">
         <v>598</v>
       </c>
-      <c r="AA104" s="10"/>
+      <c r="AA104" s="11"/>
     </row>
     <row r="105" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
@@ -12435,7 +12435,7 @@
       <c r="G105" t="s">
         <v>589</v>
       </c>
-      <c r="H105" s="11"/>
+      <c r="H105" s="12"/>
       <c r="I105" t="s">
         <v>585</v>
       </c>
@@ -12490,7 +12490,7 @@
       <c r="Z105" t="s">
         <v>598</v>
       </c>
-      <c r="AA105" s="10"/>
+      <c r="AA105" s="11"/>
     </row>
     <row r="106" spans="1:27" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
@@ -12514,7 +12514,7 @@
       <c r="G106" t="s">
         <v>601</v>
       </c>
-      <c r="H106" s="11" t="s">
+      <c r="H106" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I106" t="s">
@@ -12571,7 +12571,7 @@
       <c r="Z106" t="s">
         <v>611</v>
       </c>
-      <c r="AA106" s="10" t="s">
+      <c r="AA106" s="11" t="s">
         <v>107</v>
       </c>
     </row>
@@ -12597,7 +12597,7 @@
       <c r="G107" t="s">
         <v>601</v>
       </c>
-      <c r="H107" s="11"/>
+      <c r="H107" s="12"/>
       <c r="I107" t="s">
         <v>602</v>
       </c>
@@ -12652,7 +12652,7 @@
       <c r="Z107" t="s">
         <v>611</v>
       </c>
-      <c r="AA107" s="10"/>
+      <c r="AA107" s="11"/>
     </row>
     <row r="108" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
@@ -12676,7 +12676,7 @@
       <c r="G108" t="s">
         <v>601</v>
       </c>
-      <c r="H108" s="11"/>
+      <c r="H108" s="12"/>
       <c r="I108" t="s">
         <v>602</v>
       </c>
@@ -12731,7 +12731,7 @@
       <c r="Z108" t="s">
         <v>611</v>
       </c>
-      <c r="AA108" s="10"/>
+      <c r="AA108" s="11"/>
     </row>
     <row r="109" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
@@ -12755,7 +12755,7 @@
       <c r="G109" t="s">
         <v>601</v>
       </c>
-      <c r="H109" s="11"/>
+      <c r="H109" s="12"/>
       <c r="I109" t="s">
         <v>602</v>
       </c>
@@ -12810,7 +12810,7 @@
       <c r="Z109" t="s">
         <v>611</v>
       </c>
-      <c r="AA109" s="10"/>
+      <c r="AA109" s="11"/>
     </row>
     <row r="110" spans="1:27" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
@@ -12834,7 +12834,7 @@
       <c r="G110" t="s">
         <v>614</v>
       </c>
-      <c r="H110" s="11" t="s">
+      <c r="H110" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I110" t="s">
@@ -12891,7 +12891,7 @@
       <c r="Z110" t="s">
         <v>629</v>
       </c>
-      <c r="AA110" s="10" t="s">
+      <c r="AA110" s="11" t="s">
         <v>623</v>
       </c>
     </row>
@@ -12917,7 +12917,7 @@
       <c r="G111" t="s">
         <v>614</v>
       </c>
-      <c r="H111" s="11"/>
+      <c r="H111" s="12"/>
       <c r="I111" t="s">
         <v>619</v>
       </c>
@@ -12972,7 +12972,7 @@
       <c r="Z111" t="s">
         <v>629</v>
       </c>
-      <c r="AA111" s="10"/>
+      <c r="AA111" s="11"/>
     </row>
     <row r="112" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
@@ -12996,7 +12996,7 @@
       <c r="G112" t="s">
         <v>614</v>
       </c>
-      <c r="H112" s="11"/>
+      <c r="H112" s="12"/>
       <c r="I112" t="s">
         <v>619</v>
       </c>
@@ -13051,7 +13051,7 @@
       <c r="Z112" t="s">
         <v>629</v>
       </c>
-      <c r="AA112" s="10"/>
+      <c r="AA112" s="11"/>
     </row>
     <row r="113" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
@@ -13075,7 +13075,7 @@
       <c r="G113" t="s">
         <v>614</v>
       </c>
-      <c r="H113" s="11"/>
+      <c r="H113" s="12"/>
       <c r="I113" t="s">
         <v>619</v>
       </c>
@@ -13130,7 +13130,7 @@
       <c r="Z113" t="s">
         <v>629</v>
       </c>
-      <c r="AA113" s="10"/>
+      <c r="AA113" s="11"/>
     </row>
     <row r="114" spans="1:28" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
@@ -13154,7 +13154,7 @@
       <c r="G114" t="s">
         <v>631</v>
       </c>
-      <c r="H114" s="11" t="s">
+      <c r="H114" s="12" t="s">
         <v>637</v>
       </c>
       <c r="I114" t="s">
@@ -13199,7 +13199,7 @@
       <c r="Z114" t="s">
         <v>647</v>
       </c>
-      <c r="AA114" s="10" t="s">
+      <c r="AA114" s="11" t="s">
         <v>648</v>
       </c>
     </row>
@@ -13225,7 +13225,7 @@
       <c r="G115" t="s">
         <v>631</v>
       </c>
-      <c r="H115" s="11"/>
+      <c r="H115" s="12"/>
       <c r="I115" t="s">
         <v>638</v>
       </c>
@@ -13268,7 +13268,7 @@
       <c r="Z115" t="s">
         <v>647</v>
       </c>
-      <c r="AA115" s="10"/>
+      <c r="AA115" s="11"/>
     </row>
     <row r="116" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
@@ -13292,7 +13292,7 @@
       <c r="G116" t="s">
         <v>631</v>
       </c>
-      <c r="H116" s="11"/>
+      <c r="H116" s="12"/>
       <c r="I116" t="s">
         <v>638</v>
       </c>
@@ -13335,7 +13335,7 @@
       <c r="Z116" t="s">
         <v>647</v>
       </c>
-      <c r="AA116" s="10"/>
+      <c r="AA116" s="11"/>
     </row>
     <row r="117" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
@@ -13359,7 +13359,7 @@
       <c r="G117" t="s">
         <v>631</v>
       </c>
-      <c r="H117" s="11"/>
+      <c r="H117" s="12"/>
       <c r="I117" t="s">
         <v>638</v>
       </c>
@@ -13402,7 +13402,7 @@
       <c r="Z117" t="s">
         <v>647</v>
       </c>
-      <c r="AA117" s="10"/>
+      <c r="AA117" s="11"/>
     </row>
     <row r="118" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
@@ -13426,7 +13426,7 @@
       <c r="G118" t="s">
         <v>651</v>
       </c>
-      <c r="H118" s="11" t="s">
+      <c r="H118" s="12" t="s">
         <v>659</v>
       </c>
       <c r="I118" t="s">
@@ -13471,7 +13471,7 @@
       <c r="Z118" t="s">
         <v>664</v>
       </c>
-      <c r="AA118" s="10" t="s">
+      <c r="AA118" s="11" t="s">
         <v>111</v>
       </c>
     </row>
@@ -13497,7 +13497,7 @@
       <c r="G119" t="s">
         <v>651</v>
       </c>
-      <c r="H119" s="11"/>
+      <c r="H119" s="12"/>
       <c r="I119" t="s">
         <v>657</v>
       </c>
@@ -13540,7 +13540,7 @@
       <c r="Z119" t="s">
         <v>664</v>
       </c>
-      <c r="AA119" s="10"/>
+      <c r="AA119" s="11"/>
     </row>
     <row r="120" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
@@ -13564,7 +13564,7 @@
       <c r="G120" t="s">
         <v>651</v>
       </c>
-      <c r="H120" s="11"/>
+      <c r="H120" s="12"/>
       <c r="I120" t="s">
         <v>657</v>
       </c>
@@ -13607,7 +13607,7 @@
       <c r="Z120" t="s">
         <v>664</v>
       </c>
-      <c r="AA120" s="10"/>
+      <c r="AA120" s="11"/>
     </row>
     <row r="121" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
@@ -13631,7 +13631,7 @@
       <c r="G121" t="s">
         <v>651</v>
       </c>
-      <c r="H121" s="11"/>
+      <c r="H121" s="12"/>
       <c r="I121" t="s">
         <v>657</v>
       </c>
@@ -13674,7 +13674,7 @@
       <c r="Z121" t="s">
         <v>664</v>
       </c>
-      <c r="AA121" s="10"/>
+      <c r="AA121" s="11"/>
     </row>
     <row r="122" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
@@ -13698,7 +13698,7 @@
       <c r="G122" t="s">
         <v>668</v>
       </c>
-      <c r="H122" s="11" t="s">
+      <c r="H122" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I122" t="s">
@@ -13743,7 +13743,7 @@
       <c r="Z122" t="s">
         <v>680</v>
       </c>
-      <c r="AA122" s="10" t="s">
+      <c r="AA122" s="11" t="s">
         <v>117</v>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       <c r="G123" t="s">
         <v>668</v>
       </c>
-      <c r="H123" s="11"/>
+      <c r="H123" s="12"/>
       <c r="I123" t="s">
         <v>667</v>
       </c>
@@ -13812,7 +13812,7 @@
       <c r="Z123" t="s">
         <v>680</v>
       </c>
-      <c r="AA123" s="10"/>
+      <c r="AA123" s="11"/>
     </row>
     <row r="124" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
@@ -13836,7 +13836,7 @@
       <c r="G124" t="s">
         <v>668</v>
       </c>
-      <c r="H124" s="11"/>
+      <c r="H124" s="12"/>
       <c r="I124" t="s">
         <v>667</v>
       </c>
@@ -13879,7 +13879,7 @@
       <c r="Z124" t="s">
         <v>680</v>
       </c>
-      <c r="AA124" s="10"/>
+      <c r="AA124" s="11"/>
     </row>
     <row r="125" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
@@ -13903,7 +13903,7 @@
       <c r="G125" t="s">
         <v>668</v>
       </c>
-      <c r="H125" s="11"/>
+      <c r="H125" s="12"/>
       <c r="I125" t="s">
         <v>667</v>
       </c>
@@ -13946,7 +13946,7 @@
       <c r="Z125" t="s">
         <v>680</v>
       </c>
-      <c r="AA125" s="10"/>
+      <c r="AA125" s="11"/>
     </row>
     <row r="126" spans="1:28" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
@@ -13970,7 +13970,7 @@
       <c r="G126" t="s">
         <v>685</v>
       </c>
-      <c r="H126" s="11" t="s">
+      <c r="H126" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I126" t="s">
@@ -14027,10 +14027,10 @@
       <c r="Z126" t="s">
         <v>699</v>
       </c>
-      <c r="AA126" s="10" t="s">
+      <c r="AA126" s="11" t="s">
         <v>683</v>
       </c>
-      <c r="AB126" s="12" t="s">
+      <c r="AB126" s="13" t="s">
         <v>146</v>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
       <c r="G127" t="s">
         <v>685</v>
       </c>
-      <c r="H127" s="11"/>
+      <c r="H127" s="12"/>
       <c r="I127" t="s">
         <v>690</v>
       </c>
@@ -14111,8 +14111,8 @@
       <c r="Z127" t="s">
         <v>699</v>
       </c>
-      <c r="AA127" s="10"/>
-      <c r="AB127" s="12"/>
+      <c r="AA127" s="11"/>
+      <c r="AB127" s="13"/>
     </row>
     <row r="128" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
@@ -14136,7 +14136,7 @@
       <c r="G128" t="s">
         <v>685</v>
       </c>
-      <c r="H128" s="11"/>
+      <c r="H128" s="12"/>
       <c r="I128" t="s">
         <v>690</v>
       </c>
@@ -14191,8 +14191,8 @@
       <c r="Z128" t="s">
         <v>699</v>
       </c>
-      <c r="AA128" s="10"/>
-      <c r="AB128" s="12"/>
+      <c r="AA128" s="11"/>
+      <c r="AB128" s="13"/>
     </row>
     <row r="129" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
@@ -14216,7 +14216,7 @@
       <c r="G129" t="s">
         <v>685</v>
       </c>
-      <c r="H129" s="11"/>
+      <c r="H129" s="12"/>
       <c r="I129" t="s">
         <v>690</v>
       </c>
@@ -14271,8 +14271,8 @@
       <c r="Z129" t="s">
         <v>699</v>
       </c>
-      <c r="AA129" s="10"/>
-      <c r="AB129" s="12"/>
+      <c r="AA129" s="11"/>
+      <c r="AB129" s="13"/>
     </row>
     <row r="130" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
@@ -14296,7 +14296,7 @@
       <c r="G130" t="s">
         <v>123</v>
       </c>
-      <c r="H130" s="11" t="s">
+      <c r="H130" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I130" t="s">
@@ -14353,10 +14353,10 @@
       <c r="Z130" t="s">
         <v>708</v>
       </c>
-      <c r="AA130" s="10" t="s">
+      <c r="AA130" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="AB130" s="13" t="s">
+      <c r="AB130" s="10" t="s">
         <v>700</v>
       </c>
     </row>
@@ -14382,7 +14382,7 @@
       <c r="G131" t="s">
         <v>123</v>
       </c>
-      <c r="H131" s="11"/>
+      <c r="H131" s="12"/>
       <c r="I131" t="s">
         <v>128</v>
       </c>
@@ -14437,8 +14437,8 @@
       <c r="Z131" t="s">
         <v>708</v>
       </c>
-      <c r="AA131" s="10"/>
-      <c r="AB131" s="13"/>
+      <c r="AA131" s="11"/>
+      <c r="AB131" s="10"/>
     </row>
     <row r="132" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
@@ -14462,7 +14462,7 @@
       <c r="G132" t="s">
         <v>123</v>
       </c>
-      <c r="H132" s="11"/>
+      <c r="H132" s="12"/>
       <c r="I132" t="s">
         <v>128</v>
       </c>
@@ -14517,8 +14517,8 @@
       <c r="Z132" t="s">
         <v>708</v>
       </c>
-      <c r="AA132" s="10"/>
-      <c r="AB132" s="13"/>
+      <c r="AA132" s="11"/>
+      <c r="AB132" s="10"/>
     </row>
     <row r="133" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
@@ -14542,7 +14542,7 @@
       <c r="G133" t="s">
         <v>123</v>
       </c>
-      <c r="H133" s="11"/>
+      <c r="H133" s="12"/>
       <c r="I133" t="s">
         <v>128</v>
       </c>
@@ -14597,8 +14597,8 @@
       <c r="Z133" t="s">
         <v>708</v>
       </c>
-      <c r="AA133" s="10"/>
-      <c r="AB133" s="13"/>
+      <c r="AA133" s="11"/>
+      <c r="AB133" s="10"/>
     </row>
     <row r="134" spans="1:28" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
@@ -14622,7 +14622,7 @@
       <c r="G134" t="s">
         <v>711</v>
       </c>
-      <c r="H134" s="11" t="s">
+      <c r="H134" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I134" t="s">
@@ -14679,7 +14679,7 @@
       <c r="Z134" t="s">
         <v>721</v>
       </c>
-      <c r="AA134" s="10" t="s">
+      <c r="AA134" s="11" t="s">
         <v>136</v>
       </c>
     </row>
@@ -14705,7 +14705,7 @@
       <c r="G135" t="s">
         <v>711</v>
       </c>
-      <c r="H135" s="11"/>
+      <c r="H135" s="12"/>
       <c r="I135" t="s">
         <v>713</v>
       </c>
@@ -14760,7 +14760,7 @@
       <c r="Z135" t="s">
         <v>721</v>
       </c>
-      <c r="AA135" s="10"/>
+      <c r="AA135" s="11"/>
     </row>
     <row r="136" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
@@ -14784,7 +14784,7 @@
       <c r="G136" t="s">
         <v>711</v>
       </c>
-      <c r="H136" s="11"/>
+      <c r="H136" s="12"/>
       <c r="I136" t="s">
         <v>713</v>
       </c>
@@ -14839,7 +14839,7 @@
       <c r="Z136" t="s">
         <v>721</v>
       </c>
-      <c r="AA136" s="10"/>
+      <c r="AA136" s="11"/>
     </row>
     <row r="137" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
@@ -14863,7 +14863,7 @@
       <c r="G137" t="s">
         <v>711</v>
       </c>
-      <c r="H137" s="11"/>
+      <c r="H137" s="12"/>
       <c r="I137" t="s">
         <v>713</v>
       </c>
@@ -14918,7 +14918,7 @@
       <c r="Z137" t="s">
         <v>721</v>
       </c>
-      <c r="AA137" s="10"/>
+      <c r="AA137" s="11"/>
     </row>
     <row r="138" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
@@ -14942,7 +14942,7 @@
       <c r="G138" t="s">
         <v>724</v>
       </c>
-      <c r="H138" s="11" t="s">
+      <c r="H138" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I138" t="s">
@@ -14987,7 +14987,7 @@
       <c r="Z138" t="s">
         <v>738</v>
       </c>
-      <c r="AA138" s="10" t="s">
+      <c r="AA138" s="11" t="s">
         <v>138</v>
       </c>
     </row>
@@ -15013,7 +15013,7 @@
       <c r="G139" t="s">
         <v>724</v>
       </c>
-      <c r="H139" s="11"/>
+      <c r="H139" s="12"/>
       <c r="I139" t="s">
         <v>730</v>
       </c>
@@ -15056,7 +15056,7 @@
       <c r="Z139" t="s">
         <v>738</v>
       </c>
-      <c r="AA139" s="10"/>
+      <c r="AA139" s="11"/>
     </row>
     <row r="140" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
@@ -15080,7 +15080,7 @@
       <c r="G140" t="s">
         <v>724</v>
       </c>
-      <c r="H140" s="11"/>
+      <c r="H140" s="12"/>
       <c r="I140" t="s">
         <v>730</v>
       </c>
@@ -15123,7 +15123,7 @@
       <c r="Z140" t="s">
         <v>738</v>
       </c>
-      <c r="AA140" s="10"/>
+      <c r="AA140" s="11"/>
     </row>
     <row r="141" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
@@ -15147,7 +15147,7 @@
       <c r="G141" t="s">
         <v>724</v>
       </c>
-      <c r="H141" s="11"/>
+      <c r="H141" s="12"/>
       <c r="I141" t="s">
         <v>730</v>
       </c>
@@ -15190,7 +15190,7 @@
       <c r="Z141" t="s">
         <v>738</v>
       </c>
-      <c r="AA141" s="10"/>
+      <c r="AA141" s="11"/>
     </row>
     <row r="142" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
@@ -15214,7 +15214,7 @@
       <c r="G142" t="s">
         <v>741</v>
       </c>
-      <c r="H142" s="11" t="s">
+      <c r="H142" s="12" t="s">
         <v>140</v>
       </c>
       <c r="I142" t="s">
@@ -15259,7 +15259,7 @@
       <c r="Z142" t="s">
         <v>755</v>
       </c>
-      <c r="AA142" s="10" t="s">
+      <c r="AA142" s="11" t="s">
         <v>141</v>
       </c>
     </row>
@@ -15285,7 +15285,7 @@
       <c r="G143" t="s">
         <v>741</v>
       </c>
-      <c r="H143" s="11"/>
+      <c r="H143" s="12"/>
       <c r="I143" t="s">
         <v>746</v>
       </c>
@@ -15328,7 +15328,7 @@
       <c r="Z143" t="s">
         <v>755</v>
       </c>
-      <c r="AA143" s="10"/>
+      <c r="AA143" s="11"/>
     </row>
     <row r="144" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
@@ -15352,7 +15352,7 @@
       <c r="G144" t="s">
         <v>741</v>
       </c>
-      <c r="H144" s="11"/>
+      <c r="H144" s="12"/>
       <c r="I144" t="s">
         <v>746</v>
       </c>
@@ -15395,7 +15395,7 @@
       <c r="Z144" t="s">
         <v>755</v>
       </c>
-      <c r="AA144" s="10"/>
+      <c r="AA144" s="11"/>
     </row>
     <row r="145" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
@@ -15419,7 +15419,7 @@
       <c r="G145" t="s">
         <v>741</v>
       </c>
-      <c r="H145" s="11"/>
+      <c r="H145" s="12"/>
       <c r="I145" t="s">
         <v>746</v>
       </c>
@@ -15462,7 +15462,7 @@
       <c r="Z145" t="s">
         <v>755</v>
       </c>
-      <c r="AA145" s="10"/>
+      <c r="AA145" s="11"/>
     </row>
     <row r="146" spans="1:28" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
@@ -15486,7 +15486,7 @@
       <c r="G146" t="s">
         <v>766</v>
       </c>
-      <c r="H146" s="11" t="s">
+      <c r="H146" s="12" t="s">
         <v>767</v>
       </c>
       <c r="I146" t="s">
@@ -15531,10 +15531,10 @@
       <c r="Z146" t="s">
         <v>776</v>
       </c>
-      <c r="AA146" s="10" t="s">
+      <c r="AA146" s="11" t="s">
         <v>768</v>
       </c>
-      <c r="AB146" s="10" t="s">
+      <c r="AB146" s="11" t="s">
         <v>756</v>
       </c>
     </row>
@@ -15560,7 +15560,7 @@
       <c r="G147" t="s">
         <v>766</v>
       </c>
-      <c r="H147" s="11"/>
+      <c r="H147" s="12"/>
       <c r="I147" t="s">
         <v>764</v>
       </c>
@@ -15603,8 +15603,8 @@
       <c r="Z147" t="s">
         <v>776</v>
       </c>
-      <c r="AA147" s="10"/>
-      <c r="AB147" s="10"/>
+      <c r="AA147" s="11"/>
+      <c r="AB147" s="11"/>
     </row>
     <row r="148" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
@@ -15628,7 +15628,7 @@
       <c r="G148" t="s">
         <v>766</v>
       </c>
-      <c r="H148" s="11"/>
+      <c r="H148" s="12"/>
       <c r="I148" t="s">
         <v>764</v>
       </c>
@@ -15671,8 +15671,8 @@
       <c r="Z148" t="s">
         <v>776</v>
       </c>
-      <c r="AA148" s="10"/>
-      <c r="AB148" s="10"/>
+      <c r="AA148" s="11"/>
+      <c r="AB148" s="11"/>
     </row>
     <row r="149" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
@@ -15696,7 +15696,7 @@
       <c r="G149" t="s">
         <v>766</v>
       </c>
-      <c r="H149" s="11"/>
+      <c r="H149" s="12"/>
       <c r="I149" t="s">
         <v>764</v>
       </c>
@@ -15739,8 +15739,8 @@
       <c r="Z149" t="s">
         <v>776</v>
       </c>
-      <c r="AA149" s="10"/>
-      <c r="AB149" s="10"/>
+      <c r="AA149" s="11"/>
+      <c r="AB149" s="11"/>
     </row>
     <row r="150" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
@@ -15764,7 +15764,7 @@
       <c r="G150" t="s">
         <v>779</v>
       </c>
-      <c r="H150" s="11" t="s">
+      <c r="H150" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I150" t="s">
@@ -15821,7 +15821,7 @@
       <c r="Z150" t="s">
         <v>797</v>
       </c>
-      <c r="AA150" s="10" t="s">
+      <c r="AA150" s="11" t="s">
         <v>789</v>
       </c>
     </row>
@@ -15847,7 +15847,7 @@
       <c r="G151" t="s">
         <v>779</v>
       </c>
-      <c r="H151" s="11"/>
+      <c r="H151" s="12"/>
       <c r="I151" t="s">
         <v>784</v>
       </c>
@@ -15902,7 +15902,7 @@
       <c r="Z151" t="s">
         <v>797</v>
       </c>
-      <c r="AA151" s="10"/>
+      <c r="AA151" s="11"/>
     </row>
     <row r="152" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
@@ -15926,7 +15926,7 @@
       <c r="G152" t="s">
         <v>779</v>
       </c>
-      <c r="H152" s="11"/>
+      <c r="H152" s="12"/>
       <c r="I152" t="s">
         <v>784</v>
       </c>
@@ -15981,7 +15981,7 @@
       <c r="Z152" t="s">
         <v>797</v>
       </c>
-      <c r="AA152" s="10"/>
+      <c r="AA152" s="11"/>
     </row>
     <row r="153" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
@@ -16005,7 +16005,7 @@
       <c r="G153" t="s">
         <v>779</v>
       </c>
-      <c r="H153" s="11"/>
+      <c r="H153" s="12"/>
       <c r="I153" t="s">
         <v>784</v>
       </c>
@@ -16060,7 +16060,7 @@
       <c r="Z153" t="s">
         <v>797</v>
       </c>
-      <c r="AA153" s="10"/>
+      <c r="AA153" s="11"/>
     </row>
     <row r="154" spans="1:28" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
@@ -16084,7 +16084,7 @@
       <c r="G154" t="s">
         <v>806</v>
       </c>
-      <c r="H154" s="11" t="s">
+      <c r="H154" s="12" t="s">
         <v>807</v>
       </c>
       <c r="I154" t="s">
@@ -16141,7 +16141,7 @@
       <c r="Z154" t="s">
         <v>816</v>
       </c>
-      <c r="AA154" s="10" t="s">
+      <c r="AA154" s="11" t="s">
         <v>817</v>
       </c>
     </row>
@@ -16167,7 +16167,7 @@
       <c r="G155" t="s">
         <v>806</v>
       </c>
-      <c r="H155" s="11"/>
+      <c r="H155" s="12"/>
       <c r="I155" t="s">
         <v>808</v>
       </c>
@@ -16222,7 +16222,7 @@
       <c r="Z155" t="s">
         <v>816</v>
       </c>
-      <c r="AA155" s="10"/>
+      <c r="AA155" s="11"/>
     </row>
     <row r="156" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
@@ -16246,7 +16246,7 @@
       <c r="G156" t="s">
         <v>806</v>
       </c>
-      <c r="H156" s="11"/>
+      <c r="H156" s="12"/>
       <c r="I156" t="s">
         <v>808</v>
       </c>
@@ -16301,7 +16301,7 @@
       <c r="Z156" t="s">
         <v>816</v>
       </c>
-      <c r="AA156" s="10"/>
+      <c r="AA156" s="11"/>
     </row>
     <row r="157" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
@@ -16325,7 +16325,7 @@
       <c r="G157" t="s">
         <v>806</v>
       </c>
-      <c r="H157" s="11"/>
+      <c r="H157" s="12"/>
       <c r="I157" t="s">
         <v>808</v>
       </c>
@@ -16380,7 +16380,7 @@
       <c r="Z157" t="s">
         <v>816</v>
       </c>
-      <c r="AA157" s="10"/>
+      <c r="AA157" s="11"/>
     </row>
     <row r="158" spans="1:28" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
@@ -16404,7 +16404,7 @@
       <c r="G158" t="s">
         <v>821</v>
       </c>
-      <c r="H158" s="11" t="s">
+      <c r="H158" s="12" t="s">
         <v>828</v>
       </c>
       <c r="I158" t="s">
@@ -16461,7 +16461,7 @@
       <c r="Z158" t="s">
         <v>816</v>
       </c>
-      <c r="AA158" s="10" t="s">
+      <c r="AA158" s="11" t="s">
         <v>835</v>
       </c>
     </row>
@@ -16487,7 +16487,7 @@
       <c r="G159" t="s">
         <v>821</v>
       </c>
-      <c r="H159" s="11"/>
+      <c r="H159" s="12"/>
       <c r="I159" t="s">
         <v>827</v>
       </c>
@@ -16542,7 +16542,7 @@
       <c r="Z159" t="s">
         <v>816</v>
       </c>
-      <c r="AA159" s="10"/>
+      <c r="AA159" s="11"/>
     </row>
     <row r="160" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
@@ -16566,7 +16566,7 @@
       <c r="G160" t="s">
         <v>821</v>
       </c>
-      <c r="H160" s="11"/>
+      <c r="H160" s="12"/>
       <c r="I160" t="s">
         <v>827</v>
       </c>
@@ -16621,7 +16621,7 @@
       <c r="Z160" t="s">
         <v>816</v>
       </c>
-      <c r="AA160" s="10"/>
+      <c r="AA160" s="11"/>
     </row>
     <row r="161" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
@@ -16645,7 +16645,7 @@
       <c r="G161" t="s">
         <v>821</v>
       </c>
-      <c r="H161" s="11"/>
+      <c r="H161" s="12"/>
       <c r="I161" t="s">
         <v>827</v>
       </c>
@@ -16700,33 +16700,62 @@
       <c r="Z161" t="s">
         <v>816</v>
       </c>
-      <c r="AA161" s="10"/>
+      <c r="AA161" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="92">
-    <mergeCell ref="AB130:AB133"/>
-    <mergeCell ref="AB146:AB149"/>
-    <mergeCell ref="H154:H157"/>
-    <mergeCell ref="AA154:AA157"/>
-    <mergeCell ref="H158:H161"/>
-    <mergeCell ref="AA158:AA161"/>
-    <mergeCell ref="L90:L93"/>
-    <mergeCell ref="AB18:AB21"/>
-    <mergeCell ref="AB26:AB29"/>
-    <mergeCell ref="AB30:AB33"/>
-    <mergeCell ref="AB54:AB57"/>
-    <mergeCell ref="AB62:AB65"/>
-    <mergeCell ref="AA26:AA29"/>
-    <mergeCell ref="H142:H145"/>
-    <mergeCell ref="AA142:AA145"/>
-    <mergeCell ref="H146:H149"/>
-    <mergeCell ref="AA146:AA149"/>
-    <mergeCell ref="H150:H153"/>
-    <mergeCell ref="AA150:AA153"/>
-    <mergeCell ref="H130:H133"/>
-    <mergeCell ref="AA130:AA133"/>
-    <mergeCell ref="H134:H137"/>
-    <mergeCell ref="AA134:AA137"/>
+    <mergeCell ref="AB6:AB9"/>
+    <mergeCell ref="AB10:AB13"/>
+    <mergeCell ref="H126:H129"/>
+    <mergeCell ref="AA126:AA129"/>
+    <mergeCell ref="AB126:AB129"/>
+    <mergeCell ref="H86:H89"/>
+    <mergeCell ref="AA86:AA89"/>
+    <mergeCell ref="H102:H105"/>
+    <mergeCell ref="AA102:AA105"/>
+    <mergeCell ref="H122:H125"/>
+    <mergeCell ref="AA122:AA125"/>
+    <mergeCell ref="AA98:AA101"/>
+    <mergeCell ref="H62:H65"/>
+    <mergeCell ref="AA62:AA65"/>
+    <mergeCell ref="H66:H69"/>
+    <mergeCell ref="AA66:AA69"/>
+    <mergeCell ref="H82:H85"/>
+    <mergeCell ref="AA82:AA85"/>
+    <mergeCell ref="H70:H73"/>
+    <mergeCell ref="AA70:AA73"/>
+    <mergeCell ref="H74:H77"/>
+    <mergeCell ref="AA74:AA77"/>
+    <mergeCell ref="H78:H81"/>
+    <mergeCell ref="AA78:AA81"/>
+    <mergeCell ref="H50:H53"/>
+    <mergeCell ref="AA50:AA53"/>
+    <mergeCell ref="H54:H57"/>
+    <mergeCell ref="AA54:AA57"/>
+    <mergeCell ref="H58:H61"/>
+    <mergeCell ref="AA58:AA61"/>
+    <mergeCell ref="H2:H5"/>
+    <mergeCell ref="AA2:AA5"/>
+    <mergeCell ref="H6:H9"/>
+    <mergeCell ref="AA6:AA9"/>
+    <mergeCell ref="H10:H13"/>
+    <mergeCell ref="AA10:AA13"/>
+    <mergeCell ref="AA94:AA97"/>
+    <mergeCell ref="H98:H101"/>
+    <mergeCell ref="H14:H17"/>
+    <mergeCell ref="L14:L17"/>
+    <mergeCell ref="AA14:AA17"/>
+    <mergeCell ref="H18:H21"/>
+    <mergeCell ref="AA18:AA21"/>
+    <mergeCell ref="H30:H33"/>
+    <mergeCell ref="AA30:AA33"/>
+    <mergeCell ref="H34:H37"/>
+    <mergeCell ref="AA34:AA37"/>
+    <mergeCell ref="H38:H41"/>
+    <mergeCell ref="AA38:AA41"/>
+    <mergeCell ref="H42:H45"/>
+    <mergeCell ref="AA42:AA45"/>
+    <mergeCell ref="H46:H49"/>
     <mergeCell ref="H138:H141"/>
     <mergeCell ref="AA138:AA141"/>
     <mergeCell ref="H22:H25"/>
@@ -16743,59 +16772,30 @@
     <mergeCell ref="H114:H117"/>
     <mergeCell ref="AA114:AA117"/>
     <mergeCell ref="H94:H97"/>
-    <mergeCell ref="AA94:AA97"/>
-    <mergeCell ref="H98:H101"/>
-    <mergeCell ref="H14:H17"/>
-    <mergeCell ref="L14:L17"/>
-    <mergeCell ref="AA14:AA17"/>
-    <mergeCell ref="H18:H21"/>
-    <mergeCell ref="AA18:AA21"/>
-    <mergeCell ref="H2:H5"/>
-    <mergeCell ref="AA2:AA5"/>
-    <mergeCell ref="H6:H9"/>
-    <mergeCell ref="AA6:AA9"/>
-    <mergeCell ref="H10:H13"/>
-    <mergeCell ref="AA10:AA13"/>
-    <mergeCell ref="H30:H33"/>
-    <mergeCell ref="AA30:AA33"/>
-    <mergeCell ref="H34:H37"/>
-    <mergeCell ref="AA34:AA37"/>
-    <mergeCell ref="H38:H41"/>
-    <mergeCell ref="AA38:AA41"/>
-    <mergeCell ref="H42:H45"/>
-    <mergeCell ref="AA42:AA45"/>
-    <mergeCell ref="H46:H49"/>
+    <mergeCell ref="L90:L93"/>
+    <mergeCell ref="AB18:AB21"/>
+    <mergeCell ref="AB26:AB29"/>
+    <mergeCell ref="AB30:AB33"/>
+    <mergeCell ref="AB54:AB57"/>
+    <mergeCell ref="AB62:AB65"/>
+    <mergeCell ref="AA26:AA29"/>
     <mergeCell ref="AA46:AA49"/>
-    <mergeCell ref="H50:H53"/>
-    <mergeCell ref="AA50:AA53"/>
-    <mergeCell ref="H54:H57"/>
-    <mergeCell ref="AA54:AA57"/>
-    <mergeCell ref="H58:H61"/>
-    <mergeCell ref="AA58:AA61"/>
-    <mergeCell ref="H82:H85"/>
-    <mergeCell ref="AA82:AA85"/>
-    <mergeCell ref="H70:H73"/>
-    <mergeCell ref="AA70:AA73"/>
-    <mergeCell ref="H74:H77"/>
-    <mergeCell ref="AA74:AA77"/>
-    <mergeCell ref="H78:H81"/>
-    <mergeCell ref="AA78:AA81"/>
-    <mergeCell ref="AB6:AB9"/>
-    <mergeCell ref="AB10:AB13"/>
-    <mergeCell ref="H126:H129"/>
-    <mergeCell ref="AA126:AA129"/>
-    <mergeCell ref="AB126:AB129"/>
-    <mergeCell ref="H86:H89"/>
-    <mergeCell ref="AA86:AA89"/>
-    <mergeCell ref="H102:H105"/>
-    <mergeCell ref="AA102:AA105"/>
-    <mergeCell ref="H122:H125"/>
-    <mergeCell ref="AA122:AA125"/>
-    <mergeCell ref="AA98:AA101"/>
-    <mergeCell ref="H62:H65"/>
-    <mergeCell ref="AA62:AA65"/>
-    <mergeCell ref="H66:H69"/>
-    <mergeCell ref="AA66:AA69"/>
+    <mergeCell ref="AB130:AB133"/>
+    <mergeCell ref="AB146:AB149"/>
+    <mergeCell ref="H154:H157"/>
+    <mergeCell ref="AA154:AA157"/>
+    <mergeCell ref="H158:H161"/>
+    <mergeCell ref="AA158:AA161"/>
+    <mergeCell ref="H142:H145"/>
+    <mergeCell ref="AA142:AA145"/>
+    <mergeCell ref="H146:H149"/>
+    <mergeCell ref="AA146:AA149"/>
+    <mergeCell ref="H150:H153"/>
+    <mergeCell ref="AA150:AA153"/>
+    <mergeCell ref="H130:H133"/>
+    <mergeCell ref="AA130:AA133"/>
+    <mergeCell ref="H134:H137"/>
+    <mergeCell ref="AA134:AA137"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Resultats_modeles_coleo_2024.xlsx
+++ b/Resultats_modeles_coleo_2024.xlsx
@@ -4273,6 +4273,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4281,9 +4284,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4705,7 +4705,7 @@
       <c r="G2" t="s">
         <v>154</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I2" t="s">
@@ -4762,7 +4762,7 @@
       <c r="Z2" t="s">
         <v>173</v>
       </c>
-      <c r="AA2" s="10" t="s">
+      <c r="AA2" s="11" t="s">
         <v>45</v>
       </c>
     </row>
@@ -4788,7 +4788,7 @@
       <c r="G3" t="s">
         <v>154</v>
       </c>
-      <c r="H3" s="11"/>
+      <c r="H3" s="12"/>
       <c r="I3" t="s">
         <v>150</v>
       </c>
@@ -4843,7 +4843,7 @@
       <c r="Z3" t="s">
         <v>173</v>
       </c>
-      <c r="AA3" s="10"/>
+      <c r="AA3" s="11"/>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -4867,7 +4867,7 @@
       <c r="G4" t="s">
         <v>154</v>
       </c>
-      <c r="H4" s="11"/>
+      <c r="H4" s="12"/>
       <c r="I4" t="s">
         <v>150</v>
       </c>
@@ -4922,7 +4922,7 @@
       <c r="Z4" t="s">
         <v>173</v>
       </c>
-      <c r="AA4" s="10"/>
+      <c r="AA4" s="11"/>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -4946,7 +4946,7 @@
       <c r="G5" t="s">
         <v>154</v>
       </c>
-      <c r="H5" s="11"/>
+      <c r="H5" s="12"/>
       <c r="I5" t="s">
         <v>150</v>
       </c>
@@ -5001,7 +5001,7 @@
       <c r="Z5" t="s">
         <v>173</v>
       </c>
-      <c r="AA5" s="10"/>
+      <c r="AA5" s="11"/>
     </row>
     <row r="6" spans="1:29" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -5025,7 +5025,7 @@
       <c r="G6" t="s">
         <v>184</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I6" t="s">
@@ -5082,10 +5082,10 @@
       <c r="Z6" t="s">
         <v>182</v>
       </c>
-      <c r="AA6" s="10" t="s">
+      <c r="AA6" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="AB6" s="10" t="s">
+      <c r="AB6" s="11" t="s">
         <v>174</v>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       <c r="G7" t="s">
         <v>184</v>
       </c>
-      <c r="H7" s="11"/>
+      <c r="H7" s="12"/>
       <c r="I7" t="s">
         <v>189</v>
       </c>
@@ -5166,8 +5166,8 @@
       <c r="Z7" t="s">
         <v>182</v>
       </c>
-      <c r="AA7" s="10"/>
-      <c r="AB7" s="10"/>
+      <c r="AA7" s="11"/>
+      <c r="AB7" s="11"/>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -5191,7 +5191,7 @@
       <c r="G8" t="s">
         <v>184</v>
       </c>
-      <c r="H8" s="11"/>
+      <c r="H8" s="12"/>
       <c r="I8" t="s">
         <v>189</v>
       </c>
@@ -5246,8 +5246,8 @@
       <c r="Z8" t="s">
         <v>182</v>
       </c>
-      <c r="AA8" s="10"/>
-      <c r="AB8" s="10"/>
+      <c r="AA8" s="11"/>
+      <c r="AB8" s="11"/>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -5271,7 +5271,7 @@
       <c r="G9" t="s">
         <v>184</v>
       </c>
-      <c r="H9" s="11"/>
+      <c r="H9" s="12"/>
       <c r="I9" t="s">
         <v>189</v>
       </c>
@@ -5326,8 +5326,8 @@
       <c r="Z9" t="s">
         <v>182</v>
       </c>
-      <c r="AA9" s="10"/>
-      <c r="AB9" s="10"/>
+      <c r="AA9" s="11"/>
+      <c r="AB9" s="11"/>
     </row>
     <row r="10" spans="1:29" ht="120" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -5351,7 +5351,7 @@
       <c r="G10" t="s">
         <v>194</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I10" t="s">
@@ -5408,10 +5408,10 @@
       <c r="Z10" t="s">
         <v>208</v>
       </c>
-      <c r="AA10" s="10" t="s">
+      <c r="AA10" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="AB10" s="10" t="s">
+      <c r="AB10" s="11" t="s">
         <v>209</v>
       </c>
     </row>
@@ -5437,7 +5437,7 @@
       <c r="G11" t="s">
         <v>194</v>
       </c>
-      <c r="H11" s="11"/>
+      <c r="H11" s="12"/>
       <c r="I11" t="s">
         <v>199</v>
       </c>
@@ -5492,8 +5492,8 @@
       <c r="Z11" t="s">
         <v>208</v>
       </c>
-      <c r="AA11" s="10"/>
-      <c r="AB11" s="10"/>
+      <c r="AA11" s="11"/>
+      <c r="AB11" s="11"/>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -5517,7 +5517,7 @@
       <c r="G12" t="s">
         <v>194</v>
       </c>
-      <c r="H12" s="11"/>
+      <c r="H12" s="12"/>
       <c r="I12" t="s">
         <v>199</v>
       </c>
@@ -5572,8 +5572,8 @@
       <c r="Z12" t="s">
         <v>208</v>
       </c>
-      <c r="AA12" s="10"/>
-      <c r="AB12" s="10"/>
+      <c r="AA12" s="11"/>
+      <c r="AB12" s="11"/>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -5597,7 +5597,7 @@
       <c r="G13" t="s">
         <v>194</v>
       </c>
-      <c r="H13" s="11"/>
+      <c r="H13" s="12"/>
       <c r="I13" t="s">
         <v>199</v>
       </c>
@@ -5652,8 +5652,8 @@
       <c r="Z13" t="s">
         <v>208</v>
       </c>
-      <c r="AA13" s="10"/>
-      <c r="AB13" s="10"/>
+      <c r="AA13" s="11"/>
+      <c r="AB13" s="11"/>
     </row>
     <row r="14" spans="1:29" ht="131.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -5677,7 +5677,7 @@
       <c r="G14" t="s">
         <v>211</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I14" t="s">
@@ -5689,7 +5689,7 @@
       <c r="K14" t="s">
         <v>20</v>
       </c>
-      <c r="L14" s="10" t="s">
+      <c r="L14" s="11" t="s">
         <v>44</v>
       </c>
       <c r="M14" t="s">
@@ -5734,7 +5734,7 @@
       <c r="Z14" t="s">
         <v>223</v>
       </c>
-      <c r="AA14" s="10" t="s">
+      <c r="AA14" s="11" t="s">
         <v>48</v>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       <c r="G15" t="s">
         <v>211</v>
       </c>
-      <c r="H15" s="11"/>
+      <c r="H15" s="12"/>
       <c r="I15" t="s">
         <v>213</v>
       </c>
@@ -5770,7 +5770,7 @@
       <c r="K15" t="s">
         <v>20</v>
       </c>
-      <c r="L15" s="10"/>
+      <c r="L15" s="11"/>
       <c r="M15" t="s">
         <v>15</v>
       </c>
@@ -5813,7 +5813,7 @@
       <c r="Z15" t="s">
         <v>223</v>
       </c>
-      <c r="AA15" s="10"/>
+      <c r="AA15" s="11"/>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -5837,7 +5837,7 @@
       <c r="G16" t="s">
         <v>211</v>
       </c>
-      <c r="H16" s="11"/>
+      <c r="H16" s="12"/>
       <c r="I16" t="s">
         <v>213</v>
       </c>
@@ -5847,7 +5847,7 @@
       <c r="K16" t="s">
         <v>20</v>
       </c>
-      <c r="L16" s="10"/>
+      <c r="L16" s="11"/>
       <c r="M16" t="s">
         <v>15</v>
       </c>
@@ -5890,7 +5890,7 @@
       <c r="Z16" t="s">
         <v>223</v>
       </c>
-      <c r="AA16" s="10"/>
+      <c r="AA16" s="11"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
@@ -5914,7 +5914,7 @@
       <c r="G17" t="s">
         <v>211</v>
       </c>
-      <c r="H17" s="11"/>
+      <c r="H17" s="12"/>
       <c r="I17" t="s">
         <v>213</v>
       </c>
@@ -5924,7 +5924,7 @@
       <c r="K17" t="s">
         <v>20</v>
       </c>
-      <c r="L17" s="10"/>
+      <c r="L17" s="11"/>
       <c r="M17" t="s">
         <v>15</v>
       </c>
@@ -5967,7 +5967,7 @@
       <c r="Z17" t="s">
         <v>223</v>
       </c>
-      <c r="AA17" s="10"/>
+      <c r="AA17" s="11"/>
     </row>
     <row r="18" spans="1:28" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -5991,7 +5991,7 @@
       <c r="G18" t="s">
         <v>225</v>
       </c>
-      <c r="H18" s="11" t="s">
+      <c r="H18" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I18" t="s">
@@ -6048,10 +6048,10 @@
       <c r="Z18" t="s">
         <v>240</v>
       </c>
-      <c r="AA18" s="10" t="s">
+      <c r="AA18" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="AB18" s="10" t="s">
+      <c r="AB18" s="11" t="s">
         <v>241</v>
       </c>
     </row>
@@ -6077,7 +6077,7 @@
       <c r="G19" t="s">
         <v>225</v>
       </c>
-      <c r="H19" s="11"/>
+      <c r="H19" s="12"/>
       <c r="I19" t="s">
         <v>230</v>
       </c>
@@ -6132,8 +6132,8 @@
       <c r="Z19" t="s">
         <v>240</v>
       </c>
-      <c r="AA19" s="10"/>
-      <c r="AB19" s="10"/>
+      <c r="AA19" s="11"/>
+      <c r="AB19" s="11"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
@@ -6157,7 +6157,7 @@
       <c r="G20" t="s">
         <v>225</v>
       </c>
-      <c r="H20" s="11"/>
+      <c r="H20" s="12"/>
       <c r="I20" t="s">
         <v>230</v>
       </c>
@@ -6212,8 +6212,8 @@
       <c r="Z20" t="s">
         <v>240</v>
       </c>
-      <c r="AA20" s="10"/>
-      <c r="AB20" s="10"/>
+      <c r="AA20" s="11"/>
+      <c r="AB20" s="11"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
@@ -6237,7 +6237,7 @@
       <c r="G21" t="s">
         <v>225</v>
       </c>
-      <c r="H21" s="11"/>
+      <c r="H21" s="12"/>
       <c r="I21" t="s">
         <v>230</v>
       </c>
@@ -6292,8 +6292,8 @@
       <c r="Z21" t="s">
         <v>240</v>
       </c>
-      <c r="AA21" s="10"/>
-      <c r="AB21" s="10"/>
+      <c r="AA21" s="11"/>
+      <c r="AB21" s="11"/>
     </row>
     <row r="22" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
@@ -6317,7 +6317,7 @@
       <c r="G22" t="s">
         <v>243</v>
       </c>
-      <c r="H22" s="11" t="s">
+      <c r="H22" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I22" t="s">
@@ -6362,7 +6362,7 @@
       <c r="Z22" t="s">
         <v>258</v>
       </c>
-      <c r="AA22" s="10" t="s">
+      <c r="AA22" s="11" t="s">
         <v>52</v>
       </c>
     </row>
@@ -6388,7 +6388,7 @@
       <c r="G23" t="s">
         <v>243</v>
       </c>
-      <c r="H23" s="11"/>
+      <c r="H23" s="12"/>
       <c r="I23" t="s">
         <v>249</v>
       </c>
@@ -6431,7 +6431,7 @@
       <c r="Z23" t="s">
         <v>258</v>
       </c>
-      <c r="AA23" s="10"/>
+      <c r="AA23" s="11"/>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
@@ -6455,7 +6455,7 @@
       <c r="G24" t="s">
         <v>243</v>
       </c>
-      <c r="H24" s="11"/>
+      <c r="H24" s="12"/>
       <c r="I24" t="s">
         <v>249</v>
       </c>
@@ -6498,7 +6498,7 @@
       <c r="Z24" t="s">
         <v>258</v>
       </c>
-      <c r="AA24" s="10"/>
+      <c r="AA24" s="11"/>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
@@ -6522,7 +6522,7 @@
       <c r="G25" t="s">
         <v>243</v>
       </c>
-      <c r="H25" s="11"/>
+      <c r="H25" s="12"/>
       <c r="I25" t="s">
         <v>249</v>
       </c>
@@ -6565,7 +6565,7 @@
       <c r="Z25" t="s">
         <v>258</v>
       </c>
-      <c r="AA25" s="10"/>
+      <c r="AA25" s="11"/>
     </row>
     <row r="26" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
@@ -6589,7 +6589,7 @@
       <c r="G26" t="s">
         <v>261</v>
       </c>
-      <c r="H26" s="11" t="s">
+      <c r="H26" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I26" t="s">
@@ -6646,10 +6646,10 @@
       <c r="Z26" t="s">
         <v>278</v>
       </c>
-      <c r="AA26" s="10" t="s">
+      <c r="AA26" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="AB26" s="10" t="s">
+      <c r="AB26" s="11" t="s">
         <v>279</v>
       </c>
     </row>
@@ -6675,7 +6675,7 @@
       <c r="G27" t="s">
         <v>261</v>
       </c>
-      <c r="H27" s="11"/>
+      <c r="H27" s="12"/>
       <c r="I27" t="s">
         <v>266</v>
       </c>
@@ -6730,8 +6730,8 @@
       <c r="Z27" t="s">
         <v>278</v>
       </c>
-      <c r="AA27" s="10"/>
-      <c r="AB27" s="10"/>
+      <c r="AA27" s="11"/>
+      <c r="AB27" s="11"/>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -6755,7 +6755,7 @@
       <c r="G28" t="s">
         <v>261</v>
       </c>
-      <c r="H28" s="11"/>
+      <c r="H28" s="12"/>
       <c r="I28" t="s">
         <v>266</v>
       </c>
@@ -6810,8 +6810,8 @@
       <c r="Z28" t="s">
         <v>278</v>
       </c>
-      <c r="AA28" s="10"/>
-      <c r="AB28" s="10"/>
+      <c r="AA28" s="11"/>
+      <c r="AB28" s="11"/>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -6835,7 +6835,7 @@
       <c r="G29" t="s">
         <v>261</v>
       </c>
-      <c r="H29" s="11"/>
+      <c r="H29" s="12"/>
       <c r="I29" t="s">
         <v>266</v>
       </c>
@@ -6890,8 +6890,8 @@
       <c r="Z29" t="s">
         <v>278</v>
       </c>
-      <c r="AA29" s="10"/>
-      <c r="AB29" s="10"/>
+      <c r="AA29" s="11"/>
+      <c r="AB29" s="11"/>
     </row>
     <row r="30" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
@@ -6915,7 +6915,7 @@
       <c r="G30" t="s">
         <v>282</v>
       </c>
-      <c r="H30" s="11" t="s">
+      <c r="H30" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I30" t="s">
@@ -6972,10 +6972,10 @@
       <c r="Z30" t="s">
         <v>298</v>
       </c>
-      <c r="AA30" s="10" t="s">
+      <c r="AA30" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="AB30" s="10" t="s">
+      <c r="AB30" s="11" t="s">
         <v>299</v>
       </c>
     </row>
@@ -7001,7 +7001,7 @@
       <c r="G31" t="s">
         <v>282</v>
       </c>
-      <c r="H31" s="11"/>
+      <c r="H31" s="12"/>
       <c r="I31" t="s">
         <v>287</v>
       </c>
@@ -7056,8 +7056,8 @@
       <c r="Z31" t="s">
         <v>298</v>
       </c>
-      <c r="AA31" s="10"/>
-      <c r="AB31" s="10"/>
+      <c r="AA31" s="11"/>
+      <c r="AB31" s="11"/>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
@@ -7081,7 +7081,7 @@
       <c r="G32" t="s">
         <v>282</v>
       </c>
-      <c r="H32" s="11"/>
+      <c r="H32" s="12"/>
       <c r="I32" t="s">
         <v>287</v>
       </c>
@@ -7136,8 +7136,8 @@
       <c r="Z32" t="s">
         <v>298</v>
       </c>
-      <c r="AA32" s="10"/>
-      <c r="AB32" s="10"/>
+      <c r="AA32" s="11"/>
+      <c r="AB32" s="11"/>
     </row>
     <row r="33" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
@@ -7161,7 +7161,7 @@
       <c r="G33" t="s">
         <v>282</v>
       </c>
-      <c r="H33" s="11"/>
+      <c r="H33" s="12"/>
       <c r="I33" t="s">
         <v>287</v>
       </c>
@@ -7216,8 +7216,8 @@
       <c r="Z33" t="s">
         <v>298</v>
       </c>
-      <c r="AA33" s="10"/>
-      <c r="AB33" s="10"/>
+      <c r="AA33" s="11"/>
+      <c r="AB33" s="11"/>
     </row>
     <row r="34" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
@@ -7241,7 +7241,7 @@
       <c r="G34" t="s">
         <v>302</v>
       </c>
-      <c r="H34" s="11" t="s">
+      <c r="H34" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I34" t="s">
@@ -7286,7 +7286,7 @@
       <c r="Z34" t="s">
         <v>315</v>
       </c>
-      <c r="AA34" s="10" t="s">
+      <c r="AA34" s="11" t="s">
         <v>835</v>
       </c>
     </row>
@@ -7312,7 +7312,7 @@
       <c r="G35" t="s">
         <v>302</v>
       </c>
-      <c r="H35" s="11"/>
+      <c r="H35" s="12"/>
       <c r="I35" t="s">
         <v>306</v>
       </c>
@@ -7355,7 +7355,7 @@
       <c r="Z35" t="s">
         <v>315</v>
       </c>
-      <c r="AA35" s="10"/>
+      <c r="AA35" s="11"/>
     </row>
     <row r="36" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
@@ -7379,7 +7379,7 @@
       <c r="G36" t="s">
         <v>302</v>
       </c>
-      <c r="H36" s="11"/>
+      <c r="H36" s="12"/>
       <c r="I36" t="s">
         <v>306</v>
       </c>
@@ -7422,7 +7422,7 @@
       <c r="Z36" t="s">
         <v>315</v>
       </c>
-      <c r="AA36" s="10"/>
+      <c r="AA36" s="11"/>
     </row>
     <row r="37" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
@@ -7446,7 +7446,7 @@
       <c r="G37" t="s">
         <v>302</v>
       </c>
-      <c r="H37" s="11"/>
+      <c r="H37" s="12"/>
       <c r="I37" t="s">
         <v>306</v>
       </c>
@@ -7489,7 +7489,7 @@
       <c r="Z37" t="s">
         <v>315</v>
       </c>
-      <c r="AA37" s="10"/>
+      <c r="AA37" s="11"/>
     </row>
     <row r="38" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
@@ -7513,7 +7513,7 @@
       <c r="G38" t="s">
         <v>318</v>
       </c>
-      <c r="H38" s="11" t="s">
+      <c r="H38" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I38" t="s">
@@ -7558,7 +7558,7 @@
       <c r="Z38" t="s">
         <v>330</v>
       </c>
-      <c r="AA38" s="10" t="s">
+      <c r="AA38" s="11" t="s">
         <v>834</v>
       </c>
     </row>
@@ -7584,7 +7584,7 @@
       <c r="G39" t="s">
         <v>318</v>
       </c>
-      <c r="H39" s="11"/>
+      <c r="H39" s="12"/>
       <c r="I39" t="s">
         <v>322</v>
       </c>
@@ -7627,7 +7627,7 @@
       <c r="Z39" t="s">
         <v>330</v>
       </c>
-      <c r="AA39" s="10"/>
+      <c r="AA39" s="11"/>
     </row>
     <row r="40" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
@@ -7651,7 +7651,7 @@
       <c r="G40" t="s">
         <v>318</v>
       </c>
-      <c r="H40" s="11"/>
+      <c r="H40" s="12"/>
       <c r="I40" t="s">
         <v>322</v>
       </c>
@@ -7694,7 +7694,7 @@
       <c r="Z40" t="s">
         <v>330</v>
       </c>
-      <c r="AA40" s="10"/>
+      <c r="AA40" s="11"/>
     </row>
     <row r="41" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
@@ -7718,7 +7718,7 @@
       <c r="G41" t="s">
         <v>318</v>
       </c>
-      <c r="H41" s="11"/>
+      <c r="H41" s="12"/>
       <c r="I41" t="s">
         <v>322</v>
       </c>
@@ -7761,7 +7761,7 @@
       <c r="Z41" t="s">
         <v>330</v>
       </c>
-      <c r="AA41" s="10"/>
+      <c r="AA41" s="11"/>
     </row>
     <row r="42" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
@@ -7785,7 +7785,7 @@
       <c r="G42" t="s">
         <v>332</v>
       </c>
-      <c r="H42" s="11" t="s">
+      <c r="H42" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I42" t="s">
@@ -7830,7 +7830,7 @@
       <c r="Z42" t="s">
         <v>346</v>
       </c>
-      <c r="AA42" s="10" t="s">
+      <c r="AA42" s="11" t="s">
         <v>338</v>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       <c r="G43" t="s">
         <v>332</v>
       </c>
-      <c r="H43" s="11"/>
+      <c r="H43" s="12"/>
       <c r="I43" t="s">
         <v>336</v>
       </c>
@@ -7899,7 +7899,7 @@
       <c r="Z43" t="s">
         <v>346</v>
       </c>
-      <c r="AA43" s="10"/>
+      <c r="AA43" s="11"/>
     </row>
     <row r="44" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
@@ -7923,7 +7923,7 @@
       <c r="G44" t="s">
         <v>332</v>
       </c>
-      <c r="H44" s="11"/>
+      <c r="H44" s="12"/>
       <c r="I44" t="s">
         <v>336</v>
       </c>
@@ -7966,7 +7966,7 @@
       <c r="Z44" t="s">
         <v>346</v>
       </c>
-      <c r="AA44" s="10"/>
+      <c r="AA44" s="11"/>
     </row>
     <row r="45" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
@@ -7990,7 +7990,7 @@
       <c r="G45" t="s">
         <v>332</v>
       </c>
-      <c r="H45" s="11"/>
+      <c r="H45" s="12"/>
       <c r="I45" t="s">
         <v>336</v>
       </c>
@@ -8033,7 +8033,7 @@
       <c r="Z45" t="s">
         <v>346</v>
       </c>
-      <c r="AA45" s="10"/>
+      <c r="AA45" s="11"/>
     </row>
     <row r="46" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
@@ -8057,7 +8057,7 @@
       <c r="G46" t="s">
         <v>348</v>
       </c>
-      <c r="H46" s="11" t="s">
+      <c r="H46" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I46" t="s">
@@ -8102,7 +8102,7 @@
       <c r="Z46" t="s">
         <v>362</v>
       </c>
-      <c r="AA46" s="10" t="s">
+      <c r="AA46" s="11" t="s">
         <v>355</v>
       </c>
     </row>
@@ -8128,7 +8128,7 @@
       <c r="G47" t="s">
         <v>348</v>
       </c>
-      <c r="H47" s="11"/>
+      <c r="H47" s="12"/>
       <c r="I47" t="s">
         <v>353</v>
       </c>
@@ -8171,7 +8171,7 @@
       <c r="Z47" t="s">
         <v>362</v>
       </c>
-      <c r="AA47" s="10"/>
+      <c r="AA47" s="11"/>
     </row>
     <row r="48" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
@@ -8195,7 +8195,7 @@
       <c r="G48" t="s">
         <v>348</v>
       </c>
-      <c r="H48" s="11"/>
+      <c r="H48" s="12"/>
       <c r="I48" t="s">
         <v>353</v>
       </c>
@@ -8238,7 +8238,7 @@
       <c r="Z48" t="s">
         <v>362</v>
       </c>
-      <c r="AA48" s="10"/>
+      <c r="AA48" s="11"/>
     </row>
     <row r="49" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
@@ -8262,7 +8262,7 @@
       <c r="G49" t="s">
         <v>348</v>
       </c>
-      <c r="H49" s="11"/>
+      <c r="H49" s="12"/>
       <c r="I49" t="s">
         <v>353</v>
       </c>
@@ -8305,7 +8305,7 @@
       <c r="Z49" t="s">
         <v>362</v>
       </c>
-      <c r="AA49" s="10"/>
+      <c r="AA49" s="11"/>
     </row>
     <row r="50" spans="1:28" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
@@ -8329,7 +8329,7 @@
       <c r="G50" t="s">
         <v>364</v>
       </c>
-      <c r="H50" s="11" t="s">
+      <c r="H50" s="12" t="s">
         <v>369</v>
       </c>
       <c r="I50" t="s">
@@ -8386,7 +8386,7 @@
       <c r="Z50" t="s">
         <v>382</v>
       </c>
-      <c r="AA50" s="10" t="s">
+      <c r="AA50" s="11" t="s">
         <v>375</v>
       </c>
     </row>
@@ -8412,7 +8412,7 @@
       <c r="G51" t="s">
         <v>364</v>
       </c>
-      <c r="H51" s="11"/>
+      <c r="H51" s="12"/>
       <c r="I51" t="s">
         <v>371</v>
       </c>
@@ -8467,7 +8467,7 @@
       <c r="Z51" t="s">
         <v>382</v>
       </c>
-      <c r="AA51" s="10"/>
+      <c r="AA51" s="11"/>
     </row>
     <row r="52" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
@@ -8491,7 +8491,7 @@
       <c r="G52" t="s">
         <v>364</v>
       </c>
-      <c r="H52" s="11"/>
+      <c r="H52" s="12"/>
       <c r="I52" t="s">
         <v>371</v>
       </c>
@@ -8546,7 +8546,7 @@
       <c r="Z52" t="s">
         <v>382</v>
       </c>
-      <c r="AA52" s="10"/>
+      <c r="AA52" s="11"/>
     </row>
     <row r="53" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
@@ -8570,7 +8570,7 @@
       <c r="G53" t="s">
         <v>364</v>
       </c>
-      <c r="H53" s="11"/>
+      <c r="H53" s="12"/>
       <c r="I53" t="s">
         <v>371</v>
       </c>
@@ -8625,7 +8625,7 @@
       <c r="Z53" t="s">
         <v>382</v>
       </c>
-      <c r="AA53" s="10"/>
+      <c r="AA53" s="11"/>
     </row>
     <row r="54" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
@@ -8649,7 +8649,7 @@
       <c r="G54" t="s">
         <v>385</v>
       </c>
-      <c r="H54" s="11" t="s">
+      <c r="H54" s="12" t="s">
         <v>68</v>
       </c>
       <c r="I54" t="s">
@@ -8694,10 +8694,10 @@
       <c r="Z54" t="s">
         <v>398</v>
       </c>
-      <c r="AA54" s="10" t="s">
+      <c r="AA54" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="AB54" s="10" t="s">
+      <c r="AB54" s="11" t="s">
         <v>399</v>
       </c>
     </row>
@@ -8723,7 +8723,7 @@
       <c r="G55" t="s">
         <v>385</v>
       </c>
-      <c r="H55" s="11"/>
+      <c r="H55" s="12"/>
       <c r="I55" t="s">
         <v>392</v>
       </c>
@@ -8766,8 +8766,8 @@
       <c r="Z55" t="s">
         <v>398</v>
       </c>
-      <c r="AA55" s="10"/>
-      <c r="AB55" s="10"/>
+      <c r="AA55" s="11"/>
+      <c r="AB55" s="11"/>
     </row>
     <row r="56" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
@@ -8791,7 +8791,7 @@
       <c r="G56" t="s">
         <v>385</v>
       </c>
-      <c r="H56" s="11"/>
+      <c r="H56" s="12"/>
       <c r="I56" t="s">
         <v>392</v>
       </c>
@@ -8834,8 +8834,8 @@
       <c r="Z56" t="s">
         <v>398</v>
       </c>
-      <c r="AA56" s="10"/>
-      <c r="AB56" s="10"/>
+      <c r="AA56" s="11"/>
+      <c r="AB56" s="11"/>
     </row>
     <row r="57" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
@@ -8859,7 +8859,7 @@
       <c r="G57" t="s">
         <v>385</v>
       </c>
-      <c r="H57" s="11"/>
+      <c r="H57" s="12"/>
       <c r="I57" t="s">
         <v>392</v>
       </c>
@@ -8902,8 +8902,8 @@
       <c r="Z57" t="s">
         <v>398</v>
       </c>
-      <c r="AA57" s="10"/>
-      <c r="AB57" s="10"/>
+      <c r="AA57" s="11"/>
+      <c r="AB57" s="11"/>
     </row>
     <row r="58" spans="1:28" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
@@ -8927,7 +8927,7 @@
       <c r="G58" t="s">
         <v>402</v>
       </c>
-      <c r="H58" s="11" t="s">
+      <c r="H58" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I58" t="s">
@@ -8984,7 +8984,7 @@
       <c r="Z58" t="s">
         <v>417</v>
       </c>
-      <c r="AA58" s="10" t="s">
+      <c r="AA58" s="11" t="s">
         <v>72</v>
       </c>
     </row>
@@ -9010,7 +9010,7 @@
       <c r="G59" t="s">
         <v>402</v>
       </c>
-      <c r="H59" s="11"/>
+      <c r="H59" s="12"/>
       <c r="I59" t="s">
         <v>407</v>
       </c>
@@ -9065,7 +9065,7 @@
       <c r="Z59" t="s">
         <v>417</v>
       </c>
-      <c r="AA59" s="10"/>
+      <c r="AA59" s="11"/>
     </row>
     <row r="60" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
@@ -9089,7 +9089,7 @@
       <c r="G60" t="s">
         <v>402</v>
       </c>
-      <c r="H60" s="11"/>
+      <c r="H60" s="12"/>
       <c r="I60" t="s">
         <v>407</v>
       </c>
@@ -9144,7 +9144,7 @@
       <c r="Z60" t="s">
         <v>417</v>
       </c>
-      <c r="AA60" s="10"/>
+      <c r="AA60" s="11"/>
     </row>
     <row r="61" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
@@ -9168,7 +9168,7 @@
       <c r="G61" t="s">
         <v>402</v>
       </c>
-      <c r="H61" s="11"/>
+      <c r="H61" s="12"/>
       <c r="I61" t="s">
         <v>407</v>
       </c>
@@ -9223,7 +9223,7 @@
       <c r="Z61" t="s">
         <v>417</v>
       </c>
-      <c r="AA61" s="10"/>
+      <c r="AA61" s="11"/>
     </row>
     <row r="62" spans="1:28" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
@@ -9247,7 +9247,7 @@
       <c r="G62" t="s">
         <v>75</v>
       </c>
-      <c r="H62" s="11" t="s">
+      <c r="H62" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I62" t="s">
@@ -9304,10 +9304,10 @@
       <c r="Z62" t="s">
         <v>426</v>
       </c>
-      <c r="AA62" s="10" t="s">
+      <c r="AA62" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="AB62" s="10" t="s">
+      <c r="AB62" s="11" t="s">
         <v>418</v>
       </c>
     </row>
@@ -9333,7 +9333,7 @@
       <c r="G63" t="s">
         <v>75</v>
       </c>
-      <c r="H63" s="11"/>
+      <c r="H63" s="12"/>
       <c r="I63" t="s">
         <v>80</v>
       </c>
@@ -9388,8 +9388,8 @@
       <c r="Z63" t="s">
         <v>426</v>
       </c>
-      <c r="AA63" s="10"/>
-      <c r="AB63" s="10"/>
+      <c r="AA63" s="11"/>
+      <c r="AB63" s="11"/>
     </row>
     <row r="64" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
@@ -9413,7 +9413,7 @@
       <c r="G64" t="s">
         <v>75</v>
       </c>
-      <c r="H64" s="11"/>
+      <c r="H64" s="12"/>
       <c r="I64" t="s">
         <v>80</v>
       </c>
@@ -9468,8 +9468,8 @@
       <c r="Z64" t="s">
         <v>426</v>
       </c>
-      <c r="AA64" s="10"/>
-      <c r="AB64" s="10"/>
+      <c r="AA64" s="11"/>
+      <c r="AB64" s="11"/>
     </row>
     <row r="65" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
@@ -9493,7 +9493,7 @@
       <c r="G65" t="s">
         <v>75</v>
       </c>
-      <c r="H65" s="11"/>
+      <c r="H65" s="12"/>
       <c r="I65" t="s">
         <v>80</v>
       </c>
@@ -9548,8 +9548,8 @@
       <c r="Z65" t="s">
         <v>426</v>
       </c>
-      <c r="AA65" s="10"/>
-      <c r="AB65" s="10"/>
+      <c r="AA65" s="11"/>
+      <c r="AB65" s="11"/>
     </row>
     <row r="66" spans="1:28" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
@@ -9573,7 +9573,7 @@
       <c r="G66" t="s">
         <v>428</v>
       </c>
-      <c r="H66" s="11" t="s">
+      <c r="H66" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I66" t="s">
@@ -9630,7 +9630,7 @@
       <c r="Z66" t="s">
         <v>442</v>
       </c>
-      <c r="AA66" s="10" t="s">
+      <c r="AA66" s="11" t="s">
         <v>434</v>
       </c>
     </row>
@@ -9656,7 +9656,7 @@
       <c r="G67" t="s">
         <v>428</v>
       </c>
-      <c r="H67" s="11"/>
+      <c r="H67" s="12"/>
       <c r="I67" t="s">
         <v>432</v>
       </c>
@@ -9711,7 +9711,7 @@
       <c r="Z67" t="s">
         <v>442</v>
       </c>
-      <c r="AA67" s="10"/>
+      <c r="AA67" s="11"/>
     </row>
     <row r="68" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
@@ -9735,7 +9735,7 @@
       <c r="G68" t="s">
         <v>428</v>
       </c>
-      <c r="H68" s="11"/>
+      <c r="H68" s="12"/>
       <c r="I68" t="s">
         <v>432</v>
       </c>
@@ -9790,7 +9790,7 @@
       <c r="Z68" t="s">
         <v>442</v>
       </c>
-      <c r="AA68" s="10"/>
+      <c r="AA68" s="11"/>
     </row>
     <row r="69" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
@@ -9814,7 +9814,7 @@
       <c r="G69" t="s">
         <v>428</v>
       </c>
-      <c r="H69" s="11"/>
+      <c r="H69" s="12"/>
       <c r="I69" t="s">
         <v>432</v>
       </c>
@@ -9869,7 +9869,7 @@
       <c r="Z69" t="s">
         <v>442</v>
       </c>
-      <c r="AA69" s="10"/>
+      <c r="AA69" s="11"/>
     </row>
     <row r="70" spans="1:28" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
@@ -9893,7 +9893,7 @@
       <c r="G70" t="s">
         <v>445</v>
       </c>
-      <c r="H70" s="11" t="s">
+      <c r="H70" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I70" t="s">
@@ -9950,7 +9950,7 @@
       <c r="Z70" t="s">
         <v>461</v>
       </c>
-      <c r="AA70" s="10" t="s">
+      <c r="AA70" s="11" t="s">
         <v>454</v>
       </c>
     </row>
@@ -9976,7 +9976,7 @@
       <c r="G71" t="s">
         <v>445</v>
       </c>
-      <c r="H71" s="11"/>
+      <c r="H71" s="12"/>
       <c r="I71" t="s">
         <v>450</v>
       </c>
@@ -10031,7 +10031,7 @@
       <c r="Z71" t="s">
         <v>461</v>
       </c>
-      <c r="AA71" s="10"/>
+      <c r="AA71" s="11"/>
     </row>
     <row r="72" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
@@ -10055,7 +10055,7 @@
       <c r="G72" t="s">
         <v>445</v>
       </c>
-      <c r="H72" s="11"/>
+      <c r="H72" s="12"/>
       <c r="I72" t="s">
         <v>450</v>
       </c>
@@ -10110,7 +10110,7 @@
       <c r="Z72" t="s">
         <v>461</v>
       </c>
-      <c r="AA72" s="10"/>
+      <c r="AA72" s="11"/>
     </row>
     <row r="73" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
@@ -10134,7 +10134,7 @@
       <c r="G73" t="s">
         <v>445</v>
       </c>
-      <c r="H73" s="11"/>
+      <c r="H73" s="12"/>
       <c r="I73" t="s">
         <v>450</v>
       </c>
@@ -10189,7 +10189,7 @@
       <c r="Z73" t="s">
         <v>461</v>
       </c>
-      <c r="AA73" s="10"/>
+      <c r="AA73" s="11"/>
     </row>
     <row r="74" spans="1:28" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
@@ -10213,7 +10213,7 @@
       <c r="G74" t="s">
         <v>463</v>
       </c>
-      <c r="H74" s="11" t="s">
+      <c r="H74" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I74" t="s">
@@ -10258,7 +10258,7 @@
       <c r="Z74" t="s">
         <v>477</v>
       </c>
-      <c r="AA74" s="10" t="s">
+      <c r="AA74" s="11" t="s">
         <v>470</v>
       </c>
     </row>
@@ -10284,7 +10284,7 @@
       <c r="G75" t="s">
         <v>463</v>
       </c>
-      <c r="H75" s="11"/>
+      <c r="H75" s="12"/>
       <c r="I75" t="s">
         <v>468</v>
       </c>
@@ -10327,7 +10327,7 @@
       <c r="Z75" t="s">
         <v>477</v>
       </c>
-      <c r="AA75" s="10"/>
+      <c r="AA75" s="11"/>
     </row>
     <row r="76" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
@@ -10351,7 +10351,7 @@
       <c r="G76" t="s">
         <v>463</v>
       </c>
-      <c r="H76" s="11"/>
+      <c r="H76" s="12"/>
       <c r="I76" t="s">
         <v>468</v>
       </c>
@@ -10394,7 +10394,7 @@
       <c r="Z76" t="s">
         <v>477</v>
       </c>
-      <c r="AA76" s="10"/>
+      <c r="AA76" s="11"/>
     </row>
     <row r="77" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
@@ -10418,7 +10418,7 @@
       <c r="G77" t="s">
         <v>463</v>
       </c>
-      <c r="H77" s="11"/>
+      <c r="H77" s="12"/>
       <c r="I77" t="s">
         <v>468</v>
       </c>
@@ -10461,7 +10461,7 @@
       <c r="Z77" t="s">
         <v>477</v>
       </c>
-      <c r="AA77" s="10"/>
+      <c r="AA77" s="11"/>
     </row>
     <row r="78" spans="1:28" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
@@ -10485,7 +10485,7 @@
       <c r="G78" t="s">
         <v>480</v>
       </c>
-      <c r="H78" s="11" t="s">
+      <c r="H78" s="12" t="s">
         <v>486</v>
       </c>
       <c r="I78" t="s">
@@ -10530,7 +10530,7 @@
       <c r="Z78" t="s">
         <v>496</v>
       </c>
-      <c r="AA78" s="10" t="s">
+      <c r="AA78" s="11" t="s">
         <v>478</v>
       </c>
     </row>
@@ -10556,7 +10556,7 @@
       <c r="G79" t="s">
         <v>480</v>
       </c>
-      <c r="H79" s="11"/>
+      <c r="H79" s="12"/>
       <c r="I79" t="s">
         <v>487</v>
       </c>
@@ -10599,7 +10599,7 @@
       <c r="Z79" t="s">
         <v>496</v>
       </c>
-      <c r="AA79" s="10"/>
+      <c r="AA79" s="11"/>
     </row>
     <row r="80" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
@@ -10623,7 +10623,7 @@
       <c r="G80" t="s">
         <v>480</v>
       </c>
-      <c r="H80" s="11"/>
+      <c r="H80" s="12"/>
       <c r="I80" t="s">
         <v>487</v>
       </c>
@@ -10666,7 +10666,7 @@
       <c r="Z80" t="s">
         <v>496</v>
       </c>
-      <c r="AA80" s="10"/>
+      <c r="AA80" s="11"/>
     </row>
     <row r="81" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
@@ -10690,7 +10690,7 @@
       <c r="G81" t="s">
         <v>480</v>
       </c>
-      <c r="H81" s="11"/>
+      <c r="H81" s="12"/>
       <c r="I81" t="s">
         <v>487</v>
       </c>
@@ -10733,7 +10733,7 @@
       <c r="Z81" t="s">
         <v>496</v>
       </c>
-      <c r="AA81" s="10"/>
+      <c r="AA81" s="11"/>
     </row>
     <row r="82" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
@@ -10757,7 +10757,7 @@
       <c r="G82" t="s">
         <v>498</v>
       </c>
-      <c r="H82" s="11" t="s">
+      <c r="H82" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I82" t="s">
@@ -10802,7 +10802,7 @@
       <c r="Z82" t="s">
         <v>511</v>
       </c>
-      <c r="AA82" s="10" t="s">
+      <c r="AA82" s="11" t="s">
         <v>90</v>
       </c>
     </row>
@@ -10828,7 +10828,7 @@
       <c r="G83" t="s">
         <v>498</v>
       </c>
-      <c r="H83" s="11"/>
+      <c r="H83" s="12"/>
       <c r="I83" t="s">
         <v>503</v>
       </c>
@@ -10871,7 +10871,7 @@
       <c r="Z83" t="s">
         <v>511</v>
       </c>
-      <c r="AA83" s="10"/>
+      <c r="AA83" s="11"/>
     </row>
     <row r="84" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
@@ -10895,7 +10895,7 @@
       <c r="G84" t="s">
         <v>498</v>
       </c>
-      <c r="H84" s="11"/>
+      <c r="H84" s="12"/>
       <c r="I84" t="s">
         <v>503</v>
       </c>
@@ -10938,7 +10938,7 @@
       <c r="Z84" t="s">
         <v>511</v>
       </c>
-      <c r="AA84" s="10"/>
+      <c r="AA84" s="11"/>
     </row>
     <row r="85" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
@@ -10962,7 +10962,7 @@
       <c r="G85" t="s">
         <v>498</v>
       </c>
-      <c r="H85" s="11"/>
+      <c r="H85" s="12"/>
       <c r="I85" t="s">
         <v>503</v>
       </c>
@@ -11005,7 +11005,7 @@
       <c r="Z85" t="s">
         <v>511</v>
       </c>
-      <c r="AA85" s="10"/>
+      <c r="AA85" s="11"/>
     </row>
     <row r="86" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
@@ -11029,7 +11029,7 @@
       <c r="G86" t="s">
         <v>514</v>
       </c>
-      <c r="H86" s="11" t="s">
+      <c r="H86" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I86" t="s">
@@ -11074,7 +11074,7 @@
       <c r="Z86" t="s">
         <v>526</v>
       </c>
-      <c r="AA86" s="10" t="s">
+      <c r="AA86" s="11" t="s">
         <v>92</v>
       </c>
     </row>
@@ -11100,7 +11100,7 @@
       <c r="G87" t="s">
         <v>514</v>
       </c>
-      <c r="H87" s="11"/>
+      <c r="H87" s="12"/>
       <c r="I87" t="s">
         <v>518</v>
       </c>
@@ -11143,7 +11143,7 @@
       <c r="Z87" t="s">
         <v>526</v>
       </c>
-      <c r="AA87" s="10"/>
+      <c r="AA87" s="11"/>
     </row>
     <row r="88" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
@@ -11167,7 +11167,7 @@
       <c r="G88" t="s">
         <v>514</v>
       </c>
-      <c r="H88" s="11"/>
+      <c r="H88" s="12"/>
       <c r="I88" t="s">
         <v>518</v>
       </c>
@@ -11210,7 +11210,7 @@
       <c r="Z88" t="s">
         <v>526</v>
       </c>
-      <c r="AA88" s="10"/>
+      <c r="AA88" s="11"/>
     </row>
     <row r="89" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
@@ -11234,7 +11234,7 @@
       <c r="G89" t="s">
         <v>514</v>
       </c>
-      <c r="H89" s="11"/>
+      <c r="H89" s="12"/>
       <c r="I89" t="s">
         <v>518</v>
       </c>
@@ -11277,7 +11277,7 @@
       <c r="Z89" t="s">
         <v>526</v>
       </c>
-      <c r="AA89" s="10"/>
+      <c r="AA89" s="11"/>
     </row>
     <row r="90" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
@@ -11301,7 +11301,7 @@
       <c r="G90" t="s">
         <v>530</v>
       </c>
-      <c r="H90" s="11" t="s">
+      <c r="H90" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I90" t="s">
@@ -11313,7 +11313,7 @@
       <c r="K90" t="s">
         <v>20</v>
       </c>
-      <c r="L90" s="10" t="s">
+      <c r="L90" s="11" t="s">
         <v>536</v>
       </c>
       <c r="M90" t="s">
@@ -11358,7 +11358,7 @@
       <c r="Z90" t="s">
         <v>546</v>
       </c>
-      <c r="AA90" s="10" t="s">
+      <c r="AA90" s="11" t="s">
         <v>114</v>
       </c>
       <c r="AB90" s="5"/>
@@ -11385,7 +11385,7 @@
       <c r="G91" t="s">
         <v>530</v>
       </c>
-      <c r="H91" s="11"/>
+      <c r="H91" s="12"/>
       <c r="I91" t="s">
         <v>534</v>
       </c>
@@ -11395,7 +11395,7 @@
       <c r="K91" t="s">
         <v>20</v>
       </c>
-      <c r="L91" s="10"/>
+      <c r="L91" s="11"/>
       <c r="M91" t="s">
         <v>16</v>
       </c>
@@ -11438,7 +11438,7 @@
       <c r="Z91" t="s">
         <v>546</v>
       </c>
-      <c r="AA91" s="10"/>
+      <c r="AA91" s="11"/>
       <c r="AB91" s="5"/>
     </row>
     <row r="92" spans="1:28" x14ac:dyDescent="0.3">
@@ -11463,7 +11463,7 @@
       <c r="G92" t="s">
         <v>530</v>
       </c>
-      <c r="H92" s="11"/>
+      <c r="H92" s="12"/>
       <c r="I92" t="s">
         <v>534</v>
       </c>
@@ -11473,7 +11473,7 @@
       <c r="K92" t="s">
         <v>20</v>
       </c>
-      <c r="L92" s="10"/>
+      <c r="L92" s="11"/>
       <c r="M92" t="s">
         <v>16</v>
       </c>
@@ -11516,7 +11516,7 @@
       <c r="Z92" t="s">
         <v>546</v>
       </c>
-      <c r="AA92" s="10"/>
+      <c r="AA92" s="11"/>
       <c r="AB92" s="5"/>
     </row>
     <row r="93" spans="1:28" x14ac:dyDescent="0.3">
@@ -11541,7 +11541,7 @@
       <c r="G93" t="s">
         <v>530</v>
       </c>
-      <c r="H93" s="11"/>
+      <c r="H93" s="12"/>
       <c r="I93" t="s">
         <v>534</v>
       </c>
@@ -11551,7 +11551,7 @@
       <c r="K93" t="s">
         <v>20</v>
       </c>
-      <c r="L93" s="10"/>
+      <c r="L93" s="11"/>
       <c r="M93" t="s">
         <v>16</v>
       </c>
@@ -11594,7 +11594,7 @@
       <c r="Z93" t="s">
         <v>546</v>
       </c>
-      <c r="AA93" s="10"/>
+      <c r="AA93" s="11"/>
       <c r="AB93" s="5"/>
     </row>
     <row r="94" spans="1:28" ht="144" customHeight="1" x14ac:dyDescent="0.3">
@@ -11619,7 +11619,7 @@
       <c r="G94" t="s">
         <v>552</v>
       </c>
-      <c r="H94" s="11" t="s">
+      <c r="H94" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I94" t="s">
@@ -11676,7 +11676,7 @@
       <c r="Z94" t="s">
         <v>561</v>
       </c>
-      <c r="AA94" s="10" t="s">
+      <c r="AA94" s="11" t="s">
         <v>96</v>
       </c>
     </row>
@@ -11702,7 +11702,7 @@
       <c r="G95" t="s">
         <v>552</v>
       </c>
-      <c r="H95" s="11"/>
+      <c r="H95" s="12"/>
       <c r="I95" t="s">
         <v>553</v>
       </c>
@@ -11757,7 +11757,7 @@
       <c r="Z95" t="s">
         <v>561</v>
       </c>
-      <c r="AA95" s="10"/>
+      <c r="AA95" s="11"/>
     </row>
     <row r="96" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
@@ -11781,7 +11781,7 @@
       <c r="G96" t="s">
         <v>552</v>
       </c>
-      <c r="H96" s="11"/>
+      <c r="H96" s="12"/>
       <c r="I96" t="s">
         <v>553</v>
       </c>
@@ -11836,7 +11836,7 @@
       <c r="Z96" t="s">
         <v>561</v>
       </c>
-      <c r="AA96" s="10"/>
+      <c r="AA96" s="11"/>
     </row>
     <row r="97" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
@@ -11860,7 +11860,7 @@
       <c r="G97" t="s">
         <v>552</v>
       </c>
-      <c r="H97" s="11"/>
+      <c r="H97" s="12"/>
       <c r="I97" t="s">
         <v>553</v>
       </c>
@@ -11915,7 +11915,7 @@
       <c r="Z97" t="s">
         <v>561</v>
       </c>
-      <c r="AA97" s="10"/>
+      <c r="AA97" s="11"/>
     </row>
     <row r="98" spans="1:27" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
@@ -11939,7 +11939,7 @@
       <c r="G98" t="s">
         <v>568</v>
       </c>
-      <c r="H98" s="11" t="s">
+      <c r="H98" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I98" t="s">
@@ -11996,7 +11996,7 @@
       <c r="Z98" t="s">
         <v>580</v>
       </c>
-      <c r="AA98" s="10" t="s">
+      <c r="AA98" s="11" t="s">
         <v>572</v>
       </c>
     </row>
@@ -12022,7 +12022,7 @@
       <c r="G99" t="s">
         <v>568</v>
       </c>
-      <c r="H99" s="11"/>
+      <c r="H99" s="12"/>
       <c r="I99" t="s">
         <v>569</v>
       </c>
@@ -12077,7 +12077,7 @@
       <c r="Z99" t="s">
         <v>580</v>
       </c>
-      <c r="AA99" s="10"/>
+      <c r="AA99" s="11"/>
     </row>
     <row r="100" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
@@ -12101,7 +12101,7 @@
       <c r="G100" t="s">
         <v>568</v>
       </c>
-      <c r="H100" s="11"/>
+      <c r="H100" s="12"/>
       <c r="I100" t="s">
         <v>569</v>
       </c>
@@ -12156,7 +12156,7 @@
       <c r="Z100" t="s">
         <v>580</v>
       </c>
-      <c r="AA100" s="10"/>
+      <c r="AA100" s="11"/>
     </row>
     <row r="101" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
@@ -12180,7 +12180,7 @@
       <c r="G101" t="s">
         <v>568</v>
       </c>
-      <c r="H101" s="11"/>
+      <c r="H101" s="12"/>
       <c r="I101" t="s">
         <v>569</v>
       </c>
@@ -12235,7 +12235,7 @@
       <c r="Z101" t="s">
         <v>580</v>
       </c>
-      <c r="AA101" s="10"/>
+      <c r="AA101" s="11"/>
     </row>
     <row r="102" spans="1:27" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
@@ -12259,7 +12259,7 @@
       <c r="G102" t="s">
         <v>587</v>
       </c>
-      <c r="H102" s="11" t="s">
+      <c r="H102" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I102" t="s">
@@ -12316,7 +12316,7 @@
       <c r="Z102" t="s">
         <v>596</v>
       </c>
-      <c r="AA102" s="10" t="s">
+      <c r="AA102" s="11" t="s">
         <v>100</v>
       </c>
     </row>
@@ -12342,7 +12342,7 @@
       <c r="G103" t="s">
         <v>587</v>
       </c>
-      <c r="H103" s="11"/>
+      <c r="H103" s="12"/>
       <c r="I103" t="s">
         <v>583</v>
       </c>
@@ -12397,7 +12397,7 @@
       <c r="Z103" t="s">
         <v>596</v>
       </c>
-      <c r="AA103" s="10"/>
+      <c r="AA103" s="11"/>
     </row>
     <row r="104" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
@@ -12421,7 +12421,7 @@
       <c r="G104" t="s">
         <v>587</v>
       </c>
-      <c r="H104" s="11"/>
+      <c r="H104" s="12"/>
       <c r="I104" t="s">
         <v>583</v>
       </c>
@@ -12476,7 +12476,7 @@
       <c r="Z104" t="s">
         <v>596</v>
       </c>
-      <c r="AA104" s="10"/>
+      <c r="AA104" s="11"/>
     </row>
     <row r="105" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
@@ -12500,7 +12500,7 @@
       <c r="G105" t="s">
         <v>587</v>
       </c>
-      <c r="H105" s="11"/>
+      <c r="H105" s="12"/>
       <c r="I105" t="s">
         <v>583</v>
       </c>
@@ -12555,7 +12555,7 @@
       <c r="Z105" t="s">
         <v>596</v>
       </c>
-      <c r="AA105" s="10"/>
+      <c r="AA105" s="11"/>
     </row>
     <row r="106" spans="1:27" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
@@ -12579,7 +12579,7 @@
       <c r="G106" t="s">
         <v>599</v>
       </c>
-      <c r="H106" s="11" t="s">
+      <c r="H106" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I106" t="s">
@@ -12636,7 +12636,7 @@
       <c r="Z106" t="s">
         <v>609</v>
       </c>
-      <c r="AA106" s="10" t="s">
+      <c r="AA106" s="11" t="s">
         <v>107</v>
       </c>
     </row>
@@ -12662,7 +12662,7 @@
       <c r="G107" t="s">
         <v>599</v>
       </c>
-      <c r="H107" s="11"/>
+      <c r="H107" s="12"/>
       <c r="I107" t="s">
         <v>600</v>
       </c>
@@ -12717,7 +12717,7 @@
       <c r="Z107" t="s">
         <v>609</v>
       </c>
-      <c r="AA107" s="10"/>
+      <c r="AA107" s="11"/>
     </row>
     <row r="108" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
@@ -12741,7 +12741,7 @@
       <c r="G108" t="s">
         <v>599</v>
       </c>
-      <c r="H108" s="11"/>
+      <c r="H108" s="12"/>
       <c r="I108" t="s">
         <v>600</v>
       </c>
@@ -12796,7 +12796,7 @@
       <c r="Z108" t="s">
         <v>609</v>
       </c>
-      <c r="AA108" s="10"/>
+      <c r="AA108" s="11"/>
     </row>
     <row r="109" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
@@ -12820,7 +12820,7 @@
       <c r="G109" t="s">
         <v>599</v>
       </c>
-      <c r="H109" s="11"/>
+      <c r="H109" s="12"/>
       <c r="I109" t="s">
         <v>600</v>
       </c>
@@ -12875,7 +12875,7 @@
       <c r="Z109" t="s">
         <v>609</v>
       </c>
-      <c r="AA109" s="10"/>
+      <c r="AA109" s="11"/>
     </row>
     <row r="110" spans="1:27" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
@@ -12899,7 +12899,7 @@
       <c r="G110" t="s">
         <v>612</v>
       </c>
-      <c r="H110" s="11" t="s">
+      <c r="H110" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I110" t="s">
@@ -12956,7 +12956,7 @@
       <c r="Z110" t="s">
         <v>626</v>
       </c>
-      <c r="AA110" s="10" t="s">
+      <c r="AA110" s="11" t="s">
         <v>833</v>
       </c>
     </row>
@@ -12982,7 +12982,7 @@
       <c r="G111" t="s">
         <v>612</v>
       </c>
-      <c r="H111" s="11"/>
+      <c r="H111" s="12"/>
       <c r="I111" t="s">
         <v>617</v>
       </c>
@@ -13037,7 +13037,7 @@
       <c r="Z111" t="s">
         <v>626</v>
       </c>
-      <c r="AA111" s="10"/>
+      <c r="AA111" s="11"/>
     </row>
     <row r="112" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
@@ -13061,7 +13061,7 @@
       <c r="G112" t="s">
         <v>612</v>
       </c>
-      <c r="H112" s="11"/>
+      <c r="H112" s="12"/>
       <c r="I112" t="s">
         <v>617</v>
       </c>
@@ -13116,7 +13116,7 @@
       <c r="Z112" t="s">
         <v>626</v>
       </c>
-      <c r="AA112" s="10"/>
+      <c r="AA112" s="11"/>
     </row>
     <row r="113" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
@@ -13140,7 +13140,7 @@
       <c r="G113" t="s">
         <v>612</v>
       </c>
-      <c r="H113" s="11"/>
+      <c r="H113" s="12"/>
       <c r="I113" t="s">
         <v>617</v>
       </c>
@@ -13195,7 +13195,7 @@
       <c r="Z113" t="s">
         <v>626</v>
       </c>
-      <c r="AA113" s="10"/>
+      <c r="AA113" s="11"/>
     </row>
     <row r="114" spans="1:28" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
@@ -13219,7 +13219,7 @@
       <c r="G114" t="s">
         <v>628</v>
       </c>
-      <c r="H114" s="11" t="s">
+      <c r="H114" s="12" t="s">
         <v>634</v>
       </c>
       <c r="I114" t="s">
@@ -13264,7 +13264,7 @@
       <c r="Z114" t="s">
         <v>644</v>
       </c>
-      <c r="AA114" s="10" t="s">
+      <c r="AA114" s="11" t="s">
         <v>645</v>
       </c>
     </row>
@@ -13290,7 +13290,7 @@
       <c r="G115" t="s">
         <v>628</v>
       </c>
-      <c r="H115" s="11"/>
+      <c r="H115" s="12"/>
       <c r="I115" t="s">
         <v>635</v>
       </c>
@@ -13333,7 +13333,7 @@
       <c r="Z115" t="s">
         <v>644</v>
       </c>
-      <c r="AA115" s="10"/>
+      <c r="AA115" s="11"/>
     </row>
     <row r="116" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
@@ -13357,7 +13357,7 @@
       <c r="G116" t="s">
         <v>628</v>
       </c>
-      <c r="H116" s="11"/>
+      <c r="H116" s="12"/>
       <c r="I116" t="s">
         <v>635</v>
       </c>
@@ -13400,7 +13400,7 @@
       <c r="Z116" t="s">
         <v>644</v>
       </c>
-      <c r="AA116" s="10"/>
+      <c r="AA116" s="11"/>
     </row>
     <row r="117" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
@@ -13424,7 +13424,7 @@
       <c r="G117" t="s">
         <v>628</v>
       </c>
-      <c r="H117" s="11"/>
+      <c r="H117" s="12"/>
       <c r="I117" t="s">
         <v>635</v>
       </c>
@@ -13467,7 +13467,7 @@
       <c r="Z117" t="s">
         <v>644</v>
       </c>
-      <c r="AA117" s="10"/>
+      <c r="AA117" s="11"/>
     </row>
     <row r="118" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
@@ -13491,7 +13491,7 @@
       <c r="G118" t="s">
         <v>648</v>
       </c>
-      <c r="H118" s="11" t="s">
+      <c r="H118" s="12" t="s">
         <v>656</v>
       </c>
       <c r="I118" t="s">
@@ -13536,7 +13536,7 @@
       <c r="Z118" t="s">
         <v>661</v>
       </c>
-      <c r="AA118" s="10" t="s">
+      <c r="AA118" s="11" t="s">
         <v>111</v>
       </c>
     </row>
@@ -13562,7 +13562,7 @@
       <c r="G119" t="s">
         <v>648</v>
       </c>
-      <c r="H119" s="11"/>
+      <c r="H119" s="12"/>
       <c r="I119" t="s">
         <v>654</v>
       </c>
@@ -13605,7 +13605,7 @@
       <c r="Z119" t="s">
         <v>661</v>
       </c>
-      <c r="AA119" s="10"/>
+      <c r="AA119" s="11"/>
     </row>
     <row r="120" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
@@ -13629,7 +13629,7 @@
       <c r="G120" t="s">
         <v>648</v>
       </c>
-      <c r="H120" s="11"/>
+      <c r="H120" s="12"/>
       <c r="I120" t="s">
         <v>654</v>
       </c>
@@ -13672,7 +13672,7 @@
       <c r="Z120" t="s">
         <v>661</v>
       </c>
-      <c r="AA120" s="10"/>
+      <c r="AA120" s="11"/>
     </row>
     <row r="121" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
@@ -13696,7 +13696,7 @@
       <c r="G121" t="s">
         <v>648</v>
       </c>
-      <c r="H121" s="11"/>
+      <c r="H121" s="12"/>
       <c r="I121" t="s">
         <v>654</v>
       </c>
@@ -13739,7 +13739,7 @@
       <c r="Z121" t="s">
         <v>661</v>
       </c>
-      <c r="AA121" s="10"/>
+      <c r="AA121" s="11"/>
     </row>
     <row r="122" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
@@ -13763,7 +13763,7 @@
       <c r="G122" t="s">
         <v>665</v>
       </c>
-      <c r="H122" s="11" t="s">
+      <c r="H122" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I122" t="s">
@@ -13808,7 +13808,7 @@
       <c r="Z122" t="s">
         <v>677</v>
       </c>
-      <c r="AA122" s="10" t="s">
+      <c r="AA122" s="11" t="s">
         <v>117</v>
       </c>
     </row>
@@ -13834,7 +13834,7 @@
       <c r="G123" t="s">
         <v>665</v>
       </c>
-      <c r="H123" s="11"/>
+      <c r="H123" s="12"/>
       <c r="I123" t="s">
         <v>664</v>
       </c>
@@ -13877,7 +13877,7 @@
       <c r="Z123" t="s">
         <v>677</v>
       </c>
-      <c r="AA123" s="10"/>
+      <c r="AA123" s="11"/>
     </row>
     <row r="124" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
@@ -13901,7 +13901,7 @@
       <c r="G124" t="s">
         <v>665</v>
       </c>
-      <c r="H124" s="11"/>
+      <c r="H124" s="12"/>
       <c r="I124" t="s">
         <v>664</v>
       </c>
@@ -13944,7 +13944,7 @@
       <c r="Z124" t="s">
         <v>677</v>
       </c>
-      <c r="AA124" s="10"/>
+      <c r="AA124" s="11"/>
     </row>
     <row r="125" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
@@ -13968,7 +13968,7 @@
       <c r="G125" t="s">
         <v>665</v>
       </c>
-      <c r="H125" s="11"/>
+      <c r="H125" s="12"/>
       <c r="I125" t="s">
         <v>664</v>
       </c>
@@ -14011,7 +14011,7 @@
       <c r="Z125" t="s">
         <v>677</v>
       </c>
-      <c r="AA125" s="10"/>
+      <c r="AA125" s="11"/>
     </row>
     <row r="126" spans="1:28" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
@@ -14035,7 +14035,7 @@
       <c r="G126" t="s">
         <v>682</v>
       </c>
-      <c r="H126" s="11" t="s">
+      <c r="H126" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I126" t="s">
@@ -14092,10 +14092,10 @@
       <c r="Z126" t="s">
         <v>696</v>
       </c>
-      <c r="AA126" s="10" t="s">
+      <c r="AA126" s="11" t="s">
         <v>680</v>
       </c>
-      <c r="AB126" s="12" t="s">
+      <c r="AB126" s="13" t="s">
         <v>146</v>
       </c>
     </row>
@@ -14121,7 +14121,7 @@
       <c r="G127" t="s">
         <v>682</v>
       </c>
-      <c r="H127" s="11"/>
+      <c r="H127" s="12"/>
       <c r="I127" t="s">
         <v>687</v>
       </c>
@@ -14176,8 +14176,8 @@
       <c r="Z127" t="s">
         <v>696</v>
       </c>
-      <c r="AA127" s="10"/>
-      <c r="AB127" s="12"/>
+      <c r="AA127" s="11"/>
+      <c r="AB127" s="13"/>
     </row>
     <row r="128" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
@@ -14201,7 +14201,7 @@
       <c r="G128" t="s">
         <v>682</v>
       </c>
-      <c r="H128" s="11"/>
+      <c r="H128" s="12"/>
       <c r="I128" t="s">
         <v>687</v>
       </c>
@@ -14256,8 +14256,8 @@
       <c r="Z128" t="s">
         <v>696</v>
       </c>
-      <c r="AA128" s="10"/>
-      <c r="AB128" s="12"/>
+      <c r="AA128" s="11"/>
+      <c r="AB128" s="13"/>
     </row>
     <row r="129" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
@@ -14281,7 +14281,7 @@
       <c r="G129" t="s">
         <v>682</v>
       </c>
-      <c r="H129" s="11"/>
+      <c r="H129" s="12"/>
       <c r="I129" t="s">
         <v>687</v>
       </c>
@@ -14336,8 +14336,8 @@
       <c r="Z129" t="s">
         <v>696</v>
       </c>
-      <c r="AA129" s="10"/>
-      <c r="AB129" s="12"/>
+      <c r="AA129" s="11"/>
+      <c r="AB129" s="13"/>
     </row>
     <row r="130" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
@@ -14361,7 +14361,7 @@
       <c r="G130" t="s">
         <v>123</v>
       </c>
-      <c r="H130" s="11" t="s">
+      <c r="H130" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I130" t="s">
@@ -14418,10 +14418,10 @@
       <c r="Z130" t="s">
         <v>705</v>
       </c>
-      <c r="AA130" s="10" t="s">
+      <c r="AA130" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="AB130" s="13" t="s">
+      <c r="AB130" s="10" t="s">
         <v>697</v>
       </c>
     </row>
@@ -14447,7 +14447,7 @@
       <c r="G131" t="s">
         <v>123</v>
       </c>
-      <c r="H131" s="11"/>
+      <c r="H131" s="12"/>
       <c r="I131" t="s">
         <v>128</v>
       </c>
@@ -14502,8 +14502,8 @@
       <c r="Z131" t="s">
         <v>705</v>
       </c>
-      <c r="AA131" s="10"/>
-      <c r="AB131" s="13"/>
+      <c r="AA131" s="11"/>
+      <c r="AB131" s="10"/>
     </row>
     <row r="132" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
@@ -14527,7 +14527,7 @@
       <c r="G132" t="s">
         <v>123</v>
       </c>
-      <c r="H132" s="11"/>
+      <c r="H132" s="12"/>
       <c r="I132" t="s">
         <v>128</v>
       </c>
@@ -14582,8 +14582,8 @@
       <c r="Z132" t="s">
         <v>705</v>
       </c>
-      <c r="AA132" s="10"/>
-      <c r="AB132" s="13"/>
+      <c r="AA132" s="11"/>
+      <c r="AB132" s="10"/>
     </row>
     <row r="133" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
@@ -14607,7 +14607,7 @@
       <c r="G133" t="s">
         <v>123</v>
       </c>
-      <c r="H133" s="11"/>
+      <c r="H133" s="12"/>
       <c r="I133" t="s">
         <v>128</v>
       </c>
@@ -14662,8 +14662,8 @@
       <c r="Z133" t="s">
         <v>705</v>
       </c>
-      <c r="AA133" s="10"/>
-      <c r="AB133" s="13"/>
+      <c r="AA133" s="11"/>
+      <c r="AB133" s="10"/>
     </row>
     <row r="134" spans="1:28" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
@@ -14687,7 +14687,7 @@
       <c r="G134" t="s">
         <v>708</v>
       </c>
-      <c r="H134" s="11" t="s">
+      <c r="H134" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I134" t="s">
@@ -14744,7 +14744,7 @@
       <c r="Z134" t="s">
         <v>718</v>
       </c>
-      <c r="AA134" s="10" t="s">
+      <c r="AA134" s="11" t="s">
         <v>136</v>
       </c>
     </row>
@@ -14770,7 +14770,7 @@
       <c r="G135" t="s">
         <v>708</v>
       </c>
-      <c r="H135" s="11"/>
+      <c r="H135" s="12"/>
       <c r="I135" t="s">
         <v>710</v>
       </c>
@@ -14825,7 +14825,7 @@
       <c r="Z135" t="s">
         <v>718</v>
       </c>
-      <c r="AA135" s="10"/>
+      <c r="AA135" s="11"/>
     </row>
     <row r="136" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
@@ -14849,7 +14849,7 @@
       <c r="G136" t="s">
         <v>708</v>
       </c>
-      <c r="H136" s="11"/>
+      <c r="H136" s="12"/>
       <c r="I136" t="s">
         <v>710</v>
       </c>
@@ -14904,7 +14904,7 @@
       <c r="Z136" t="s">
         <v>718</v>
       </c>
-      <c r="AA136" s="10"/>
+      <c r="AA136" s="11"/>
     </row>
     <row r="137" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
@@ -14928,7 +14928,7 @@
       <c r="G137" t="s">
         <v>708</v>
       </c>
-      <c r="H137" s="11"/>
+      <c r="H137" s="12"/>
       <c r="I137" t="s">
         <v>710</v>
       </c>
@@ -14983,7 +14983,7 @@
       <c r="Z137" t="s">
         <v>718</v>
       </c>
-      <c r="AA137" s="10"/>
+      <c r="AA137" s="11"/>
     </row>
     <row r="138" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
@@ -15007,7 +15007,7 @@
       <c r="G138" t="s">
         <v>721</v>
       </c>
-      <c r="H138" s="11" t="s">
+      <c r="H138" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I138" t="s">
@@ -15052,7 +15052,7 @@
       <c r="Z138" t="s">
         <v>735</v>
       </c>
-      <c r="AA138" s="10" t="s">
+      <c r="AA138" s="11" t="s">
         <v>138</v>
       </c>
     </row>
@@ -15078,7 +15078,7 @@
       <c r="G139" t="s">
         <v>721</v>
       </c>
-      <c r="H139" s="11"/>
+      <c r="H139" s="12"/>
       <c r="I139" t="s">
         <v>727</v>
       </c>
@@ -15121,7 +15121,7 @@
       <c r="Z139" t="s">
         <v>735</v>
       </c>
-      <c r="AA139" s="10"/>
+      <c r="AA139" s="11"/>
     </row>
     <row r="140" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
@@ -15145,7 +15145,7 @@
       <c r="G140" t="s">
         <v>721</v>
       </c>
-      <c r="H140" s="11"/>
+      <c r="H140" s="12"/>
       <c r="I140" t="s">
         <v>727</v>
       </c>
@@ -15188,7 +15188,7 @@
       <c r="Z140" t="s">
         <v>735</v>
       </c>
-      <c r="AA140" s="10"/>
+      <c r="AA140" s="11"/>
     </row>
     <row r="141" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
@@ -15212,7 +15212,7 @@
       <c r="G141" t="s">
         <v>721</v>
       </c>
-      <c r="H141" s="11"/>
+      <c r="H141" s="12"/>
       <c r="I141" t="s">
         <v>727</v>
       </c>
@@ -15255,7 +15255,7 @@
       <c r="Z141" t="s">
         <v>735</v>
       </c>
-      <c r="AA141" s="10"/>
+      <c r="AA141" s="11"/>
     </row>
     <row r="142" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
@@ -15279,7 +15279,7 @@
       <c r="G142" t="s">
         <v>738</v>
       </c>
-      <c r="H142" s="11" t="s">
+      <c r="H142" s="12" t="s">
         <v>140</v>
       </c>
       <c r="I142" t="s">
@@ -15324,7 +15324,7 @@
       <c r="Z142" t="s">
         <v>752</v>
       </c>
-      <c r="AA142" s="10" t="s">
+      <c r="AA142" s="11" t="s">
         <v>141</v>
       </c>
     </row>
@@ -15350,7 +15350,7 @@
       <c r="G143" t="s">
         <v>738</v>
       </c>
-      <c r="H143" s="11"/>
+      <c r="H143" s="12"/>
       <c r="I143" t="s">
         <v>743</v>
       </c>
@@ -15393,7 +15393,7 @@
       <c r="Z143" t="s">
         <v>752</v>
       </c>
-      <c r="AA143" s="10"/>
+      <c r="AA143" s="11"/>
     </row>
     <row r="144" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
@@ -15417,7 +15417,7 @@
       <c r="G144" t="s">
         <v>738</v>
       </c>
-      <c r="H144" s="11"/>
+      <c r="H144" s="12"/>
       <c r="I144" t="s">
         <v>743</v>
       </c>
@@ -15460,7 +15460,7 @@
       <c r="Z144" t="s">
         <v>752</v>
       </c>
-      <c r="AA144" s="10"/>
+      <c r="AA144" s="11"/>
     </row>
     <row r="145" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
@@ -15484,7 +15484,7 @@
       <c r="G145" t="s">
         <v>738</v>
       </c>
-      <c r="H145" s="11"/>
+      <c r="H145" s="12"/>
       <c r="I145" t="s">
         <v>743</v>
       </c>
@@ -15527,7 +15527,7 @@
       <c r="Z145" t="s">
         <v>752</v>
       </c>
-      <c r="AA145" s="10"/>
+      <c r="AA145" s="11"/>
     </row>
     <row r="146" spans="1:28" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
@@ -15551,7 +15551,7 @@
       <c r="G146" t="s">
         <v>763</v>
       </c>
-      <c r="H146" s="11" t="s">
+      <c r="H146" s="12" t="s">
         <v>764</v>
       </c>
       <c r="I146" t="s">
@@ -15596,10 +15596,10 @@
       <c r="Z146" t="s">
         <v>773</v>
       </c>
-      <c r="AA146" s="10" t="s">
+      <c r="AA146" s="11" t="s">
         <v>765</v>
       </c>
-      <c r="AB146" s="10" t="s">
+      <c r="AB146" s="11" t="s">
         <v>753</v>
       </c>
     </row>
@@ -15625,7 +15625,7 @@
       <c r="G147" t="s">
         <v>763</v>
       </c>
-      <c r="H147" s="11"/>
+      <c r="H147" s="12"/>
       <c r="I147" t="s">
         <v>761</v>
       </c>
@@ -15668,8 +15668,8 @@
       <c r="Z147" t="s">
         <v>773</v>
       </c>
-      <c r="AA147" s="10"/>
-      <c r="AB147" s="10"/>
+      <c r="AA147" s="11"/>
+      <c r="AB147" s="11"/>
     </row>
     <row r="148" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
@@ -15693,7 +15693,7 @@
       <c r="G148" t="s">
         <v>763</v>
       </c>
-      <c r="H148" s="11"/>
+      <c r="H148" s="12"/>
       <c r="I148" t="s">
         <v>761</v>
       </c>
@@ -15736,8 +15736,8 @@
       <c r="Z148" t="s">
         <v>773</v>
       </c>
-      <c r="AA148" s="10"/>
-      <c r="AB148" s="10"/>
+      <c r="AA148" s="11"/>
+      <c r="AB148" s="11"/>
     </row>
     <row r="149" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
@@ -15761,7 +15761,7 @@
       <c r="G149" t="s">
         <v>763</v>
       </c>
-      <c r="H149" s="11"/>
+      <c r="H149" s="12"/>
       <c r="I149" t="s">
         <v>761</v>
       </c>
@@ -15804,8 +15804,8 @@
       <c r="Z149" t="s">
         <v>773</v>
       </c>
-      <c r="AA149" s="10"/>
-      <c r="AB149" s="10"/>
+      <c r="AA149" s="11"/>
+      <c r="AB149" s="11"/>
     </row>
     <row r="150" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
@@ -15829,7 +15829,7 @@
       <c r="G150" t="s">
         <v>776</v>
       </c>
-      <c r="H150" s="11" t="s">
+      <c r="H150" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I150" t="s">
@@ -15886,7 +15886,7 @@
       <c r="Z150" t="s">
         <v>794</v>
       </c>
-      <c r="AA150" s="10" t="s">
+      <c r="AA150" s="11" t="s">
         <v>786</v>
       </c>
     </row>
@@ -15912,7 +15912,7 @@
       <c r="G151" t="s">
         <v>776</v>
       </c>
-      <c r="H151" s="11"/>
+      <c r="H151" s="12"/>
       <c r="I151" t="s">
         <v>781</v>
       </c>
@@ -15967,7 +15967,7 @@
       <c r="Z151" t="s">
         <v>794</v>
       </c>
-      <c r="AA151" s="10"/>
+      <c r="AA151" s="11"/>
     </row>
     <row r="152" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
@@ -15991,7 +15991,7 @@
       <c r="G152" t="s">
         <v>776</v>
       </c>
-      <c r="H152" s="11"/>
+      <c r="H152" s="12"/>
       <c r="I152" t="s">
         <v>781</v>
       </c>
@@ -16046,7 +16046,7 @@
       <c r="Z152" t="s">
         <v>794</v>
       </c>
-      <c r="AA152" s="10"/>
+      <c r="AA152" s="11"/>
     </row>
     <row r="153" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
@@ -16070,7 +16070,7 @@
       <c r="G153" t="s">
         <v>776</v>
       </c>
-      <c r="H153" s="11"/>
+      <c r="H153" s="12"/>
       <c r="I153" t="s">
         <v>781</v>
       </c>
@@ -16125,7 +16125,7 @@
       <c r="Z153" t="s">
         <v>794</v>
       </c>
-      <c r="AA153" s="10"/>
+      <c r="AA153" s="11"/>
     </row>
     <row r="154" spans="1:28" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
@@ -16149,7 +16149,7 @@
       <c r="G154" t="s">
         <v>803</v>
       </c>
-      <c r="H154" s="11" t="s">
+      <c r="H154" s="12" t="s">
         <v>804</v>
       </c>
       <c r="I154" t="s">
@@ -16206,7 +16206,7 @@
       <c r="Z154" t="s">
         <v>813</v>
       </c>
-      <c r="AA154" s="10" t="s">
+      <c r="AA154" s="11" t="s">
         <v>814</v>
       </c>
     </row>
@@ -16232,7 +16232,7 @@
       <c r="G155" t="s">
         <v>803</v>
       </c>
-      <c r="H155" s="11"/>
+      <c r="H155" s="12"/>
       <c r="I155" t="s">
         <v>805</v>
       </c>
@@ -16287,7 +16287,7 @@
       <c r="Z155" t="s">
         <v>813</v>
       </c>
-      <c r="AA155" s="10"/>
+      <c r="AA155" s="11"/>
     </row>
     <row r="156" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
@@ -16311,7 +16311,7 @@
       <c r="G156" t="s">
         <v>803</v>
       </c>
-      <c r="H156" s="11"/>
+      <c r="H156" s="12"/>
       <c r="I156" t="s">
         <v>805</v>
       </c>
@@ -16366,7 +16366,7 @@
       <c r="Z156" t="s">
         <v>813</v>
       </c>
-      <c r="AA156" s="10"/>
+      <c r="AA156" s="11"/>
     </row>
     <row r="157" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
@@ -16390,7 +16390,7 @@
       <c r="G157" t="s">
         <v>803</v>
       </c>
-      <c r="H157" s="11"/>
+      <c r="H157" s="12"/>
       <c r="I157" t="s">
         <v>805</v>
       </c>
@@ -16445,7 +16445,7 @@
       <c r="Z157" t="s">
         <v>813</v>
       </c>
-      <c r="AA157" s="10"/>
+      <c r="AA157" s="11"/>
     </row>
     <row r="158" spans="1:28" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
@@ -16469,7 +16469,7 @@
       <c r="G158" t="s">
         <v>818</v>
       </c>
-      <c r="H158" s="11" t="s">
+      <c r="H158" s="12" t="s">
         <v>825</v>
       </c>
       <c r="I158" t="s">
@@ -16526,7 +16526,7 @@
       <c r="Z158" t="s">
         <v>813</v>
       </c>
-      <c r="AA158" s="10" t="s">
+      <c r="AA158" s="11" t="s">
         <v>832</v>
       </c>
     </row>
@@ -16552,7 +16552,7 @@
       <c r="G159" t="s">
         <v>818</v>
       </c>
-      <c r="H159" s="11"/>
+      <c r="H159" s="12"/>
       <c r="I159" t="s">
         <v>824</v>
       </c>
@@ -16607,7 +16607,7 @@
       <c r="Z159" t="s">
         <v>813</v>
       </c>
-      <c r="AA159" s="10"/>
+      <c r="AA159" s="11"/>
     </row>
     <row r="160" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
@@ -16631,7 +16631,7 @@
       <c r="G160" t="s">
         <v>818</v>
       </c>
-      <c r="H160" s="11"/>
+      <c r="H160" s="12"/>
       <c r="I160" t="s">
         <v>824</v>
       </c>
@@ -16686,7 +16686,7 @@
       <c r="Z160" t="s">
         <v>813</v>
       </c>
-      <c r="AA160" s="10"/>
+      <c r="AA160" s="11"/>
     </row>
     <row r="161" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
@@ -16710,7 +16710,7 @@
       <c r="G161" t="s">
         <v>818</v>
       </c>
-      <c r="H161" s="11"/>
+      <c r="H161" s="12"/>
       <c r="I161" t="s">
         <v>824</v>
       </c>
@@ -16765,10 +16765,86 @@
       <c r="Z161" t="s">
         <v>813</v>
       </c>
-      <c r="AA161" s="10"/>
+      <c r="AA161" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="92">
+    <mergeCell ref="AB6:AB9"/>
+    <mergeCell ref="AB10:AB13"/>
+    <mergeCell ref="H126:H129"/>
+    <mergeCell ref="AA126:AA129"/>
+    <mergeCell ref="AB126:AB129"/>
+    <mergeCell ref="H86:H89"/>
+    <mergeCell ref="AA86:AA89"/>
+    <mergeCell ref="H102:H105"/>
+    <mergeCell ref="AA102:AA105"/>
+    <mergeCell ref="H122:H125"/>
+    <mergeCell ref="AA122:AA125"/>
+    <mergeCell ref="AA98:AA101"/>
+    <mergeCell ref="H62:H65"/>
+    <mergeCell ref="AA62:AA65"/>
+    <mergeCell ref="H66:H69"/>
+    <mergeCell ref="AA66:AA69"/>
+    <mergeCell ref="H82:H85"/>
+    <mergeCell ref="AA82:AA85"/>
+    <mergeCell ref="H70:H73"/>
+    <mergeCell ref="AA70:AA73"/>
+    <mergeCell ref="H74:H77"/>
+    <mergeCell ref="AA74:AA77"/>
+    <mergeCell ref="H78:H81"/>
+    <mergeCell ref="AA78:AA81"/>
+    <mergeCell ref="H50:H53"/>
+    <mergeCell ref="AA50:AA53"/>
+    <mergeCell ref="H54:H57"/>
+    <mergeCell ref="AA54:AA57"/>
+    <mergeCell ref="H58:H61"/>
+    <mergeCell ref="AA58:AA61"/>
+    <mergeCell ref="H2:H5"/>
+    <mergeCell ref="AA2:AA5"/>
+    <mergeCell ref="H6:H9"/>
+    <mergeCell ref="AA6:AA9"/>
+    <mergeCell ref="H10:H13"/>
+    <mergeCell ref="AA10:AA13"/>
+    <mergeCell ref="AA94:AA97"/>
+    <mergeCell ref="H98:H101"/>
+    <mergeCell ref="H14:H17"/>
+    <mergeCell ref="L14:L17"/>
+    <mergeCell ref="AA14:AA17"/>
+    <mergeCell ref="H18:H21"/>
+    <mergeCell ref="AA18:AA21"/>
+    <mergeCell ref="H30:H33"/>
+    <mergeCell ref="AA30:AA33"/>
+    <mergeCell ref="H34:H37"/>
+    <mergeCell ref="AA34:AA37"/>
+    <mergeCell ref="H38:H41"/>
+    <mergeCell ref="AA38:AA41"/>
+    <mergeCell ref="H42:H45"/>
+    <mergeCell ref="AA42:AA45"/>
+    <mergeCell ref="H46:H49"/>
+    <mergeCell ref="H138:H141"/>
+    <mergeCell ref="AA138:AA141"/>
+    <mergeCell ref="H22:H25"/>
+    <mergeCell ref="AA22:AA25"/>
+    <mergeCell ref="H26:H29"/>
+    <mergeCell ref="H118:H121"/>
+    <mergeCell ref="AA118:AA121"/>
+    <mergeCell ref="H90:H93"/>
+    <mergeCell ref="AA90:AA93"/>
+    <mergeCell ref="H106:H109"/>
+    <mergeCell ref="AA106:AA109"/>
+    <mergeCell ref="H110:H113"/>
+    <mergeCell ref="AA110:AA113"/>
+    <mergeCell ref="H114:H117"/>
+    <mergeCell ref="AA114:AA117"/>
+    <mergeCell ref="H94:H97"/>
+    <mergeCell ref="L90:L93"/>
+    <mergeCell ref="AB18:AB21"/>
+    <mergeCell ref="AB26:AB29"/>
+    <mergeCell ref="AB30:AB33"/>
+    <mergeCell ref="AB54:AB57"/>
+    <mergeCell ref="AB62:AB65"/>
+    <mergeCell ref="AA26:AA29"/>
+    <mergeCell ref="AA46:AA49"/>
     <mergeCell ref="AB130:AB133"/>
     <mergeCell ref="AB146:AB149"/>
     <mergeCell ref="H154:H157"/>
@@ -16785,82 +16861,6 @@
     <mergeCell ref="AA130:AA133"/>
     <mergeCell ref="H134:H137"/>
     <mergeCell ref="AA134:AA137"/>
-    <mergeCell ref="L90:L93"/>
-    <mergeCell ref="AB18:AB21"/>
-    <mergeCell ref="AB26:AB29"/>
-    <mergeCell ref="AB30:AB33"/>
-    <mergeCell ref="AB54:AB57"/>
-    <mergeCell ref="AB62:AB65"/>
-    <mergeCell ref="AA26:AA29"/>
-    <mergeCell ref="AA46:AA49"/>
-    <mergeCell ref="H138:H141"/>
-    <mergeCell ref="AA138:AA141"/>
-    <mergeCell ref="H22:H25"/>
-    <mergeCell ref="AA22:AA25"/>
-    <mergeCell ref="H26:H29"/>
-    <mergeCell ref="H118:H121"/>
-    <mergeCell ref="AA118:AA121"/>
-    <mergeCell ref="H90:H93"/>
-    <mergeCell ref="AA90:AA93"/>
-    <mergeCell ref="H106:H109"/>
-    <mergeCell ref="AA106:AA109"/>
-    <mergeCell ref="H110:H113"/>
-    <mergeCell ref="AA110:AA113"/>
-    <mergeCell ref="H114:H117"/>
-    <mergeCell ref="AA114:AA117"/>
-    <mergeCell ref="H94:H97"/>
-    <mergeCell ref="AA94:AA97"/>
-    <mergeCell ref="H98:H101"/>
-    <mergeCell ref="H14:H17"/>
-    <mergeCell ref="L14:L17"/>
-    <mergeCell ref="AA14:AA17"/>
-    <mergeCell ref="H18:H21"/>
-    <mergeCell ref="AA18:AA21"/>
-    <mergeCell ref="H30:H33"/>
-    <mergeCell ref="AA30:AA33"/>
-    <mergeCell ref="H34:H37"/>
-    <mergeCell ref="AA34:AA37"/>
-    <mergeCell ref="H38:H41"/>
-    <mergeCell ref="AA38:AA41"/>
-    <mergeCell ref="H42:H45"/>
-    <mergeCell ref="AA42:AA45"/>
-    <mergeCell ref="H46:H49"/>
-    <mergeCell ref="H2:H5"/>
-    <mergeCell ref="AA2:AA5"/>
-    <mergeCell ref="H6:H9"/>
-    <mergeCell ref="AA6:AA9"/>
-    <mergeCell ref="H10:H13"/>
-    <mergeCell ref="AA10:AA13"/>
-    <mergeCell ref="H50:H53"/>
-    <mergeCell ref="AA50:AA53"/>
-    <mergeCell ref="H54:H57"/>
-    <mergeCell ref="AA54:AA57"/>
-    <mergeCell ref="H58:H61"/>
-    <mergeCell ref="AA58:AA61"/>
-    <mergeCell ref="H82:H85"/>
-    <mergeCell ref="AA82:AA85"/>
-    <mergeCell ref="H70:H73"/>
-    <mergeCell ref="AA70:AA73"/>
-    <mergeCell ref="H74:H77"/>
-    <mergeCell ref="AA74:AA77"/>
-    <mergeCell ref="H78:H81"/>
-    <mergeCell ref="AA78:AA81"/>
-    <mergeCell ref="AB6:AB9"/>
-    <mergeCell ref="AB10:AB13"/>
-    <mergeCell ref="H126:H129"/>
-    <mergeCell ref="AA126:AA129"/>
-    <mergeCell ref="AB126:AB129"/>
-    <mergeCell ref="H86:H89"/>
-    <mergeCell ref="AA86:AA89"/>
-    <mergeCell ref="H102:H105"/>
-    <mergeCell ref="AA102:AA105"/>
-    <mergeCell ref="H122:H125"/>
-    <mergeCell ref="AA122:AA125"/>
-    <mergeCell ref="AA98:AA101"/>
-    <mergeCell ref="H62:H65"/>
-    <mergeCell ref="AA62:AA65"/>
-    <mergeCell ref="H66:H69"/>
-    <mergeCell ref="AA66:AA69"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Resultats_modeles_coleo_2024.xlsx
+++ b/Resultats_modeles_coleo_2024.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192"/>
   </bookViews>
   <sheets>
     <sheet name="Enssillage_resultats_GLMM" sheetId="1" r:id="rId1"/>
@@ -7033,72 +7033,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -7192,14 +7126,26 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7210,20 +7156,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7234,9 +7183,60 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7657,7 +7657,7 @@
       <c r="G2" t="s">
         <v>154</v>
       </c>
-      <c r="H2" s="80" t="s">
+      <c r="H2" s="123" t="s">
         <v>89</v>
       </c>
       <c r="I2" t="s">
@@ -7714,7 +7714,7 @@
       <c r="Z2" t="s">
         <v>173</v>
       </c>
-      <c r="AA2" s="79" t="s">
+      <c r="AA2" s="122" t="s">
         <v>45</v>
       </c>
     </row>
@@ -7740,7 +7740,7 @@
       <c r="G3" t="s">
         <v>154</v>
       </c>
-      <c r="H3" s="80"/>
+      <c r="H3" s="123"/>
       <c r="I3" t="s">
         <v>150</v>
       </c>
@@ -7795,7 +7795,7 @@
       <c r="Z3" t="s">
         <v>173</v>
       </c>
-      <c r="AA3" s="79"/>
+      <c r="AA3" s="122"/>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -7819,7 +7819,7 @@
       <c r="G4" t="s">
         <v>154</v>
       </c>
-      <c r="H4" s="80"/>
+      <c r="H4" s="123"/>
       <c r="I4" t="s">
         <v>150</v>
       </c>
@@ -7874,7 +7874,7 @@
       <c r="Z4" t="s">
         <v>173</v>
       </c>
-      <c r="AA4" s="79"/>
+      <c r="AA4" s="122"/>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -7898,7 +7898,7 @@
       <c r="G5" t="s">
         <v>154</v>
       </c>
-      <c r="H5" s="80"/>
+      <c r="H5" s="123"/>
       <c r="I5" t="s">
         <v>150</v>
       </c>
@@ -7953,7 +7953,7 @@
       <c r="Z5" t="s">
         <v>173</v>
       </c>
-      <c r="AA5" s="79"/>
+      <c r="AA5" s="122"/>
     </row>
     <row r="6" spans="1:29" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -7977,7 +7977,7 @@
       <c r="G6" t="s">
         <v>184</v>
       </c>
-      <c r="H6" s="80" t="s">
+      <c r="H6" s="123" t="s">
         <v>89</v>
       </c>
       <c r="I6" t="s">
@@ -8034,10 +8034,10 @@
       <c r="Z6" t="s">
         <v>182</v>
       </c>
-      <c r="AA6" s="79" t="s">
+      <c r="AA6" s="122" t="s">
         <v>46</v>
       </c>
-      <c r="AB6" s="79" t="s">
+      <c r="AB6" s="122" t="s">
         <v>174</v>
       </c>
     </row>
@@ -8063,7 +8063,7 @@
       <c r="G7" t="s">
         <v>184</v>
       </c>
-      <c r="H7" s="80"/>
+      <c r="H7" s="123"/>
       <c r="I7" t="s">
         <v>189</v>
       </c>
@@ -8118,8 +8118,8 @@
       <c r="Z7" t="s">
         <v>182</v>
       </c>
-      <c r="AA7" s="79"/>
-      <c r="AB7" s="79"/>
+      <c r="AA7" s="122"/>
+      <c r="AB7" s="122"/>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -8143,7 +8143,7 @@
       <c r="G8" t="s">
         <v>184</v>
       </c>
-      <c r="H8" s="80"/>
+      <c r="H8" s="123"/>
       <c r="I8" t="s">
         <v>189</v>
       </c>
@@ -8198,8 +8198,8 @@
       <c r="Z8" t="s">
         <v>182</v>
       </c>
-      <c r="AA8" s="79"/>
-      <c r="AB8" s="79"/>
+      <c r="AA8" s="122"/>
+      <c r="AB8" s="122"/>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -8223,7 +8223,7 @@
       <c r="G9" t="s">
         <v>184</v>
       </c>
-      <c r="H9" s="80"/>
+      <c r="H9" s="123"/>
       <c r="I9" t="s">
         <v>189</v>
       </c>
@@ -8278,8 +8278,8 @@
       <c r="Z9" t="s">
         <v>182</v>
       </c>
-      <c r="AA9" s="79"/>
-      <c r="AB9" s="79"/>
+      <c r="AA9" s="122"/>
+      <c r="AB9" s="122"/>
     </row>
     <row r="10" spans="1:29" ht="120" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -8303,7 +8303,7 @@
       <c r="G10" t="s">
         <v>194</v>
       </c>
-      <c r="H10" s="80" t="s">
+      <c r="H10" s="123" t="s">
         <v>89</v>
       </c>
       <c r="I10" t="s">
@@ -8360,10 +8360,10 @@
       <c r="Z10" t="s">
         <v>208</v>
       </c>
-      <c r="AA10" s="79" t="s">
+      <c r="AA10" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="AB10" s="79" t="s">
+      <c r="AB10" s="122" t="s">
         <v>209</v>
       </c>
     </row>
@@ -8389,7 +8389,7 @@
       <c r="G11" t="s">
         <v>194</v>
       </c>
-      <c r="H11" s="80"/>
+      <c r="H11" s="123"/>
       <c r="I11" t="s">
         <v>199</v>
       </c>
@@ -8444,8 +8444,8 @@
       <c r="Z11" t="s">
         <v>208</v>
       </c>
-      <c r="AA11" s="79"/>
-      <c r="AB11" s="79"/>
+      <c r="AA11" s="122"/>
+      <c r="AB11" s="122"/>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -8469,7 +8469,7 @@
       <c r="G12" t="s">
         <v>194</v>
       </c>
-      <c r="H12" s="80"/>
+      <c r="H12" s="123"/>
       <c r="I12" t="s">
         <v>199</v>
       </c>
@@ -8524,8 +8524,8 @@
       <c r="Z12" t="s">
         <v>208</v>
       </c>
-      <c r="AA12" s="79"/>
-      <c r="AB12" s="79"/>
+      <c r="AA12" s="122"/>
+      <c r="AB12" s="122"/>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -8549,7 +8549,7 @@
       <c r="G13" t="s">
         <v>194</v>
       </c>
-      <c r="H13" s="80"/>
+      <c r="H13" s="123"/>
       <c r="I13" t="s">
         <v>199</v>
       </c>
@@ -8604,8 +8604,8 @@
       <c r="Z13" t="s">
         <v>208</v>
       </c>
-      <c r="AA13" s="79"/>
-      <c r="AB13" s="79"/>
+      <c r="AA13" s="122"/>
+      <c r="AB13" s="122"/>
     </row>
     <row r="14" spans="1:29" ht="131.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -8629,7 +8629,7 @@
       <c r="G14" t="s">
         <v>211</v>
       </c>
-      <c r="H14" s="80" t="s">
+      <c r="H14" s="123" t="s">
         <v>41</v>
       </c>
       <c r="I14" t="s">
@@ -8641,7 +8641,7 @@
       <c r="K14" t="s">
         <v>20</v>
       </c>
-      <c r="L14" s="79" t="s">
+      <c r="L14" s="122" t="s">
         <v>44</v>
       </c>
       <c r="M14" t="s">
@@ -8686,7 +8686,7 @@
       <c r="Z14" t="s">
         <v>223</v>
       </c>
-      <c r="AA14" s="79" t="s">
+      <c r="AA14" s="122" t="s">
         <v>48</v>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       <c r="G15" t="s">
         <v>211</v>
       </c>
-      <c r="H15" s="80"/>
+      <c r="H15" s="123"/>
       <c r="I15" t="s">
         <v>213</v>
       </c>
@@ -8722,7 +8722,7 @@
       <c r="K15" t="s">
         <v>20</v>
       </c>
-      <c r="L15" s="79"/>
+      <c r="L15" s="122"/>
       <c r="M15" t="s">
         <v>15</v>
       </c>
@@ -8765,7 +8765,7 @@
       <c r="Z15" t="s">
         <v>223</v>
       </c>
-      <c r="AA15" s="79"/>
+      <c r="AA15" s="122"/>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -8789,7 +8789,7 @@
       <c r="G16" t="s">
         <v>211</v>
       </c>
-      <c r="H16" s="80"/>
+      <c r="H16" s="123"/>
       <c r="I16" t="s">
         <v>213</v>
       </c>
@@ -8799,7 +8799,7 @@
       <c r="K16" t="s">
         <v>20</v>
       </c>
-      <c r="L16" s="79"/>
+      <c r="L16" s="122"/>
       <c r="M16" t="s">
         <v>15</v>
       </c>
@@ -8842,7 +8842,7 @@
       <c r="Z16" t="s">
         <v>223</v>
       </c>
-      <c r="AA16" s="79"/>
+      <c r="AA16" s="122"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
@@ -8866,7 +8866,7 @@
       <c r="G17" t="s">
         <v>211</v>
       </c>
-      <c r="H17" s="80"/>
+      <c r="H17" s="123"/>
       <c r="I17" t="s">
         <v>213</v>
       </c>
@@ -8876,7 +8876,7 @@
       <c r="K17" t="s">
         <v>20</v>
       </c>
-      <c r="L17" s="79"/>
+      <c r="L17" s="122"/>
       <c r="M17" t="s">
         <v>15</v>
       </c>
@@ -8919,7 +8919,7 @@
       <c r="Z17" t="s">
         <v>223</v>
       </c>
-      <c r="AA17" s="79"/>
+      <c r="AA17" s="122"/>
     </row>
     <row r="18" spans="1:28" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -8943,7 +8943,7 @@
       <c r="G18" t="s">
         <v>225</v>
       </c>
-      <c r="H18" s="80" t="s">
+      <c r="H18" s="123" t="s">
         <v>41</v>
       </c>
       <c r="I18" t="s">
@@ -9000,10 +9000,10 @@
       <c r="Z18" t="s">
         <v>240</v>
       </c>
-      <c r="AA18" s="79" t="s">
+      <c r="AA18" s="122" t="s">
         <v>233</v>
       </c>
-      <c r="AB18" s="79" t="s">
+      <c r="AB18" s="122" t="s">
         <v>241</v>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       <c r="G19" t="s">
         <v>225</v>
       </c>
-      <c r="H19" s="80"/>
+      <c r="H19" s="123"/>
       <c r="I19" t="s">
         <v>230</v>
       </c>
@@ -9084,8 +9084,8 @@
       <c r="Z19" t="s">
         <v>240</v>
       </c>
-      <c r="AA19" s="79"/>
-      <c r="AB19" s="79"/>
+      <c r="AA19" s="122"/>
+      <c r="AB19" s="122"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
@@ -9109,7 +9109,7 @@
       <c r="G20" t="s">
         <v>225</v>
       </c>
-      <c r="H20" s="80"/>
+      <c r="H20" s="123"/>
       <c r="I20" t="s">
         <v>230</v>
       </c>
@@ -9164,8 +9164,8 @@
       <c r="Z20" t="s">
         <v>240</v>
       </c>
-      <c r="AA20" s="79"/>
-      <c r="AB20" s="79"/>
+      <c r="AA20" s="122"/>
+      <c r="AB20" s="122"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
@@ -9189,7 +9189,7 @@
       <c r="G21" t="s">
         <v>225</v>
       </c>
-      <c r="H21" s="80"/>
+      <c r="H21" s="123"/>
       <c r="I21" t="s">
         <v>230</v>
       </c>
@@ -9244,8 +9244,8 @@
       <c r="Z21" t="s">
         <v>240</v>
       </c>
-      <c r="AA21" s="79"/>
-      <c r="AB21" s="79"/>
+      <c r="AA21" s="122"/>
+      <c r="AB21" s="122"/>
     </row>
     <row r="22" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
@@ -9269,7 +9269,7 @@
       <c r="G22" t="s">
         <v>243</v>
       </c>
-      <c r="H22" s="80" t="s">
+      <c r="H22" s="123" t="s">
         <v>41</v>
       </c>
       <c r="I22" t="s">
@@ -9314,7 +9314,7 @@
       <c r="Z22" t="s">
         <v>258</v>
       </c>
-      <c r="AA22" s="79" t="s">
+      <c r="AA22" s="122" t="s">
         <v>52</v>
       </c>
     </row>
@@ -9340,7 +9340,7 @@
       <c r="G23" t="s">
         <v>243</v>
       </c>
-      <c r="H23" s="80"/>
+      <c r="H23" s="123"/>
       <c r="I23" t="s">
         <v>249</v>
       </c>
@@ -9383,7 +9383,7 @@
       <c r="Z23" t="s">
         <v>258</v>
       </c>
-      <c r="AA23" s="79"/>
+      <c r="AA23" s="122"/>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
@@ -9407,7 +9407,7 @@
       <c r="G24" t="s">
         <v>243</v>
       </c>
-      <c r="H24" s="80"/>
+      <c r="H24" s="123"/>
       <c r="I24" t="s">
         <v>249</v>
       </c>
@@ -9450,7 +9450,7 @@
       <c r="Z24" t="s">
         <v>258</v>
       </c>
-      <c r="AA24" s="79"/>
+      <c r="AA24" s="122"/>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
@@ -9474,7 +9474,7 @@
       <c r="G25" t="s">
         <v>243</v>
       </c>
-      <c r="H25" s="80"/>
+      <c r="H25" s="123"/>
       <c r="I25" t="s">
         <v>249</v>
       </c>
@@ -9517,7 +9517,7 @@
       <c r="Z25" t="s">
         <v>258</v>
       </c>
-      <c r="AA25" s="79"/>
+      <c r="AA25" s="122"/>
     </row>
     <row r="26" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
@@ -9541,7 +9541,7 @@
       <c r="G26" t="s">
         <v>261</v>
       </c>
-      <c r="H26" s="80" t="s">
+      <c r="H26" s="123" t="s">
         <v>41</v>
       </c>
       <c r="I26" t="s">
@@ -9598,10 +9598,10 @@
       <c r="Z26" t="s">
         <v>278</v>
       </c>
-      <c r="AA26" s="79" t="s">
+      <c r="AA26" s="122" t="s">
         <v>54</v>
       </c>
-      <c r="AB26" s="79" t="s">
+      <c r="AB26" s="122" t="s">
         <v>279</v>
       </c>
     </row>
@@ -9627,7 +9627,7 @@
       <c r="G27" t="s">
         <v>261</v>
       </c>
-      <c r="H27" s="80"/>
+      <c r="H27" s="123"/>
       <c r="I27" t="s">
         <v>266</v>
       </c>
@@ -9682,8 +9682,8 @@
       <c r="Z27" t="s">
         <v>278</v>
       </c>
-      <c r="AA27" s="79"/>
-      <c r="AB27" s="79"/>
+      <c r="AA27" s="122"/>
+      <c r="AB27" s="122"/>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -9707,7 +9707,7 @@
       <c r="G28" t="s">
         <v>261</v>
       </c>
-      <c r="H28" s="80"/>
+      <c r="H28" s="123"/>
       <c r="I28" t="s">
         <v>266</v>
       </c>
@@ -9762,8 +9762,8 @@
       <c r="Z28" t="s">
         <v>278</v>
       </c>
-      <c r="AA28" s="79"/>
-      <c r="AB28" s="79"/>
+      <c r="AA28" s="122"/>
+      <c r="AB28" s="122"/>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -9787,7 +9787,7 @@
       <c r="G29" t="s">
         <v>261</v>
       </c>
-      <c r="H29" s="80"/>
+      <c r="H29" s="123"/>
       <c r="I29" t="s">
         <v>266</v>
       </c>
@@ -9842,8 +9842,8 @@
       <c r="Z29" t="s">
         <v>278</v>
       </c>
-      <c r="AA29" s="79"/>
-      <c r="AB29" s="79"/>
+      <c r="AA29" s="122"/>
+      <c r="AB29" s="122"/>
     </row>
     <row r="30" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
@@ -9867,7 +9867,7 @@
       <c r="G30" t="s">
         <v>282</v>
       </c>
-      <c r="H30" s="80" t="s">
+      <c r="H30" s="123" t="s">
         <v>41</v>
       </c>
       <c r="I30" t="s">
@@ -9924,10 +9924,10 @@
       <c r="Z30" t="s">
         <v>298</v>
       </c>
-      <c r="AA30" s="79" t="s">
+      <c r="AA30" s="122" t="s">
         <v>56</v>
       </c>
-      <c r="AB30" s="79" t="s">
+      <c r="AB30" s="122" t="s">
         <v>299</v>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       <c r="G31" t="s">
         <v>282</v>
       </c>
-      <c r="H31" s="80"/>
+      <c r="H31" s="123"/>
       <c r="I31" t="s">
         <v>287</v>
       </c>
@@ -10008,8 +10008,8 @@
       <c r="Z31" t="s">
         <v>298</v>
       </c>
-      <c r="AA31" s="79"/>
-      <c r="AB31" s="79"/>
+      <c r="AA31" s="122"/>
+      <c r="AB31" s="122"/>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
@@ -10033,7 +10033,7 @@
       <c r="G32" t="s">
         <v>282</v>
       </c>
-      <c r="H32" s="80"/>
+      <c r="H32" s="123"/>
       <c r="I32" t="s">
         <v>287</v>
       </c>
@@ -10088,8 +10088,8 @@
       <c r="Z32" t="s">
         <v>298</v>
       </c>
-      <c r="AA32" s="79"/>
-      <c r="AB32" s="79"/>
+      <c r="AA32" s="122"/>
+      <c r="AB32" s="122"/>
     </row>
     <row r="33" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
@@ -10113,7 +10113,7 @@
       <c r="G33" t="s">
         <v>282</v>
       </c>
-      <c r="H33" s="80"/>
+      <c r="H33" s="123"/>
       <c r="I33" t="s">
         <v>287</v>
       </c>
@@ -10168,8 +10168,8 @@
       <c r="Z33" t="s">
         <v>298</v>
       </c>
-      <c r="AA33" s="79"/>
-      <c r="AB33" s="79"/>
+      <c r="AA33" s="122"/>
+      <c r="AB33" s="122"/>
     </row>
     <row r="34" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
@@ -10193,7 +10193,7 @@
       <c r="G34" t="s">
         <v>302</v>
       </c>
-      <c r="H34" s="80" t="s">
+      <c r="H34" s="123" t="s">
         <v>41</v>
       </c>
       <c r="I34" t="s">
@@ -10238,7 +10238,7 @@
       <c r="Z34" t="s">
         <v>315</v>
       </c>
-      <c r="AA34" s="79" t="s">
+      <c r="AA34" s="122" t="s">
         <v>835</v>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
       <c r="G35" t="s">
         <v>302</v>
       </c>
-      <c r="H35" s="80"/>
+      <c r="H35" s="123"/>
       <c r="I35" t="s">
         <v>306</v>
       </c>
@@ -10307,7 +10307,7 @@
       <c r="Z35" t="s">
         <v>315</v>
       </c>
-      <c r="AA35" s="79"/>
+      <c r="AA35" s="122"/>
     </row>
     <row r="36" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
@@ -10331,7 +10331,7 @@
       <c r="G36" t="s">
         <v>302</v>
       </c>
-      <c r="H36" s="80"/>
+      <c r="H36" s="123"/>
       <c r="I36" t="s">
         <v>306</v>
       </c>
@@ -10374,7 +10374,7 @@
       <c r="Z36" t="s">
         <v>315</v>
       </c>
-      <c r="AA36" s="79"/>
+      <c r="AA36" s="122"/>
     </row>
     <row r="37" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
@@ -10398,7 +10398,7 @@
       <c r="G37" t="s">
         <v>302</v>
       </c>
-      <c r="H37" s="80"/>
+      <c r="H37" s="123"/>
       <c r="I37" t="s">
         <v>306</v>
       </c>
@@ -10441,7 +10441,7 @@
       <c r="Z37" t="s">
         <v>315</v>
       </c>
-      <c r="AA37" s="79"/>
+      <c r="AA37" s="122"/>
     </row>
     <row r="38" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
@@ -10465,7 +10465,7 @@
       <c r="G38" t="s">
         <v>318</v>
       </c>
-      <c r="H38" s="80" t="s">
+      <c r="H38" s="123" t="s">
         <v>41</v>
       </c>
       <c r="I38" t="s">
@@ -10510,7 +10510,7 @@
       <c r="Z38" t="s">
         <v>330</v>
       </c>
-      <c r="AA38" s="79" t="s">
+      <c r="AA38" s="122" t="s">
         <v>834</v>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       <c r="G39" t="s">
         <v>318</v>
       </c>
-      <c r="H39" s="80"/>
+      <c r="H39" s="123"/>
       <c r="I39" t="s">
         <v>322</v>
       </c>
@@ -10579,7 +10579,7 @@
       <c r="Z39" t="s">
         <v>330</v>
       </c>
-      <c r="AA39" s="79"/>
+      <c r="AA39" s="122"/>
     </row>
     <row r="40" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
@@ -10603,7 +10603,7 @@
       <c r="G40" t="s">
         <v>318</v>
       </c>
-      <c r="H40" s="80"/>
+      <c r="H40" s="123"/>
       <c r="I40" t="s">
         <v>322</v>
       </c>
@@ -10646,7 +10646,7 @@
       <c r="Z40" t="s">
         <v>330</v>
       </c>
-      <c r="AA40" s="79"/>
+      <c r="AA40" s="122"/>
     </row>
     <row r="41" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
@@ -10670,7 +10670,7 @@
       <c r="G41" t="s">
         <v>318</v>
       </c>
-      <c r="H41" s="80"/>
+      <c r="H41" s="123"/>
       <c r="I41" t="s">
         <v>322</v>
       </c>
@@ -10713,7 +10713,7 @@
       <c r="Z41" t="s">
         <v>330</v>
       </c>
-      <c r="AA41" s="79"/>
+      <c r="AA41" s="122"/>
     </row>
     <row r="42" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
@@ -10737,7 +10737,7 @@
       <c r="G42" t="s">
         <v>332</v>
       </c>
-      <c r="H42" s="80" t="s">
+      <c r="H42" s="123" t="s">
         <v>41</v>
       </c>
       <c r="I42" t="s">
@@ -10782,7 +10782,7 @@
       <c r="Z42" t="s">
         <v>346</v>
       </c>
-      <c r="AA42" s="79" t="s">
+      <c r="AA42" s="122" t="s">
         <v>338</v>
       </c>
     </row>
@@ -10808,7 +10808,7 @@
       <c r="G43" t="s">
         <v>332</v>
       </c>
-      <c r="H43" s="80"/>
+      <c r="H43" s="123"/>
       <c r="I43" t="s">
         <v>336</v>
       </c>
@@ -10851,7 +10851,7 @@
       <c r="Z43" t="s">
         <v>346</v>
       </c>
-      <c r="AA43" s="79"/>
+      <c r="AA43" s="122"/>
     </row>
     <row r="44" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
@@ -10875,7 +10875,7 @@
       <c r="G44" t="s">
         <v>332</v>
       </c>
-      <c r="H44" s="80"/>
+      <c r="H44" s="123"/>
       <c r="I44" t="s">
         <v>336</v>
       </c>
@@ -10918,7 +10918,7 @@
       <c r="Z44" t="s">
         <v>346</v>
       </c>
-      <c r="AA44" s="79"/>
+      <c r="AA44" s="122"/>
     </row>
     <row r="45" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
@@ -10942,7 +10942,7 @@
       <c r="G45" t="s">
         <v>332</v>
       </c>
-      <c r="H45" s="80"/>
+      <c r="H45" s="123"/>
       <c r="I45" t="s">
         <v>336</v>
       </c>
@@ -10985,7 +10985,7 @@
       <c r="Z45" t="s">
         <v>346</v>
       </c>
-      <c r="AA45" s="79"/>
+      <c r="AA45" s="122"/>
     </row>
     <row r="46" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
@@ -11009,7 +11009,7 @@
       <c r="G46" t="s">
         <v>348</v>
       </c>
-      <c r="H46" s="80" t="s">
+      <c r="H46" s="123" t="s">
         <v>41</v>
       </c>
       <c r="I46" t="s">
@@ -11054,7 +11054,7 @@
       <c r="Z46" t="s">
         <v>362</v>
       </c>
-      <c r="AA46" s="79" t="s">
+      <c r="AA46" s="122" t="s">
         <v>355</v>
       </c>
     </row>
@@ -11080,7 +11080,7 @@
       <c r="G47" t="s">
         <v>348</v>
       </c>
-      <c r="H47" s="80"/>
+      <c r="H47" s="123"/>
       <c r="I47" t="s">
         <v>353</v>
       </c>
@@ -11123,7 +11123,7 @@
       <c r="Z47" t="s">
         <v>362</v>
       </c>
-      <c r="AA47" s="79"/>
+      <c r="AA47" s="122"/>
     </row>
     <row r="48" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
@@ -11147,7 +11147,7 @@
       <c r="G48" t="s">
         <v>348</v>
       </c>
-      <c r="H48" s="80"/>
+      <c r="H48" s="123"/>
       <c r="I48" t="s">
         <v>353</v>
       </c>
@@ -11190,7 +11190,7 @@
       <c r="Z48" t="s">
         <v>362</v>
       </c>
-      <c r="AA48" s="79"/>
+      <c r="AA48" s="122"/>
     </row>
     <row r="49" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
@@ -11214,7 +11214,7 @@
       <c r="G49" t="s">
         <v>348</v>
       </c>
-      <c r="H49" s="80"/>
+      <c r="H49" s="123"/>
       <c r="I49" t="s">
         <v>353</v>
       </c>
@@ -11257,7 +11257,7 @@
       <c r="Z49" t="s">
         <v>362</v>
       </c>
-      <c r="AA49" s="79"/>
+      <c r="AA49" s="122"/>
     </row>
     <row r="50" spans="1:28" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
@@ -11281,7 +11281,7 @@
       <c r="G50" t="s">
         <v>364</v>
       </c>
-      <c r="H50" s="80" t="s">
+      <c r="H50" s="123" t="s">
         <v>369</v>
       </c>
       <c r="I50" t="s">
@@ -11338,7 +11338,7 @@
       <c r="Z50" t="s">
         <v>382</v>
       </c>
-      <c r="AA50" s="79" t="s">
+      <c r="AA50" s="122" t="s">
         <v>375</v>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       <c r="G51" t="s">
         <v>364</v>
       </c>
-      <c r="H51" s="80"/>
+      <c r="H51" s="123"/>
       <c r="I51" t="s">
         <v>371</v>
       </c>
@@ -11419,7 +11419,7 @@
       <c r="Z51" t="s">
         <v>382</v>
       </c>
-      <c r="AA51" s="79"/>
+      <c r="AA51" s="122"/>
     </row>
     <row r="52" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
@@ -11443,7 +11443,7 @@
       <c r="G52" t="s">
         <v>364</v>
       </c>
-      <c r="H52" s="80"/>
+      <c r="H52" s="123"/>
       <c r="I52" t="s">
         <v>371</v>
       </c>
@@ -11498,7 +11498,7 @@
       <c r="Z52" t="s">
         <v>382</v>
       </c>
-      <c r="AA52" s="79"/>
+      <c r="AA52" s="122"/>
     </row>
     <row r="53" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
@@ -11522,7 +11522,7 @@
       <c r="G53" t="s">
         <v>364</v>
       </c>
-      <c r="H53" s="80"/>
+      <c r="H53" s="123"/>
       <c r="I53" t="s">
         <v>371</v>
       </c>
@@ -11577,7 +11577,7 @@
       <c r="Z53" t="s">
         <v>382</v>
       </c>
-      <c r="AA53" s="79"/>
+      <c r="AA53" s="122"/>
     </row>
     <row r="54" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
@@ -11601,7 +11601,7 @@
       <c r="G54" t="s">
         <v>385</v>
       </c>
-      <c r="H54" s="80" t="s">
+      <c r="H54" s="123" t="s">
         <v>68</v>
       </c>
       <c r="I54" t="s">
@@ -11646,10 +11646,10 @@
       <c r="Z54" t="s">
         <v>398</v>
       </c>
-      <c r="AA54" s="79" t="s">
+      <c r="AA54" s="122" t="s">
         <v>69</v>
       </c>
-      <c r="AB54" s="79" t="s">
+      <c r="AB54" s="122" t="s">
         <v>399</v>
       </c>
     </row>
@@ -11675,7 +11675,7 @@
       <c r="G55" t="s">
         <v>385</v>
       </c>
-      <c r="H55" s="80"/>
+      <c r="H55" s="123"/>
       <c r="I55" t="s">
         <v>392</v>
       </c>
@@ -11718,8 +11718,8 @@
       <c r="Z55" t="s">
         <v>398</v>
       </c>
-      <c r="AA55" s="79"/>
-      <c r="AB55" s="79"/>
+      <c r="AA55" s="122"/>
+      <c r="AB55" s="122"/>
     </row>
     <row r="56" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
@@ -11743,7 +11743,7 @@
       <c r="G56" t="s">
         <v>385</v>
       </c>
-      <c r="H56" s="80"/>
+      <c r="H56" s="123"/>
       <c r="I56" t="s">
         <v>392</v>
       </c>
@@ -11786,8 +11786,8 @@
       <c r="Z56" t="s">
         <v>398</v>
       </c>
-      <c r="AA56" s="79"/>
-      <c r="AB56" s="79"/>
+      <c r="AA56" s="122"/>
+      <c r="AB56" s="122"/>
     </row>
     <row r="57" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
@@ -11811,7 +11811,7 @@
       <c r="G57" t="s">
         <v>385</v>
       </c>
-      <c r="H57" s="80"/>
+      <c r="H57" s="123"/>
       <c r="I57" t="s">
         <v>392</v>
       </c>
@@ -11854,8 +11854,8 @@
       <c r="Z57" t="s">
         <v>398</v>
       </c>
-      <c r="AA57" s="79"/>
-      <c r="AB57" s="79"/>
+      <c r="AA57" s="122"/>
+      <c r="AB57" s="122"/>
     </row>
     <row r="58" spans="1:28" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
@@ -11879,7 +11879,7 @@
       <c r="G58" t="s">
         <v>402</v>
       </c>
-      <c r="H58" s="80" t="s">
+      <c r="H58" s="123" t="s">
         <v>41</v>
       </c>
       <c r="I58" t="s">
@@ -11936,7 +11936,7 @@
       <c r="Z58" t="s">
         <v>417</v>
       </c>
-      <c r="AA58" s="79" t="s">
+      <c r="AA58" s="122" t="s">
         <v>72</v>
       </c>
     </row>
@@ -11962,7 +11962,7 @@
       <c r="G59" t="s">
         <v>402</v>
       </c>
-      <c r="H59" s="80"/>
+      <c r="H59" s="123"/>
       <c r="I59" t="s">
         <v>407</v>
       </c>
@@ -12017,7 +12017,7 @@
       <c r="Z59" t="s">
         <v>417</v>
       </c>
-      <c r="AA59" s="79"/>
+      <c r="AA59" s="122"/>
     </row>
     <row r="60" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
@@ -12041,7 +12041,7 @@
       <c r="G60" t="s">
         <v>402</v>
       </c>
-      <c r="H60" s="80"/>
+      <c r="H60" s="123"/>
       <c r="I60" t="s">
         <v>407</v>
       </c>
@@ -12096,7 +12096,7 @@
       <c r="Z60" t="s">
         <v>417</v>
       </c>
-      <c r="AA60" s="79"/>
+      <c r="AA60" s="122"/>
     </row>
     <row r="61" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
@@ -12120,7 +12120,7 @@
       <c r="G61" t="s">
         <v>402</v>
       </c>
-      <c r="H61" s="80"/>
+      <c r="H61" s="123"/>
       <c r="I61" t="s">
         <v>407</v>
       </c>
@@ -12175,7 +12175,7 @@
       <c r="Z61" t="s">
         <v>417</v>
       </c>
-      <c r="AA61" s="79"/>
+      <c r="AA61" s="122"/>
     </row>
     <row r="62" spans="1:28" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
@@ -12199,7 +12199,7 @@
       <c r="G62" t="s">
         <v>75</v>
       </c>
-      <c r="H62" s="80" t="s">
+      <c r="H62" s="123" t="s">
         <v>41</v>
       </c>
       <c r="I62" t="s">
@@ -12256,10 +12256,10 @@
       <c r="Z62" t="s">
         <v>426</v>
       </c>
-      <c r="AA62" s="79" t="s">
+      <c r="AA62" s="122" t="s">
         <v>83</v>
       </c>
-      <c r="AB62" s="79" t="s">
+      <c r="AB62" s="122" t="s">
         <v>418</v>
       </c>
     </row>
@@ -12285,7 +12285,7 @@
       <c r="G63" t="s">
         <v>75</v>
       </c>
-      <c r="H63" s="80"/>
+      <c r="H63" s="123"/>
       <c r="I63" t="s">
         <v>80</v>
       </c>
@@ -12340,8 +12340,8 @@
       <c r="Z63" t="s">
         <v>426</v>
       </c>
-      <c r="AA63" s="79"/>
-      <c r="AB63" s="79"/>
+      <c r="AA63" s="122"/>
+      <c r="AB63" s="122"/>
     </row>
     <row r="64" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
@@ -12365,7 +12365,7 @@
       <c r="G64" t="s">
         <v>75</v>
       </c>
-      <c r="H64" s="80"/>
+      <c r="H64" s="123"/>
       <c r="I64" t="s">
         <v>80</v>
       </c>
@@ -12420,8 +12420,8 @@
       <c r="Z64" t="s">
         <v>426</v>
       </c>
-      <c r="AA64" s="79"/>
-      <c r="AB64" s="79"/>
+      <c r="AA64" s="122"/>
+      <c r="AB64" s="122"/>
     </row>
     <row r="65" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
@@ -12445,7 +12445,7 @@
       <c r="G65" t="s">
         <v>75</v>
       </c>
-      <c r="H65" s="80"/>
+      <c r="H65" s="123"/>
       <c r="I65" t="s">
         <v>80</v>
       </c>
@@ -12500,8 +12500,8 @@
       <c r="Z65" t="s">
         <v>426</v>
       </c>
-      <c r="AA65" s="79"/>
-      <c r="AB65" s="79"/>
+      <c r="AA65" s="122"/>
+      <c r="AB65" s="122"/>
     </row>
     <row r="66" spans="1:28" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
@@ -12525,7 +12525,7 @@
       <c r="G66" t="s">
         <v>428</v>
       </c>
-      <c r="H66" s="80" t="s">
+      <c r="H66" s="123" t="s">
         <v>41</v>
       </c>
       <c r="I66" t="s">
@@ -12582,7 +12582,7 @@
       <c r="Z66" t="s">
         <v>442</v>
       </c>
-      <c r="AA66" s="79" t="s">
+      <c r="AA66" s="122" t="s">
         <v>434</v>
       </c>
     </row>
@@ -12608,7 +12608,7 @@
       <c r="G67" t="s">
         <v>428</v>
       </c>
-      <c r="H67" s="80"/>
+      <c r="H67" s="123"/>
       <c r="I67" t="s">
         <v>432</v>
       </c>
@@ -12663,7 +12663,7 @@
       <c r="Z67" t="s">
         <v>442</v>
       </c>
-      <c r="AA67" s="79"/>
+      <c r="AA67" s="122"/>
     </row>
     <row r="68" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
@@ -12687,7 +12687,7 @@
       <c r="G68" t="s">
         <v>428</v>
       </c>
-      <c r="H68" s="80"/>
+      <c r="H68" s="123"/>
       <c r="I68" t="s">
         <v>432</v>
       </c>
@@ -12742,7 +12742,7 @@
       <c r="Z68" t="s">
         <v>442</v>
       </c>
-      <c r="AA68" s="79"/>
+      <c r="AA68" s="122"/>
     </row>
     <row r="69" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
@@ -12766,7 +12766,7 @@
       <c r="G69" t="s">
         <v>428</v>
       </c>
-      <c r="H69" s="80"/>
+      <c r="H69" s="123"/>
       <c r="I69" t="s">
         <v>432</v>
       </c>
@@ -12821,7 +12821,7 @@
       <c r="Z69" t="s">
         <v>442</v>
       </c>
-      <c r="AA69" s="79"/>
+      <c r="AA69" s="122"/>
     </row>
     <row r="70" spans="1:28" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
@@ -12845,7 +12845,7 @@
       <c r="G70" t="s">
         <v>445</v>
       </c>
-      <c r="H70" s="80" t="s">
+      <c r="H70" s="123" t="s">
         <v>41</v>
       </c>
       <c r="I70" t="s">
@@ -12902,7 +12902,7 @@
       <c r="Z70" t="s">
         <v>461</v>
       </c>
-      <c r="AA70" s="79" t="s">
+      <c r="AA70" s="122" t="s">
         <v>454</v>
       </c>
     </row>
@@ -12928,7 +12928,7 @@
       <c r="G71" t="s">
         <v>445</v>
       </c>
-      <c r="H71" s="80"/>
+      <c r="H71" s="123"/>
       <c r="I71" t="s">
         <v>450</v>
       </c>
@@ -12983,7 +12983,7 @@
       <c r="Z71" t="s">
         <v>461</v>
       </c>
-      <c r="AA71" s="79"/>
+      <c r="AA71" s="122"/>
     </row>
     <row r="72" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
@@ -13007,7 +13007,7 @@
       <c r="G72" t="s">
         <v>445</v>
       </c>
-      <c r="H72" s="80"/>
+      <c r="H72" s="123"/>
       <c r="I72" t="s">
         <v>450</v>
       </c>
@@ -13062,7 +13062,7 @@
       <c r="Z72" t="s">
         <v>461</v>
       </c>
-      <c r="AA72" s="79"/>
+      <c r="AA72" s="122"/>
     </row>
     <row r="73" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
@@ -13086,7 +13086,7 @@
       <c r="G73" t="s">
         <v>445</v>
       </c>
-      <c r="H73" s="80"/>
+      <c r="H73" s="123"/>
       <c r="I73" t="s">
         <v>450</v>
       </c>
@@ -13141,7 +13141,7 @@
       <c r="Z73" t="s">
         <v>461</v>
       </c>
-      <c r="AA73" s="79"/>
+      <c r="AA73" s="122"/>
     </row>
     <row r="74" spans="1:28" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
@@ -13165,7 +13165,7 @@
       <c r="G74" t="s">
         <v>463</v>
       </c>
-      <c r="H74" s="80" t="s">
+      <c r="H74" s="123" t="s">
         <v>41</v>
       </c>
       <c r="I74" t="s">
@@ -13210,7 +13210,7 @@
       <c r="Z74" t="s">
         <v>477</v>
       </c>
-      <c r="AA74" s="79" t="s">
+      <c r="AA74" s="122" t="s">
         <v>470</v>
       </c>
     </row>
@@ -13236,7 +13236,7 @@
       <c r="G75" t="s">
         <v>463</v>
       </c>
-      <c r="H75" s="80"/>
+      <c r="H75" s="123"/>
       <c r="I75" t="s">
         <v>468</v>
       </c>
@@ -13279,7 +13279,7 @@
       <c r="Z75" t="s">
         <v>477</v>
       </c>
-      <c r="AA75" s="79"/>
+      <c r="AA75" s="122"/>
     </row>
     <row r="76" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
@@ -13303,7 +13303,7 @@
       <c r="G76" t="s">
         <v>463</v>
       </c>
-      <c r="H76" s="80"/>
+      <c r="H76" s="123"/>
       <c r="I76" t="s">
         <v>468</v>
       </c>
@@ -13346,7 +13346,7 @@
       <c r="Z76" t="s">
         <v>477</v>
       </c>
-      <c r="AA76" s="79"/>
+      <c r="AA76" s="122"/>
     </row>
     <row r="77" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
@@ -13370,7 +13370,7 @@
       <c r="G77" t="s">
         <v>463</v>
       </c>
-      <c r="H77" s="80"/>
+      <c r="H77" s="123"/>
       <c r="I77" t="s">
         <v>468</v>
       </c>
@@ -13413,7 +13413,7 @@
       <c r="Z77" t="s">
         <v>477</v>
       </c>
-      <c r="AA77" s="79"/>
+      <c r="AA77" s="122"/>
     </row>
     <row r="78" spans="1:28" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
@@ -13437,7 +13437,7 @@
       <c r="G78" t="s">
         <v>480</v>
       </c>
-      <c r="H78" s="80" t="s">
+      <c r="H78" s="123" t="s">
         <v>486</v>
       </c>
       <c r="I78" t="s">
@@ -13482,7 +13482,7 @@
       <c r="Z78" t="s">
         <v>496</v>
       </c>
-      <c r="AA78" s="79" t="s">
+      <c r="AA78" s="122" t="s">
         <v>478</v>
       </c>
     </row>
@@ -13508,7 +13508,7 @@
       <c r="G79" t="s">
         <v>480</v>
       </c>
-      <c r="H79" s="80"/>
+      <c r="H79" s="123"/>
       <c r="I79" t="s">
         <v>487</v>
       </c>
@@ -13551,7 +13551,7 @@
       <c r="Z79" t="s">
         <v>496</v>
       </c>
-      <c r="AA79" s="79"/>
+      <c r="AA79" s="122"/>
     </row>
     <row r="80" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
@@ -13575,7 +13575,7 @@
       <c r="G80" t="s">
         <v>480</v>
       </c>
-      <c r="H80" s="80"/>
+      <c r="H80" s="123"/>
       <c r="I80" t="s">
         <v>487</v>
       </c>
@@ -13618,7 +13618,7 @@
       <c r="Z80" t="s">
         <v>496</v>
       </c>
-      <c r="AA80" s="79"/>
+      <c r="AA80" s="122"/>
     </row>
     <row r="81" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
@@ -13642,7 +13642,7 @@
       <c r="G81" t="s">
         <v>480</v>
       </c>
-      <c r="H81" s="80"/>
+      <c r="H81" s="123"/>
       <c r="I81" t="s">
         <v>487</v>
       </c>
@@ -13685,7 +13685,7 @@
       <c r="Z81" t="s">
         <v>496</v>
       </c>
-      <c r="AA81" s="79"/>
+      <c r="AA81" s="122"/>
     </row>
     <row r="82" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
@@ -13709,7 +13709,7 @@
       <c r="G82" t="s">
         <v>498</v>
       </c>
-      <c r="H82" s="80" t="s">
+      <c r="H82" s="123" t="s">
         <v>89</v>
       </c>
       <c r="I82" t="s">
@@ -13754,7 +13754,7 @@
       <c r="Z82" t="s">
         <v>511</v>
       </c>
-      <c r="AA82" s="79" t="s">
+      <c r="AA82" s="122" t="s">
         <v>90</v>
       </c>
     </row>
@@ -13780,7 +13780,7 @@
       <c r="G83" t="s">
         <v>498</v>
       </c>
-      <c r="H83" s="80"/>
+      <c r="H83" s="123"/>
       <c r="I83" t="s">
         <v>503</v>
       </c>
@@ -13823,7 +13823,7 @@
       <c r="Z83" t="s">
         <v>511</v>
       </c>
-      <c r="AA83" s="79"/>
+      <c r="AA83" s="122"/>
     </row>
     <row r="84" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
@@ -13847,7 +13847,7 @@
       <c r="G84" t="s">
         <v>498</v>
       </c>
-      <c r="H84" s="80"/>
+      <c r="H84" s="123"/>
       <c r="I84" t="s">
         <v>503</v>
       </c>
@@ -13890,7 +13890,7 @@
       <c r="Z84" t="s">
         <v>511</v>
       </c>
-      <c r="AA84" s="79"/>
+      <c r="AA84" s="122"/>
     </row>
     <row r="85" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
@@ -13914,7 +13914,7 @@
       <c r="G85" t="s">
         <v>498</v>
       </c>
-      <c r="H85" s="80"/>
+      <c r="H85" s="123"/>
       <c r="I85" t="s">
         <v>503</v>
       </c>
@@ -13957,7 +13957,7 @@
       <c r="Z85" t="s">
         <v>511</v>
       </c>
-      <c r="AA85" s="79"/>
+      <c r="AA85" s="122"/>
     </row>
     <row r="86" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
@@ -13981,7 +13981,7 @@
       <c r="G86" t="s">
         <v>514</v>
       </c>
-      <c r="H86" s="80" t="s">
+      <c r="H86" s="123" t="s">
         <v>89</v>
       </c>
       <c r="I86" t="s">
@@ -14026,7 +14026,7 @@
       <c r="Z86" t="s">
         <v>526</v>
       </c>
-      <c r="AA86" s="79" t="s">
+      <c r="AA86" s="122" t="s">
         <v>92</v>
       </c>
     </row>
@@ -14052,7 +14052,7 @@
       <c r="G87" t="s">
         <v>514</v>
       </c>
-      <c r="H87" s="80"/>
+      <c r="H87" s="123"/>
       <c r="I87" t="s">
         <v>518</v>
       </c>
@@ -14095,7 +14095,7 @@
       <c r="Z87" t="s">
         <v>526</v>
       </c>
-      <c r="AA87" s="79"/>
+      <c r="AA87" s="122"/>
     </row>
     <row r="88" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
@@ -14119,7 +14119,7 @@
       <c r="G88" t="s">
         <v>514</v>
       </c>
-      <c r="H88" s="80"/>
+      <c r="H88" s="123"/>
       <c r="I88" t="s">
         <v>518</v>
       </c>
@@ -14162,7 +14162,7 @@
       <c r="Z88" t="s">
         <v>526</v>
       </c>
-      <c r="AA88" s="79"/>
+      <c r="AA88" s="122"/>
     </row>
     <row r="89" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
@@ -14186,7 +14186,7 @@
       <c r="G89" t="s">
         <v>514</v>
       </c>
-      <c r="H89" s="80"/>
+      <c r="H89" s="123"/>
       <c r="I89" t="s">
         <v>518</v>
       </c>
@@ -14229,7 +14229,7 @@
       <c r="Z89" t="s">
         <v>526</v>
       </c>
-      <c r="AA89" s="79"/>
+      <c r="AA89" s="122"/>
     </row>
     <row r="90" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
@@ -14253,7 +14253,7 @@
       <c r="G90" t="s">
         <v>530</v>
       </c>
-      <c r="H90" s="80" t="s">
+      <c r="H90" s="123" t="s">
         <v>89</v>
       </c>
       <c r="I90" t="s">
@@ -14265,7 +14265,7 @@
       <c r="K90" t="s">
         <v>20</v>
       </c>
-      <c r="L90" s="79" t="s">
+      <c r="L90" s="122" t="s">
         <v>536</v>
       </c>
       <c r="M90" t="s">
@@ -14310,7 +14310,7 @@
       <c r="Z90" t="s">
         <v>546</v>
       </c>
-      <c r="AA90" s="79" t="s">
+      <c r="AA90" s="122" t="s">
         <v>114</v>
       </c>
       <c r="AB90" s="5"/>
@@ -14337,7 +14337,7 @@
       <c r="G91" t="s">
         <v>530</v>
       </c>
-      <c r="H91" s="80"/>
+      <c r="H91" s="123"/>
       <c r="I91" t="s">
         <v>534</v>
       </c>
@@ -14347,7 +14347,7 @@
       <c r="K91" t="s">
         <v>20</v>
       </c>
-      <c r="L91" s="79"/>
+      <c r="L91" s="122"/>
       <c r="M91" t="s">
         <v>16</v>
       </c>
@@ -14390,7 +14390,7 @@
       <c r="Z91" t="s">
         <v>546</v>
       </c>
-      <c r="AA91" s="79"/>
+      <c r="AA91" s="122"/>
       <c r="AB91" s="5"/>
     </row>
     <row r="92" spans="1:28" x14ac:dyDescent="0.3">
@@ -14415,7 +14415,7 @@
       <c r="G92" t="s">
         <v>530</v>
       </c>
-      <c r="H92" s="80"/>
+      <c r="H92" s="123"/>
       <c r="I92" t="s">
         <v>534</v>
       </c>
@@ -14425,7 +14425,7 @@
       <c r="K92" t="s">
         <v>20</v>
       </c>
-      <c r="L92" s="79"/>
+      <c r="L92" s="122"/>
       <c r="M92" t="s">
         <v>16</v>
       </c>
@@ -14468,7 +14468,7 @@
       <c r="Z92" t="s">
         <v>546</v>
       </c>
-      <c r="AA92" s="79"/>
+      <c r="AA92" s="122"/>
       <c r="AB92" s="5"/>
     </row>
     <row r="93" spans="1:28" x14ac:dyDescent="0.3">
@@ -14493,7 +14493,7 @@
       <c r="G93" t="s">
         <v>530</v>
       </c>
-      <c r="H93" s="80"/>
+      <c r="H93" s="123"/>
       <c r="I93" t="s">
         <v>534</v>
       </c>
@@ -14503,7 +14503,7 @@
       <c r="K93" t="s">
         <v>20</v>
       </c>
-      <c r="L93" s="79"/>
+      <c r="L93" s="122"/>
       <c r="M93" t="s">
         <v>16</v>
       </c>
@@ -14546,7 +14546,7 @@
       <c r="Z93" t="s">
         <v>546</v>
       </c>
-      <c r="AA93" s="79"/>
+      <c r="AA93" s="122"/>
       <c r="AB93" s="5"/>
     </row>
     <row r="94" spans="1:28" ht="144" customHeight="1" x14ac:dyDescent="0.3">
@@ -14571,7 +14571,7 @@
       <c r="G94" t="s">
         <v>552</v>
       </c>
-      <c r="H94" s="80" t="s">
+      <c r="H94" s="123" t="s">
         <v>89</v>
       </c>
       <c r="I94" t="s">
@@ -14628,7 +14628,7 @@
       <c r="Z94" t="s">
         <v>561</v>
       </c>
-      <c r="AA94" s="79" t="s">
+      <c r="AA94" s="122" t="s">
         <v>96</v>
       </c>
     </row>
@@ -14654,7 +14654,7 @@
       <c r="G95" t="s">
         <v>552</v>
       </c>
-      <c r="H95" s="80"/>
+      <c r="H95" s="123"/>
       <c r="I95" t="s">
         <v>553</v>
       </c>
@@ -14709,7 +14709,7 @@
       <c r="Z95" t="s">
         <v>561</v>
       </c>
-      <c r="AA95" s="79"/>
+      <c r="AA95" s="122"/>
     </row>
     <row r="96" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
@@ -14733,7 +14733,7 @@
       <c r="G96" t="s">
         <v>552</v>
       </c>
-      <c r="H96" s="80"/>
+      <c r="H96" s="123"/>
       <c r="I96" t="s">
         <v>553</v>
       </c>
@@ -14788,7 +14788,7 @@
       <c r="Z96" t="s">
         <v>561</v>
       </c>
-      <c r="AA96" s="79"/>
+      <c r="AA96" s="122"/>
     </row>
     <row r="97" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
@@ -14812,7 +14812,7 @@
       <c r="G97" t="s">
         <v>552</v>
       </c>
-      <c r="H97" s="80"/>
+      <c r="H97" s="123"/>
       <c r="I97" t="s">
         <v>553</v>
       </c>
@@ -14867,7 +14867,7 @@
       <c r="Z97" t="s">
         <v>561</v>
       </c>
-      <c r="AA97" s="79"/>
+      <c r="AA97" s="122"/>
     </row>
     <row r="98" spans="1:27" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
@@ -14891,7 +14891,7 @@
       <c r="G98" t="s">
         <v>568</v>
       </c>
-      <c r="H98" s="80" t="s">
+      <c r="H98" s="123" t="s">
         <v>89</v>
       </c>
       <c r="I98" t="s">
@@ -14948,7 +14948,7 @@
       <c r="Z98" t="s">
         <v>580</v>
       </c>
-      <c r="AA98" s="79" t="s">
+      <c r="AA98" s="122" t="s">
         <v>572</v>
       </c>
     </row>
@@ -14974,7 +14974,7 @@
       <c r="G99" t="s">
         <v>568</v>
       </c>
-      <c r="H99" s="80"/>
+      <c r="H99" s="123"/>
       <c r="I99" t="s">
         <v>569</v>
       </c>
@@ -15029,7 +15029,7 @@
       <c r="Z99" t="s">
         <v>580</v>
       </c>
-      <c r="AA99" s="79"/>
+      <c r="AA99" s="122"/>
     </row>
     <row r="100" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
@@ -15053,7 +15053,7 @@
       <c r="G100" t="s">
         <v>568</v>
       </c>
-      <c r="H100" s="80"/>
+      <c r="H100" s="123"/>
       <c r="I100" t="s">
         <v>569</v>
       </c>
@@ -15108,7 +15108,7 @@
       <c r="Z100" t="s">
         <v>580</v>
       </c>
-      <c r="AA100" s="79"/>
+      <c r="AA100" s="122"/>
     </row>
     <row r="101" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
@@ -15132,7 +15132,7 @@
       <c r="G101" t="s">
         <v>568</v>
       </c>
-      <c r="H101" s="80"/>
+      <c r="H101" s="123"/>
       <c r="I101" t="s">
         <v>569</v>
       </c>
@@ -15187,7 +15187,7 @@
       <c r="Z101" t="s">
         <v>580</v>
       </c>
-      <c r="AA101" s="79"/>
+      <c r="AA101" s="122"/>
     </row>
     <row r="102" spans="1:27" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
@@ -15211,7 +15211,7 @@
       <c r="G102" t="s">
         <v>587</v>
       </c>
-      <c r="H102" s="80" t="s">
+      <c r="H102" s="123" t="s">
         <v>89</v>
       </c>
       <c r="I102" t="s">
@@ -15268,7 +15268,7 @@
       <c r="Z102" t="s">
         <v>596</v>
       </c>
-      <c r="AA102" s="79" t="s">
+      <c r="AA102" s="122" t="s">
         <v>100</v>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       <c r="G103" t="s">
         <v>587</v>
       </c>
-      <c r="H103" s="80"/>
+      <c r="H103" s="123"/>
       <c r="I103" t="s">
         <v>583</v>
       </c>
@@ -15349,7 +15349,7 @@
       <c r="Z103" t="s">
         <v>596</v>
       </c>
-      <c r="AA103" s="79"/>
+      <c r="AA103" s="122"/>
     </row>
     <row r="104" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
@@ -15373,7 +15373,7 @@
       <c r="G104" t="s">
         <v>587</v>
       </c>
-      <c r="H104" s="80"/>
+      <c r="H104" s="123"/>
       <c r="I104" t="s">
         <v>583</v>
       </c>
@@ -15428,7 +15428,7 @@
       <c r="Z104" t="s">
         <v>596</v>
       </c>
-      <c r="AA104" s="79"/>
+      <c r="AA104" s="122"/>
     </row>
     <row r="105" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
@@ -15452,7 +15452,7 @@
       <c r="G105" t="s">
         <v>587</v>
       </c>
-      <c r="H105" s="80"/>
+      <c r="H105" s="123"/>
       <c r="I105" t="s">
         <v>583</v>
       </c>
@@ -15507,7 +15507,7 @@
       <c r="Z105" t="s">
         <v>596</v>
       </c>
-      <c r="AA105" s="79"/>
+      <c r="AA105" s="122"/>
     </row>
     <row r="106" spans="1:27" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
@@ -15531,7 +15531,7 @@
       <c r="G106" t="s">
         <v>599</v>
       </c>
-      <c r="H106" s="80" t="s">
+      <c r="H106" s="123" t="s">
         <v>89</v>
       </c>
       <c r="I106" t="s">
@@ -15588,7 +15588,7 @@
       <c r="Z106" t="s">
         <v>609</v>
       </c>
-      <c r="AA106" s="79" t="s">
+      <c r="AA106" s="122" t="s">
         <v>107</v>
       </c>
     </row>
@@ -15614,7 +15614,7 @@
       <c r="G107" t="s">
         <v>599</v>
       </c>
-      <c r="H107" s="80"/>
+      <c r="H107" s="123"/>
       <c r="I107" t="s">
         <v>600</v>
       </c>
@@ -15669,7 +15669,7 @@
       <c r="Z107" t="s">
         <v>609</v>
       </c>
-      <c r="AA107" s="79"/>
+      <c r="AA107" s="122"/>
     </row>
     <row r="108" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
@@ -15693,7 +15693,7 @@
       <c r="G108" t="s">
         <v>599</v>
       </c>
-      <c r="H108" s="80"/>
+      <c r="H108" s="123"/>
       <c r="I108" t="s">
         <v>600</v>
       </c>
@@ -15748,7 +15748,7 @@
       <c r="Z108" t="s">
         <v>609</v>
       </c>
-      <c r="AA108" s="79"/>
+      <c r="AA108" s="122"/>
     </row>
     <row r="109" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
@@ -15772,7 +15772,7 @@
       <c r="G109" t="s">
         <v>599</v>
       </c>
-      <c r="H109" s="80"/>
+      <c r="H109" s="123"/>
       <c r="I109" t="s">
         <v>600</v>
       </c>
@@ -15827,7 +15827,7 @@
       <c r="Z109" t="s">
         <v>609</v>
       </c>
-      <c r="AA109" s="79"/>
+      <c r="AA109" s="122"/>
     </row>
     <row r="110" spans="1:27" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
@@ -15851,7 +15851,7 @@
       <c r="G110" t="s">
         <v>612</v>
       </c>
-      <c r="H110" s="80" t="s">
+      <c r="H110" s="123" t="s">
         <v>89</v>
       </c>
       <c r="I110" t="s">
@@ -15908,7 +15908,7 @@
       <c r="Z110" t="s">
         <v>626</v>
       </c>
-      <c r="AA110" s="79" t="s">
+      <c r="AA110" s="122" t="s">
         <v>833</v>
       </c>
     </row>
@@ -15934,7 +15934,7 @@
       <c r="G111" t="s">
         <v>612</v>
       </c>
-      <c r="H111" s="80"/>
+      <c r="H111" s="123"/>
       <c r="I111" t="s">
         <v>617</v>
       </c>
@@ -15989,7 +15989,7 @@
       <c r="Z111" t="s">
         <v>626</v>
       </c>
-      <c r="AA111" s="79"/>
+      <c r="AA111" s="122"/>
     </row>
     <row r="112" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
@@ -16013,7 +16013,7 @@
       <c r="G112" t="s">
         <v>612</v>
       </c>
-      <c r="H112" s="80"/>
+      <c r="H112" s="123"/>
       <c r="I112" t="s">
         <v>617</v>
       </c>
@@ -16068,7 +16068,7 @@
       <c r="Z112" t="s">
         <v>626</v>
       </c>
-      <c r="AA112" s="79"/>
+      <c r="AA112" s="122"/>
     </row>
     <row r="113" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
@@ -16092,7 +16092,7 @@
       <c r="G113" t="s">
         <v>612</v>
       </c>
-      <c r="H113" s="80"/>
+      <c r="H113" s="123"/>
       <c r="I113" t="s">
         <v>617</v>
       </c>
@@ -16147,7 +16147,7 @@
       <c r="Z113" t="s">
         <v>626</v>
       </c>
-      <c r="AA113" s="79"/>
+      <c r="AA113" s="122"/>
     </row>
     <row r="114" spans="1:28" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
@@ -16171,7 +16171,7 @@
       <c r="G114" t="s">
         <v>628</v>
       </c>
-      <c r="H114" s="80" t="s">
+      <c r="H114" s="123" t="s">
         <v>634</v>
       </c>
       <c r="I114" t="s">
@@ -16216,7 +16216,7 @@
       <c r="Z114" t="s">
         <v>644</v>
       </c>
-      <c r="AA114" s="79" t="s">
+      <c r="AA114" s="122" t="s">
         <v>645</v>
       </c>
     </row>
@@ -16242,7 +16242,7 @@
       <c r="G115" t="s">
         <v>628</v>
       </c>
-      <c r="H115" s="80"/>
+      <c r="H115" s="123"/>
       <c r="I115" t="s">
         <v>635</v>
       </c>
@@ -16285,7 +16285,7 @@
       <c r="Z115" t="s">
         <v>644</v>
       </c>
-      <c r="AA115" s="79"/>
+      <c r="AA115" s="122"/>
     </row>
     <row r="116" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
@@ -16309,7 +16309,7 @@
       <c r="G116" t="s">
         <v>628</v>
       </c>
-      <c r="H116" s="80"/>
+      <c r="H116" s="123"/>
       <c r="I116" t="s">
         <v>635</v>
       </c>
@@ -16352,7 +16352,7 @@
       <c r="Z116" t="s">
         <v>644</v>
       </c>
-      <c r="AA116" s="79"/>
+      <c r="AA116" s="122"/>
     </row>
     <row r="117" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
@@ -16376,7 +16376,7 @@
       <c r="G117" t="s">
         <v>628</v>
       </c>
-      <c r="H117" s="80"/>
+      <c r="H117" s="123"/>
       <c r="I117" t="s">
         <v>635</v>
       </c>
@@ -16419,7 +16419,7 @@
       <c r="Z117" t="s">
         <v>644</v>
       </c>
-      <c r="AA117" s="79"/>
+      <c r="AA117" s="122"/>
     </row>
     <row r="118" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
@@ -16443,7 +16443,7 @@
       <c r="G118" t="s">
         <v>648</v>
       </c>
-      <c r="H118" s="80" t="s">
+      <c r="H118" s="123" t="s">
         <v>656</v>
       </c>
       <c r="I118" t="s">
@@ -16488,7 +16488,7 @@
       <c r="Z118" t="s">
         <v>661</v>
       </c>
-      <c r="AA118" s="79" t="s">
+      <c r="AA118" s="122" t="s">
         <v>111</v>
       </c>
     </row>
@@ -16514,7 +16514,7 @@
       <c r="G119" t="s">
         <v>648</v>
       </c>
-      <c r="H119" s="80"/>
+      <c r="H119" s="123"/>
       <c r="I119" t="s">
         <v>654</v>
       </c>
@@ -16557,7 +16557,7 @@
       <c r="Z119" t="s">
         <v>661</v>
       </c>
-      <c r="AA119" s="79"/>
+      <c r="AA119" s="122"/>
     </row>
     <row r="120" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
@@ -16581,7 +16581,7 @@
       <c r="G120" t="s">
         <v>648</v>
       </c>
-      <c r="H120" s="80"/>
+      <c r="H120" s="123"/>
       <c r="I120" t="s">
         <v>654</v>
       </c>
@@ -16624,7 +16624,7 @@
       <c r="Z120" t="s">
         <v>661</v>
       </c>
-      <c r="AA120" s="79"/>
+      <c r="AA120" s="122"/>
     </row>
     <row r="121" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
@@ -16648,7 +16648,7 @@
       <c r="G121" t="s">
         <v>648</v>
       </c>
-      <c r="H121" s="80"/>
+      <c r="H121" s="123"/>
       <c r="I121" t="s">
         <v>654</v>
       </c>
@@ -16691,7 +16691,7 @@
       <c r="Z121" t="s">
         <v>661</v>
       </c>
-      <c r="AA121" s="79"/>
+      <c r="AA121" s="122"/>
     </row>
     <row r="122" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
@@ -16715,7 +16715,7 @@
       <c r="G122" t="s">
         <v>665</v>
       </c>
-      <c r="H122" s="80" t="s">
+      <c r="H122" s="123" t="s">
         <v>89</v>
       </c>
       <c r="I122" t="s">
@@ -16760,7 +16760,7 @@
       <c r="Z122" t="s">
         <v>677</v>
       </c>
-      <c r="AA122" s="79" t="s">
+      <c r="AA122" s="122" t="s">
         <v>117</v>
       </c>
     </row>
@@ -16786,7 +16786,7 @@
       <c r="G123" t="s">
         <v>665</v>
       </c>
-      <c r="H123" s="80"/>
+      <c r="H123" s="123"/>
       <c r="I123" t="s">
         <v>664</v>
       </c>
@@ -16829,7 +16829,7 @@
       <c r="Z123" t="s">
         <v>677</v>
       </c>
-      <c r="AA123" s="79"/>
+      <c r="AA123" s="122"/>
     </row>
     <row r="124" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
@@ -16853,7 +16853,7 @@
       <c r="G124" t="s">
         <v>665</v>
       </c>
-      <c r="H124" s="80"/>
+      <c r="H124" s="123"/>
       <c r="I124" t="s">
         <v>664</v>
       </c>
@@ -16896,7 +16896,7 @@
       <c r="Z124" t="s">
         <v>677</v>
       </c>
-      <c r="AA124" s="79"/>
+      <c r="AA124" s="122"/>
     </row>
     <row r="125" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
@@ -16920,7 +16920,7 @@
       <c r="G125" t="s">
         <v>665</v>
       </c>
-      <c r="H125" s="80"/>
+      <c r="H125" s="123"/>
       <c r="I125" t="s">
         <v>664</v>
       </c>
@@ -16963,7 +16963,7 @@
       <c r="Z125" t="s">
         <v>677</v>
       </c>
-      <c r="AA125" s="79"/>
+      <c r="AA125" s="122"/>
     </row>
     <row r="126" spans="1:28" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
@@ -16987,7 +16987,7 @@
       <c r="G126" t="s">
         <v>682</v>
       </c>
-      <c r="H126" s="80" t="s">
+      <c r="H126" s="123" t="s">
         <v>89</v>
       </c>
       <c r="I126" t="s">
@@ -17044,10 +17044,10 @@
       <c r="Z126" t="s">
         <v>696</v>
       </c>
-      <c r="AA126" s="79" t="s">
+      <c r="AA126" s="122" t="s">
         <v>680</v>
       </c>
-      <c r="AB126" s="81" t="s">
+      <c r="AB126" s="124" t="s">
         <v>146</v>
       </c>
     </row>
@@ -17073,7 +17073,7 @@
       <c r="G127" t="s">
         <v>682</v>
       </c>
-      <c r="H127" s="80"/>
+      <c r="H127" s="123"/>
       <c r="I127" t="s">
         <v>687</v>
       </c>
@@ -17128,8 +17128,8 @@
       <c r="Z127" t="s">
         <v>696</v>
       </c>
-      <c r="AA127" s="79"/>
-      <c r="AB127" s="81"/>
+      <c r="AA127" s="122"/>
+      <c r="AB127" s="124"/>
     </row>
     <row r="128" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
@@ -17153,7 +17153,7 @@
       <c r="G128" t="s">
         <v>682</v>
       </c>
-      <c r="H128" s="80"/>
+      <c r="H128" s="123"/>
       <c r="I128" t="s">
         <v>687</v>
       </c>
@@ -17208,8 +17208,8 @@
       <c r="Z128" t="s">
         <v>696</v>
       </c>
-      <c r="AA128" s="79"/>
-      <c r="AB128" s="81"/>
+      <c r="AA128" s="122"/>
+      <c r="AB128" s="124"/>
     </row>
     <row r="129" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
@@ -17233,7 +17233,7 @@
       <c r="G129" t="s">
         <v>682</v>
       </c>
-      <c r="H129" s="80"/>
+      <c r="H129" s="123"/>
       <c r="I129" t="s">
         <v>687</v>
       </c>
@@ -17288,8 +17288,8 @@
       <c r="Z129" t="s">
         <v>696</v>
       </c>
-      <c r="AA129" s="79"/>
-      <c r="AB129" s="81"/>
+      <c r="AA129" s="122"/>
+      <c r="AB129" s="124"/>
     </row>
     <row r="130" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
@@ -17313,7 +17313,7 @@
       <c r="G130" t="s">
         <v>123</v>
       </c>
-      <c r="H130" s="80" t="s">
+      <c r="H130" s="123" t="s">
         <v>89</v>
       </c>
       <c r="I130" t="s">
@@ -17370,10 +17370,10 @@
       <c r="Z130" t="s">
         <v>705</v>
       </c>
-      <c r="AA130" s="79" t="s">
+      <c r="AA130" s="122" t="s">
         <v>130</v>
       </c>
-      <c r="AB130" s="82" t="s">
+      <c r="AB130" s="121" t="s">
         <v>697</v>
       </c>
     </row>
@@ -17399,7 +17399,7 @@
       <c r="G131" t="s">
         <v>123</v>
       </c>
-      <c r="H131" s="80"/>
+      <c r="H131" s="123"/>
       <c r="I131" t="s">
         <v>128</v>
       </c>
@@ -17454,8 +17454,8 @@
       <c r="Z131" t="s">
         <v>705</v>
       </c>
-      <c r="AA131" s="79"/>
-      <c r="AB131" s="82"/>
+      <c r="AA131" s="122"/>
+      <c r="AB131" s="121"/>
     </row>
     <row r="132" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
@@ -17479,7 +17479,7 @@
       <c r="G132" t="s">
         <v>123</v>
       </c>
-      <c r="H132" s="80"/>
+      <c r="H132" s="123"/>
       <c r="I132" t="s">
         <v>128</v>
       </c>
@@ -17534,8 +17534,8 @@
       <c r="Z132" t="s">
         <v>705</v>
       </c>
-      <c r="AA132" s="79"/>
-      <c r="AB132" s="82"/>
+      <c r="AA132" s="122"/>
+      <c r="AB132" s="121"/>
     </row>
     <row r="133" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
@@ -17559,7 +17559,7 @@
       <c r="G133" t="s">
         <v>123</v>
       </c>
-      <c r="H133" s="80"/>
+      <c r="H133" s="123"/>
       <c r="I133" t="s">
         <v>128</v>
       </c>
@@ -17614,8 +17614,8 @@
       <c r="Z133" t="s">
         <v>705</v>
       </c>
-      <c r="AA133" s="79"/>
-      <c r="AB133" s="82"/>
+      <c r="AA133" s="122"/>
+      <c r="AB133" s="121"/>
     </row>
     <row r="134" spans="1:28" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
@@ -17639,7 +17639,7 @@
       <c r="G134" t="s">
         <v>708</v>
       </c>
-      <c r="H134" s="80" t="s">
+      <c r="H134" s="123" t="s">
         <v>89</v>
       </c>
       <c r="I134" t="s">
@@ -17696,7 +17696,7 @@
       <c r="Z134" t="s">
         <v>718</v>
       </c>
-      <c r="AA134" s="79" t="s">
+      <c r="AA134" s="122" t="s">
         <v>136</v>
       </c>
     </row>
@@ -17722,7 +17722,7 @@
       <c r="G135" t="s">
         <v>708</v>
       </c>
-      <c r="H135" s="80"/>
+      <c r="H135" s="123"/>
       <c r="I135" t="s">
         <v>710</v>
       </c>
@@ -17777,7 +17777,7 @@
       <c r="Z135" t="s">
         <v>718</v>
       </c>
-      <c r="AA135" s="79"/>
+      <c r="AA135" s="122"/>
     </row>
     <row r="136" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
@@ -17801,7 +17801,7 @@
       <c r="G136" t="s">
         <v>708</v>
       </c>
-      <c r="H136" s="80"/>
+      <c r="H136" s="123"/>
       <c r="I136" t="s">
         <v>710</v>
       </c>
@@ -17856,7 +17856,7 @@
       <c r="Z136" t="s">
         <v>718</v>
       </c>
-      <c r="AA136" s="79"/>
+      <c r="AA136" s="122"/>
     </row>
     <row r="137" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
@@ -17880,7 +17880,7 @@
       <c r="G137" t="s">
         <v>708</v>
       </c>
-      <c r="H137" s="80"/>
+      <c r="H137" s="123"/>
       <c r="I137" t="s">
         <v>710</v>
       </c>
@@ -17935,7 +17935,7 @@
       <c r="Z137" t="s">
         <v>718</v>
       </c>
-      <c r="AA137" s="79"/>
+      <c r="AA137" s="122"/>
     </row>
     <row r="138" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
@@ -17959,7 +17959,7 @@
       <c r="G138" t="s">
         <v>721</v>
       </c>
-      <c r="H138" s="80" t="s">
+      <c r="H138" s="123" t="s">
         <v>89</v>
       </c>
       <c r="I138" t="s">
@@ -18004,7 +18004,7 @@
       <c r="Z138" t="s">
         <v>735</v>
       </c>
-      <c r="AA138" s="79" t="s">
+      <c r="AA138" s="122" t="s">
         <v>138</v>
       </c>
     </row>
@@ -18030,7 +18030,7 @@
       <c r="G139" t="s">
         <v>721</v>
       </c>
-      <c r="H139" s="80"/>
+      <c r="H139" s="123"/>
       <c r="I139" t="s">
         <v>727</v>
       </c>
@@ -18073,7 +18073,7 @@
       <c r="Z139" t="s">
         <v>735</v>
       </c>
-      <c r="AA139" s="79"/>
+      <c r="AA139" s="122"/>
     </row>
     <row r="140" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
@@ -18097,7 +18097,7 @@
       <c r="G140" t="s">
         <v>721</v>
       </c>
-      <c r="H140" s="80"/>
+      <c r="H140" s="123"/>
       <c r="I140" t="s">
         <v>727</v>
       </c>
@@ -18140,7 +18140,7 @@
       <c r="Z140" t="s">
         <v>735</v>
       </c>
-      <c r="AA140" s="79"/>
+      <c r="AA140" s="122"/>
     </row>
     <row r="141" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
@@ -18164,7 +18164,7 @@
       <c r="G141" t="s">
         <v>721</v>
       </c>
-      <c r="H141" s="80"/>
+      <c r="H141" s="123"/>
       <c r="I141" t="s">
         <v>727</v>
       </c>
@@ -18207,7 +18207,7 @@
       <c r="Z141" t="s">
         <v>735</v>
       </c>
-      <c r="AA141" s="79"/>
+      <c r="AA141" s="122"/>
     </row>
     <row r="142" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
@@ -18231,7 +18231,7 @@
       <c r="G142" t="s">
         <v>738</v>
       </c>
-      <c r="H142" s="80" t="s">
+      <c r="H142" s="123" t="s">
         <v>140</v>
       </c>
       <c r="I142" t="s">
@@ -18276,7 +18276,7 @@
       <c r="Z142" t="s">
         <v>752</v>
       </c>
-      <c r="AA142" s="79" t="s">
+      <c r="AA142" s="122" t="s">
         <v>141</v>
       </c>
     </row>
@@ -18302,7 +18302,7 @@
       <c r="G143" t="s">
         <v>738</v>
       </c>
-      <c r="H143" s="80"/>
+      <c r="H143" s="123"/>
       <c r="I143" t="s">
         <v>743</v>
       </c>
@@ -18345,7 +18345,7 @@
       <c r="Z143" t="s">
         <v>752</v>
       </c>
-      <c r="AA143" s="79"/>
+      <c r="AA143" s="122"/>
     </row>
     <row r="144" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
@@ -18369,7 +18369,7 @@
       <c r="G144" t="s">
         <v>738</v>
       </c>
-      <c r="H144" s="80"/>
+      <c r="H144" s="123"/>
       <c r="I144" t="s">
         <v>743</v>
       </c>
@@ -18412,7 +18412,7 @@
       <c r="Z144" t="s">
         <v>752</v>
       </c>
-      <c r="AA144" s="79"/>
+      <c r="AA144" s="122"/>
     </row>
     <row r="145" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
@@ -18436,7 +18436,7 @@
       <c r="G145" t="s">
         <v>738</v>
       </c>
-      <c r="H145" s="80"/>
+      <c r="H145" s="123"/>
       <c r="I145" t="s">
         <v>743</v>
       </c>
@@ -18479,7 +18479,7 @@
       <c r="Z145" t="s">
         <v>752</v>
       </c>
-      <c r="AA145" s="79"/>
+      <c r="AA145" s="122"/>
     </row>
     <row r="146" spans="1:28" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
@@ -18503,7 +18503,7 @@
       <c r="G146" t="s">
         <v>763</v>
       </c>
-      <c r="H146" s="80" t="s">
+      <c r="H146" s="123" t="s">
         <v>764</v>
       </c>
       <c r="I146" t="s">
@@ -18548,10 +18548,10 @@
       <c r="Z146" t="s">
         <v>773</v>
       </c>
-      <c r="AA146" s="79" t="s">
+      <c r="AA146" s="122" t="s">
         <v>765</v>
       </c>
-      <c r="AB146" s="79" t="s">
+      <c r="AB146" s="122" t="s">
         <v>753</v>
       </c>
     </row>
@@ -18577,7 +18577,7 @@
       <c r="G147" t="s">
         <v>763</v>
       </c>
-      <c r="H147" s="80"/>
+      <c r="H147" s="123"/>
       <c r="I147" t="s">
         <v>761</v>
       </c>
@@ -18620,8 +18620,8 @@
       <c r="Z147" t="s">
         <v>773</v>
       </c>
-      <c r="AA147" s="79"/>
-      <c r="AB147" s="79"/>
+      <c r="AA147" s="122"/>
+      <c r="AB147" s="122"/>
     </row>
     <row r="148" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
@@ -18645,7 +18645,7 @@
       <c r="G148" t="s">
         <v>763</v>
       </c>
-      <c r="H148" s="80"/>
+      <c r="H148" s="123"/>
       <c r="I148" t="s">
         <v>761</v>
       </c>
@@ -18688,8 +18688,8 @@
       <c r="Z148" t="s">
         <v>773</v>
       </c>
-      <c r="AA148" s="79"/>
-      <c r="AB148" s="79"/>
+      <c r="AA148" s="122"/>
+      <c r="AB148" s="122"/>
     </row>
     <row r="149" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
@@ -18713,7 +18713,7 @@
       <c r="G149" t="s">
         <v>763</v>
       </c>
-      <c r="H149" s="80"/>
+      <c r="H149" s="123"/>
       <c r="I149" t="s">
         <v>761</v>
       </c>
@@ -18756,8 +18756,8 @@
       <c r="Z149" t="s">
         <v>773</v>
       </c>
-      <c r="AA149" s="79"/>
-      <c r="AB149" s="79"/>
+      <c r="AA149" s="122"/>
+      <c r="AB149" s="122"/>
     </row>
     <row r="150" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
@@ -18781,7 +18781,7 @@
       <c r="G150" t="s">
         <v>776</v>
       </c>
-      <c r="H150" s="80" t="s">
+      <c r="H150" s="123" t="s">
         <v>89</v>
       </c>
       <c r="I150" t="s">
@@ -18838,7 +18838,7 @@
       <c r="Z150" t="s">
         <v>794</v>
       </c>
-      <c r="AA150" s="79" t="s">
+      <c r="AA150" s="122" t="s">
         <v>786</v>
       </c>
     </row>
@@ -18864,7 +18864,7 @@
       <c r="G151" t="s">
         <v>776</v>
       </c>
-      <c r="H151" s="80"/>
+      <c r="H151" s="123"/>
       <c r="I151" t="s">
         <v>781</v>
       </c>
@@ -18919,7 +18919,7 @@
       <c r="Z151" t="s">
         <v>794</v>
       </c>
-      <c r="AA151" s="79"/>
+      <c r="AA151" s="122"/>
     </row>
     <row r="152" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
@@ -18943,7 +18943,7 @@
       <c r="G152" t="s">
         <v>776</v>
       </c>
-      <c r="H152" s="80"/>
+      <c r="H152" s="123"/>
       <c r="I152" t="s">
         <v>781</v>
       </c>
@@ -18998,7 +18998,7 @@
       <c r="Z152" t="s">
         <v>794</v>
       </c>
-      <c r="AA152" s="79"/>
+      <c r="AA152" s="122"/>
     </row>
     <row r="153" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
@@ -19022,7 +19022,7 @@
       <c r="G153" t="s">
         <v>776</v>
       </c>
-      <c r="H153" s="80"/>
+      <c r="H153" s="123"/>
       <c r="I153" t="s">
         <v>781</v>
       </c>
@@ -19077,7 +19077,7 @@
       <c r="Z153" t="s">
         <v>794</v>
       </c>
-      <c r="AA153" s="79"/>
+      <c r="AA153" s="122"/>
     </row>
     <row r="154" spans="1:28" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
@@ -19101,7 +19101,7 @@
       <c r="G154" t="s">
         <v>803</v>
       </c>
-      <c r="H154" s="80" t="s">
+      <c r="H154" s="123" t="s">
         <v>804</v>
       </c>
       <c r="I154" t="s">
@@ -19158,7 +19158,7 @@
       <c r="Z154" t="s">
         <v>813</v>
       </c>
-      <c r="AA154" s="79" t="s">
+      <c r="AA154" s="122" t="s">
         <v>814</v>
       </c>
     </row>
@@ -19184,7 +19184,7 @@
       <c r="G155" t="s">
         <v>803</v>
       </c>
-      <c r="H155" s="80"/>
+      <c r="H155" s="123"/>
       <c r="I155" t="s">
         <v>805</v>
       </c>
@@ -19239,7 +19239,7 @@
       <c r="Z155" t="s">
         <v>813</v>
       </c>
-      <c r="AA155" s="79"/>
+      <c r="AA155" s="122"/>
     </row>
     <row r="156" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
@@ -19263,7 +19263,7 @@
       <c r="G156" t="s">
         <v>803</v>
       </c>
-      <c r="H156" s="80"/>
+      <c r="H156" s="123"/>
       <c r="I156" t="s">
         <v>805</v>
       </c>
@@ -19318,7 +19318,7 @@
       <c r="Z156" t="s">
         <v>813</v>
       </c>
-      <c r="AA156" s="79"/>
+      <c r="AA156" s="122"/>
     </row>
     <row r="157" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
@@ -19342,7 +19342,7 @@
       <c r="G157" t="s">
         <v>803</v>
       </c>
-      <c r="H157" s="80"/>
+      <c r="H157" s="123"/>
       <c r="I157" t="s">
         <v>805</v>
       </c>
@@ -19397,7 +19397,7 @@
       <c r="Z157" t="s">
         <v>813</v>
       </c>
-      <c r="AA157" s="79"/>
+      <c r="AA157" s="122"/>
     </row>
     <row r="158" spans="1:28" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
@@ -19421,7 +19421,7 @@
       <c r="G158" t="s">
         <v>818</v>
       </c>
-      <c r="H158" s="80" t="s">
+      <c r="H158" s="123" t="s">
         <v>825</v>
       </c>
       <c r="I158" t="s">
@@ -19478,7 +19478,7 @@
       <c r="Z158" t="s">
         <v>813</v>
       </c>
-      <c r="AA158" s="79" t="s">
+      <c r="AA158" s="122" t="s">
         <v>832</v>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       <c r="G159" t="s">
         <v>818</v>
       </c>
-      <c r="H159" s="80"/>
+      <c r="H159" s="123"/>
       <c r="I159" t="s">
         <v>824</v>
       </c>
@@ -19559,7 +19559,7 @@
       <c r="Z159" t="s">
         <v>813</v>
       </c>
-      <c r="AA159" s="79"/>
+      <c r="AA159" s="122"/>
     </row>
     <row r="160" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
@@ -19583,7 +19583,7 @@
       <c r="G160" t="s">
         <v>818</v>
       </c>
-      <c r="H160" s="80"/>
+      <c r="H160" s="123"/>
       <c r="I160" t="s">
         <v>824</v>
       </c>
@@ -19638,7 +19638,7 @@
       <c r="Z160" t="s">
         <v>813</v>
       </c>
-      <c r="AA160" s="79"/>
+      <c r="AA160" s="122"/>
     </row>
     <row r="161" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
@@ -19662,7 +19662,7 @@
       <c r="G161" t="s">
         <v>818</v>
       </c>
-      <c r="H161" s="80"/>
+      <c r="H161" s="123"/>
       <c r="I161" t="s">
         <v>824</v>
       </c>
@@ -19717,10 +19717,86 @@
       <c r="Z161" t="s">
         <v>813</v>
       </c>
-      <c r="AA161" s="79"/>
+      <c r="AA161" s="122"/>
     </row>
   </sheetData>
   <mergeCells count="92">
+    <mergeCell ref="AB6:AB9"/>
+    <mergeCell ref="AB10:AB13"/>
+    <mergeCell ref="H126:H129"/>
+    <mergeCell ref="AA126:AA129"/>
+    <mergeCell ref="AB126:AB129"/>
+    <mergeCell ref="H86:H89"/>
+    <mergeCell ref="AA86:AA89"/>
+    <mergeCell ref="H102:H105"/>
+    <mergeCell ref="AA102:AA105"/>
+    <mergeCell ref="H122:H125"/>
+    <mergeCell ref="AA122:AA125"/>
+    <mergeCell ref="AA98:AA101"/>
+    <mergeCell ref="H62:H65"/>
+    <mergeCell ref="AA62:AA65"/>
+    <mergeCell ref="H66:H69"/>
+    <mergeCell ref="AA66:AA69"/>
+    <mergeCell ref="H82:H85"/>
+    <mergeCell ref="AA82:AA85"/>
+    <mergeCell ref="H70:H73"/>
+    <mergeCell ref="AA70:AA73"/>
+    <mergeCell ref="H74:H77"/>
+    <mergeCell ref="AA74:AA77"/>
+    <mergeCell ref="H78:H81"/>
+    <mergeCell ref="AA78:AA81"/>
+    <mergeCell ref="H50:H53"/>
+    <mergeCell ref="AA50:AA53"/>
+    <mergeCell ref="H54:H57"/>
+    <mergeCell ref="AA54:AA57"/>
+    <mergeCell ref="H58:H61"/>
+    <mergeCell ref="AA58:AA61"/>
+    <mergeCell ref="H2:H5"/>
+    <mergeCell ref="AA2:AA5"/>
+    <mergeCell ref="H6:H9"/>
+    <mergeCell ref="AA6:AA9"/>
+    <mergeCell ref="H10:H13"/>
+    <mergeCell ref="AA10:AA13"/>
+    <mergeCell ref="AA94:AA97"/>
+    <mergeCell ref="H98:H101"/>
+    <mergeCell ref="H14:H17"/>
+    <mergeCell ref="L14:L17"/>
+    <mergeCell ref="AA14:AA17"/>
+    <mergeCell ref="H18:H21"/>
+    <mergeCell ref="AA18:AA21"/>
+    <mergeCell ref="H30:H33"/>
+    <mergeCell ref="AA30:AA33"/>
+    <mergeCell ref="H34:H37"/>
+    <mergeCell ref="AA34:AA37"/>
+    <mergeCell ref="H38:H41"/>
+    <mergeCell ref="AA38:AA41"/>
+    <mergeCell ref="H42:H45"/>
+    <mergeCell ref="AA42:AA45"/>
+    <mergeCell ref="H46:H49"/>
+    <mergeCell ref="H138:H141"/>
+    <mergeCell ref="AA138:AA141"/>
+    <mergeCell ref="H22:H25"/>
+    <mergeCell ref="AA22:AA25"/>
+    <mergeCell ref="H26:H29"/>
+    <mergeCell ref="H118:H121"/>
+    <mergeCell ref="AA118:AA121"/>
+    <mergeCell ref="H90:H93"/>
+    <mergeCell ref="AA90:AA93"/>
+    <mergeCell ref="H106:H109"/>
+    <mergeCell ref="AA106:AA109"/>
+    <mergeCell ref="H110:H113"/>
+    <mergeCell ref="AA110:AA113"/>
+    <mergeCell ref="H114:H117"/>
+    <mergeCell ref="AA114:AA117"/>
+    <mergeCell ref="H94:H97"/>
+    <mergeCell ref="L90:L93"/>
+    <mergeCell ref="AB18:AB21"/>
+    <mergeCell ref="AB26:AB29"/>
+    <mergeCell ref="AB30:AB33"/>
+    <mergeCell ref="AB54:AB57"/>
+    <mergeCell ref="AB62:AB65"/>
+    <mergeCell ref="AA26:AA29"/>
+    <mergeCell ref="AA46:AA49"/>
     <mergeCell ref="AB130:AB133"/>
     <mergeCell ref="AB146:AB149"/>
     <mergeCell ref="H154:H157"/>
@@ -19737,82 +19813,6 @@
     <mergeCell ref="AA130:AA133"/>
     <mergeCell ref="H134:H137"/>
     <mergeCell ref="AA134:AA137"/>
-    <mergeCell ref="L90:L93"/>
-    <mergeCell ref="AB18:AB21"/>
-    <mergeCell ref="AB26:AB29"/>
-    <mergeCell ref="AB30:AB33"/>
-    <mergeCell ref="AB54:AB57"/>
-    <mergeCell ref="AB62:AB65"/>
-    <mergeCell ref="AA26:AA29"/>
-    <mergeCell ref="AA46:AA49"/>
-    <mergeCell ref="H138:H141"/>
-    <mergeCell ref="AA138:AA141"/>
-    <mergeCell ref="H22:H25"/>
-    <mergeCell ref="AA22:AA25"/>
-    <mergeCell ref="H26:H29"/>
-    <mergeCell ref="H118:H121"/>
-    <mergeCell ref="AA118:AA121"/>
-    <mergeCell ref="H90:H93"/>
-    <mergeCell ref="AA90:AA93"/>
-    <mergeCell ref="H106:H109"/>
-    <mergeCell ref="AA106:AA109"/>
-    <mergeCell ref="H110:H113"/>
-    <mergeCell ref="AA110:AA113"/>
-    <mergeCell ref="H114:H117"/>
-    <mergeCell ref="AA114:AA117"/>
-    <mergeCell ref="H94:H97"/>
-    <mergeCell ref="AA94:AA97"/>
-    <mergeCell ref="H98:H101"/>
-    <mergeCell ref="H14:H17"/>
-    <mergeCell ref="L14:L17"/>
-    <mergeCell ref="AA14:AA17"/>
-    <mergeCell ref="H18:H21"/>
-    <mergeCell ref="AA18:AA21"/>
-    <mergeCell ref="H30:H33"/>
-    <mergeCell ref="AA30:AA33"/>
-    <mergeCell ref="H34:H37"/>
-    <mergeCell ref="AA34:AA37"/>
-    <mergeCell ref="H38:H41"/>
-    <mergeCell ref="AA38:AA41"/>
-    <mergeCell ref="H42:H45"/>
-    <mergeCell ref="AA42:AA45"/>
-    <mergeCell ref="H46:H49"/>
-    <mergeCell ref="H2:H5"/>
-    <mergeCell ref="AA2:AA5"/>
-    <mergeCell ref="H6:H9"/>
-    <mergeCell ref="AA6:AA9"/>
-    <mergeCell ref="H10:H13"/>
-    <mergeCell ref="AA10:AA13"/>
-    <mergeCell ref="H50:H53"/>
-    <mergeCell ref="AA50:AA53"/>
-    <mergeCell ref="H54:H57"/>
-    <mergeCell ref="AA54:AA57"/>
-    <mergeCell ref="H58:H61"/>
-    <mergeCell ref="AA58:AA61"/>
-    <mergeCell ref="H82:H85"/>
-    <mergeCell ref="AA82:AA85"/>
-    <mergeCell ref="H70:H73"/>
-    <mergeCell ref="AA70:AA73"/>
-    <mergeCell ref="H74:H77"/>
-    <mergeCell ref="AA74:AA77"/>
-    <mergeCell ref="H78:H81"/>
-    <mergeCell ref="AA78:AA81"/>
-    <mergeCell ref="AB6:AB9"/>
-    <mergeCell ref="AB10:AB13"/>
-    <mergeCell ref="H126:H129"/>
-    <mergeCell ref="AA126:AA129"/>
-    <mergeCell ref="AB126:AB129"/>
-    <mergeCell ref="H86:H89"/>
-    <mergeCell ref="AA86:AA89"/>
-    <mergeCell ref="H102:H105"/>
-    <mergeCell ref="AA102:AA105"/>
-    <mergeCell ref="H122:H125"/>
-    <mergeCell ref="AA122:AA125"/>
-    <mergeCell ref="AA98:AA101"/>
-    <mergeCell ref="H62:H65"/>
-    <mergeCell ref="AA62:AA65"/>
-    <mergeCell ref="H66:H69"/>
-    <mergeCell ref="AA66:AA69"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -19882,31 +19882,31 @@
         <v>112</v>
       </c>
       <c r="N1" s="33"/>
-      <c r="O1" s="109" t="s">
+      <c r="O1" s="87" t="s">
         <v>1414</v>
       </c>
-      <c r="P1" s="112" t="s">
+      <c r="P1" s="90" t="s">
         <v>1417</v>
       </c>
       <c r="Q1" s="30" t="s">
         <v>1408</v>
       </c>
-      <c r="R1" s="105"/>
-      <c r="S1" s="92" t="s">
+      <c r="R1" s="83"/>
+      <c r="S1" s="137" t="s">
         <v>1420</v>
       </c>
-      <c r="T1" s="93"/>
-      <c r="U1" s="93"/>
-      <c r="V1" s="93"/>
-      <c r="W1" s="94"/>
+      <c r="T1" s="138"/>
+      <c r="U1" s="138"/>
+      <c r="V1" s="138"/>
+      <c r="W1" s="139"/>
       <c r="X1" s="36"/>
-      <c r="Y1" s="139" t="s">
+      <c r="Y1" s="125" t="s">
         <v>1421</v>
       </c>
-      <c r="Z1" s="140"/>
-      <c r="AA1" s="140"/>
-      <c r="AB1" s="140"/>
-      <c r="AC1" s="141"/>
+      <c r="Z1" s="126"/>
+      <c r="AA1" s="126"/>
+      <c r="AB1" s="126"/>
+      <c r="AC1" s="127"/>
     </row>
     <row r="2" spans="1:30" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
@@ -19931,33 +19931,33 @@
       <c r="J2" s="44"/>
       <c r="K2" s="44"/>
       <c r="L2" s="44"/>
-      <c r="M2" s="86"/>
-      <c r="N2" s="108"/>
-      <c r="O2" s="110" t="s">
+      <c r="M2" s="151"/>
+      <c r="N2" s="86"/>
+      <c r="O2" s="88" t="s">
         <v>1415</v>
       </c>
-      <c r="P2" s="113" t="s">
+      <c r="P2" s="91" t="s">
         <v>1419</v>
       </c>
-      <c r="Q2" s="106">
+      <c r="Q2" s="84">
         <v>0.16450699999999999</v>
       </c>
-      <c r="R2" s="105"/>
+      <c r="R2" s="83"/>
       <c r="S2" s="59"/>
-      <c r="T2" s="89" t="s">
+      <c r="T2" s="152" t="s">
         <v>1393</v>
       </c>
-      <c r="U2" s="90"/>
-      <c r="V2" s="90"/>
-      <c r="W2" s="91"/>
-      <c r="X2" s="105"/>
+      <c r="U2" s="153"/>
+      <c r="V2" s="153"/>
+      <c r="W2" s="154"/>
+      <c r="X2" s="83"/>
       <c r="Y2" s="50"/>
-      <c r="Z2" s="136" t="s">
+      <c r="Z2" s="128" t="s">
         <v>1393</v>
       </c>
-      <c r="AA2" s="137"/>
-      <c r="AB2" s="137"/>
-      <c r="AC2" s="138"/>
+      <c r="AA2" s="129"/>
+      <c r="AB2" s="129"/>
+      <c r="AC2" s="130"/>
     </row>
     <row r="3" spans="1:30" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
@@ -19977,23 +19977,23 @@
       <c r="G3" s="15" t="s">
         <v>1048</v>
       </c>
-      <c r="H3" s="127"/>
-      <c r="I3" s="127"/>
-      <c r="J3" s="127"/>
-      <c r="K3" s="127"/>
-      <c r="L3" s="127"/>
-      <c r="M3" s="87"/>
-      <c r="N3" s="108"/>
-      <c r="O3" s="111" t="s">
+      <c r="H3" s="105"/>
+      <c r="I3" s="105"/>
+      <c r="J3" s="105"/>
+      <c r="K3" s="105"/>
+      <c r="L3" s="105"/>
+      <c r="M3" s="132"/>
+      <c r="N3" s="86"/>
+      <c r="O3" s="89" t="s">
         <v>1416</v>
       </c>
-      <c r="P3" s="114" t="s">
+      <c r="P3" s="92" t="s">
         <v>1418</v>
       </c>
-      <c r="Q3" s="107">
+      <c r="Q3" s="85">
         <v>0.16454779999999999</v>
       </c>
-      <c r="R3" s="105"/>
+      <c r="R3" s="83"/>
       <c r="S3" s="65" t="s">
         <v>1393</v>
       </c>
@@ -20052,8 +20052,8 @@
       <c r="J4" s="49"/>
       <c r="K4" s="49"/>
       <c r="L4" s="49"/>
-      <c r="M4" s="87"/>
-      <c r="N4" s="128"/>
+      <c r="M4" s="132"/>
+      <c r="N4" s="106"/>
       <c r="O4" s="60"/>
       <c r="P4" s="15"/>
       <c r="Q4" s="60"/>
@@ -20077,16 +20077,16 @@
       <c r="Y4" s="66" t="s">
         <v>1038</v>
       </c>
-      <c r="Z4" s="124" t="s">
+      <c r="Z4" s="102" t="s">
         <v>1400</v>
       </c>
-      <c r="AA4" s="125">
+      <c r="AA4" s="103">
         <v>0.77471239999999997</v>
       </c>
-      <c r="AB4" s="126">
+      <c r="AB4" s="104">
         <v>0.84573540000000003</v>
       </c>
-      <c r="AC4" s="135">
+      <c r="AC4" s="113">
         <v>0.86288480000000001</v>
       </c>
     </row>
@@ -20115,8 +20115,8 @@
       <c r="J5" s="49"/>
       <c r="K5" s="49"/>
       <c r="L5" s="49"/>
-      <c r="M5" s="87"/>
-      <c r="N5" s="101"/>
+      <c r="M5" s="132"/>
+      <c r="N5" s="79"/>
       <c r="O5" s="15"/>
       <c r="P5" s="15"/>
       <c r="Q5" s="15"/>
@@ -20139,16 +20139,16 @@
       <c r="Y5" s="67" t="s">
         <v>1039</v>
       </c>
-      <c r="Z5" s="115">
+      <c r="Z5" s="93">
         <v>0.77471239999999997</v>
       </c>
-      <c r="AA5" s="116" t="s">
+      <c r="AA5" s="94" t="s">
         <v>1400</v>
       </c>
-      <c r="AB5" s="117">
+      <c r="AB5" s="95">
         <v>0.81822309999999998</v>
       </c>
-      <c r="AC5" s="118">
+      <c r="AC5" s="96">
         <v>0.84944229999999998</v>
       </c>
     </row>
@@ -20177,8 +20177,8 @@
       <c r="J6" s="49"/>
       <c r="K6" s="49"/>
       <c r="L6" s="49"/>
-      <c r="M6" s="87"/>
-      <c r="N6" s="101"/>
+      <c r="M6" s="132"/>
+      <c r="N6" s="79"/>
       <c r="R6" s="58"/>
       <c r="S6" s="68" t="s">
         <v>1394</v>
@@ -20199,16 +20199,16 @@
       <c r="Y6" s="68" t="s">
         <v>1394</v>
       </c>
-      <c r="Z6" s="115">
+      <c r="Z6" s="93">
         <v>0.84573540000000003</v>
       </c>
-      <c r="AA6" s="119">
+      <c r="AA6" s="97">
         <v>0.81822309999999998</v>
       </c>
-      <c r="AB6" s="120" t="s">
+      <c r="AB6" s="98" t="s">
         <v>1400</v>
       </c>
-      <c r="AC6" s="118">
+      <c r="AC6" s="96">
         <v>0.78118350000000003</v>
       </c>
     </row>
@@ -20237,8 +20237,8 @@
       <c r="J7" s="49"/>
       <c r="K7" s="49"/>
       <c r="L7" s="49"/>
-      <c r="M7" s="87"/>
-      <c r="N7" s="101"/>
+      <c r="M7" s="132"/>
+      <c r="N7" s="79"/>
       <c r="R7" s="15"/>
       <c r="S7" s="68" t="s">
         <v>1041</v>
@@ -20259,16 +20259,16 @@
       <c r="Y7" s="69" t="s">
         <v>1041</v>
       </c>
-      <c r="Z7" s="121">
+      <c r="Z7" s="99">
         <v>0.86288480000000001</v>
       </c>
-      <c r="AA7" s="133">
+      <c r="AA7" s="111">
         <v>0.84944229999999998</v>
       </c>
-      <c r="AB7" s="122">
+      <c r="AB7" s="100">
         <v>0.78118350000000003</v>
       </c>
-      <c r="AC7" s="134" t="s">
+      <c r="AC7" s="112" t="s">
         <v>1404</v>
       </c>
       <c r="AD7" s="36"/>
@@ -20298,8 +20298,8 @@
       <c r="J8" s="49"/>
       <c r="K8" s="49"/>
       <c r="L8" s="49"/>
-      <c r="M8" s="87"/>
-      <c r="N8" s="101"/>
+      <c r="M8" s="132"/>
+      <c r="N8" s="79"/>
       <c r="S8" s="60"/>
       <c r="T8" s="60"/>
       <c r="U8" s="60"/>
@@ -20334,8 +20334,8 @@
       <c r="J9" s="50"/>
       <c r="K9" s="50"/>
       <c r="L9" s="50"/>
-      <c r="M9" s="88"/>
-      <c r="N9" s="101"/>
+      <c r="M9" s="133"/>
+      <c r="N9" s="79"/>
       <c r="S9" s="15"/>
       <c r="T9" s="15"/>
       <c r="U9" s="15"/>
@@ -20367,8 +20367,8 @@
       <c r="J10" s="49"/>
       <c r="K10" s="49"/>
       <c r="L10" s="49"/>
-      <c r="M10" s="142"/>
-      <c r="N10" s="101"/>
+      <c r="M10" s="131"/>
+      <c r="N10" s="79"/>
       <c r="S10" s="15"/>
       <c r="T10" s="15"/>
       <c r="U10" s="15"/>
@@ -20400,8 +20400,8 @@
       <c r="J11" s="49"/>
       <c r="K11" s="49"/>
       <c r="L11" s="49"/>
-      <c r="M11" s="87"/>
-      <c r="N11" s="101"/>
+      <c r="M11" s="132"/>
+      <c r="N11" s="79"/>
       <c r="S11" s="15"/>
       <c r="T11" s="15"/>
       <c r="U11" s="15"/>
@@ -20433,8 +20433,8 @@
       <c r="J12" s="49"/>
       <c r="K12" s="49"/>
       <c r="L12" s="49"/>
-      <c r="M12" s="87"/>
-      <c r="N12" s="101"/>
+      <c r="M12" s="132"/>
+      <c r="N12" s="79"/>
       <c r="S12" s="15"/>
       <c r="T12" s="15"/>
       <c r="U12" s="15"/>
@@ -20466,8 +20466,8 @@
       <c r="J13" s="49"/>
       <c r="K13" s="49"/>
       <c r="L13" s="49"/>
-      <c r="M13" s="87"/>
-      <c r="N13" s="101"/>
+      <c r="M13" s="132"/>
+      <c r="N13" s="79"/>
       <c r="S13" s="15"/>
       <c r="T13" s="15"/>
       <c r="U13" s="15"/>
@@ -20499,8 +20499,8 @@
       <c r="J14" s="49"/>
       <c r="K14" s="49"/>
       <c r="L14" s="49"/>
-      <c r="M14" s="87"/>
-      <c r="N14" s="101"/>
+      <c r="M14" s="132"/>
+      <c r="N14" s="79"/>
       <c r="S14" s="15"/>
       <c r="T14" s="15"/>
       <c r="U14" s="15"/>
@@ -20532,8 +20532,8 @@
       <c r="J15" s="49"/>
       <c r="K15" s="49"/>
       <c r="L15" s="49"/>
-      <c r="M15" s="88"/>
-      <c r="N15" s="101"/>
+      <c r="M15" s="133"/>
+      <c r="N15" s="79"/>
       <c r="S15" s="15"/>
       <c r="T15" s="15"/>
       <c r="U15" s="15"/>
@@ -20561,16 +20561,16 @@
       <c r="J16" s="51"/>
       <c r="K16" s="51"/>
       <c r="L16" s="51"/>
-      <c r="M16" s="147" t="s">
+      <c r="M16" s="140" t="s">
         <v>1426</v>
       </c>
-      <c r="N16" s="102"/>
+      <c r="N16" s="80"/>
       <c r="R16" s="15"/>
-      <c r="S16" s="131"/>
-      <c r="T16" s="132"/>
-      <c r="U16" s="132"/>
-      <c r="V16" s="132"/>
-      <c r="W16" s="132"/>
+      <c r="S16" s="109"/>
+      <c r="T16" s="110"/>
+      <c r="U16" s="110"/>
+      <c r="V16" s="110"/>
+      <c r="W16" s="110"/>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
@@ -20593,14 +20593,14 @@
       <c r="J17" s="49"/>
       <c r="K17" s="49"/>
       <c r="L17" s="49"/>
-      <c r="M17" s="148"/>
-      <c r="N17" s="102"/>
+      <c r="M17" s="141"/>
+      <c r="N17" s="80"/>
       <c r="R17" s="15"/>
       <c r="S17" s="45"/>
-      <c r="T17" s="131"/>
-      <c r="U17" s="132"/>
-      <c r="V17" s="132"/>
-      <c r="W17" s="132"/>
+      <c r="T17" s="109"/>
+      <c r="U17" s="110"/>
+      <c r="V17" s="110"/>
+      <c r="W17" s="110"/>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
@@ -20623,13 +20623,13 @@
       <c r="J18" s="49"/>
       <c r="K18" s="49"/>
       <c r="L18" s="49"/>
-      <c r="M18" s="148"/>
-      <c r="N18" s="102"/>
-      <c r="S18" s="129"/>
-      <c r="T18" s="129"/>
-      <c r="U18" s="129"/>
-      <c r="V18" s="129"/>
-      <c r="W18" s="129"/>
+      <c r="M18" s="141"/>
+      <c r="N18" s="80"/>
+      <c r="S18" s="107"/>
+      <c r="T18" s="107"/>
+      <c r="U18" s="107"/>
+      <c r="V18" s="107"/>
+      <c r="W18" s="107"/>
       <c r="X18" s="15"/>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.3">
@@ -20653,13 +20653,13 @@
       <c r="J19" s="49"/>
       <c r="K19" s="49"/>
       <c r="L19" s="49"/>
-      <c r="M19" s="148"/>
-      <c r="N19" s="102"/>
-      <c r="S19" s="130"/>
-      <c r="T19" s="123"/>
-      <c r="U19" s="123"/>
-      <c r="V19" s="123"/>
-      <c r="W19" s="123"/>
+      <c r="M19" s="141"/>
+      <c r="N19" s="80"/>
+      <c r="S19" s="108"/>
+      <c r="T19" s="101"/>
+      <c r="U19" s="101"/>
+      <c r="V19" s="101"/>
+      <c r="W19" s="101"/>
       <c r="X19" s="15"/>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.3">
@@ -20683,13 +20683,13 @@
       <c r="J20" s="49"/>
       <c r="K20" s="49"/>
       <c r="L20" s="49"/>
-      <c r="M20" s="148"/>
-      <c r="N20" s="102"/>
-      <c r="S20" s="130"/>
-      <c r="T20" s="123"/>
-      <c r="U20" s="123"/>
-      <c r="V20" s="123"/>
-      <c r="W20" s="123"/>
+      <c r="M20" s="141"/>
+      <c r="N20" s="80"/>
+      <c r="S20" s="108"/>
+      <c r="T20" s="101"/>
+      <c r="U20" s="101"/>
+      <c r="V20" s="101"/>
+      <c r="W20" s="101"/>
     </row>
     <row r="21" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="14" t="s">
@@ -20712,13 +20712,13 @@
       <c r="J21" s="49"/>
       <c r="K21" s="49"/>
       <c r="L21" s="49"/>
-      <c r="M21" s="148"/>
-      <c r="N21" s="102"/>
-      <c r="S21" s="130"/>
-      <c r="T21" s="123"/>
-      <c r="U21" s="123"/>
-      <c r="V21" s="123"/>
-      <c r="W21" s="123"/>
+      <c r="M21" s="141"/>
+      <c r="N21" s="80"/>
+      <c r="S21" s="108"/>
+      <c r="T21" s="101"/>
+      <c r="U21" s="101"/>
+      <c r="V21" s="101"/>
+      <c r="W21" s="101"/>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
@@ -20737,19 +20737,19 @@
       <c r="H22" s="11" t="s">
         <v>1057</v>
       </c>
-      <c r="I22" s="152"/>
-      <c r="J22" s="152"/>
-      <c r="K22" s="152"/>
-      <c r="L22" s="152"/>
-      <c r="M22" s="149" t="s">
+      <c r="I22" s="118"/>
+      <c r="J22" s="118"/>
+      <c r="K22" s="118"/>
+      <c r="L22" s="118"/>
+      <c r="M22" s="134" t="s">
         <v>1425</v>
       </c>
-      <c r="N22" s="102"/>
-      <c r="S22" s="130"/>
-      <c r="T22" s="123"/>
-      <c r="U22" s="123"/>
-      <c r="V22" s="123"/>
-      <c r="W22" s="123"/>
+      <c r="N22" s="80"/>
+      <c r="S22" s="108"/>
+      <c r="T22" s="101"/>
+      <c r="U22" s="101"/>
+      <c r="V22" s="101"/>
+      <c r="W22" s="101"/>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
@@ -20768,17 +20768,17 @@
       <c r="H23" s="15" t="s">
         <v>1058</v>
       </c>
-      <c r="I23" s="153"/>
-      <c r="J23" s="153"/>
-      <c r="K23" s="153"/>
-      <c r="L23" s="153"/>
-      <c r="M23" s="150"/>
-      <c r="N23" s="102"/>
-      <c r="S23" s="130"/>
-      <c r="T23" s="123"/>
-      <c r="U23" s="123"/>
-      <c r="V23" s="123"/>
-      <c r="W23" s="123"/>
+      <c r="I23" s="119"/>
+      <c r="J23" s="119"/>
+      <c r="K23" s="119"/>
+      <c r="L23" s="119"/>
+      <c r="M23" s="135"/>
+      <c r="N23" s="80"/>
+      <c r="S23" s="108"/>
+      <c r="T23" s="101"/>
+      <c r="U23" s="101"/>
+      <c r="V23" s="101"/>
+      <c r="W23" s="101"/>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
@@ -20797,17 +20797,17 @@
       <c r="H24" s="15" t="s">
         <v>1059</v>
       </c>
-      <c r="I24" s="153"/>
-      <c r="J24" s="153"/>
-      <c r="K24" s="153"/>
-      <c r="L24" s="153"/>
-      <c r="M24" s="150"/>
-      <c r="N24" s="102"/>
-      <c r="S24" s="130"/>
-      <c r="T24" s="123"/>
-      <c r="U24" s="123"/>
-      <c r="V24" s="123"/>
-      <c r="W24" s="123"/>
+      <c r="I24" s="119"/>
+      <c r="J24" s="119"/>
+      <c r="K24" s="119"/>
+      <c r="L24" s="119"/>
+      <c r="M24" s="135"/>
+      <c r="N24" s="80"/>
+      <c r="S24" s="108"/>
+      <c r="T24" s="101"/>
+      <c r="U24" s="101"/>
+      <c r="V24" s="101"/>
+      <c r="W24" s="101"/>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
@@ -20826,17 +20826,17 @@
       <c r="H25" s="15" t="s">
         <v>1060</v>
       </c>
-      <c r="I25" s="153"/>
-      <c r="J25" s="153"/>
-      <c r="K25" s="153"/>
-      <c r="L25" s="153"/>
-      <c r="M25" s="150"/>
-      <c r="N25" s="102"/>
-      <c r="S25" s="130"/>
-      <c r="T25" s="123"/>
-      <c r="U25" s="123"/>
-      <c r="V25" s="123"/>
-      <c r="W25" s="123"/>
+      <c r="I25" s="119"/>
+      <c r="J25" s="119"/>
+      <c r="K25" s="119"/>
+      <c r="L25" s="119"/>
+      <c r="M25" s="135"/>
+      <c r="N25" s="80"/>
+      <c r="S25" s="108"/>
+      <c r="T25" s="101"/>
+      <c r="U25" s="101"/>
+      <c r="V25" s="101"/>
+      <c r="W25" s="101"/>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
@@ -20855,17 +20855,17 @@
       <c r="H26" s="15" t="s">
         <v>1056</v>
       </c>
-      <c r="I26" s="153"/>
-      <c r="J26" s="153"/>
-      <c r="K26" s="153"/>
-      <c r="L26" s="153"/>
-      <c r="M26" s="150"/>
-      <c r="N26" s="102"/>
-      <c r="S26" s="130"/>
-      <c r="T26" s="123"/>
-      <c r="U26" s="123"/>
-      <c r="V26" s="123"/>
-      <c r="W26" s="123"/>
+      <c r="I26" s="119"/>
+      <c r="J26" s="119"/>
+      <c r="K26" s="119"/>
+      <c r="L26" s="119"/>
+      <c r="M26" s="135"/>
+      <c r="N26" s="80"/>
+      <c r="S26" s="108"/>
+      <c r="T26" s="101"/>
+      <c r="U26" s="101"/>
+      <c r="V26" s="101"/>
+      <c r="W26" s="101"/>
     </row>
     <row r="27" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="18" t="s">
@@ -20884,17 +20884,17 @@
       <c r="H27" s="19" t="s">
         <v>1055</v>
       </c>
-      <c r="I27" s="154"/>
-      <c r="J27" s="154"/>
-      <c r="K27" s="154"/>
-      <c r="L27" s="154"/>
-      <c r="M27" s="151"/>
-      <c r="N27" s="102"/>
-      <c r="S27" s="130"/>
-      <c r="T27" s="123"/>
-      <c r="U27" s="123"/>
-      <c r="V27" s="123"/>
-      <c r="W27" s="123"/>
+      <c r="I27" s="120"/>
+      <c r="J27" s="120"/>
+      <c r="K27" s="120"/>
+      <c r="L27" s="120"/>
+      <c r="M27" s="136"/>
+      <c r="N27" s="80"/>
+      <c r="S27" s="108"/>
+      <c r="T27" s="101"/>
+      <c r="U27" s="101"/>
+      <c r="V27" s="101"/>
+      <c r="W27" s="101"/>
     </row>
     <row r="28" spans="1:24" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="18" t="s">
@@ -20904,26 +20904,26 @@
         <v>1063</v>
       </c>
       <c r="C28" s="27"/>
-      <c r="D28" s="143"/>
+      <c r="D28" s="114"/>
       <c r="E28" s="27"/>
       <c r="F28" s="27"/>
-      <c r="G28" s="144" t="s">
+      <c r="G28" s="115" t="s">
         <v>1064</v>
       </c>
-      <c r="H28" s="145"/>
+      <c r="H28" s="116"/>
       <c r="I28" s="50"/>
       <c r="J28" s="50"/>
       <c r="K28" s="50"/>
       <c r="L28" s="50"/>
-      <c r="M28" s="146" t="s">
+      <c r="M28" s="117" t="s">
         <v>1409</v>
       </c>
-      <c r="N28" s="103"/>
-      <c r="S28" s="130"/>
-      <c r="T28" s="123"/>
-      <c r="U28" s="123"/>
-      <c r="V28" s="123"/>
-      <c r="W28" s="123"/>
+      <c r="N28" s="81"/>
+      <c r="S28" s="108"/>
+      <c r="T28" s="101"/>
+      <c r="U28" s="101"/>
+      <c r="V28" s="101"/>
+      <c r="W28" s="101"/>
       <c r="X28" s="15"/>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.3">
@@ -20949,10 +20949,10 @@
       <c r="J29" s="51"/>
       <c r="K29" s="51"/>
       <c r="L29" s="51"/>
-      <c r="M29" s="95" t="s">
+      <c r="M29" s="142" t="s">
         <v>1300</v>
       </c>
-      <c r="N29" s="104"/>
+      <c r="N29" s="82"/>
       <c r="T29" s="15"/>
       <c r="U29" s="15"/>
       <c r="V29" s="15"/>
@@ -20981,8 +20981,8 @@
       <c r="J30" s="49"/>
       <c r="K30" s="49"/>
       <c r="L30" s="49"/>
-      <c r="M30" s="96"/>
-      <c r="N30" s="104"/>
+      <c r="M30" s="143"/>
+      <c r="N30" s="82"/>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" s="14" t="s">
@@ -21007,8 +21007,8 @@
       <c r="J31" s="49"/>
       <c r="K31" s="49"/>
       <c r="L31" s="49"/>
-      <c r="M31" s="96"/>
-      <c r="N31" s="104"/>
+      <c r="M31" s="143"/>
+      <c r="N31" s="82"/>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32" s="14" t="s">
@@ -21033,8 +21033,8 @@
       <c r="J32" s="49"/>
       <c r="K32" s="49"/>
       <c r="L32" s="49"/>
-      <c r="M32" s="96"/>
-      <c r="N32" s="104"/>
+      <c r="M32" s="143"/>
+      <c r="N32" s="82"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="14" t="s">
@@ -21059,8 +21059,8 @@
       <c r="J33" s="49"/>
       <c r="K33" s="49"/>
       <c r="L33" s="49"/>
-      <c r="M33" s="96"/>
-      <c r="N33" s="104"/>
+      <c r="M33" s="143"/>
+      <c r="N33" s="82"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="14" t="s">
@@ -21085,8 +21085,8 @@
       <c r="J34" s="49"/>
       <c r="K34" s="49"/>
       <c r="L34" s="49"/>
-      <c r="M34" s="96"/>
-      <c r="N34" s="104"/>
+      <c r="M34" s="143"/>
+      <c r="N34" s="82"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="14" t="s">
@@ -21111,8 +21111,8 @@
       <c r="J35" s="49"/>
       <c r="K35" s="49"/>
       <c r="L35" s="49"/>
-      <c r="M35" s="96"/>
-      <c r="N35" s="104"/>
+      <c r="M35" s="143"/>
+      <c r="N35" s="82"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="14" t="s">
@@ -21137,8 +21137,8 @@
       <c r="J36" s="49"/>
       <c r="K36" s="49"/>
       <c r="L36" s="49"/>
-      <c r="M36" s="96"/>
-      <c r="N36" s="104"/>
+      <c r="M36" s="143"/>
+      <c r="N36" s="82"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="14" t="s">
@@ -21163,8 +21163,8 @@
       <c r="J37" s="49"/>
       <c r="K37" s="49"/>
       <c r="L37" s="49"/>
-      <c r="M37" s="96"/>
-      <c r="N37" s="104"/>
+      <c r="M37" s="143"/>
+      <c r="N37" s="82"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="14" t="s">
@@ -21189,8 +21189,8 @@
       <c r="J38" s="49"/>
       <c r="K38" s="49"/>
       <c r="L38" s="49"/>
-      <c r="M38" s="96"/>
-      <c r="N38" s="104"/>
+      <c r="M38" s="143"/>
+      <c r="N38" s="82"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="14" t="s">
@@ -21215,8 +21215,8 @@
       <c r="J39" s="49"/>
       <c r="K39" s="49"/>
       <c r="L39" s="49"/>
-      <c r="M39" s="96"/>
-      <c r="N39" s="104"/>
+      <c r="M39" s="143"/>
+      <c r="N39" s="82"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="14" t="s">
@@ -21241,8 +21241,8 @@
       <c r="J40" s="49"/>
       <c r="K40" s="49"/>
       <c r="L40" s="49"/>
-      <c r="M40" s="96"/>
-      <c r="N40" s="104"/>
+      <c r="M40" s="143"/>
+      <c r="N40" s="82"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
@@ -21267,8 +21267,8 @@
       <c r="J41" s="49"/>
       <c r="K41" s="49"/>
       <c r="L41" s="49"/>
-      <c r="M41" s="96"/>
-      <c r="N41" s="104"/>
+      <c r="M41" s="143"/>
+      <c r="N41" s="82"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="14" t="s">
@@ -21293,8 +21293,8 @@
       <c r="J42" s="49"/>
       <c r="K42" s="49"/>
       <c r="L42" s="49"/>
-      <c r="M42" s="96"/>
-      <c r="N42" s="104"/>
+      <c r="M42" s="143"/>
+      <c r="N42" s="82"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
@@ -21319,8 +21319,8 @@
       <c r="J43" s="49"/>
       <c r="K43" s="49"/>
       <c r="L43" s="49"/>
-      <c r="M43" s="96"/>
-      <c r="N43" s="104"/>
+      <c r="M43" s="143"/>
+      <c r="N43" s="82"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="14" t="s">
@@ -21345,8 +21345,8 @@
       <c r="J44" s="49"/>
       <c r="K44" s="49"/>
       <c r="L44" s="49"/>
-      <c r="M44" s="96"/>
-      <c r="N44" s="104"/>
+      <c r="M44" s="143"/>
+      <c r="N44" s="82"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="14" t="s">
@@ -21371,8 +21371,8 @@
       <c r="J45" s="49"/>
       <c r="K45" s="49"/>
       <c r="L45" s="49"/>
-      <c r="M45" s="96"/>
-      <c r="N45" s="104"/>
+      <c r="M45" s="143"/>
+      <c r="N45" s="82"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="14" t="s">
@@ -21397,8 +21397,8 @@
       <c r="J46" s="49"/>
       <c r="K46" s="49"/>
       <c r="L46" s="49"/>
-      <c r="M46" s="96"/>
-      <c r="N46" s="104"/>
+      <c r="M46" s="143"/>
+      <c r="N46" s="82"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="14" t="s">
@@ -21423,8 +21423,8 @@
       <c r="J47" s="49"/>
       <c r="K47" s="49"/>
       <c r="L47" s="49"/>
-      <c r="M47" s="96"/>
-      <c r="N47" s="104"/>
+      <c r="M47" s="143"/>
+      <c r="N47" s="82"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="14" t="s">
@@ -21449,8 +21449,8 @@
       <c r="J48" s="49"/>
       <c r="K48" s="49"/>
       <c r="L48" s="49"/>
-      <c r="M48" s="96"/>
-      <c r="N48" s="104"/>
+      <c r="M48" s="143"/>
+      <c r="N48" s="82"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="14" t="s">
@@ -21475,8 +21475,8 @@
       <c r="J49" s="49"/>
       <c r="K49" s="49"/>
       <c r="L49" s="49"/>
-      <c r="M49" s="96"/>
-      <c r="N49" s="104"/>
+      <c r="M49" s="143"/>
+      <c r="N49" s="82"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="14" t="s">
@@ -21501,8 +21501,8 @@
       <c r="J50" s="49"/>
       <c r="K50" s="49"/>
       <c r="L50" s="49"/>
-      <c r="M50" s="96"/>
-      <c r="N50" s="104"/>
+      <c r="M50" s="143"/>
+      <c r="N50" s="82"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="14" t="s">
@@ -21527,8 +21527,8 @@
       <c r="J51" s="49"/>
       <c r="K51" s="49"/>
       <c r="L51" s="49"/>
-      <c r="M51" s="96"/>
-      <c r="N51" s="104"/>
+      <c r="M51" s="143"/>
+      <c r="N51" s="82"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="14" t="s">
@@ -21553,8 +21553,8 @@
       <c r="J52" s="49"/>
       <c r="K52" s="49"/>
       <c r="L52" s="49"/>
-      <c r="M52" s="96"/>
-      <c r="N52" s="104"/>
+      <c r="M52" s="143"/>
+      <c r="N52" s="82"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="14" t="s">
@@ -21579,8 +21579,8 @@
       <c r="J53" s="49"/>
       <c r="K53" s="49"/>
       <c r="L53" s="49"/>
-      <c r="M53" s="96"/>
-      <c r="N53" s="104"/>
+      <c r="M53" s="143"/>
+      <c r="N53" s="82"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="14" t="s">
@@ -21605,8 +21605,8 @@
       <c r="J54" s="49"/>
       <c r="K54" s="49"/>
       <c r="L54" s="49"/>
-      <c r="M54" s="96"/>
-      <c r="N54" s="104"/>
+      <c r="M54" s="143"/>
+      <c r="N54" s="82"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="14" t="s">
@@ -21631,8 +21631,8 @@
       <c r="J55" s="49"/>
       <c r="K55" s="49"/>
       <c r="L55" s="49"/>
-      <c r="M55" s="96"/>
-      <c r="N55" s="104"/>
+      <c r="M55" s="143"/>
+      <c r="N55" s="82"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="14" t="s">
@@ -21657,8 +21657,8 @@
       <c r="J56" s="49"/>
       <c r="K56" s="49"/>
       <c r="L56" s="49"/>
-      <c r="M56" s="96"/>
-      <c r="N56" s="104"/>
+      <c r="M56" s="143"/>
+      <c r="N56" s="82"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
@@ -21683,8 +21683,8 @@
       <c r="J57" s="49"/>
       <c r="K57" s="49"/>
       <c r="L57" s="49"/>
-      <c r="M57" s="96"/>
-      <c r="N57" s="104"/>
+      <c r="M57" s="143"/>
+      <c r="N57" s="82"/>
     </row>
     <row r="58" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="18" t="s">
@@ -21709,8 +21709,8 @@
       <c r="J58" s="49"/>
       <c r="K58" s="49"/>
       <c r="L58" s="49"/>
-      <c r="M58" s="96"/>
-      <c r="N58" s="104"/>
+      <c r="M58" s="143"/>
+      <c r="N58" s="82"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="10" t="s">
@@ -21735,8 +21735,8 @@
       <c r="J59" s="49"/>
       <c r="K59" s="49"/>
       <c r="L59" s="49"/>
-      <c r="M59" s="96"/>
-      <c r="N59" s="104"/>
+      <c r="M59" s="143"/>
+      <c r="N59" s="82"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="14" t="s">
@@ -21761,8 +21761,8 @@
       <c r="J60" s="49"/>
       <c r="K60" s="49"/>
       <c r="L60" s="49"/>
-      <c r="M60" s="96"/>
-      <c r="N60" s="104"/>
+      <c r="M60" s="143"/>
+      <c r="N60" s="82"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="14" t="s">
@@ -21787,8 +21787,8 @@
       <c r="J61" s="49"/>
       <c r="K61" s="49"/>
       <c r="L61" s="49"/>
-      <c r="M61" s="96"/>
-      <c r="N61" s="104"/>
+      <c r="M61" s="143"/>
+      <c r="N61" s="82"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="14" t="s">
@@ -21813,8 +21813,8 @@
       <c r="J62" s="49"/>
       <c r="K62" s="49"/>
       <c r="L62" s="49"/>
-      <c r="M62" s="96"/>
-      <c r="N62" s="104"/>
+      <c r="M62" s="143"/>
+      <c r="N62" s="82"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="14" t="s">
@@ -21839,8 +21839,8 @@
       <c r="J63" s="49"/>
       <c r="K63" s="49"/>
       <c r="L63" s="49"/>
-      <c r="M63" s="96"/>
-      <c r="N63" s="104"/>
+      <c r="M63" s="143"/>
+      <c r="N63" s="82"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="14" t="s">
@@ -21865,8 +21865,8 @@
       <c r="J64" s="49"/>
       <c r="K64" s="49"/>
       <c r="L64" s="49"/>
-      <c r="M64" s="96"/>
-      <c r="N64" s="104"/>
+      <c r="M64" s="143"/>
+      <c r="N64" s="82"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="14" t="s">
@@ -21891,8 +21891,8 @@
       <c r="J65" s="49"/>
       <c r="K65" s="49"/>
       <c r="L65" s="49"/>
-      <c r="M65" s="96"/>
-      <c r="N65" s="104"/>
+      <c r="M65" s="143"/>
+      <c r="N65" s="82"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="14" t="s">
@@ -21917,8 +21917,8 @@
       <c r="J66" s="49"/>
       <c r="K66" s="49"/>
       <c r="L66" s="49"/>
-      <c r="M66" s="96"/>
-      <c r="N66" s="104"/>
+      <c r="M66" s="143"/>
+      <c r="N66" s="82"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="14" t="s">
@@ -21943,8 +21943,8 @@
       <c r="J67" s="49"/>
       <c r="K67" s="49"/>
       <c r="L67" s="49"/>
-      <c r="M67" s="96"/>
-      <c r="N67" s="104"/>
+      <c r="M67" s="143"/>
+      <c r="N67" s="82"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="14" t="s">
@@ -21969,8 +21969,8 @@
       <c r="J68" s="49"/>
       <c r="K68" s="49"/>
       <c r="L68" s="49"/>
-      <c r="M68" s="96"/>
-      <c r="N68" s="104"/>
+      <c r="M68" s="143"/>
+      <c r="N68" s="82"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="14" t="s">
@@ -21995,8 +21995,8 @@
       <c r="J69" s="49"/>
       <c r="K69" s="49"/>
       <c r="L69" s="49"/>
-      <c r="M69" s="96"/>
-      <c r="N69" s="104"/>
+      <c r="M69" s="143"/>
+      <c r="N69" s="82"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="14" t="s">
@@ -22021,8 +22021,8 @@
       <c r="J70" s="49"/>
       <c r="K70" s="49"/>
       <c r="L70" s="49"/>
-      <c r="M70" s="96"/>
-      <c r="N70" s="104"/>
+      <c r="M70" s="143"/>
+      <c r="N70" s="82"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="14" t="s">
@@ -22047,8 +22047,8 @@
       <c r="J71" s="49"/>
       <c r="K71" s="49"/>
       <c r="L71" s="49"/>
-      <c r="M71" s="96"/>
-      <c r="N71" s="104"/>
+      <c r="M71" s="143"/>
+      <c r="N71" s="82"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="14" t="s">
@@ -22073,8 +22073,8 @@
       <c r="J72" s="49"/>
       <c r="K72" s="49"/>
       <c r="L72" s="49"/>
-      <c r="M72" s="96"/>
-      <c r="N72" s="104"/>
+      <c r="M72" s="143"/>
+      <c r="N72" s="82"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="14" t="s">
@@ -22099,8 +22099,8 @@
       <c r="J73" s="49"/>
       <c r="K73" s="49"/>
       <c r="L73" s="49"/>
-      <c r="M73" s="96"/>
-      <c r="N73" s="104"/>
+      <c r="M73" s="143"/>
+      <c r="N73" s="82"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="14" t="s">
@@ -22125,8 +22125,8 @@
       <c r="J74" s="49"/>
       <c r="K74" s="49"/>
       <c r="L74" s="49"/>
-      <c r="M74" s="96"/>
-      <c r="N74" s="104"/>
+      <c r="M74" s="143"/>
+      <c r="N74" s="82"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="14" t="s">
@@ -22151,8 +22151,8 @@
       <c r="J75" s="49"/>
       <c r="K75" s="49"/>
       <c r="L75" s="49"/>
-      <c r="M75" s="96"/>
-      <c r="N75" s="104"/>
+      <c r="M75" s="143"/>
+      <c r="N75" s="82"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="14" t="s">
@@ -22177,8 +22177,8 @@
       <c r="J76" s="49"/>
       <c r="K76" s="49"/>
       <c r="L76" s="49"/>
-      <c r="M76" s="96"/>
-      <c r="N76" s="104"/>
+      <c r="M76" s="143"/>
+      <c r="N76" s="82"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="14" t="s">
@@ -22203,8 +22203,8 @@
       <c r="J77" s="49"/>
       <c r="K77" s="49"/>
       <c r="L77" s="49"/>
-      <c r="M77" s="96"/>
-      <c r="N77" s="104"/>
+      <c r="M77" s="143"/>
+      <c r="N77" s="82"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="14" t="s">
@@ -22229,8 +22229,8 @@
       <c r="J78" s="49"/>
       <c r="K78" s="49"/>
       <c r="L78" s="49"/>
-      <c r="M78" s="96"/>
-      <c r="N78" s="104"/>
+      <c r="M78" s="143"/>
+      <c r="N78" s="82"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="14" t="s">
@@ -22255,8 +22255,8 @@
       <c r="J79" s="49"/>
       <c r="K79" s="49"/>
       <c r="L79" s="49"/>
-      <c r="M79" s="96"/>
-      <c r="N79" s="104"/>
+      <c r="M79" s="143"/>
+      <c r="N79" s="82"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="14" t="s">
@@ -22281,8 +22281,8 @@
       <c r="J80" s="49"/>
       <c r="K80" s="49"/>
       <c r="L80" s="49"/>
-      <c r="M80" s="96"/>
-      <c r="N80" s="104"/>
+      <c r="M80" s="143"/>
+      <c r="N80" s="82"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="14" t="s">
@@ -22307,8 +22307,8 @@
       <c r="J81" s="49"/>
       <c r="K81" s="49"/>
       <c r="L81" s="49"/>
-      <c r="M81" s="96"/>
-      <c r="N81" s="104"/>
+      <c r="M81" s="143"/>
+      <c r="N81" s="82"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="14" t="s">
@@ -22333,8 +22333,8 @@
       <c r="J82" s="49"/>
       <c r="K82" s="49"/>
       <c r="L82" s="49"/>
-      <c r="M82" s="96"/>
-      <c r="N82" s="104"/>
+      <c r="M82" s="143"/>
+      <c r="N82" s="82"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="14" t="s">
@@ -22359,8 +22359,8 @@
       <c r="J83" s="49"/>
       <c r="K83" s="49"/>
       <c r="L83" s="49"/>
-      <c r="M83" s="96"/>
-      <c r="N83" s="104"/>
+      <c r="M83" s="143"/>
+      <c r="N83" s="82"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="14" t="s">
@@ -22385,8 +22385,8 @@
       <c r="J84" s="49"/>
       <c r="K84" s="49"/>
       <c r="L84" s="49"/>
-      <c r="M84" s="96"/>
-      <c r="N84" s="104"/>
+      <c r="M84" s="143"/>
+      <c r="N84" s="82"/>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="14" t="s">
@@ -22411,8 +22411,8 @@
       <c r="J85" s="49"/>
       <c r="K85" s="49"/>
       <c r="L85" s="49"/>
-      <c r="M85" s="96"/>
-      <c r="N85" s="104"/>
+      <c r="M85" s="143"/>
+      <c r="N85" s="82"/>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="14" t="s">
@@ -22437,8 +22437,8 @@
       <c r="J86" s="49"/>
       <c r="K86" s="49"/>
       <c r="L86" s="49"/>
-      <c r="M86" s="96"/>
-      <c r="N86" s="104"/>
+      <c r="M86" s="143"/>
+      <c r="N86" s="82"/>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="14" t="s">
@@ -22463,8 +22463,8 @@
       <c r="J87" s="49"/>
       <c r="K87" s="49"/>
       <c r="L87" s="49"/>
-      <c r="M87" s="96"/>
-      <c r="N87" s="104"/>
+      <c r="M87" s="143"/>
+      <c r="N87" s="82"/>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="14" t="s">
@@ -22489,8 +22489,8 @@
       <c r="J88" s="49"/>
       <c r="K88" s="49"/>
       <c r="L88" s="49"/>
-      <c r="M88" s="96"/>
-      <c r="N88" s="104"/>
+      <c r="M88" s="143"/>
+      <c r="N88" s="82"/>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="14" t="s">
@@ -22515,8 +22515,8 @@
       <c r="J89" s="49"/>
       <c r="K89" s="49"/>
       <c r="L89" s="49"/>
-      <c r="M89" s="96"/>
-      <c r="N89" s="104"/>
+      <c r="M89" s="143"/>
+      <c r="N89" s="82"/>
     </row>
     <row r="90" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="18" t="s">
@@ -22541,8 +22541,8 @@
       <c r="J90" s="49"/>
       <c r="K90" s="49"/>
       <c r="L90" s="49"/>
-      <c r="M90" s="96"/>
-      <c r="N90" s="104"/>
+      <c r="M90" s="143"/>
+      <c r="N90" s="82"/>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="14" t="s">
@@ -22567,8 +22567,8 @@
       <c r="J91" s="49"/>
       <c r="K91" s="49"/>
       <c r="L91" s="49"/>
-      <c r="M91" s="96"/>
-      <c r="N91" s="104"/>
+      <c r="M91" s="143"/>
+      <c r="N91" s="82"/>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="14" t="s">
@@ -22593,8 +22593,8 @@
       <c r="J92" s="49"/>
       <c r="K92" s="49"/>
       <c r="L92" s="49"/>
-      <c r="M92" s="96"/>
-      <c r="N92" s="104"/>
+      <c r="M92" s="143"/>
+      <c r="N92" s="82"/>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" s="14" t="s">
@@ -22619,8 +22619,8 @@
       <c r="J93" s="49"/>
       <c r="K93" s="49"/>
       <c r="L93" s="49"/>
-      <c r="M93" s="96"/>
-      <c r="N93" s="104"/>
+      <c r="M93" s="143"/>
+      <c r="N93" s="82"/>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" s="14" t="s">
@@ -22645,8 +22645,8 @@
       <c r="J94" s="49"/>
       <c r="K94" s="49"/>
       <c r="L94" s="49"/>
-      <c r="M94" s="96"/>
-      <c r="N94" s="104"/>
+      <c r="M94" s="143"/>
+      <c r="N94" s="82"/>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" s="14" t="s">
@@ -22671,8 +22671,8 @@
       <c r="J95" s="49"/>
       <c r="K95" s="49"/>
       <c r="L95" s="49"/>
-      <c r="M95" s="96"/>
-      <c r="N95" s="104"/>
+      <c r="M95" s="143"/>
+      <c r="N95" s="82"/>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="14" t="s">
@@ -22697,8 +22697,8 @@
       <c r="J96" s="49"/>
       <c r="K96" s="49"/>
       <c r="L96" s="49"/>
-      <c r="M96" s="96"/>
-      <c r="N96" s="104"/>
+      <c r="M96" s="143"/>
+      <c r="N96" s="82"/>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" s="14" t="s">
@@ -22723,8 +22723,8 @@
       <c r="J97" s="49"/>
       <c r="K97" s="49"/>
       <c r="L97" s="49"/>
-      <c r="M97" s="96"/>
-      <c r="N97" s="104"/>
+      <c r="M97" s="143"/>
+      <c r="N97" s="82"/>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" s="14" t="s">
@@ -22749,8 +22749,8 @@
       <c r="J98" s="49"/>
       <c r="K98" s="49"/>
       <c r="L98" s="49"/>
-      <c r="M98" s="96"/>
-      <c r="N98" s="104"/>
+      <c r="M98" s="143"/>
+      <c r="N98" s="82"/>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="14" t="s">
@@ -22775,8 +22775,8 @@
       <c r="J99" s="49"/>
       <c r="K99" s="49"/>
       <c r="L99" s="49"/>
-      <c r="M99" s="96"/>
-      <c r="N99" s="104"/>
+      <c r="M99" s="143"/>
+      <c r="N99" s="82"/>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="14" t="s">
@@ -22801,8 +22801,8 @@
       <c r="J100" s="49"/>
       <c r="K100" s="49"/>
       <c r="L100" s="49"/>
-      <c r="M100" s="96"/>
-      <c r="N100" s="104"/>
+      <c r="M100" s="143"/>
+      <c r="N100" s="82"/>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" s="14" t="s">
@@ -22827,8 +22827,8 @@
       <c r="J101" s="49"/>
       <c r="K101" s="49"/>
       <c r="L101" s="49"/>
-      <c r="M101" s="96"/>
-      <c r="N101" s="104"/>
+      <c r="M101" s="143"/>
+      <c r="N101" s="82"/>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="14" t="s">
@@ -22853,8 +22853,8 @@
       <c r="J102" s="49"/>
       <c r="K102" s="49"/>
       <c r="L102" s="49"/>
-      <c r="M102" s="96"/>
-      <c r="N102" s="104"/>
+      <c r="M102" s="143"/>
+      <c r="N102" s="82"/>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="14" t="s">
@@ -22879,8 +22879,8 @@
       <c r="J103" s="49"/>
       <c r="K103" s="49"/>
       <c r="L103" s="49"/>
-      <c r="M103" s="96"/>
-      <c r="N103" s="104"/>
+      <c r="M103" s="143"/>
+      <c r="N103" s="82"/>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" s="14" t="s">
@@ -22905,8 +22905,8 @@
       <c r="J104" s="49"/>
       <c r="K104" s="49"/>
       <c r="L104" s="49"/>
-      <c r="M104" s="96"/>
-      <c r="N104" s="104"/>
+      <c r="M104" s="143"/>
+      <c r="N104" s="82"/>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" s="14" t="s">
@@ -22931,8 +22931,8 @@
       <c r="J105" s="49"/>
       <c r="K105" s="49"/>
       <c r="L105" s="49"/>
-      <c r="M105" s="96"/>
-      <c r="N105" s="104"/>
+      <c r="M105" s="143"/>
+      <c r="N105" s="82"/>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" s="14" t="s">
@@ -22957,8 +22957,8 @@
       <c r="J106" s="49"/>
       <c r="K106" s="49"/>
       <c r="L106" s="49"/>
-      <c r="M106" s="96"/>
-      <c r="N106" s="104"/>
+      <c r="M106" s="143"/>
+      <c r="N106" s="82"/>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" s="14" t="s">
@@ -22983,8 +22983,8 @@
       <c r="J107" s="49"/>
       <c r="K107" s="49"/>
       <c r="L107" s="49"/>
-      <c r="M107" s="96"/>
-      <c r="N107" s="104"/>
+      <c r="M107" s="143"/>
+      <c r="N107" s="82"/>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" s="14" t="s">
@@ -23009,8 +23009,8 @@
       <c r="J108" s="49"/>
       <c r="K108" s="49"/>
       <c r="L108" s="49"/>
-      <c r="M108" s="96"/>
-      <c r="N108" s="104"/>
+      <c r="M108" s="143"/>
+      <c r="N108" s="82"/>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" s="14" t="s">
@@ -23035,8 +23035,8 @@
       <c r="J109" s="49"/>
       <c r="K109" s="49"/>
       <c r="L109" s="49"/>
-      <c r="M109" s="96"/>
-      <c r="N109" s="104"/>
+      <c r="M109" s="143"/>
+      <c r="N109" s="82"/>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" s="14" t="s">
@@ -23061,8 +23061,8 @@
       <c r="J110" s="49"/>
       <c r="K110" s="49"/>
       <c r="L110" s="49"/>
-      <c r="M110" s="96"/>
-      <c r="N110" s="104"/>
+      <c r="M110" s="143"/>
+      <c r="N110" s="82"/>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" s="14" t="s">
@@ -23087,8 +23087,8 @@
       <c r="J111" s="49"/>
       <c r="K111" s="49"/>
       <c r="L111" s="49"/>
-      <c r="M111" s="96"/>
-      <c r="N111" s="104"/>
+      <c r="M111" s="143"/>
+      <c r="N111" s="82"/>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" s="14" t="s">
@@ -23113,8 +23113,8 @@
       <c r="J112" s="49"/>
       <c r="K112" s="49"/>
       <c r="L112" s="49"/>
-      <c r="M112" s="96"/>
-      <c r="N112" s="104"/>
+      <c r="M112" s="143"/>
+      <c r="N112" s="82"/>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" s="14" t="s">
@@ -23139,8 +23139,8 @@
       <c r="J113" s="49"/>
       <c r="K113" s="49"/>
       <c r="L113" s="49"/>
-      <c r="M113" s="96"/>
-      <c r="N113" s="104"/>
+      <c r="M113" s="143"/>
+      <c r="N113" s="82"/>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" s="14" t="s">
@@ -23165,8 +23165,8 @@
       <c r="J114" s="49"/>
       <c r="K114" s="49"/>
       <c r="L114" s="49"/>
-      <c r="M114" s="96"/>
-      <c r="N114" s="104"/>
+      <c r="M114" s="143"/>
+      <c r="N114" s="82"/>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" s="14" t="s">
@@ -23191,8 +23191,8 @@
       <c r="J115" s="49"/>
       <c r="K115" s="49"/>
       <c r="L115" s="49"/>
-      <c r="M115" s="96"/>
-      <c r="N115" s="104"/>
+      <c r="M115" s="143"/>
+      <c r="N115" s="82"/>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116" s="14" t="s">
@@ -23217,8 +23217,8 @@
       <c r="J116" s="49"/>
       <c r="K116" s="49"/>
       <c r="L116" s="49"/>
-      <c r="M116" s="96"/>
-      <c r="N116" s="104"/>
+      <c r="M116" s="143"/>
+      <c r="N116" s="82"/>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117" s="14" t="s">
@@ -23243,8 +23243,8 @@
       <c r="J117" s="49"/>
       <c r="K117" s="49"/>
       <c r="L117" s="49"/>
-      <c r="M117" s="96"/>
-      <c r="N117" s="104"/>
+      <c r="M117" s="143"/>
+      <c r="N117" s="82"/>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118" s="14" t="s">
@@ -23269,8 +23269,8 @@
       <c r="J118" s="49"/>
       <c r="K118" s="49"/>
       <c r="L118" s="49"/>
-      <c r="M118" s="96"/>
-      <c r="N118" s="104"/>
+      <c r="M118" s="143"/>
+      <c r="N118" s="82"/>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119" s="14" t="s">
@@ -23295,8 +23295,8 @@
       <c r="J119" s="49"/>
       <c r="K119" s="49"/>
       <c r="L119" s="49"/>
-      <c r="M119" s="96"/>
-      <c r="N119" s="104"/>
+      <c r="M119" s="143"/>
+      <c r="N119" s="82"/>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120" s="14" t="s">
@@ -23321,8 +23321,8 @@
       <c r="J120" s="49"/>
       <c r="K120" s="49"/>
       <c r="L120" s="49"/>
-      <c r="M120" s="96"/>
-      <c r="N120" s="104"/>
+      <c r="M120" s="143"/>
+      <c r="N120" s="82"/>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121" s="14" t="s">
@@ -23347,8 +23347,8 @@
       <c r="J121" s="49"/>
       <c r="K121" s="49"/>
       <c r="L121" s="49"/>
-      <c r="M121" s="96"/>
-      <c r="N121" s="104"/>
+      <c r="M121" s="143"/>
+      <c r="N121" s="82"/>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A122" s="14" t="s">
@@ -23373,8 +23373,8 @@
       <c r="J122" s="49"/>
       <c r="K122" s="49"/>
       <c r="L122" s="49"/>
-      <c r="M122" s="96"/>
-      <c r="N122" s="104"/>
+      <c r="M122" s="143"/>
+      <c r="N122" s="82"/>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A123" s="14" t="s">
@@ -23399,8 +23399,8 @@
       <c r="J123" s="49"/>
       <c r="K123" s="49"/>
       <c r="L123" s="49"/>
-      <c r="M123" s="96"/>
-      <c r="N123" s="104"/>
+      <c r="M123" s="143"/>
+      <c r="N123" s="82"/>
     </row>
     <row r="124" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="18" t="s">
@@ -23425,8 +23425,8 @@
       <c r="J124" s="49"/>
       <c r="K124" s="49"/>
       <c r="L124" s="49"/>
-      <c r="M124" s="96"/>
-      <c r="N124" s="104"/>
+      <c r="M124" s="143"/>
+      <c r="N124" s="82"/>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A125" s="14" t="s">
@@ -23451,8 +23451,8 @@
       <c r="J125" s="49"/>
       <c r="K125" s="49"/>
       <c r="L125" s="49"/>
-      <c r="M125" s="96"/>
-      <c r="N125" s="104"/>
+      <c r="M125" s="143"/>
+      <c r="N125" s="82"/>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A126" s="14" t="s">
@@ -23477,8 +23477,8 @@
       <c r="J126" s="49"/>
       <c r="K126" s="49"/>
       <c r="L126" s="49"/>
-      <c r="M126" s="96"/>
-      <c r="N126" s="104"/>
+      <c r="M126" s="143"/>
+      <c r="N126" s="82"/>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A127" s="14" t="s">
@@ -23503,8 +23503,8 @@
       <c r="J127" s="49"/>
       <c r="K127" s="49"/>
       <c r="L127" s="49"/>
-      <c r="M127" s="96"/>
-      <c r="N127" s="104"/>
+      <c r="M127" s="143"/>
+      <c r="N127" s="82"/>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A128" s="14" t="s">
@@ -23529,8 +23529,8 @@
       <c r="J128" s="49"/>
       <c r="K128" s="49"/>
       <c r="L128" s="49"/>
-      <c r="M128" s="96"/>
-      <c r="N128" s="104"/>
+      <c r="M128" s="143"/>
+      <c r="N128" s="82"/>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A129" s="14" t="s">
@@ -23555,8 +23555,8 @@
       <c r="J129" s="49"/>
       <c r="K129" s="49"/>
       <c r="L129" s="49"/>
-      <c r="M129" s="96"/>
-      <c r="N129" s="104"/>
+      <c r="M129" s="143"/>
+      <c r="N129" s="82"/>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A130" s="14" t="s">
@@ -23581,8 +23581,8 @@
       <c r="J130" s="49"/>
       <c r="K130" s="49"/>
       <c r="L130" s="49"/>
-      <c r="M130" s="96"/>
-      <c r="N130" s="104"/>
+      <c r="M130" s="143"/>
+      <c r="N130" s="82"/>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A131" s="14" t="s">
@@ -23607,8 +23607,8 @@
       <c r="J131" s="49"/>
       <c r="K131" s="49"/>
       <c r="L131" s="49"/>
-      <c r="M131" s="96"/>
-      <c r="N131" s="104"/>
+      <c r="M131" s="143"/>
+      <c r="N131" s="82"/>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A132" s="14" t="s">
@@ -23633,8 +23633,8 @@
       <c r="J132" s="49"/>
       <c r="K132" s="49"/>
       <c r="L132" s="49"/>
-      <c r="M132" s="96"/>
-      <c r="N132" s="104"/>
+      <c r="M132" s="143"/>
+      <c r="N132" s="82"/>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A133" s="14" t="s">
@@ -23659,8 +23659,8 @@
       <c r="J133" s="49"/>
       <c r="K133" s="49"/>
       <c r="L133" s="49"/>
-      <c r="M133" s="96"/>
-      <c r="N133" s="104"/>
+      <c r="M133" s="143"/>
+      <c r="N133" s="82"/>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A134" s="14" t="s">
@@ -23685,8 +23685,8 @@
       <c r="J134" s="49"/>
       <c r="K134" s="49"/>
       <c r="L134" s="49"/>
-      <c r="M134" s="96"/>
-      <c r="N134" s="104"/>
+      <c r="M134" s="143"/>
+      <c r="N134" s="82"/>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A135" s="14" t="s">
@@ -23711,8 +23711,8 @@
       <c r="J135" s="49"/>
       <c r="K135" s="49"/>
       <c r="L135" s="49"/>
-      <c r="M135" s="96"/>
-      <c r="N135" s="104"/>
+      <c r="M135" s="143"/>
+      <c r="N135" s="82"/>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A136" s="14" t="s">
@@ -23737,8 +23737,8 @@
       <c r="J136" s="49"/>
       <c r="K136" s="49"/>
       <c r="L136" s="49"/>
-      <c r="M136" s="96"/>
-      <c r="N136" s="104"/>
+      <c r="M136" s="143"/>
+      <c r="N136" s="82"/>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A137" s="14" t="s">
@@ -23763,8 +23763,8 @@
       <c r="J137" s="49"/>
       <c r="K137" s="49"/>
       <c r="L137" s="49"/>
-      <c r="M137" s="96"/>
-      <c r="N137" s="104"/>
+      <c r="M137" s="143"/>
+      <c r="N137" s="82"/>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A138" s="14" t="s">
@@ -23789,8 +23789,8 @@
       <c r="J138" s="49"/>
       <c r="K138" s="49"/>
       <c r="L138" s="49"/>
-      <c r="M138" s="96"/>
-      <c r="N138" s="104"/>
+      <c r="M138" s="143"/>
+      <c r="N138" s="82"/>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A139" s="14" t="s">
@@ -23815,8 +23815,8 @@
       <c r="J139" s="49"/>
       <c r="K139" s="49"/>
       <c r="L139" s="49"/>
-      <c r="M139" s="96"/>
-      <c r="N139" s="104"/>
+      <c r="M139" s="143"/>
+      <c r="N139" s="82"/>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A140" s="14" t="s">
@@ -23841,8 +23841,8 @@
       <c r="J140" s="49"/>
       <c r="K140" s="49"/>
       <c r="L140" s="49"/>
-      <c r="M140" s="96"/>
-      <c r="N140" s="104"/>
+      <c r="M140" s="143"/>
+      <c r="N140" s="82"/>
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A141" s="14" t="s">
@@ -23867,8 +23867,8 @@
       <c r="J141" s="49"/>
       <c r="K141" s="49"/>
       <c r="L141" s="49"/>
-      <c r="M141" s="96"/>
-      <c r="N141" s="104"/>
+      <c r="M141" s="143"/>
+      <c r="N141" s="82"/>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A142" s="14" t="s">
@@ -23893,8 +23893,8 @@
       <c r="J142" s="49"/>
       <c r="K142" s="49"/>
       <c r="L142" s="49"/>
-      <c r="M142" s="96"/>
-      <c r="N142" s="104"/>
+      <c r="M142" s="143"/>
+      <c r="N142" s="82"/>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A143" s="14" t="s">
@@ -23919,8 +23919,8 @@
       <c r="J143" s="49"/>
       <c r="K143" s="49"/>
       <c r="L143" s="49"/>
-      <c r="M143" s="96"/>
-      <c r="N143" s="104"/>
+      <c r="M143" s="143"/>
+      <c r="N143" s="82"/>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A144" s="14" t="s">
@@ -23945,8 +23945,8 @@
       <c r="J144" s="49"/>
       <c r="K144" s="49"/>
       <c r="L144" s="49"/>
-      <c r="M144" s="96"/>
-      <c r="N144" s="104"/>
+      <c r="M144" s="143"/>
+      <c r="N144" s="82"/>
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A145" s="14" t="s">
@@ -23971,8 +23971,8 @@
       <c r="J145" s="49"/>
       <c r="K145" s="49"/>
       <c r="L145" s="49"/>
-      <c r="M145" s="96"/>
-      <c r="N145" s="104"/>
+      <c r="M145" s="143"/>
+      <c r="N145" s="82"/>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A146" s="14" t="s">
@@ -23997,8 +23997,8 @@
       <c r="J146" s="49"/>
       <c r="K146" s="49"/>
       <c r="L146" s="49"/>
-      <c r="M146" s="96"/>
-      <c r="N146" s="104"/>
+      <c r="M146" s="143"/>
+      <c r="N146" s="82"/>
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A147" s="14" t="s">
@@ -24023,8 +24023,8 @@
       <c r="J147" s="49"/>
       <c r="K147" s="49"/>
       <c r="L147" s="49"/>
-      <c r="M147" s="96"/>
-      <c r="N147" s="104"/>
+      <c r="M147" s="143"/>
+      <c r="N147" s="82"/>
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A148" s="14" t="s">
@@ -24049,8 +24049,8 @@
       <c r="J148" s="49"/>
       <c r="K148" s="49"/>
       <c r="L148" s="49"/>
-      <c r="M148" s="96"/>
-      <c r="N148" s="104"/>
+      <c r="M148" s="143"/>
+      <c r="N148" s="82"/>
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A149" s="14" t="s">
@@ -24075,8 +24075,8 @@
       <c r="J149" s="49"/>
       <c r="K149" s="49"/>
       <c r="L149" s="49"/>
-      <c r="M149" s="96"/>
-      <c r="N149" s="104"/>
+      <c r="M149" s="143"/>
+      <c r="N149" s="82"/>
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A150" s="14" t="s">
@@ -24101,8 +24101,8 @@
       <c r="J150" s="49"/>
       <c r="K150" s="49"/>
       <c r="L150" s="49"/>
-      <c r="M150" s="96"/>
-      <c r="N150" s="104"/>
+      <c r="M150" s="143"/>
+      <c r="N150" s="82"/>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A151" s="14" t="s">
@@ -24127,8 +24127,8 @@
       <c r="J151" s="49"/>
       <c r="K151" s="49"/>
       <c r="L151" s="49"/>
-      <c r="M151" s="96"/>
-      <c r="N151" s="104"/>
+      <c r="M151" s="143"/>
+      <c r="N151" s="82"/>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A152" s="14" t="s">
@@ -24153,8 +24153,8 @@
       <c r="J152" s="49"/>
       <c r="K152" s="49"/>
       <c r="L152" s="49"/>
-      <c r="M152" s="96"/>
-      <c r="N152" s="104"/>
+      <c r="M152" s="143"/>
+      <c r="N152" s="82"/>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A153" s="14" t="s">
@@ -24179,8 +24179,8 @@
       <c r="J153" s="49"/>
       <c r="K153" s="49"/>
       <c r="L153" s="49"/>
-      <c r="M153" s="96"/>
-      <c r="N153" s="104"/>
+      <c r="M153" s="143"/>
+      <c r="N153" s="82"/>
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A154" s="14" t="s">
@@ -24205,8 +24205,8 @@
       <c r="J154" s="49"/>
       <c r="K154" s="49"/>
       <c r="L154" s="49"/>
-      <c r="M154" s="96"/>
-      <c r="N154" s="104"/>
+      <c r="M154" s="143"/>
+      <c r="N154" s="82"/>
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A155" s="14" t="s">
@@ -24231,8 +24231,8 @@
       <c r="J155" s="49"/>
       <c r="K155" s="49"/>
       <c r="L155" s="49"/>
-      <c r="M155" s="96"/>
-      <c r="N155" s="104"/>
+      <c r="M155" s="143"/>
+      <c r="N155" s="82"/>
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A156" s="14" t="s">
@@ -24257,8 +24257,8 @@
       <c r="J156" s="49"/>
       <c r="K156" s="49"/>
       <c r="L156" s="49"/>
-      <c r="M156" s="96"/>
-      <c r="N156" s="104"/>
+      <c r="M156" s="143"/>
+      <c r="N156" s="82"/>
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A157" s="14" t="s">
@@ -24283,8 +24283,8 @@
       <c r="J157" s="49"/>
       <c r="K157" s="49"/>
       <c r="L157" s="49"/>
-      <c r="M157" s="96"/>
-      <c r="N157" s="104"/>
+      <c r="M157" s="143"/>
+      <c r="N157" s="82"/>
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A158" s="14" t="s">
@@ -24309,8 +24309,8 @@
       <c r="J158" s="49"/>
       <c r="K158" s="49"/>
       <c r="L158" s="49"/>
-      <c r="M158" s="96"/>
-      <c r="N158" s="104"/>
+      <c r="M158" s="143"/>
+      <c r="N158" s="82"/>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A159" s="14" t="s">
@@ -24335,8 +24335,8 @@
       <c r="J159" s="49"/>
       <c r="K159" s="49"/>
       <c r="L159" s="49"/>
-      <c r="M159" s="96"/>
-      <c r="N159" s="104"/>
+      <c r="M159" s="143"/>
+      <c r="N159" s="82"/>
     </row>
     <row r="160" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="18" t="s">
@@ -24361,8 +24361,8 @@
       <c r="J160" s="49"/>
       <c r="K160" s="49"/>
       <c r="L160" s="49"/>
-      <c r="M160" s="96"/>
-      <c r="N160" s="104"/>
+      <c r="M160" s="143"/>
+      <c r="N160" s="82"/>
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A161" s="14" t="s">
@@ -24387,8 +24387,8 @@
       <c r="J161" s="49"/>
       <c r="K161" s="49"/>
       <c r="L161" s="49"/>
-      <c r="M161" s="96"/>
-      <c r="N161" s="104"/>
+      <c r="M161" s="143"/>
+      <c r="N161" s="82"/>
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A162" s="14" t="s">
@@ -24413,8 +24413,8 @@
       <c r="J162" s="49"/>
       <c r="K162" s="49"/>
       <c r="L162" s="49"/>
-      <c r="M162" s="96"/>
-      <c r="N162" s="104"/>
+      <c r="M162" s="143"/>
+      <c r="N162" s="82"/>
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A163" s="14" t="s">
@@ -24439,8 +24439,8 @@
       <c r="J163" s="49"/>
       <c r="K163" s="49"/>
       <c r="L163" s="49"/>
-      <c r="M163" s="96"/>
-      <c r="N163" s="104"/>
+      <c r="M163" s="143"/>
+      <c r="N163" s="82"/>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A164" s="14" t="s">
@@ -24465,8 +24465,8 @@
       <c r="J164" s="49"/>
       <c r="K164" s="49"/>
       <c r="L164" s="49"/>
-      <c r="M164" s="96"/>
-      <c r="N164" s="104"/>
+      <c r="M164" s="143"/>
+      <c r="N164" s="82"/>
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A165" s="14" t="s">
@@ -24491,8 +24491,8 @@
       <c r="J165" s="49"/>
       <c r="K165" s="49"/>
       <c r="L165" s="49"/>
-      <c r="M165" s="96"/>
-      <c r="N165" s="104"/>
+      <c r="M165" s="143"/>
+      <c r="N165" s="82"/>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A166" s="14" t="s">
@@ -24517,8 +24517,8 @@
       <c r="J166" s="49"/>
       <c r="K166" s="49"/>
       <c r="L166" s="49"/>
-      <c r="M166" s="96"/>
-      <c r="N166" s="104"/>
+      <c r="M166" s="143"/>
+      <c r="N166" s="82"/>
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A167" s="14" t="s">
@@ -24543,8 +24543,8 @@
       <c r="J167" s="49"/>
       <c r="K167" s="49"/>
       <c r="L167" s="49"/>
-      <c r="M167" s="96"/>
-      <c r="N167" s="104"/>
+      <c r="M167" s="143"/>
+      <c r="N167" s="82"/>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A168" s="14" t="s">
@@ -24569,8 +24569,8 @@
       <c r="J168" s="49"/>
       <c r="K168" s="49"/>
       <c r="L168" s="49"/>
-      <c r="M168" s="96"/>
-      <c r="N168" s="104"/>
+      <c r="M168" s="143"/>
+      <c r="N168" s="82"/>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A169" s="14" t="s">
@@ -24595,8 +24595,8 @@
       <c r="J169" s="49"/>
       <c r="K169" s="49"/>
       <c r="L169" s="49"/>
-      <c r="M169" s="96"/>
-      <c r="N169" s="104"/>
+      <c r="M169" s="143"/>
+      <c r="N169" s="82"/>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A170" s="14" t="s">
@@ -24621,8 +24621,8 @@
       <c r="J170" s="49"/>
       <c r="K170" s="49"/>
       <c r="L170" s="49"/>
-      <c r="M170" s="96"/>
-      <c r="N170" s="104"/>
+      <c r="M170" s="143"/>
+      <c r="N170" s="82"/>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A171" s="14" t="s">
@@ -24647,8 +24647,8 @@
       <c r="J171" s="49"/>
       <c r="K171" s="49"/>
       <c r="L171" s="49"/>
-      <c r="M171" s="96"/>
-      <c r="N171" s="104"/>
+      <c r="M171" s="143"/>
+      <c r="N171" s="82"/>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A172" s="14" t="s">
@@ -24673,8 +24673,8 @@
       <c r="J172" s="49"/>
       <c r="K172" s="49"/>
       <c r="L172" s="49"/>
-      <c r="M172" s="96"/>
-      <c r="N172" s="104"/>
+      <c r="M172" s="143"/>
+      <c r="N172" s="82"/>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A173" s="14" t="s">
@@ -24699,8 +24699,8 @@
       <c r="J173" s="49"/>
       <c r="K173" s="49"/>
       <c r="L173" s="49"/>
-      <c r="M173" s="96"/>
-      <c r="N173" s="104"/>
+      <c r="M173" s="143"/>
+      <c r="N173" s="82"/>
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A174" s="14" t="s">
@@ -24725,8 +24725,8 @@
       <c r="J174" s="49"/>
       <c r="K174" s="49"/>
       <c r="L174" s="49"/>
-      <c r="M174" s="96"/>
-      <c r="N174" s="104"/>
+      <c r="M174" s="143"/>
+      <c r="N174" s="82"/>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A175" s="14" t="s">
@@ -24751,8 +24751,8 @@
       <c r="J175" s="49"/>
       <c r="K175" s="49"/>
       <c r="L175" s="49"/>
-      <c r="M175" s="96"/>
-      <c r="N175" s="104"/>
+      <c r="M175" s="143"/>
+      <c r="N175" s="82"/>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A176" s="14" t="s">
@@ -24777,8 +24777,8 @@
       <c r="J176" s="49"/>
       <c r="K176" s="49"/>
       <c r="L176" s="49"/>
-      <c r="M176" s="96"/>
-      <c r="N176" s="104"/>
+      <c r="M176" s="143"/>
+      <c r="N176" s="82"/>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A177" s="14" t="s">
@@ -24803,8 +24803,8 @@
       <c r="J177" s="49"/>
       <c r="K177" s="49"/>
       <c r="L177" s="49"/>
-      <c r="M177" s="96"/>
-      <c r="N177" s="104"/>
+      <c r="M177" s="143"/>
+      <c r="N177" s="82"/>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A178" s="14" t="s">
@@ -24829,8 +24829,8 @@
       <c r="J178" s="49"/>
       <c r="K178" s="49"/>
       <c r="L178" s="49"/>
-      <c r="M178" s="96"/>
-      <c r="N178" s="104"/>
+      <c r="M178" s="143"/>
+      <c r="N178" s="82"/>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A179" s="14" t="s">
@@ -24855,8 +24855,8 @@
       <c r="J179" s="49"/>
       <c r="K179" s="49"/>
       <c r="L179" s="49"/>
-      <c r="M179" s="96"/>
-      <c r="N179" s="104"/>
+      <c r="M179" s="143"/>
+      <c r="N179" s="82"/>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A180" s="14" t="s">
@@ -24881,8 +24881,8 @@
       <c r="J180" s="49"/>
       <c r="K180" s="49"/>
       <c r="L180" s="49"/>
-      <c r="M180" s="96"/>
-      <c r="N180" s="104"/>
+      <c r="M180" s="143"/>
+      <c r="N180" s="82"/>
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A181" s="14" t="s">
@@ -24907,8 +24907,8 @@
       <c r="J181" s="49"/>
       <c r="K181" s="49"/>
       <c r="L181" s="49"/>
-      <c r="M181" s="96"/>
-      <c r="N181" s="104"/>
+      <c r="M181" s="143"/>
+      <c r="N181" s="82"/>
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A182" s="14" t="s">
@@ -24933,8 +24933,8 @@
       <c r="J182" s="49"/>
       <c r="K182" s="49"/>
       <c r="L182" s="49"/>
-      <c r="M182" s="96"/>
-      <c r="N182" s="104"/>
+      <c r="M182" s="143"/>
+      <c r="N182" s="82"/>
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A183" s="14" t="s">
@@ -24959,8 +24959,8 @@
       <c r="J183" s="49"/>
       <c r="K183" s="49"/>
       <c r="L183" s="49"/>
-      <c r="M183" s="96"/>
-      <c r="N183" s="104"/>
+      <c r="M183" s="143"/>
+      <c r="N183" s="82"/>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A184" s="14" t="s">
@@ -24985,8 +24985,8 @@
       <c r="J184" s="49"/>
       <c r="K184" s="49"/>
       <c r="L184" s="49"/>
-      <c r="M184" s="96"/>
-      <c r="N184" s="104"/>
+      <c r="M184" s="143"/>
+      <c r="N184" s="82"/>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A185" s="14" t="s">
@@ -25011,8 +25011,8 @@
       <c r="J185" s="49"/>
       <c r="K185" s="49"/>
       <c r="L185" s="49"/>
-      <c r="M185" s="96"/>
-      <c r="N185" s="104"/>
+      <c r="M185" s="143"/>
+      <c r="N185" s="82"/>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A186" s="14" t="s">
@@ -25037,8 +25037,8 @@
       <c r="J186" s="49"/>
       <c r="K186" s="49"/>
       <c r="L186" s="49"/>
-      <c r="M186" s="96"/>
-      <c r="N186" s="104"/>
+      <c r="M186" s="143"/>
+      <c r="N186" s="82"/>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A187" s="14" t="s">
@@ -25063,8 +25063,8 @@
       <c r="J187" s="49"/>
       <c r="K187" s="49"/>
       <c r="L187" s="49"/>
-      <c r="M187" s="96"/>
-      <c r="N187" s="104"/>
+      <c r="M187" s="143"/>
+      <c r="N187" s="82"/>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A188" s="14" t="s">
@@ -25089,8 +25089,8 @@
       <c r="J188" s="49"/>
       <c r="K188" s="49"/>
       <c r="L188" s="49"/>
-      <c r="M188" s="96"/>
-      <c r="N188" s="104"/>
+      <c r="M188" s="143"/>
+      <c r="N188" s="82"/>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A189" s="14" t="s">
@@ -25115,8 +25115,8 @@
       <c r="J189" s="49"/>
       <c r="K189" s="49"/>
       <c r="L189" s="49"/>
-      <c r="M189" s="96"/>
-      <c r="N189" s="104"/>
+      <c r="M189" s="143"/>
+      <c r="N189" s="82"/>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A190" s="14" t="s">
@@ -25141,8 +25141,8 @@
       <c r="J190" s="49"/>
       <c r="K190" s="49"/>
       <c r="L190" s="49"/>
-      <c r="M190" s="96"/>
-      <c r="N190" s="104"/>
+      <c r="M190" s="143"/>
+      <c r="N190" s="82"/>
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A191" s="14" t="s">
@@ -25167,8 +25167,8 @@
       <c r="J191" s="49"/>
       <c r="K191" s="49"/>
       <c r="L191" s="49"/>
-      <c r="M191" s="96"/>
-      <c r="N191" s="104"/>
+      <c r="M191" s="143"/>
+      <c r="N191" s="82"/>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A192" s="14" t="s">
@@ -25193,8 +25193,8 @@
       <c r="J192" s="49"/>
       <c r="K192" s="49"/>
       <c r="L192" s="49"/>
-      <c r="M192" s="96"/>
-      <c r="N192" s="104"/>
+      <c r="M192" s="143"/>
+      <c r="N192" s="82"/>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A193" s="14" t="s">
@@ -25219,8 +25219,8 @@
       <c r="J193" s="49"/>
       <c r="K193" s="49"/>
       <c r="L193" s="49"/>
-      <c r="M193" s="96"/>
-      <c r="N193" s="104"/>
+      <c r="M193" s="143"/>
+      <c r="N193" s="82"/>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A194" s="14" t="s">
@@ -25245,8 +25245,8 @@
       <c r="J194" s="49"/>
       <c r="K194" s="49"/>
       <c r="L194" s="49"/>
-      <c r="M194" s="96"/>
-      <c r="N194" s="104"/>
+      <c r="M194" s="143"/>
+      <c r="N194" s="82"/>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A195" s="14" t="s">
@@ -25271,8 +25271,8 @@
       <c r="J195" s="49"/>
       <c r="K195" s="49"/>
       <c r="L195" s="49"/>
-      <c r="M195" s="96"/>
-      <c r="N195" s="104"/>
+      <c r="M195" s="143"/>
+      <c r="N195" s="82"/>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A196" s="14" t="s">
@@ -25297,8 +25297,8 @@
       <c r="J196" s="49"/>
       <c r="K196" s="49"/>
       <c r="L196" s="49"/>
-      <c r="M196" s="96"/>
-      <c r="N196" s="104"/>
+      <c r="M196" s="143"/>
+      <c r="N196" s="82"/>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A197" s="14" t="s">
@@ -25323,8 +25323,8 @@
       <c r="J197" s="49"/>
       <c r="K197" s="49"/>
       <c r="L197" s="49"/>
-      <c r="M197" s="96"/>
-      <c r="N197" s="104"/>
+      <c r="M197" s="143"/>
+      <c r="N197" s="82"/>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A198" s="14" t="s">
@@ -25349,8 +25349,8 @@
       <c r="J198" s="49"/>
       <c r="K198" s="49"/>
       <c r="L198" s="49"/>
-      <c r="M198" s="96"/>
-      <c r="N198" s="104"/>
+      <c r="M198" s="143"/>
+      <c r="N198" s="82"/>
     </row>
     <row r="199" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A199" s="18" t="s">
@@ -25375,8 +25375,8 @@
       <c r="J199" s="49"/>
       <c r="K199" s="49"/>
       <c r="L199" s="49"/>
-      <c r="M199" s="96"/>
-      <c r="N199" s="104"/>
+      <c r="M199" s="143"/>
+      <c r="N199" s="82"/>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A200" s="14" t="s">
@@ -25401,8 +25401,8 @@
       <c r="J200" s="49"/>
       <c r="K200" s="49"/>
       <c r="L200" s="49"/>
-      <c r="M200" s="96"/>
-      <c r="N200" s="104"/>
+      <c r="M200" s="143"/>
+      <c r="N200" s="82"/>
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A201" s="14" t="s">
@@ -25427,8 +25427,8 @@
       <c r="J201" s="49"/>
       <c r="K201" s="49"/>
       <c r="L201" s="49"/>
-      <c r="M201" s="96"/>
-      <c r="N201" s="104"/>
+      <c r="M201" s="143"/>
+      <c r="N201" s="82"/>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A202" s="14" t="s">
@@ -25453,8 +25453,8 @@
       <c r="J202" s="49"/>
       <c r="K202" s="49"/>
       <c r="L202" s="49"/>
-      <c r="M202" s="96"/>
-      <c r="N202" s="104"/>
+      <c r="M202" s="143"/>
+      <c r="N202" s="82"/>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A203" s="14" t="s">
@@ -25479,8 +25479,8 @@
       <c r="J203" s="49"/>
       <c r="K203" s="49"/>
       <c r="L203" s="49"/>
-      <c r="M203" s="96"/>
-      <c r="N203" s="104"/>
+      <c r="M203" s="143"/>
+      <c r="N203" s="82"/>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A204" s="14" t="s">
@@ -25505,8 +25505,8 @@
       <c r="J204" s="49"/>
       <c r="K204" s="49"/>
       <c r="L204" s="49"/>
-      <c r="M204" s="96"/>
-      <c r="N204" s="104"/>
+      <c r="M204" s="143"/>
+      <c r="N204" s="82"/>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A205" s="14" t="s">
@@ -25531,8 +25531,8 @@
       <c r="J205" s="49"/>
       <c r="K205" s="49"/>
       <c r="L205" s="49"/>
-      <c r="M205" s="96"/>
-      <c r="N205" s="104"/>
+      <c r="M205" s="143"/>
+      <c r="N205" s="82"/>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A206" s="14" t="s">
@@ -25557,8 +25557,8 @@
       <c r="J206" s="49"/>
       <c r="K206" s="49"/>
       <c r="L206" s="49"/>
-      <c r="M206" s="96"/>
-      <c r="N206" s="104"/>
+      <c r="M206" s="143"/>
+      <c r="N206" s="82"/>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A207" s="14" t="s">
@@ -25583,8 +25583,8 @@
       <c r="J207" s="49"/>
       <c r="K207" s="49"/>
       <c r="L207" s="49"/>
-      <c r="M207" s="96"/>
-      <c r="N207" s="104"/>
+      <c r="M207" s="143"/>
+      <c r="N207" s="82"/>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A208" s="14" t="s">
@@ -25609,8 +25609,8 @@
       <c r="J208" s="49"/>
       <c r="K208" s="49"/>
       <c r="L208" s="49"/>
-      <c r="M208" s="96"/>
-      <c r="N208" s="104"/>
+      <c r="M208" s="143"/>
+      <c r="N208" s="82"/>
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A209" s="14" t="s">
@@ -25635,8 +25635,8 @@
       <c r="J209" s="49"/>
       <c r="K209" s="49"/>
       <c r="L209" s="49"/>
-      <c r="M209" s="96"/>
-      <c r="N209" s="104"/>
+      <c r="M209" s="143"/>
+      <c r="N209" s="82"/>
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A210" s="14" t="s">
@@ -25661,8 +25661,8 @@
       <c r="J210" s="49"/>
       <c r="K210" s="49"/>
       <c r="L210" s="49"/>
-      <c r="M210" s="96"/>
-      <c r="N210" s="104"/>
+      <c r="M210" s="143"/>
+      <c r="N210" s="82"/>
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A211" s="14" t="s">
@@ -25687,8 +25687,8 @@
       <c r="J211" s="49"/>
       <c r="K211" s="49"/>
       <c r="L211" s="49"/>
-      <c r="M211" s="96"/>
-      <c r="N211" s="104"/>
+      <c r="M211" s="143"/>
+      <c r="N211" s="82"/>
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A212" s="14" t="s">
@@ -25713,8 +25713,8 @@
       <c r="J212" s="49"/>
       <c r="K212" s="49"/>
       <c r="L212" s="49"/>
-      <c r="M212" s="96"/>
-      <c r="N212" s="104"/>
+      <c r="M212" s="143"/>
+      <c r="N212" s="82"/>
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A213" s="14" t="s">
@@ -25739,8 +25739,8 @@
       <c r="J213" s="49"/>
       <c r="K213" s="49"/>
       <c r="L213" s="49"/>
-      <c r="M213" s="96"/>
-      <c r="N213" s="104"/>
+      <c r="M213" s="143"/>
+      <c r="N213" s="82"/>
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A214" s="14" t="s">
@@ -25765,8 +25765,8 @@
       <c r="J214" s="49"/>
       <c r="K214" s="49"/>
       <c r="L214" s="49"/>
-      <c r="M214" s="96"/>
-      <c r="N214" s="104"/>
+      <c r="M214" s="143"/>
+      <c r="N214" s="82"/>
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A215" s="14" t="s">
@@ -25791,8 +25791,8 @@
       <c r="J215" s="49"/>
       <c r="K215" s="49"/>
       <c r="L215" s="49"/>
-      <c r="M215" s="96"/>
-      <c r="N215" s="104"/>
+      <c r="M215" s="143"/>
+      <c r="N215" s="82"/>
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A216" s="14" t="s">
@@ -25817,8 +25817,8 @@
       <c r="J216" s="49"/>
       <c r="K216" s="49"/>
       <c r="L216" s="49"/>
-      <c r="M216" s="96"/>
-      <c r="N216" s="104"/>
+      <c r="M216" s="143"/>
+      <c r="N216" s="82"/>
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A217" s="14" t="s">
@@ -25843,8 +25843,8 @@
       <c r="J217" s="49"/>
       <c r="K217" s="49"/>
       <c r="L217" s="49"/>
-      <c r="M217" s="96"/>
-      <c r="N217" s="104"/>
+      <c r="M217" s="143"/>
+      <c r="N217" s="82"/>
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A218" s="14" t="s">
@@ -25869,8 +25869,8 @@
       <c r="J218" s="49"/>
       <c r="K218" s="49"/>
       <c r="L218" s="49"/>
-      <c r="M218" s="96"/>
-      <c r="N218" s="104"/>
+      <c r="M218" s="143"/>
+      <c r="N218" s="82"/>
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A219" s="14" t="s">
@@ -25895,8 +25895,8 @@
       <c r="J219" s="49"/>
       <c r="K219" s="49"/>
       <c r="L219" s="49"/>
-      <c r="M219" s="96"/>
-      <c r="N219" s="104"/>
+      <c r="M219" s="143"/>
+      <c r="N219" s="82"/>
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A220" s="14" t="s">
@@ -25921,8 +25921,8 @@
       <c r="J220" s="49"/>
       <c r="K220" s="49"/>
       <c r="L220" s="49"/>
-      <c r="M220" s="96"/>
-      <c r="N220" s="104"/>
+      <c r="M220" s="143"/>
+      <c r="N220" s="82"/>
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A221" s="14" t="s">
@@ -25947,8 +25947,8 @@
       <c r="J221" s="49"/>
       <c r="K221" s="49"/>
       <c r="L221" s="49"/>
-      <c r="M221" s="96"/>
-      <c r="N221" s="104"/>
+      <c r="M221" s="143"/>
+      <c r="N221" s="82"/>
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A222" s="14" t="s">
@@ -25973,8 +25973,8 @@
       <c r="J222" s="49"/>
       <c r="K222" s="49"/>
       <c r="L222" s="49"/>
-      <c r="M222" s="96"/>
-      <c r="N222" s="104"/>
+      <c r="M222" s="143"/>
+      <c r="N222" s="82"/>
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A223" s="14" t="s">
@@ -25999,8 +25999,8 @@
       <c r="J223" s="49"/>
       <c r="K223" s="49"/>
       <c r="L223" s="49"/>
-      <c r="M223" s="96"/>
-      <c r="N223" s="104"/>
+      <c r="M223" s="143"/>
+      <c r="N223" s="82"/>
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A224" s="14" t="s">
@@ -26025,8 +26025,8 @@
       <c r="J224" s="49"/>
       <c r="K224" s="49"/>
       <c r="L224" s="49"/>
-      <c r="M224" s="96"/>
-      <c r="N224" s="104"/>
+      <c r="M224" s="143"/>
+      <c r="N224" s="82"/>
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A225" s="14" t="s">
@@ -26051,8 +26051,8 @@
       <c r="J225" s="49"/>
       <c r="K225" s="49"/>
       <c r="L225" s="49"/>
-      <c r="M225" s="96"/>
-      <c r="N225" s="104"/>
+      <c r="M225" s="143"/>
+      <c r="N225" s="82"/>
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A226" s="14" t="s">
@@ -26077,8 +26077,8 @@
       <c r="J226" s="49"/>
       <c r="K226" s="49"/>
       <c r="L226" s="49"/>
-      <c r="M226" s="96"/>
-      <c r="N226" s="104"/>
+      <c r="M226" s="143"/>
+      <c r="N226" s="82"/>
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A227" s="14" t="s">
@@ -26103,8 +26103,8 @@
       <c r="J227" s="49"/>
       <c r="K227" s="49"/>
       <c r="L227" s="49"/>
-      <c r="M227" s="96"/>
-      <c r="N227" s="104"/>
+      <c r="M227" s="143"/>
+      <c r="N227" s="82"/>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A228" s="14" t="s">
@@ -26129,8 +26129,8 @@
       <c r="J228" s="49"/>
       <c r="K228" s="49"/>
       <c r="L228" s="49"/>
-      <c r="M228" s="96"/>
-      <c r="N228" s="104"/>
+      <c r="M228" s="143"/>
+      <c r="N228" s="82"/>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A229" s="14" t="s">
@@ -26155,8 +26155,8 @@
       <c r="J229" s="49"/>
       <c r="K229" s="49"/>
       <c r="L229" s="49"/>
-      <c r="M229" s="96"/>
-      <c r="N229" s="104"/>
+      <c r="M229" s="143"/>
+      <c r="N229" s="82"/>
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A230" s="14" t="s">
@@ -26181,8 +26181,8 @@
       <c r="J230" s="49"/>
       <c r="K230" s="49"/>
       <c r="L230" s="49"/>
-      <c r="M230" s="96"/>
-      <c r="N230" s="104"/>
+      <c r="M230" s="143"/>
+      <c r="N230" s="82"/>
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A231" s="14" t="s">
@@ -26207,8 +26207,8 @@
       <c r="J231" s="49"/>
       <c r="K231" s="49"/>
       <c r="L231" s="49"/>
-      <c r="M231" s="96"/>
-      <c r="N231" s="104"/>
+      <c r="M231" s="143"/>
+      <c r="N231" s="82"/>
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A232" s="14" t="s">
@@ -26233,8 +26233,8 @@
       <c r="J232" s="49"/>
       <c r="K232" s="49"/>
       <c r="L232" s="49"/>
-      <c r="M232" s="96"/>
-      <c r="N232" s="104"/>
+      <c r="M232" s="143"/>
+      <c r="N232" s="82"/>
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A233" s="14" t="s">
@@ -26259,8 +26259,8 @@
       <c r="J233" s="49"/>
       <c r="K233" s="49"/>
       <c r="L233" s="49"/>
-      <c r="M233" s="96"/>
-      <c r="N233" s="104"/>
+      <c r="M233" s="143"/>
+      <c r="N233" s="82"/>
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A234" s="14" t="s">
@@ -26285,8 +26285,8 @@
       <c r="J234" s="49"/>
       <c r="K234" s="49"/>
       <c r="L234" s="49"/>
-      <c r="M234" s="96"/>
-      <c r="N234" s="104"/>
+      <c r="M234" s="143"/>
+      <c r="N234" s="82"/>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A235" s="14" t="s">
@@ -26311,8 +26311,8 @@
       <c r="J235" s="49"/>
       <c r="K235" s="49"/>
       <c r="L235" s="49"/>
-      <c r="M235" s="96"/>
-      <c r="N235" s="104"/>
+      <c r="M235" s="143"/>
+      <c r="N235" s="82"/>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A236" s="14" t="s">
@@ -26337,8 +26337,8 @@
       <c r="J236" s="49"/>
       <c r="K236" s="49"/>
       <c r="L236" s="49"/>
-      <c r="M236" s="96"/>
-      <c r="N236" s="104"/>
+      <c r="M236" s="143"/>
+      <c r="N236" s="82"/>
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A237" s="14" t="s">
@@ -26363,8 +26363,8 @@
       <c r="J237" s="49"/>
       <c r="K237" s="49"/>
       <c r="L237" s="49"/>
-      <c r="M237" s="96"/>
-      <c r="N237" s="104"/>
+      <c r="M237" s="143"/>
+      <c r="N237" s="82"/>
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A238" s="14" t="s">
@@ -26389,8 +26389,8 @@
       <c r="J238" s="49"/>
       <c r="K238" s="49"/>
       <c r="L238" s="49"/>
-      <c r="M238" s="96"/>
-      <c r="N238" s="104"/>
+      <c r="M238" s="143"/>
+      <c r="N238" s="82"/>
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A239" s="14" t="s">
@@ -26415,8 +26415,8 @@
       <c r="J239" s="49"/>
       <c r="K239" s="49"/>
       <c r="L239" s="49"/>
-      <c r="M239" s="96"/>
-      <c r="N239" s="104"/>
+      <c r="M239" s="143"/>
+      <c r="N239" s="82"/>
     </row>
     <row r="240" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A240" s="14" t="s">
@@ -26441,8 +26441,8 @@
       <c r="J240" s="49"/>
       <c r="K240" s="49"/>
       <c r="L240" s="49"/>
-      <c r="M240" s="97"/>
-      <c r="N240" s="104"/>
+      <c r="M240" s="144"/>
+      <c r="N240" s="82"/>
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A241" s="46" t="s">
@@ -26471,10 +26471,10 @@
       <c r="L241" s="48" t="s">
         <v>1347</v>
       </c>
-      <c r="M241" s="98" t="s">
+      <c r="M241" s="145" t="s">
         <v>1411</v>
       </c>
-      <c r="N241" s="102"/>
+      <c r="N241" s="80"/>
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A242" s="14" t="s">
@@ -26503,8 +26503,8 @@
       <c r="L242" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M242" s="99"/>
-      <c r="N242" s="102"/>
+      <c r="M242" s="146"/>
+      <c r="N242" s="80"/>
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A243" s="14" t="s">
@@ -26533,8 +26533,8 @@
       <c r="L243" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M243" s="99"/>
-      <c r="N243" s="102"/>
+      <c r="M243" s="146"/>
+      <c r="N243" s="80"/>
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A244" s="14" t="s">
@@ -26563,8 +26563,8 @@
       <c r="L244" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M244" s="99"/>
-      <c r="N244" s="102"/>
+      <c r="M244" s="146"/>
+      <c r="N244" s="80"/>
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A245" s="14" t="s">
@@ -26593,8 +26593,8 @@
       <c r="L245" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M245" s="99"/>
-      <c r="N245" s="102"/>
+      <c r="M245" s="146"/>
+      <c r="N245" s="80"/>
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A246" s="14" t="s">
@@ -26623,8 +26623,8 @@
       <c r="L246" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M246" s="99"/>
-      <c r="N246" s="102"/>
+      <c r="M246" s="146"/>
+      <c r="N246" s="80"/>
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A247" s="14" t="s">
@@ -26653,8 +26653,8 @@
       <c r="L247" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M247" s="99"/>
-      <c r="N247" s="102"/>
+      <c r="M247" s="146"/>
+      <c r="N247" s="80"/>
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A248" s="14" t="s">
@@ -26683,8 +26683,8 @@
       <c r="L248" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M248" s="99"/>
-      <c r="N248" s="102"/>
+      <c r="M248" s="146"/>
+      <c r="N248" s="80"/>
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A249" s="14" t="s">
@@ -26713,8 +26713,8 @@
       <c r="L249" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M249" s="99"/>
-      <c r="N249" s="102"/>
+      <c r="M249" s="146"/>
+      <c r="N249" s="80"/>
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A250" s="14" t="s">
@@ -26743,8 +26743,8 @@
       <c r="L250" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M250" s="99"/>
-      <c r="N250" s="102"/>
+      <c r="M250" s="146"/>
+      <c r="N250" s="80"/>
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A251" s="14" t="s">
@@ -26773,8 +26773,8 @@
       <c r="L251" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M251" s="99"/>
-      <c r="N251" s="102"/>
+      <c r="M251" s="146"/>
+      <c r="N251" s="80"/>
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A252" s="14" t="s">
@@ -26803,8 +26803,8 @@
       <c r="L252" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M252" s="99"/>
-      <c r="N252" s="102"/>
+      <c r="M252" s="146"/>
+      <c r="N252" s="80"/>
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A253" s="14" t="s">
@@ -26833,8 +26833,8 @@
       <c r="L253" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M253" s="99"/>
-      <c r="N253" s="102"/>
+      <c r="M253" s="146"/>
+      <c r="N253" s="80"/>
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A254" s="14" t="s">
@@ -26863,8 +26863,8 @@
       <c r="L254" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M254" s="99"/>
-      <c r="N254" s="102"/>
+      <c r="M254" s="146"/>
+      <c r="N254" s="80"/>
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A255" s="14" t="s">
@@ -26893,8 +26893,8 @@
       <c r="L255" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M255" s="99"/>
-      <c r="N255" s="102"/>
+      <c r="M255" s="146"/>
+      <c r="N255" s="80"/>
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A256" s="14" t="s">
@@ -26923,8 +26923,8 @@
       <c r="L256" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M256" s="99"/>
-      <c r="N256" s="102"/>
+      <c r="M256" s="146"/>
+      <c r="N256" s="80"/>
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A257" s="14" t="s">
@@ -26953,8 +26953,8 @@
       <c r="L257" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M257" s="99"/>
-      <c r="N257" s="102"/>
+      <c r="M257" s="146"/>
+      <c r="N257" s="80"/>
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A258" s="14" t="s">
@@ -26983,8 +26983,8 @@
       <c r="L258" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M258" s="99"/>
-      <c r="N258" s="102"/>
+      <c r="M258" s="146"/>
+      <c r="N258" s="80"/>
     </row>
     <row r="259" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A259" s="14" t="s">
@@ -27013,8 +27013,8 @@
       <c r="L259" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M259" s="99"/>
-      <c r="N259" s="102"/>
+      <c r="M259" s="146"/>
+      <c r="N259" s="80"/>
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A260" s="14" t="s">
@@ -27043,8 +27043,8 @@
       <c r="L260" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M260" s="99"/>
-      <c r="N260" s="102"/>
+      <c r="M260" s="146"/>
+      <c r="N260" s="80"/>
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A261" s="14" t="s">
@@ -27073,8 +27073,8 @@
       <c r="L261" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M261" s="99"/>
-      <c r="N261" s="102"/>
+      <c r="M261" s="146"/>
+      <c r="N261" s="80"/>
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A262" s="14" t="s">
@@ -27103,8 +27103,8 @@
       <c r="L262" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M262" s="99"/>
-      <c r="N262" s="102"/>
+      <c r="M262" s="146"/>
+      <c r="N262" s="80"/>
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A263" s="14" t="s">
@@ -27133,8 +27133,8 @@
       <c r="L263" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M263" s="99"/>
-      <c r="N263" s="102"/>
+      <c r="M263" s="146"/>
+      <c r="N263" s="80"/>
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A264" s="14" t="s">
@@ -27163,8 +27163,8 @@
       <c r="L264" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M264" s="99"/>
-      <c r="N264" s="102"/>
+      <c r="M264" s="146"/>
+      <c r="N264" s="80"/>
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A265" s="14" t="s">
@@ -27193,8 +27193,8 @@
       <c r="L265" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M265" s="99"/>
-      <c r="N265" s="102"/>
+      <c r="M265" s="146"/>
+      <c r="N265" s="80"/>
     </row>
     <row r="266" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A266" s="18" t="s">
@@ -27223,8 +27223,8 @@
       <c r="L266" s="24" t="s">
         <v>1347</v>
       </c>
-      <c r="M266" s="100"/>
-      <c r="N266" s="102"/>
+      <c r="M266" s="147"/>
+      <c r="N266" s="80"/>
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A267" s="10" t="s">
@@ -27253,10 +27253,10 @@
       <c r="L267" s="48" t="s">
         <v>1367</v>
       </c>
-      <c r="M267" s="83" t="s">
+      <c r="M267" s="148" t="s">
         <v>1413</v>
       </c>
-      <c r="N267" s="102"/>
+      <c r="N267" s="80"/>
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A268" s="14"/>
@@ -27281,8 +27281,8 @@
       <c r="L268" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M268" s="84"/>
-      <c r="N268" s="102"/>
+      <c r="M268" s="149"/>
+      <c r="N268" s="80"/>
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A269" s="14" t="s">
@@ -27311,8 +27311,8 @@
       <c r="L269" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M269" s="84"/>
-      <c r="N269" s="102"/>
+      <c r="M269" s="149"/>
+      <c r="N269" s="80"/>
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A270" s="14" t="s">
@@ -27341,8 +27341,8 @@
       <c r="L270" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M270" s="84"/>
-      <c r="N270" s="102"/>
+      <c r="M270" s="149"/>
+      <c r="N270" s="80"/>
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A271" s="14" t="s">
@@ -27371,8 +27371,8 @@
       <c r="L271" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M271" s="84"/>
-      <c r="N271" s="102"/>
+      <c r="M271" s="149"/>
+      <c r="N271" s="80"/>
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A272" s="14" t="s">
@@ -27401,8 +27401,8 @@
       <c r="L272" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M272" s="84"/>
-      <c r="N272" s="102"/>
+      <c r="M272" s="149"/>
+      <c r="N272" s="80"/>
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A273" s="14" t="s">
@@ -27431,8 +27431,8 @@
       <c r="L273" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M273" s="84"/>
-      <c r="N273" s="102"/>
+      <c r="M273" s="149"/>
+      <c r="N273" s="80"/>
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A274" s="14" t="s">
@@ -27461,8 +27461,8 @@
       <c r="L274" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M274" s="84"/>
-      <c r="N274" s="102"/>
+      <c r="M274" s="149"/>
+      <c r="N274" s="80"/>
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A275" s="14" t="s">
@@ -27491,8 +27491,8 @@
       <c r="L275" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M275" s="84"/>
-      <c r="N275" s="102"/>
+      <c r="M275" s="149"/>
+      <c r="N275" s="80"/>
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A276" s="14" t="s">
@@ -27521,8 +27521,8 @@
       <c r="L276" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M276" s="84"/>
-      <c r="N276" s="102"/>
+      <c r="M276" s="149"/>
+      <c r="N276" s="80"/>
     </row>
     <row r="277" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A277" s="14" t="s">
@@ -27551,8 +27551,8 @@
       <c r="L277" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M277" s="84"/>
-      <c r="N277" s="102"/>
+      <c r="M277" s="149"/>
+      <c r="N277" s="80"/>
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A278" s="14" t="s">
@@ -27581,8 +27581,8 @@
       <c r="L278" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M278" s="84"/>
-      <c r="N278" s="102"/>
+      <c r="M278" s="149"/>
+      <c r="N278" s="80"/>
     </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A279" s="14" t="s">
@@ -27611,8 +27611,8 @@
       <c r="L279" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M279" s="84"/>
-      <c r="N279" s="102"/>
+      <c r="M279" s="149"/>
+      <c r="N279" s="80"/>
     </row>
     <row r="280" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A280" s="14" t="s">
@@ -27641,8 +27641,8 @@
       <c r="L280" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M280" s="84"/>
-      <c r="N280" s="102"/>
+      <c r="M280" s="149"/>
+      <c r="N280" s="80"/>
     </row>
     <row r="281" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A281" s="14" t="s">
@@ -27671,8 +27671,8 @@
       <c r="L281" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M281" s="84"/>
-      <c r="N281" s="102"/>
+      <c r="M281" s="149"/>
+      <c r="N281" s="80"/>
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A282" s="14" t="s">
@@ -27701,8 +27701,8 @@
       <c r="L282" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M282" s="84"/>
-      <c r="N282" s="102"/>
+      <c r="M282" s="149"/>
+      <c r="N282" s="80"/>
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A283" s="14" t="s">
@@ -27731,8 +27731,8 @@
       <c r="L283" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M283" s="84"/>
-      <c r="N283" s="102"/>
+      <c r="M283" s="149"/>
+      <c r="N283" s="80"/>
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A284" s="14" t="s">
@@ -27761,8 +27761,8 @@
       <c r="L284" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M284" s="84"/>
-      <c r="N284" s="102"/>
+      <c r="M284" s="149"/>
+      <c r="N284" s="80"/>
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A285" s="14" t="s">
@@ -27791,8 +27791,8 @@
       <c r="L285" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M285" s="84"/>
-      <c r="N285" s="102"/>
+      <c r="M285" s="149"/>
+      <c r="N285" s="80"/>
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A286" s="14" t="s">
@@ -27821,8 +27821,8 @@
       <c r="L286" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M286" s="84"/>
-      <c r="N286" s="102"/>
+      <c r="M286" s="149"/>
+      <c r="N286" s="80"/>
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A287" s="14" t="s">
@@ -27851,8 +27851,8 @@
       <c r="L287" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M287" s="84"/>
-      <c r="N287" s="102"/>
+      <c r="M287" s="149"/>
+      <c r="N287" s="80"/>
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A288" s="14" t="s">
@@ -27881,8 +27881,8 @@
       <c r="L288" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M288" s="84"/>
-      <c r="N288" s="102"/>
+      <c r="M288" s="149"/>
+      <c r="N288" s="80"/>
     </row>
     <row r="289" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A289" s="14" t="s">
@@ -27911,8 +27911,8 @@
       <c r="L289" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M289" s="84"/>
-      <c r="N289" s="102"/>
+      <c r="M289" s="149"/>
+      <c r="N289" s="80"/>
     </row>
     <row r="290" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A290" s="14" t="s">
@@ -27941,8 +27941,8 @@
       <c r="L290" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M290" s="84"/>
-      <c r="N290" s="102"/>
+      <c r="M290" s="149"/>
+      <c r="N290" s="80"/>
     </row>
     <row r="291" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A291" s="14" t="s">
@@ -27971,8 +27971,8 @@
       <c r="L291" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M291" s="84"/>
-      <c r="N291" s="102"/>
+      <c r="M291" s="149"/>
+      <c r="N291" s="80"/>
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A292" s="14" t="s">
@@ -28001,8 +28001,8 @@
       <c r="L292" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M292" s="84"/>
-      <c r="N292" s="102"/>
+      <c r="M292" s="149"/>
+      <c r="N292" s="80"/>
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A293" s="14" t="s">
@@ -28031,8 +28031,8 @@
       <c r="L293" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M293" s="84"/>
-      <c r="N293" s="102"/>
+      <c r="M293" s="149"/>
+      <c r="N293" s="80"/>
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A294" s="14" t="s">
@@ -28061,8 +28061,8 @@
       <c r="L294" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M294" s="84"/>
-      <c r="N294" s="102"/>
+      <c r="M294" s="149"/>
+      <c r="N294" s="80"/>
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A295" s="14" t="s">
@@ -28091,8 +28091,8 @@
       <c r="L295" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M295" s="84"/>
-      <c r="N295" s="102"/>
+      <c r="M295" s="149"/>
+      <c r="N295" s="80"/>
     </row>
     <row r="296" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A296" s="14" t="s">
@@ -28121,8 +28121,8 @@
       <c r="L296" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M296" s="84"/>
-      <c r="N296" s="102"/>
+      <c r="M296" s="149"/>
+      <c r="N296" s="80"/>
     </row>
     <row r="297" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A297" s="14" t="s">
@@ -28151,8 +28151,8 @@
       <c r="L297" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M297" s="84"/>
-      <c r="N297" s="102"/>
+      <c r="M297" s="149"/>
+      <c r="N297" s="80"/>
     </row>
     <row r="298" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A298" s="14" t="s">
@@ -28181,8 +28181,8 @@
       <c r="L298" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M298" s="84"/>
-      <c r="N298" s="102"/>
+      <c r="M298" s="149"/>
+      <c r="N298" s="80"/>
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A299" s="14" t="s">
@@ -28211,8 +28211,8 @@
       <c r="L299" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M299" s="84"/>
-      <c r="N299" s="102"/>
+      <c r="M299" s="149"/>
+      <c r="N299" s="80"/>
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A300" s="14" t="s">
@@ -28241,8 +28241,8 @@
       <c r="L300" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M300" s="84"/>
-      <c r="N300" s="102"/>
+      <c r="M300" s="149"/>
+      <c r="N300" s="80"/>
     </row>
     <row r="301" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A301" s="18" t="s">
@@ -28271,8 +28271,8 @@
       <c r="L301" s="53" t="s">
         <v>1367</v>
       </c>
-      <c r="M301" s="85"/>
-      <c r="N301" s="102"/>
+      <c r="M301" s="150"/>
+      <c r="N301" s="80"/>
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A302" s="10" t="s">
@@ -28301,10 +28301,10 @@
       <c r="L302" s="48" t="s">
         <v>1381</v>
       </c>
-      <c r="M302" s="83" t="s">
+      <c r="M302" s="148" t="s">
         <v>1383</v>
       </c>
-      <c r="N302" s="102"/>
+      <c r="N302" s="80"/>
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A303" s="14" t="s">
@@ -28333,8 +28333,8 @@
       <c r="L303" s="43" t="s">
         <v>1381</v>
       </c>
-      <c r="M303" s="84"/>
-      <c r="N303" s="102"/>
+      <c r="M303" s="149"/>
+      <c r="N303" s="80"/>
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A304" s="14" t="s">
@@ -28363,8 +28363,8 @@
       <c r="L304" s="43" t="s">
         <v>1381</v>
       </c>
-      <c r="M304" s="84"/>
-      <c r="N304" s="102"/>
+      <c r="M304" s="149"/>
+      <c r="N304" s="80"/>
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A305" s="14" t="s">
@@ -28393,8 +28393,8 @@
       <c r="L305" s="43" t="s">
         <v>1381</v>
       </c>
-      <c r="M305" s="84"/>
-      <c r="N305" s="102"/>
+      <c r="M305" s="149"/>
+      <c r="N305" s="80"/>
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A306" s="14" t="s">
@@ -28423,8 +28423,8 @@
       <c r="L306" s="43" t="s">
         <v>1381</v>
       </c>
-      <c r="M306" s="84"/>
-      <c r="N306" s="102"/>
+      <c r="M306" s="149"/>
+      <c r="N306" s="80"/>
     </row>
     <row r="307" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A307" s="14" t="s">
@@ -28453,8 +28453,8 @@
       <c r="L307" s="43" t="s">
         <v>1381</v>
       </c>
-      <c r="M307" s="84"/>
-      <c r="N307" s="102"/>
+      <c r="M307" s="149"/>
+      <c r="N307" s="80"/>
     </row>
     <row r="308" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A308" s="18" t="s">
@@ -28483,8 +28483,8 @@
       <c r="L308" s="53" t="s">
         <v>1381</v>
       </c>
-      <c r="M308" s="85"/>
-      <c r="N308" s="102"/>
+      <c r="M308" s="150"/>
+      <c r="N308" s="80"/>
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A309" s="10" t="s">
@@ -28513,10 +28513,10 @@
       <c r="L309" s="48" t="s">
         <v>1384</v>
       </c>
-      <c r="M309" s="83" t="s">
+      <c r="M309" s="148" t="s">
         <v>1391</v>
       </c>
-      <c r="N309" s="102"/>
+      <c r="N309" s="80"/>
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A310" s="14" t="s">
@@ -28545,8 +28545,8 @@
       <c r="L310" s="43" t="s">
         <v>1384</v>
       </c>
-      <c r="M310" s="84"/>
-      <c r="N310" s="102"/>
+      <c r="M310" s="149"/>
+      <c r="N310" s="80"/>
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A311" s="14" t="s">
@@ -28575,8 +28575,8 @@
       <c r="L311" s="43" t="s">
         <v>1384</v>
       </c>
-      <c r="M311" s="84"/>
-      <c r="N311" s="102"/>
+      <c r="M311" s="149"/>
+      <c r="N311" s="80"/>
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A312" s="14" t="s">
@@ -28605,8 +28605,8 @@
       <c r="L312" s="43" t="s">
         <v>1384</v>
       </c>
-      <c r="M312" s="84"/>
-      <c r="N312" s="102"/>
+      <c r="M312" s="149"/>
+      <c r="N312" s="80"/>
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A313" s="14" t="s">
@@ -28635,8 +28635,8 @@
       <c r="L313" s="43" t="s">
         <v>1384</v>
       </c>
-      <c r="M313" s="84"/>
-      <c r="N313" s="102"/>
+      <c r="M313" s="149"/>
+      <c r="N313" s="80"/>
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A314" s="14" t="s">
@@ -28665,8 +28665,8 @@
       <c r="L314" s="43" t="s">
         <v>1384</v>
       </c>
-      <c r="M314" s="84"/>
-      <c r="N314" s="102"/>
+      <c r="M314" s="149"/>
+      <c r="N314" s="80"/>
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A315" s="14" t="s">
@@ -28695,8 +28695,8 @@
       <c r="L315" s="43" t="s">
         <v>1384</v>
       </c>
-      <c r="M315" s="84"/>
-      <c r="N315" s="102"/>
+      <c r="M315" s="149"/>
+      <c r="N315" s="80"/>
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A316" s="14" t="s">
@@ -28725,8 +28725,8 @@
       <c r="L316" s="43" t="s">
         <v>1384</v>
       </c>
-      <c r="M316" s="84"/>
-      <c r="N316" s="102"/>
+      <c r="M316" s="149"/>
+      <c r="N316" s="80"/>
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A317" s="14" t="s">
@@ -28755,8 +28755,8 @@
       <c r="L317" s="43" t="s">
         <v>1384</v>
       </c>
-      <c r="M317" s="84"/>
-      <c r="N317" s="102"/>
+      <c r="M317" s="149"/>
+      <c r="N317" s="80"/>
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A318" s="14" t="s">
@@ -28785,8 +28785,8 @@
       <c r="L318" s="43" t="s">
         <v>1384</v>
       </c>
-      <c r="M318" s="84"/>
-      <c r="N318" s="102"/>
+      <c r="M318" s="149"/>
+      <c r="N318" s="80"/>
     </row>
     <row r="319" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A319" s="18" t="s">
@@ -28815,22 +28815,22 @@
       <c r="L319" s="53" t="s">
         <v>1384</v>
       </c>
-      <c r="M319" s="85"/>
-      <c r="N319" s="102"/>
+      <c r="M319" s="150"/>
+      <c r="N319" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="M29:M240"/>
+    <mergeCell ref="M241:M266"/>
+    <mergeCell ref="M267:M301"/>
+    <mergeCell ref="M302:M308"/>
+    <mergeCell ref="M309:M319"/>
     <mergeCell ref="Y1:AC1"/>
     <mergeCell ref="Z2:AC2"/>
     <mergeCell ref="M10:M15"/>
     <mergeCell ref="M22:M27"/>
     <mergeCell ref="S1:W1"/>
     <mergeCell ref="M16:M21"/>
-    <mergeCell ref="M29:M240"/>
-    <mergeCell ref="M241:M266"/>
-    <mergeCell ref="M267:M301"/>
-    <mergeCell ref="M302:M308"/>
-    <mergeCell ref="M309:M319"/>
     <mergeCell ref="M2:M9"/>
     <mergeCell ref="T2:W2"/>
   </mergeCells>

--- a/Resultats_modeles_coleo_2024.xlsx
+++ b/Resultats_modeles_coleo_2024.xlsx
@@ -7135,9 +7135,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7146,6 +7143,36 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7197,33 +7224,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7657,7 +7657,7 @@
       <c r="G2" t="s">
         <v>154</v>
       </c>
-      <c r="H2" s="123" t="s">
+      <c r="H2" s="122" t="s">
         <v>89</v>
       </c>
       <c r="I2" t="s">
@@ -7714,7 +7714,7 @@
       <c r="Z2" t="s">
         <v>173</v>
       </c>
-      <c r="AA2" s="122" t="s">
+      <c r="AA2" s="121" t="s">
         <v>45</v>
       </c>
     </row>
@@ -7740,7 +7740,7 @@
       <c r="G3" t="s">
         <v>154</v>
       </c>
-      <c r="H3" s="123"/>
+      <c r="H3" s="122"/>
       <c r="I3" t="s">
         <v>150</v>
       </c>
@@ -7795,7 +7795,7 @@
       <c r="Z3" t="s">
         <v>173</v>
       </c>
-      <c r="AA3" s="122"/>
+      <c r="AA3" s="121"/>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -7819,7 +7819,7 @@
       <c r="G4" t="s">
         <v>154</v>
       </c>
-      <c r="H4" s="123"/>
+      <c r="H4" s="122"/>
       <c r="I4" t="s">
         <v>150</v>
       </c>
@@ -7874,7 +7874,7 @@
       <c r="Z4" t="s">
         <v>173</v>
       </c>
-      <c r="AA4" s="122"/>
+      <c r="AA4" s="121"/>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -7898,7 +7898,7 @@
       <c r="G5" t="s">
         <v>154</v>
       </c>
-      <c r="H5" s="123"/>
+      <c r="H5" s="122"/>
       <c r="I5" t="s">
         <v>150</v>
       </c>
@@ -7953,7 +7953,7 @@
       <c r="Z5" t="s">
         <v>173</v>
       </c>
-      <c r="AA5" s="122"/>
+      <c r="AA5" s="121"/>
     </row>
     <row r="6" spans="1:29" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -7977,7 +7977,7 @@
       <c r="G6" t="s">
         <v>184</v>
       </c>
-      <c r="H6" s="123" t="s">
+      <c r="H6" s="122" t="s">
         <v>89</v>
       </c>
       <c r="I6" t="s">
@@ -8034,10 +8034,10 @@
       <c r="Z6" t="s">
         <v>182</v>
       </c>
-      <c r="AA6" s="122" t="s">
+      <c r="AA6" s="121" t="s">
         <v>46</v>
       </c>
-      <c r="AB6" s="122" t="s">
+      <c r="AB6" s="121" t="s">
         <v>174</v>
       </c>
     </row>
@@ -8063,7 +8063,7 @@
       <c r="G7" t="s">
         <v>184</v>
       </c>
-      <c r="H7" s="123"/>
+      <c r="H7" s="122"/>
       <c r="I7" t="s">
         <v>189</v>
       </c>
@@ -8118,8 +8118,8 @@
       <c r="Z7" t="s">
         <v>182</v>
       </c>
-      <c r="AA7" s="122"/>
-      <c r="AB7" s="122"/>
+      <c r="AA7" s="121"/>
+      <c r="AB7" s="121"/>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -8143,7 +8143,7 @@
       <c r="G8" t="s">
         <v>184</v>
       </c>
-      <c r="H8" s="123"/>
+      <c r="H8" s="122"/>
       <c r="I8" t="s">
         <v>189</v>
       </c>
@@ -8198,8 +8198,8 @@
       <c r="Z8" t="s">
         <v>182</v>
       </c>
-      <c r="AA8" s="122"/>
-      <c r="AB8" s="122"/>
+      <c r="AA8" s="121"/>
+      <c r="AB8" s="121"/>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -8223,7 +8223,7 @@
       <c r="G9" t="s">
         <v>184</v>
       </c>
-      <c r="H9" s="123"/>
+      <c r="H9" s="122"/>
       <c r="I9" t="s">
         <v>189</v>
       </c>
@@ -8278,8 +8278,8 @@
       <c r="Z9" t="s">
         <v>182</v>
       </c>
-      <c r="AA9" s="122"/>
-      <c r="AB9" s="122"/>
+      <c r="AA9" s="121"/>
+      <c r="AB9" s="121"/>
     </row>
     <row r="10" spans="1:29" ht="120" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -8303,7 +8303,7 @@
       <c r="G10" t="s">
         <v>194</v>
       </c>
-      <c r="H10" s="123" t="s">
+      <c r="H10" s="122" t="s">
         <v>89</v>
       </c>
       <c r="I10" t="s">
@@ -8360,10 +8360,10 @@
       <c r="Z10" t="s">
         <v>208</v>
       </c>
-      <c r="AA10" s="122" t="s">
+      <c r="AA10" s="121" t="s">
         <v>47</v>
       </c>
-      <c r="AB10" s="122" t="s">
+      <c r="AB10" s="121" t="s">
         <v>209</v>
       </c>
     </row>
@@ -8389,7 +8389,7 @@
       <c r="G11" t="s">
         <v>194</v>
       </c>
-      <c r="H11" s="123"/>
+      <c r="H11" s="122"/>
       <c r="I11" t="s">
         <v>199</v>
       </c>
@@ -8444,8 +8444,8 @@
       <c r="Z11" t="s">
         <v>208</v>
       </c>
-      <c r="AA11" s="122"/>
-      <c r="AB11" s="122"/>
+      <c r="AA11" s="121"/>
+      <c r="AB11" s="121"/>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -8469,7 +8469,7 @@
       <c r="G12" t="s">
         <v>194</v>
       </c>
-      <c r="H12" s="123"/>
+      <c r="H12" s="122"/>
       <c r="I12" t="s">
         <v>199</v>
       </c>
@@ -8524,8 +8524,8 @@
       <c r="Z12" t="s">
         <v>208</v>
       </c>
-      <c r="AA12" s="122"/>
-      <c r="AB12" s="122"/>
+      <c r="AA12" s="121"/>
+      <c r="AB12" s="121"/>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -8549,7 +8549,7 @@
       <c r="G13" t="s">
         <v>194</v>
       </c>
-      <c r="H13" s="123"/>
+      <c r="H13" s="122"/>
       <c r="I13" t="s">
         <v>199</v>
       </c>
@@ -8604,8 +8604,8 @@
       <c r="Z13" t="s">
         <v>208</v>
       </c>
-      <c r="AA13" s="122"/>
-      <c r="AB13" s="122"/>
+      <c r="AA13" s="121"/>
+      <c r="AB13" s="121"/>
     </row>
     <row r="14" spans="1:29" ht="131.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -8629,7 +8629,7 @@
       <c r="G14" t="s">
         <v>211</v>
       </c>
-      <c r="H14" s="123" t="s">
+      <c r="H14" s="122" t="s">
         <v>41</v>
       </c>
       <c r="I14" t="s">
@@ -8641,7 +8641,7 @@
       <c r="K14" t="s">
         <v>20</v>
       </c>
-      <c r="L14" s="122" t="s">
+      <c r="L14" s="121" t="s">
         <v>44</v>
       </c>
       <c r="M14" t="s">
@@ -8686,7 +8686,7 @@
       <c r="Z14" t="s">
         <v>223</v>
       </c>
-      <c r="AA14" s="122" t="s">
+      <c r="AA14" s="121" t="s">
         <v>48</v>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       <c r="G15" t="s">
         <v>211</v>
       </c>
-      <c r="H15" s="123"/>
+      <c r="H15" s="122"/>
       <c r="I15" t="s">
         <v>213</v>
       </c>
@@ -8722,7 +8722,7 @@
       <c r="K15" t="s">
         <v>20</v>
       </c>
-      <c r="L15" s="122"/>
+      <c r="L15" s="121"/>
       <c r="M15" t="s">
         <v>15</v>
       </c>
@@ -8765,7 +8765,7 @@
       <c r="Z15" t="s">
         <v>223</v>
       </c>
-      <c r="AA15" s="122"/>
+      <c r="AA15" s="121"/>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -8789,7 +8789,7 @@
       <c r="G16" t="s">
         <v>211</v>
       </c>
-      <c r="H16" s="123"/>
+      <c r="H16" s="122"/>
       <c r="I16" t="s">
         <v>213</v>
       </c>
@@ -8799,7 +8799,7 @@
       <c r="K16" t="s">
         <v>20</v>
       </c>
-      <c r="L16" s="122"/>
+      <c r="L16" s="121"/>
       <c r="M16" t="s">
         <v>15</v>
       </c>
@@ -8842,7 +8842,7 @@
       <c r="Z16" t="s">
         <v>223</v>
       </c>
-      <c r="AA16" s="122"/>
+      <c r="AA16" s="121"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
@@ -8866,7 +8866,7 @@
       <c r="G17" t="s">
         <v>211</v>
       </c>
-      <c r="H17" s="123"/>
+      <c r="H17" s="122"/>
       <c r="I17" t="s">
         <v>213</v>
       </c>
@@ -8876,7 +8876,7 @@
       <c r="K17" t="s">
         <v>20</v>
       </c>
-      <c r="L17" s="122"/>
+      <c r="L17" s="121"/>
       <c r="M17" t="s">
         <v>15</v>
       </c>
@@ -8919,7 +8919,7 @@
       <c r="Z17" t="s">
         <v>223</v>
       </c>
-      <c r="AA17" s="122"/>
+      <c r="AA17" s="121"/>
     </row>
     <row r="18" spans="1:28" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -8943,7 +8943,7 @@
       <c r="G18" t="s">
         <v>225</v>
       </c>
-      <c r="H18" s="123" t="s">
+      <c r="H18" s="122" t="s">
         <v>41</v>
       </c>
       <c r="I18" t="s">
@@ -9000,10 +9000,10 @@
       <c r="Z18" t="s">
         <v>240</v>
       </c>
-      <c r="AA18" s="122" t="s">
+      <c r="AA18" s="121" t="s">
         <v>233</v>
       </c>
-      <c r="AB18" s="122" t="s">
+      <c r="AB18" s="121" t="s">
         <v>241</v>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       <c r="G19" t="s">
         <v>225</v>
       </c>
-      <c r="H19" s="123"/>
+      <c r="H19" s="122"/>
       <c r="I19" t="s">
         <v>230</v>
       </c>
@@ -9084,8 +9084,8 @@
       <c r="Z19" t="s">
         <v>240</v>
       </c>
-      <c r="AA19" s="122"/>
-      <c r="AB19" s="122"/>
+      <c r="AA19" s="121"/>
+      <c r="AB19" s="121"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
@@ -9109,7 +9109,7 @@
       <c r="G20" t="s">
         <v>225</v>
       </c>
-      <c r="H20" s="123"/>
+      <c r="H20" s="122"/>
       <c r="I20" t="s">
         <v>230</v>
       </c>
@@ -9164,8 +9164,8 @@
       <c r="Z20" t="s">
         <v>240</v>
       </c>
-      <c r="AA20" s="122"/>
-      <c r="AB20" s="122"/>
+      <c r="AA20" s="121"/>
+      <c r="AB20" s="121"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
@@ -9189,7 +9189,7 @@
       <c r="G21" t="s">
         <v>225</v>
       </c>
-      <c r="H21" s="123"/>
+      <c r="H21" s="122"/>
       <c r="I21" t="s">
         <v>230</v>
       </c>
@@ -9244,8 +9244,8 @@
       <c r="Z21" t="s">
         <v>240</v>
       </c>
-      <c r="AA21" s="122"/>
-      <c r="AB21" s="122"/>
+      <c r="AA21" s="121"/>
+      <c r="AB21" s="121"/>
     </row>
     <row r="22" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
@@ -9269,7 +9269,7 @@
       <c r="G22" t="s">
         <v>243</v>
       </c>
-      <c r="H22" s="123" t="s">
+      <c r="H22" s="122" t="s">
         <v>41</v>
       </c>
       <c r="I22" t="s">
@@ -9314,7 +9314,7 @@
       <c r="Z22" t="s">
         <v>258</v>
       </c>
-      <c r="AA22" s="122" t="s">
+      <c r="AA22" s="121" t="s">
         <v>52</v>
       </c>
     </row>
@@ -9340,7 +9340,7 @@
       <c r="G23" t="s">
         <v>243</v>
       </c>
-      <c r="H23" s="123"/>
+      <c r="H23" s="122"/>
       <c r="I23" t="s">
         <v>249</v>
       </c>
@@ -9383,7 +9383,7 @@
       <c r="Z23" t="s">
         <v>258</v>
       </c>
-      <c r="AA23" s="122"/>
+      <c r="AA23" s="121"/>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
@@ -9407,7 +9407,7 @@
       <c r="G24" t="s">
         <v>243</v>
       </c>
-      <c r="H24" s="123"/>
+      <c r="H24" s="122"/>
       <c r="I24" t="s">
         <v>249</v>
       </c>
@@ -9450,7 +9450,7 @@
       <c r="Z24" t="s">
         <v>258</v>
       </c>
-      <c r="AA24" s="122"/>
+      <c r="AA24" s="121"/>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
@@ -9474,7 +9474,7 @@
       <c r="G25" t="s">
         <v>243</v>
       </c>
-      <c r="H25" s="123"/>
+      <c r="H25" s="122"/>
       <c r="I25" t="s">
         <v>249</v>
       </c>
@@ -9517,7 +9517,7 @@
       <c r="Z25" t="s">
         <v>258</v>
       </c>
-      <c r="AA25" s="122"/>
+      <c r="AA25" s="121"/>
     </row>
     <row r="26" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
@@ -9541,7 +9541,7 @@
       <c r="G26" t="s">
         <v>261</v>
       </c>
-      <c r="H26" s="123" t="s">
+      <c r="H26" s="122" t="s">
         <v>41</v>
       </c>
       <c r="I26" t="s">
@@ -9598,10 +9598,10 @@
       <c r="Z26" t="s">
         <v>278</v>
       </c>
-      <c r="AA26" s="122" t="s">
+      <c r="AA26" s="121" t="s">
         <v>54</v>
       </c>
-      <c r="AB26" s="122" t="s">
+      <c r="AB26" s="121" t="s">
         <v>279</v>
       </c>
     </row>
@@ -9627,7 +9627,7 @@
       <c r="G27" t="s">
         <v>261</v>
       </c>
-      <c r="H27" s="123"/>
+      <c r="H27" s="122"/>
       <c r="I27" t="s">
         <v>266</v>
       </c>
@@ -9682,8 +9682,8 @@
       <c r="Z27" t="s">
         <v>278</v>
       </c>
-      <c r="AA27" s="122"/>
-      <c r="AB27" s="122"/>
+      <c r="AA27" s="121"/>
+      <c r="AB27" s="121"/>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -9707,7 +9707,7 @@
       <c r="G28" t="s">
         <v>261</v>
       </c>
-      <c r="H28" s="123"/>
+      <c r="H28" s="122"/>
       <c r="I28" t="s">
         <v>266</v>
       </c>
@@ -9762,8 +9762,8 @@
       <c r="Z28" t="s">
         <v>278</v>
       </c>
-      <c r="AA28" s="122"/>
-      <c r="AB28" s="122"/>
+      <c r="AA28" s="121"/>
+      <c r="AB28" s="121"/>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -9787,7 +9787,7 @@
       <c r="G29" t="s">
         <v>261</v>
       </c>
-      <c r="H29" s="123"/>
+      <c r="H29" s="122"/>
       <c r="I29" t="s">
         <v>266</v>
       </c>
@@ -9842,8 +9842,8 @@
       <c r="Z29" t="s">
         <v>278</v>
       </c>
-      <c r="AA29" s="122"/>
-      <c r="AB29" s="122"/>
+      <c r="AA29" s="121"/>
+      <c r="AB29" s="121"/>
     </row>
     <row r="30" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
@@ -9867,7 +9867,7 @@
       <c r="G30" t="s">
         <v>282</v>
       </c>
-      <c r="H30" s="123" t="s">
+      <c r="H30" s="122" t="s">
         <v>41</v>
       </c>
       <c r="I30" t="s">
@@ -9924,10 +9924,10 @@
       <c r="Z30" t="s">
         <v>298</v>
       </c>
-      <c r="AA30" s="122" t="s">
+      <c r="AA30" s="121" t="s">
         <v>56</v>
       </c>
-      <c r="AB30" s="122" t="s">
+      <c r="AB30" s="121" t="s">
         <v>299</v>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       <c r="G31" t="s">
         <v>282</v>
       </c>
-      <c r="H31" s="123"/>
+      <c r="H31" s="122"/>
       <c r="I31" t="s">
         <v>287</v>
       </c>
@@ -10008,8 +10008,8 @@
       <c r="Z31" t="s">
         <v>298</v>
       </c>
-      <c r="AA31" s="122"/>
-      <c r="AB31" s="122"/>
+      <c r="AA31" s="121"/>
+      <c r="AB31" s="121"/>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
@@ -10033,7 +10033,7 @@
       <c r="G32" t="s">
         <v>282</v>
       </c>
-      <c r="H32" s="123"/>
+      <c r="H32" s="122"/>
       <c r="I32" t="s">
         <v>287</v>
       </c>
@@ -10088,8 +10088,8 @@
       <c r="Z32" t="s">
         <v>298</v>
       </c>
-      <c r="AA32" s="122"/>
-      <c r="AB32" s="122"/>
+      <c r="AA32" s="121"/>
+      <c r="AB32" s="121"/>
     </row>
     <row r="33" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
@@ -10113,7 +10113,7 @@
       <c r="G33" t="s">
         <v>282</v>
       </c>
-      <c r="H33" s="123"/>
+      <c r="H33" s="122"/>
       <c r="I33" t="s">
         <v>287</v>
       </c>
@@ -10168,8 +10168,8 @@
       <c r="Z33" t="s">
         <v>298</v>
       </c>
-      <c r="AA33" s="122"/>
-      <c r="AB33" s="122"/>
+      <c r="AA33" s="121"/>
+      <c r="AB33" s="121"/>
     </row>
     <row r="34" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
@@ -10193,7 +10193,7 @@
       <c r="G34" t="s">
         <v>302</v>
       </c>
-      <c r="H34" s="123" t="s">
+      <c r="H34" s="122" t="s">
         <v>41</v>
       </c>
       <c r="I34" t="s">
@@ -10238,7 +10238,7 @@
       <c r="Z34" t="s">
         <v>315</v>
       </c>
-      <c r="AA34" s="122" t="s">
+      <c r="AA34" s="121" t="s">
         <v>835</v>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
       <c r="G35" t="s">
         <v>302</v>
       </c>
-      <c r="H35" s="123"/>
+      <c r="H35" s="122"/>
       <c r="I35" t="s">
         <v>306</v>
       </c>
@@ -10307,7 +10307,7 @@
       <c r="Z35" t="s">
         <v>315</v>
       </c>
-      <c r="AA35" s="122"/>
+      <c r="AA35" s="121"/>
     </row>
     <row r="36" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
@@ -10331,7 +10331,7 @@
       <c r="G36" t="s">
         <v>302</v>
       </c>
-      <c r="H36" s="123"/>
+      <c r="H36" s="122"/>
       <c r="I36" t="s">
         <v>306</v>
       </c>
@@ -10374,7 +10374,7 @@
       <c r="Z36" t="s">
         <v>315</v>
       </c>
-      <c r="AA36" s="122"/>
+      <c r="AA36" s="121"/>
     </row>
     <row r="37" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
@@ -10398,7 +10398,7 @@
       <c r="G37" t="s">
         <v>302</v>
       </c>
-      <c r="H37" s="123"/>
+      <c r="H37" s="122"/>
       <c r="I37" t="s">
         <v>306</v>
       </c>
@@ -10441,7 +10441,7 @@
       <c r="Z37" t="s">
         <v>315</v>
       </c>
-      <c r="AA37" s="122"/>
+      <c r="AA37" s="121"/>
     </row>
     <row r="38" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
@@ -10465,7 +10465,7 @@
       <c r="G38" t="s">
         <v>318</v>
       </c>
-      <c r="H38" s="123" t="s">
+      <c r="H38" s="122" t="s">
         <v>41</v>
       </c>
       <c r="I38" t="s">
@@ -10510,7 +10510,7 @@
       <c r="Z38" t="s">
         <v>330</v>
       </c>
-      <c r="AA38" s="122" t="s">
+      <c r="AA38" s="121" t="s">
         <v>834</v>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       <c r="G39" t="s">
         <v>318</v>
       </c>
-      <c r="H39" s="123"/>
+      <c r="H39" s="122"/>
       <c r="I39" t="s">
         <v>322</v>
       </c>
@@ -10579,7 +10579,7 @@
       <c r="Z39" t="s">
         <v>330</v>
       </c>
-      <c r="AA39" s="122"/>
+      <c r="AA39" s="121"/>
     </row>
     <row r="40" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
@@ -10603,7 +10603,7 @@
       <c r="G40" t="s">
         <v>318</v>
       </c>
-      <c r="H40" s="123"/>
+      <c r="H40" s="122"/>
       <c r="I40" t="s">
         <v>322</v>
       </c>
@@ -10646,7 +10646,7 @@
       <c r="Z40" t="s">
         <v>330</v>
       </c>
-      <c r="AA40" s="122"/>
+      <c r="AA40" s="121"/>
     </row>
     <row r="41" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
@@ -10670,7 +10670,7 @@
       <c r="G41" t="s">
         <v>318</v>
       </c>
-      <c r="H41" s="123"/>
+      <c r="H41" s="122"/>
       <c r="I41" t="s">
         <v>322</v>
       </c>
@@ -10713,7 +10713,7 @@
       <c r="Z41" t="s">
         <v>330</v>
       </c>
-      <c r="AA41" s="122"/>
+      <c r="AA41" s="121"/>
     </row>
     <row r="42" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
@@ -10737,7 +10737,7 @@
       <c r="G42" t="s">
         <v>332</v>
       </c>
-      <c r="H42" s="123" t="s">
+      <c r="H42" s="122" t="s">
         <v>41</v>
       </c>
       <c r="I42" t="s">
@@ -10782,7 +10782,7 @@
       <c r="Z42" t="s">
         <v>346</v>
       </c>
-      <c r="AA42" s="122" t="s">
+      <c r="AA42" s="121" t="s">
         <v>338</v>
       </c>
     </row>
@@ -10808,7 +10808,7 @@
       <c r="G43" t="s">
         <v>332</v>
       </c>
-      <c r="H43" s="123"/>
+      <c r="H43" s="122"/>
       <c r="I43" t="s">
         <v>336</v>
       </c>
@@ -10851,7 +10851,7 @@
       <c r="Z43" t="s">
         <v>346</v>
       </c>
-      <c r="AA43" s="122"/>
+      <c r="AA43" s="121"/>
     </row>
     <row r="44" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
@@ -10875,7 +10875,7 @@
       <c r="G44" t="s">
         <v>332</v>
       </c>
-      <c r="H44" s="123"/>
+      <c r="H44" s="122"/>
       <c r="I44" t="s">
         <v>336</v>
       </c>
@@ -10918,7 +10918,7 @@
       <c r="Z44" t="s">
         <v>346</v>
       </c>
-      <c r="AA44" s="122"/>
+      <c r="AA44" s="121"/>
     </row>
     <row r="45" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
@@ -10942,7 +10942,7 @@
       <c r="G45" t="s">
         <v>332</v>
       </c>
-      <c r="H45" s="123"/>
+      <c r="H45" s="122"/>
       <c r="I45" t="s">
         <v>336</v>
       </c>
@@ -10985,7 +10985,7 @@
       <c r="Z45" t="s">
         <v>346</v>
       </c>
-      <c r="AA45" s="122"/>
+      <c r="AA45" s="121"/>
     </row>
     <row r="46" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
@@ -11009,7 +11009,7 @@
       <c r="G46" t="s">
         <v>348</v>
       </c>
-      <c r="H46" s="123" t="s">
+      <c r="H46" s="122" t="s">
         <v>41</v>
       </c>
       <c r="I46" t="s">
@@ -11054,7 +11054,7 @@
       <c r="Z46" t="s">
         <v>362</v>
       </c>
-      <c r="AA46" s="122" t="s">
+      <c r="AA46" s="121" t="s">
         <v>355</v>
       </c>
     </row>
@@ -11080,7 +11080,7 @@
       <c r="G47" t="s">
         <v>348</v>
       </c>
-      <c r="H47" s="123"/>
+      <c r="H47" s="122"/>
       <c r="I47" t="s">
         <v>353</v>
       </c>
@@ -11123,7 +11123,7 @@
       <c r="Z47" t="s">
         <v>362</v>
       </c>
-      <c r="AA47" s="122"/>
+      <c r="AA47" s="121"/>
     </row>
     <row r="48" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
@@ -11147,7 +11147,7 @@
       <c r="G48" t="s">
         <v>348</v>
       </c>
-      <c r="H48" s="123"/>
+      <c r="H48" s="122"/>
       <c r="I48" t="s">
         <v>353</v>
       </c>
@@ -11190,7 +11190,7 @@
       <c r="Z48" t="s">
         <v>362</v>
       </c>
-      <c r="AA48" s="122"/>
+      <c r="AA48" s="121"/>
     </row>
     <row r="49" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
@@ -11214,7 +11214,7 @@
       <c r="G49" t="s">
         <v>348</v>
       </c>
-      <c r="H49" s="123"/>
+      <c r="H49" s="122"/>
       <c r="I49" t="s">
         <v>353</v>
       </c>
@@ -11257,7 +11257,7 @@
       <c r="Z49" t="s">
         <v>362</v>
       </c>
-      <c r="AA49" s="122"/>
+      <c r="AA49" s="121"/>
     </row>
     <row r="50" spans="1:28" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
@@ -11281,7 +11281,7 @@
       <c r="G50" t="s">
         <v>364</v>
       </c>
-      <c r="H50" s="123" t="s">
+      <c r="H50" s="122" t="s">
         <v>369</v>
       </c>
       <c r="I50" t="s">
@@ -11338,7 +11338,7 @@
       <c r="Z50" t="s">
         <v>382</v>
       </c>
-      <c r="AA50" s="122" t="s">
+      <c r="AA50" s="121" t="s">
         <v>375</v>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       <c r="G51" t="s">
         <v>364</v>
       </c>
-      <c r="H51" s="123"/>
+      <c r="H51" s="122"/>
       <c r="I51" t="s">
         <v>371</v>
       </c>
@@ -11419,7 +11419,7 @@
       <c r="Z51" t="s">
         <v>382</v>
       </c>
-      <c r="AA51" s="122"/>
+      <c r="AA51" s="121"/>
     </row>
     <row r="52" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
@@ -11443,7 +11443,7 @@
       <c r="G52" t="s">
         <v>364</v>
       </c>
-      <c r="H52" s="123"/>
+      <c r="H52" s="122"/>
       <c r="I52" t="s">
         <v>371</v>
       </c>
@@ -11498,7 +11498,7 @@
       <c r="Z52" t="s">
         <v>382</v>
       </c>
-      <c r="AA52" s="122"/>
+      <c r="AA52" s="121"/>
     </row>
     <row r="53" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
@@ -11522,7 +11522,7 @@
       <c r="G53" t="s">
         <v>364</v>
       </c>
-      <c r="H53" s="123"/>
+      <c r="H53" s="122"/>
       <c r="I53" t="s">
         <v>371</v>
       </c>
@@ -11577,7 +11577,7 @@
       <c r="Z53" t="s">
         <v>382</v>
       </c>
-      <c r="AA53" s="122"/>
+      <c r="AA53" s="121"/>
     </row>
     <row r="54" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
@@ -11601,7 +11601,7 @@
       <c r="G54" t="s">
         <v>385</v>
       </c>
-      <c r="H54" s="123" t="s">
+      <c r="H54" s="122" t="s">
         <v>68</v>
       </c>
       <c r="I54" t="s">
@@ -11646,10 +11646,10 @@
       <c r="Z54" t="s">
         <v>398</v>
       </c>
-      <c r="AA54" s="122" t="s">
+      <c r="AA54" s="121" t="s">
         <v>69</v>
       </c>
-      <c r="AB54" s="122" t="s">
+      <c r="AB54" s="121" t="s">
         <v>399</v>
       </c>
     </row>
@@ -11675,7 +11675,7 @@
       <c r="G55" t="s">
         <v>385</v>
       </c>
-      <c r="H55" s="123"/>
+      <c r="H55" s="122"/>
       <c r="I55" t="s">
         <v>392</v>
       </c>
@@ -11718,8 +11718,8 @@
       <c r="Z55" t="s">
         <v>398</v>
       </c>
-      <c r="AA55" s="122"/>
-      <c r="AB55" s="122"/>
+      <c r="AA55" s="121"/>
+      <c r="AB55" s="121"/>
     </row>
     <row r="56" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
@@ -11743,7 +11743,7 @@
       <c r="G56" t="s">
         <v>385</v>
       </c>
-      <c r="H56" s="123"/>
+      <c r="H56" s="122"/>
       <c r="I56" t="s">
         <v>392</v>
       </c>
@@ -11786,8 +11786,8 @@
       <c r="Z56" t="s">
         <v>398</v>
       </c>
-      <c r="AA56" s="122"/>
-      <c r="AB56" s="122"/>
+      <c r="AA56" s="121"/>
+      <c r="AB56" s="121"/>
     </row>
     <row r="57" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
@@ -11811,7 +11811,7 @@
       <c r="G57" t="s">
         <v>385</v>
       </c>
-      <c r="H57" s="123"/>
+      <c r="H57" s="122"/>
       <c r="I57" t="s">
         <v>392</v>
       </c>
@@ -11854,8 +11854,8 @@
       <c r="Z57" t="s">
         <v>398</v>
       </c>
-      <c r="AA57" s="122"/>
-      <c r="AB57" s="122"/>
+      <c r="AA57" s="121"/>
+      <c r="AB57" s="121"/>
     </row>
     <row r="58" spans="1:28" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
@@ -11879,7 +11879,7 @@
       <c r="G58" t="s">
         <v>402</v>
       </c>
-      <c r="H58" s="123" t="s">
+      <c r="H58" s="122" t="s">
         <v>41</v>
       </c>
       <c r="I58" t="s">
@@ -11936,7 +11936,7 @@
       <c r="Z58" t="s">
         <v>417</v>
       </c>
-      <c r="AA58" s="122" t="s">
+      <c r="AA58" s="121" t="s">
         <v>72</v>
       </c>
     </row>
@@ -11962,7 +11962,7 @@
       <c r="G59" t="s">
         <v>402</v>
       </c>
-      <c r="H59" s="123"/>
+      <c r="H59" s="122"/>
       <c r="I59" t="s">
         <v>407</v>
       </c>
@@ -12017,7 +12017,7 @@
       <c r="Z59" t="s">
         <v>417</v>
       </c>
-      <c r="AA59" s="122"/>
+      <c r="AA59" s="121"/>
     </row>
     <row r="60" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
@@ -12041,7 +12041,7 @@
       <c r="G60" t="s">
         <v>402</v>
       </c>
-      <c r="H60" s="123"/>
+      <c r="H60" s="122"/>
       <c r="I60" t="s">
         <v>407</v>
       </c>
@@ -12096,7 +12096,7 @@
       <c r="Z60" t="s">
         <v>417</v>
       </c>
-      <c r="AA60" s="122"/>
+      <c r="AA60" s="121"/>
     </row>
     <row r="61" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
@@ -12120,7 +12120,7 @@
       <c r="G61" t="s">
         <v>402</v>
       </c>
-      <c r="H61" s="123"/>
+      <c r="H61" s="122"/>
       <c r="I61" t="s">
         <v>407</v>
       </c>
@@ -12175,7 +12175,7 @@
       <c r="Z61" t="s">
         <v>417</v>
       </c>
-      <c r="AA61" s="122"/>
+      <c r="AA61" s="121"/>
     </row>
     <row r="62" spans="1:28" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
@@ -12199,7 +12199,7 @@
       <c r="G62" t="s">
         <v>75</v>
       </c>
-      <c r="H62" s="123" t="s">
+      <c r="H62" s="122" t="s">
         <v>41</v>
       </c>
       <c r="I62" t="s">
@@ -12256,10 +12256,10 @@
       <c r="Z62" t="s">
         <v>426</v>
       </c>
-      <c r="AA62" s="122" t="s">
+      <c r="AA62" s="121" t="s">
         <v>83</v>
       </c>
-      <c r="AB62" s="122" t="s">
+      <c r="AB62" s="121" t="s">
         <v>418</v>
       </c>
     </row>
@@ -12285,7 +12285,7 @@
       <c r="G63" t="s">
         <v>75</v>
       </c>
-      <c r="H63" s="123"/>
+      <c r="H63" s="122"/>
       <c r="I63" t="s">
         <v>80</v>
       </c>
@@ -12340,8 +12340,8 @@
       <c r="Z63" t="s">
         <v>426</v>
       </c>
-      <c r="AA63" s="122"/>
-      <c r="AB63" s="122"/>
+      <c r="AA63" s="121"/>
+      <c r="AB63" s="121"/>
     </row>
     <row r="64" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
@@ -12365,7 +12365,7 @@
       <c r="G64" t="s">
         <v>75</v>
       </c>
-      <c r="H64" s="123"/>
+      <c r="H64" s="122"/>
       <c r="I64" t="s">
         <v>80</v>
       </c>
@@ -12420,8 +12420,8 @@
       <c r="Z64" t="s">
         <v>426</v>
       </c>
-      <c r="AA64" s="122"/>
-      <c r="AB64" s="122"/>
+      <c r="AA64" s="121"/>
+      <c r="AB64" s="121"/>
     </row>
     <row r="65" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
@@ -12445,7 +12445,7 @@
       <c r="G65" t="s">
         <v>75</v>
       </c>
-      <c r="H65" s="123"/>
+      <c r="H65" s="122"/>
       <c r="I65" t="s">
         <v>80</v>
       </c>
@@ -12500,8 +12500,8 @@
       <c r="Z65" t="s">
         <v>426</v>
       </c>
-      <c r="AA65" s="122"/>
-      <c r="AB65" s="122"/>
+      <c r="AA65" s="121"/>
+      <c r="AB65" s="121"/>
     </row>
     <row r="66" spans="1:28" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
@@ -12525,7 +12525,7 @@
       <c r="G66" t="s">
         <v>428</v>
       </c>
-      <c r="H66" s="123" t="s">
+      <c r="H66" s="122" t="s">
         <v>41</v>
       </c>
       <c r="I66" t="s">
@@ -12582,7 +12582,7 @@
       <c r="Z66" t="s">
         <v>442</v>
       </c>
-      <c r="AA66" s="122" t="s">
+      <c r="AA66" s="121" t="s">
         <v>434</v>
       </c>
     </row>
@@ -12608,7 +12608,7 @@
       <c r="G67" t="s">
         <v>428</v>
       </c>
-      <c r="H67" s="123"/>
+      <c r="H67" s="122"/>
       <c r="I67" t="s">
         <v>432</v>
       </c>
@@ -12663,7 +12663,7 @@
       <c r="Z67" t="s">
         <v>442</v>
       </c>
-      <c r="AA67" s="122"/>
+      <c r="AA67" s="121"/>
     </row>
     <row r="68" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
@@ -12687,7 +12687,7 @@
       <c r="G68" t="s">
         <v>428</v>
       </c>
-      <c r="H68" s="123"/>
+      <c r="H68" s="122"/>
       <c r="I68" t="s">
         <v>432</v>
       </c>
@@ -12742,7 +12742,7 @@
       <c r="Z68" t="s">
         <v>442</v>
       </c>
-      <c r="AA68" s="122"/>
+      <c r="AA68" s="121"/>
     </row>
     <row r="69" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
@@ -12766,7 +12766,7 @@
       <c r="G69" t="s">
         <v>428</v>
       </c>
-      <c r="H69" s="123"/>
+      <c r="H69" s="122"/>
       <c r="I69" t="s">
         <v>432</v>
       </c>
@@ -12821,7 +12821,7 @@
       <c r="Z69" t="s">
         <v>442</v>
       </c>
-      <c r="AA69" s="122"/>
+      <c r="AA69" s="121"/>
     </row>
     <row r="70" spans="1:28" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
@@ -12845,7 +12845,7 @@
       <c r="G70" t="s">
         <v>445</v>
       </c>
-      <c r="H70" s="123" t="s">
+      <c r="H70" s="122" t="s">
         <v>41</v>
       </c>
       <c r="I70" t="s">
@@ -12902,7 +12902,7 @@
       <c r="Z70" t="s">
         <v>461</v>
       </c>
-      <c r="AA70" s="122" t="s">
+      <c r="AA70" s="121" t="s">
         <v>454</v>
       </c>
     </row>
@@ -12928,7 +12928,7 @@
       <c r="G71" t="s">
         <v>445</v>
       </c>
-      <c r="H71" s="123"/>
+      <c r="H71" s="122"/>
       <c r="I71" t="s">
         <v>450</v>
       </c>
@@ -12983,7 +12983,7 @@
       <c r="Z71" t="s">
         <v>461</v>
       </c>
-      <c r="AA71" s="122"/>
+      <c r="AA71" s="121"/>
     </row>
     <row r="72" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
@@ -13007,7 +13007,7 @@
       <c r="G72" t="s">
         <v>445</v>
       </c>
-      <c r="H72" s="123"/>
+      <c r="H72" s="122"/>
       <c r="I72" t="s">
         <v>450</v>
       </c>
@@ -13062,7 +13062,7 @@
       <c r="Z72" t="s">
         <v>461</v>
       </c>
-      <c r="AA72" s="122"/>
+      <c r="AA72" s="121"/>
     </row>
     <row r="73" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
@@ -13086,7 +13086,7 @@
       <c r="G73" t="s">
         <v>445</v>
       </c>
-      <c r="H73" s="123"/>
+      <c r="H73" s="122"/>
       <c r="I73" t="s">
         <v>450</v>
       </c>
@@ -13141,7 +13141,7 @@
       <c r="Z73" t="s">
         <v>461</v>
       </c>
-      <c r="AA73" s="122"/>
+      <c r="AA73" s="121"/>
     </row>
     <row r="74" spans="1:28" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
@@ -13165,7 +13165,7 @@
       <c r="G74" t="s">
         <v>463</v>
       </c>
-      <c r="H74" s="123" t="s">
+      <c r="H74" s="122" t="s">
         <v>41</v>
       </c>
       <c r="I74" t="s">
@@ -13210,7 +13210,7 @@
       <c r="Z74" t="s">
         <v>477</v>
       </c>
-      <c r="AA74" s="122" t="s">
+      <c r="AA74" s="121" t="s">
         <v>470</v>
       </c>
     </row>
@@ -13236,7 +13236,7 @@
       <c r="G75" t="s">
         <v>463</v>
       </c>
-      <c r="H75" s="123"/>
+      <c r="H75" s="122"/>
       <c r="I75" t="s">
         <v>468</v>
       </c>
@@ -13279,7 +13279,7 @@
       <c r="Z75" t="s">
         <v>477</v>
       </c>
-      <c r="AA75" s="122"/>
+      <c r="AA75" s="121"/>
     </row>
     <row r="76" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
@@ -13303,7 +13303,7 @@
       <c r="G76" t="s">
         <v>463</v>
       </c>
-      <c r="H76" s="123"/>
+      <c r="H76" s="122"/>
       <c r="I76" t="s">
         <v>468</v>
       </c>
@@ -13346,7 +13346,7 @@
       <c r="Z76" t="s">
         <v>477</v>
       </c>
-      <c r="AA76" s="122"/>
+      <c r="AA76" s="121"/>
     </row>
     <row r="77" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
@@ -13370,7 +13370,7 @@
       <c r="G77" t="s">
         <v>463</v>
       </c>
-      <c r="H77" s="123"/>
+      <c r="H77" s="122"/>
       <c r="I77" t="s">
         <v>468</v>
       </c>
@@ -13413,7 +13413,7 @@
       <c r="Z77" t="s">
         <v>477</v>
       </c>
-      <c r="AA77" s="122"/>
+      <c r="AA77" s="121"/>
     </row>
     <row r="78" spans="1:28" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
@@ -13437,7 +13437,7 @@
       <c r="G78" t="s">
         <v>480</v>
       </c>
-      <c r="H78" s="123" t="s">
+      <c r="H78" s="122" t="s">
         <v>486</v>
       </c>
       <c r="I78" t="s">
@@ -13482,7 +13482,7 @@
       <c r="Z78" t="s">
         <v>496</v>
       </c>
-      <c r="AA78" s="122" t="s">
+      <c r="AA78" s="121" t="s">
         <v>478</v>
       </c>
     </row>
@@ -13508,7 +13508,7 @@
       <c r="G79" t="s">
         <v>480</v>
       </c>
-      <c r="H79" s="123"/>
+      <c r="H79" s="122"/>
       <c r="I79" t="s">
         <v>487</v>
       </c>
@@ -13551,7 +13551,7 @@
       <c r="Z79" t="s">
         <v>496</v>
       </c>
-      <c r="AA79" s="122"/>
+      <c r="AA79" s="121"/>
     </row>
     <row r="80" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
@@ -13575,7 +13575,7 @@
       <c r="G80" t="s">
         <v>480</v>
       </c>
-      <c r="H80" s="123"/>
+      <c r="H80" s="122"/>
       <c r="I80" t="s">
         <v>487</v>
       </c>
@@ -13618,7 +13618,7 @@
       <c r="Z80" t="s">
         <v>496</v>
       </c>
-      <c r="AA80" s="122"/>
+      <c r="AA80" s="121"/>
     </row>
     <row r="81" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
@@ -13642,7 +13642,7 @@
       <c r="G81" t="s">
         <v>480</v>
       </c>
-      <c r="H81" s="123"/>
+      <c r="H81" s="122"/>
       <c r="I81" t="s">
         <v>487</v>
       </c>
@@ -13685,7 +13685,7 @@
       <c r="Z81" t="s">
         <v>496</v>
       </c>
-      <c r="AA81" s="122"/>
+      <c r="AA81" s="121"/>
     </row>
     <row r="82" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
@@ -13709,7 +13709,7 @@
       <c r="G82" t="s">
         <v>498</v>
       </c>
-      <c r="H82" s="123" t="s">
+      <c r="H82" s="122" t="s">
         <v>89</v>
       </c>
       <c r="I82" t="s">
@@ -13754,7 +13754,7 @@
       <c r="Z82" t="s">
         <v>511</v>
       </c>
-      <c r="AA82" s="122" t="s">
+      <c r="AA82" s="121" t="s">
         <v>90</v>
       </c>
     </row>
@@ -13780,7 +13780,7 @@
       <c r="G83" t="s">
         <v>498</v>
       </c>
-      <c r="H83" s="123"/>
+      <c r="H83" s="122"/>
       <c r="I83" t="s">
         <v>503</v>
       </c>
@@ -13823,7 +13823,7 @@
       <c r="Z83" t="s">
         <v>511</v>
       </c>
-      <c r="AA83" s="122"/>
+      <c r="AA83" s="121"/>
     </row>
     <row r="84" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
@@ -13847,7 +13847,7 @@
       <c r="G84" t="s">
         <v>498</v>
       </c>
-      <c r="H84" s="123"/>
+      <c r="H84" s="122"/>
       <c r="I84" t="s">
         <v>503</v>
       </c>
@@ -13890,7 +13890,7 @@
       <c r="Z84" t="s">
         <v>511</v>
       </c>
-      <c r="AA84" s="122"/>
+      <c r="AA84" s="121"/>
     </row>
     <row r="85" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
@@ -13914,7 +13914,7 @@
       <c r="G85" t="s">
         <v>498</v>
       </c>
-      <c r="H85" s="123"/>
+      <c r="H85" s="122"/>
       <c r="I85" t="s">
         <v>503</v>
       </c>
@@ -13957,7 +13957,7 @@
       <c r="Z85" t="s">
         <v>511</v>
       </c>
-      <c r="AA85" s="122"/>
+      <c r="AA85" s="121"/>
     </row>
     <row r="86" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
@@ -13981,7 +13981,7 @@
       <c r="G86" t="s">
         <v>514</v>
       </c>
-      <c r="H86" s="123" t="s">
+      <c r="H86" s="122" t="s">
         <v>89</v>
       </c>
       <c r="I86" t="s">
@@ -14026,7 +14026,7 @@
       <c r="Z86" t="s">
         <v>526</v>
       </c>
-      <c r="AA86" s="122" t="s">
+      <c r="AA86" s="121" t="s">
         <v>92</v>
       </c>
     </row>
@@ -14052,7 +14052,7 @@
       <c r="G87" t="s">
         <v>514</v>
       </c>
-      <c r="H87" s="123"/>
+      <c r="H87" s="122"/>
       <c r="I87" t="s">
         <v>518</v>
       </c>
@@ -14095,7 +14095,7 @@
       <c r="Z87" t="s">
         <v>526</v>
       </c>
-      <c r="AA87" s="122"/>
+      <c r="AA87" s="121"/>
     </row>
     <row r="88" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
@@ -14119,7 +14119,7 @@
       <c r="G88" t="s">
         <v>514</v>
       </c>
-      <c r="H88" s="123"/>
+      <c r="H88" s="122"/>
       <c r="I88" t="s">
         <v>518</v>
       </c>
@@ -14162,7 +14162,7 @@
       <c r="Z88" t="s">
         <v>526</v>
       </c>
-      <c r="AA88" s="122"/>
+      <c r="AA88" s="121"/>
     </row>
     <row r="89" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
@@ -14186,7 +14186,7 @@
       <c r="G89" t="s">
         <v>514</v>
       </c>
-      <c r="H89" s="123"/>
+      <c r="H89" s="122"/>
       <c r="I89" t="s">
         <v>518</v>
       </c>
@@ -14229,7 +14229,7 @@
       <c r="Z89" t="s">
         <v>526</v>
       </c>
-      <c r="AA89" s="122"/>
+      <c r="AA89" s="121"/>
     </row>
     <row r="90" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
@@ -14253,7 +14253,7 @@
       <c r="G90" t="s">
         <v>530</v>
       </c>
-      <c r="H90" s="123" t="s">
+      <c r="H90" s="122" t="s">
         <v>89</v>
       </c>
       <c r="I90" t="s">
@@ -14265,7 +14265,7 @@
       <c r="K90" t="s">
         <v>20</v>
       </c>
-      <c r="L90" s="122" t="s">
+      <c r="L90" s="121" t="s">
         <v>536</v>
       </c>
       <c r="M90" t="s">
@@ -14310,7 +14310,7 @@
       <c r="Z90" t="s">
         <v>546</v>
       </c>
-      <c r="AA90" s="122" t="s">
+      <c r="AA90" s="121" t="s">
         <v>114</v>
       </c>
       <c r="AB90" s="5"/>
@@ -14337,7 +14337,7 @@
       <c r="G91" t="s">
         <v>530</v>
       </c>
-      <c r="H91" s="123"/>
+      <c r="H91" s="122"/>
       <c r="I91" t="s">
         <v>534</v>
       </c>
@@ -14347,7 +14347,7 @@
       <c r="K91" t="s">
         <v>20</v>
       </c>
-      <c r="L91" s="122"/>
+      <c r="L91" s="121"/>
       <c r="M91" t="s">
         <v>16</v>
       </c>
@@ -14390,7 +14390,7 @@
       <c r="Z91" t="s">
         <v>546</v>
       </c>
-      <c r="AA91" s="122"/>
+      <c r="AA91" s="121"/>
       <c r="AB91" s="5"/>
     </row>
     <row r="92" spans="1:28" x14ac:dyDescent="0.3">
@@ -14415,7 +14415,7 @@
       <c r="G92" t="s">
         <v>530</v>
       </c>
-      <c r="H92" s="123"/>
+      <c r="H92" s="122"/>
       <c r="I92" t="s">
         <v>534</v>
       </c>
@@ -14425,7 +14425,7 @@
       <c r="K92" t="s">
         <v>20</v>
       </c>
-      <c r="L92" s="122"/>
+      <c r="L92" s="121"/>
       <c r="M92" t="s">
         <v>16</v>
       </c>
@@ -14468,7 +14468,7 @@
       <c r="Z92" t="s">
         <v>546</v>
       </c>
-      <c r="AA92" s="122"/>
+      <c r="AA92" s="121"/>
       <c r="AB92" s="5"/>
     </row>
     <row r="93" spans="1:28" x14ac:dyDescent="0.3">
@@ -14493,7 +14493,7 @@
       <c r="G93" t="s">
         <v>530</v>
       </c>
-      <c r="H93" s="123"/>
+      <c r="H93" s="122"/>
       <c r="I93" t="s">
         <v>534</v>
       </c>
@@ -14503,7 +14503,7 @@
       <c r="K93" t="s">
         <v>20</v>
       </c>
-      <c r="L93" s="122"/>
+      <c r="L93" s="121"/>
       <c r="M93" t="s">
         <v>16</v>
       </c>
@@ -14546,7 +14546,7 @@
       <c r="Z93" t="s">
         <v>546</v>
       </c>
-      <c r="AA93" s="122"/>
+      <c r="AA93" s="121"/>
       <c r="AB93" s="5"/>
     </row>
     <row r="94" spans="1:28" ht="144" customHeight="1" x14ac:dyDescent="0.3">
@@ -14571,7 +14571,7 @@
       <c r="G94" t="s">
         <v>552</v>
       </c>
-      <c r="H94" s="123" t="s">
+      <c r="H94" s="122" t="s">
         <v>89</v>
       </c>
       <c r="I94" t="s">
@@ -14628,7 +14628,7 @@
       <c r="Z94" t="s">
         <v>561</v>
       </c>
-      <c r="AA94" s="122" t="s">
+      <c r="AA94" s="121" t="s">
         <v>96</v>
       </c>
     </row>
@@ -14654,7 +14654,7 @@
       <c r="G95" t="s">
         <v>552</v>
       </c>
-      <c r="H95" s="123"/>
+      <c r="H95" s="122"/>
       <c r="I95" t="s">
         <v>553</v>
       </c>
@@ -14709,7 +14709,7 @@
       <c r="Z95" t="s">
         <v>561</v>
       </c>
-      <c r="AA95" s="122"/>
+      <c r="AA95" s="121"/>
     </row>
     <row r="96" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
@@ -14733,7 +14733,7 @@
       <c r="G96" t="s">
         <v>552</v>
       </c>
-      <c r="H96" s="123"/>
+      <c r="H96" s="122"/>
       <c r="I96" t="s">
         <v>553</v>
       </c>
@@ -14788,7 +14788,7 @@
       <c r="Z96" t="s">
         <v>561</v>
       </c>
-      <c r="AA96" s="122"/>
+      <c r="AA96" s="121"/>
     </row>
     <row r="97" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
@@ -14812,7 +14812,7 @@
       <c r="G97" t="s">
         <v>552</v>
       </c>
-      <c r="H97" s="123"/>
+      <c r="H97" s="122"/>
       <c r="I97" t="s">
         <v>553</v>
       </c>
@@ -14867,7 +14867,7 @@
       <c r="Z97" t="s">
         <v>561</v>
       </c>
-      <c r="AA97" s="122"/>
+      <c r="AA97" s="121"/>
     </row>
     <row r="98" spans="1:27" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
@@ -14891,7 +14891,7 @@
       <c r="G98" t="s">
         <v>568</v>
       </c>
-      <c r="H98" s="123" t="s">
+      <c r="H98" s="122" t="s">
         <v>89</v>
       </c>
       <c r="I98" t="s">
@@ -14948,7 +14948,7 @@
       <c r="Z98" t="s">
         <v>580</v>
       </c>
-      <c r="AA98" s="122" t="s">
+      <c r="AA98" s="121" t="s">
         <v>572</v>
       </c>
     </row>
@@ -14974,7 +14974,7 @@
       <c r="G99" t="s">
         <v>568</v>
       </c>
-      <c r="H99" s="123"/>
+      <c r="H99" s="122"/>
       <c r="I99" t="s">
         <v>569</v>
       </c>
@@ -15029,7 +15029,7 @@
       <c r="Z99" t="s">
         <v>580</v>
       </c>
-      <c r="AA99" s="122"/>
+      <c r="AA99" s="121"/>
     </row>
     <row r="100" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
@@ -15053,7 +15053,7 @@
       <c r="G100" t="s">
         <v>568</v>
       </c>
-      <c r="H100" s="123"/>
+      <c r="H100" s="122"/>
       <c r="I100" t="s">
         <v>569</v>
       </c>
@@ -15108,7 +15108,7 @@
       <c r="Z100" t="s">
         <v>580</v>
       </c>
-      <c r="AA100" s="122"/>
+      <c r="AA100" s="121"/>
     </row>
     <row r="101" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
@@ -15132,7 +15132,7 @@
       <c r="G101" t="s">
         <v>568</v>
       </c>
-      <c r="H101" s="123"/>
+      <c r="H101" s="122"/>
       <c r="I101" t="s">
         <v>569</v>
       </c>
@@ -15187,7 +15187,7 @@
       <c r="Z101" t="s">
         <v>580</v>
       </c>
-      <c r="AA101" s="122"/>
+      <c r="AA101" s="121"/>
     </row>
     <row r="102" spans="1:27" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
@@ -15211,7 +15211,7 @@
       <c r="G102" t="s">
         <v>587</v>
       </c>
-      <c r="H102" s="123" t="s">
+      <c r="H102" s="122" t="s">
         <v>89</v>
       </c>
       <c r="I102" t="s">
@@ -15268,7 +15268,7 @@
       <c r="Z102" t="s">
         <v>596</v>
       </c>
-      <c r="AA102" s="122" t="s">
+      <c r="AA102" s="121" t="s">
         <v>100</v>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       <c r="G103" t="s">
         <v>587</v>
       </c>
-      <c r="H103" s="123"/>
+      <c r="H103" s="122"/>
       <c r="I103" t="s">
         <v>583</v>
       </c>
@@ -15349,7 +15349,7 @@
       <c r="Z103" t="s">
         <v>596</v>
       </c>
-      <c r="AA103" s="122"/>
+      <c r="AA103" s="121"/>
     </row>
     <row r="104" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
@@ -15373,7 +15373,7 @@
       <c r="G104" t="s">
         <v>587</v>
       </c>
-      <c r="H104" s="123"/>
+      <c r="H104" s="122"/>
       <c r="I104" t="s">
         <v>583</v>
       </c>
@@ -15428,7 +15428,7 @@
       <c r="Z104" t="s">
         <v>596</v>
       </c>
-      <c r="AA104" s="122"/>
+      <c r="AA104" s="121"/>
     </row>
     <row r="105" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
@@ -15452,7 +15452,7 @@
       <c r="G105" t="s">
         <v>587</v>
       </c>
-      <c r="H105" s="123"/>
+      <c r="H105" s="122"/>
       <c r="I105" t="s">
         <v>583</v>
       </c>
@@ -15507,7 +15507,7 @@
       <c r="Z105" t="s">
         <v>596</v>
       </c>
-      <c r="AA105" s="122"/>
+      <c r="AA105" s="121"/>
     </row>
     <row r="106" spans="1:27" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
@@ -15531,7 +15531,7 @@
       <c r="G106" t="s">
         <v>599</v>
       </c>
-      <c r="H106" s="123" t="s">
+      <c r="H106" s="122" t="s">
         <v>89</v>
       </c>
       <c r="I106" t="s">
@@ -15588,7 +15588,7 @@
       <c r="Z106" t="s">
         <v>609</v>
       </c>
-      <c r="AA106" s="122" t="s">
+      <c r="AA106" s="121" t="s">
         <v>107</v>
       </c>
     </row>
@@ -15614,7 +15614,7 @@
       <c r="G107" t="s">
         <v>599</v>
       </c>
-      <c r="H107" s="123"/>
+      <c r="H107" s="122"/>
       <c r="I107" t="s">
         <v>600</v>
       </c>
@@ -15669,7 +15669,7 @@
       <c r="Z107" t="s">
         <v>609</v>
       </c>
-      <c r="AA107" s="122"/>
+      <c r="AA107" s="121"/>
     </row>
     <row r="108" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
@@ -15693,7 +15693,7 @@
       <c r="G108" t="s">
         <v>599</v>
       </c>
-      <c r="H108" s="123"/>
+      <c r="H108" s="122"/>
       <c r="I108" t="s">
         <v>600</v>
       </c>
@@ -15748,7 +15748,7 @@
       <c r="Z108" t="s">
         <v>609</v>
       </c>
-      <c r="AA108" s="122"/>
+      <c r="AA108" s="121"/>
     </row>
     <row r="109" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
@@ -15772,7 +15772,7 @@
       <c r="G109" t="s">
         <v>599</v>
       </c>
-      <c r="H109" s="123"/>
+      <c r="H109" s="122"/>
       <c r="I109" t="s">
         <v>600</v>
       </c>
@@ -15827,7 +15827,7 @@
       <c r="Z109" t="s">
         <v>609</v>
       </c>
-      <c r="AA109" s="122"/>
+      <c r="AA109" s="121"/>
     </row>
     <row r="110" spans="1:27" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
@@ -15851,7 +15851,7 @@
       <c r="G110" t="s">
         <v>612</v>
       </c>
-      <c r="H110" s="123" t="s">
+      <c r="H110" s="122" t="s">
         <v>89</v>
       </c>
       <c r="I110" t="s">
@@ -15908,7 +15908,7 @@
       <c r="Z110" t="s">
         <v>626</v>
       </c>
-      <c r="AA110" s="122" t="s">
+      <c r="AA110" s="121" t="s">
         <v>833</v>
       </c>
     </row>
@@ -15934,7 +15934,7 @@
       <c r="G111" t="s">
         <v>612</v>
       </c>
-      <c r="H111" s="123"/>
+      <c r="H111" s="122"/>
       <c r="I111" t="s">
         <v>617</v>
       </c>
@@ -15989,7 +15989,7 @@
       <c r="Z111" t="s">
         <v>626</v>
       </c>
-      <c r="AA111" s="122"/>
+      <c r="AA111" s="121"/>
     </row>
     <row r="112" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
@@ -16013,7 +16013,7 @@
       <c r="G112" t="s">
         <v>612</v>
       </c>
-      <c r="H112" s="123"/>
+      <c r="H112" s="122"/>
       <c r="I112" t="s">
         <v>617</v>
       </c>
@@ -16068,7 +16068,7 @@
       <c r="Z112" t="s">
         <v>626</v>
       </c>
-      <c r="AA112" s="122"/>
+      <c r="AA112" s="121"/>
     </row>
     <row r="113" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
@@ -16092,7 +16092,7 @@
       <c r="G113" t="s">
         <v>612</v>
       </c>
-      <c r="H113" s="123"/>
+      <c r="H113" s="122"/>
       <c r="I113" t="s">
         <v>617</v>
       </c>
@@ -16147,7 +16147,7 @@
       <c r="Z113" t="s">
         <v>626</v>
       </c>
-      <c r="AA113" s="122"/>
+      <c r="AA113" s="121"/>
     </row>
     <row r="114" spans="1:28" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
@@ -16171,7 +16171,7 @@
       <c r="G114" t="s">
         <v>628</v>
       </c>
-      <c r="H114" s="123" t="s">
+      <c r="H114" s="122" t="s">
         <v>634</v>
       </c>
       <c r="I114" t="s">
@@ -16216,7 +16216,7 @@
       <c r="Z114" t="s">
         <v>644</v>
       </c>
-      <c r="AA114" s="122" t="s">
+      <c r="AA114" s="121" t="s">
         <v>645</v>
       </c>
     </row>
@@ -16242,7 +16242,7 @@
       <c r="G115" t="s">
         <v>628</v>
       </c>
-      <c r="H115" s="123"/>
+      <c r="H115" s="122"/>
       <c r="I115" t="s">
         <v>635</v>
       </c>
@@ -16285,7 +16285,7 @@
       <c r="Z115" t="s">
         <v>644</v>
       </c>
-      <c r="AA115" s="122"/>
+      <c r="AA115" s="121"/>
     </row>
     <row r="116" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
@@ -16309,7 +16309,7 @@
       <c r="G116" t="s">
         <v>628</v>
       </c>
-      <c r="H116" s="123"/>
+      <c r="H116" s="122"/>
       <c r="I116" t="s">
         <v>635</v>
       </c>
@@ -16352,7 +16352,7 @@
       <c r="Z116" t="s">
         <v>644</v>
       </c>
-      <c r="AA116" s="122"/>
+      <c r="AA116" s="121"/>
     </row>
     <row r="117" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
@@ -16376,7 +16376,7 @@
       <c r="G117" t="s">
         <v>628</v>
       </c>
-      <c r="H117" s="123"/>
+      <c r="H117" s="122"/>
       <c r="I117" t="s">
         <v>635</v>
       </c>
@@ -16419,7 +16419,7 @@
       <c r="Z117" t="s">
         <v>644</v>
       </c>
-      <c r="AA117" s="122"/>
+      <c r="AA117" s="121"/>
     </row>
     <row r="118" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
@@ -16443,7 +16443,7 @@
       <c r="G118" t="s">
         <v>648</v>
       </c>
-      <c r="H118" s="123" t="s">
+      <c r="H118" s="122" t="s">
         <v>656</v>
       </c>
       <c r="I118" t="s">
@@ -16488,7 +16488,7 @@
       <c r="Z118" t="s">
         <v>661</v>
       </c>
-      <c r="AA118" s="122" t="s">
+      <c r="AA118" s="121" t="s">
         <v>111</v>
       </c>
     </row>
@@ -16514,7 +16514,7 @@
       <c r="G119" t="s">
         <v>648</v>
       </c>
-      <c r="H119" s="123"/>
+      <c r="H119" s="122"/>
       <c r="I119" t="s">
         <v>654</v>
       </c>
@@ -16557,7 +16557,7 @@
       <c r="Z119" t="s">
         <v>661</v>
       </c>
-      <c r="AA119" s="122"/>
+      <c r="AA119" s="121"/>
     </row>
     <row r="120" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
@@ -16581,7 +16581,7 @@
       <c r="G120" t="s">
         <v>648</v>
       </c>
-      <c r="H120" s="123"/>
+      <c r="H120" s="122"/>
       <c r="I120" t="s">
         <v>654</v>
       </c>
@@ -16624,7 +16624,7 @@
       <c r="Z120" t="s">
         <v>661</v>
       </c>
-      <c r="AA120" s="122"/>
+      <c r="AA120" s="121"/>
     </row>
     <row r="121" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
@@ -16648,7 +16648,7 @@
       <c r="G121" t="s">
         <v>648</v>
       </c>
-      <c r="H121" s="123"/>
+      <c r="H121" s="122"/>
       <c r="I121" t="s">
         <v>654</v>
       </c>
@@ -16691,7 +16691,7 @@
       <c r="Z121" t="s">
         <v>661</v>
       </c>
-      <c r="AA121" s="122"/>
+      <c r="AA121" s="121"/>
     </row>
     <row r="122" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
@@ -16715,7 +16715,7 @@
       <c r="G122" t="s">
         <v>665</v>
       </c>
-      <c r="H122" s="123" t="s">
+      <c r="H122" s="122" t="s">
         <v>89</v>
       </c>
       <c r="I122" t="s">
@@ -16760,7 +16760,7 @@
       <c r="Z122" t="s">
         <v>677</v>
       </c>
-      <c r="AA122" s="122" t="s">
+      <c r="AA122" s="121" t="s">
         <v>117</v>
       </c>
     </row>
@@ -16786,7 +16786,7 @@
       <c r="G123" t="s">
         <v>665</v>
       </c>
-      <c r="H123" s="123"/>
+      <c r="H123" s="122"/>
       <c r="I123" t="s">
         <v>664</v>
       </c>
@@ -16829,7 +16829,7 @@
       <c r="Z123" t="s">
         <v>677</v>
       </c>
-      <c r="AA123" s="122"/>
+      <c r="AA123" s="121"/>
     </row>
     <row r="124" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
@@ -16853,7 +16853,7 @@
       <c r="G124" t="s">
         <v>665</v>
       </c>
-      <c r="H124" s="123"/>
+      <c r="H124" s="122"/>
       <c r="I124" t="s">
         <v>664</v>
       </c>
@@ -16896,7 +16896,7 @@
       <c r="Z124" t="s">
         <v>677</v>
       </c>
-      <c r="AA124" s="122"/>
+      <c r="AA124" s="121"/>
     </row>
     <row r="125" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
@@ -16920,7 +16920,7 @@
       <c r="G125" t="s">
         <v>665</v>
       </c>
-      <c r="H125" s="123"/>
+      <c r="H125" s="122"/>
       <c r="I125" t="s">
         <v>664</v>
       </c>
@@ -16963,7 +16963,7 @@
       <c r="Z125" t="s">
         <v>677</v>
       </c>
-      <c r="AA125" s="122"/>
+      <c r="AA125" s="121"/>
     </row>
     <row r="126" spans="1:28" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
@@ -16987,7 +16987,7 @@
       <c r="G126" t="s">
         <v>682</v>
       </c>
-      <c r="H126" s="123" t="s">
+      <c r="H126" s="122" t="s">
         <v>89</v>
       </c>
       <c r="I126" t="s">
@@ -17044,10 +17044,10 @@
       <c r="Z126" t="s">
         <v>696</v>
       </c>
-      <c r="AA126" s="122" t="s">
+      <c r="AA126" s="121" t="s">
         <v>680</v>
       </c>
-      <c r="AB126" s="124" t="s">
+      <c r="AB126" s="123" t="s">
         <v>146</v>
       </c>
     </row>
@@ -17073,7 +17073,7 @@
       <c r="G127" t="s">
         <v>682</v>
       </c>
-      <c r="H127" s="123"/>
+      <c r="H127" s="122"/>
       <c r="I127" t="s">
         <v>687</v>
       </c>
@@ -17128,8 +17128,8 @@
       <c r="Z127" t="s">
         <v>696</v>
       </c>
-      <c r="AA127" s="122"/>
-      <c r="AB127" s="124"/>
+      <c r="AA127" s="121"/>
+      <c r="AB127" s="123"/>
     </row>
     <row r="128" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
@@ -17153,7 +17153,7 @@
       <c r="G128" t="s">
         <v>682</v>
       </c>
-      <c r="H128" s="123"/>
+      <c r="H128" s="122"/>
       <c r="I128" t="s">
         <v>687</v>
       </c>
@@ -17208,8 +17208,8 @@
       <c r="Z128" t="s">
         <v>696</v>
       </c>
-      <c r="AA128" s="122"/>
-      <c r="AB128" s="124"/>
+      <c r="AA128" s="121"/>
+      <c r="AB128" s="123"/>
     </row>
     <row r="129" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
@@ -17233,7 +17233,7 @@
       <c r="G129" t="s">
         <v>682</v>
       </c>
-      <c r="H129" s="123"/>
+      <c r="H129" s="122"/>
       <c r="I129" t="s">
         <v>687</v>
       </c>
@@ -17288,8 +17288,8 @@
       <c r="Z129" t="s">
         <v>696</v>
       </c>
-      <c r="AA129" s="122"/>
-      <c r="AB129" s="124"/>
+      <c r="AA129" s="121"/>
+      <c r="AB129" s="123"/>
     </row>
     <row r="130" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
@@ -17313,7 +17313,7 @@
       <c r="G130" t="s">
         <v>123</v>
       </c>
-      <c r="H130" s="123" t="s">
+      <c r="H130" s="122" t="s">
         <v>89</v>
       </c>
       <c r="I130" t="s">
@@ -17370,10 +17370,10 @@
       <c r="Z130" t="s">
         <v>705</v>
       </c>
-      <c r="AA130" s="122" t="s">
+      <c r="AA130" s="121" t="s">
         <v>130</v>
       </c>
-      <c r="AB130" s="121" t="s">
+      <c r="AB130" s="124" t="s">
         <v>697</v>
       </c>
     </row>
@@ -17399,7 +17399,7 @@
       <c r="G131" t="s">
         <v>123</v>
       </c>
-      <c r="H131" s="123"/>
+      <c r="H131" s="122"/>
       <c r="I131" t="s">
         <v>128</v>
       </c>
@@ -17454,8 +17454,8 @@
       <c r="Z131" t="s">
         <v>705</v>
       </c>
-      <c r="AA131" s="122"/>
-      <c r="AB131" s="121"/>
+      <c r="AA131" s="121"/>
+      <c r="AB131" s="124"/>
     </row>
     <row r="132" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
@@ -17479,7 +17479,7 @@
       <c r="G132" t="s">
         <v>123</v>
       </c>
-      <c r="H132" s="123"/>
+      <c r="H132" s="122"/>
       <c r="I132" t="s">
         <v>128</v>
       </c>
@@ -17534,8 +17534,8 @@
       <c r="Z132" t="s">
         <v>705</v>
       </c>
-      <c r="AA132" s="122"/>
-      <c r="AB132" s="121"/>
+      <c r="AA132" s="121"/>
+      <c r="AB132" s="124"/>
     </row>
     <row r="133" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
@@ -17559,7 +17559,7 @@
       <c r="G133" t="s">
         <v>123</v>
       </c>
-      <c r="H133" s="123"/>
+      <c r="H133" s="122"/>
       <c r="I133" t="s">
         <v>128</v>
       </c>
@@ -17614,8 +17614,8 @@
       <c r="Z133" t="s">
         <v>705</v>
       </c>
-      <c r="AA133" s="122"/>
-      <c r="AB133" s="121"/>
+      <c r="AA133" s="121"/>
+      <c r="AB133" s="124"/>
     </row>
     <row r="134" spans="1:28" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
@@ -17639,7 +17639,7 @@
       <c r="G134" t="s">
         <v>708</v>
       </c>
-      <c r="H134" s="123" t="s">
+      <c r="H134" s="122" t="s">
         <v>89</v>
       </c>
       <c r="I134" t="s">
@@ -17696,7 +17696,7 @@
       <c r="Z134" t="s">
         <v>718</v>
       </c>
-      <c r="AA134" s="122" t="s">
+      <c r="AA134" s="121" t="s">
         <v>136</v>
       </c>
     </row>
@@ -17722,7 +17722,7 @@
       <c r="G135" t="s">
         <v>708</v>
       </c>
-      <c r="H135" s="123"/>
+      <c r="H135" s="122"/>
       <c r="I135" t="s">
         <v>710</v>
       </c>
@@ -17777,7 +17777,7 @@
       <c r="Z135" t="s">
         <v>718</v>
       </c>
-      <c r="AA135" s="122"/>
+      <c r="AA135" s="121"/>
     </row>
     <row r="136" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
@@ -17801,7 +17801,7 @@
       <c r="G136" t="s">
         <v>708</v>
       </c>
-      <c r="H136" s="123"/>
+      <c r="H136" s="122"/>
       <c r="I136" t="s">
         <v>710</v>
       </c>
@@ -17856,7 +17856,7 @@
       <c r="Z136" t="s">
         <v>718</v>
       </c>
-      <c r="AA136" s="122"/>
+      <c r="AA136" s="121"/>
     </row>
     <row r="137" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
@@ -17880,7 +17880,7 @@
       <c r="G137" t="s">
         <v>708</v>
       </c>
-      <c r="H137" s="123"/>
+      <c r="H137" s="122"/>
       <c r="I137" t="s">
         <v>710</v>
       </c>
@@ -17935,7 +17935,7 @@
       <c r="Z137" t="s">
         <v>718</v>
       </c>
-      <c r="AA137" s="122"/>
+      <c r="AA137" s="121"/>
     </row>
     <row r="138" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
@@ -17959,7 +17959,7 @@
       <c r="G138" t="s">
         <v>721</v>
       </c>
-      <c r="H138" s="123" t="s">
+      <c r="H138" s="122" t="s">
         <v>89</v>
       </c>
       <c r="I138" t="s">
@@ -18004,7 +18004,7 @@
       <c r="Z138" t="s">
         <v>735</v>
       </c>
-      <c r="AA138" s="122" t="s">
+      <c r="AA138" s="121" t="s">
         <v>138</v>
       </c>
     </row>
@@ -18030,7 +18030,7 @@
       <c r="G139" t="s">
         <v>721</v>
       </c>
-      <c r="H139" s="123"/>
+      <c r="H139" s="122"/>
       <c r="I139" t="s">
         <v>727</v>
       </c>
@@ -18073,7 +18073,7 @@
       <c r="Z139" t="s">
         <v>735</v>
       </c>
-      <c r="AA139" s="122"/>
+      <c r="AA139" s="121"/>
     </row>
     <row r="140" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
@@ -18097,7 +18097,7 @@
       <c r="G140" t="s">
         <v>721</v>
       </c>
-      <c r="H140" s="123"/>
+      <c r="H140" s="122"/>
       <c r="I140" t="s">
         <v>727</v>
       </c>
@@ -18140,7 +18140,7 @@
       <c r="Z140" t="s">
         <v>735</v>
       </c>
-      <c r="AA140" s="122"/>
+      <c r="AA140" s="121"/>
     </row>
     <row r="141" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
@@ -18164,7 +18164,7 @@
       <c r="G141" t="s">
         <v>721</v>
       </c>
-      <c r="H141" s="123"/>
+      <c r="H141" s="122"/>
       <c r="I141" t="s">
         <v>727</v>
       </c>
@@ -18207,7 +18207,7 @@
       <c r="Z141" t="s">
         <v>735</v>
       </c>
-      <c r="AA141" s="122"/>
+      <c r="AA141" s="121"/>
     </row>
     <row r="142" spans="1:28" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
@@ -18231,7 +18231,7 @@
       <c r="G142" t="s">
         <v>738</v>
       </c>
-      <c r="H142" s="123" t="s">
+      <c r="H142" s="122" t="s">
         <v>140</v>
       </c>
       <c r="I142" t="s">
@@ -18276,7 +18276,7 @@
       <c r="Z142" t="s">
         <v>752</v>
       </c>
-      <c r="AA142" s="122" t="s">
+      <c r="AA142" s="121" t="s">
         <v>141</v>
       </c>
     </row>
@@ -18302,7 +18302,7 @@
       <c r="G143" t="s">
         <v>738</v>
       </c>
-      <c r="H143" s="123"/>
+      <c r="H143" s="122"/>
       <c r="I143" t="s">
         <v>743</v>
       </c>
@@ -18345,7 +18345,7 @@
       <c r="Z143" t="s">
         <v>752</v>
       </c>
-      <c r="AA143" s="122"/>
+      <c r="AA143" s="121"/>
     </row>
     <row r="144" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
@@ -18369,7 +18369,7 @@
       <c r="G144" t="s">
         <v>738</v>
       </c>
-      <c r="H144" s="123"/>
+      <c r="H144" s="122"/>
       <c r="I144" t="s">
         <v>743</v>
       </c>
@@ -18412,7 +18412,7 @@
       <c r="Z144" t="s">
         <v>752</v>
       </c>
-      <c r="AA144" s="122"/>
+      <c r="AA144" s="121"/>
     </row>
     <row r="145" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
@@ -18436,7 +18436,7 @@
       <c r="G145" t="s">
         <v>738</v>
       </c>
-      <c r="H145" s="123"/>
+      <c r="H145" s="122"/>
       <c r="I145" t="s">
         <v>743</v>
       </c>
@@ -18479,7 +18479,7 @@
       <c r="Z145" t="s">
         <v>752</v>
       </c>
-      <c r="AA145" s="122"/>
+      <c r="AA145" s="121"/>
     </row>
     <row r="146" spans="1:28" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
@@ -18503,7 +18503,7 @@
       <c r="G146" t="s">
         <v>763</v>
       </c>
-      <c r="H146" s="123" t="s">
+      <c r="H146" s="122" t="s">
         <v>764</v>
       </c>
       <c r="I146" t="s">
@@ -18548,10 +18548,10 @@
       <c r="Z146" t="s">
         <v>773</v>
       </c>
-      <c r="AA146" s="122" t="s">
+      <c r="AA146" s="121" t="s">
         <v>765</v>
       </c>
-      <c r="AB146" s="122" t="s">
+      <c r="AB146" s="121" t="s">
         <v>753</v>
       </c>
     </row>
@@ -18577,7 +18577,7 @@
       <c r="G147" t="s">
         <v>763</v>
       </c>
-      <c r="H147" s="123"/>
+      <c r="H147" s="122"/>
       <c r="I147" t="s">
         <v>761</v>
       </c>
@@ -18620,8 +18620,8 @@
       <c r="Z147" t="s">
         <v>773</v>
       </c>
-      <c r="AA147" s="122"/>
-      <c r="AB147" s="122"/>
+      <c r="AA147" s="121"/>
+      <c r="AB147" s="121"/>
     </row>
     <row r="148" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
@@ -18645,7 +18645,7 @@
       <c r="G148" t="s">
         <v>763</v>
       </c>
-      <c r="H148" s="123"/>
+      <c r="H148" s="122"/>
       <c r="I148" t="s">
         <v>761</v>
       </c>
@@ -18688,8 +18688,8 @@
       <c r="Z148" t="s">
         <v>773</v>
       </c>
-      <c r="AA148" s="122"/>
-      <c r="AB148" s="122"/>
+      <c r="AA148" s="121"/>
+      <c r="AB148" s="121"/>
     </row>
     <row r="149" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
@@ -18713,7 +18713,7 @@
       <c r="G149" t="s">
         <v>763</v>
       </c>
-      <c r="H149" s="123"/>
+      <c r="H149" s="122"/>
       <c r="I149" t="s">
         <v>761</v>
       </c>
@@ -18756,8 +18756,8 @@
       <c r="Z149" t="s">
         <v>773</v>
       </c>
-      <c r="AA149" s="122"/>
-      <c r="AB149" s="122"/>
+      <c r="AA149" s="121"/>
+      <c r="AB149" s="121"/>
     </row>
     <row r="150" spans="1:28" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
@@ -18781,7 +18781,7 @@
       <c r="G150" t="s">
         <v>776</v>
       </c>
-      <c r="H150" s="123" t="s">
+      <c r="H150" s="122" t="s">
         <v>89</v>
       </c>
       <c r="I150" t="s">
@@ -18838,7 +18838,7 @@
       <c r="Z150" t="s">
         <v>794</v>
       </c>
-      <c r="AA150" s="122" t="s">
+      <c r="AA150" s="121" t="s">
         <v>786</v>
       </c>
     </row>
@@ -18864,7 +18864,7 @@
       <c r="G151" t="s">
         <v>776</v>
       </c>
-      <c r="H151" s="123"/>
+      <c r="H151" s="122"/>
       <c r="I151" t="s">
         <v>781</v>
       </c>
@@ -18919,7 +18919,7 @@
       <c r="Z151" t="s">
         <v>794</v>
       </c>
-      <c r="AA151" s="122"/>
+      <c r="AA151" s="121"/>
     </row>
     <row r="152" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
@@ -18943,7 +18943,7 @@
       <c r="G152" t="s">
         <v>776</v>
       </c>
-      <c r="H152" s="123"/>
+      <c r="H152" s="122"/>
       <c r="I152" t="s">
         <v>781</v>
       </c>
@@ -18998,7 +18998,7 @@
       <c r="Z152" t="s">
         <v>794</v>
       </c>
-      <c r="AA152" s="122"/>
+      <c r="AA152" s="121"/>
     </row>
     <row r="153" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
@@ -19022,7 +19022,7 @@
       <c r="G153" t="s">
         <v>776</v>
       </c>
-      <c r="H153" s="123"/>
+      <c r="H153" s="122"/>
       <c r="I153" t="s">
         <v>781</v>
       </c>
@@ -19077,7 +19077,7 @@
       <c r="Z153" t="s">
         <v>794</v>
       </c>
-      <c r="AA153" s="122"/>
+      <c r="AA153" s="121"/>
     </row>
     <row r="154" spans="1:28" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
@@ -19101,7 +19101,7 @@
       <c r="G154" t="s">
         <v>803</v>
       </c>
-      <c r="H154" s="123" t="s">
+      <c r="H154" s="122" t="s">
         <v>804</v>
       </c>
       <c r="I154" t="s">
@@ -19158,7 +19158,7 @@
       <c r="Z154" t="s">
         <v>813</v>
       </c>
-      <c r="AA154" s="122" t="s">
+      <c r="AA154" s="121" t="s">
         <v>814</v>
       </c>
     </row>
@@ -19184,7 +19184,7 @@
       <c r="G155" t="s">
         <v>803</v>
       </c>
-      <c r="H155" s="123"/>
+      <c r="H155" s="122"/>
       <c r="I155" t="s">
         <v>805</v>
       </c>
@@ -19239,7 +19239,7 @@
       <c r="Z155" t="s">
         <v>813</v>
       </c>
-      <c r="AA155" s="122"/>
+      <c r="AA155" s="121"/>
     </row>
     <row r="156" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
@@ -19263,7 +19263,7 @@
       <c r="G156" t="s">
         <v>803</v>
       </c>
-      <c r="H156" s="123"/>
+      <c r="H156" s="122"/>
       <c r="I156" t="s">
         <v>805</v>
       </c>
@@ -19318,7 +19318,7 @@
       <c r="Z156" t="s">
         <v>813</v>
       </c>
-      <c r="AA156" s="122"/>
+      <c r="AA156" s="121"/>
     </row>
     <row r="157" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
@@ -19342,7 +19342,7 @@
       <c r="G157" t="s">
         <v>803</v>
       </c>
-      <c r="H157" s="123"/>
+      <c r="H157" s="122"/>
       <c r="I157" t="s">
         <v>805</v>
       </c>
@@ -19397,7 +19397,7 @@
       <c r="Z157" t="s">
         <v>813</v>
       </c>
-      <c r="AA157" s="122"/>
+      <c r="AA157" s="121"/>
     </row>
     <row r="158" spans="1:28" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
@@ -19421,7 +19421,7 @@
       <c r="G158" t="s">
         <v>818</v>
       </c>
-      <c r="H158" s="123" t="s">
+      <c r="H158" s="122" t="s">
         <v>825</v>
       </c>
       <c r="I158" t="s">
@@ -19478,7 +19478,7 @@
       <c r="Z158" t="s">
         <v>813</v>
       </c>
-      <c r="AA158" s="122" t="s">
+      <c r="AA158" s="121" t="s">
         <v>832</v>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       <c r="G159" t="s">
         <v>818</v>
       </c>
-      <c r="H159" s="123"/>
+      <c r="H159" s="122"/>
       <c r="I159" t="s">
         <v>824</v>
       </c>
@@ -19559,7 +19559,7 @@
       <c r="Z159" t="s">
         <v>813</v>
       </c>
-      <c r="AA159" s="122"/>
+      <c r="AA159" s="121"/>
     </row>
     <row r="160" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
@@ -19583,7 +19583,7 @@
       <c r="G160" t="s">
         <v>818</v>
       </c>
-      <c r="H160" s="123"/>
+      <c r="H160" s="122"/>
       <c r="I160" t="s">
         <v>824</v>
       </c>
@@ -19638,7 +19638,7 @@
       <c r="Z160" t="s">
         <v>813</v>
       </c>
-      <c r="AA160" s="122"/>
+      <c r="AA160" s="121"/>
     </row>
     <row r="161" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
@@ -19662,7 +19662,7 @@
       <c r="G161" t="s">
         <v>818</v>
       </c>
-      <c r="H161" s="123"/>
+      <c r="H161" s="122"/>
       <c r="I161" t="s">
         <v>824</v>
       </c>
@@ -19717,10 +19717,86 @@
       <c r="Z161" t="s">
         <v>813</v>
       </c>
-      <c r="AA161" s="122"/>
+      <c r="AA161" s="121"/>
     </row>
   </sheetData>
   <mergeCells count="92">
+    <mergeCell ref="AB130:AB133"/>
+    <mergeCell ref="AB146:AB149"/>
+    <mergeCell ref="H154:H157"/>
+    <mergeCell ref="AA154:AA157"/>
+    <mergeCell ref="H158:H161"/>
+    <mergeCell ref="AA158:AA161"/>
+    <mergeCell ref="H142:H145"/>
+    <mergeCell ref="AA142:AA145"/>
+    <mergeCell ref="H146:H149"/>
+    <mergeCell ref="AA146:AA149"/>
+    <mergeCell ref="H150:H153"/>
+    <mergeCell ref="AA150:AA153"/>
+    <mergeCell ref="H130:H133"/>
+    <mergeCell ref="AA130:AA133"/>
+    <mergeCell ref="H134:H137"/>
+    <mergeCell ref="AA134:AA137"/>
+    <mergeCell ref="L90:L93"/>
+    <mergeCell ref="AB18:AB21"/>
+    <mergeCell ref="AB26:AB29"/>
+    <mergeCell ref="AB30:AB33"/>
+    <mergeCell ref="AB54:AB57"/>
+    <mergeCell ref="AB62:AB65"/>
+    <mergeCell ref="AA26:AA29"/>
+    <mergeCell ref="AA46:AA49"/>
+    <mergeCell ref="H138:H141"/>
+    <mergeCell ref="AA138:AA141"/>
+    <mergeCell ref="H22:H25"/>
+    <mergeCell ref="AA22:AA25"/>
+    <mergeCell ref="H26:H29"/>
+    <mergeCell ref="H118:H121"/>
+    <mergeCell ref="AA118:AA121"/>
+    <mergeCell ref="H90:H93"/>
+    <mergeCell ref="AA90:AA93"/>
+    <mergeCell ref="H106:H109"/>
+    <mergeCell ref="AA106:AA109"/>
+    <mergeCell ref="H110:H113"/>
+    <mergeCell ref="AA110:AA113"/>
+    <mergeCell ref="H114:H117"/>
+    <mergeCell ref="AA114:AA117"/>
+    <mergeCell ref="H94:H97"/>
+    <mergeCell ref="AA94:AA97"/>
+    <mergeCell ref="H98:H101"/>
+    <mergeCell ref="H14:H17"/>
+    <mergeCell ref="L14:L17"/>
+    <mergeCell ref="AA14:AA17"/>
+    <mergeCell ref="H18:H21"/>
+    <mergeCell ref="AA18:AA21"/>
+    <mergeCell ref="H30:H33"/>
+    <mergeCell ref="AA30:AA33"/>
+    <mergeCell ref="H34:H37"/>
+    <mergeCell ref="AA34:AA37"/>
+    <mergeCell ref="H38:H41"/>
+    <mergeCell ref="AA38:AA41"/>
+    <mergeCell ref="H42:H45"/>
+    <mergeCell ref="AA42:AA45"/>
+    <mergeCell ref="H46:H49"/>
+    <mergeCell ref="H2:H5"/>
+    <mergeCell ref="AA2:AA5"/>
+    <mergeCell ref="H6:H9"/>
+    <mergeCell ref="AA6:AA9"/>
+    <mergeCell ref="H10:H13"/>
+    <mergeCell ref="AA10:AA13"/>
+    <mergeCell ref="H50:H53"/>
+    <mergeCell ref="AA50:AA53"/>
+    <mergeCell ref="H54:H57"/>
+    <mergeCell ref="AA54:AA57"/>
+    <mergeCell ref="H58:H61"/>
+    <mergeCell ref="AA58:AA61"/>
+    <mergeCell ref="H82:H85"/>
+    <mergeCell ref="AA82:AA85"/>
+    <mergeCell ref="H70:H73"/>
+    <mergeCell ref="AA70:AA73"/>
+    <mergeCell ref="H74:H77"/>
+    <mergeCell ref="AA74:AA77"/>
+    <mergeCell ref="H78:H81"/>
+    <mergeCell ref="AA78:AA81"/>
     <mergeCell ref="AB6:AB9"/>
     <mergeCell ref="AB10:AB13"/>
     <mergeCell ref="H126:H129"/>
@@ -19737,82 +19813,6 @@
     <mergeCell ref="AA62:AA65"/>
     <mergeCell ref="H66:H69"/>
     <mergeCell ref="AA66:AA69"/>
-    <mergeCell ref="H82:H85"/>
-    <mergeCell ref="AA82:AA85"/>
-    <mergeCell ref="H70:H73"/>
-    <mergeCell ref="AA70:AA73"/>
-    <mergeCell ref="H74:H77"/>
-    <mergeCell ref="AA74:AA77"/>
-    <mergeCell ref="H78:H81"/>
-    <mergeCell ref="AA78:AA81"/>
-    <mergeCell ref="H50:H53"/>
-    <mergeCell ref="AA50:AA53"/>
-    <mergeCell ref="H54:H57"/>
-    <mergeCell ref="AA54:AA57"/>
-    <mergeCell ref="H58:H61"/>
-    <mergeCell ref="AA58:AA61"/>
-    <mergeCell ref="H2:H5"/>
-    <mergeCell ref="AA2:AA5"/>
-    <mergeCell ref="H6:H9"/>
-    <mergeCell ref="AA6:AA9"/>
-    <mergeCell ref="H10:H13"/>
-    <mergeCell ref="AA10:AA13"/>
-    <mergeCell ref="AA94:AA97"/>
-    <mergeCell ref="H98:H101"/>
-    <mergeCell ref="H14:H17"/>
-    <mergeCell ref="L14:L17"/>
-    <mergeCell ref="AA14:AA17"/>
-    <mergeCell ref="H18:H21"/>
-    <mergeCell ref="AA18:AA21"/>
-    <mergeCell ref="H30:H33"/>
-    <mergeCell ref="AA30:AA33"/>
-    <mergeCell ref="H34:H37"/>
-    <mergeCell ref="AA34:AA37"/>
-    <mergeCell ref="H38:H41"/>
-    <mergeCell ref="AA38:AA41"/>
-    <mergeCell ref="H42:H45"/>
-    <mergeCell ref="AA42:AA45"/>
-    <mergeCell ref="H46:H49"/>
-    <mergeCell ref="H138:H141"/>
-    <mergeCell ref="AA138:AA141"/>
-    <mergeCell ref="H22:H25"/>
-    <mergeCell ref="AA22:AA25"/>
-    <mergeCell ref="H26:H29"/>
-    <mergeCell ref="H118:H121"/>
-    <mergeCell ref="AA118:AA121"/>
-    <mergeCell ref="H90:H93"/>
-    <mergeCell ref="AA90:AA93"/>
-    <mergeCell ref="H106:H109"/>
-    <mergeCell ref="AA106:AA109"/>
-    <mergeCell ref="H110:H113"/>
-    <mergeCell ref="AA110:AA113"/>
-    <mergeCell ref="H114:H117"/>
-    <mergeCell ref="AA114:AA117"/>
-    <mergeCell ref="H94:H97"/>
-    <mergeCell ref="L90:L93"/>
-    <mergeCell ref="AB18:AB21"/>
-    <mergeCell ref="AB26:AB29"/>
-    <mergeCell ref="AB30:AB33"/>
-    <mergeCell ref="AB54:AB57"/>
-    <mergeCell ref="AB62:AB65"/>
-    <mergeCell ref="AA26:AA29"/>
-    <mergeCell ref="AA46:AA49"/>
-    <mergeCell ref="AB130:AB133"/>
-    <mergeCell ref="AB146:AB149"/>
-    <mergeCell ref="H154:H157"/>
-    <mergeCell ref="AA154:AA157"/>
-    <mergeCell ref="H158:H161"/>
-    <mergeCell ref="AA158:AA161"/>
-    <mergeCell ref="H142:H145"/>
-    <mergeCell ref="AA142:AA145"/>
-    <mergeCell ref="H146:H149"/>
-    <mergeCell ref="AA146:AA149"/>
-    <mergeCell ref="H150:H153"/>
-    <mergeCell ref="AA150:AA153"/>
-    <mergeCell ref="H130:H133"/>
-    <mergeCell ref="AA130:AA133"/>
-    <mergeCell ref="H134:H137"/>
-    <mergeCell ref="AA134:AA137"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -19892,21 +19892,21 @@
         <v>1408</v>
       </c>
       <c r="R1" s="83"/>
-      <c r="S1" s="137" t="s">
+      <c r="S1" s="146" t="s">
         <v>1420</v>
       </c>
-      <c r="T1" s="138"/>
-      <c r="U1" s="138"/>
-      <c r="V1" s="138"/>
-      <c r="W1" s="139"/>
+      <c r="T1" s="147"/>
+      <c r="U1" s="147"/>
+      <c r="V1" s="147"/>
+      <c r="W1" s="148"/>
       <c r="X1" s="36"/>
-      <c r="Y1" s="125" t="s">
+      <c r="Y1" s="134" t="s">
         <v>1421</v>
       </c>
-      <c r="Z1" s="126"/>
-      <c r="AA1" s="126"/>
-      <c r="AB1" s="126"/>
-      <c r="AC1" s="127"/>
+      <c r="Z1" s="135"/>
+      <c r="AA1" s="135"/>
+      <c r="AB1" s="135"/>
+      <c r="AC1" s="136"/>
     </row>
     <row r="2" spans="1:30" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
@@ -19952,12 +19952,12 @@
       <c r="W2" s="154"/>
       <c r="X2" s="83"/>
       <c r="Y2" s="50"/>
-      <c r="Z2" s="128" t="s">
+      <c r="Z2" s="137" t="s">
         <v>1393</v>
       </c>
-      <c r="AA2" s="129"/>
-      <c r="AB2" s="129"/>
-      <c r="AC2" s="130"/>
+      <c r="AA2" s="138"/>
+      <c r="AB2" s="138"/>
+      <c r="AC2" s="139"/>
     </row>
     <row r="3" spans="1:30" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
@@ -19982,7 +19982,7 @@
       <c r="J3" s="105"/>
       <c r="K3" s="105"/>
       <c r="L3" s="105"/>
-      <c r="M3" s="132"/>
+      <c r="M3" s="141"/>
       <c r="N3" s="86"/>
       <c r="O3" s="89" t="s">
         <v>1416</v>
@@ -20052,7 +20052,7 @@
       <c r="J4" s="49"/>
       <c r="K4" s="49"/>
       <c r="L4" s="49"/>
-      <c r="M4" s="132"/>
+      <c r="M4" s="141"/>
       <c r="N4" s="106"/>
       <c r="O4" s="60"/>
       <c r="P4" s="15"/>
@@ -20115,7 +20115,7 @@
       <c r="J5" s="49"/>
       <c r="K5" s="49"/>
       <c r="L5" s="49"/>
-      <c r="M5" s="132"/>
+      <c r="M5" s="141"/>
       <c r="N5" s="79"/>
       <c r="O5" s="15"/>
       <c r="P5" s="15"/>
@@ -20177,7 +20177,7 @@
       <c r="J6" s="49"/>
       <c r="K6" s="49"/>
       <c r="L6" s="49"/>
-      <c r="M6" s="132"/>
+      <c r="M6" s="141"/>
       <c r="N6" s="79"/>
       <c r="R6" s="58"/>
       <c r="S6" s="68" t="s">
@@ -20237,7 +20237,7 @@
       <c r="J7" s="49"/>
       <c r="K7" s="49"/>
       <c r="L7" s="49"/>
-      <c r="M7" s="132"/>
+      <c r="M7" s="141"/>
       <c r="N7" s="79"/>
       <c r="R7" s="15"/>
       <c r="S7" s="68" t="s">
@@ -20298,7 +20298,7 @@
       <c r="J8" s="49"/>
       <c r="K8" s="49"/>
       <c r="L8" s="49"/>
-      <c r="M8" s="132"/>
+      <c r="M8" s="141"/>
       <c r="N8" s="79"/>
       <c r="S8" s="60"/>
       <c r="T8" s="60"/>
@@ -20334,7 +20334,7 @@
       <c r="J9" s="50"/>
       <c r="K9" s="50"/>
       <c r="L9" s="50"/>
-      <c r="M9" s="133"/>
+      <c r="M9" s="142"/>
       <c r="N9" s="79"/>
       <c r="S9" s="15"/>
       <c r="T9" s="15"/>
@@ -20367,7 +20367,7 @@
       <c r="J10" s="49"/>
       <c r="K10" s="49"/>
       <c r="L10" s="49"/>
-      <c r="M10" s="131"/>
+      <c r="M10" s="140"/>
       <c r="N10" s="79"/>
       <c r="S10" s="15"/>
       <c r="T10" s="15"/>
@@ -20400,7 +20400,7 @@
       <c r="J11" s="49"/>
       <c r="K11" s="49"/>
       <c r="L11" s="49"/>
-      <c r="M11" s="132"/>
+      <c r="M11" s="141"/>
       <c r="N11" s="79"/>
       <c r="S11" s="15"/>
       <c r="T11" s="15"/>
@@ -20433,7 +20433,7 @@
       <c r="J12" s="49"/>
       <c r="K12" s="49"/>
       <c r="L12" s="49"/>
-      <c r="M12" s="132"/>
+      <c r="M12" s="141"/>
       <c r="N12" s="79"/>
       <c r="S12" s="15"/>
       <c r="T12" s="15"/>
@@ -20466,7 +20466,7 @@
       <c r="J13" s="49"/>
       <c r="K13" s="49"/>
       <c r="L13" s="49"/>
-      <c r="M13" s="132"/>
+      <c r="M13" s="141"/>
       <c r="N13" s="79"/>
       <c r="S13" s="15"/>
       <c r="T13" s="15"/>
@@ -20499,7 +20499,7 @@
       <c r="J14" s="49"/>
       <c r="K14" s="49"/>
       <c r="L14" s="49"/>
-      <c r="M14" s="132"/>
+      <c r="M14" s="141"/>
       <c r="N14" s="79"/>
       <c r="S14" s="15"/>
       <c r="T14" s="15"/>
@@ -20532,7 +20532,7 @@
       <c r="J15" s="49"/>
       <c r="K15" s="49"/>
       <c r="L15" s="49"/>
-      <c r="M15" s="133"/>
+      <c r="M15" s="142"/>
       <c r="N15" s="79"/>
       <c r="S15" s="15"/>
       <c r="T15" s="15"/>
@@ -20561,7 +20561,7 @@
       <c r="J16" s="51"/>
       <c r="K16" s="51"/>
       <c r="L16" s="51"/>
-      <c r="M16" s="140" t="s">
+      <c r="M16" s="149" t="s">
         <v>1426</v>
       </c>
       <c r="N16" s="80"/>
@@ -20593,7 +20593,7 @@
       <c r="J17" s="49"/>
       <c r="K17" s="49"/>
       <c r="L17" s="49"/>
-      <c r="M17" s="141"/>
+      <c r="M17" s="150"/>
       <c r="N17" s="80"/>
       <c r="R17" s="15"/>
       <c r="S17" s="45"/>
@@ -20623,7 +20623,7 @@
       <c r="J18" s="49"/>
       <c r="K18" s="49"/>
       <c r="L18" s="49"/>
-      <c r="M18" s="141"/>
+      <c r="M18" s="150"/>
       <c r="N18" s="80"/>
       <c r="S18" s="107"/>
       <c r="T18" s="107"/>
@@ -20653,7 +20653,7 @@
       <c r="J19" s="49"/>
       <c r="K19" s="49"/>
       <c r="L19" s="49"/>
-      <c r="M19" s="141"/>
+      <c r="M19" s="150"/>
       <c r="N19" s="80"/>
       <c r="S19" s="108"/>
       <c r="T19" s="101"/>
@@ -20683,7 +20683,7 @@
       <c r="J20" s="49"/>
       <c r="K20" s="49"/>
       <c r="L20" s="49"/>
-      <c r="M20" s="141"/>
+      <c r="M20" s="150"/>
       <c r="N20" s="80"/>
       <c r="S20" s="108"/>
       <c r="T20" s="101"/>
@@ -20712,7 +20712,7 @@
       <c r="J21" s="49"/>
       <c r="K21" s="49"/>
       <c r="L21" s="49"/>
-      <c r="M21" s="141"/>
+      <c r="M21" s="150"/>
       <c r="N21" s="80"/>
       <c r="S21" s="108"/>
       <c r="T21" s="101"/>
@@ -20741,7 +20741,7 @@
       <c r="J22" s="118"/>
       <c r="K22" s="118"/>
       <c r="L22" s="118"/>
-      <c r="M22" s="134" t="s">
+      <c r="M22" s="143" t="s">
         <v>1425</v>
       </c>
       <c r="N22" s="80"/>
@@ -20772,7 +20772,7 @@
       <c r="J23" s="119"/>
       <c r="K23" s="119"/>
       <c r="L23" s="119"/>
-      <c r="M23" s="135"/>
+      <c r="M23" s="144"/>
       <c r="N23" s="80"/>
       <c r="S23" s="108"/>
       <c r="T23" s="101"/>
@@ -20801,7 +20801,7 @@
       <c r="J24" s="119"/>
       <c r="K24" s="119"/>
       <c r="L24" s="119"/>
-      <c r="M24" s="135"/>
+      <c r="M24" s="144"/>
       <c r="N24" s="80"/>
       <c r="S24" s="108"/>
       <c r="T24" s="101"/>
@@ -20830,7 +20830,7 @@
       <c r="J25" s="119"/>
       <c r="K25" s="119"/>
       <c r="L25" s="119"/>
-      <c r="M25" s="135"/>
+      <c r="M25" s="144"/>
       <c r="N25" s="80"/>
       <c r="S25" s="108"/>
       <c r="T25" s="101"/>
@@ -20859,7 +20859,7 @@
       <c r="J26" s="119"/>
       <c r="K26" s="119"/>
       <c r="L26" s="119"/>
-      <c r="M26" s="135"/>
+      <c r="M26" s="144"/>
       <c r="N26" s="80"/>
       <c r="S26" s="108"/>
       <c r="T26" s="101"/>
@@ -20888,7 +20888,7 @@
       <c r="J27" s="120"/>
       <c r="K27" s="120"/>
       <c r="L27" s="120"/>
-      <c r="M27" s="136"/>
+      <c r="M27" s="145"/>
       <c r="N27" s="80"/>
       <c r="S27" s="108"/>
       <c r="T27" s="101"/>
@@ -20949,7 +20949,7 @@
       <c r="J29" s="51"/>
       <c r="K29" s="51"/>
       <c r="L29" s="51"/>
-      <c r="M29" s="142" t="s">
+      <c r="M29" s="125" t="s">
         <v>1300</v>
       </c>
       <c r="N29" s="82"/>
@@ -20981,7 +20981,7 @@
       <c r="J30" s="49"/>
       <c r="K30" s="49"/>
       <c r="L30" s="49"/>
-      <c r="M30" s="143"/>
+      <c r="M30" s="126"/>
       <c r="N30" s="82"/>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.3">
@@ -21007,7 +21007,7 @@
       <c r="J31" s="49"/>
       <c r="K31" s="49"/>
       <c r="L31" s="49"/>
-      <c r="M31" s="143"/>
+      <c r="M31" s="126"/>
       <c r="N31" s="82"/>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.3">
@@ -21033,7 +21033,7 @@
       <c r="J32" s="49"/>
       <c r="K32" s="49"/>
       <c r="L32" s="49"/>
-      <c r="M32" s="143"/>
+      <c r="M32" s="126"/>
       <c r="N32" s="82"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
@@ -21059,7 +21059,7 @@
       <c r="J33" s="49"/>
       <c r="K33" s="49"/>
       <c r="L33" s="49"/>
-      <c r="M33" s="143"/>
+      <c r="M33" s="126"/>
       <c r="N33" s="82"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
@@ -21085,7 +21085,7 @@
       <c r="J34" s="49"/>
       <c r="K34" s="49"/>
       <c r="L34" s="49"/>
-      <c r="M34" s="143"/>
+      <c r="M34" s="126"/>
       <c r="N34" s="82"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
@@ -21111,7 +21111,7 @@
       <c r="J35" s="49"/>
       <c r="K35" s="49"/>
       <c r="L35" s="49"/>
-      <c r="M35" s="143"/>
+      <c r="M35" s="126"/>
       <c r="N35" s="82"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
@@ -21137,7 +21137,7 @@
       <c r="J36" s="49"/>
       <c r="K36" s="49"/>
       <c r="L36" s="49"/>
-      <c r="M36" s="143"/>
+      <c r="M36" s="126"/>
       <c r="N36" s="82"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
@@ -21163,7 +21163,7 @@
       <c r="J37" s="49"/>
       <c r="K37" s="49"/>
       <c r="L37" s="49"/>
-      <c r="M37" s="143"/>
+      <c r="M37" s="126"/>
       <c r="N37" s="82"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
@@ -21189,7 +21189,7 @@
       <c r="J38" s="49"/>
       <c r="K38" s="49"/>
       <c r="L38" s="49"/>
-      <c r="M38" s="143"/>
+      <c r="M38" s="126"/>
       <c r="N38" s="82"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
@@ -21215,7 +21215,7 @@
       <c r="J39" s="49"/>
       <c r="K39" s="49"/>
       <c r="L39" s="49"/>
-      <c r="M39" s="143"/>
+      <c r="M39" s="126"/>
       <c r="N39" s="82"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
@@ -21241,7 +21241,7 @@
       <c r="J40" s="49"/>
       <c r="K40" s="49"/>
       <c r="L40" s="49"/>
-      <c r="M40" s="143"/>
+      <c r="M40" s="126"/>
       <c r="N40" s="82"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
@@ -21267,7 +21267,7 @@
       <c r="J41" s="49"/>
       <c r="K41" s="49"/>
       <c r="L41" s="49"/>
-      <c r="M41" s="143"/>
+      <c r="M41" s="126"/>
       <c r="N41" s="82"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
@@ -21293,7 +21293,7 @@
       <c r="J42" s="49"/>
       <c r="K42" s="49"/>
       <c r="L42" s="49"/>
-      <c r="M42" s="143"/>
+      <c r="M42" s="126"/>
       <c r="N42" s="82"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
@@ -21319,7 +21319,7 @@
       <c r="J43" s="49"/>
       <c r="K43" s="49"/>
       <c r="L43" s="49"/>
-      <c r="M43" s="143"/>
+      <c r="M43" s="126"/>
       <c r="N43" s="82"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
@@ -21345,7 +21345,7 @@
       <c r="J44" s="49"/>
       <c r="K44" s="49"/>
       <c r="L44" s="49"/>
-      <c r="M44" s="143"/>
+      <c r="M44" s="126"/>
       <c r="N44" s="82"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
@@ -21371,7 +21371,7 @@
       <c r="J45" s="49"/>
       <c r="K45" s="49"/>
       <c r="L45" s="49"/>
-      <c r="M45" s="143"/>
+      <c r="M45" s="126"/>
       <c r="N45" s="82"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
@@ -21397,7 +21397,7 @@
       <c r="J46" s="49"/>
       <c r="K46" s="49"/>
       <c r="L46" s="49"/>
-      <c r="M46" s="143"/>
+      <c r="M46" s="126"/>
       <c r="N46" s="82"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
@@ -21423,7 +21423,7 @@
       <c r="J47" s="49"/>
       <c r="K47" s="49"/>
       <c r="L47" s="49"/>
-      <c r="M47" s="143"/>
+      <c r="M47" s="126"/>
       <c r="N47" s="82"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
@@ -21449,7 +21449,7 @@
       <c r="J48" s="49"/>
       <c r="K48" s="49"/>
       <c r="L48" s="49"/>
-      <c r="M48" s="143"/>
+      <c r="M48" s="126"/>
       <c r="N48" s="82"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
@@ -21475,7 +21475,7 @@
       <c r="J49" s="49"/>
       <c r="K49" s="49"/>
       <c r="L49" s="49"/>
-      <c r="M49" s="143"/>
+      <c r="M49" s="126"/>
       <c r="N49" s="82"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
@@ -21501,7 +21501,7 @@
       <c r="J50" s="49"/>
       <c r="K50" s="49"/>
       <c r="L50" s="49"/>
-      <c r="M50" s="143"/>
+      <c r="M50" s="126"/>
       <c r="N50" s="82"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
@@ -21527,7 +21527,7 @@
       <c r="J51" s="49"/>
       <c r="K51" s="49"/>
       <c r="L51" s="49"/>
-      <c r="M51" s="143"/>
+      <c r="M51" s="126"/>
       <c r="N51" s="82"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
@@ -21553,7 +21553,7 @@
       <c r="J52" s="49"/>
       <c r="K52" s="49"/>
       <c r="L52" s="49"/>
-      <c r="M52" s="143"/>
+      <c r="M52" s="126"/>
       <c r="N52" s="82"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
@@ -21579,7 +21579,7 @@
       <c r="J53" s="49"/>
       <c r="K53" s="49"/>
       <c r="L53" s="49"/>
-      <c r="M53" s="143"/>
+      <c r="M53" s="126"/>
       <c r="N53" s="82"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
@@ -21605,7 +21605,7 @@
       <c r="J54" s="49"/>
       <c r="K54" s="49"/>
       <c r="L54" s="49"/>
-      <c r="M54" s="143"/>
+      <c r="M54" s="126"/>
       <c r="N54" s="82"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
@@ -21631,7 +21631,7 @@
       <c r="J55" s="49"/>
       <c r="K55" s="49"/>
       <c r="L55" s="49"/>
-      <c r="M55" s="143"/>
+      <c r="M55" s="126"/>
       <c r="N55" s="82"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
@@ -21657,7 +21657,7 @@
       <c r="J56" s="49"/>
       <c r="K56" s="49"/>
       <c r="L56" s="49"/>
-      <c r="M56" s="143"/>
+      <c r="M56" s="126"/>
       <c r="N56" s="82"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
@@ -21683,7 +21683,7 @@
       <c r="J57" s="49"/>
       <c r="K57" s="49"/>
       <c r="L57" s="49"/>
-      <c r="M57" s="143"/>
+      <c r="M57" s="126"/>
       <c r="N57" s="82"/>
     </row>
     <row r="58" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -21709,7 +21709,7 @@
       <c r="J58" s="49"/>
       <c r="K58" s="49"/>
       <c r="L58" s="49"/>
-      <c r="M58" s="143"/>
+      <c r="M58" s="126"/>
       <c r="N58" s="82"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
@@ -21735,7 +21735,7 @@
       <c r="J59" s="49"/>
       <c r="K59" s="49"/>
       <c r="L59" s="49"/>
-      <c r="M59" s="143"/>
+      <c r="M59" s="126"/>
       <c r="N59" s="82"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
@@ -21761,7 +21761,7 @@
       <c r="J60" s="49"/>
       <c r="K60" s="49"/>
       <c r="L60" s="49"/>
-      <c r="M60" s="143"/>
+      <c r="M60" s="126"/>
       <c r="N60" s="82"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
@@ -21787,7 +21787,7 @@
       <c r="J61" s="49"/>
       <c r="K61" s="49"/>
       <c r="L61" s="49"/>
-      <c r="M61" s="143"/>
+      <c r="M61" s="126"/>
       <c r="N61" s="82"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
@@ -21813,7 +21813,7 @@
       <c r="J62" s="49"/>
       <c r="K62" s="49"/>
       <c r="L62" s="49"/>
-      <c r="M62" s="143"/>
+      <c r="M62" s="126"/>
       <c r="N62" s="82"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
@@ -21839,7 +21839,7 @@
       <c r="J63" s="49"/>
       <c r="K63" s="49"/>
       <c r="L63" s="49"/>
-      <c r="M63" s="143"/>
+      <c r="M63" s="126"/>
       <c r="N63" s="82"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
@@ -21865,7 +21865,7 @@
       <c r="J64" s="49"/>
       <c r="K64" s="49"/>
       <c r="L64" s="49"/>
-      <c r="M64" s="143"/>
+      <c r="M64" s="126"/>
       <c r="N64" s="82"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
@@ -21891,7 +21891,7 @@
       <c r="J65" s="49"/>
       <c r="K65" s="49"/>
       <c r="L65" s="49"/>
-      <c r="M65" s="143"/>
+      <c r="M65" s="126"/>
       <c r="N65" s="82"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
@@ -21917,7 +21917,7 @@
       <c r="J66" s="49"/>
       <c r="K66" s="49"/>
       <c r="L66" s="49"/>
-      <c r="M66" s="143"/>
+      <c r="M66" s="126"/>
       <c r="N66" s="82"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
@@ -21943,7 +21943,7 @@
       <c r="J67" s="49"/>
       <c r="K67" s="49"/>
       <c r="L67" s="49"/>
-      <c r="M67" s="143"/>
+      <c r="M67" s="126"/>
       <c r="N67" s="82"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
@@ -21969,7 +21969,7 @@
       <c r="J68" s="49"/>
       <c r="K68" s="49"/>
       <c r="L68" s="49"/>
-      <c r="M68" s="143"/>
+      <c r="M68" s="126"/>
       <c r="N68" s="82"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
@@ -21995,7 +21995,7 @@
       <c r="J69" s="49"/>
       <c r="K69" s="49"/>
       <c r="L69" s="49"/>
-      <c r="M69" s="143"/>
+      <c r="M69" s="126"/>
       <c r="N69" s="82"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
@@ -22021,7 +22021,7 @@
       <c r="J70" s="49"/>
       <c r="K70" s="49"/>
       <c r="L70" s="49"/>
-      <c r="M70" s="143"/>
+      <c r="M70" s="126"/>
       <c r="N70" s="82"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
@@ -22047,7 +22047,7 @@
       <c r="J71" s="49"/>
       <c r="K71" s="49"/>
       <c r="L71" s="49"/>
-      <c r="M71" s="143"/>
+      <c r="M71" s="126"/>
       <c r="N71" s="82"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
@@ -22073,7 +22073,7 @@
       <c r="J72" s="49"/>
       <c r="K72" s="49"/>
       <c r="L72" s="49"/>
-      <c r="M72" s="143"/>
+      <c r="M72" s="126"/>
       <c r="N72" s="82"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
@@ -22099,7 +22099,7 @@
       <c r="J73" s="49"/>
       <c r="K73" s="49"/>
       <c r="L73" s="49"/>
-      <c r="M73" s="143"/>
+      <c r="M73" s="126"/>
       <c r="N73" s="82"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
@@ -22125,7 +22125,7 @@
       <c r="J74" s="49"/>
       <c r="K74" s="49"/>
       <c r="L74" s="49"/>
-      <c r="M74" s="143"/>
+      <c r="M74" s="126"/>
       <c r="N74" s="82"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
@@ -22151,7 +22151,7 @@
       <c r="J75" s="49"/>
       <c r="K75" s="49"/>
       <c r="L75" s="49"/>
-      <c r="M75" s="143"/>
+      <c r="M75" s="126"/>
       <c r="N75" s="82"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
@@ -22177,7 +22177,7 @@
       <c r="J76" s="49"/>
       <c r="K76" s="49"/>
       <c r="L76" s="49"/>
-      <c r="M76" s="143"/>
+      <c r="M76" s="126"/>
       <c r="N76" s="82"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
@@ -22203,7 +22203,7 @@
       <c r="J77" s="49"/>
       <c r="K77" s="49"/>
       <c r="L77" s="49"/>
-      <c r="M77" s="143"/>
+      <c r="M77" s="126"/>
       <c r="N77" s="82"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
@@ -22229,7 +22229,7 @@
       <c r="J78" s="49"/>
       <c r="K78" s="49"/>
       <c r="L78" s="49"/>
-      <c r="M78" s="143"/>
+      <c r="M78" s="126"/>
       <c r="N78" s="82"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
@@ -22255,7 +22255,7 @@
       <c r="J79" s="49"/>
       <c r="K79" s="49"/>
       <c r="L79" s="49"/>
-      <c r="M79" s="143"/>
+      <c r="M79" s="126"/>
       <c r="N79" s="82"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
@@ -22281,7 +22281,7 @@
       <c r="J80" s="49"/>
       <c r="K80" s="49"/>
       <c r="L80" s="49"/>
-      <c r="M80" s="143"/>
+      <c r="M80" s="126"/>
       <c r="N80" s="82"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
@@ -22307,7 +22307,7 @@
       <c r="J81" s="49"/>
       <c r="K81" s="49"/>
       <c r="L81" s="49"/>
-      <c r="M81" s="143"/>
+      <c r="M81" s="126"/>
       <c r="N81" s="82"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
@@ -22333,7 +22333,7 @@
       <c r="J82" s="49"/>
       <c r="K82" s="49"/>
       <c r="L82" s="49"/>
-      <c r="M82" s="143"/>
+      <c r="M82" s="126"/>
       <c r="N82" s="82"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.3">
@@ -22359,7 +22359,7 @@
       <c r="J83" s="49"/>
       <c r="K83" s="49"/>
       <c r="L83" s="49"/>
-      <c r="M83" s="143"/>
+      <c r="M83" s="126"/>
       <c r="N83" s="82"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
@@ -22385,7 +22385,7 @@
       <c r="J84" s="49"/>
       <c r="K84" s="49"/>
       <c r="L84" s="49"/>
-      <c r="M84" s="143"/>
+      <c r="M84" s="126"/>
       <c r="N84" s="82"/>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">
@@ -22411,7 +22411,7 @@
       <c r="J85" s="49"/>
       <c r="K85" s="49"/>
       <c r="L85" s="49"/>
-      <c r="M85" s="143"/>
+      <c r="M85" s="126"/>
       <c r="N85" s="82"/>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.3">
@@ -22437,7 +22437,7 @@
       <c r="J86" s="49"/>
       <c r="K86" s="49"/>
       <c r="L86" s="49"/>
-      <c r="M86" s="143"/>
+      <c r="M86" s="126"/>
       <c r="N86" s="82"/>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.3">
@@ -22463,7 +22463,7 @@
       <c r="J87" s="49"/>
       <c r="K87" s="49"/>
       <c r="L87" s="49"/>
-      <c r="M87" s="143"/>
+      <c r="M87" s="126"/>
       <c r="N87" s="82"/>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.3">
@@ -22489,7 +22489,7 @@
       <c r="J88" s="49"/>
       <c r="K88" s="49"/>
       <c r="L88" s="49"/>
-      <c r="M88" s="143"/>
+      <c r="M88" s="126"/>
       <c r="N88" s="82"/>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.3">
@@ -22515,7 +22515,7 @@
       <c r="J89" s="49"/>
       <c r="K89" s="49"/>
       <c r="L89" s="49"/>
-      <c r="M89" s="143"/>
+      <c r="M89" s="126"/>
       <c r="N89" s="82"/>
     </row>
     <row r="90" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -22541,7 +22541,7 @@
       <c r="J90" s="49"/>
       <c r="K90" s="49"/>
       <c r="L90" s="49"/>
-      <c r="M90" s="143"/>
+      <c r="M90" s="126"/>
       <c r="N90" s="82"/>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.3">
@@ -22567,7 +22567,7 @@
       <c r="J91" s="49"/>
       <c r="K91" s="49"/>
       <c r="L91" s="49"/>
-      <c r="M91" s="143"/>
+      <c r="M91" s="126"/>
       <c r="N91" s="82"/>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.3">
@@ -22593,7 +22593,7 @@
       <c r="J92" s="49"/>
       <c r="K92" s="49"/>
       <c r="L92" s="49"/>
-      <c r="M92" s="143"/>
+      <c r="M92" s="126"/>
       <c r="N92" s="82"/>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.3">
@@ -22619,7 +22619,7 @@
       <c r="J93" s="49"/>
       <c r="K93" s="49"/>
       <c r="L93" s="49"/>
-      <c r="M93" s="143"/>
+      <c r="M93" s="126"/>
       <c r="N93" s="82"/>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.3">
@@ -22645,7 +22645,7 @@
       <c r="J94" s="49"/>
       <c r="K94" s="49"/>
       <c r="L94" s="49"/>
-      <c r="M94" s="143"/>
+      <c r="M94" s="126"/>
       <c r="N94" s="82"/>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.3">
@@ -22671,7 +22671,7 @@
       <c r="J95" s="49"/>
       <c r="K95" s="49"/>
       <c r="L95" s="49"/>
-      <c r="M95" s="143"/>
+      <c r="M95" s="126"/>
       <c r="N95" s="82"/>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.3">
@@ -22697,7 +22697,7 @@
       <c r="J96" s="49"/>
       <c r="K96" s="49"/>
       <c r="L96" s="49"/>
-      <c r="M96" s="143"/>
+      <c r="M96" s="126"/>
       <c r="N96" s="82"/>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.3">
@@ -22723,7 +22723,7 @@
       <c r="J97" s="49"/>
       <c r="K97" s="49"/>
       <c r="L97" s="49"/>
-      <c r="M97" s="143"/>
+      <c r="M97" s="126"/>
       <c r="N97" s="82"/>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.3">
@@ -22749,7 +22749,7 @@
       <c r="J98" s="49"/>
       <c r="K98" s="49"/>
       <c r="L98" s="49"/>
-      <c r="M98" s="143"/>
+      <c r="M98" s="126"/>
       <c r="N98" s="82"/>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.3">
@@ -22775,7 +22775,7 @@
       <c r="J99" s="49"/>
       <c r="K99" s="49"/>
       <c r="L99" s="49"/>
-      <c r="M99" s="143"/>
+      <c r="M99" s="126"/>
       <c r="N99" s="82"/>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.3">
@@ -22801,7 +22801,7 @@
       <c r="J100" s="49"/>
       <c r="K100" s="49"/>
       <c r="L100" s="49"/>
-      <c r="M100" s="143"/>
+      <c r="M100" s="126"/>
       <c r="N100" s="82"/>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.3">
@@ -22827,7 +22827,7 @@
       <c r="J101" s="49"/>
       <c r="K101" s="49"/>
       <c r="L101" s="49"/>
-      <c r="M101" s="143"/>
+      <c r="M101" s="126"/>
       <c r="N101" s="82"/>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.3">
@@ -22853,7 +22853,7 @@
       <c r="J102" s="49"/>
       <c r="K102" s="49"/>
       <c r="L102" s="49"/>
-      <c r="M102" s="143"/>
+      <c r="M102" s="126"/>
       <c r="N102" s="82"/>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.3">
@@ -22879,7 +22879,7 @@
       <c r="J103" s="49"/>
       <c r="K103" s="49"/>
       <c r="L103" s="49"/>
-      <c r="M103" s="143"/>
+      <c r="M103" s="126"/>
       <c r="N103" s="82"/>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.3">
@@ -22905,7 +22905,7 @@
       <c r="J104" s="49"/>
       <c r="K104" s="49"/>
       <c r="L104" s="49"/>
-      <c r="M104" s="143"/>
+      <c r="M104" s="126"/>
       <c r="N104" s="82"/>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.3">
@@ -22931,7 +22931,7 @@
       <c r="J105" s="49"/>
       <c r="K105" s="49"/>
       <c r="L105" s="49"/>
-      <c r="M105" s="143"/>
+      <c r="M105" s="126"/>
       <c r="N105" s="82"/>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.3">
@@ -22957,7 +22957,7 @@
       <c r="J106" s="49"/>
       <c r="K106" s="49"/>
       <c r="L106" s="49"/>
-      <c r="M106" s="143"/>
+      <c r="M106" s="126"/>
       <c r="N106" s="82"/>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.3">
@@ -22983,7 +22983,7 @@
       <c r="J107" s="49"/>
       <c r="K107" s="49"/>
       <c r="L107" s="49"/>
-      <c r="M107" s="143"/>
+      <c r="M107" s="126"/>
       <c r="N107" s="82"/>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.3">
@@ -23009,7 +23009,7 @@
       <c r="J108" s="49"/>
       <c r="K108" s="49"/>
       <c r="L108" s="49"/>
-      <c r="M108" s="143"/>
+      <c r="M108" s="126"/>
       <c r="N108" s="82"/>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.3">
@@ -23035,7 +23035,7 @@
       <c r="J109" s="49"/>
       <c r="K109" s="49"/>
       <c r="L109" s="49"/>
-      <c r="M109" s="143"/>
+      <c r="M109" s="126"/>
       <c r="N109" s="82"/>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.3">
@@ -23061,7 +23061,7 @@
       <c r="J110" s="49"/>
       <c r="K110" s="49"/>
       <c r="L110" s="49"/>
-      <c r="M110" s="143"/>
+      <c r="M110" s="126"/>
       <c r="N110" s="82"/>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.3">
@@ -23087,7 +23087,7 @@
       <c r="J111" s="49"/>
       <c r="K111" s="49"/>
       <c r="L111" s="49"/>
-      <c r="M111" s="143"/>
+      <c r="M111" s="126"/>
       <c r="N111" s="82"/>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.3">
@@ -23113,7 +23113,7 @@
       <c r="J112" s="49"/>
       <c r="K112" s="49"/>
       <c r="L112" s="49"/>
-      <c r="M112" s="143"/>
+      <c r="M112" s="126"/>
       <c r="N112" s="82"/>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.3">
@@ -23139,7 +23139,7 @@
       <c r="J113" s="49"/>
       <c r="K113" s="49"/>
       <c r="L113" s="49"/>
-      <c r="M113" s="143"/>
+      <c r="M113" s="126"/>
       <c r="N113" s="82"/>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.3">
@@ -23165,7 +23165,7 @@
       <c r="J114" s="49"/>
       <c r="K114" s="49"/>
       <c r="L114" s="49"/>
-      <c r="M114" s="143"/>
+      <c r="M114" s="126"/>
       <c r="N114" s="82"/>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.3">
@@ -23191,7 +23191,7 @@
       <c r="J115" s="49"/>
       <c r="K115" s="49"/>
       <c r="L115" s="49"/>
-      <c r="M115" s="143"/>
+      <c r="M115" s="126"/>
       <c r="N115" s="82"/>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.3">
@@ -23217,7 +23217,7 @@
       <c r="J116" s="49"/>
       <c r="K116" s="49"/>
       <c r="L116" s="49"/>
-      <c r="M116" s="143"/>
+      <c r="M116" s="126"/>
       <c r="N116" s="82"/>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.3">
@@ -23243,7 +23243,7 @@
       <c r="J117" s="49"/>
       <c r="K117" s="49"/>
       <c r="L117" s="49"/>
-      <c r="M117" s="143"/>
+      <c r="M117" s="126"/>
       <c r="N117" s="82"/>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.3">
@@ -23269,7 +23269,7 @@
       <c r="J118" s="49"/>
       <c r="K118" s="49"/>
       <c r="L118" s="49"/>
-      <c r="M118" s="143"/>
+      <c r="M118" s="126"/>
       <c r="N118" s="82"/>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.3">
@@ -23295,7 +23295,7 @@
       <c r="J119" s="49"/>
       <c r="K119" s="49"/>
       <c r="L119" s="49"/>
-      <c r="M119" s="143"/>
+      <c r="M119" s="126"/>
       <c r="N119" s="82"/>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.3">
@@ -23321,7 +23321,7 @@
       <c r="J120" s="49"/>
       <c r="K120" s="49"/>
       <c r="L120" s="49"/>
-      <c r="M120" s="143"/>
+      <c r="M120" s="126"/>
       <c r="N120" s="82"/>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.3">
@@ -23347,7 +23347,7 @@
       <c r="J121" s="49"/>
       <c r="K121" s="49"/>
       <c r="L121" s="49"/>
-      <c r="M121" s="143"/>
+      <c r="M121" s="126"/>
       <c r="N121" s="82"/>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.3">
@@ -23373,7 +23373,7 @@
       <c r="J122" s="49"/>
       <c r="K122" s="49"/>
       <c r="L122" s="49"/>
-      <c r="M122" s="143"/>
+      <c r="M122" s="126"/>
       <c r="N122" s="82"/>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.3">
@@ -23399,7 +23399,7 @@
       <c r="J123" s="49"/>
       <c r="K123" s="49"/>
       <c r="L123" s="49"/>
-      <c r="M123" s="143"/>
+      <c r="M123" s="126"/>
       <c r="N123" s="82"/>
     </row>
     <row r="124" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -23425,7 +23425,7 @@
       <c r="J124" s="49"/>
       <c r="K124" s="49"/>
       <c r="L124" s="49"/>
-      <c r="M124" s="143"/>
+      <c r="M124" s="126"/>
       <c r="N124" s="82"/>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.3">
@@ -23451,7 +23451,7 @@
       <c r="J125" s="49"/>
       <c r="K125" s="49"/>
       <c r="L125" s="49"/>
-      <c r="M125" s="143"/>
+      <c r="M125" s="126"/>
       <c r="N125" s="82"/>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.3">
@@ -23477,7 +23477,7 @@
       <c r="J126" s="49"/>
       <c r="K126" s="49"/>
       <c r="L126" s="49"/>
-      <c r="M126" s="143"/>
+      <c r="M126" s="126"/>
       <c r="N126" s="82"/>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.3">
@@ -23503,7 +23503,7 @@
       <c r="J127" s="49"/>
       <c r="K127" s="49"/>
       <c r="L127" s="49"/>
-      <c r="M127" s="143"/>
+      <c r="M127" s="126"/>
       <c r="N127" s="82"/>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.3">
@@ -23529,7 +23529,7 @@
       <c r="J128" s="49"/>
       <c r="K128" s="49"/>
       <c r="L128" s="49"/>
-      <c r="M128" s="143"/>
+      <c r="M128" s="126"/>
       <c r="N128" s="82"/>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.3">
@@ -23555,7 +23555,7 @@
       <c r="J129" s="49"/>
       <c r="K129" s="49"/>
       <c r="L129" s="49"/>
-      <c r="M129" s="143"/>
+      <c r="M129" s="126"/>
       <c r="N129" s="82"/>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.3">
@@ -23581,7 +23581,7 @@
       <c r="J130" s="49"/>
       <c r="K130" s="49"/>
       <c r="L130" s="49"/>
-      <c r="M130" s="143"/>
+      <c r="M130" s="126"/>
       <c r="N130" s="82"/>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.3">
@@ -23607,7 +23607,7 @@
       <c r="J131" s="49"/>
       <c r="K131" s="49"/>
       <c r="L131" s="49"/>
-      <c r="M131" s="143"/>
+      <c r="M131" s="126"/>
       <c r="N131" s="82"/>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.3">
@@ -23633,7 +23633,7 @@
       <c r="J132" s="49"/>
       <c r="K132" s="49"/>
       <c r="L132" s="49"/>
-      <c r="M132" s="143"/>
+      <c r="M132" s="126"/>
       <c r="N132" s="82"/>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.3">
@@ -23659,7 +23659,7 @@
       <c r="J133" s="49"/>
       <c r="K133" s="49"/>
       <c r="L133" s="49"/>
-      <c r="M133" s="143"/>
+      <c r="M133" s="126"/>
       <c r="N133" s="82"/>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.3">
@@ -23685,7 +23685,7 @@
       <c r="J134" s="49"/>
       <c r="K134" s="49"/>
       <c r="L134" s="49"/>
-      <c r="M134" s="143"/>
+      <c r="M134" s="126"/>
       <c r="N134" s="82"/>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.3">
@@ -23711,7 +23711,7 @@
       <c r="J135" s="49"/>
       <c r="K135" s="49"/>
       <c r="L135" s="49"/>
-      <c r="M135" s="143"/>
+      <c r="M135" s="126"/>
       <c r="N135" s="82"/>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.3">
@@ -23737,7 +23737,7 @@
       <c r="J136" s="49"/>
       <c r="K136" s="49"/>
       <c r="L136" s="49"/>
-      <c r="M136" s="143"/>
+      <c r="M136" s="126"/>
       <c r="N136" s="82"/>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.3">
@@ -23763,7 +23763,7 @@
       <c r="J137" s="49"/>
       <c r="K137" s="49"/>
       <c r="L137" s="49"/>
-      <c r="M137" s="143"/>
+      <c r="M137" s="126"/>
       <c r="N137" s="82"/>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.3">
@@ -23789,7 +23789,7 @@
       <c r="J138" s="49"/>
       <c r="K138" s="49"/>
       <c r="L138" s="49"/>
-      <c r="M138" s="143"/>
+      <c r="M138" s="126"/>
       <c r="N138" s="82"/>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.3">
@@ -23815,7 +23815,7 @@
       <c r="J139" s="49"/>
       <c r="K139" s="49"/>
       <c r="L139" s="49"/>
-      <c r="M139" s="143"/>
+      <c r="M139" s="126"/>
       <c r="N139" s="82"/>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.3">
@@ -23841,7 +23841,7 @@
       <c r="J140" s="49"/>
       <c r="K140" s="49"/>
       <c r="L140" s="49"/>
-      <c r="M140" s="143"/>
+      <c r="M140" s="126"/>
       <c r="N140" s="82"/>
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.3">
@@ -23867,7 +23867,7 @@
       <c r="J141" s="49"/>
       <c r="K141" s="49"/>
       <c r="L141" s="49"/>
-      <c r="M141" s="143"/>
+      <c r="M141" s="126"/>
       <c r="N141" s="82"/>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.3">
@@ -23893,7 +23893,7 @@
       <c r="J142" s="49"/>
       <c r="K142" s="49"/>
       <c r="L142" s="49"/>
-      <c r="M142" s="143"/>
+      <c r="M142" s="126"/>
       <c r="N142" s="82"/>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.3">
@@ -23919,7 +23919,7 @@
       <c r="J143" s="49"/>
       <c r="K143" s="49"/>
       <c r="L143" s="49"/>
-      <c r="M143" s="143"/>
+      <c r="M143" s="126"/>
       <c r="N143" s="82"/>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.3">
@@ -23945,7 +23945,7 @@
       <c r="J144" s="49"/>
       <c r="K144" s="49"/>
       <c r="L144" s="49"/>
-      <c r="M144" s="143"/>
+      <c r="M144" s="126"/>
       <c r="N144" s="82"/>
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.3">
@@ -23971,7 +23971,7 @@
       <c r="J145" s="49"/>
       <c r="K145" s="49"/>
       <c r="L145" s="49"/>
-      <c r="M145" s="143"/>
+      <c r="M145" s="126"/>
       <c r="N145" s="82"/>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.3">
@@ -23997,7 +23997,7 @@
       <c r="J146" s="49"/>
       <c r="K146" s="49"/>
       <c r="L146" s="49"/>
-      <c r="M146" s="143"/>
+      <c r="M146" s="126"/>
       <c r="N146" s="82"/>
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.3">
@@ -24023,7 +24023,7 @@
       <c r="J147" s="49"/>
       <c r="K147" s="49"/>
       <c r="L147" s="49"/>
-      <c r="M147" s="143"/>
+      <c r="M147" s="126"/>
       <c r="N147" s="82"/>
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.3">
@@ -24049,7 +24049,7 @@
       <c r="J148" s="49"/>
       <c r="K148" s="49"/>
       <c r="L148" s="49"/>
-      <c r="M148" s="143"/>
+      <c r="M148" s="126"/>
       <c r="N148" s="82"/>
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.3">
@@ -24075,7 +24075,7 @@
       <c r="J149" s="49"/>
       <c r="K149" s="49"/>
       <c r="L149" s="49"/>
-      <c r="M149" s="143"/>
+      <c r="M149" s="126"/>
       <c r="N149" s="82"/>
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.3">
@@ -24101,7 +24101,7 @@
       <c r="J150" s="49"/>
       <c r="K150" s="49"/>
       <c r="L150" s="49"/>
-      <c r="M150" s="143"/>
+      <c r="M150" s="126"/>
       <c r="N150" s="82"/>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.3">
@@ -24127,7 +24127,7 @@
       <c r="J151" s="49"/>
       <c r="K151" s="49"/>
       <c r="L151" s="49"/>
-      <c r="M151" s="143"/>
+      <c r="M151" s="126"/>
       <c r="N151" s="82"/>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.3">
@@ -24153,7 +24153,7 @@
       <c r="J152" s="49"/>
       <c r="K152" s="49"/>
       <c r="L152" s="49"/>
-      <c r="M152" s="143"/>
+      <c r="M152" s="126"/>
       <c r="N152" s="82"/>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.3">
@@ -24179,7 +24179,7 @@
       <c r="J153" s="49"/>
       <c r="K153" s="49"/>
       <c r="L153" s="49"/>
-      <c r="M153" s="143"/>
+      <c r="M153" s="126"/>
       <c r="N153" s="82"/>
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.3">
@@ -24205,7 +24205,7 @@
       <c r="J154" s="49"/>
       <c r="K154" s="49"/>
       <c r="L154" s="49"/>
-      <c r="M154" s="143"/>
+      <c r="M154" s="126"/>
       <c r="N154" s="82"/>
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.3">
@@ -24231,7 +24231,7 @@
       <c r="J155" s="49"/>
       <c r="K155" s="49"/>
       <c r="L155" s="49"/>
-      <c r="M155" s="143"/>
+      <c r="M155" s="126"/>
       <c r="N155" s="82"/>
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.3">
@@ -24257,7 +24257,7 @@
       <c r="J156" s="49"/>
       <c r="K156" s="49"/>
       <c r="L156" s="49"/>
-      <c r="M156" s="143"/>
+      <c r="M156" s="126"/>
       <c r="N156" s="82"/>
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.3">
@@ -24283,7 +24283,7 @@
       <c r="J157" s="49"/>
       <c r="K157" s="49"/>
       <c r="L157" s="49"/>
-      <c r="M157" s="143"/>
+      <c r="M157" s="126"/>
       <c r="N157" s="82"/>
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.3">
@@ -24309,7 +24309,7 @@
       <c r="J158" s="49"/>
       <c r="K158" s="49"/>
       <c r="L158" s="49"/>
-      <c r="M158" s="143"/>
+      <c r="M158" s="126"/>
       <c r="N158" s="82"/>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.3">
@@ -24335,7 +24335,7 @@
       <c r="J159" s="49"/>
       <c r="K159" s="49"/>
       <c r="L159" s="49"/>
-      <c r="M159" s="143"/>
+      <c r="M159" s="126"/>
       <c r="N159" s="82"/>
     </row>
     <row r="160" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -24361,7 +24361,7 @@
       <c r="J160" s="49"/>
       <c r="K160" s="49"/>
       <c r="L160" s="49"/>
-      <c r="M160" s="143"/>
+      <c r="M160" s="126"/>
       <c r="N160" s="82"/>
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.3">
@@ -24387,7 +24387,7 @@
       <c r="J161" s="49"/>
       <c r="K161" s="49"/>
       <c r="L161" s="49"/>
-      <c r="M161" s="143"/>
+      <c r="M161" s="126"/>
       <c r="N161" s="82"/>
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.3">
@@ -24413,7 +24413,7 @@
       <c r="J162" s="49"/>
       <c r="K162" s="49"/>
       <c r="L162" s="49"/>
-      <c r="M162" s="143"/>
+      <c r="M162" s="126"/>
       <c r="N162" s="82"/>
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.3">
@@ -24439,7 +24439,7 @@
       <c r="J163" s="49"/>
       <c r="K163" s="49"/>
       <c r="L163" s="49"/>
-      <c r="M163" s="143"/>
+      <c r="M163" s="126"/>
       <c r="N163" s="82"/>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.3">
@@ -24465,7 +24465,7 @@
       <c r="J164" s="49"/>
       <c r="K164" s="49"/>
       <c r="L164" s="49"/>
-      <c r="M164" s="143"/>
+      <c r="M164" s="126"/>
       <c r="N164" s="82"/>
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.3">
@@ -24491,7 +24491,7 @@
       <c r="J165" s="49"/>
       <c r="K165" s="49"/>
       <c r="L165" s="49"/>
-      <c r="M165" s="143"/>
+      <c r="M165" s="126"/>
       <c r="N165" s="82"/>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.3">
@@ -24517,7 +24517,7 @@
       <c r="J166" s="49"/>
       <c r="K166" s="49"/>
       <c r="L166" s="49"/>
-      <c r="M166" s="143"/>
+      <c r="M166" s="126"/>
       <c r="N166" s="82"/>
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.3">
@@ -24543,7 +24543,7 @@
       <c r="J167" s="49"/>
       <c r="K167" s="49"/>
       <c r="L167" s="49"/>
-      <c r="M167" s="143"/>
+      <c r="M167" s="126"/>
       <c r="N167" s="82"/>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.3">
@@ -24569,7 +24569,7 @@
       <c r="J168" s="49"/>
       <c r="K168" s="49"/>
       <c r="L168" s="49"/>
-      <c r="M168" s="143"/>
+      <c r="M168" s="126"/>
       <c r="N168" s="82"/>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.3">
@@ -24595,7 +24595,7 @@
       <c r="J169" s="49"/>
       <c r="K169" s="49"/>
       <c r="L169" s="49"/>
-      <c r="M169" s="143"/>
+      <c r="M169" s="126"/>
       <c r="N169" s="82"/>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.3">
@@ -24621,7 +24621,7 @@
       <c r="J170" s="49"/>
       <c r="K170" s="49"/>
       <c r="L170" s="49"/>
-      <c r="M170" s="143"/>
+      <c r="M170" s="126"/>
       <c r="N170" s="82"/>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.3">
@@ -24647,7 +24647,7 @@
       <c r="J171" s="49"/>
       <c r="K171" s="49"/>
       <c r="L171" s="49"/>
-      <c r="M171" s="143"/>
+      <c r="M171" s="126"/>
       <c r="N171" s="82"/>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.3">
@@ -24673,7 +24673,7 @@
       <c r="J172" s="49"/>
       <c r="K172" s="49"/>
       <c r="L172" s="49"/>
-      <c r="M172" s="143"/>
+      <c r="M172" s="126"/>
       <c r="N172" s="82"/>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.3">
@@ -24699,7 +24699,7 @@
       <c r="J173" s="49"/>
       <c r="K173" s="49"/>
       <c r="L173" s="49"/>
-      <c r="M173" s="143"/>
+      <c r="M173" s="126"/>
       <c r="N173" s="82"/>
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.3">
@@ -24725,7 +24725,7 @@
       <c r="J174" s="49"/>
       <c r="K174" s="49"/>
       <c r="L174" s="49"/>
-      <c r="M174" s="143"/>
+      <c r="M174" s="126"/>
       <c r="N174" s="82"/>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.3">
@@ -24751,7 +24751,7 @@
       <c r="J175" s="49"/>
       <c r="K175" s="49"/>
       <c r="L175" s="49"/>
-      <c r="M175" s="143"/>
+      <c r="M175" s="126"/>
       <c r="N175" s="82"/>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.3">
@@ -24777,7 +24777,7 @@
       <c r="J176" s="49"/>
       <c r="K176" s="49"/>
       <c r="L176" s="49"/>
-      <c r="M176" s="143"/>
+      <c r="M176" s="126"/>
       <c r="N176" s="82"/>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.3">
@@ -24803,7 +24803,7 @@
       <c r="J177" s="49"/>
       <c r="K177" s="49"/>
       <c r="L177" s="49"/>
-      <c r="M177" s="143"/>
+      <c r="M177" s="126"/>
       <c r="N177" s="82"/>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.3">
@@ -24829,7 +24829,7 @@
       <c r="J178" s="49"/>
       <c r="K178" s="49"/>
       <c r="L178" s="49"/>
-      <c r="M178" s="143"/>
+      <c r="M178" s="126"/>
       <c r="N178" s="82"/>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.3">
@@ -24855,7 +24855,7 @@
       <c r="J179" s="49"/>
       <c r="K179" s="49"/>
       <c r="L179" s="49"/>
-      <c r="M179" s="143"/>
+      <c r="M179" s="126"/>
       <c r="N179" s="82"/>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.3">
@@ -24881,7 +24881,7 @@
       <c r="J180" s="49"/>
       <c r="K180" s="49"/>
       <c r="L180" s="49"/>
-      <c r="M180" s="143"/>
+      <c r="M180" s="126"/>
       <c r="N180" s="82"/>
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.3">
@@ -24907,7 +24907,7 @@
       <c r="J181" s="49"/>
       <c r="K181" s="49"/>
       <c r="L181" s="49"/>
-      <c r="M181" s="143"/>
+      <c r="M181" s="126"/>
       <c r="N181" s="82"/>
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.3">
@@ -24933,7 +24933,7 @@
       <c r="J182" s="49"/>
       <c r="K182" s="49"/>
       <c r="L182" s="49"/>
-      <c r="M182" s="143"/>
+      <c r="M182" s="126"/>
       <c r="N182" s="82"/>
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.3">
@@ -24959,7 +24959,7 @@
       <c r="J183" s="49"/>
       <c r="K183" s="49"/>
       <c r="L183" s="49"/>
-      <c r="M183" s="143"/>
+      <c r="M183" s="126"/>
       <c r="N183" s="82"/>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.3">
@@ -24985,7 +24985,7 @@
       <c r="J184" s="49"/>
       <c r="K184" s="49"/>
       <c r="L184" s="49"/>
-      <c r="M184" s="143"/>
+      <c r="M184" s="126"/>
       <c r="N184" s="82"/>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.3">
@@ -25011,7 +25011,7 @@
       <c r="J185" s="49"/>
       <c r="K185" s="49"/>
       <c r="L185" s="49"/>
-      <c r="M185" s="143"/>
+      <c r="M185" s="126"/>
       <c r="N185" s="82"/>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.3">
@@ -25037,7 +25037,7 @@
       <c r="J186" s="49"/>
       <c r="K186" s="49"/>
       <c r="L186" s="49"/>
-      <c r="M186" s="143"/>
+      <c r="M186" s="126"/>
       <c r="N186" s="82"/>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.3">
@@ -25063,7 +25063,7 @@
       <c r="J187" s="49"/>
       <c r="K187" s="49"/>
       <c r="L187" s="49"/>
-      <c r="M187" s="143"/>
+      <c r="M187" s="126"/>
       <c r="N187" s="82"/>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.3">
@@ -25089,7 +25089,7 @@
       <c r="J188" s="49"/>
       <c r="K188" s="49"/>
       <c r="L188" s="49"/>
-      <c r="M188" s="143"/>
+      <c r="M188" s="126"/>
       <c r="N188" s="82"/>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.3">
@@ -25115,7 +25115,7 @@
       <c r="J189" s="49"/>
       <c r="K189" s="49"/>
       <c r="L189" s="49"/>
-      <c r="M189" s="143"/>
+      <c r="M189" s="126"/>
       <c r="N189" s="82"/>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.3">
@@ -25141,7 +25141,7 @@
       <c r="J190" s="49"/>
       <c r="K190" s="49"/>
       <c r="L190" s="49"/>
-      <c r="M190" s="143"/>
+      <c r="M190" s="126"/>
       <c r="N190" s="82"/>
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.3">
@@ -25167,7 +25167,7 @@
       <c r="J191" s="49"/>
       <c r="K191" s="49"/>
       <c r="L191" s="49"/>
-      <c r="M191" s="143"/>
+      <c r="M191" s="126"/>
       <c r="N191" s="82"/>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.3">
@@ -25193,7 +25193,7 @@
       <c r="J192" s="49"/>
       <c r="K192" s="49"/>
       <c r="L192" s="49"/>
-      <c r="M192" s="143"/>
+      <c r="M192" s="126"/>
       <c r="N192" s="82"/>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.3">
@@ -25219,7 +25219,7 @@
       <c r="J193" s="49"/>
       <c r="K193" s="49"/>
       <c r="L193" s="49"/>
-      <c r="M193" s="143"/>
+      <c r="M193" s="126"/>
       <c r="N193" s="82"/>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.3">
@@ -25245,7 +25245,7 @@
       <c r="J194" s="49"/>
       <c r="K194" s="49"/>
       <c r="L194" s="49"/>
-      <c r="M194" s="143"/>
+      <c r="M194" s="126"/>
       <c r="N194" s="82"/>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.3">
@@ -25271,7 +25271,7 @@
       <c r="J195" s="49"/>
       <c r="K195" s="49"/>
       <c r="L195" s="49"/>
-      <c r="M195" s="143"/>
+      <c r="M195" s="126"/>
       <c r="N195" s="82"/>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.3">
@@ -25297,7 +25297,7 @@
       <c r="J196" s="49"/>
       <c r="K196" s="49"/>
       <c r="L196" s="49"/>
-      <c r="M196" s="143"/>
+      <c r="M196" s="126"/>
       <c r="N196" s="82"/>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.3">
@@ -25323,7 +25323,7 @@
       <c r="J197" s="49"/>
       <c r="K197" s="49"/>
       <c r="L197" s="49"/>
-      <c r="M197" s="143"/>
+      <c r="M197" s="126"/>
       <c r="N197" s="82"/>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.3">
@@ -25349,7 +25349,7 @@
       <c r="J198" s="49"/>
       <c r="K198" s="49"/>
       <c r="L198" s="49"/>
-      <c r="M198" s="143"/>
+      <c r="M198" s="126"/>
       <c r="N198" s="82"/>
     </row>
     <row r="199" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -25375,7 +25375,7 @@
       <c r="J199" s="49"/>
       <c r="K199" s="49"/>
       <c r="L199" s="49"/>
-      <c r="M199" s="143"/>
+      <c r="M199" s="126"/>
       <c r="N199" s="82"/>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.3">
@@ -25401,7 +25401,7 @@
       <c r="J200" s="49"/>
       <c r="K200" s="49"/>
       <c r="L200" s="49"/>
-      <c r="M200" s="143"/>
+      <c r="M200" s="126"/>
       <c r="N200" s="82"/>
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.3">
@@ -25427,7 +25427,7 @@
       <c r="J201" s="49"/>
       <c r="K201" s="49"/>
       <c r="L201" s="49"/>
-      <c r="M201" s="143"/>
+      <c r="M201" s="126"/>
       <c r="N201" s="82"/>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.3">
@@ -25453,7 +25453,7 @@
       <c r="J202" s="49"/>
       <c r="K202" s="49"/>
       <c r="L202" s="49"/>
-      <c r="M202" s="143"/>
+      <c r="M202" s="126"/>
       <c r="N202" s="82"/>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.3">
@@ -25479,7 +25479,7 @@
       <c r="J203" s="49"/>
       <c r="K203" s="49"/>
       <c r="L203" s="49"/>
-      <c r="M203" s="143"/>
+      <c r="M203" s="126"/>
       <c r="N203" s="82"/>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.3">
@@ -25505,7 +25505,7 @@
       <c r="J204" s="49"/>
       <c r="K204" s="49"/>
       <c r="L204" s="49"/>
-      <c r="M204" s="143"/>
+      <c r="M204" s="126"/>
       <c r="N204" s="82"/>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.3">
@@ -25531,7 +25531,7 @@
       <c r="J205" s="49"/>
       <c r="K205" s="49"/>
       <c r="L205" s="49"/>
-      <c r="M205" s="143"/>
+      <c r="M205" s="126"/>
       <c r="N205" s="82"/>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.3">
@@ -25557,7 +25557,7 @@
       <c r="J206" s="49"/>
       <c r="K206" s="49"/>
       <c r="L206" s="49"/>
-      <c r="M206" s="143"/>
+      <c r="M206" s="126"/>
       <c r="N206" s="82"/>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.3">
@@ -25583,7 +25583,7 @@
       <c r="J207" s="49"/>
       <c r="K207" s="49"/>
       <c r="L207" s="49"/>
-      <c r="M207" s="143"/>
+      <c r="M207" s="126"/>
       <c r="N207" s="82"/>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.3">
@@ -25609,7 +25609,7 @@
       <c r="J208" s="49"/>
       <c r="K208" s="49"/>
       <c r="L208" s="49"/>
-      <c r="M208" s="143"/>
+      <c r="M208" s="126"/>
       <c r="N208" s="82"/>
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.3">
@@ -25635,7 +25635,7 @@
       <c r="J209" s="49"/>
       <c r="K209" s="49"/>
       <c r="L209" s="49"/>
-      <c r="M209" s="143"/>
+      <c r="M209" s="126"/>
       <c r="N209" s="82"/>
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.3">
@@ -25661,7 +25661,7 @@
       <c r="J210" s="49"/>
       <c r="K210" s="49"/>
       <c r="L210" s="49"/>
-      <c r="M210" s="143"/>
+      <c r="M210" s="126"/>
       <c r="N210" s="82"/>
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.3">
@@ -25687,7 +25687,7 @@
       <c r="J211" s="49"/>
       <c r="K211" s="49"/>
       <c r="L211" s="49"/>
-      <c r="M211" s="143"/>
+      <c r="M211" s="126"/>
       <c r="N211" s="82"/>
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.3">
@@ -25713,7 +25713,7 @@
       <c r="J212" s="49"/>
       <c r="K212" s="49"/>
       <c r="L212" s="49"/>
-      <c r="M212" s="143"/>
+      <c r="M212" s="126"/>
       <c r="N212" s="82"/>
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.3">
@@ -25739,7 +25739,7 @@
       <c r="J213" s="49"/>
       <c r="K213" s="49"/>
       <c r="L213" s="49"/>
-      <c r="M213" s="143"/>
+      <c r="M213" s="126"/>
       <c r="N213" s="82"/>
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.3">
@@ -25765,7 +25765,7 @@
       <c r="J214" s="49"/>
       <c r="K214" s="49"/>
       <c r="L214" s="49"/>
-      <c r="M214" s="143"/>
+      <c r="M214" s="126"/>
       <c r="N214" s="82"/>
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.3">
@@ -25791,7 +25791,7 @@
       <c r="J215" s="49"/>
       <c r="K215" s="49"/>
       <c r="L215" s="49"/>
-      <c r="M215" s="143"/>
+      <c r="M215" s="126"/>
       <c r="N215" s="82"/>
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.3">
@@ -25817,7 +25817,7 @@
       <c r="J216" s="49"/>
       <c r="K216" s="49"/>
       <c r="L216" s="49"/>
-      <c r="M216" s="143"/>
+      <c r="M216" s="126"/>
       <c r="N216" s="82"/>
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.3">
@@ -25843,7 +25843,7 @@
       <c r="J217" s="49"/>
       <c r="K217" s="49"/>
       <c r="L217" s="49"/>
-      <c r="M217" s="143"/>
+      <c r="M217" s="126"/>
       <c r="N217" s="82"/>
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.3">
@@ -25869,7 +25869,7 @@
       <c r="J218" s="49"/>
       <c r="K218" s="49"/>
       <c r="L218" s="49"/>
-      <c r="M218" s="143"/>
+      <c r="M218" s="126"/>
       <c r="N218" s="82"/>
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.3">
@@ -25895,7 +25895,7 @@
       <c r="J219" s="49"/>
       <c r="K219" s="49"/>
       <c r="L219" s="49"/>
-      <c r="M219" s="143"/>
+      <c r="M219" s="126"/>
       <c r="N219" s="82"/>
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.3">
@@ -25921,7 +25921,7 @@
       <c r="J220" s="49"/>
       <c r="K220" s="49"/>
       <c r="L220" s="49"/>
-      <c r="M220" s="143"/>
+      <c r="M220" s="126"/>
       <c r="N220" s="82"/>
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.3">
@@ -25947,7 +25947,7 @@
       <c r="J221" s="49"/>
       <c r="K221" s="49"/>
       <c r="L221" s="49"/>
-      <c r="M221" s="143"/>
+      <c r="M221" s="126"/>
       <c r="N221" s="82"/>
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.3">
@@ -25973,7 +25973,7 @@
       <c r="J222" s="49"/>
       <c r="K222" s="49"/>
       <c r="L222" s="49"/>
-      <c r="M222" s="143"/>
+      <c r="M222" s="126"/>
       <c r="N222" s="82"/>
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.3">
@@ -25999,7 +25999,7 @@
       <c r="J223" s="49"/>
       <c r="K223" s="49"/>
       <c r="L223" s="49"/>
-      <c r="M223" s="143"/>
+      <c r="M223" s="126"/>
       <c r="N223" s="82"/>
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.3">
@@ -26025,7 +26025,7 @@
       <c r="J224" s="49"/>
       <c r="K224" s="49"/>
       <c r="L224" s="49"/>
-      <c r="M224" s="143"/>
+      <c r="M224" s="126"/>
       <c r="N224" s="82"/>
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.3">
@@ -26051,7 +26051,7 @@
       <c r="J225" s="49"/>
       <c r="K225" s="49"/>
       <c r="L225" s="49"/>
-      <c r="M225" s="143"/>
+      <c r="M225" s="126"/>
       <c r="N225" s="82"/>
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.3">
@@ -26077,7 +26077,7 @@
       <c r="J226" s="49"/>
       <c r="K226" s="49"/>
       <c r="L226" s="49"/>
-      <c r="M226" s="143"/>
+      <c r="M226" s="126"/>
       <c r="N226" s="82"/>
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.3">
@@ -26103,7 +26103,7 @@
       <c r="J227" s="49"/>
       <c r="K227" s="49"/>
       <c r="L227" s="49"/>
-      <c r="M227" s="143"/>
+      <c r="M227" s="126"/>
       <c r="N227" s="82"/>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.3">
@@ -26129,7 +26129,7 @@
       <c r="J228" s="49"/>
       <c r="K228" s="49"/>
       <c r="L228" s="49"/>
-      <c r="M228" s="143"/>
+      <c r="M228" s="126"/>
       <c r="N228" s="82"/>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.3">
@@ -26155,7 +26155,7 @@
       <c r="J229" s="49"/>
       <c r="K229" s="49"/>
       <c r="L229" s="49"/>
-      <c r="M229" s="143"/>
+      <c r="M229" s="126"/>
       <c r="N229" s="82"/>
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.3">
@@ -26181,7 +26181,7 @@
       <c r="J230" s="49"/>
       <c r="K230" s="49"/>
       <c r="L230" s="49"/>
-      <c r="M230" s="143"/>
+      <c r="M230" s="126"/>
       <c r="N230" s="82"/>
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.3">
@@ -26207,7 +26207,7 @@
       <c r="J231" s="49"/>
       <c r="K231" s="49"/>
       <c r="L231" s="49"/>
-      <c r="M231" s="143"/>
+      <c r="M231" s="126"/>
       <c r="N231" s="82"/>
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.3">
@@ -26233,7 +26233,7 @@
       <c r="J232" s="49"/>
       <c r="K232" s="49"/>
       <c r="L232" s="49"/>
-      <c r="M232" s="143"/>
+      <c r="M232" s="126"/>
       <c r="N232" s="82"/>
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.3">
@@ -26259,7 +26259,7 @@
       <c r="J233" s="49"/>
       <c r="K233" s="49"/>
       <c r="L233" s="49"/>
-      <c r="M233" s="143"/>
+      <c r="M233" s="126"/>
       <c r="N233" s="82"/>
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.3">
@@ -26285,7 +26285,7 @@
       <c r="J234" s="49"/>
       <c r="K234" s="49"/>
       <c r="L234" s="49"/>
-      <c r="M234" s="143"/>
+      <c r="M234" s="126"/>
       <c r="N234" s="82"/>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.3">
@@ -26311,7 +26311,7 @@
       <c r="J235" s="49"/>
       <c r="K235" s="49"/>
       <c r="L235" s="49"/>
-      <c r="M235" s="143"/>
+      <c r="M235" s="126"/>
       <c r="N235" s="82"/>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.3">
@@ -26337,7 +26337,7 @@
       <c r="J236" s="49"/>
       <c r="K236" s="49"/>
       <c r="L236" s="49"/>
-      <c r="M236" s="143"/>
+      <c r="M236" s="126"/>
       <c r="N236" s="82"/>
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.3">
@@ -26363,7 +26363,7 @@
       <c r="J237" s="49"/>
       <c r="K237" s="49"/>
       <c r="L237" s="49"/>
-      <c r="M237" s="143"/>
+      <c r="M237" s="126"/>
       <c r="N237" s="82"/>
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.3">
@@ -26389,7 +26389,7 @@
       <c r="J238" s="49"/>
       <c r="K238" s="49"/>
       <c r="L238" s="49"/>
-      <c r="M238" s="143"/>
+      <c r="M238" s="126"/>
       <c r="N238" s="82"/>
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.3">
@@ -26415,7 +26415,7 @@
       <c r="J239" s="49"/>
       <c r="K239" s="49"/>
       <c r="L239" s="49"/>
-      <c r="M239" s="143"/>
+      <c r="M239" s="126"/>
       <c r="N239" s="82"/>
     </row>
     <row r="240" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -26441,7 +26441,7 @@
       <c r="J240" s="49"/>
       <c r="K240" s="49"/>
       <c r="L240" s="49"/>
-      <c r="M240" s="144"/>
+      <c r="M240" s="127"/>
       <c r="N240" s="82"/>
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.3">
@@ -26471,7 +26471,7 @@
       <c r="L241" s="48" t="s">
         <v>1347</v>
       </c>
-      <c r="M241" s="145" t="s">
+      <c r="M241" s="128" t="s">
         <v>1411</v>
       </c>
       <c r="N241" s="80"/>
@@ -26503,7 +26503,7 @@
       <c r="L242" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M242" s="146"/>
+      <c r="M242" s="129"/>
       <c r="N242" s="80"/>
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.3">
@@ -26533,7 +26533,7 @@
       <c r="L243" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M243" s="146"/>
+      <c r="M243" s="129"/>
       <c r="N243" s="80"/>
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.3">
@@ -26563,7 +26563,7 @@
       <c r="L244" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M244" s="146"/>
+      <c r="M244" s="129"/>
       <c r="N244" s="80"/>
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.3">
@@ -26593,7 +26593,7 @@
       <c r="L245" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M245" s="146"/>
+      <c r="M245" s="129"/>
       <c r="N245" s="80"/>
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.3">
@@ -26623,7 +26623,7 @@
       <c r="L246" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M246" s="146"/>
+      <c r="M246" s="129"/>
       <c r="N246" s="80"/>
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.3">
@@ -26653,7 +26653,7 @@
       <c r="L247" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M247" s="146"/>
+      <c r="M247" s="129"/>
       <c r="N247" s="80"/>
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.3">
@@ -26683,7 +26683,7 @@
       <c r="L248" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M248" s="146"/>
+      <c r="M248" s="129"/>
       <c r="N248" s="80"/>
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.3">
@@ -26713,7 +26713,7 @@
       <c r="L249" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M249" s="146"/>
+      <c r="M249" s="129"/>
       <c r="N249" s="80"/>
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.3">
@@ -26743,7 +26743,7 @@
       <c r="L250" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M250" s="146"/>
+      <c r="M250" s="129"/>
       <c r="N250" s="80"/>
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.3">
@@ -26773,7 +26773,7 @@
       <c r="L251" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M251" s="146"/>
+      <c r="M251" s="129"/>
       <c r="N251" s="80"/>
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.3">
@@ -26803,7 +26803,7 @@
       <c r="L252" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M252" s="146"/>
+      <c r="M252" s="129"/>
       <c r="N252" s="80"/>
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.3">
@@ -26833,7 +26833,7 @@
       <c r="L253" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M253" s="146"/>
+      <c r="M253" s="129"/>
       <c r="N253" s="80"/>
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.3">
@@ -26863,7 +26863,7 @@
       <c r="L254" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M254" s="146"/>
+      <c r="M254" s="129"/>
       <c r="N254" s="80"/>
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.3">
@@ -26893,7 +26893,7 @@
       <c r="L255" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M255" s="146"/>
+      <c r="M255" s="129"/>
       <c r="N255" s="80"/>
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.3">
@@ -26923,7 +26923,7 @@
       <c r="L256" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M256" s="146"/>
+      <c r="M256" s="129"/>
       <c r="N256" s="80"/>
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.3">
@@ -26953,7 +26953,7 @@
       <c r="L257" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M257" s="146"/>
+      <c r="M257" s="129"/>
       <c r="N257" s="80"/>
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.3">
@@ -26983,7 +26983,7 @@
       <c r="L258" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M258" s="146"/>
+      <c r="M258" s="129"/>
       <c r="N258" s="80"/>
     </row>
     <row r="259" spans="1:14" x14ac:dyDescent="0.3">
@@ -27013,7 +27013,7 @@
       <c r="L259" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M259" s="146"/>
+      <c r="M259" s="129"/>
       <c r="N259" s="80"/>
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.3">
@@ -27043,7 +27043,7 @@
       <c r="L260" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M260" s="146"/>
+      <c r="M260" s="129"/>
       <c r="N260" s="80"/>
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.3">
@@ -27073,7 +27073,7 @@
       <c r="L261" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M261" s="146"/>
+      <c r="M261" s="129"/>
       <c r="N261" s="80"/>
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.3">
@@ -27103,7 +27103,7 @@
       <c r="L262" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M262" s="146"/>
+      <c r="M262" s="129"/>
       <c r="N262" s="80"/>
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.3">
@@ -27133,7 +27133,7 @@
       <c r="L263" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M263" s="146"/>
+      <c r="M263" s="129"/>
       <c r="N263" s="80"/>
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.3">
@@ -27163,7 +27163,7 @@
       <c r="L264" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M264" s="146"/>
+      <c r="M264" s="129"/>
       <c r="N264" s="80"/>
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.3">
@@ -27193,7 +27193,7 @@
       <c r="L265" s="23" t="s">
         <v>1347</v>
       </c>
-      <c r="M265" s="146"/>
+      <c r="M265" s="129"/>
       <c r="N265" s="80"/>
     </row>
     <row r="266" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -27223,7 +27223,7 @@
       <c r="L266" s="24" t="s">
         <v>1347</v>
       </c>
-      <c r="M266" s="147"/>
+      <c r="M266" s="130"/>
       <c r="N266" s="80"/>
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.3">
@@ -27253,7 +27253,7 @@
       <c r="L267" s="48" t="s">
         <v>1367</v>
       </c>
-      <c r="M267" s="148" t="s">
+      <c r="M267" s="131" t="s">
         <v>1413</v>
       </c>
       <c r="N267" s="80"/>
@@ -27281,7 +27281,7 @@
       <c r="L268" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M268" s="149"/>
+      <c r="M268" s="132"/>
       <c r="N268" s="80"/>
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.3">
@@ -27311,7 +27311,7 @@
       <c r="L269" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M269" s="149"/>
+      <c r="M269" s="132"/>
       <c r="N269" s="80"/>
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.3">
@@ -27341,7 +27341,7 @@
       <c r="L270" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M270" s="149"/>
+      <c r="M270" s="132"/>
       <c r="N270" s="80"/>
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.3">
@@ -27371,7 +27371,7 @@
       <c r="L271" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M271" s="149"/>
+      <c r="M271" s="132"/>
       <c r="N271" s="80"/>
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.3">
@@ -27401,7 +27401,7 @@
       <c r="L272" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M272" s="149"/>
+      <c r="M272" s="132"/>
       <c r="N272" s="80"/>
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.3">
@@ -27431,7 +27431,7 @@
       <c r="L273" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M273" s="149"/>
+      <c r="M273" s="132"/>
       <c r="N273" s="80"/>
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.3">
@@ -27461,7 +27461,7 @@
       <c r="L274" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M274" s="149"/>
+      <c r="M274" s="132"/>
       <c r="N274" s="80"/>
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.3">
@@ -27491,7 +27491,7 @@
       <c r="L275" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M275" s="149"/>
+      <c r="M275" s="132"/>
       <c r="N275" s="80"/>
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.3">
@@ -27521,7 +27521,7 @@
       <c r="L276" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M276" s="149"/>
+      <c r="M276" s="132"/>
       <c r="N276" s="80"/>
     </row>
     <row r="277" spans="1:14" x14ac:dyDescent="0.3">
@@ -27551,7 +27551,7 @@
       <c r="L277" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M277" s="149"/>
+      <c r="M277" s="132"/>
       <c r="N277" s="80"/>
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.3">
@@ -27581,7 +27581,7 @@
       <c r="L278" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M278" s="149"/>
+      <c r="M278" s="132"/>
       <c r="N278" s="80"/>
     </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.3">
@@ -27611,7 +27611,7 @@
       <c r="L279" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M279" s="149"/>
+      <c r="M279" s="132"/>
       <c r="N279" s="80"/>
     </row>
     <row r="280" spans="1:14" x14ac:dyDescent="0.3">
@@ -27641,7 +27641,7 @@
       <c r="L280" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M280" s="149"/>
+      <c r="M280" s="132"/>
       <c r="N280" s="80"/>
     </row>
     <row r="281" spans="1:14" x14ac:dyDescent="0.3">
@@ -27671,7 +27671,7 @@
       <c r="L281" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M281" s="149"/>
+      <c r="M281" s="132"/>
       <c r="N281" s="80"/>
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.3">
@@ -27701,7 +27701,7 @@
       <c r="L282" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M282" s="149"/>
+      <c r="M282" s="132"/>
       <c r="N282" s="80"/>
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.3">
@@ -27731,7 +27731,7 @@
       <c r="L283" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M283" s="149"/>
+      <c r="M283" s="132"/>
       <c r="N283" s="80"/>
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.3">
@@ -27761,7 +27761,7 @@
       <c r="L284" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M284" s="149"/>
+      <c r="M284" s="132"/>
       <c r="N284" s="80"/>
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.3">
@@ -27791,7 +27791,7 @@
       <c r="L285" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M285" s="149"/>
+      <c r="M285" s="132"/>
       <c r="N285" s="80"/>
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.3">
@@ -27821,7 +27821,7 @@
       <c r="L286" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M286" s="149"/>
+      <c r="M286" s="132"/>
       <c r="N286" s="80"/>
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.3">
@@ -27851,7 +27851,7 @@
       <c r="L287" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M287" s="149"/>
+      <c r="M287" s="132"/>
       <c r="N287" s="80"/>
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.3">
@@ -27881,7 +27881,7 @@
       <c r="L288" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M288" s="149"/>
+      <c r="M288" s="132"/>
       <c r="N288" s="80"/>
     </row>
     <row r="289" spans="1:14" x14ac:dyDescent="0.3">
@@ -27911,7 +27911,7 @@
       <c r="L289" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M289" s="149"/>
+      <c r="M289" s="132"/>
       <c r="N289" s="80"/>
     </row>
     <row r="290" spans="1:14" x14ac:dyDescent="0.3">
@@ -27941,7 +27941,7 @@
       <c r="L290" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M290" s="149"/>
+      <c r="M290" s="132"/>
       <c r="N290" s="80"/>
     </row>
     <row r="291" spans="1:14" x14ac:dyDescent="0.3">
@@ -27971,7 +27971,7 @@
       <c r="L291" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M291" s="149"/>
+      <c r="M291" s="132"/>
       <c r="N291" s="80"/>
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.3">
@@ -28001,7 +28001,7 @@
       <c r="L292" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M292" s="149"/>
+      <c r="M292" s="132"/>
       <c r="N292" s="80"/>
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.3">
@@ -28031,7 +28031,7 @@
       <c r="L293" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M293" s="149"/>
+      <c r="M293" s="132"/>
       <c r="N293" s="80"/>
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.3">
@@ -28061,7 +28061,7 @@
       <c r="L294" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M294" s="149"/>
+      <c r="M294" s="132"/>
       <c r="N294" s="80"/>
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.3">
@@ -28091,7 +28091,7 @@
       <c r="L295" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M295" s="149"/>
+      <c r="M295" s="132"/>
       <c r="N295" s="80"/>
     </row>
     <row r="296" spans="1:14" x14ac:dyDescent="0.3">
@@ -28121,7 +28121,7 @@
       <c r="L296" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M296" s="149"/>
+      <c r="M296" s="132"/>
       <c r="N296" s="80"/>
     </row>
     <row r="297" spans="1:14" x14ac:dyDescent="0.3">
@@ -28151,7 +28151,7 @@
       <c r="L297" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M297" s="149"/>
+      <c r="M297" s="132"/>
       <c r="N297" s="80"/>
     </row>
     <row r="298" spans="1:14" x14ac:dyDescent="0.3">
@@ -28181,7 +28181,7 @@
       <c r="L298" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M298" s="149"/>
+      <c r="M298" s="132"/>
       <c r="N298" s="80"/>
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.3">
@@ -28211,7 +28211,7 @@
       <c r="L299" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M299" s="149"/>
+      <c r="M299" s="132"/>
       <c r="N299" s="80"/>
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.3">
@@ -28241,7 +28241,7 @@
       <c r="L300" s="43" t="s">
         <v>1367</v>
       </c>
-      <c r="M300" s="149"/>
+      <c r="M300" s="132"/>
       <c r="N300" s="80"/>
     </row>
     <row r="301" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -28271,7 +28271,7 @@
       <c r="L301" s="53" t="s">
         <v>1367</v>
       </c>
-      <c r="M301" s="150"/>
+      <c r="M301" s="133"/>
       <c r="N301" s="80"/>
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.3">
@@ -28301,7 +28301,7 @@
       <c r="L302" s="48" t="s">
         <v>1381</v>
       </c>
-      <c r="M302" s="148" t="s">
+      <c r="M302" s="131" t="s">
         <v>1383</v>
       </c>
       <c r="N302" s="80"/>
@@ -28333,7 +28333,7 @@
       <c r="L303" s="43" t="s">
         <v>1381</v>
       </c>
-      <c r="M303" s="149"/>
+      <c r="M303" s="132"/>
       <c r="N303" s="80"/>
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.3">
@@ -28363,7 +28363,7 @@
       <c r="L304" s="43" t="s">
         <v>1381</v>
       </c>
-      <c r="M304" s="149"/>
+      <c r="M304" s="132"/>
       <c r="N304" s="80"/>
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.3">
@@ -28393,7 +28393,7 @@
       <c r="L305" s="43" t="s">
         <v>1381</v>
       </c>
-      <c r="M305" s="149"/>
+      <c r="M305" s="132"/>
       <c r="N305" s="80"/>
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.3">
@@ -28423,7 +28423,7 @@
       <c r="L306" s="43" t="s">
         <v>1381</v>
       </c>
-      <c r="M306" s="149"/>
+      <c r="M306" s="132"/>
       <c r="N306" s="80"/>
     </row>
     <row r="307" spans="1:14" x14ac:dyDescent="0.3">
@@ -28453,7 +28453,7 @@
       <c r="L307" s="43" t="s">
         <v>1381</v>
       </c>
-      <c r="M307" s="149"/>
+      <c r="M307" s="132"/>
       <c r="N307" s="80"/>
     </row>
     <row r="308" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -28483,7 +28483,7 @@
       <c r="L308" s="53" t="s">
         <v>1381</v>
       </c>
-      <c r="M308" s="150"/>
+      <c r="M308" s="133"/>
       <c r="N308" s="80"/>
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.3">
@@ -28513,7 +28513,7 @@
       <c r="L309" s="48" t="s">
         <v>1384</v>
       </c>
-      <c r="M309" s="148" t="s">
+      <c r="M309" s="131" t="s">
         <v>1391</v>
       </c>
       <c r="N309" s="80"/>
@@ -28545,7 +28545,7 @@
       <c r="L310" s="43" t="s">
         <v>1384</v>
       </c>
-      <c r="M310" s="149"/>
+      <c r="M310" s="132"/>
       <c r="N310" s="80"/>
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.3">
@@ -28575,7 +28575,7 @@
       <c r="L311" s="43" t="s">
         <v>1384</v>
       </c>
-      <c r="M311" s="149"/>
+      <c r="M311" s="132"/>
       <c r="N311" s="80"/>
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.3">
@@ -28605,7 +28605,7 @@
       <c r="L312" s="43" t="s">
         <v>1384</v>
       </c>
-      <c r="M312" s="149"/>
+      <c r="M312" s="132"/>
       <c r="N312" s="80"/>
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.3">
@@ -28635,7 +28635,7 @@
       <c r="L313" s="43" t="s">
         <v>1384</v>
       </c>
-      <c r="M313" s="149"/>
+      <c r="M313" s="132"/>
       <c r="N313" s="80"/>
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.3">
@@ -28665,7 +28665,7 @@
       <c r="L314" s="43" t="s">
         <v>1384</v>
       </c>
-      <c r="M314" s="149"/>
+      <c r="M314" s="132"/>
       <c r="N314" s="80"/>
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.3">
@@ -28695,7 +28695,7 @@
       <c r="L315" s="43" t="s">
         <v>1384</v>
       </c>
-      <c r="M315" s="149"/>
+      <c r="M315" s="132"/>
       <c r="N315" s="80"/>
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.3">
@@ -28725,7 +28725,7 @@
       <c r="L316" s="43" t="s">
         <v>1384</v>
       </c>
-      <c r="M316" s="149"/>
+      <c r="M316" s="132"/>
       <c r="N316" s="80"/>
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.3">
@@ -28755,7 +28755,7 @@
       <c r="L317" s="43" t="s">
         <v>1384</v>
       </c>
-      <c r="M317" s="149"/>
+      <c r="M317" s="132"/>
       <c r="N317" s="80"/>
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.3">
@@ -28785,7 +28785,7 @@
       <c r="L318" s="43" t="s">
         <v>1384</v>
       </c>
-      <c r="M318" s="149"/>
+      <c r="M318" s="132"/>
       <c r="N318" s="80"/>
     </row>
     <row r="319" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -28815,16 +28815,11 @@
       <c r="L319" s="53" t="s">
         <v>1384</v>
       </c>
-      <c r="M319" s="150"/>
+      <c r="M319" s="133"/>
       <c r="N319" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="M29:M240"/>
-    <mergeCell ref="M241:M266"/>
-    <mergeCell ref="M267:M301"/>
-    <mergeCell ref="M302:M308"/>
-    <mergeCell ref="M309:M319"/>
     <mergeCell ref="Y1:AC1"/>
     <mergeCell ref="Z2:AC2"/>
     <mergeCell ref="M10:M15"/>
@@ -28833,6 +28828,11 @@
     <mergeCell ref="M16:M21"/>
     <mergeCell ref="M2:M9"/>
     <mergeCell ref="T2:W2"/>
+    <mergeCell ref="M29:M240"/>
+    <mergeCell ref="M241:M266"/>
+    <mergeCell ref="M267:M301"/>
+    <mergeCell ref="M302:M308"/>
+    <mergeCell ref="M309:M319"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
